--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -4056,7 +4056,11 @@
         </is>
       </c>
       <c r="B215" t="inlineStr"/>
-      <c r="C215" t="inlineStr"/>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>PN Toll Freight</t>
+        </is>
+      </c>
       <c r="D215" t="inlineStr">
         <is>
           <t>2026-04-05 15:26:42</t>
@@ -7399,7 +7403,11 @@
         </is>
       </c>
       <c r="B424" t="inlineStr"/>
-      <c r="C424" t="inlineStr"/>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Aurizon Empty Grain</t>
+        </is>
+      </c>
       <c r="D424" t="inlineStr">
         <is>
           <t>2026-04-05 01:09:16</t>
@@ -7577,7 +7585,11 @@
         </is>
       </c>
       <c r="B435" t="inlineStr"/>
-      <c r="C435" t="inlineStr"/>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Hunter Line Service</t>
+        </is>
+      </c>
       <c r="D435" t="inlineStr">
         <is>
           <t>2026-04-03 15:09:22</t>
@@ -22586,7 +22598,11 @@
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PN Toll Freight</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>2026-04-05 15:26:42</t>
@@ -24916,7 +24932,11 @@
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
-      <c r="C135" t="inlineStr"/>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Aurizon Empty Grain</t>
+        </is>
+      </c>
       <c r="D135" t="inlineStr">
         <is>
           <t>2026-04-05 01:09:16</t>
@@ -33245,7 +33265,11 @@
         </is>
       </c>
       <c r="B617" t="inlineStr"/>
-      <c r="C617" t="inlineStr"/>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Hunter Line Service</t>
+        </is>
+      </c>
       <c r="D617" t="inlineStr">
         <is>
           <t>2026-04-03 15:09:22</t>

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -5998,7 +5998,7 @@
       <c r="B315" t="inlineStr"/>
       <c r="C315" t="inlineStr">
         <is>
-          <t>PN Local Shunter</t>
+          <t>PN Grain Shuttle</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -11755,7 +11755,7 @@
       <c r="B652" t="inlineStr"/>
       <c r="C652" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Hunter Railcar Transfer</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
@@ -18819,7 +18819,7 @@
       <c r="B1048" t="inlineStr"/>
       <c r="C1048" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1048" t="inlineStr">
@@ -19107,7 +19107,7 @@
       <c r="B1064" t="inlineStr"/>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1064" t="inlineStr">
@@ -37916,7 +37916,7 @@
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PN Local Shunter</t>
+          <t>PN Grain Shuttle</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -51238,7 +51238,7 @@
       <c r="B841" t="inlineStr"/>
       <c r="C841" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Hunter Railcar Transfer</t>
         </is>
       </c>
       <c r="D841" t="inlineStr">
@@ -51670,7 +51670,7 @@
       <c r="B865" t="inlineStr"/>
       <c r="C865" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
@@ -63211,7 +63211,7 @@
       <c r="B1512" t="inlineStr"/>
       <c r="C1512" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1512" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -11441,7 +11441,11 @@
         </is>
       </c>
       <c r="B634" t="inlineStr"/>
-      <c r="C634" t="inlineStr"/>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>ORA Coal</t>
+        </is>
+      </c>
       <c r="D634" t="inlineStr">
         <is>
           <t>2026-04-14 15:50:41</t>
@@ -11579,7 +11583,7 @@
       <c r="B642" t="inlineStr"/>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Aurizon Wagon Transfer</t>
+          <t>Aurizon Empty Ore</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
@@ -14307,7 +14311,7 @@
       <c r="B796" t="inlineStr"/>
       <c r="C796" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D796" t="inlineStr">
@@ -14375,7 +14379,7 @@
       <c r="B800" t="inlineStr"/>
       <c r="C800" t="inlineStr">
         <is>
-          <t>South Coast Service</t>
+          <t>South Coast Empty Car Transfer</t>
         </is>
       </c>
       <c r="D800" t="inlineStr">
@@ -22205,7 +22209,7 @@
       <c r="B1237" t="inlineStr"/>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SSR BG Grain</t>
         </is>
       </c>
       <c r="D1237" t="inlineStr">
@@ -24537,7 +24541,7 @@
       <c r="B1373" t="inlineStr"/>
       <c r="C1373" t="inlineStr">
         <is>
-          <t>Watco Trip Train</t>
+          <t>Watco Light Engine Movement</t>
         </is>
       </c>
       <c r="D1373" t="inlineStr">
@@ -27459,7 +27463,7 @@
       <c r="B1544" t="inlineStr"/>
       <c r="C1544" t="inlineStr">
         <is>
-          <t>PN Coal</t>
+          <t>PN Light Engine Movement</t>
         </is>
       </c>
       <c r="D1544" t="inlineStr">
@@ -36448,7 +36452,11 @@
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ORA Coal</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>2026-04-14 15:50:41</t>
@@ -36532,7 +36540,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Watco Trip Train</t>
+          <t>Watco Light Engine Movement</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -39456,7 +39464,7 @@
       <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr">
         <is>
-          <t>PN Coal</t>
+          <t>PN Light Engine Movement</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -43676,7 +43684,7 @@
       <c r="B415" t="inlineStr"/>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -50666,7 +50674,7 @@
       <c r="B808" t="inlineStr"/>
       <c r="C808" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SSR BG Grain</t>
         </is>
       </c>
       <c r="D808" t="inlineStr">
@@ -51320,7 +51328,7 @@
       <c r="B845" t="inlineStr"/>
       <c r="C845" t="inlineStr">
         <is>
-          <t>Aurizon Wagon Transfer</t>
+          <t>Aurizon Empty Ore</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
@@ -67567,7 +67575,7 @@
       <c r="B1761" t="inlineStr"/>
       <c r="C1761" t="inlineStr">
         <is>
-          <t>South Coast Service</t>
+          <t>South Coast Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1761" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -3066,7 +3066,7 @@
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>QUBE Trip Train</t>
+          <t>QUBE Containerised Freight</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -3586,7 +3586,7 @@
       <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr">
         <is>
-          <t>SSR NIF Set Transfer Movement</t>
+          <t>SSR Cement</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -5156,7 +5156,7 @@
       <c r="B268" t="inlineStr"/>
       <c r="C268" t="inlineStr">
         <is>
-          <t>PN Limestone</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -11353,7 +11353,7 @@
       <c r="B629" t="inlineStr"/>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Aurizon North Quay Container Shuttle</t>
+          <t>Aurizon Empty Grain</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
@@ -11665,7 +11665,7 @@
       <c r="B647" t="inlineStr"/>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
@@ -14275,7 +14275,7 @@
       <c r="B794" t="inlineStr"/>
       <c r="C794" t="inlineStr">
         <is>
-          <t>Hunter Railcar Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D794" t="inlineStr">
@@ -14361,7 +14361,7 @@
       <c r="B799" t="inlineStr"/>
       <c r="C799" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D799" t="inlineStr">
@@ -14379,7 +14379,7 @@
       <c r="B800" t="inlineStr"/>
       <c r="C800" t="inlineStr">
         <is>
-          <t>South Coast Empty Car Transfer</t>
+          <t>NSW Trainlink South Coast Service</t>
         </is>
       </c>
       <c r="D800" t="inlineStr">
@@ -36069,7 +36069,7 @@
       <c r="B2023" t="inlineStr"/>
       <c r="C2023" t="inlineStr">
         <is>
-          <t>ORA Coal</t>
+          <t>ORA Shunter</t>
         </is>
       </c>
       <c r="D2023" t="inlineStr">
@@ -44314,7 +44314,7 @@
       <c r="B450" t="inlineStr"/>
       <c r="C450" t="inlineStr">
         <is>
-          <t>QUBE Trip Train</t>
+          <t>QUBE Containerised Freight</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -49778,7 +49778,7 @@
       <c r="B758" t="inlineStr"/>
       <c r="C758" t="inlineStr">
         <is>
-          <t>PN Limestone</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D758" t="inlineStr">
@@ -51364,7 +51364,7 @@
       <c r="B847" t="inlineStr"/>
       <c r="C847" t="inlineStr">
         <is>
-          <t>Hunter Railcar Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D847" t="inlineStr">
@@ -53232,7 +53232,7 @@
       <c r="B951" t="inlineStr"/>
       <c r="C951" t="inlineStr">
         <is>
-          <t>Aurizon North Quay Container Shuttle</t>
+          <t>Aurizon Empty Grain</t>
         </is>
       </c>
       <c r="D951" t="inlineStr">
@@ -57160,7 +57160,7 @@
       <c r="B1171" t="inlineStr"/>
       <c r="C1171" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1171" t="inlineStr">
@@ -65523,7 +65523,7 @@
       <c r="B1641" t="inlineStr"/>
       <c r="C1641" t="inlineStr">
         <is>
-          <t>SSR NIF Set Transfer Movement</t>
+          <t>SSR Cement</t>
         </is>
       </c>
       <c r="D1641" t="inlineStr">
@@ -67323,7 +67323,7 @@
       <c r="B1747" t="inlineStr"/>
       <c r="C1747" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1747" t="inlineStr">
@@ -67575,7 +67575,7 @@
       <c r="B1761" t="inlineStr"/>
       <c r="C1761" t="inlineStr">
         <is>
-          <t>South Coast Empty Car Transfer</t>
+          <t>NSW Trainlink South Coast Service</t>
         </is>
       </c>
       <c r="D1761" t="inlineStr">
@@ -71831,7 +71831,7 @@
       <c r="B2003" t="inlineStr"/>
       <c r="C2003" t="inlineStr">
         <is>
-          <t>ORA Coal</t>
+          <t>ORA Shunter</t>
         </is>
       </c>
       <c r="D2003" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1810,7 +1810,7 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -1986,7 +1986,7 @@
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2580,7 +2580,7 @@
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5140,7 +5140,7 @@
       <c r="B268" t="inlineStr"/>
       <c r="C268" t="inlineStr">
         <is>
-          <t>PN Grain Shuttle</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -5302,7 +5302,7 @@
       <c r="B277" t="inlineStr"/>
       <c r="C277" t="inlineStr">
         <is>
-          <t>PN Cement - RailTrain Crewed</t>
+          <t>PN Cement</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -6378,7 +6378,7 @@
       <c r="B337" t="inlineStr"/>
       <c r="C337" t="inlineStr">
         <is>
-          <t>PN Morandoo Shunter</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -9070,7 +9070,7 @@
       <c r="B501" t="inlineStr"/>
       <c r="C501" t="inlineStr">
         <is>
-          <t>SSR Freight Shuttle</t>
+          <t>SSR Manildra Grain Shuttle</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
@@ -10443,7 +10443,7 @@
       <c r="B578" t="inlineStr"/>
       <c r="C578" t="inlineStr">
         <is>
-          <t>NSW TrainLink Xplorer</t>
+          <t>NSW Trainlink Xplorer</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
@@ -14349,7 +14349,7 @@
       <c r="B799" t="inlineStr"/>
       <c r="C799" t="inlineStr">
         <is>
-          <t>Bathurst Bullet - Transfer</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D799" t="inlineStr">
@@ -15815,7 +15815,7 @@
       <c r="B882" t="inlineStr"/>
       <c r="C882" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D882" t="inlineStr">
@@ -18137,7 +18137,7 @@
       <c r="B1011" t="inlineStr"/>
       <c r="C1011" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1011" t="inlineStr">
@@ -18227,7 +18227,7 @@
       <c r="B1016" t="inlineStr"/>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1016" t="inlineStr">
@@ -18389,7 +18389,7 @@
       <c r="B1025" t="inlineStr"/>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1025" t="inlineStr">
@@ -18821,7 +18821,7 @@
       <c r="B1049" t="inlineStr"/>
       <c r="C1049" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1049" t="inlineStr">
@@ -19541,7 +19541,7 @@
       <c r="B1089" t="inlineStr"/>
       <c r="C1089" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1089" t="inlineStr">
@@ -20369,7 +20369,7 @@
       <c r="B1135" t="inlineStr"/>
       <c r="C1135" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1135" t="inlineStr">
@@ -20801,7 +20801,7 @@
       <c r="B1159" t="inlineStr"/>
       <c r="C1159" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1159" t="inlineStr">
@@ -20981,7 +20981,7 @@
       <c r="B1169" t="inlineStr"/>
       <c r="C1169" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1169" t="inlineStr">
@@ -21143,7 +21143,7 @@
       <c r="B1178" t="inlineStr"/>
       <c r="C1178" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1178" t="inlineStr">
@@ -21395,7 +21395,7 @@
       <c r="B1192" t="inlineStr"/>
       <c r="C1192" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1192" t="inlineStr">
@@ -21755,7 +21755,7 @@
       <c r="B1212" t="inlineStr"/>
       <c r="C1212" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1212" t="inlineStr">
@@ -25137,7 +25137,7 @@
       <c r="B1409" t="inlineStr"/>
       <c r="C1409" t="inlineStr">
         <is>
-          <t>QUBE Container Train</t>
+          <t>QUBE Shuttle</t>
         </is>
       </c>
       <c r="D1409" t="inlineStr">
@@ -27173,7 +27173,7 @@
       <c r="B1527" t="inlineStr"/>
       <c r="C1527" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Additional Bathurst Service</t>
         </is>
       </c>
       <c r="D1527" t="inlineStr">
@@ -37238,7 +37238,7 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -38410,7 +38410,7 @@
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>PN Morandoo Shunter</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -43718,7 +43718,7 @@
       <c r="B405" t="inlineStr"/>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -43804,7 +43804,7 @@
       <c r="B410" t="inlineStr"/>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -44980,7 +44980,7 @@
       <c r="B476" t="inlineStr"/>
       <c r="C476" t="inlineStr">
         <is>
-          <t>QUBE Container Train</t>
+          <t>QUBE Shuttle</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -48654,7 +48654,7 @@
       <c r="B683" t="inlineStr"/>
       <c r="C683" t="inlineStr">
         <is>
-          <t>PN Grain Shuttle</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
@@ -48798,7 +48798,7 @@
       <c r="B691" t="inlineStr"/>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
@@ -49248,7 +49248,7 @@
       <c r="B716" t="inlineStr"/>
       <c r="C716" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
@@ -49374,7 +49374,7 @@
       <c r="B723" t="inlineStr"/>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
@@ -56352,7 +56352,7 @@
       <c r="B1114" t="inlineStr"/>
       <c r="C1114" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1114" t="inlineStr">
@@ -58268,7 +58268,7 @@
       <c r="B1222" t="inlineStr"/>
       <c r="C1222" t="inlineStr">
         <is>
-          <t>SSR Freight Shuttle</t>
+          <t>SSR Manildra Grain Shuttle</t>
         </is>
       </c>
       <c r="D1222" t="inlineStr">
@@ -61496,7 +61496,7 @@
       <c r="B1403" t="inlineStr"/>
       <c r="C1403" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Additional Bathurst Service</t>
         </is>
       </c>
       <c r="D1403" t="inlineStr">
@@ -61655,7 +61655,7 @@
       <c r="B1412" t="inlineStr"/>
       <c r="C1412" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1412" t="inlineStr">
@@ -61903,7 +61903,7 @@
       <c r="B1426" t="inlineStr"/>
       <c r="C1426" t="inlineStr">
         <is>
-          <t>Bathurst Bullet - Transfer</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1426" t="inlineStr">
@@ -62119,7 +62119,7 @@
       <c r="B1438" t="inlineStr"/>
       <c r="C1438" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1438" t="inlineStr">
@@ -63115,7 +63115,7 @@
       <c r="B1494" t="inlineStr"/>
       <c r="C1494" t="inlineStr">
         <is>
-          <t>NSW TrainLink Xplorer</t>
+          <t>NSW Trainlink Xplorer</t>
         </is>
       </c>
       <c r="D1494" t="inlineStr">
@@ -64719,7 +64719,7 @@
       <c r="B1584" t="inlineStr"/>
       <c r="C1584" t="inlineStr">
         <is>
-          <t>PN Cement - RailTrain Crewed</t>
+          <t>PN Cement</t>
         </is>
       </c>
       <c r="D1584" t="inlineStr">
@@ -65053,7 +65053,7 @@
       <c r="B1603" t="inlineStr"/>
       <c r="C1603" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1603" t="inlineStr">
@@ -65845,7 +65845,7 @@
       <c r="B1647" t="inlineStr"/>
       <c r="C1647" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1647" t="inlineStr">
@@ -68645,7 +68645,7 @@
       <c r="B1809" t="inlineStr"/>
       <c r="C1809" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1809" t="inlineStr">
@@ -68717,7 +68717,7 @@
       <c r="B1813" t="inlineStr"/>
       <c r="C1813" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1813" t="inlineStr">
@@ -69545,7 +69545,7 @@
       <c r="B1859" t="inlineStr"/>
       <c r="C1859" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1859" t="inlineStr">
@@ -69869,7 +69869,7 @@
       <c r="B1877" t="inlineStr"/>
       <c r="C1877" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1877" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1494,7 +1494,7 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>V/line Empty Car Movement</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1702,7 +1702,7 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SouthWest Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1720,7 +1720,7 @@
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2544,7 +2544,7 @@
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3278,7 +3278,7 @@
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr">
         <is>
-          <t>QUBE Light Engine</t>
+          <t>QUBE Trip Train</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -4888,7 +4888,7 @@
       <c r="B254" t="inlineStr"/>
       <c r="C254" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Cement - RailTrain Crewed</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -5338,7 +5338,7 @@
       <c r="B279" t="inlineStr"/>
       <c r="C279" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Intermodal Trip Train - RSS Crewed</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -5662,7 +5662,7 @@
       <c r="B297" t="inlineStr"/>
       <c r="C297" t="inlineStr">
         <is>
-          <t>PN Coal</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -8020,7 +8020,7 @@
       <c r="B436" t="inlineStr"/>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Aurizon Mineral Sands shuttle</t>
+          <t>Aurizon Loaded Mineral Sands Shuttle</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -10880,7 +10880,7 @@
       <c r="B603" t="inlineStr"/>
       <c r="C603" t="inlineStr">
         <is>
-          <t>QUBE Light Engine Movement</t>
+          <t>QUBE Containerised Freight</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
@@ -11562,7 +11562,7 @@
       <c r="B642" t="inlineStr"/>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Aurizon Intermodal</t>
+          <t>Aurizon Wagon Transfer</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
@@ -11810,7 +11810,7 @@
       <c r="B656" t="inlineStr"/>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Ore</t>
+          <t>Aurizon Empty Ore</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
@@ -14692,7 +14692,7 @@
       <c r="B819" t="inlineStr"/>
       <c r="C819" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D819" t="inlineStr">
@@ -15460,7 +15460,7 @@
       <c r="B863" t="inlineStr"/>
       <c r="C863" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D863" t="inlineStr">
@@ -16468,7 +16468,7 @@
       <c r="B919" t="inlineStr"/>
       <c r="C919" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D919" t="inlineStr">
@@ -17260,7 +17260,7 @@
       <c r="B963" t="inlineStr"/>
       <c r="C963" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D963" t="inlineStr">
@@ -18196,7 +18196,7 @@
       <c r="B1015" t="inlineStr"/>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1015" t="inlineStr">
@@ -19330,7 +19330,7 @@
       <c r="B1078" t="inlineStr"/>
       <c r="C1078" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1078" t="inlineStr">
@@ -19942,7 +19942,7 @@
       <c r="B1112" t="inlineStr"/>
       <c r="C1112" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1112" t="inlineStr">
@@ -20050,7 +20050,7 @@
       <c r="B1118" t="inlineStr"/>
       <c r="C1118" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1118" t="inlineStr">
@@ -20284,7 +20284,7 @@
       <c r="B1131" t="inlineStr"/>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1131" t="inlineStr">
@@ -20608,7 +20608,7 @@
       <c r="B1149" t="inlineStr"/>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1149" t="inlineStr">
@@ -20986,7 +20986,7 @@
       <c r="B1170" t="inlineStr"/>
       <c r="C1170" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1170" t="inlineStr">
@@ -21004,7 +21004,7 @@
       <c r="B1171" t="inlineStr"/>
       <c r="C1171" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1171" t="inlineStr">
@@ -21220,7 +21220,7 @@
       <c r="B1183" t="inlineStr"/>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1183" t="inlineStr">
@@ -21850,7 +21850,7 @@
       <c r="B1218" t="inlineStr"/>
       <c r="C1218" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1218" t="inlineStr">
@@ -22102,7 +22102,7 @@
       <c r="B1232" t="inlineStr"/>
       <c r="C1232" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1232" t="inlineStr">
@@ -22210,7 +22210,7 @@
       <c r="B1238" t="inlineStr"/>
       <c r="C1238" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1238" t="inlineStr">
@@ -22282,7 +22282,7 @@
       <c r="B1242" t="inlineStr"/>
       <c r="C1242" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1242" t="inlineStr">
@@ -23998,7 +23998,7 @@
       <c r="B1340" t="inlineStr"/>
       <c r="C1340" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>PN Infrabuild Steel</t>
         </is>
       </c>
       <c r="D1340" t="inlineStr">
@@ -37075,7 +37075,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>QUBE Light Engine</t>
+          <t>QUBE Trip Train</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -38873,7 +38873,7 @@
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Cement - RailTrain Crewed</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -41777,7 +41777,7 @@
       <c r="B278" t="inlineStr"/>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Aurizon Intermodal</t>
+          <t>Aurizon Wagon Transfer</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -44533,7 +44533,7 @@
       <c r="B434" t="inlineStr"/>
       <c r="C434" t="inlineStr">
         <is>
-          <t>QUBE Light Engine Movement</t>
+          <t>QUBE Containerised Freight</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -45195,7 +45195,7 @@
       <c r="B471" t="inlineStr"/>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -46059,7 +46059,7 @@
       <c r="B521" t="inlineStr"/>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
@@ -48005,7 +48005,7 @@
       <c r="B630" t="inlineStr"/>
       <c r="C630" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
@@ -48761,7 +48761,7 @@
       <c r="B672" t="inlineStr"/>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
@@ -48779,7 +48779,7 @@
       <c r="B673" t="inlineStr"/>
       <c r="C673" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
@@ -51757,7 +51757,7 @@
       <c r="B840" t="inlineStr"/>
       <c r="C840" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
@@ -52069,7 +52069,7 @@
       <c r="B858" t="inlineStr"/>
       <c r="C858" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D858" t="inlineStr">
@@ -52159,7 +52159,7 @@
       <c r="B863" t="inlineStr"/>
       <c r="C863" t="inlineStr">
         <is>
-          <t>V/line Empty Car Movement</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D863" t="inlineStr">
@@ -52519,7 +52519,7 @@
       <c r="B883" t="inlineStr"/>
       <c r="C883" t="inlineStr">
         <is>
-          <t>Aurizon Mineral Sands shuttle</t>
+          <t>Aurizon Loaded Mineral Sands Shuttle</t>
         </is>
       </c>
       <c r="D883" t="inlineStr">
@@ -52807,7 +52807,7 @@
       <c r="B899" t="inlineStr"/>
       <c r="C899" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
@@ -54477,7 +54477,7 @@
       <c r="B992" t="inlineStr"/>
       <c r="C992" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D992" t="inlineStr">
@@ -56991,7 +56991,7 @@
       <c r="B1133" t="inlineStr"/>
       <c r="C1133" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D1133" t="inlineStr">
@@ -58979,7 +58979,7 @@
       <c r="B1245" t="inlineStr"/>
       <c r="C1245" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Ore</t>
+          <t>Aurizon Empty Ore</t>
         </is>
       </c>
       <c r="D1245" t="inlineStr">
@@ -59407,7 +59407,7 @@
       <c r="B1269" t="inlineStr"/>
       <c r="C1269" t="inlineStr">
         <is>
-          <t>PN Coal</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D1269" t="inlineStr">
@@ -61364,7 +61364,7 @@
       <c r="B1379" t="inlineStr"/>
       <c r="C1379" t="inlineStr">
         <is>
-          <t>SouthWest Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1379" t="inlineStr">
@@ -62991,7 +62991,7 @@
       <c r="B1470" t="inlineStr"/>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Intermodal Trip Train - RSS Crewed</t>
         </is>
       </c>
       <c r="D1470" t="inlineStr">
@@ -63239,7 +63239,7 @@
       <c r="B1484" t="inlineStr"/>
       <c r="C1484" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>PN Infrabuild Steel</t>
         </is>
       </c>
       <c r="D1484" t="inlineStr">
@@ -63807,7 +63807,7 @@
       <c r="B1516" t="inlineStr"/>
       <c r="C1516" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1516" t="inlineStr">
@@ -65285,7 +65285,7 @@
       <c r="B1599" t="inlineStr"/>
       <c r="C1599" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1599" t="inlineStr">
@@ -69049,7 +69049,7 @@
       <c r="B1815" t="inlineStr"/>
       <c r="C1815" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1815" t="inlineStr">
@@ -69067,7 +69067,7 @@
       <c r="B1816" t="inlineStr"/>
       <c r="C1816" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1816" t="inlineStr">
@@ -69229,7 +69229,7 @@
       <c r="B1825" t="inlineStr"/>
       <c r="C1825" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1825" t="inlineStr">
@@ -69805,7 +69805,7 @@
       <c r="B1857" t="inlineStr"/>
       <c r="C1857" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1857" t="inlineStr">
@@ -70075,7 +70075,7 @@
       <c r="B1872" t="inlineStr"/>
       <c r="C1872" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1872" t="inlineStr">
@@ -70597,7 +70597,7 @@
       <c r="B1901" t="inlineStr"/>
       <c r="C1901" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1901" t="inlineStr">
@@ -70651,7 +70651,7 @@
       <c r="B1904" t="inlineStr"/>
       <c r="C1904" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1904" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -472,7 +472,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -670,7 +670,7 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>North East Line BG Service</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1616,7 +1616,7 @@
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>V1165</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2202,7 +2202,7 @@
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>North East Line BG Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2850,7 +2850,7 @@
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>North East SG Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -9246,7 +9246,7 @@
       <c r="B511" t="inlineStr"/>
       <c r="C511" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Limestone</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
@@ -10582,7 +10582,7 @@
       <c r="B586" t="inlineStr"/>
       <c r="C586" t="inlineStr">
         <is>
-          <t>NSW TrainLink Xplorer</t>
+          <t>NSW Trainlink Empty Car Transfer</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
@@ -11236,7 +11236,7 @@
       <c r="B623" t="inlineStr"/>
       <c r="C623" t="inlineStr">
         <is>
-          <t>SCT Wagon Transfer</t>
+          <t>SCT Steel Shunt / Wine Train</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
@@ -11562,7 +11562,7 @@
       <c r="B642" t="inlineStr"/>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Aurizon Wagon Transfer</t>
+          <t>Aurizon Intermodal</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
@@ -16180,7 +16180,7 @@
       <c r="B903" t="inlineStr"/>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
@@ -19312,7 +19312,7 @@
       <c r="B1077" t="inlineStr"/>
       <c r="C1077" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1077" t="inlineStr">
@@ -19888,7 +19888,7 @@
       <c r="B1109" t="inlineStr"/>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1109" t="inlineStr">
@@ -20572,7 +20572,7 @@
       <c r="B1147" t="inlineStr"/>
       <c r="C1147" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1147" t="inlineStr">
@@ -20644,7 +20644,7 @@
       <c r="B1151" t="inlineStr"/>
       <c r="C1151" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1151" t="inlineStr">
@@ -21076,7 +21076,7 @@
       <c r="B1175" t="inlineStr"/>
       <c r="C1175" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1175" t="inlineStr">
@@ -21670,7 +21670,7 @@
       <c r="B1208" t="inlineStr"/>
       <c r="C1208" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1208" t="inlineStr">
@@ -21958,7 +21958,7 @@
       <c r="B1224" t="inlineStr"/>
       <c r="C1224" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1224" t="inlineStr">
@@ -27398,7 +27398,7 @@
       <c r="B1540" t="inlineStr"/>
       <c r="C1540" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Hunter Railcar Transfer</t>
         </is>
       </c>
       <c r="D1540" t="inlineStr">
@@ -27744,7 +27744,7 @@
       <c r="B1561" t="inlineStr"/>
       <c r="C1561" t="inlineStr">
         <is>
-          <t>PN Empty Aggregate</t>
+          <t>PN Minerals</t>
         </is>
       </c>
       <c r="D1561" t="inlineStr">
@@ -38239,7 +38239,7 @@
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -41777,7 +41777,7 @@
       <c r="B278" t="inlineStr"/>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Aurizon Wagon Transfer</t>
+          <t>Aurizon Intermodal</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -41813,7 +41813,7 @@
       <c r="B280" t="inlineStr"/>
       <c r="C280" t="inlineStr">
         <is>
-          <t>SCT Wagon Transfer</t>
+          <t>SCT Steel Shunt / Wine Train</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -42907,7 +42907,7 @@
       <c r="B341" t="inlineStr"/>
       <c r="C341" t="inlineStr">
         <is>
-          <t>North East Line BG Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -44461,7 +44461,7 @@
       <c r="B430" t="inlineStr"/>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -44479,7 +44479,7 @@
       <c r="B431" t="inlineStr"/>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -44551,7 +44551,7 @@
       <c r="B435" t="inlineStr"/>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -47303,7 +47303,7 @@
       <c r="B591" t="inlineStr"/>
       <c r="C591" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
@@ -49383,7 +49383,7 @@
       <c r="B707" t="inlineStr"/>
       <c r="C707" t="inlineStr">
         <is>
-          <t>PN Empty Aggregate</t>
+          <t>PN Minerals</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
@@ -49905,7 +49905,7 @@
       <c r="B736" t="inlineStr"/>
       <c r="C736" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
@@ -55131,7 +55131,7 @@
       <c r="B1029" t="inlineStr"/>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>North East Line BG Service</t>
         </is>
       </c>
       <c r="D1029" t="inlineStr">
@@ -56199,7 +56199,7 @@
       <c r="B1089" t="inlineStr"/>
       <c r="C1089" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1089" t="inlineStr">
@@ -62667,7 +62667,7 @@
       <c r="B1452" t="inlineStr"/>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Hunter Railcar Transfer</t>
         </is>
       </c>
       <c r="D1452" t="inlineStr">
@@ -62775,7 +62775,7 @@
       <c r="B1458" t="inlineStr"/>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1458" t="inlineStr">
@@ -66411,7 +66411,7 @@
       <c r="B1662" t="inlineStr"/>
       <c r="C1662" t="inlineStr">
         <is>
-          <t>V1165</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1662" t="inlineStr">
@@ -66519,7 +66519,7 @@
       <c r="B1668" t="inlineStr"/>
       <c r="C1668" t="inlineStr">
         <is>
-          <t>North East SG Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1668" t="inlineStr">
@@ -67869,7 +67869,7 @@
       <c r="B1749" t="inlineStr"/>
       <c r="C1749" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Limestone</t>
         </is>
       </c>
       <c r="D1749" t="inlineStr">
@@ -68211,7 +68211,7 @@
       <c r="B1768" t="inlineStr"/>
       <c r="C1768" t="inlineStr">
         <is>
-          <t>NSW TrainLink Xplorer</t>
+          <t>NSW Trainlink Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1768" t="inlineStr">
@@ -69733,7 +69733,7 @@
       <c r="B1853" t="inlineStr"/>
       <c r="C1853" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1853" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -5914,7 +5914,7 @@
       <c r="B311" t="inlineStr"/>
       <c r="C311" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Light Engine Movement</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -11946,7 +11946,7 @@
       <c r="B664" t="inlineStr"/>
       <c r="C664" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
@@ -19334,7 +19334,7 @@
       <c r="B1078" t="inlineStr"/>
       <c r="C1078" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1078" t="inlineStr">
@@ -19658,7 +19658,7 @@
       <c r="B1096" t="inlineStr"/>
       <c r="C1096" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1096" t="inlineStr">
@@ -19874,7 +19874,7 @@
       <c r="B1108" t="inlineStr"/>
       <c r="C1108" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1108" t="inlineStr">
@@ -19892,7 +19892,7 @@
       <c r="B1109" t="inlineStr"/>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1109" t="inlineStr">
@@ -20990,7 +20990,7 @@
       <c r="B1170" t="inlineStr"/>
       <c r="C1170" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1170" t="inlineStr">
@@ -24498,7 +24498,7 @@
       <c r="B1368" t="inlineStr"/>
       <c r="C1368" t="inlineStr">
         <is>
-          <t>PN Sadleirs Transfer</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D1368" t="inlineStr">
@@ -25574,7 +25574,7 @@
       <c r="B1434" t="inlineStr"/>
       <c r="C1434" t="inlineStr">
         <is>
-          <t>QUBE WM Shunter</t>
+          <t>QUBE BlueScope Steel</t>
         </is>
       </c>
       <c r="D1434" t="inlineStr">
@@ -36814,7 +36814,7 @@
       <c r="B2066" t="inlineStr"/>
       <c r="C2066" t="inlineStr">
         <is>
-          <t>ORA Shunter</t>
+          <t>ORA Coal</t>
         </is>
       </c>
       <c r="D2066" t="inlineStr">
@@ -38541,7 +38541,7 @@
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>QUBE WM Shunter</t>
+          <t>QUBE BlueScope Steel</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -41673,7 +41673,7 @@
       <c r="B272" t="inlineStr"/>
       <c r="C272" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Light Engine Movement</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -52829,7 +52829,7 @@
       <c r="B900" t="inlineStr"/>
       <c r="C900" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D900" t="inlineStr">
@@ -52865,7 +52865,7 @@
       <c r="B902" t="inlineStr"/>
       <c r="C902" t="inlineStr">
         <is>
-          <t>PN Sadleirs Transfer</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D902" t="inlineStr">
@@ -68445,7 +68445,7 @@
       <c r="B1781" t="inlineStr"/>
       <c r="C1781" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1781" t="inlineStr">
@@ -69611,7 +69611,7 @@
       <c r="B1846" t="inlineStr"/>
       <c r="C1846" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1846" t="inlineStr">
@@ -69737,7 +69737,7 @@
       <c r="B1853" t="inlineStr"/>
       <c r="C1853" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1853" t="inlineStr">
@@ -69755,7 +69755,7 @@
       <c r="B1854" t="inlineStr"/>
       <c r="C1854" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1854" t="inlineStr">
@@ -70097,7 +70097,7 @@
       <c r="B1873" t="inlineStr"/>
       <c r="C1873" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1873" t="inlineStr">
@@ -73043,7 +73043,7 @@
       <c r="B2042" t="inlineStr"/>
       <c r="C2042" t="inlineStr">
         <is>
-          <t>ORA Shunter</t>
+          <t>ORA Coal</t>
         </is>
       </c>
       <c r="D2042" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -4002,7 +4002,11 @@
         </is>
       </c>
       <c r="B202" t="inlineStr"/>
-      <c r="C202" t="inlineStr"/>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>AZ Coal</t>
+        </is>
+      </c>
       <c r="D202" t="inlineStr">
         <is>
           <t>2026-04-07 22:28:28</t>
@@ -6504,7 +6508,7 @@
       <c r="B344" t="inlineStr"/>
       <c r="C344" t="inlineStr">
         <is>
-          <t>PN Grain</t>
+          <t>PN Morandoo Shunter</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -11910,7 +11914,7 @@
       <c r="B662" t="inlineStr"/>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
@@ -14732,7 +14736,7 @@
       <c r="B821" t="inlineStr"/>
       <c r="C821" t="inlineStr">
         <is>
-          <t>South Coast Service</t>
+          <t>South Coast Empty Car Transfer</t>
         </is>
       </c>
       <c r="D821" t="inlineStr">
@@ -43857,7 +43861,11 @@
         </is>
       </c>
       <c r="B395" t="inlineStr"/>
-      <c r="C395" t="inlineStr"/>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>AZ Coal</t>
+        </is>
+      </c>
       <c r="D395" t="inlineStr">
         <is>
           <t>2026-04-07 22:28:28</t>
@@ -51965,7 +51973,7 @@
       <c r="B852" t="inlineStr"/>
       <c r="C852" t="inlineStr">
         <is>
-          <t>PN Grain</t>
+          <t>PN Morandoo Shunter</t>
         </is>
       </c>
       <c r="D852" t="inlineStr">
@@ -65483,7 +65491,7 @@
       <c r="B1610" t="inlineStr"/>
       <c r="C1610" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1610" t="inlineStr">
@@ -68697,7 +68705,7 @@
       <c r="B1795" t="inlineStr"/>
       <c r="C1795" t="inlineStr">
         <is>
-          <t>South Coast Service</t>
+          <t>South Coast Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1795" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -4746,7 +4746,7 @@
       <c r="B245" t="inlineStr"/>
       <c r="C245" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -5972,7 +5972,7 @@
       <c r="B314" t="inlineStr"/>
       <c r="C314" t="inlineStr">
         <is>
-          <t>PN Grain</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -6260,7 +6260,7 @@
       <c r="B330" t="inlineStr"/>
       <c r="C330" t="inlineStr">
         <is>
-          <t>PN Shunter</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -8028,7 +8028,7 @@
       <c r="B436" t="inlineStr"/>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Mineral Sands Shuttle</t>
+          <t>Aurizon Mineral Sands shuttle</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -8168,7 +8168,7 @@
       <c r="B444" t="inlineStr"/>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Aurizon Empty Copper</t>
+          <t>Aurizon Loaded Copper</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -9466,7 +9466,7 @@
       <c r="B523" t="inlineStr"/>
       <c r="C523" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
@@ -11642,7 +11642,7 @@
       <c r="B646" t="inlineStr"/>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Ore</t>
+          <t>Aurizon Empty Ore</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
@@ -12022,7 +12022,7 @@
       <c r="B668" t="inlineStr"/>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
@@ -14736,7 +14736,7 @@
       <c r="B821" t="inlineStr"/>
       <c r="C821" t="inlineStr">
         <is>
-          <t>South Coast Empty Car Transfer</t>
+          <t>NSW Trainlink South Coast Service</t>
         </is>
       </c>
       <c r="D821" t="inlineStr">
@@ -25704,7 +25704,7 @@
       <c r="B1441" t="inlineStr"/>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>QUBE BlueScope Steel Transfer</t>
+          <t>QUBE Trip Train</t>
         </is>
       </c>
       <c r="D1441" t="inlineStr">
@@ -27438,7 +27438,7 @@
       <c r="B1542" t="inlineStr"/>
       <c r="C1542" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1542" t="inlineStr">
@@ -37365,7 +37365,7 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PN Shunter</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -39627,7 +39627,7 @@
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Ore</t>
+          <t>Aurizon Empty Ore</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -41821,7 +41821,7 @@
       <c r="B280" t="inlineStr"/>
       <c r="C280" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -45297,7 +45297,7 @@
       <c r="B476" t="inlineStr"/>
       <c r="C476" t="inlineStr">
         <is>
-          <t>QUBE BlueScope Steel Transfer</t>
+          <t>QUBE Trip Train</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -52549,7 +52549,7 @@
       <c r="B884" t="inlineStr"/>
       <c r="C884" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Mineral Sands Shuttle</t>
+          <t>Aurizon Mineral Sands shuttle</t>
         </is>
       </c>
       <c r="D884" t="inlineStr">
@@ -63201,7 +63201,7 @@
       <c r="B1481" t="inlineStr"/>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1481" t="inlineStr">
@@ -67019,7 +67019,7 @@
       <c r="B1696" t="inlineStr"/>
       <c r="C1696" t="inlineStr">
         <is>
-          <t>PN Grain</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D1696" t="inlineStr">
@@ -67523,7 +67523,7 @@
       <c r="B1726" t="inlineStr"/>
       <c r="C1726" t="inlineStr">
         <is>
-          <t>Aurizon Empty Copper</t>
+          <t>Aurizon Loaded Copper</t>
         </is>
       </c>
       <c r="D1726" t="inlineStr">
@@ -68489,7 +68489,7 @@
       <c r="B1783" t="inlineStr"/>
       <c r="C1783" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1783" t="inlineStr">
@@ -68705,7 +68705,7 @@
       <c r="B1795" t="inlineStr"/>
       <c r="C1795" t="inlineStr">
         <is>
-          <t>South Coast Empty Car Transfer</t>
+          <t>NSW Trainlink South Coast Service</t>
         </is>
       </c>
       <c r="D1795" t="inlineStr">
@@ -71845,7 +71845,7 @@
       <c r="B1975" t="inlineStr"/>
       <c r="C1975" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1975" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -634,7 +634,7 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1174,7 +1174,7 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1332,7 +1332,7 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NorthEast BG Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1986,7 +1986,7 @@
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2328,7 +2328,7 @@
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2436,7 +2436,7 @@
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -8028,7 +8028,7 @@
       <c r="B436" t="inlineStr"/>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Aurizon Mineral Sands shuttle</t>
+          <t>Aurizon Mineral Sands Shuttle</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -9164,7 +9164,7 @@
       <c r="B506" t="inlineStr"/>
       <c r="C506" t="inlineStr">
         <is>
-          <t>SSR Grain</t>
+          <t>C504</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
@@ -11968,7 +11968,7 @@
       <c r="B665" t="inlineStr"/>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
@@ -14560,7 +14560,7 @@
       <c r="B811" t="inlineStr"/>
       <c r="C811" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning (Forms SN34)</t>
+          <t>Southern Highlands Service</t>
         </is>
       </c>
       <c r="D811" t="inlineStr">
@@ -15396,7 +15396,7 @@
       <c r="B859" t="inlineStr"/>
       <c r="C859" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D859" t="inlineStr">
@@ -15576,7 +15576,7 @@
       <c r="B869" t="inlineStr"/>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D869" t="inlineStr">
@@ -15612,7 +15612,7 @@
       <c r="B871" t="inlineStr"/>
       <c r="C871" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D871" t="inlineStr">
@@ -15738,7 +15738,7 @@
       <c r="B878" t="inlineStr"/>
       <c r="C878" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D878" t="inlineStr">
@@ -15810,7 +15810,7 @@
       <c r="B882" t="inlineStr"/>
       <c r="C882" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D882" t="inlineStr">
@@ -15864,7 +15864,7 @@
       <c r="B885" t="inlineStr"/>
       <c r="C885" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D885" t="inlineStr">
@@ -15972,7 +15972,7 @@
       <c r="B891" t="inlineStr"/>
       <c r="C891" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D891" t="inlineStr">
@@ -16008,7 +16008,7 @@
       <c r="B893" t="inlineStr"/>
       <c r="C893" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D893" t="inlineStr">
@@ -16584,7 +16584,7 @@
       <c r="B925" t="inlineStr"/>
       <c r="C925" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D925" t="inlineStr">
@@ -17808,7 +17808,7 @@
       <c r="B993" t="inlineStr"/>
       <c r="C993" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D993" t="inlineStr">
@@ -18042,7 +18042,7 @@
       <c r="B1006" t="inlineStr"/>
       <c r="C1006" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1006" t="inlineStr">
@@ -18078,7 +18078,7 @@
       <c r="B1008" t="inlineStr"/>
       <c r="C1008" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1008" t="inlineStr">
@@ -18132,7 +18132,7 @@
       <c r="B1011" t="inlineStr"/>
       <c r="C1011" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1011" t="inlineStr">
@@ -18456,7 +18456,7 @@
       <c r="B1029" t="inlineStr"/>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1029" t="inlineStr">
@@ -18528,7 +18528,7 @@
       <c r="B1033" t="inlineStr"/>
       <c r="C1033" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1033" t="inlineStr">
@@ -18690,7 +18690,7 @@
       <c r="B1042" t="inlineStr"/>
       <c r="C1042" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1042" t="inlineStr">
@@ -19194,7 +19194,7 @@
       <c r="B1070" t="inlineStr"/>
       <c r="C1070" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1070" t="inlineStr">
@@ -19446,7 +19446,7 @@
       <c r="B1084" t="inlineStr"/>
       <c r="C1084" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1084" t="inlineStr">
@@ -19644,7 +19644,7 @@
       <c r="B1095" t="inlineStr"/>
       <c r="C1095" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1095" t="inlineStr">
@@ -20040,7 +20040,7 @@
       <c r="B1117" t="inlineStr"/>
       <c r="C1117" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1117" t="inlineStr">
@@ -20058,7 +20058,7 @@
       <c r="B1118" t="inlineStr"/>
       <c r="C1118" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1118" t="inlineStr">
@@ -20202,7 +20202,7 @@
       <c r="B1126" t="inlineStr"/>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1126" t="inlineStr">
@@ -20328,7 +20328,7 @@
       <c r="B1133" t="inlineStr"/>
       <c r="C1133" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1133" t="inlineStr">
@@ -20364,7 +20364,7 @@
       <c r="B1135" t="inlineStr"/>
       <c r="C1135" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1135" t="inlineStr">
@@ -20472,7 +20472,7 @@
       <c r="B1141" t="inlineStr"/>
       <c r="C1141" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1141" t="inlineStr">
@@ -20526,7 +20526,7 @@
       <c r="B1144" t="inlineStr"/>
       <c r="C1144" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1144" t="inlineStr">
@@ -20796,7 +20796,7 @@
       <c r="B1159" t="inlineStr"/>
       <c r="C1159" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1159" t="inlineStr">
@@ -20868,7 +20868,7 @@
       <c r="B1163" t="inlineStr"/>
       <c r="C1163" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1163" t="inlineStr">
@@ -20940,7 +20940,7 @@
       <c r="B1167" t="inlineStr"/>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D1167" t="inlineStr">
@@ -21030,7 +21030,7 @@
       <c r="B1172" t="inlineStr"/>
       <c r="C1172" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1172" t="inlineStr">
@@ -21048,7 +21048,7 @@
       <c r="B1173" t="inlineStr"/>
       <c r="C1173" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1173" t="inlineStr">
@@ -21174,7 +21174,7 @@
       <c r="B1180" t="inlineStr"/>
       <c r="C1180" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1180" t="inlineStr">
@@ -21264,7 +21264,7 @@
       <c r="B1185" t="inlineStr"/>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1185" t="inlineStr">
@@ -21282,7 +21282,7 @@
       <c r="B1186" t="inlineStr"/>
       <c r="C1186" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1186" t="inlineStr">
@@ -21300,7 +21300,7 @@
       <c r="B1187" t="inlineStr"/>
       <c r="C1187" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1187" t="inlineStr">
@@ -21390,7 +21390,7 @@
       <c r="B1192" t="inlineStr"/>
       <c r="C1192" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1192" t="inlineStr">
@@ -21588,7 +21588,7 @@
       <c r="B1203" t="inlineStr"/>
       <c r="C1203" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1203" t="inlineStr">
@@ -21660,7 +21660,7 @@
       <c r="B1207" t="inlineStr"/>
       <c r="C1207" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1207" t="inlineStr">
@@ -21732,7 +21732,7 @@
       <c r="B1211" t="inlineStr"/>
       <c r="C1211" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1211" t="inlineStr">
@@ -21786,7 +21786,7 @@
       <c r="B1214" t="inlineStr"/>
       <c r="C1214" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1214" t="inlineStr">
@@ -21912,7 +21912,7 @@
       <c r="B1221" t="inlineStr"/>
       <c r="C1221" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1221" t="inlineStr">
@@ -21930,7 +21930,7 @@
       <c r="B1222" t="inlineStr"/>
       <c r="C1222" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1222" t="inlineStr">
@@ -21966,7 +21966,7 @@
       <c r="B1224" t="inlineStr"/>
       <c r="C1224" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1224" t="inlineStr">
@@ -22038,7 +22038,7 @@
       <c r="B1228" t="inlineStr"/>
       <c r="C1228" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1228" t="inlineStr">
@@ -22092,7 +22092,7 @@
       <c r="B1231" t="inlineStr"/>
       <c r="C1231" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1231" t="inlineStr">
@@ -22128,7 +22128,7 @@
       <c r="B1233" t="inlineStr"/>
       <c r="C1233" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1233" t="inlineStr">
@@ -22182,7 +22182,7 @@
       <c r="B1236" t="inlineStr"/>
       <c r="C1236" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1236" t="inlineStr">
@@ -22218,7 +22218,7 @@
       <c r="B1238" t="inlineStr"/>
       <c r="C1238" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1238" t="inlineStr">
@@ -22236,7 +22236,7 @@
       <c r="B1239" t="inlineStr"/>
       <c r="C1239" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1239" t="inlineStr">
@@ -22254,7 +22254,7 @@
       <c r="B1240" t="inlineStr"/>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1240" t="inlineStr">
@@ -22308,7 +22308,7 @@
       <c r="B1243" t="inlineStr"/>
       <c r="C1243" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1243" t="inlineStr">
@@ -22398,7 +22398,7 @@
       <c r="B1248" t="inlineStr"/>
       <c r="C1248" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1248" t="inlineStr">
@@ -22416,7 +22416,7 @@
       <c r="B1249" t="inlineStr"/>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1249" t="inlineStr">
@@ -22434,7 +22434,7 @@
       <c r="B1250" t="inlineStr"/>
       <c r="C1250" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1250" t="inlineStr">
@@ -22452,7 +22452,7 @@
       <c r="B1251" t="inlineStr"/>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1251" t="inlineStr">
@@ -26636,7 +26636,7 @@
       <c r="B1495" t="inlineStr"/>
       <c r="C1495" t="inlineStr">
         <is>
-          <t>NorthEast BG Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D1495" t="inlineStr">
@@ -26830,7 +26830,7 @@
       <c r="B1506" t="inlineStr"/>
       <c r="C1506" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>North Eastern BG Line Service</t>
         </is>
       </c>
       <c r="D1506" t="inlineStr">
@@ -27046,7 +27046,7 @@
       <c r="B1518" t="inlineStr"/>
       <c r="C1518" t="inlineStr">
         <is>
-          <t>SCT Intermodal</t>
+          <t>SCT Sadliers Transfer</t>
         </is>
       </c>
       <c r="D1518" t="inlineStr">
@@ -27490,7 +27490,7 @@
       <c r="B1544" t="inlineStr"/>
       <c r="C1544" t="inlineStr">
         <is>
-          <t>Hunter Railcar Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1544" t="inlineStr">
@@ -27540,7 +27540,7 @@
       <c r="B1547" t="inlineStr"/>
       <c r="C1547" t="inlineStr">
         <is>
-          <t>Bathurst Bullet - Transfer</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D1547" t="inlineStr">
@@ -36456,7 +36456,7 @@
       <c r="B2045" t="inlineStr"/>
       <c r="C2045" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (ex NT34)</t>
         </is>
       </c>
       <c r="D2045" t="inlineStr">
@@ -36772,7 +36772,7 @@
       <c r="B2063" t="inlineStr"/>
       <c r="C2063" t="inlineStr">
         <is>
-          <t>ORA Coal</t>
+          <t>ORA Shunter</t>
         </is>
       </c>
       <c r="D2063" t="inlineStr">
@@ -37983,7 +37983,7 @@
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -38037,7 +38037,7 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SCT Intermodal</t>
+          <t>SCT Sadliers Transfer</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -39901,7 +39901,7 @@
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -40519,7 +40519,7 @@
       <c r="B200" t="inlineStr"/>
       <c r="C200" t="inlineStr">
         <is>
-          <t>ORA Coal</t>
+          <t>ORA Shunter</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -41685,7 +41685,7 @@
       <c r="B267" t="inlineStr"/>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -41901,7 +41901,7 @@
       <c r="B279" t="inlineStr"/>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -44019,7 +44019,7 @@
       <c r="B398" t="inlineStr"/>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -44539,7 +44539,7 @@
       <c r="B428" t="inlineStr"/>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -44697,7 +44697,7 @@
       <c r="B437" t="inlineStr"/>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -45413,7 +45413,7 @@
       <c r="B477" t="inlineStr"/>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -45449,7 +45449,7 @@
       <c r="B479" t="inlineStr"/>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -46277,7 +46277,7 @@
       <c r="B527" t="inlineStr"/>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
@@ -47287,7 +47287,7 @@
       <c r="B584" t="inlineStr"/>
       <c r="C584" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
@@ -48943,7 +48943,7 @@
       <c r="B676" t="inlineStr"/>
       <c r="C676" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
@@ -48997,7 +48997,7 @@
       <c r="B679" t="inlineStr"/>
       <c r="C679" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
@@ -49299,7 +49299,7 @@
       <c r="B696" t="inlineStr"/>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
@@ -49619,7 +49619,7 @@
       <c r="B714" t="inlineStr"/>
       <c r="C714" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
@@ -49763,7 +49763,7 @@
       <c r="B722" t="inlineStr"/>
       <c r="C722" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
@@ -51579,7 +51579,7 @@
       <c r="B824" t="inlineStr"/>
       <c r="C824" t="inlineStr">
         <is>
-          <t>SSR Grain</t>
+          <t>C504</t>
         </is>
       </c>
       <c r="D824" t="inlineStr">
@@ -51615,7 +51615,7 @@
       <c r="B826" t="inlineStr"/>
       <c r="C826" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D826" t="inlineStr">
@@ -51939,7 +51939,7 @@
       <c r="B844" t="inlineStr"/>
       <c r="C844" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D844" t="inlineStr">
@@ -52323,7 +52323,7 @@
       <c r="B866" t="inlineStr"/>
       <c r="C866" t="inlineStr">
         <is>
-          <t>NorthEast BG Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
@@ -52737,7 +52737,7 @@
       <c r="B889" t="inlineStr"/>
       <c r="C889" t="inlineStr">
         <is>
-          <t>Aurizon Mineral Sands shuttle</t>
+          <t>Aurizon Mineral Sands Shuttle</t>
         </is>
       </c>
       <c r="D889" t="inlineStr">
@@ -52917,7 +52917,7 @@
       <c r="B899" t="inlineStr"/>
       <c r="C899" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
@@ -52935,7 +52935,7 @@
       <c r="B900" t="inlineStr"/>
       <c r="C900" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D900" t="inlineStr">
@@ -53385,7 +53385,7 @@
       <c r="B925" t="inlineStr"/>
       <c r="C925" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>North Eastern BG Line Service</t>
         </is>
       </c>
       <c r="D925" t="inlineStr">
@@ -54371,7 +54371,7 @@
       <c r="B980" t="inlineStr"/>
       <c r="C980" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D980" t="inlineStr">
@@ -54605,7 +54605,7 @@
       <c r="B993" t="inlineStr"/>
       <c r="C993" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D993" t="inlineStr">
@@ -54677,7 +54677,7 @@
       <c r="B997" t="inlineStr"/>
       <c r="C997" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D997" t="inlineStr">
@@ -55921,7 +55921,7 @@
       <c r="B1067" t="inlineStr"/>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1067" t="inlineStr">
@@ -57173,7 +57173,7 @@
       <c r="B1137" t="inlineStr"/>
       <c r="C1137" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1137" t="inlineStr">
@@ -57349,7 +57349,7 @@
       <c r="B1147" t="inlineStr"/>
       <c r="C1147" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1147" t="inlineStr">
@@ -57961,7 +57961,7 @@
       <c r="B1181" t="inlineStr"/>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1181" t="inlineStr">
@@ -58551,7 +58551,7 @@
       <c r="B1214" t="inlineStr"/>
       <c r="C1214" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1214" t="inlineStr">
@@ -59949,7 +59949,7 @@
       <c r="B1293" t="inlineStr"/>
       <c r="C1293" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1293" t="inlineStr">
@@ -60463,7 +60463,7 @@
       <c r="B1322" t="inlineStr"/>
       <c r="C1322" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1322" t="inlineStr">
@@ -61320,7 +61320,7 @@
       <c r="B1370" t="inlineStr"/>
       <c r="C1370" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning (Forms SN34)</t>
+          <t>Southern Highlands Service</t>
         </is>
       </c>
       <c r="D1370" t="inlineStr">
@@ -61356,7 +61356,7 @@
       <c r="B1372" t="inlineStr"/>
       <c r="C1372" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1372" t="inlineStr">
@@ -61694,7 +61694,7 @@
       <c r="B1391" t="inlineStr"/>
       <c r="C1391" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1391" t="inlineStr">
@@ -61730,7 +61730,7 @@
       <c r="B1393" t="inlineStr"/>
       <c r="C1393" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1393" t="inlineStr">
@@ -62037,7 +62037,7 @@
       <c r="B1410" t="inlineStr"/>
       <c r="C1410" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1410" t="inlineStr">
@@ -62127,7 +62127,7 @@
       <c r="B1415" t="inlineStr"/>
       <c r="C1415" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1415" t="inlineStr">
@@ -62145,7 +62145,7 @@
       <c r="B1416" t="inlineStr"/>
       <c r="C1416" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1416" t="inlineStr">
@@ -62163,7 +62163,7 @@
       <c r="B1417" t="inlineStr"/>
       <c r="C1417" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1417" t="inlineStr">
@@ -62217,7 +62217,7 @@
       <c r="B1420" t="inlineStr"/>
       <c r="C1420" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1420" t="inlineStr">
@@ -62289,7 +62289,7 @@
       <c r="B1424" t="inlineStr"/>
       <c r="C1424" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D1424" t="inlineStr">
@@ -62379,7 +62379,7 @@
       <c r="B1429" t="inlineStr"/>
       <c r="C1429" t="inlineStr">
         <is>
-          <t>Bathurst Bullet - Transfer</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D1429" t="inlineStr">
@@ -62821,7 +62821,7 @@
       <c r="B1454" t="inlineStr"/>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1454" t="inlineStr">
@@ -62893,7 +62893,7 @@
       <c r="B1458" t="inlineStr"/>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>Hunter Railcar Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1458" t="inlineStr">
@@ -63871,7 +63871,7 @@
       <c r="B1513" t="inlineStr"/>
       <c r="C1513" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1513" t="inlineStr">
@@ -63889,7 +63889,7 @@
       <c r="B1514" t="inlineStr"/>
       <c r="C1514" t="inlineStr">
         <is>
-          <t>NorthEast BG Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1514" t="inlineStr">
@@ -65917,7 +65917,7 @@
       <c r="B1628" t="inlineStr"/>
       <c r="C1628" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1628" t="inlineStr">
@@ -66727,7 +66727,7 @@
       <c r="B1673" t="inlineStr"/>
       <c r="C1673" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1673" t="inlineStr">
@@ -68667,7 +68667,7 @@
       <c r="B1787" t="inlineStr"/>
       <c r="C1787" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1787" t="inlineStr">
@@ -69509,7 +69509,7 @@
       <c r="B1834" t="inlineStr"/>
       <c r="C1834" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1834" t="inlineStr">
@@ -69527,7 +69527,7 @@
       <c r="B1835" t="inlineStr"/>
       <c r="C1835" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1835" t="inlineStr">
@@ -69563,7 +69563,7 @@
       <c r="B1837" t="inlineStr"/>
       <c r="C1837" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1837" t="inlineStr">
@@ -69599,7 +69599,7 @@
       <c r="B1839" t="inlineStr"/>
       <c r="C1839" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1839" t="inlineStr">
@@ -69743,7 +69743,7 @@
       <c r="B1847" t="inlineStr"/>
       <c r="C1847" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1847" t="inlineStr">
@@ -69779,7 +69779,7 @@
       <c r="B1849" t="inlineStr"/>
       <c r="C1849" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1849" t="inlineStr">
@@ -69995,7 +69995,7 @@
       <c r="B1861" t="inlineStr"/>
       <c r="C1861" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1861" t="inlineStr">
@@ -70157,7 +70157,7 @@
       <c r="B1870" t="inlineStr"/>
       <c r="C1870" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1870" t="inlineStr">
@@ -70247,7 +70247,7 @@
       <c r="B1875" t="inlineStr"/>
       <c r="C1875" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1875" t="inlineStr">
@@ -70265,7 +70265,7 @@
       <c r="B1876" t="inlineStr"/>
       <c r="C1876" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D1876" t="inlineStr">
@@ -70373,7 +70373,7 @@
       <c r="B1882" t="inlineStr"/>
       <c r="C1882" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1882" t="inlineStr">
@@ -70391,7 +70391,7 @@
       <c r="B1883" t="inlineStr"/>
       <c r="C1883" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1883" t="inlineStr">
@@ -70625,7 +70625,7 @@
       <c r="B1896" t="inlineStr"/>
       <c r="C1896" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1896" t="inlineStr">
@@ -70643,7 +70643,7 @@
       <c r="B1897" t="inlineStr"/>
       <c r="C1897" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1897" t="inlineStr">
@@ -70733,7 +70733,7 @@
       <c r="B1902" t="inlineStr"/>
       <c r="C1902" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1902" t="inlineStr">
@@ -70769,7 +70769,7 @@
       <c r="B1904" t="inlineStr"/>
       <c r="C1904" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1904" t="inlineStr">
@@ -70823,7 +70823,7 @@
       <c r="B1907" t="inlineStr"/>
       <c r="C1907" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1907" t="inlineStr">
@@ -73013,7 +73013,7 @@
       <c r="B2034" t="inlineStr"/>
       <c r="C2034" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (ex NT34)</t>
         </is>
       </c>
       <c r="D2034" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1120,7 +1120,7 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>North East Line BG Service</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1580,7 +1580,7 @@
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northeast Line BG Service</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2620,7 +2620,7 @@
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3562,7 +3562,7 @@
       <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr">
         <is>
-          <t>SRS/SCT Sadleirs Trip Train</t>
+          <t>SRS Light Engine</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -5516,7 +5516,7 @@
       <c r="B288" t="inlineStr"/>
       <c r="C288" t="inlineStr">
         <is>
-          <t>PN Empty Ballast</t>
+          <t>PN Ballast</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -5836,7 +5836,7 @@
       <c r="B306" t="inlineStr"/>
       <c r="C306" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Loaded Ore / Grain</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -9488,7 +9488,7 @@
       <c r="B524" t="inlineStr"/>
       <c r="C524" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
@@ -10738,7 +10738,7 @@
       <c r="B594" t="inlineStr"/>
       <c r="C594" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer (Joins SP34)</t>
+          <t>NSW Trainlink Xplorer</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
@@ -11180,7 +11180,7 @@
       <c r="B619" t="inlineStr"/>
       <c r="C619" t="inlineStr">
         <is>
-          <t>QUBE Empty Aggregates</t>
+          <t>QUBE Loaded Aggregates</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
@@ -11538,7 +11538,7 @@
       <c r="B640" t="inlineStr"/>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Aurizon Wagon Transfer</t>
+          <t>Aurizon Light Engine</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
@@ -12098,7 +12098,7 @@
       <c r="B672" t="inlineStr"/>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
@@ -12152,7 +12152,7 @@
       <c r="B675" t="inlineStr"/>
       <c r="C675" t="inlineStr">
         <is>
-          <t>Hunter Railcar Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
@@ -16012,7 +16012,7 @@
       <c r="B893" t="inlineStr"/>
       <c r="C893" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D893" t="inlineStr">
@@ -16066,7 +16066,7 @@
       <c r="B896" t="inlineStr"/>
       <c r="C896" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
@@ -16084,7 +16084,7 @@
       <c r="B897" t="inlineStr"/>
       <c r="C897" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D897" t="inlineStr">
@@ -16624,7 +16624,7 @@
       <c r="B927" t="inlineStr"/>
       <c r="C927" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D927" t="inlineStr">
@@ -17056,7 +17056,7 @@
       <c r="B951" t="inlineStr"/>
       <c r="C951" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D951" t="inlineStr">
@@ -17722,7 +17722,7 @@
       <c r="B988" t="inlineStr"/>
       <c r="C988" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D988" t="inlineStr">
@@ -17920,7 +17920,7 @@
       <c r="B999" t="inlineStr"/>
       <c r="C999" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D999" t="inlineStr">
@@ -18064,7 +18064,7 @@
       <c r="B1007" t="inlineStr"/>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1007" t="inlineStr">
@@ -18154,7 +18154,7 @@
       <c r="B1012" t="inlineStr"/>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1012" t="inlineStr">
@@ -18244,7 +18244,7 @@
       <c r="B1017" t="inlineStr"/>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1017" t="inlineStr">
@@ -18838,7 +18838,7 @@
       <c r="B1050" t="inlineStr"/>
       <c r="C1050" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1050" t="inlineStr">
@@ -18856,7 +18856,7 @@
       <c r="B1051" t="inlineStr"/>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1051" t="inlineStr">
@@ -19126,7 +19126,7 @@
       <c r="B1066" t="inlineStr"/>
       <c r="C1066" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1066" t="inlineStr">
@@ -19216,7 +19216,7 @@
       <c r="B1071" t="inlineStr"/>
       <c r="C1071" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1071" t="inlineStr">
@@ -19324,7 +19324,7 @@
       <c r="B1077" t="inlineStr"/>
       <c r="C1077" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1077" t="inlineStr">
@@ -19756,7 +19756,7 @@
       <c r="B1101" t="inlineStr"/>
       <c r="C1101" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1101" t="inlineStr">
@@ -19846,7 +19846,7 @@
       <c r="B1106" t="inlineStr"/>
       <c r="C1106" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1106" t="inlineStr">
@@ -19936,7 +19936,7 @@
       <c r="B1111" t="inlineStr"/>
       <c r="C1111" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1111" t="inlineStr">
@@ -20098,7 +20098,7 @@
       <c r="B1120" t="inlineStr"/>
       <c r="C1120" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1120" t="inlineStr">
@@ -20152,7 +20152,7 @@
       <c r="B1123" t="inlineStr"/>
       <c r="C1123" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1123" t="inlineStr">
@@ -20188,7 +20188,7 @@
       <c r="B1125" t="inlineStr"/>
       <c r="C1125" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1125" t="inlineStr">
@@ -20314,7 +20314,7 @@
       <c r="B1132" t="inlineStr"/>
       <c r="C1132" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1132" t="inlineStr">
@@ -20692,7 +20692,7 @@
       <c r="B1153" t="inlineStr"/>
       <c r="C1153" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1153" t="inlineStr">
@@ -20818,7 +20818,7 @@
       <c r="B1160" t="inlineStr"/>
       <c r="C1160" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1160" t="inlineStr">
@@ -20836,7 +20836,7 @@
       <c r="B1161" t="inlineStr"/>
       <c r="C1161" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1161" t="inlineStr">
@@ -20908,7 +20908,7 @@
       <c r="B1165" t="inlineStr"/>
       <c r="C1165" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1165" t="inlineStr">
@@ -20962,7 +20962,7 @@
       <c r="B1168" t="inlineStr"/>
       <c r="C1168" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1168" t="inlineStr">
@@ -20998,7 +20998,7 @@
       <c r="B1170" t="inlineStr"/>
       <c r="C1170" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1170" t="inlineStr">
@@ -21142,7 +21142,7 @@
       <c r="B1178" t="inlineStr"/>
       <c r="C1178" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1178" t="inlineStr">
@@ -21160,7 +21160,7 @@
       <c r="B1179" t="inlineStr"/>
       <c r="C1179" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1179" t="inlineStr">
@@ -21340,7 +21340,7 @@
       <c r="B1189" t="inlineStr"/>
       <c r="C1189" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1189" t="inlineStr">
@@ -21538,7 +21538,7 @@
       <c r="B1200" t="inlineStr"/>
       <c r="C1200" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1200" t="inlineStr">
@@ -21574,7 +21574,7 @@
       <c r="B1202" t="inlineStr"/>
       <c r="C1202" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1202" t="inlineStr">
@@ -21700,7 +21700,7 @@
       <c r="B1209" t="inlineStr"/>
       <c r="C1209" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1209" t="inlineStr">
@@ -21790,7 +21790,7 @@
       <c r="B1214" t="inlineStr"/>
       <c r="C1214" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1214" t="inlineStr">
@@ -21808,7 +21808,7 @@
       <c r="B1215" t="inlineStr"/>
       <c r="C1215" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1215" t="inlineStr">
@@ -21862,7 +21862,7 @@
       <c r="B1218" t="inlineStr"/>
       <c r="C1218" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1218" t="inlineStr">
@@ -22006,7 +22006,7 @@
       <c r="B1226" t="inlineStr"/>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1226" t="inlineStr">
@@ -22114,7 +22114,7 @@
       <c r="B1232" t="inlineStr"/>
       <c r="C1232" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1232" t="inlineStr">
@@ -22150,7 +22150,7 @@
       <c r="B1234" t="inlineStr"/>
       <c r="C1234" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1234" t="inlineStr">
@@ -22312,7 +22312,7 @@
       <c r="B1243" t="inlineStr"/>
       <c r="C1243" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1243" t="inlineStr">
@@ -22366,7 +22366,7 @@
       <c r="B1246" t="inlineStr"/>
       <c r="C1246" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1246" t="inlineStr">
@@ -22384,7 +22384,7 @@
       <c r="B1247" t="inlineStr"/>
       <c r="C1247" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1247" t="inlineStr">
@@ -22492,7 +22492,7 @@
       <c r="B1253" t="inlineStr"/>
       <c r="C1253" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1253" t="inlineStr">
@@ -23628,7 +23628,7 @@
       <c r="B1317" t="inlineStr"/>
       <c r="C1317" t="inlineStr">
         <is>
-          <t>Maintenance Train</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D1317" t="inlineStr">
@@ -24816,7 +24816,7 @@
       <c r="B1385" t="inlineStr"/>
       <c r="C1385" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>PN SFT Shunter</t>
         </is>
       </c>
       <c r="D1385" t="inlineStr">
@@ -25878,7 +25878,7 @@
       <c r="B1450" t="inlineStr"/>
       <c r="C1450" t="inlineStr">
         <is>
-          <t>QUBE Containerised Grain</t>
+          <t>QUBE Light Engine</t>
         </is>
       </c>
       <c r="D1450" t="inlineStr">
@@ -26392,7 +26392,7 @@
       <c r="B1479" t="inlineStr"/>
       <c r="C1479" t="inlineStr">
         <is>
-          <t>SSR Shunter</t>
+          <t>SSR Light Engine Movement</t>
         </is>
       </c>
       <c r="D1479" t="inlineStr">
@@ -28264,7 +28264,7 @@
       <c r="B1589" t="inlineStr"/>
       <c r="C1589" t="inlineStr">
         <is>
-          <t>PN Coal</t>
+          <t>PN Coal (Train Rake Unit 2)</t>
         </is>
       </c>
       <c r="D1589" t="inlineStr">
@@ -36536,7 +36536,7 @@
       <c r="B2049" t="inlineStr"/>
       <c r="C2049" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (Forms WT27)</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D2049" t="inlineStr">
@@ -37086,7 +37086,7 @@
       <c r="B2080" t="inlineStr"/>
       <c r="C2080" t="inlineStr">
         <is>
-          <t>ORA Coal</t>
+          <t>ORA Shunter</t>
         </is>
       </c>
       <c r="D2080" t="inlineStr">
@@ -37122,7 +37122,7 @@
       <c r="B2082" t="inlineStr"/>
       <c r="C2082" t="inlineStr">
         <is>
-          <t>ORA Light Engine</t>
+          <t>ORA Shunter</t>
         </is>
       </c>
       <c r="D2082" t="inlineStr">
@@ -37251,7 +37251,7 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Maintenance Train</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -37787,7 +37787,7 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -39179,7 +39179,7 @@
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -40269,7 +40269,7 @@
       <c r="B178" t="inlineStr"/>
       <c r="C178" t="inlineStr">
         <is>
-          <t>ORA Coal</t>
+          <t>ORA Shunter</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -42129,7 +42129,7 @@
       <c r="B284" t="inlineStr"/>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -42183,7 +42183,7 @@
       <c r="B287" t="inlineStr"/>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -44007,7 +44007,7 @@
       <c r="B389" t="inlineStr"/>
       <c r="C389" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Loaded Ore / Grain</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -44659,7 +44659,7 @@
       <c r="B427" t="inlineStr"/>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -44821,7 +44821,7 @@
       <c r="B436" t="inlineStr"/>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -44857,7 +44857,7 @@
       <c r="B438" t="inlineStr"/>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -44961,7 +44961,7 @@
       <c r="B444" t="inlineStr"/>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -44979,7 +44979,7 @@
       <c r="B445" t="inlineStr"/>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -45123,7 +45123,7 @@
       <c r="B453" t="inlineStr"/>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -45227,7 +45227,7 @@
       <c r="B459" t="inlineStr"/>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -46871,7 +46871,7 @@
       <c r="B553" t="inlineStr"/>
       <c r="C553" t="inlineStr">
         <is>
-          <t>QUBE Empty Aggregates</t>
+          <t>QUBE Loaded Aggregates</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
@@ -47569,7 +47569,7 @@
       <c r="B592" t="inlineStr"/>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
@@ -48055,7 +48055,7 @@
       <c r="B619" t="inlineStr"/>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
@@ -48289,7 +48289,7 @@
       <c r="B632" t="inlineStr"/>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
@@ -48487,7 +48487,7 @@
       <c r="B643" t="inlineStr"/>
       <c r="C643" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
@@ -49581,7 +49581,7 @@
       <c r="B704" t="inlineStr"/>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
@@ -50405,7 +50405,7 @@
       <c r="B750" t="inlineStr"/>
       <c r="C750" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
@@ -50675,7 +50675,7 @@
       <c r="B765" t="inlineStr"/>
       <c r="C765" t="inlineStr">
         <is>
-          <t>SRS/SCT Sadleirs Trip Train</t>
+          <t>SRS Light Engine</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
@@ -51951,7 +51951,7 @@
       <c r="B837" t="inlineStr"/>
       <c r="C837" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>PN SFT Shunter</t>
         </is>
       </c>
       <c r="D837" t="inlineStr">
@@ -52095,7 +52095,7 @@
       <c r="B845" t="inlineStr"/>
       <c r="C845" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
@@ -52569,7 +52569,7 @@
       <c r="B872" t="inlineStr"/>
       <c r="C872" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D872" t="inlineStr">
@@ -53199,7 +53199,7 @@
       <c r="B907" t="inlineStr"/>
       <c r="C907" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
@@ -53217,7 +53217,7 @@
       <c r="B908" t="inlineStr"/>
       <c r="C908" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D908" t="inlineStr">
@@ -54653,7 +54653,7 @@
       <c r="B988" t="inlineStr"/>
       <c r="C988" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D988" t="inlineStr">
@@ -54923,7 +54923,7 @@
       <c r="B1003" t="inlineStr"/>
       <c r="C1003" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1003" t="inlineStr">
@@ -54959,7 +54959,7 @@
       <c r="B1005" t="inlineStr"/>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1005" t="inlineStr">
@@ -55613,7 +55613,7 @@
       <c r="B1042" t="inlineStr"/>
       <c r="C1042" t="inlineStr">
         <is>
-          <t>PN Coal</t>
+          <t>PN Coal (Train Rake Unit 2)</t>
         </is>
       </c>
       <c r="D1042" t="inlineStr">
@@ -55933,7 +55933,7 @@
       <c r="B1060" t="inlineStr"/>
       <c r="C1060" t="inlineStr">
         <is>
-          <t>Aurizon Wagon Transfer</t>
+          <t>Aurizon Light Engine</t>
         </is>
       </c>
       <c r="D1060" t="inlineStr">
@@ -56465,7 +56465,7 @@
       <c r="B1090" t="inlineStr"/>
       <c r="C1090" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>North East Line BG Service</t>
         </is>
       </c>
       <c r="D1090" t="inlineStr">
@@ -56663,7 +56663,7 @@
       <c r="B1101" t="inlineStr"/>
       <c r="C1101" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D1101" t="inlineStr">
@@ -57631,7 +57631,7 @@
       <c r="B1155" t="inlineStr"/>
       <c r="C1155" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1155" t="inlineStr">
@@ -60655,7 +60655,7 @@
       <c r="B1325" t="inlineStr"/>
       <c r="C1325" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer (Joins SP34)</t>
+          <t>NSW Trainlink Xplorer</t>
         </is>
       </c>
       <c r="D1325" t="inlineStr">
@@ -61890,7 +61890,7 @@
       <c r="B1394" t="inlineStr"/>
       <c r="C1394" t="inlineStr">
         <is>
-          <t>PN Empty Ballast</t>
+          <t>PN Ballast</t>
         </is>
       </c>
       <c r="D1394" t="inlineStr">
@@ -61958,7 +61958,7 @@
       <c r="B1398" t="inlineStr"/>
       <c r="C1398" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1398" t="inlineStr">
@@ -61976,7 +61976,7 @@
       <c r="B1399" t="inlineStr"/>
       <c r="C1399" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1399" t="inlineStr">
@@ -62210,7 +62210,7 @@
       <c r="B1412" t="inlineStr"/>
       <c r="C1412" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northeast Line BG Service</t>
         </is>
       </c>
       <c r="D1412" t="inlineStr">
@@ -62445,7 +62445,7 @@
       <c r="B1425" t="inlineStr"/>
       <c r="C1425" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1425" t="inlineStr">
@@ -62535,7 +62535,7 @@
       <c r="B1430" t="inlineStr"/>
       <c r="C1430" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1430" t="inlineStr">
@@ -62855,7 +62855,7 @@
       <c r="B1448" t="inlineStr"/>
       <c r="C1448" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1448" t="inlineStr">
@@ -64459,7 +64459,7 @@
       <c r="B1538" t="inlineStr"/>
       <c r="C1538" t="inlineStr">
         <is>
-          <t>SSR Shunter</t>
+          <t>SSR Light Engine Movement</t>
         </is>
       </c>
       <c r="D1538" t="inlineStr">
@@ -66005,7 +66005,7 @@
       <c r="B1625" t="inlineStr"/>
       <c r="C1625" t="inlineStr">
         <is>
-          <t>Hunter Railcar Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1625" t="inlineStr">
@@ -66631,7 +66631,7 @@
       <c r="B1660" t="inlineStr"/>
       <c r="C1660" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (Forms WT27)</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1660" t="inlineStr">
@@ -68467,7 +68467,7 @@
       <c r="B1768" t="inlineStr"/>
       <c r="C1768" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1768" t="inlineStr">
@@ -68985,7 +68985,7 @@
       <c r="B1797" t="inlineStr"/>
       <c r="C1797" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1797" t="inlineStr">
@@ -69521,7 +69521,7 @@
       <c r="B1827" t="inlineStr"/>
       <c r="C1827" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1827" t="inlineStr">
@@ -69611,7 +69611,7 @@
       <c r="B1832" t="inlineStr"/>
       <c r="C1832" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1832" t="inlineStr">
@@ -69665,7 +69665,7 @@
       <c r="B1835" t="inlineStr"/>
       <c r="C1835" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1835" t="inlineStr">
@@ -69899,7 +69899,7 @@
       <c r="B1848" t="inlineStr"/>
       <c r="C1848" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1848" t="inlineStr">
@@ -69953,7 +69953,7 @@
       <c r="B1851" t="inlineStr"/>
       <c r="C1851" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1851" t="inlineStr">
@@ -70061,7 +70061,7 @@
       <c r="B1857" t="inlineStr"/>
       <c r="C1857" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1857" t="inlineStr">
@@ -70097,7 +70097,7 @@
       <c r="B1859" t="inlineStr"/>
       <c r="C1859" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1859" t="inlineStr">
@@ -70133,7 +70133,7 @@
       <c r="B1861" t="inlineStr"/>
       <c r="C1861" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1861" t="inlineStr">
@@ -70295,7 +70295,7 @@
       <c r="B1870" t="inlineStr"/>
       <c r="C1870" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1870" t="inlineStr">
@@ -70763,7 +70763,7 @@
       <c r="B1896" t="inlineStr"/>
       <c r="C1896" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1896" t="inlineStr">
@@ -70943,7 +70943,7 @@
       <c r="B1906" t="inlineStr"/>
       <c r="C1906" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1906" t="inlineStr">
@@ -70979,7 +70979,7 @@
       <c r="B1908" t="inlineStr"/>
       <c r="C1908" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1908" t="inlineStr">
@@ -71123,7 +71123,7 @@
       <c r="B1916" t="inlineStr"/>
       <c r="C1916" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1916" t="inlineStr">
@@ -71177,7 +71177,7 @@
       <c r="B1919" t="inlineStr"/>
       <c r="C1919" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1919" t="inlineStr">
@@ -72059,7 +72059,7 @@
       <c r="B1972" t="inlineStr"/>
       <c r="C1972" t="inlineStr">
         <is>
-          <t>QUBE Containerised Grain</t>
+          <t>QUBE Light Engine</t>
         </is>
       </c>
       <c r="D1972" t="inlineStr">
@@ -73547,7 +73547,7 @@
       <c r="B2056" t="inlineStr"/>
       <c r="C2056" t="inlineStr">
         <is>
-          <t>ORA Light Engine</t>
+          <t>ORA Shunter</t>
         </is>
       </c>
       <c r="D2056" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -634,7 +634,7 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -670,7 +670,7 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>North East Line BG Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -688,7 +688,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -814,7 +814,7 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1120,7 +1120,7 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>North East Line BG Service</t>
+          <t>North Eastern Line BG Service</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1138,7 +1138,7 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1174,7 +1174,7 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1386,7 +1386,7 @@
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1616,7 +1616,7 @@
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1742,7 +1742,7 @@
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -1972,7 +1972,7 @@
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2152,7 +2152,7 @@
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2242,7 +2242,7 @@
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2332,7 +2332,7 @@
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2386,7 +2386,7 @@
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2602,7 +2602,7 @@
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -2692,7 +2692,7 @@
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -2710,7 +2710,7 @@
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -2728,7 +2728,7 @@
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3048,7 +3048,7 @@
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>QUBE Containerised Freight</t>
+          <t>Qube Trip Train</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -3350,7 +3350,7 @@
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Aurizon Light Engine Movement</t>
+          <t>Aurizon Wagon Transfer</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -8834,7 +8834,7 @@
       <c r="B485" t="inlineStr"/>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Aurizon Empty Grain</t>
+          <t>Aurizon Loaded Grain</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -11126,7 +11126,7 @@
       <c r="B616" t="inlineStr"/>
       <c r="C616" t="inlineStr">
         <is>
-          <t>QUBE Maryvale Paper Train</t>
+          <t>QUBE Light Engine Movement</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
@@ -12224,7 +12224,7 @@
       <c r="B679" t="inlineStr"/>
       <c r="C679" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
@@ -15562,7 +15562,7 @@
       <c r="B868" t="inlineStr"/>
       <c r="C868" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D868" t="inlineStr">
@@ -15580,7 +15580,7 @@
       <c r="B869" t="inlineStr"/>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D869" t="inlineStr">
@@ -15652,7 +15652,7 @@
       <c r="B873" t="inlineStr"/>
       <c r="C873" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D873" t="inlineStr">
@@ -15724,7 +15724,7 @@
       <c r="B877" t="inlineStr"/>
       <c r="C877" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D877" t="inlineStr">
@@ -15796,7 +15796,7 @@
       <c r="B881" t="inlineStr"/>
       <c r="C881" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D881" t="inlineStr">
@@ -15886,7 +15886,7 @@
       <c r="B886" t="inlineStr"/>
       <c r="C886" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D886" t="inlineStr">
@@ -16048,7 +16048,7 @@
       <c r="B895" t="inlineStr"/>
       <c r="C895" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D895" t="inlineStr">
@@ -16084,7 +16084,7 @@
       <c r="B897" t="inlineStr"/>
       <c r="C897" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D897" t="inlineStr">
@@ -16120,7 +16120,7 @@
       <c r="B899" t="inlineStr"/>
       <c r="C899" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
@@ -16534,7 +16534,7 @@
       <c r="B922" t="inlineStr"/>
       <c r="C922" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D922" t="inlineStr">
@@ -16822,7 +16822,7 @@
       <c r="B938" t="inlineStr"/>
       <c r="C938" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D938" t="inlineStr">
@@ -16966,7 +16966,7 @@
       <c r="B946" t="inlineStr"/>
       <c r="C946" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D946" t="inlineStr">
@@ -17038,7 +17038,7 @@
       <c r="B950" t="inlineStr"/>
       <c r="C950" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D950" t="inlineStr">
@@ -17848,7 +17848,7 @@
       <c r="B995" t="inlineStr"/>
       <c r="C995" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D995" t="inlineStr">
@@ -18082,7 +18082,7 @@
       <c r="B1008" t="inlineStr"/>
       <c r="C1008" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1008" t="inlineStr">
@@ -18172,7 +18172,7 @@
       <c r="B1013" t="inlineStr"/>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1013" t="inlineStr">
@@ -18244,7 +18244,7 @@
       <c r="B1017" t="inlineStr"/>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1017" t="inlineStr">
@@ -18262,7 +18262,7 @@
       <c r="B1018" t="inlineStr"/>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1018" t="inlineStr">
@@ -18658,7 +18658,7 @@
       <c r="B1040" t="inlineStr"/>
       <c r="C1040" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1040" t="inlineStr">
@@ -18820,7 +18820,7 @@
       <c r="B1049" t="inlineStr"/>
       <c r="C1049" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1049" t="inlineStr">
@@ -18856,7 +18856,7 @@
       <c r="B1051" t="inlineStr"/>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1051" t="inlineStr">
@@ -18874,7 +18874,7 @@
       <c r="B1052" t="inlineStr"/>
       <c r="C1052" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1052" t="inlineStr">
@@ -18928,7 +18928,7 @@
       <c r="B1055" t="inlineStr"/>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1055" t="inlineStr">
@@ -18946,7 +18946,7 @@
       <c r="B1056" t="inlineStr"/>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1056" t="inlineStr">
@@ -19288,7 +19288,7 @@
       <c r="B1075" t="inlineStr"/>
       <c r="C1075" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1075" t="inlineStr">
@@ -19720,7 +19720,7 @@
       <c r="B1099" t="inlineStr"/>
       <c r="C1099" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1099" t="inlineStr">
@@ -19882,7 +19882,7 @@
       <c r="B1108" t="inlineStr"/>
       <c r="C1108" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1108" t="inlineStr">
@@ -19900,7 +19900,7 @@
       <c r="B1109" t="inlineStr"/>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1109" t="inlineStr">
@@ -19972,7 +19972,7 @@
       <c r="B1113" t="inlineStr"/>
       <c r="C1113" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1113" t="inlineStr">
@@ -20476,7 +20476,7 @@
       <c r="B1141" t="inlineStr"/>
       <c r="C1141" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1141" t="inlineStr">
@@ -20512,7 +20512,7 @@
       <c r="B1143" t="inlineStr"/>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D1143" t="inlineStr">
@@ -20854,7 +20854,7 @@
       <c r="B1162" t="inlineStr"/>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1162" t="inlineStr">
@@ -21088,7 +21088,7 @@
       <c r="B1175" t="inlineStr"/>
       <c r="C1175" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1175" t="inlineStr">
@@ -21376,7 +21376,7 @@
       <c r="B1191" t="inlineStr"/>
       <c r="C1191" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1191" t="inlineStr">
@@ -21394,7 +21394,7 @@
       <c r="B1192" t="inlineStr"/>
       <c r="C1192" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1192" t="inlineStr">
@@ -21466,7 +21466,7 @@
       <c r="B1196" t="inlineStr"/>
       <c r="C1196" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1196" t="inlineStr">
@@ -21502,7 +21502,7 @@
       <c r="B1198" t="inlineStr"/>
       <c r="C1198" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1198" t="inlineStr">
@@ -21520,7 +21520,7 @@
       <c r="B1199" t="inlineStr"/>
       <c r="C1199" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1199" t="inlineStr">
@@ -21610,7 +21610,7 @@
       <c r="B1204" t="inlineStr"/>
       <c r="C1204" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1204" t="inlineStr">
@@ -21826,7 +21826,7 @@
       <c r="B1216" t="inlineStr"/>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1216" t="inlineStr">
@@ -22042,7 +22042,7 @@
       <c r="B1228" t="inlineStr"/>
       <c r="C1228" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1228" t="inlineStr">
@@ -22060,7 +22060,7 @@
       <c r="B1229" t="inlineStr"/>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1229" t="inlineStr">
@@ -22078,7 +22078,7 @@
       <c r="B1230" t="inlineStr"/>
       <c r="C1230" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1230" t="inlineStr">
@@ -22114,7 +22114,7 @@
       <c r="B1232" t="inlineStr"/>
       <c r="C1232" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1232" t="inlineStr">
@@ -22276,7 +22276,7 @@
       <c r="B1241" t="inlineStr"/>
       <c r="C1241" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1241" t="inlineStr">
@@ -22348,7 +22348,7 @@
       <c r="B1245" t="inlineStr"/>
       <c r="C1245" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1245" t="inlineStr">
@@ -22420,7 +22420,7 @@
       <c r="B1249" t="inlineStr"/>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1249" t="inlineStr">
@@ -22456,7 +22456,7 @@
       <c r="B1251" t="inlineStr"/>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1251" t="inlineStr">
@@ -22510,7 +22510,7 @@
       <c r="B1254" t="inlineStr"/>
       <c r="C1254" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1254" t="inlineStr">
@@ -22546,7 +22546,7 @@
       <c r="B1256" t="inlineStr"/>
       <c r="C1256" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1256" t="inlineStr">
@@ -22600,7 +22600,7 @@
       <c r="B1259" t="inlineStr"/>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1259" t="inlineStr">
@@ -24486,7 +24486,7 @@
       <c r="B1366" t="inlineStr"/>
       <c r="C1366" t="inlineStr">
         <is>
-          <t>PN Fuel Train</t>
+          <t>PN Loaded Fuel Service</t>
         </is>
       </c>
       <c r="D1366" t="inlineStr">
@@ -26788,7 +26788,7 @@
       <c r="B1503" t="inlineStr"/>
       <c r="C1503" t="inlineStr">
         <is>
-          <t>North-East BG Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D1503" t="inlineStr">
@@ -27180,7 +27180,7 @@
       <c r="B1525" t="inlineStr"/>
       <c r="C1525" t="inlineStr">
         <is>
-          <t>SCT Intermodal</t>
+          <t>SCT Light Engine</t>
         </is>
       </c>
       <c r="D1525" t="inlineStr">
@@ -37377,7 +37377,7 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -38605,7 +38605,7 @@
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Aurizon Empty Grain</t>
+          <t>Aurizon Loaded Grain</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -39573,7 +39573,7 @@
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -39731,7 +39731,7 @@
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -40251,7 +40251,7 @@
       <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -40779,7 +40779,7 @@
       <c r="B205" t="inlineStr"/>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -41193,7 +41193,7 @@
       <c r="B228" t="inlineStr"/>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -42201,7 +42201,7 @@
       <c r="B286" t="inlineStr"/>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -42579,7 +42579,7 @@
       <c r="B307" t="inlineStr"/>
       <c r="C307" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -44731,7 +44731,7 @@
       <c r="B429" t="inlineStr"/>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -45803,7 +45803,7 @@
       <c r="B489" t="inlineStr"/>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -46631,7 +46631,7 @@
       <c r="B537" t="inlineStr"/>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
@@ -47177,7 +47177,7 @@
       <c r="B568" t="inlineStr"/>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
@@ -47335,7 +47335,7 @@
       <c r="B577" t="inlineStr"/>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
@@ -47443,7 +47443,7 @@
       <c r="B583" t="inlineStr"/>
       <c r="C583" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
@@ -47857,7 +47857,7 @@
       <c r="B606" t="inlineStr"/>
       <c r="C606" t="inlineStr">
         <is>
-          <t>QUBE Containerised Freight</t>
+          <t>Qube Trip Train</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
@@ -48127,7 +48127,7 @@
       <c r="B621" t="inlineStr"/>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
@@ -48487,7 +48487,7 @@
       <c r="B641" t="inlineStr"/>
       <c r="C641" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
@@ -48919,7 +48919,7 @@
       <c r="B665" t="inlineStr"/>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
@@ -49351,7 +49351,7 @@
       <c r="B689" t="inlineStr"/>
       <c r="C689" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
@@ -50117,7 +50117,7 @@
       <c r="B732" t="inlineStr"/>
       <c r="C732" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
@@ -50585,7 +50585,7 @@
       <c r="B758" t="inlineStr"/>
       <c r="C758" t="inlineStr">
         <is>
-          <t>Aurizon Light Engine Movement</t>
+          <t>Aurizon Wagon Transfer</t>
         </is>
       </c>
       <c r="D758" t="inlineStr">
@@ -52275,7 +52275,7 @@
       <c r="B853" t="inlineStr"/>
       <c r="C853" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D853" t="inlineStr">
@@ -52767,7 +52767,7 @@
       <c r="B881" t="inlineStr"/>
       <c r="C881" t="inlineStr">
         <is>
-          <t>QUBE Maryvale Paper Train</t>
+          <t>QUBE Light Engine Movement</t>
         </is>
       </c>
       <c r="D881" t="inlineStr">
@@ -53325,7 +53325,7 @@
       <c r="B912" t="inlineStr"/>
       <c r="C912" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D912" t="inlineStr">
@@ -54977,7 +54977,7 @@
       <c r="B1004" t="inlineStr"/>
       <c r="C1004" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1004" t="inlineStr">
@@ -54995,7 +54995,7 @@
       <c r="B1005" t="inlineStr"/>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1005" t="inlineStr">
@@ -55703,7 +55703,7 @@
       <c r="B1045" t="inlineStr"/>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>North East Line BG Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1045" t="inlineStr">
@@ -55793,7 +55793,7 @@
       <c r="B1050" t="inlineStr"/>
       <c r="C1050" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1050" t="inlineStr">
@@ -56131,7 +56131,7 @@
       <c r="B1069" t="inlineStr"/>
       <c r="C1069" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1069" t="inlineStr">
@@ -56221,7 +56221,7 @@
       <c r="B1074" t="inlineStr"/>
       <c r="C1074" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1074" t="inlineStr">
@@ -56275,7 +56275,7 @@
       <c r="B1077" t="inlineStr"/>
       <c r="C1077" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1077" t="inlineStr">
@@ -56537,7 +56537,7 @@
       <c r="B1092" t="inlineStr"/>
       <c r="C1092" t="inlineStr">
         <is>
-          <t>North East Line BG Service</t>
+          <t>North Eastern Line BG Service</t>
         </is>
       </c>
       <c r="D1092" t="inlineStr">
@@ -57527,7 +57527,7 @@
       <c r="B1147" t="inlineStr"/>
       <c r="C1147" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1147" t="inlineStr">
@@ -57703,7 +57703,7 @@
       <c r="B1157" t="inlineStr"/>
       <c r="C1157" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1157" t="inlineStr">
@@ -57757,7 +57757,7 @@
       <c r="B1160" t="inlineStr"/>
       <c r="C1160" t="inlineStr">
         <is>
-          <t>North-East BG Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D1160" t="inlineStr">
@@ -60425,7 +60425,7 @@
       <c r="B1310" t="inlineStr"/>
       <c r="C1310" t="inlineStr">
         <is>
-          <t>SCT Intermodal</t>
+          <t>SCT Light Engine</t>
         </is>
       </c>
       <c r="D1310" t="inlineStr">
@@ -60587,7 +60587,7 @@
       <c r="B1319" t="inlineStr"/>
       <c r="C1319" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1319" t="inlineStr">
@@ -60641,7 +60641,7 @@
       <c r="B1322" t="inlineStr"/>
       <c r="C1322" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D1322" t="inlineStr">
@@ -60817,7 +60817,7 @@
       <c r="B1332" t="inlineStr"/>
       <c r="C1332" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1332" t="inlineStr">
@@ -61043,7 +61043,7 @@
       <c r="B1345" t="inlineStr"/>
       <c r="C1345" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1345" t="inlineStr">
@@ -61710,7 +61710,7 @@
       <c r="B1382" t="inlineStr"/>
       <c r="C1382" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1382" t="inlineStr">
@@ -62030,7 +62030,7 @@
       <c r="B1400" t="inlineStr"/>
       <c r="C1400" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1400" t="inlineStr">
@@ -62246,7 +62246,7 @@
       <c r="B1412" t="inlineStr"/>
       <c r="C1412" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1412" t="inlineStr">
@@ -62427,7 +62427,7 @@
       <c r="B1422" t="inlineStr"/>
       <c r="C1422" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1422" t="inlineStr">
@@ -62481,7 +62481,7 @@
       <c r="B1425" t="inlineStr"/>
       <c r="C1425" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1425" t="inlineStr">
@@ -62517,7 +62517,7 @@
       <c r="B1427" t="inlineStr"/>
       <c r="C1427" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1427" t="inlineStr">
@@ -62535,7 +62535,7 @@
       <c r="B1428" t="inlineStr"/>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1428" t="inlineStr">
@@ -62571,7 +62571,7 @@
       <c r="B1430" t="inlineStr"/>
       <c r="C1430" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1430" t="inlineStr">
@@ -62607,7 +62607,7 @@
       <c r="B1432" t="inlineStr"/>
       <c r="C1432" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1432" t="inlineStr">
@@ -62891,7 +62891,7 @@
       <c r="B1448" t="inlineStr"/>
       <c r="C1448" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1448" t="inlineStr">
@@ -63337,7 +63337,7 @@
       <c r="B1473" t="inlineStr"/>
       <c r="C1473" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1473" t="inlineStr">
@@ -64225,7 +64225,7 @@
       <c r="B1523" t="inlineStr"/>
       <c r="C1523" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1523" t="inlineStr">
@@ -64657,7 +64657,7 @@
       <c r="B1547" t="inlineStr"/>
       <c r="C1547" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1547" t="inlineStr">
@@ -65113,7 +65113,7 @@
       <c r="B1573" t="inlineStr"/>
       <c r="C1573" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1573" t="inlineStr">
@@ -65131,7 +65131,7 @@
       <c r="B1574" t="inlineStr"/>
       <c r="C1574" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1574" t="inlineStr">
@@ -66113,7 +66113,7 @@
       <c r="B1629" t="inlineStr"/>
       <c r="C1629" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1629" t="inlineStr">
@@ -66865,7 +66865,7 @@
       <c r="B1671" t="inlineStr"/>
       <c r="C1671" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1671" t="inlineStr">
@@ -66991,7 +66991,7 @@
       <c r="B1678" t="inlineStr"/>
       <c r="C1678" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1678" t="inlineStr">
@@ -67009,7 +67009,7 @@
       <c r="B1679" t="inlineStr"/>
       <c r="C1679" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1679" t="inlineStr">
@@ -69737,7 +69737,7 @@
       <c r="B1837" t="inlineStr"/>
       <c r="C1837" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1837" t="inlineStr">
@@ -69827,7 +69827,7 @@
       <c r="B1842" t="inlineStr"/>
       <c r="C1842" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1842" t="inlineStr">
@@ -69881,7 +69881,7 @@
       <c r="B1845" t="inlineStr"/>
       <c r="C1845" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1845" t="inlineStr">
@@ -69953,7 +69953,7 @@
       <c r="B1849" t="inlineStr"/>
       <c r="C1849" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1849" t="inlineStr">
@@ -69971,7 +69971,7 @@
       <c r="B1850" t="inlineStr"/>
       <c r="C1850" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1850" t="inlineStr">
@@ -70115,7 +70115,7 @@
       <c r="B1858" t="inlineStr"/>
       <c r="C1858" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1858" t="inlineStr">
@@ -70169,7 +70169,7 @@
       <c r="B1861" t="inlineStr"/>
       <c r="C1861" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1861" t="inlineStr">
@@ -70187,7 +70187,7 @@
       <c r="B1862" t="inlineStr"/>
       <c r="C1862" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1862" t="inlineStr">
@@ -70205,7 +70205,7 @@
       <c r="B1863" t="inlineStr"/>
       <c r="C1863" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1863" t="inlineStr">
@@ -70619,7 +70619,7 @@
       <c r="B1886" t="inlineStr"/>
       <c r="C1886" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1886" t="inlineStr">
@@ -70763,7 +70763,7 @@
       <c r="B1894" t="inlineStr"/>
       <c r="C1894" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1894" t="inlineStr">
@@ -70799,7 +70799,7 @@
       <c r="B1896" t="inlineStr"/>
       <c r="C1896" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1896" t="inlineStr">
@@ -70835,7 +70835,7 @@
       <c r="B1898" t="inlineStr"/>
       <c r="C1898" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1898" t="inlineStr">
@@ -71015,7 +71015,7 @@
       <c r="B1908" t="inlineStr"/>
       <c r="C1908" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1908" t="inlineStr">
@@ -71123,7 +71123,7 @@
       <c r="B1914" t="inlineStr"/>
       <c r="C1914" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1914" t="inlineStr">
@@ -71195,7 +71195,7 @@
       <c r="B1918" t="inlineStr"/>
       <c r="C1918" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1918" t="inlineStr">
@@ -71231,7 +71231,7 @@
       <c r="B1920" t="inlineStr"/>
       <c r="C1920" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1920" t="inlineStr">
@@ -73723,7 +73723,7 @@
       <c r="B2064" t="inlineStr"/>
       <c r="C2064" t="inlineStr">
         <is>
-          <t>PN Fuel Train</t>
+          <t>PN Loaded Fuel Service</t>
         </is>
       </c>
       <c r="D2064" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -976,7 +976,7 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1120,7 +1120,7 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>North Eastern Line BG Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1368,7 +1368,7 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1598,7 +1598,7 @@
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2368,7 +2368,7 @@
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5786,7 +5786,7 @@
       <c r="B303" t="inlineStr"/>
       <c r="C303" t="inlineStr">
         <is>
-          <t>PN Trip Train, pre 1821</t>
+          <t>PN Loaded Containerised Logs</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -6484,7 +6484,7 @@
       <c r="B342" t="inlineStr"/>
       <c r="C342" t="inlineStr">
         <is>
-          <t>PN Morandoo Shunter</t>
+          <t>PN Port Waratah Shunter</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -6502,7 +6502,7 @@
       <c r="B343" t="inlineStr"/>
       <c r="C343" t="inlineStr">
         <is>
-          <t>PN Grain Shuttle</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -7538,7 +7538,7 @@
       <c r="B405" t="inlineStr"/>
       <c r="C405" t="inlineStr">
         <is>
-          <t>QUBE Trip Train</t>
+          <t>Qube Light Engine</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -9488,7 +9488,7 @@
       <c r="B524" t="inlineStr"/>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Aurizon Empty Grain</t>
+          <t>Cockburn Cement Empty Coal</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
@@ -9614,7 +9614,7 @@
       <c r="B531" t="inlineStr"/>
       <c r="C531" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
@@ -11162,7 +11162,7 @@
       <c r="B618" t="inlineStr"/>
       <c r="C618" t="inlineStr">
         <is>
-          <t>PN Wagon Transfer</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
@@ -11736,7 +11736,7 @@
       <c r="B651" t="inlineStr"/>
       <c r="C651" t="inlineStr">
         <is>
-          <t>Aurizon Empty Ore</t>
+          <t>Aurizon Loaded Iron Ore</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
@@ -12044,7 +12044,7 @@
       <c r="B669" t="inlineStr"/>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
@@ -12224,7 +12224,7 @@
       <c r="B679" t="inlineStr"/>
       <c r="C679" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
@@ -12242,7 +12242,7 @@
       <c r="B680" t="inlineStr"/>
       <c r="C680" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
@@ -14726,7 +14726,7 @@
       <c r="B820" t="inlineStr"/>
       <c r="C820" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Southern Highlands Service</t>
         </is>
       </c>
       <c r="D820" t="inlineStr">
@@ -14834,7 +14834,7 @@
       <c r="B826" t="inlineStr"/>
       <c r="C826" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D826" t="inlineStr">
@@ -14866,7 +14866,7 @@
       <c r="B828" t="inlineStr"/>
       <c r="C828" t="inlineStr">
         <is>
-          <t>Additional Bathurst Service</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D828" t="inlineStr">
@@ -15616,7 +15616,7 @@
       <c r="B871" t="inlineStr"/>
       <c r="C871" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D871" t="inlineStr">
@@ -15886,7 +15886,7 @@
       <c r="B886" t="inlineStr"/>
       <c r="C886" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D886" t="inlineStr">
@@ -16120,7 +16120,7 @@
       <c r="B899" t="inlineStr"/>
       <c r="C899" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
@@ -16210,7 +16210,7 @@
       <c r="B904" t="inlineStr"/>
       <c r="C904" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D904" t="inlineStr">
@@ -16678,7 +16678,7 @@
       <c r="B930" t="inlineStr"/>
       <c r="C930" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D930" t="inlineStr">
@@ -17110,7 +17110,7 @@
       <c r="B954" t="inlineStr"/>
       <c r="C954" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D954" t="inlineStr">
@@ -17218,7 +17218,7 @@
       <c r="B960" t="inlineStr"/>
       <c r="C960" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D960" t="inlineStr">
@@ -17974,7 +17974,7 @@
       <c r="B1002" t="inlineStr"/>
       <c r="C1002" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1002" t="inlineStr">
@@ -18136,7 +18136,7 @@
       <c r="B1011" t="inlineStr"/>
       <c r="C1011" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1011" t="inlineStr">
@@ -18172,7 +18172,7 @@
       <c r="B1013" t="inlineStr"/>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1013" t="inlineStr">
@@ -18208,7 +18208,7 @@
       <c r="B1015" t="inlineStr"/>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1015" t="inlineStr">
@@ -18694,7 +18694,7 @@
       <c r="B1042" t="inlineStr"/>
       <c r="C1042" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1042" t="inlineStr">
@@ -18730,7 +18730,7 @@
       <c r="B1044" t="inlineStr"/>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1044" t="inlineStr">
@@ -18766,7 +18766,7 @@
       <c r="B1046" t="inlineStr"/>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1046" t="inlineStr">
@@ -18892,7 +18892,7 @@
       <c r="B1053" t="inlineStr"/>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1053" t="inlineStr">
@@ -18964,7 +18964,7 @@
       <c r="B1057" t="inlineStr"/>
       <c r="C1057" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1057" t="inlineStr">
@@ -19054,7 +19054,7 @@
       <c r="B1062" t="inlineStr"/>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1062" t="inlineStr">
@@ -19486,7 +19486,7 @@
       <c r="B1086" t="inlineStr"/>
       <c r="C1086" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1086" t="inlineStr">
@@ -19738,7 +19738,7 @@
       <c r="B1100" t="inlineStr"/>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1100" t="inlineStr">
@@ -19756,7 +19756,7 @@
       <c r="B1101" t="inlineStr"/>
       <c r="C1101" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1101" t="inlineStr">
@@ -19828,7 +19828,7 @@
       <c r="B1105" t="inlineStr"/>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1105" t="inlineStr">
@@ -19918,7 +19918,7 @@
       <c r="B1110" t="inlineStr"/>
       <c r="C1110" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1110" t="inlineStr">
@@ -20098,7 +20098,7 @@
       <c r="B1120" t="inlineStr"/>
       <c r="C1120" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1120" t="inlineStr">
@@ -20170,7 +20170,7 @@
       <c r="B1124" t="inlineStr"/>
       <c r="C1124" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1124" t="inlineStr">
@@ -20224,7 +20224,7 @@
       <c r="B1127" t="inlineStr"/>
       <c r="C1127" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1127" t="inlineStr">
@@ -20638,7 +20638,7 @@
       <c r="B1150" t="inlineStr"/>
       <c r="C1150" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1150" t="inlineStr">
@@ -20926,7 +20926,7 @@
       <c r="B1166" t="inlineStr"/>
       <c r="C1166" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1166" t="inlineStr">
@@ -21088,7 +21088,7 @@
       <c r="B1175" t="inlineStr"/>
       <c r="C1175" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1175" t="inlineStr">
@@ -21142,7 +21142,7 @@
       <c r="B1178" t="inlineStr"/>
       <c r="C1178" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1178" t="inlineStr">
@@ -21268,7 +21268,7 @@
       <c r="B1185" t="inlineStr"/>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1185" t="inlineStr">
@@ -21340,7 +21340,7 @@
       <c r="B1189" t="inlineStr"/>
       <c r="C1189" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1189" t="inlineStr">
@@ -21394,7 +21394,7 @@
       <c r="B1192" t="inlineStr"/>
       <c r="C1192" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1192" t="inlineStr">
@@ -21430,7 +21430,7 @@
       <c r="B1194" t="inlineStr"/>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1194" t="inlineStr">
@@ -21448,7 +21448,7 @@
       <c r="B1195" t="inlineStr"/>
       <c r="C1195" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1195" t="inlineStr">
@@ -21556,7 +21556,7 @@
       <c r="B1201" t="inlineStr"/>
       <c r="C1201" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1201" t="inlineStr">
@@ -21610,7 +21610,7 @@
       <c r="B1204" t="inlineStr"/>
       <c r="C1204" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1204" t="inlineStr">
@@ -21628,7 +21628,7 @@
       <c r="B1205" t="inlineStr"/>
       <c r="C1205" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1205" t="inlineStr">
@@ -21700,7 +21700,7 @@
       <c r="B1209" t="inlineStr"/>
       <c r="C1209" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1209" t="inlineStr">
@@ -21736,7 +21736,7 @@
       <c r="B1211" t="inlineStr"/>
       <c r="C1211" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1211" t="inlineStr">
@@ -21862,7 +21862,7 @@
       <c r="B1218" t="inlineStr"/>
       <c r="C1218" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1218" t="inlineStr">
@@ -21880,7 +21880,7 @@
       <c r="B1219" t="inlineStr"/>
       <c r="C1219" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1219" t="inlineStr">
@@ -22078,7 +22078,7 @@
       <c r="B1230" t="inlineStr"/>
       <c r="C1230" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1230" t="inlineStr">
@@ -22096,7 +22096,7 @@
       <c r="B1231" t="inlineStr"/>
       <c r="C1231" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1231" t="inlineStr">
@@ -22438,7 +22438,7 @@
       <c r="B1250" t="inlineStr"/>
       <c r="C1250" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1250" t="inlineStr">
@@ -22456,7 +22456,7 @@
       <c r="B1251" t="inlineStr"/>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1251" t="inlineStr">
@@ -22474,7 +22474,7 @@
       <c r="B1252" t="inlineStr"/>
       <c r="C1252" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1252" t="inlineStr">
@@ -22492,7 +22492,7 @@
       <c r="B1253" t="inlineStr"/>
       <c r="C1253" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1253" t="inlineStr">
@@ -22564,7 +22564,7 @@
       <c r="B1257" t="inlineStr"/>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1257" t="inlineStr">
@@ -22582,7 +22582,7 @@
       <c r="B1258" t="inlineStr"/>
       <c r="C1258" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1258" t="inlineStr">
@@ -23434,7 +23434,7 @@
       <c r="B1306" t="inlineStr"/>
       <c r="C1306" t="inlineStr">
         <is>
-          <t>NR20</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D1306" t="inlineStr">
@@ -24622,7 +24622,7 @@
       <c r="B1374" t="inlineStr"/>
       <c r="C1374" t="inlineStr">
         <is>
-          <t>PN Infrabuild Steel</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D1374" t="inlineStr">
@@ -27252,7 +27252,7 @@
       <c r="B1529" t="inlineStr"/>
       <c r="C1529" t="inlineStr">
         <is>
-          <t>SCT Steel Transfer</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D1529" t="inlineStr">
@@ -36752,7 +36752,7 @@
       <c r="B2061" t="inlineStr"/>
       <c r="C2061" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D2061" t="inlineStr">
@@ -37230,7 +37230,7 @@
       <c r="B2088" t="inlineStr"/>
       <c r="C2088" t="inlineStr">
         <is>
-          <t>ORA Shunter</t>
+          <t>ORA Coal</t>
         </is>
       </c>
       <c r="D2088" t="inlineStr">
@@ -38455,7 +38455,7 @@
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SCT Steel Transfer</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -40233,7 +40233,7 @@
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Aurizon Empty Ore</t>
+          <t>Aurizon Loaded Iron Ore</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -40323,7 +40323,7 @@
       <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -40851,7 +40851,7 @@
       <c r="B207" t="inlineStr"/>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -42201,7 +42201,7 @@
       <c r="B284" t="inlineStr"/>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -44595,7 +44595,7 @@
       <c r="B419" t="inlineStr"/>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -45001,7 +45001,7 @@
       <c r="B442" t="inlineStr"/>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -45267,7 +45267,7 @@
       <c r="B457" t="inlineStr"/>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -45425,7 +45425,7 @@
       <c r="B466" t="inlineStr"/>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -47087,7 +47087,7 @@
       <c r="B561" t="inlineStr"/>
       <c r="C561" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
@@ -47965,7 +47965,7 @@
       <c r="B610" t="inlineStr"/>
       <c r="C610" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
@@ -48055,7 +48055,7 @@
       <c r="B615" t="inlineStr"/>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -48127,7 +48127,7 @@
       <c r="B619" t="inlineStr"/>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
@@ -48613,7 +48613,7 @@
       <c r="B646" t="inlineStr"/>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
@@ -48631,7 +48631,7 @@
       <c r="B647" t="inlineStr"/>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
@@ -49405,7 +49405,7 @@
       <c r="B690" t="inlineStr"/>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
@@ -49725,7 +49725,7 @@
       <c r="B708" t="inlineStr"/>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
@@ -51089,7 +51089,7 @@
       <c r="B784" t="inlineStr"/>
       <c r="C784" t="inlineStr">
         <is>
-          <t>PN Trip Train, pre 1821</t>
+          <t>PN Loaded Containerised Logs</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
@@ -51387,7 +51387,7 @@
       <c r="B801" t="inlineStr"/>
       <c r="C801" t="inlineStr">
         <is>
-          <t>NR20</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D801" t="inlineStr">
@@ -51505,7 +51505,7 @@
       <c r="B808" t="inlineStr"/>
       <c r="C808" t="inlineStr">
         <is>
-          <t>ORA Shunter</t>
+          <t>ORA Coal</t>
         </is>
       </c>
       <c r="D808" t="inlineStr">
@@ -51955,7 +51955,7 @@
       <c r="B833" t="inlineStr"/>
       <c r="C833" t="inlineStr">
         <is>
-          <t>PN Wagon Transfer</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D833" t="inlineStr">
@@ -52167,7 +52167,7 @@
       <c r="B845" t="inlineStr"/>
       <c r="C845" t="inlineStr">
         <is>
-          <t>PN Morandoo Shunter</t>
+          <t>PN Port Waratah Shunter</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
@@ -52275,7 +52275,7 @@
       <c r="B851" t="inlineStr"/>
       <c r="C851" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D851" t="inlineStr">
@@ -52713,7 +52713,7 @@
       <c r="B876" t="inlineStr"/>
       <c r="C876" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D876" t="inlineStr">
@@ -53343,7 +53343,7 @@
       <c r="B911" t="inlineStr"/>
       <c r="C911" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D911" t="inlineStr">
@@ -53397,7 +53397,7 @@
       <c r="B914" t="inlineStr"/>
       <c r="C914" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D914" t="inlineStr">
@@ -53469,7 +53469,7 @@
       <c r="B918" t="inlineStr"/>
       <c r="C918" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D918" t="inlineStr">
@@ -53685,7 +53685,7 @@
       <c r="B930" t="inlineStr"/>
       <c r="C930" t="inlineStr">
         <is>
-          <t>Aurizon Empty Grain</t>
+          <t>Cockburn Cement Empty Coal</t>
         </is>
       </c>
       <c r="D930" t="inlineStr">
@@ -53793,7 +53793,7 @@
       <c r="B936" t="inlineStr"/>
       <c r="C936" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D936" t="inlineStr">
@@ -55067,7 +55067,7 @@
       <c r="B1007" t="inlineStr"/>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1007" t="inlineStr">
@@ -55121,7 +55121,7 @@
       <c r="B1010" t="inlineStr"/>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1010" t="inlineStr">
@@ -56591,7 +56591,7 @@
       <c r="B1093" t="inlineStr"/>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1093" t="inlineStr">
@@ -56609,7 +56609,7 @@
       <c r="B1094" t="inlineStr"/>
       <c r="C1094" t="inlineStr">
         <is>
-          <t>North Eastern Line BG Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D1094" t="inlineStr">
@@ -57721,7 +57721,7 @@
       <c r="B1156" t="inlineStr"/>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1156" t="inlineStr">
@@ -57775,7 +57775,7 @@
       <c r="B1159" t="inlineStr"/>
       <c r="C1159" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1159" t="inlineStr">
@@ -58441,7 +58441,7 @@
       <c r="B1196" t="inlineStr"/>
       <c r="C1196" t="inlineStr">
         <is>
-          <t>QUBE Trip Train</t>
+          <t>Qube Light Engine</t>
         </is>
       </c>
       <c r="D1196" t="inlineStr">
@@ -58959,7 +58959,7 @@
       <c r="B1225" t="inlineStr"/>
       <c r="C1225" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1225" t="inlineStr">
@@ -60731,7 +60731,7 @@
       <c r="B1325" t="inlineStr"/>
       <c r="C1325" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1325" t="inlineStr">
@@ -60889,7 +60889,7 @@
       <c r="B1334" t="inlineStr"/>
       <c r="C1334" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1334" t="inlineStr">
@@ -61223,7 +61223,7 @@
       <c r="B1353" t="inlineStr"/>
       <c r="C1353" t="inlineStr">
         <is>
-          <t>PN Grain Shuttle</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D1353" t="inlineStr">
@@ -61782,7 +61782,7 @@
       <c r="B1384" t="inlineStr"/>
       <c r="C1384" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1384" t="inlineStr">
@@ -62120,7 +62120,7 @@
       <c r="B1403" t="inlineStr"/>
       <c r="C1403" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1403" t="inlineStr">
@@ -62607,7 +62607,7 @@
       <c r="B1430" t="inlineStr"/>
       <c r="C1430" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1430" t="inlineStr">
@@ -62679,7 +62679,7 @@
       <c r="B1434" t="inlineStr"/>
       <c r="C1434" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1434" t="inlineStr">
@@ -63017,7 +63017,7 @@
       <c r="B1453" t="inlineStr"/>
       <c r="C1453" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1453" t="inlineStr">
@@ -63211,7 +63211,7 @@
       <c r="B1464" t="inlineStr"/>
       <c r="C1464" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Southern Highlands Service</t>
         </is>
       </c>
       <c r="D1464" t="inlineStr">
@@ -63427,7 +63427,7 @@
       <c r="B1476" t="inlineStr"/>
       <c r="C1476" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1476" t="inlineStr">
@@ -64459,7 +64459,7 @@
       <c r="B1534" t="inlineStr"/>
       <c r="C1534" t="inlineStr">
         <is>
-          <t>Additional Bathurst Service</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1534" t="inlineStr">
@@ -65901,7 +65901,7 @@
       <c r="B1615" t="inlineStr"/>
       <c r="C1615" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D1615" t="inlineStr">
@@ -66185,7 +66185,7 @@
       <c r="B1631" t="inlineStr"/>
       <c r="C1631" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1631" t="inlineStr">
@@ -69075,7 +69075,7 @@
       <c r="B1798" t="inlineStr"/>
       <c r="C1798" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1798" t="inlineStr">
@@ -69147,7 +69147,7 @@
       <c r="B1802" t="inlineStr"/>
       <c r="C1802" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1802" t="inlineStr">
@@ -69665,7 +69665,7 @@
       <c r="B1831" t="inlineStr"/>
       <c r="C1831" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1831" t="inlineStr">
@@ -69827,7 +69827,7 @@
       <c r="B1840" t="inlineStr"/>
       <c r="C1840" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1840" t="inlineStr">
@@ -69953,7 +69953,7 @@
       <c r="B1847" t="inlineStr"/>
       <c r="C1847" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1847" t="inlineStr">
@@ -69971,7 +69971,7 @@
       <c r="B1848" t="inlineStr"/>
       <c r="C1848" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1848" t="inlineStr">
@@ -69989,7 +69989,7 @@
       <c r="B1849" t="inlineStr"/>
       <c r="C1849" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1849" t="inlineStr">
@@ -70043,7 +70043,7 @@
       <c r="B1852" t="inlineStr"/>
       <c r="C1852" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1852" t="inlineStr">
@@ -70187,7 +70187,7 @@
       <c r="B1860" t="inlineStr"/>
       <c r="C1860" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1860" t="inlineStr">
@@ -70205,7 +70205,7 @@
       <c r="B1861" t="inlineStr"/>
       <c r="C1861" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1861" t="inlineStr">
@@ -70241,7 +70241,7 @@
       <c r="B1863" t="inlineStr"/>
       <c r="C1863" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1863" t="inlineStr">
@@ -70331,7 +70331,7 @@
       <c r="B1868" t="inlineStr"/>
       <c r="C1868" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1868" t="inlineStr">
@@ -70781,7 +70781,7 @@
       <c r="B1893" t="inlineStr"/>
       <c r="C1893" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1893" t="inlineStr">
@@ -70799,7 +70799,7 @@
       <c r="B1894" t="inlineStr"/>
       <c r="C1894" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1894" t="inlineStr">
@@ -70871,7 +70871,7 @@
       <c r="B1898" t="inlineStr"/>
       <c r="C1898" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1898" t="inlineStr">
@@ -70889,7 +70889,7 @@
       <c r="B1899" t="inlineStr"/>
       <c r="C1899" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1899" t="inlineStr">
@@ -70943,7 +70943,7 @@
       <c r="B1902" t="inlineStr"/>
       <c r="C1902" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1902" t="inlineStr">
@@ -71087,7 +71087,7 @@
       <c r="B1910" t="inlineStr"/>
       <c r="C1910" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1910" t="inlineStr">
@@ -71267,7 +71267,7 @@
       <c r="B1920" t="inlineStr"/>
       <c r="C1920" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1920" t="inlineStr">
@@ -71321,7 +71321,7 @@
       <c r="B1923" t="inlineStr"/>
       <c r="C1923" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1923" t="inlineStr">
@@ -71375,7 +71375,7 @@
       <c r="B1926" t="inlineStr"/>
       <c r="C1926" t="inlineStr">
         <is>
-          <t>PN Infrabuild Steel</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D1926" t="inlineStr">
@@ -73511,7 +73511,7 @@
       <c r="B2050" t="inlineStr"/>
       <c r="C2050" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D2050" t="inlineStr">
@@ -73759,7 +73759,7 @@
       <c r="B2064" t="inlineStr"/>
       <c r="C2064" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D2064" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1120,7 +1120,7 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2332,7 +2332,7 @@
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2710,7 +2710,7 @@
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -2746,7 +2746,7 @@
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -2890,7 +2890,7 @@
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>North East SG Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -3102,7 +3102,7 @@
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
-          <t>QUBE Containerised Freight</t>
+          <t>QUBE Shuttle</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -6586,7 +6586,11 @@
         </is>
       </c>
       <c r="B348" t="inlineStr"/>
-      <c r="C348" t="inlineStr"/>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>PN Grain via Greta TSF</t>
+        </is>
+      </c>
       <c r="D348" t="inlineStr">
         <is>
           <t>2026-04-12 05:01:26</t>
@@ -8478,7 +8482,7 @@
       <c r="B461" t="inlineStr"/>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Aurizon Empty Grain</t>
+          <t>Aurizon Loaded Grain</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -9352,7 +9356,7 @@
       <c r="B516" t="inlineStr"/>
       <c r="C516" t="inlineStr">
         <is>
-          <t>SSR Limestone</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
@@ -9492,7 +9496,7 @@
       <c r="B524" t="inlineStr"/>
       <c r="C524" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
@@ -11112,7 +11116,7 @@
       <c r="B615" t="inlineStr"/>
       <c r="C615" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -11596,7 +11600,7 @@
       <c r="B643" t="inlineStr"/>
       <c r="C643" t="inlineStr">
         <is>
-          <t>Aurizon Light Engine</t>
+          <t>Aurizon Wagon Transfer</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
@@ -14856,7 +14860,7 @@
       <c r="B827" t="inlineStr"/>
       <c r="C827" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
@@ -15638,7 +15642,7 @@
       <c r="B872" t="inlineStr"/>
       <c r="C872" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D872" t="inlineStr">
@@ -15908,7 +15912,7 @@
       <c r="B887" t="inlineStr"/>
       <c r="C887" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D887" t="inlineStr">
@@ -16016,7 +16020,7 @@
       <c r="B893" t="inlineStr"/>
       <c r="C893" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D893" t="inlineStr">
@@ -16124,7 +16128,7 @@
       <c r="B899" t="inlineStr"/>
       <c r="C899" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
@@ -16178,7 +16182,7 @@
       <c r="B902" t="inlineStr"/>
       <c r="C902" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D902" t="inlineStr">
@@ -17132,7 +17136,7 @@
       <c r="B955" t="inlineStr"/>
       <c r="C955" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D955" t="inlineStr">
@@ -17240,7 +17244,7 @@
       <c r="B961" t="inlineStr"/>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D961" t="inlineStr">
@@ -17258,7 +17262,7 @@
       <c r="B962" t="inlineStr"/>
       <c r="C962" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D962" t="inlineStr">
@@ -18932,7 +18936,7 @@
       <c r="B1055" t="inlineStr"/>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1055" t="inlineStr">
@@ -18950,7 +18954,7 @@
       <c r="B1056" t="inlineStr"/>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1056" t="inlineStr">
@@ -19418,7 +19422,7 @@
       <c r="B1082" t="inlineStr"/>
       <c r="C1082" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1082" t="inlineStr">
@@ -19436,7 +19440,7 @@
       <c r="B1083" t="inlineStr"/>
       <c r="C1083" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1083" t="inlineStr">
@@ -20264,7 +20268,7 @@
       <c r="B1129" t="inlineStr"/>
       <c r="C1129" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1129" t="inlineStr">
@@ -20696,7 +20700,7 @@
       <c r="B1153" t="inlineStr"/>
       <c r="C1153" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1153" t="inlineStr">
@@ -20876,7 +20880,7 @@
       <c r="B1163" t="inlineStr"/>
       <c r="C1163" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1163" t="inlineStr">
@@ -20948,7 +20952,7 @@
       <c r="B1167" t="inlineStr"/>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1167" t="inlineStr">
@@ -21380,7 +21384,7 @@
       <c r="B1191" t="inlineStr"/>
       <c r="C1191" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1191" t="inlineStr">
@@ -21416,7 +21420,7 @@
       <c r="B1193" t="inlineStr"/>
       <c r="C1193" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1193" t="inlineStr">
@@ -21470,7 +21474,7 @@
       <c r="B1196" t="inlineStr"/>
       <c r="C1196" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1196" t="inlineStr">
@@ -21650,7 +21654,7 @@
       <c r="B1206" t="inlineStr"/>
       <c r="C1206" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1206" t="inlineStr">
@@ -21740,7 +21744,7 @@
       <c r="B1211" t="inlineStr"/>
       <c r="C1211" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1211" t="inlineStr">
@@ -21902,7 +21906,7 @@
       <c r="B1220" t="inlineStr"/>
       <c r="C1220" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1220" t="inlineStr">
@@ -22118,7 +22122,7 @@
       <c r="B1232" t="inlineStr"/>
       <c r="C1232" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1232" t="inlineStr">
@@ -22136,7 +22140,7 @@
       <c r="B1233" t="inlineStr"/>
       <c r="C1233" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1233" t="inlineStr">
@@ -22550,7 +22554,7 @@
       <c r="B1256" t="inlineStr"/>
       <c r="C1256" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1256" t="inlineStr">
@@ -22604,7 +22608,7 @@
       <c r="B1259" t="inlineStr"/>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1259" t="inlineStr">
@@ -22658,7 +22662,7 @@
       <c r="B1262" t="inlineStr"/>
       <c r="C1262" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1262" t="inlineStr">
@@ -25032,7 +25036,7 @@
       <c r="B1397" t="inlineStr"/>
       <c r="C1397" t="inlineStr">
         <is>
-          <t>Maintenance Train</t>
+          <t>SSR Inspection Train</t>
         </is>
       </c>
       <c r="D1397" t="inlineStr">
@@ -26008,7 +26012,7 @@
       <c r="B1457" t="inlineStr"/>
       <c r="C1457" t="inlineStr">
         <is>
-          <t>QUBE Containerised Freight</t>
+          <t>QUBE Trip Train</t>
         </is>
       </c>
       <c r="D1457" t="inlineStr">
@@ -26238,7 +26242,7 @@
       <c r="B1470" t="inlineStr"/>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>QUBE Empty Grain</t>
+          <t>QUBE Grain</t>
         </is>
       </c>
       <c r="D1470" t="inlineStr">
@@ -36612,7 +36616,7 @@
       <c r="B2053" t="inlineStr"/>
       <c r="C2053" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (Forms ST23)</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D2053" t="inlineStr">
@@ -38301,7 +38305,7 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (Forms ST23)</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -39475,7 +39479,11 @@
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
-      <c r="C126" t="inlineStr"/>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>PN Grain via Greta TSF</t>
+        </is>
+      </c>
       <c r="D126" t="inlineStr">
         <is>
           <t>2026-04-12 05:01:26</t>
@@ -40399,7 +40407,7 @@
       <c r="B179" t="inlineStr"/>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -40927,7 +40935,7 @@
       <c r="B209" t="inlineStr"/>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41107,7 +41115,7 @@
       <c r="B219" t="inlineStr"/>
       <c r="C219" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -41707,7 +41715,7 @@
       <c r="B253" t="inlineStr"/>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -45081,7 +45089,7 @@
       <c r="B444" t="inlineStr"/>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -45329,7 +45337,7 @@
       <c r="B458" t="inlineStr"/>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -45383,7 +45391,7 @@
       <c r="B461" t="inlineStr"/>
       <c r="C461" t="inlineStr">
         <is>
-          <t>QUBE Containerised Freight</t>
+          <t>QUBE Trip Train</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -45505,7 +45513,7 @@
       <c r="B468" t="inlineStr"/>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -46135,7 +46143,7 @@
       <c r="B503" t="inlineStr"/>
       <c r="C503" t="inlineStr">
         <is>
-          <t>QUBE Containerised Freight</t>
+          <t>QUBE Shuttle</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
@@ -48135,7 +48143,7 @@
       <c r="B617" t="inlineStr"/>
       <c r="C617" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
@@ -49071,7 +49079,7 @@
       <c r="B669" t="inlineStr"/>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
@@ -49999,7 +50007,7 @@
       <c r="B721" t="inlineStr"/>
       <c r="C721" t="inlineStr">
         <is>
-          <t>QUBE Empty Grain</t>
+          <t>QUBE Grain</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
@@ -50629,7 +50637,7 @@
       <c r="B756" t="inlineStr"/>
       <c r="C756" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
@@ -53423,7 +53431,7 @@
       <c r="B913" t="inlineStr"/>
       <c r="C913" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D913" t="inlineStr">
@@ -53477,7 +53485,7 @@
       <c r="B916" t="inlineStr"/>
       <c r="C916" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D916" t="inlineStr">
@@ -55111,7 +55119,7 @@
       <c r="B1007" t="inlineStr"/>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1007" t="inlineStr">
@@ -56157,7 +56165,7 @@
       <c r="B1066" t="inlineStr"/>
       <c r="C1066" t="inlineStr">
         <is>
-          <t>Aurizon Light Engine</t>
+          <t>Aurizon Wagon Transfer</t>
         </is>
       </c>
       <c r="D1066" t="inlineStr">
@@ -56689,7 +56697,7 @@
       <c r="B1096" t="inlineStr"/>
       <c r="C1096" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1096" t="inlineStr">
@@ -56923,7 +56931,7 @@
       <c r="B1109" t="inlineStr"/>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1109" t="inlineStr">
@@ -61195,7 +61203,7 @@
       <c r="B1349" t="inlineStr"/>
       <c r="C1349" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1349" t="inlineStr">
@@ -62182,7 +62190,7 @@
       <c r="B1404" t="inlineStr"/>
       <c r="C1404" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1404" t="inlineStr">
@@ -62236,7 +62244,7 @@
       <c r="B1407" t="inlineStr"/>
       <c r="C1407" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1407" t="inlineStr">
@@ -62759,7 +62767,7 @@
       <c r="B1436" t="inlineStr"/>
       <c r="C1436" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1436" t="inlineStr">
@@ -63327,7 +63335,7 @@
       <c r="B1468" t="inlineStr"/>
       <c r="C1468" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1468" t="inlineStr">
@@ -63507,7 +63515,7 @@
       <c r="B1478" t="inlineStr"/>
       <c r="C1478" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1478" t="inlineStr">
@@ -63867,7 +63875,7 @@
       <c r="B1498" t="inlineStr"/>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>Maintenance Train</t>
+          <t>SSR Inspection Train</t>
         </is>
       </c>
       <c r="D1498" t="inlineStr">
@@ -64377,7 +64385,7 @@
       <c r="B1527" t="inlineStr"/>
       <c r="C1527" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1527" t="inlineStr">
@@ -64899,7 +64907,7 @@
       <c r="B1556" t="inlineStr"/>
       <c r="C1556" t="inlineStr">
         <is>
-          <t>North East SG Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1556" t="inlineStr">
@@ -65319,7 +65327,7 @@
       <c r="B1580" t="inlineStr"/>
       <c r="C1580" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D1580" t="inlineStr">
@@ -65513,7 +65521,7 @@
       <c r="B1591" t="inlineStr"/>
       <c r="C1591" t="inlineStr">
         <is>
-          <t>Aurizon Empty Grain</t>
+          <t>Aurizon Loaded Grain</t>
         </is>
       </c>
       <c r="D1591" t="inlineStr">
@@ -68601,7 +68609,7 @@
       <c r="B1769" t="inlineStr"/>
       <c r="C1769" t="inlineStr">
         <is>
-          <t>SSR Limestone</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1769" t="inlineStr">
@@ -68655,7 +68663,7 @@
       <c r="B1772" t="inlineStr"/>
       <c r="C1772" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1772" t="inlineStr">
@@ -69745,7 +69753,7 @@
       <c r="B1833" t="inlineStr"/>
       <c r="C1833" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1833" t="inlineStr">
@@ -70069,7 +70077,7 @@
       <c r="B1851" t="inlineStr"/>
       <c r="C1851" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1851" t="inlineStr">
@@ -70123,7 +70131,7 @@
       <c r="B1854" t="inlineStr"/>
       <c r="C1854" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1854" t="inlineStr">
@@ -70177,7 +70185,7 @@
       <c r="B1857" t="inlineStr"/>
       <c r="C1857" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1857" t="inlineStr">
@@ -70717,7 +70725,7 @@
       <c r="B1887" t="inlineStr"/>
       <c r="C1887" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1887" t="inlineStr">
@@ -70843,7 +70851,7 @@
       <c r="B1894" t="inlineStr"/>
       <c r="C1894" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1894" t="inlineStr">
@@ -71023,7 +71031,7 @@
       <c r="B1904" t="inlineStr"/>
       <c r="C1904" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1904" t="inlineStr">
@@ -71167,7 +71175,7 @@
       <c r="B1912" t="inlineStr"/>
       <c r="C1912" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1912" t="inlineStr">
@@ -71365,7 +71373,7 @@
       <c r="B1923" t="inlineStr"/>
       <c r="C1923" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1923" t="inlineStr">
@@ -71401,7 +71409,7 @@
       <c r="B1925" t="inlineStr"/>
       <c r="C1925" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1925" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1174,7 +1174,7 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1814,7 +1814,7 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bank Siding Shunter (should be 6969)</t>
+          <t>Empty Transfer for Maintenance</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -1882,7 +1882,7 @@
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>V/Line empty cars</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5872,7 +5872,7 @@
       <c r="B308" t="inlineStr"/>
       <c r="C308" t="inlineStr">
         <is>
-          <t>PN Trip Train, ex 8124</t>
+          <t>PN Containerised Cotton</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -6484,7 +6484,7 @@
       <c r="B342" t="inlineStr"/>
       <c r="C342" t="inlineStr">
         <is>
-          <t>PN Port Waratah Shunter</t>
+          <t>PN Coal</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -8518,7 +8518,7 @@
       <c r="B463" t="inlineStr"/>
       <c r="C463" t="inlineStr">
         <is>
-          <t>MRL Empty Iron Ore</t>
+          <t>MRL Loaded Iron Ore</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -11756,7 +11756,7 @@
       <c r="B651" t="inlineStr"/>
       <c r="C651" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Ore</t>
+          <t>Aurizon Empty Ore</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
@@ -15316,7 +15316,7 @@
       <c r="B853" t="inlineStr"/>
       <c r="C853" t="inlineStr">
         <is>
-          <t>SSR Loaded Manildra Flour</t>
+          <t>SSR Empty Manildra Flour</t>
         </is>
       </c>
       <c r="D853" t="inlineStr">
@@ -25988,7 +25988,7 @@
       <c r="B1455" t="inlineStr"/>
       <c r="C1455" t="inlineStr">
         <is>
-          <t>QUBE BlueScope Steel</t>
+          <t>QUBE BlueScope Steel Shunt</t>
         </is>
       </c>
       <c r="D1455" t="inlineStr">
@@ -52121,7 +52121,7 @@
       <c r="B836" t="inlineStr"/>
       <c r="C836" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>V/Line empty cars</t>
         </is>
       </c>
       <c r="D836" t="inlineStr">
@@ -52351,7 +52351,7 @@
       <c r="B849" t="inlineStr"/>
       <c r="C849" t="inlineStr">
         <is>
-          <t>PN Port Waratah Shunter</t>
+          <t>PN Coal</t>
         </is>
       </c>
       <c r="D849" t="inlineStr">
@@ -52825,7 +52825,7 @@
       <c r="B876" t="inlineStr"/>
       <c r="C876" t="inlineStr">
         <is>
-          <t>MRL Empty Iron Ore</t>
+          <t>MRL Loaded Iron Ore</t>
         </is>
       </c>
       <c r="D876" t="inlineStr">
@@ -57783,7 +57783,7 @@
       <c r="B1153" t="inlineStr"/>
       <c r="C1153" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1153" t="inlineStr">
@@ -57837,7 +57837,7 @@
       <c r="B1156" t="inlineStr"/>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>Bank Siding Shunter (should be 6969)</t>
+          <t>Empty Transfer for Maintenance</t>
         </is>
       </c>
       <c r="D1156" t="inlineStr">
@@ -58963,7 +58963,7 @@
       <c r="B1219" t="inlineStr"/>
       <c r="C1219" t="inlineStr">
         <is>
-          <t>PN Trip Train, ex 8124</t>
+          <t>PN Containerised Cotton</t>
         </is>
       </c>
       <c r="D1219" t="inlineStr">
@@ -69187,7 +69187,7 @@
       <c r="B1798" t="inlineStr"/>
       <c r="C1798" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Ore</t>
+          <t>Aurizon Empty Ore</t>
         </is>
       </c>
       <c r="D1798" t="inlineStr">
@@ -69633,7 +69633,7 @@
       <c r="B1823" t="inlineStr"/>
       <c r="C1823" t="inlineStr">
         <is>
-          <t>SSR Loaded Manildra Flour</t>
+          <t>SSR Empty Manildra Flour</t>
         </is>
       </c>
       <c r="D1823" t="inlineStr">
@@ -72369,7 +72369,7 @@
       <c r="B1979" t="inlineStr"/>
       <c r="C1979" t="inlineStr">
         <is>
-          <t>QUBE BlueScope Steel</t>
+          <t>QUBE BlueScope Steel Shunt</t>
         </is>
       </c>
       <c r="D1979" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -3048,7 +3048,7 @@
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Qube Trip Train</t>
+          <t>QUBE Trip Train</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -5750,7 +5750,7 @@
       <c r="B301" t="inlineStr"/>
       <c r="C301" t="inlineStr">
         <is>
-          <t>PN Coal</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -9684,7 +9684,7 @@
       <c r="B534" t="inlineStr"/>
       <c r="C534" t="inlineStr">
         <is>
-          <t>QUBE Container Train</t>
+          <t>QUBE Grain</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
@@ -10008,7 +10008,7 @@
       <c r="B552" t="inlineStr"/>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Aurizon Wagon Transfer</t>
+          <t>Aurizon Empty Grain</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
@@ -10486,7 +10486,7 @@
       <c r="B579" t="inlineStr"/>
       <c r="C579" t="inlineStr">
         <is>
-          <t>SCT Intermodal</t>
+          <t>SCT Light Engine Movement</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
@@ -12100,7 +12100,7 @@
       <c r="B671" t="inlineStr"/>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
@@ -12208,7 +12208,7 @@
       <c r="B677" t="inlineStr"/>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
@@ -12280,7 +12280,7 @@
       <c r="B681" t="inlineStr"/>
       <c r="C681" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
@@ -14940,7 +14940,7 @@
       <c r="B831" t="inlineStr"/>
       <c r="C831" t="inlineStr">
         <is>
-          <t>South Coast Service</t>
+          <t>Sydney Trains Empty Car Transfer</t>
         </is>
       </c>
       <c r="D831" t="inlineStr">
@@ -26628,7 +26628,7 @@
       <c r="B1491" t="inlineStr"/>
       <c r="C1491" t="inlineStr">
         <is>
-          <t>SSR D Set Transfer / Grain Shuttle</t>
+          <t>SSR Grain</t>
         </is>
       </c>
       <c r="D1491" t="inlineStr">
@@ -27434,7 +27434,7 @@
       <c r="B1538" t="inlineStr"/>
       <c r="C1538" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1538" t="inlineStr">
@@ -27524,7 +27524,7 @@
       <c r="B1543" t="inlineStr"/>
       <c r="C1543" t="inlineStr">
         <is>
-          <t>Watco Light Engine Movement</t>
+          <t>Watco Trip Train</t>
         </is>
       </c>
       <c r="D1543" t="inlineStr">
@@ -42355,7 +42355,7 @@
       <c r="B287" t="inlineStr"/>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Watco Light Engine Movement</t>
+          <t>Watco Trip Train</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -44215,7 +44215,7 @@
       <c r="B391" t="inlineStr"/>
       <c r="C391" t="inlineStr">
         <is>
-          <t>SSR D Set Transfer / Grain Shuttle</t>
+          <t>SSR Grain</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -48109,7 +48109,7 @@
       <c r="B612" t="inlineStr"/>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Qube Trip Train</t>
+          <t>QUBE Trip Train</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
@@ -55535,7 +55535,7 @@
       <c r="B1027" t="inlineStr"/>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>SCT Intermodal</t>
+          <t>SCT Light Engine Movement</t>
         </is>
       </c>
       <c r="D1027" t="inlineStr">
@@ -58697,7 +58697,7 @@
       <c r="B1204" t="inlineStr"/>
       <c r="C1204" t="inlineStr">
         <is>
-          <t>QUBE Container Train</t>
+          <t>QUBE Grain</t>
         </is>
       </c>
       <c r="D1204" t="inlineStr">
@@ -59789,7 +59789,7 @@
       <c r="B1266" t="inlineStr"/>
       <c r="C1266" t="inlineStr">
         <is>
-          <t>Aurizon Wagon Transfer</t>
+          <t>Aurizon Empty Grain</t>
         </is>
       </c>
       <c r="D1266" t="inlineStr">
@@ -61839,7 +61839,7 @@
       <c r="B1381" t="inlineStr"/>
       <c r="C1381" t="inlineStr">
         <is>
-          <t>PN Coal</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D1381" t="inlineStr">
@@ -63485,7 +63485,7 @@
       <c r="B1473" t="inlineStr"/>
       <c r="C1473" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1473" t="inlineStr">
@@ -65707,7 +65707,7 @@
       <c r="B1598" t="inlineStr"/>
       <c r="C1598" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1598" t="inlineStr">
@@ -66369,7 +66369,7 @@
       <c r="B1635" t="inlineStr"/>
       <c r="C1635" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1635" t="inlineStr">
@@ -69277,7 +69277,7 @@
       <c r="B1803" t="inlineStr"/>
       <c r="C1803" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1803" t="inlineStr">
@@ -69511,7 +69511,7 @@
       <c r="B1816" t="inlineStr"/>
       <c r="C1816" t="inlineStr">
         <is>
-          <t>South Coast Service</t>
+          <t>Sydney Trains Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1816" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -4922,7 +4922,7 @@
       <c r="B255" t="inlineStr"/>
       <c r="C255" t="inlineStr">
         <is>
-          <t>PN Cement - RailTrain Crewed</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -5786,7 +5786,7 @@
       <c r="B303" t="inlineStr"/>
       <c r="C303" t="inlineStr">
         <is>
-          <t>PN Loaded Containerised Logs</t>
+          <t>PN Trip Train, pre 1821</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -7984,7 +7984,7 @@
       <c r="B432" t="inlineStr"/>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Aurizon Cockburn Cement -  Empty Lime / Cement Train</t>
+          <t>CBH SG Empty Grain</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -9238,7 +9238,7 @@
       <c r="B509" t="inlineStr"/>
       <c r="C509" t="inlineStr">
         <is>
-          <t>SSR Containerised Freight</t>
+          <t>SSR Freight Shuttle</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
@@ -10486,7 +10486,7 @@
       <c r="B579" t="inlineStr"/>
       <c r="C579" t="inlineStr">
         <is>
-          <t>SCT Light Engine Movement</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
@@ -12154,7 +12154,7 @@
       <c r="B674" t="inlineStr"/>
       <c r="C674" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
@@ -14922,7 +14922,7 @@
       <c r="B830" t="inlineStr"/>
       <c r="C830" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D830" t="inlineStr">
@@ -14940,7 +14940,7 @@
       <c r="B831" t="inlineStr"/>
       <c r="C831" t="inlineStr">
         <is>
-          <t>Sydney Trains Empty Car Transfer</t>
+          <t>NSW Trainlink South Coast Service</t>
         </is>
       </c>
       <c r="D831" t="inlineStr">
@@ -28626,7 +28626,7 @@
       <c r="B1608" t="inlineStr"/>
       <c r="C1608" t="inlineStr">
         <is>
-          <t>QUBE Light Engine Movement</t>
+          <t>QUBE Wagon Transfer</t>
         </is>
       </c>
       <c r="D1608" t="inlineStr">
@@ -38601,7 +38601,7 @@
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>QUBE Light Engine Movement</t>
+          <t>QUBE Wagon Transfer</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -39669,7 +39669,7 @@
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>PN Cement - RailTrain Crewed</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -44721,7 +44721,7 @@
       <c r="B420" t="inlineStr"/>
       <c r="C420" t="inlineStr">
         <is>
-          <t>SSR Containerised Freight</t>
+          <t>SSR Freight Shuttle</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -51269,7 +51269,7 @@
       <c r="B788" t="inlineStr"/>
       <c r="C788" t="inlineStr">
         <is>
-          <t>PN Loaded Containerised Logs</t>
+          <t>PN Trip Train, pre 1821</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
@@ -55535,7 +55535,7 @@
       <c r="B1027" t="inlineStr"/>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>SCT Light Engine Movement</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D1027" t="inlineStr">
@@ -59089,7 +59089,7 @@
       <c r="B1226" t="inlineStr"/>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1226" t="inlineStr">
@@ -68193,7 +68193,7 @@
       <c r="B1739" t="inlineStr"/>
       <c r="C1739" t="inlineStr">
         <is>
-          <t>Aurizon Cockburn Cement -  Empty Lime / Cement Train</t>
+          <t>CBH SG Empty Grain</t>
         </is>
       </c>
       <c r="D1739" t="inlineStr">
@@ -69295,7 +69295,7 @@
       <c r="B1804" t="inlineStr"/>
       <c r="C1804" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1804" t="inlineStr">
@@ -69511,7 +69511,7 @@
       <c r="B1816" t="inlineStr"/>
       <c r="C1816" t="inlineStr">
         <is>
-          <t>Sydney Trains Empty Car Transfer</t>
+          <t>NSW Trainlink South Coast Service</t>
         </is>
       </c>
       <c r="D1816" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -616,7 +616,7 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Gippsland Line Service</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -742,7 +742,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1706,7 +1706,7 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1972,7 +1972,7 @@
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2476,7 +2476,7 @@
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5404,7 +5404,7 @@
       <c r="B282" t="inlineStr"/>
       <c r="C282" t="inlineStr">
         <is>
-          <t>PN Local Shunter</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -9626,7 +9626,7 @@
       <c r="B531" t="inlineStr"/>
       <c r="C531" t="inlineStr">
         <is>
-          <t>SRS-Crawfords Container Train</t>
+          <t>SRS Shunter</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
@@ -10714,7 +10714,7 @@
       <c r="B592" t="inlineStr"/>
       <c r="C592" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer</t>
+          <t>NSW Trainlink Xplorer to Sydney (connects with NP24)</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
@@ -10750,7 +10750,7 @@
       <c r="B594" t="inlineStr"/>
       <c r="C594" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer</t>
+          <t>NSW Trainlink Empty Car Transfer</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
@@ -12060,7 +12060,7 @@
       <c r="B669" t="inlineStr"/>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
@@ -12168,7 +12168,7 @@
       <c r="B675" t="inlineStr"/>
       <c r="C675" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Hunter Railcar Transfer</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
@@ -15686,7 +15686,7 @@
       <c r="B874" t="inlineStr"/>
       <c r="C874" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D874" t="inlineStr">
@@ -15830,7 +15830,7 @@
       <c r="B882" t="inlineStr"/>
       <c r="C882" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D882" t="inlineStr">
@@ -17054,7 +17054,7 @@
       <c r="B950" t="inlineStr"/>
       <c r="C950" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D950" t="inlineStr">
@@ -17342,7 +17342,7 @@
       <c r="B966" t="inlineStr"/>
       <c r="C966" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D966" t="inlineStr">
@@ -17918,7 +17918,7 @@
       <c r="B998" t="inlineStr"/>
       <c r="C998" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D998" t="inlineStr">
@@ -18044,7 +18044,7 @@
       <c r="B1005" t="inlineStr"/>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1005" t="inlineStr">
@@ -19250,7 +19250,7 @@
       <c r="B1072" t="inlineStr"/>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1072" t="inlineStr">
@@ -19808,7 +19808,7 @@
       <c r="B1103" t="inlineStr"/>
       <c r="C1103" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1103" t="inlineStr">
@@ -19916,7 +19916,7 @@
       <c r="B1109" t="inlineStr"/>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1109" t="inlineStr">
@@ -20042,7 +20042,7 @@
       <c r="B1116" t="inlineStr"/>
       <c r="C1116" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1116" t="inlineStr">
@@ -20474,7 +20474,7 @@
       <c r="B1140" t="inlineStr"/>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1140" t="inlineStr">
@@ -20690,7 +20690,7 @@
       <c r="B1152" t="inlineStr"/>
       <c r="C1152" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1152" t="inlineStr">
@@ -20762,7 +20762,7 @@
       <c r="B1156" t="inlineStr"/>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1156" t="inlineStr">
@@ -20780,7 +20780,7 @@
       <c r="B1157" t="inlineStr"/>
       <c r="C1157" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1157" t="inlineStr">
@@ -20852,7 +20852,7 @@
       <c r="B1161" t="inlineStr"/>
       <c r="C1161" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D1161" t="inlineStr">
@@ -20978,7 +20978,7 @@
       <c r="B1168" t="inlineStr"/>
       <c r="C1168" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1168" t="inlineStr">
@@ -21050,7 +21050,7 @@
       <c r="B1172" t="inlineStr"/>
       <c r="C1172" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1172" t="inlineStr">
@@ -21248,7 +21248,7 @@
       <c r="B1183" t="inlineStr"/>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1183" t="inlineStr">
@@ -21392,7 +21392,7 @@
       <c r="B1191" t="inlineStr"/>
       <c r="C1191" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1191" t="inlineStr">
@@ -21500,7 +21500,7 @@
       <c r="B1197" t="inlineStr"/>
       <c r="C1197" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1197" t="inlineStr">
@@ -21536,7 +21536,7 @@
       <c r="B1199" t="inlineStr"/>
       <c r="C1199" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1199" t="inlineStr">
@@ -21554,7 +21554,7 @@
       <c r="B1200" t="inlineStr"/>
       <c r="C1200" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D1200" t="inlineStr">
@@ -21680,7 +21680,7 @@
       <c r="B1207" t="inlineStr"/>
       <c r="C1207" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1207" t="inlineStr">
@@ -21734,7 +21734,7 @@
       <c r="B1210" t="inlineStr"/>
       <c r="C1210" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1210" t="inlineStr">
@@ -21842,7 +21842,7 @@
       <c r="B1216" t="inlineStr"/>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1216" t="inlineStr">
@@ -21860,7 +21860,7 @@
       <c r="B1217" t="inlineStr"/>
       <c r="C1217" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1217" t="inlineStr">
@@ -21932,7 +21932,7 @@
       <c r="B1221" t="inlineStr"/>
       <c r="C1221" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1221" t="inlineStr">
@@ -21968,7 +21968,7 @@
       <c r="B1223" t="inlineStr"/>
       <c r="C1223" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1223" t="inlineStr">
@@ -22040,7 +22040,7 @@
       <c r="B1227" t="inlineStr"/>
       <c r="C1227" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1227" t="inlineStr">
@@ -22148,7 +22148,7 @@
       <c r="B1233" t="inlineStr"/>
       <c r="C1233" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1233" t="inlineStr">
@@ -22220,7 +22220,7 @@
       <c r="B1237" t="inlineStr"/>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1237" t="inlineStr">
@@ -22256,7 +22256,7 @@
       <c r="B1239" t="inlineStr"/>
       <c r="C1239" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1239" t="inlineStr">
@@ -22346,7 +22346,7 @@
       <c r="B1244" t="inlineStr"/>
       <c r="C1244" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1244" t="inlineStr">
@@ -22364,7 +22364,7 @@
       <c r="B1245" t="inlineStr"/>
       <c r="C1245" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1245" t="inlineStr">
@@ -22454,7 +22454,7 @@
       <c r="B1250" t="inlineStr"/>
       <c r="C1250" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1250" t="inlineStr">
@@ -22598,7 +22598,7 @@
       <c r="B1258" t="inlineStr"/>
       <c r="C1258" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1258" t="inlineStr">
@@ -22616,7 +22616,7 @@
       <c r="B1259" t="inlineStr"/>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1259" t="inlineStr">
@@ -22634,7 +22634,7 @@
       <c r="B1260" t="inlineStr"/>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1260" t="inlineStr">
@@ -22688,7 +22688,7 @@
       <c r="B1263" t="inlineStr"/>
       <c r="C1263" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1263" t="inlineStr">
@@ -22724,7 +22724,7 @@
       <c r="B1265" t="inlineStr"/>
       <c r="C1265" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1265" t="inlineStr">
@@ -22796,7 +22796,7 @@
       <c r="B1269" t="inlineStr"/>
       <c r="C1269" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1269" t="inlineStr">
@@ -24646,7 +24646,7 @@
       <c r="B1374" t="inlineStr"/>
       <c r="C1374" t="inlineStr">
         <is>
-          <t>PN Infrabuild Steel</t>
+          <t>PN Shunter</t>
         </is>
       </c>
       <c r="D1374" t="inlineStr">
@@ -27002,7 +27002,7 @@
       <c r="B1514" t="inlineStr"/>
       <c r="C1514" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>North Eastern BG Line Service</t>
         </is>
       </c>
       <c r="D1514" t="inlineStr">
@@ -27628,7 +27628,7 @@
       <c r="B1549" t="inlineStr"/>
       <c r="C1549" t="inlineStr">
         <is>
-          <t>Watco Light Engine</t>
+          <t>Watco Trip Train</t>
         </is>
       </c>
       <c r="D1549" t="inlineStr">
@@ -28238,7 +28238,7 @@
       <c r="B1586" t="inlineStr"/>
       <c r="C1586" t="inlineStr">
         <is>
-          <t>PN Loaded Aggregate</t>
+          <t>PN Empty Aggregate</t>
         </is>
       </c>
       <c r="D1586" t="inlineStr">
@@ -36736,7 +36736,7 @@
       <c r="B2059" t="inlineStr"/>
       <c r="C2059" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (ex NT34)</t>
         </is>
       </c>
       <c r="D2059" t="inlineStr">
@@ -39433,7 +39433,7 @@
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -39899,7 +39899,7 @@
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>PN Local Shunter</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -40707,7 +40707,7 @@
       <c r="B187" t="inlineStr"/>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -42495,7 +42495,7 @@
       <c r="B289" t="inlineStr"/>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -42567,7 +42567,7 @@
       <c r="B293" t="inlineStr"/>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Watco Light Engine</t>
+          <t>Watco Trip Train</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -42603,7 +42603,7 @@
       <c r="B295" t="inlineStr"/>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -42711,7 +42711,7 @@
       <c r="B301" t="inlineStr"/>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -43625,7 +43625,7 @@
       <c r="B352" t="inlineStr"/>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -45411,7 +45411,7 @@
       <c r="B453" t="inlineStr"/>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -45659,7 +45659,7 @@
       <c r="B467" t="inlineStr"/>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -46249,7 +46249,7 @@
       <c r="B500" t="inlineStr"/>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
@@ -48447,7 +48447,7 @@
       <c r="B625" t="inlineStr"/>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
@@ -48573,7 +48573,7 @@
       <c r="B632" t="inlineStr"/>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
@@ -48591,7 +48591,7 @@
       <c r="B633" t="inlineStr"/>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
@@ -50725,7 +50725,7 @@
       <c r="B752" t="inlineStr"/>
       <c r="C752" t="inlineStr">
         <is>
-          <t>PN Loaded Aggregate</t>
+          <t>PN Empty Aggregate</t>
         </is>
       </c>
       <c r="D752" t="inlineStr">
@@ -51639,7 +51639,7 @@
       <c r="B803" t="inlineStr"/>
       <c r="C803" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D803" t="inlineStr">
@@ -52099,7 +52099,7 @@
       <c r="B829" t="inlineStr"/>
       <c r="C829" t="inlineStr">
         <is>
-          <t>SRS-Crawfords Container Train</t>
+          <t>SRS Shunter</t>
         </is>
       </c>
       <c r="D829" t="inlineStr">
@@ -53271,7 +53271,7 @@
       <c r="B895" t="inlineStr"/>
       <c r="C895" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D895" t="inlineStr">
@@ -53865,7 +53865,7 @@
       <c r="B928" t="inlineStr"/>
       <c r="C928" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D928" t="inlineStr">
@@ -55391,7 +55391,7 @@
       <c r="B1013" t="inlineStr"/>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D1013" t="inlineStr">
@@ -55499,7 +55499,7 @@
       <c r="B1019" t="inlineStr"/>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1019" t="inlineStr">
@@ -55517,7 +55517,7 @@
       <c r="B1020" t="inlineStr"/>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1020" t="inlineStr">
@@ -56261,7 +56261,7 @@
       <c r="B1062" t="inlineStr"/>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1062" t="inlineStr">
@@ -56599,7 +56599,7 @@
       <c r="B1081" t="inlineStr"/>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1081" t="inlineStr">
@@ -56671,7 +56671,7 @@
       <c r="B1085" t="inlineStr"/>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1085" t="inlineStr">
@@ -56707,7 +56707,7 @@
       <c r="B1087" t="inlineStr"/>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1087" t="inlineStr">
@@ -56743,7 +56743,7 @@
       <c r="B1089" t="inlineStr"/>
       <c r="C1089" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1089" t="inlineStr">
@@ -57347,7 +57347,7 @@
       <c r="B1123" t="inlineStr"/>
       <c r="C1123" t="inlineStr">
         <is>
-          <t>PN Infrabuild Steel</t>
+          <t>PN Shunter</t>
         </is>
       </c>
       <c r="D1123" t="inlineStr">
@@ -58135,7 +58135,7 @@
       <c r="B1167" t="inlineStr"/>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer</t>
+          <t>NSW Trainlink Xplorer to Sydney (connects with NP24)</t>
         </is>
       </c>
       <c r="D1167" t="inlineStr">
@@ -58225,7 +58225,7 @@
       <c r="B1172" t="inlineStr"/>
       <c r="C1172" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>North Eastern BG Line Service</t>
         </is>
       </c>
       <c r="D1172" t="inlineStr">
@@ -61529,7 +61529,7 @@
       <c r="B1358" t="inlineStr"/>
       <c r="C1358" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1358" t="inlineStr">
@@ -62412,7 +62412,7 @@
       <c r="B1407" t="inlineStr"/>
       <c r="C1407" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1407" t="inlineStr">
@@ -62448,7 +62448,7 @@
       <c r="B1409" t="inlineStr"/>
       <c r="C1409" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer</t>
+          <t>NSW Trainlink Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1409" t="inlineStr">
@@ -62516,7 +62516,7 @@
       <c r="B1413" t="inlineStr"/>
       <c r="C1413" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1413" t="inlineStr">
@@ -62534,7 +62534,7 @@
       <c r="B1414" t="inlineStr"/>
       <c r="C1414" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1414" t="inlineStr">
@@ -62895,7 +62895,7 @@
       <c r="B1434" t="inlineStr"/>
       <c r="C1434" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1434" t="inlineStr">
@@ -63093,7 +63093,7 @@
       <c r="B1445" t="inlineStr"/>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1445" t="inlineStr">
@@ -63823,7 +63823,7 @@
       <c r="B1486" t="inlineStr"/>
       <c r="C1486" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1486" t="inlineStr">
@@ -64657,7 +64657,7 @@
       <c r="B1533" t="inlineStr"/>
       <c r="C1533" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (ex NT34)</t>
         </is>
       </c>
       <c r="D1533" t="inlineStr">
@@ -65143,7 +65143,7 @@
       <c r="B1560" t="inlineStr"/>
       <c r="C1560" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D1560" t="inlineStr">
@@ -65395,7 +65395,7 @@
       <c r="B1574" t="inlineStr"/>
       <c r="C1574" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1574" t="inlineStr">
@@ -66513,7 +66513,7 @@
       <c r="B1637" t="inlineStr"/>
       <c r="C1637" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1637" t="inlineStr">
@@ -67229,7 +67229,7 @@
       <c r="B1677" t="inlineStr"/>
       <c r="C1677" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Gippsland Line Service</t>
         </is>
       </c>
       <c r="D1677" t="inlineStr">
@@ -69511,7 +69511,7 @@
       <c r="B1810" t="inlineStr"/>
       <c r="C1810" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Hunter Railcar Transfer</t>
         </is>
       </c>
       <c r="D1810" t="inlineStr">
@@ -70587,7 +70587,7 @@
       <c r="B1870" t="inlineStr"/>
       <c r="C1870" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1870" t="inlineStr">
@@ -70857,7 +70857,7 @@
       <c r="B1885" t="inlineStr"/>
       <c r="C1885" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1885" t="inlineStr">
@@ -70929,7 +70929,7 @@
       <c r="B1889" t="inlineStr"/>
       <c r="C1889" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1889" t="inlineStr">
@@ -70965,7 +70965,7 @@
       <c r="B1891" t="inlineStr"/>
       <c r="C1891" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D1891" t="inlineStr">
@@ -71163,7 +71163,7 @@
       <c r="B1902" t="inlineStr"/>
       <c r="C1902" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1902" t="inlineStr">
@@ -71181,7 +71181,7 @@
       <c r="B1903" t="inlineStr"/>
       <c r="C1903" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D1903" t="inlineStr">
@@ -71253,7 +71253,7 @@
       <c r="B1907" t="inlineStr"/>
       <c r="C1907" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1907" t="inlineStr">
@@ -71343,7 +71343,7 @@
       <c r="B1912" t="inlineStr"/>
       <c r="C1912" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1912" t="inlineStr">
@@ -71523,7 +71523,7 @@
       <c r="B1922" t="inlineStr"/>
       <c r="C1922" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1922" t="inlineStr">
@@ -71541,7 +71541,7 @@
       <c r="B1923" t="inlineStr"/>
       <c r="C1923" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1923" t="inlineStr">
@@ -71577,7 +71577,7 @@
       <c r="B1925" t="inlineStr"/>
       <c r="C1925" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1925" t="inlineStr">
@@ -71667,7 +71667,7 @@
       <c r="B1930" t="inlineStr"/>
       <c r="C1930" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1930" t="inlineStr">
@@ -71721,7 +71721,7 @@
       <c r="B1933" t="inlineStr"/>
       <c r="C1933" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1933" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -634,7 +634,7 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -688,7 +688,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -922,7 +922,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1084,7 +1084,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1476,7 +1476,7 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1580,7 +1580,7 @@
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>NorthEast BG Service</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1814,7 +1814,7 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -1936,7 +1936,7 @@
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -1990,7 +1990,7 @@
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2062,7 +2062,7 @@
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northern Line</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2080,7 +2080,7 @@
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2278,7 +2278,7 @@
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2440,7 +2440,7 @@
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -2908,7 +2908,7 @@
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>North East Line SG Service</t>
+          <t>NorthEast Special Movement</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4312,7 +4312,7 @@
       <c r="B220" t="inlineStr"/>
       <c r="C220" t="inlineStr">
         <is>
-          <t>AZ Coal</t>
+          <t>AZ Light Engine</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -8094,7 +8094,7 @@
       <c r="B439" t="inlineStr"/>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Aurizon Kalgoorlie Mixed Freight</t>
+          <t>Aurizon Cockburn Cement - Lime and Cement Train</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -12060,7 +12060,7 @@
       <c r="B669" t="inlineStr"/>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
@@ -12240,7 +12240,7 @@
       <c r="B679" t="inlineStr"/>
       <c r="C679" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
@@ -12294,7 +12294,7 @@
       <c r="B682" t="inlineStr"/>
       <c r="C682" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
@@ -15222,7 +15222,7 @@
       <c r="B848" t="inlineStr"/>
       <c r="C848" t="inlineStr">
         <is>
-          <t>SSR Loaded Manildra Grain Banker</t>
+          <t>SSR Light Engine Movement</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
@@ -15686,7 +15686,7 @@
       <c r="B874" t="inlineStr"/>
       <c r="C874" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D874" t="inlineStr">
@@ -15848,7 +15848,7 @@
       <c r="B883" t="inlineStr"/>
       <c r="C883" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D883" t="inlineStr">
@@ -15956,7 +15956,7 @@
       <c r="B889" t="inlineStr"/>
       <c r="C889" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D889" t="inlineStr">
@@ -16064,7 +16064,7 @@
       <c r="B895" t="inlineStr"/>
       <c r="C895" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D895" t="inlineStr">
@@ -16100,7 +16100,7 @@
       <c r="B897" t="inlineStr"/>
       <c r="C897" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D897" t="inlineStr">
@@ -16136,7 +16136,7 @@
       <c r="B899" t="inlineStr"/>
       <c r="C899" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
@@ -16190,7 +16190,7 @@
       <c r="B902" t="inlineStr"/>
       <c r="C902" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D902" t="inlineStr">
@@ -16280,7 +16280,7 @@
       <c r="B907" t="inlineStr"/>
       <c r="C907" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
@@ -16604,7 +16604,7 @@
       <c r="B925" t="inlineStr"/>
       <c r="C925" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D925" t="inlineStr">
@@ -16856,7 +16856,7 @@
       <c r="B939" t="inlineStr"/>
       <c r="C939" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D939" t="inlineStr">
@@ -17126,7 +17126,7 @@
       <c r="B954" t="inlineStr"/>
       <c r="C954" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D954" t="inlineStr">
@@ -17396,7 +17396,7 @@
       <c r="B969" t="inlineStr"/>
       <c r="C969" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D969" t="inlineStr">
@@ -18404,7 +18404,7 @@
       <c r="B1025" t="inlineStr"/>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1025" t="inlineStr">
@@ -18854,7 +18854,7 @@
       <c r="B1050" t="inlineStr"/>
       <c r="C1050" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1050" t="inlineStr">
@@ -19556,7 +19556,7 @@
       <c r="B1089" t="inlineStr"/>
       <c r="C1089" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1089" t="inlineStr">
@@ -19718,7 +19718,7 @@
       <c r="B1098" t="inlineStr"/>
       <c r="C1098" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1098" t="inlineStr">
@@ -19808,7 +19808,7 @@
       <c r="B1103" t="inlineStr"/>
       <c r="C1103" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1103" t="inlineStr">
@@ -20294,7 +20294,7 @@
       <c r="B1130" t="inlineStr"/>
       <c r="C1130" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1130" t="inlineStr">
@@ -20312,7 +20312,7 @@
       <c r="B1131" t="inlineStr"/>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1131" t="inlineStr">
@@ -20708,7 +20708,7 @@
       <c r="B1153" t="inlineStr"/>
       <c r="C1153" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D1153" t="inlineStr">
@@ -20798,7 +20798,7 @@
       <c r="B1158" t="inlineStr"/>
       <c r="C1158" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1158" t="inlineStr">
@@ -20870,7 +20870,7 @@
       <c r="B1162" t="inlineStr"/>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1162" t="inlineStr">
@@ -20924,7 +20924,7 @@
       <c r="B1165" t="inlineStr"/>
       <c r="C1165" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D1165" t="inlineStr">
@@ -21050,7 +21050,7 @@
       <c r="B1172" t="inlineStr"/>
       <c r="C1172" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1172" t="inlineStr">
@@ -21194,7 +21194,7 @@
       <c r="B1180" t="inlineStr"/>
       <c r="C1180" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1180" t="inlineStr">
@@ -21230,7 +21230,7 @@
       <c r="B1182" t="inlineStr"/>
       <c r="C1182" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1182" t="inlineStr">
@@ -21320,7 +21320,7 @@
       <c r="B1187" t="inlineStr"/>
       <c r="C1187" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1187" t="inlineStr">
@@ -21356,7 +21356,7 @@
       <c r="B1189" t="inlineStr"/>
       <c r="C1189" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1189" t="inlineStr">
@@ -21428,7 +21428,7 @@
       <c r="B1193" t="inlineStr"/>
       <c r="C1193" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1193" t="inlineStr">
@@ -21446,7 +21446,7 @@
       <c r="B1194" t="inlineStr"/>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1194" t="inlineStr">
@@ -21518,7 +21518,7 @@
       <c r="B1198" t="inlineStr"/>
       <c r="C1198" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1198" t="inlineStr">
@@ -21572,7 +21572,7 @@
       <c r="B1201" t="inlineStr"/>
       <c r="C1201" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1201" t="inlineStr">
@@ -21626,7 +21626,7 @@
       <c r="B1204" t="inlineStr"/>
       <c r="C1204" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1204" t="inlineStr">
@@ -21662,7 +21662,7 @@
       <c r="B1206" t="inlineStr"/>
       <c r="C1206" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1206" t="inlineStr">
@@ -21716,7 +21716,7 @@
       <c r="B1209" t="inlineStr"/>
       <c r="C1209" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1209" t="inlineStr">
@@ -21770,7 +21770,7 @@
       <c r="B1212" t="inlineStr"/>
       <c r="C1212" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1212" t="inlineStr">
@@ -21878,7 +21878,7 @@
       <c r="B1218" t="inlineStr"/>
       <c r="C1218" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1218" t="inlineStr">
@@ -22022,7 +22022,7 @@
       <c r="B1226" t="inlineStr"/>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1226" t="inlineStr">
@@ -22058,7 +22058,7 @@
       <c r="B1228" t="inlineStr"/>
       <c r="C1228" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1228" t="inlineStr">
@@ -22094,7 +22094,7 @@
       <c r="B1230" t="inlineStr"/>
       <c r="C1230" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1230" t="inlineStr">
@@ -22112,7 +22112,7 @@
       <c r="B1231" t="inlineStr"/>
       <c r="C1231" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1231" t="inlineStr">
@@ -22130,7 +22130,7 @@
       <c r="B1232" t="inlineStr"/>
       <c r="C1232" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1232" t="inlineStr">
@@ -22166,7 +22166,7 @@
       <c r="B1234" t="inlineStr"/>
       <c r="C1234" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1234" t="inlineStr">
@@ -22184,7 +22184,7 @@
       <c r="B1235" t="inlineStr"/>
       <c r="C1235" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1235" t="inlineStr">
@@ -22220,7 +22220,7 @@
       <c r="B1237" t="inlineStr"/>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1237" t="inlineStr">
@@ -22238,7 +22238,7 @@
       <c r="B1238" t="inlineStr"/>
       <c r="C1238" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1238" t="inlineStr">
@@ -22310,7 +22310,7 @@
       <c r="B1242" t="inlineStr"/>
       <c r="C1242" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1242" t="inlineStr">
@@ -22346,7 +22346,7 @@
       <c r="B1244" t="inlineStr"/>
       <c r="C1244" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1244" t="inlineStr">
@@ -22382,7 +22382,7 @@
       <c r="B1246" t="inlineStr"/>
       <c r="C1246" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1246" t="inlineStr">
@@ -22400,7 +22400,7 @@
       <c r="B1247" t="inlineStr"/>
       <c r="C1247" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1247" t="inlineStr">
@@ -22526,7 +22526,7 @@
       <c r="B1254" t="inlineStr"/>
       <c r="C1254" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1254" t="inlineStr">
@@ -22544,7 +22544,7 @@
       <c r="B1255" t="inlineStr"/>
       <c r="C1255" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1255" t="inlineStr">
@@ -22562,7 +22562,7 @@
       <c r="B1256" t="inlineStr"/>
       <c r="C1256" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1256" t="inlineStr">
@@ -22652,7 +22652,7 @@
       <c r="B1261" t="inlineStr"/>
       <c r="C1261" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1261" t="inlineStr">
@@ -27538,7 +27538,7 @@
       <c r="B1544" t="inlineStr"/>
       <c r="C1544" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1544" t="inlineStr">
@@ -36934,7 +36934,7 @@
       <c r="B2070" t="inlineStr"/>
       <c r="C2070" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW TrainLink XPT</t>
         </is>
       </c>
       <c r="D2070" t="inlineStr">
@@ -37304,7 +37304,7 @@
       <c r="B2091" t="inlineStr"/>
       <c r="C2091" t="inlineStr">
         <is>
-          <t>ORA Coal</t>
+          <t>ORA Trip Train</t>
         </is>
       </c>
       <c r="D2091" t="inlineStr">
@@ -37595,7 +37595,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -38777,7 +38777,7 @@
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -39243,7 +39243,7 @@
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -39699,7 +39699,7 @@
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -40183,7 +40183,7 @@
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -40653,7 +40653,7 @@
       <c r="B184" t="inlineStr"/>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -42657,7 +42657,7 @@
       <c r="B298" t="inlineStr"/>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -43625,7 +43625,7 @@
       <c r="B352" t="inlineStr"/>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -45159,7 +45159,7 @@
       <c r="B439" t="inlineStr"/>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -45177,7 +45177,7 @@
       <c r="B440" t="inlineStr"/>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -45195,7 +45195,7 @@
       <c r="B441" t="inlineStr"/>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -45393,7 +45393,7 @@
       <c r="B452" t="inlineStr"/>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -45497,7 +45497,7 @@
       <c r="B458" t="inlineStr"/>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -45515,7 +45515,7 @@
       <c r="B459" t="inlineStr"/>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -45605,7 +45605,7 @@
       <c r="B464" t="inlineStr"/>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -45677,7 +45677,7 @@
       <c r="B468" t="inlineStr"/>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -45763,7 +45763,7 @@
       <c r="B473" t="inlineStr"/>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -46249,7 +46249,7 @@
       <c r="B500" t="inlineStr"/>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
@@ -46267,7 +46267,7 @@
       <c r="B501" t="inlineStr"/>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
@@ -46939,7 +46939,7 @@
       <c r="B539" t="inlineStr"/>
       <c r="C539" t="inlineStr">
         <is>
-          <t>AZ Coal</t>
+          <t>AZ Light Engine</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
@@ -47095,7 +47095,7 @@
       <c r="B549" t="inlineStr"/>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
@@ -48411,7 +48411,7 @@
       <c r="B623" t="inlineStr"/>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
@@ -48591,7 +48591,7 @@
       <c r="B633" t="inlineStr"/>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
@@ -48609,7 +48609,7 @@
       <c r="B634" t="inlineStr"/>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
@@ -48843,7 +48843,7 @@
       <c r="B647" t="inlineStr"/>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
@@ -49761,7 +49761,7 @@
       <c r="B698" t="inlineStr"/>
       <c r="C698" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
@@ -49797,7 +49797,7 @@
       <c r="B700" t="inlineStr"/>
       <c r="C700" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
@@ -50581,7 +50581,7 @@
       <c r="B744" t="inlineStr"/>
       <c r="C744" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
@@ -53019,7 +53019,7 @@
       <c r="B881" t="inlineStr"/>
       <c r="C881" t="inlineStr">
         <is>
-          <t>SSR Loaded Manildra Grain Banker</t>
+          <t>SSR Light Engine Movement</t>
         </is>
       </c>
       <c r="D881" t="inlineStr">
@@ -54585,7 +54585,7 @@
       <c r="B968" t="inlineStr"/>
       <c r="C968" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D968" t="inlineStr">
@@ -54995,7 +54995,7 @@
       <c r="B991" t="inlineStr"/>
       <c r="C991" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D991" t="inlineStr">
@@ -55445,7 +55445,7 @@
       <c r="B1016" t="inlineStr"/>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1016" t="inlineStr">
@@ -58049,7 +58049,7 @@
       <c r="B1162" t="inlineStr"/>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1162" t="inlineStr">
@@ -58783,7 +58783,7 @@
       <c r="B1203" t="inlineStr"/>
       <c r="C1203" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1203" t="inlineStr">
@@ -59373,7 +59373,7 @@
       <c r="B1236" t="inlineStr"/>
       <c r="C1236" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1236" t="inlineStr">
@@ -59865,7 +59865,7 @@
       <c r="B1264" t="inlineStr"/>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>North East Line SG Service</t>
+          <t>NorthEast Special Movement</t>
         </is>
       </c>
       <c r="D1264" t="inlineStr">
@@ -60771,7 +60771,7 @@
       <c r="B1315" t="inlineStr"/>
       <c r="C1315" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1315" t="inlineStr">
@@ -61285,7 +61285,7 @@
       <c r="B1344" t="inlineStr"/>
       <c r="C1344" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1344" t="inlineStr">
@@ -62750,7 +62750,7 @@
       <c r="B1426" t="inlineStr"/>
       <c r="C1426" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>NorthEast BG Service</t>
         </is>
       </c>
       <c r="D1426" t="inlineStr">
@@ -62895,7 +62895,7 @@
       <c r="B1434" t="inlineStr"/>
       <c r="C1434" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1434" t="inlineStr">
@@ -62949,7 +62949,7 @@
       <c r="B1437" t="inlineStr"/>
       <c r="C1437" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1437" t="inlineStr">
@@ -62967,7 +62967,7 @@
       <c r="B1438" t="inlineStr"/>
       <c r="C1438" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1438" t="inlineStr">
@@ -63057,7 +63057,7 @@
       <c r="B1443" t="inlineStr"/>
       <c r="C1443" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1443" t="inlineStr">
@@ -63075,7 +63075,7 @@
       <c r="B1444" t="inlineStr"/>
       <c r="C1444" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1444" t="inlineStr">
@@ -63111,7 +63111,7 @@
       <c r="B1446" t="inlineStr"/>
       <c r="C1446" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1446" t="inlineStr">
@@ -63395,7 +63395,7 @@
       <c r="B1462" t="inlineStr"/>
       <c r="C1462" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D1462" t="inlineStr">
@@ -63697,7 +63697,7 @@
       <c r="B1479" t="inlineStr"/>
       <c r="C1479" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1479" t="inlineStr">
@@ -65125,7 +65125,7 @@
       <c r="B1559" t="inlineStr"/>
       <c r="C1559" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1559" t="inlineStr">
@@ -66229,7 +66229,7 @@
       <c r="B1621" t="inlineStr"/>
       <c r="C1621" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northern Line</t>
         </is>
       </c>
       <c r="D1621" t="inlineStr">
@@ -66513,7 +66513,7 @@
       <c r="B1637" t="inlineStr"/>
       <c r="C1637" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1637" t="inlineStr">
@@ -66549,7 +66549,7 @@
       <c r="B1639" t="inlineStr"/>
       <c r="C1639" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1639" t="inlineStr">
@@ -66585,7 +66585,7 @@
       <c r="B1641" t="inlineStr"/>
       <c r="C1641" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1641" t="inlineStr">
@@ -67193,7 +67193,7 @@
       <c r="B1675" t="inlineStr"/>
       <c r="C1675" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW TrainLink XPT</t>
         </is>
       </c>
       <c r="D1675" t="inlineStr">
@@ -67265,7 +67265,7 @@
       <c r="B1679" t="inlineStr"/>
       <c r="C1679" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1679" t="inlineStr">
@@ -67373,7 +67373,7 @@
       <c r="B1685" t="inlineStr"/>
       <c r="C1685" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1685" t="inlineStr">
@@ -67409,7 +67409,7 @@
       <c r="B1687" t="inlineStr"/>
       <c r="C1687" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1687" t="inlineStr">
@@ -67535,7 +67535,7 @@
       <c r="B1694" t="inlineStr"/>
       <c r="C1694" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1694" t="inlineStr">
@@ -67553,7 +67553,7 @@
       <c r="B1695" t="inlineStr"/>
       <c r="C1695" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1695" t="inlineStr">
@@ -68491,7 +68491,7 @@
       <c r="B1750" t="inlineStr"/>
       <c r="C1750" t="inlineStr">
         <is>
-          <t>Aurizon Kalgoorlie Mixed Freight</t>
+          <t>Aurizon Cockburn Cement - Lime and Cement Train</t>
         </is>
       </c>
       <c r="D1750" t="inlineStr">
@@ -70353,7 +70353,7 @@
       <c r="B1857" t="inlineStr"/>
       <c r="C1857" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1857" t="inlineStr">
@@ -70497,7 +70497,7 @@
       <c r="B1865" t="inlineStr"/>
       <c r="C1865" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1865" t="inlineStr">
@@ -70569,7 +70569,7 @@
       <c r="B1869" t="inlineStr"/>
       <c r="C1869" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D1869" t="inlineStr">
@@ -70767,7 +70767,7 @@
       <c r="B1880" t="inlineStr"/>
       <c r="C1880" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1880" t="inlineStr">
@@ -70785,7 +70785,7 @@
       <c r="B1881" t="inlineStr"/>
       <c r="C1881" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1881" t="inlineStr">
@@ -70983,7 +70983,7 @@
       <c r="B1892" t="inlineStr"/>
       <c r="C1892" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1892" t="inlineStr">
@@ -71145,7 +71145,7 @@
       <c r="B1901" t="inlineStr"/>
       <c r="C1901" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1901" t="inlineStr">
@@ -71217,7 +71217,7 @@
       <c r="B1905" t="inlineStr"/>
       <c r="C1905" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1905" t="inlineStr">
@@ -71235,7 +71235,7 @@
       <c r="B1906" t="inlineStr"/>
       <c r="C1906" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1906" t="inlineStr">
@@ -71271,7 +71271,7 @@
       <c r="B1908" t="inlineStr"/>
       <c r="C1908" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1908" t="inlineStr">
@@ -71361,7 +71361,7 @@
       <c r="B1913" t="inlineStr"/>
       <c r="C1913" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1913" t="inlineStr">
@@ -71433,7 +71433,7 @@
       <c r="B1917" t="inlineStr"/>
       <c r="C1917" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1917" t="inlineStr">
@@ -71469,7 +71469,7 @@
       <c r="B1919" t="inlineStr"/>
       <c r="C1919" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1919" t="inlineStr">
@@ -71487,7 +71487,7 @@
       <c r="B1920" t="inlineStr"/>
       <c r="C1920" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1920" t="inlineStr">
@@ -71523,7 +71523,7 @@
       <c r="B1922" t="inlineStr"/>
       <c r="C1922" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1922" t="inlineStr">
@@ -71649,7 +71649,7 @@
       <c r="B1929" t="inlineStr"/>
       <c r="C1929" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1929" t="inlineStr">
@@ -74055,7 +74055,7 @@
       <c r="B2068" t="inlineStr"/>
       <c r="C2068" t="inlineStr">
         <is>
-          <t>ORA Coal</t>
+          <t>ORA Trip Train</t>
         </is>
       </c>
       <c r="D2068" t="inlineStr">
@@ -74159,7 +74159,7 @@
       <c r="B2074" t="inlineStr"/>
       <c r="C2074" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D2074" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -598,7 +598,7 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>North East Line BG Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -616,7 +616,7 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Gippsland Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -688,7 +688,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -778,7 +778,7 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -868,7 +868,7 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -994,7 +994,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1742,7 +1742,7 @@
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2422,7 +2422,7 @@
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2602,7 +2602,7 @@
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -2746,7 +2746,7 @@
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Northeast Line BG Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6048,7 +6048,7 @@
       <c r="B318" t="inlineStr"/>
       <c r="C318" t="inlineStr">
         <is>
-          <t>PN Trip Train, ex 8124</t>
+          <t>PN Containerised Cotton</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -6550,7 +6550,11 @@
         </is>
       </c>
       <c r="B346" t="inlineStr"/>
-      <c r="C346" t="inlineStr"/>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>PN Light Engine</t>
+        </is>
+      </c>
       <c r="D346" t="inlineStr">
         <is>
           <t>2026-04-14 11:46:39</t>
@@ -8496,7 +8500,7 @@
       <c r="B462" t="inlineStr"/>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Aurizon Wagon Transfer</t>
+          <t>Aurizon Empty Grain/Wagon Transfer</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -9590,7 +9594,7 @@
       <c r="B529" t="inlineStr"/>
       <c r="C529" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
@@ -11576,7 +11580,7 @@
       <c r="B641" t="inlineStr"/>
       <c r="C641" t="inlineStr">
         <is>
-          <t>Aurizon Wagon Transfer</t>
+          <t>Aurizon Shunter</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
@@ -12168,7 +12172,7 @@
       <c r="B675" t="inlineStr"/>
       <c r="C675" t="inlineStr">
         <is>
-          <t>Hunter Railcar Transfer</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
@@ -15560,7 +15564,7 @@
       <c r="B867" t="inlineStr"/>
       <c r="C867" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D867" t="inlineStr">
@@ -16496,7 +16500,7 @@
       <c r="B919" t="inlineStr"/>
       <c r="C919" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D919" t="inlineStr">
@@ -16550,7 +16554,7 @@
       <c r="B922" t="inlineStr"/>
       <c r="C922" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D922" t="inlineStr">
@@ -17054,7 +17058,7 @@
       <c r="B950" t="inlineStr"/>
       <c r="C950" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D950" t="inlineStr">
@@ -17540,7 +17544,7 @@
       <c r="B977" t="inlineStr"/>
       <c r="C977" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D977" t="inlineStr">
@@ -19070,7 +19074,7 @@
       <c r="B1062" t="inlineStr"/>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1062" t="inlineStr">
@@ -19088,7 +19092,7 @@
       <c r="B1063" t="inlineStr"/>
       <c r="C1063" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1063" t="inlineStr">
@@ -19916,7 +19920,7 @@
       <c r="B1109" t="inlineStr"/>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1109" t="inlineStr">
@@ -20042,7 +20046,7 @@
       <c r="B1116" t="inlineStr"/>
       <c r="C1116" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1116" t="inlineStr">
@@ -20492,7 +20496,7 @@
       <c r="B1141" t="inlineStr"/>
       <c r="C1141" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1141" t="inlineStr">
@@ -20654,7 +20658,7 @@
       <c r="B1150" t="inlineStr"/>
       <c r="C1150" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D1150" t="inlineStr">
@@ -20762,7 +20766,7 @@
       <c r="B1156" t="inlineStr"/>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1156" t="inlineStr">
@@ -21122,7 +21126,7 @@
       <c r="B1176" t="inlineStr"/>
       <c r="C1176" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1176" t="inlineStr">
@@ -21320,7 +21324,7 @@
       <c r="B1187" t="inlineStr"/>
       <c r="C1187" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1187" t="inlineStr">
@@ -21554,7 +21558,7 @@
       <c r="B1200" t="inlineStr"/>
       <c r="C1200" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1200" t="inlineStr">
@@ -21608,7 +21612,7 @@
       <c r="B1203" t="inlineStr"/>
       <c r="C1203" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1203" t="inlineStr">
@@ -21644,7 +21648,7 @@
       <c r="B1205" t="inlineStr"/>
       <c r="C1205" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1205" t="inlineStr">
@@ -21680,7 +21684,7 @@
       <c r="B1207" t="inlineStr"/>
       <c r="C1207" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1207" t="inlineStr">
@@ -21734,7 +21738,7 @@
       <c r="B1210" t="inlineStr"/>
       <c r="C1210" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1210" t="inlineStr">
@@ -21788,7 +21792,7 @@
       <c r="B1213" t="inlineStr"/>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1213" t="inlineStr">
@@ -21806,7 +21810,7 @@
       <c r="B1214" t="inlineStr"/>
       <c r="C1214" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1214" t="inlineStr">
@@ -22004,7 +22008,7 @@
       <c r="B1225" t="inlineStr"/>
       <c r="C1225" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1225" t="inlineStr">
@@ -22130,7 +22134,7 @@
       <c r="B1232" t="inlineStr"/>
       <c r="C1232" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1232" t="inlineStr">
@@ -22472,7 +22476,7 @@
       <c r="B1251" t="inlineStr"/>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1251" t="inlineStr">
@@ -22616,7 +22620,7 @@
       <c r="B1259" t="inlineStr"/>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1259" t="inlineStr">
@@ -22670,7 +22674,7 @@
       <c r="B1262" t="inlineStr"/>
       <c r="C1262" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1262" t="inlineStr">
@@ -22706,7 +22710,7 @@
       <c r="B1264" t="inlineStr"/>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1264" t="inlineStr">
@@ -22724,7 +22728,7 @@
       <c r="B1265" t="inlineStr"/>
       <c r="C1265" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1265" t="inlineStr">
@@ -23576,7 +23580,7 @@
       <c r="B1313" t="inlineStr"/>
       <c r="C1313" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>PN Intermodal Shuttle, Loads at Wumbulgal</t>
         </is>
       </c>
       <c r="D1313" t="inlineStr">
@@ -26678,7 +26682,7 @@
       <c r="B1494" t="inlineStr"/>
       <c r="C1494" t="inlineStr">
         <is>
-          <t>SSR D Set Transfer / Grain Shuttle</t>
+          <t>SSR Grain</t>
         </is>
       </c>
       <c r="D1494" t="inlineStr">
@@ -38585,7 +38589,11 @@
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>PN Light Engine</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
           <t>2026-04-14 11:46:39</t>
@@ -40933,7 +40941,7 @@
       <c r="B200" t="inlineStr"/>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -41181,7 +41189,7 @@
       <c r="B214" t="inlineStr"/>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42287,7 +42295,7 @@
       <c r="B277" t="inlineStr"/>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -42319,7 +42327,7 @@
       <c r="B279" t="inlineStr"/>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Aurizon Wagon Transfer</t>
+          <t>Aurizon Shunter</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -42495,7 +42503,7 @@
       <c r="B289" t="inlineStr"/>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -42603,7 +42611,7 @@
       <c r="B295" t="inlineStr"/>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -45587,7 +45595,7 @@
       <c r="B463" t="inlineStr"/>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -46231,7 +46239,7 @@
       <c r="B499" t="inlineStr"/>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
@@ -48609,7 +48617,7 @@
       <c r="B634" t="inlineStr"/>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
@@ -49365,7 +49373,7 @@
       <c r="B676" t="inlineStr"/>
       <c r="C676" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
@@ -50329,7 +50337,7 @@
       <c r="B730" t="inlineStr"/>
       <c r="C730" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
@@ -50437,7 +50445,7 @@
       <c r="B736" t="inlineStr"/>
       <c r="C736" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
@@ -51639,7 +51647,7 @@
       <c r="B803" t="inlineStr"/>
       <c r="C803" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D803" t="inlineStr">
@@ -53127,7 +53135,7 @@
       <c r="B887" t="inlineStr"/>
       <c r="C887" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D887" t="inlineStr">
@@ -53397,7 +53405,7 @@
       <c r="B902" t="inlineStr"/>
       <c r="C902" t="inlineStr">
         <is>
-          <t>PN Trip Train, ex 8124</t>
+          <t>PN Containerised Cotton</t>
         </is>
       </c>
       <c r="D902" t="inlineStr">
@@ -56027,7 +56035,7 @@
       <c r="B1049" t="inlineStr"/>
       <c r="C1049" t="inlineStr">
         <is>
-          <t>North East Line BG Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1049" t="inlineStr">
@@ -56225,7 +56233,7 @@
       <c r="B1060" t="inlineStr"/>
       <c r="C1060" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1060" t="inlineStr">
@@ -57275,7 +57283,7 @@
       <c r="B1119" t="inlineStr"/>
       <c r="C1119" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>PN Intermodal Shuttle, Loads at Wumbulgal</t>
         </is>
       </c>
       <c r="D1119" t="inlineStr">
@@ -61037,7 +61045,7 @@
       <c r="B1330" t="inlineStr"/>
       <c r="C1330" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1330" t="inlineStr">
@@ -61709,7 +61717,7 @@
       <c r="B1368" t="inlineStr"/>
       <c r="C1368" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1368" t="inlineStr">
@@ -62498,7 +62506,7 @@
       <c r="B1412" t="inlineStr"/>
       <c r="C1412" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1412" t="inlineStr">
@@ -65125,7 +65133,7 @@
       <c r="B1559" t="inlineStr"/>
       <c r="C1559" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1559" t="inlineStr">
@@ -65395,7 +65403,7 @@
       <c r="B1574" t="inlineStr"/>
       <c r="C1574" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1574" t="inlineStr">
@@ -65603,7 +65611,7 @@
       <c r="B1586" t="inlineStr"/>
       <c r="C1586" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1586" t="inlineStr">
@@ -65639,7 +65647,7 @@
       <c r="B1588" t="inlineStr"/>
       <c r="C1588" t="inlineStr">
         <is>
-          <t>Northeast Line BG Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D1588" t="inlineStr">
@@ -65833,7 +65841,7 @@
       <c r="B1599" t="inlineStr"/>
       <c r="C1599" t="inlineStr">
         <is>
-          <t>Aurizon Wagon Transfer</t>
+          <t>Aurizon Empty Grain/Wagon Transfer</t>
         </is>
       </c>
       <c r="D1599" t="inlineStr">
@@ -66779,7 +66787,7 @@
       <c r="B1652" t="inlineStr"/>
       <c r="C1652" t="inlineStr">
         <is>
-          <t>SSR D Set Transfer / Grain Shuttle</t>
+          <t>SSR Grain</t>
         </is>
       </c>
       <c r="D1652" t="inlineStr">
@@ -67229,7 +67237,7 @@
       <c r="B1677" t="inlineStr"/>
       <c r="C1677" t="inlineStr">
         <is>
-          <t>Gippsland Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1677" t="inlineStr">
@@ -67391,7 +67399,7 @@
       <c r="B1686" t="inlineStr"/>
       <c r="C1686" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1686" t="inlineStr">
@@ -67481,7 +67489,7 @@
       <c r="B1691" t="inlineStr"/>
       <c r="C1691" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1691" t="inlineStr">
@@ -69029,7 +69037,7 @@
       <c r="B1783" t="inlineStr"/>
       <c r="C1783" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1783" t="inlineStr">
@@ -69511,7 +69519,7 @@
       <c r="B1810" t="inlineStr"/>
       <c r="C1810" t="inlineStr">
         <is>
-          <t>Hunter Railcar Transfer</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1810" t="inlineStr">
@@ -70587,7 +70595,7 @@
       <c r="B1870" t="inlineStr"/>
       <c r="C1870" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1870" t="inlineStr">
@@ -71181,7 +71189,7 @@
       <c r="B1903" t="inlineStr"/>
       <c r="C1903" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1903" t="inlineStr">
@@ -71199,7 +71207,7 @@
       <c r="B1904" t="inlineStr"/>
       <c r="C1904" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1904" t="inlineStr">
@@ -71253,7 +71261,7 @@
       <c r="B1907" t="inlineStr"/>
       <c r="C1907" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1907" t="inlineStr">
@@ -71289,7 +71297,7 @@
       <c r="B1909" t="inlineStr"/>
       <c r="C1909" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1909" t="inlineStr">
@@ -71307,7 +71315,7 @@
       <c r="B1910" t="inlineStr"/>
       <c r="C1910" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1910" t="inlineStr">
@@ -71469,7 +71477,7 @@
       <c r="B1919" t="inlineStr"/>
       <c r="C1919" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1919" t="inlineStr">
@@ -71595,7 +71603,7 @@
       <c r="B1926" t="inlineStr"/>
       <c r="C1926" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1926" t="inlineStr">
@@ -71667,7 +71675,7 @@
       <c r="B1930" t="inlineStr"/>
       <c r="C1930" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1930" t="inlineStr">
@@ -71685,7 +71693,7 @@
       <c r="B1931" t="inlineStr"/>
       <c r="C1931" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1931" t="inlineStr">
@@ -71703,7 +71711,7 @@
       <c r="B1932" t="inlineStr"/>
       <c r="C1932" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1932" t="inlineStr">
@@ -71721,7 +71729,7 @@
       <c r="B1933" t="inlineStr"/>
       <c r="C1933" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1933" t="inlineStr">
@@ -71739,7 +71747,7 @@
       <c r="B1934" t="inlineStr"/>
       <c r="C1934" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1934" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -634,7 +634,7 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -742,7 +742,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Gippsland Line Service</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -796,7 +796,7 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -850,7 +850,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1156,7 +1156,7 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1174,7 +1174,7 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1580,7 +1580,7 @@
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>North Eastern Line BG Service</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1814,7 +1814,7 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -1832,7 +1832,7 @@
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -1972,7 +1972,7 @@
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2026,7 +2026,7 @@
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2080,7 +2080,7 @@
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2332,7 +2332,7 @@
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2782,7 +2782,7 @@
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3562,7 +3562,7 @@
       <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr">
         <is>
-          <t>SRS/SCT Sadleirs Trip Train</t>
+          <t>SRS Light Engine</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -9084,7 +9084,7 @@
       <c r="B500" t="inlineStr"/>
       <c r="C500" t="inlineStr">
         <is>
-          <t>PN Loaded BG Grain</t>
+          <t>PN Empty BG Grain</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
@@ -9770,7 +9770,7 @@
       <c r="B539" t="inlineStr"/>
       <c r="C539" t="inlineStr">
         <is>
-          <t>QUBE Empty Containerised Ore</t>
+          <t>Qube Trip Train</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
@@ -10254,7 +10254,11 @@
         </is>
       </c>
       <c r="B566" t="inlineStr"/>
-      <c r="C566" t="inlineStr"/>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>SRS Light Engine</t>
+        </is>
+      </c>
       <c r="D566" t="inlineStr">
         <is>
           <t>2026-04-06 23:02:27</t>
@@ -15366,7 +15370,7 @@
       <c r="B856" t="inlineStr"/>
       <c r="C856" t="inlineStr">
         <is>
-          <t>SSR Loaded Manildra Flour</t>
+          <t>SSR Empty Manildra Flour</t>
         </is>
       </c>
       <c r="D856" t="inlineStr">
@@ -15992,7 +15996,7 @@
       <c r="B891" t="inlineStr"/>
       <c r="C891" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D891" t="inlineStr">
@@ -16172,7 +16176,7 @@
       <c r="B901" t="inlineStr"/>
       <c r="C901" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D901" t="inlineStr">
@@ -16208,7 +16212,7 @@
       <c r="B903" t="inlineStr"/>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
@@ -16928,7 +16932,7 @@
       <c r="B943" t="inlineStr"/>
       <c r="C943" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D943" t="inlineStr">
@@ -17414,7 +17418,7 @@
       <c r="B970" t="inlineStr"/>
       <c r="C970" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D970" t="inlineStr">
@@ -17846,7 +17850,7 @@
       <c r="B994" t="inlineStr"/>
       <c r="C994" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D994" t="inlineStr">
@@ -18170,7 +18174,7 @@
       <c r="B1012" t="inlineStr"/>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1012" t="inlineStr">
@@ -18368,7 +18372,7 @@
       <c r="B1023" t="inlineStr"/>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1023" t="inlineStr">
@@ -18422,7 +18426,7 @@
       <c r="B1026" t="inlineStr"/>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1026" t="inlineStr">
@@ -19034,7 +19038,7 @@
       <c r="B1060" t="inlineStr"/>
       <c r="C1060" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1060" t="inlineStr">
@@ -19106,7 +19110,7 @@
       <c r="B1064" t="inlineStr"/>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1064" t="inlineStr">
@@ -19448,7 +19452,7 @@
       <c r="B1083" t="inlineStr"/>
       <c r="C1083" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1083" t="inlineStr">
@@ -19574,7 +19578,7 @@
       <c r="B1090" t="inlineStr"/>
       <c r="C1090" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1090" t="inlineStr">
@@ -19664,7 +19668,7 @@
       <c r="B1095" t="inlineStr"/>
       <c r="C1095" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1095" t="inlineStr">
@@ -19934,7 +19938,7 @@
       <c r="B1110" t="inlineStr"/>
       <c r="C1110" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1110" t="inlineStr">
@@ -20060,7 +20064,7 @@
       <c r="B1117" t="inlineStr"/>
       <c r="C1117" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1117" t="inlineStr">
@@ -20114,7 +20118,7 @@
       <c r="B1120" t="inlineStr"/>
       <c r="C1120" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1120" t="inlineStr">
@@ -20258,7 +20262,7 @@
       <c r="B1128" t="inlineStr"/>
       <c r="C1128" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1128" t="inlineStr">
@@ -20438,7 +20442,7 @@
       <c r="B1138" t="inlineStr"/>
       <c r="C1138" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1138" t="inlineStr">
@@ -20474,7 +20478,7 @@
       <c r="B1140" t="inlineStr"/>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1140" t="inlineStr">
@@ -20510,7 +20514,7 @@
       <c r="B1142" t="inlineStr"/>
       <c r="C1142" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1142" t="inlineStr">
@@ -20690,7 +20694,7 @@
       <c r="B1152" t="inlineStr"/>
       <c r="C1152" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1152" t="inlineStr">
@@ -20906,7 +20910,7 @@
       <c r="B1164" t="inlineStr"/>
       <c r="C1164" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1164" t="inlineStr">
@@ -20996,7 +21000,7 @@
       <c r="B1169" t="inlineStr"/>
       <c r="C1169" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1169" t="inlineStr">
@@ -21158,7 +21162,7 @@
       <c r="B1178" t="inlineStr"/>
       <c r="C1178" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1178" t="inlineStr">
@@ -21194,7 +21198,7 @@
       <c r="B1180" t="inlineStr"/>
       <c r="C1180" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1180" t="inlineStr">
@@ -21320,7 +21324,7 @@
       <c r="B1187" t="inlineStr"/>
       <c r="C1187" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1187" t="inlineStr">
@@ -21338,7 +21342,7 @@
       <c r="B1188" t="inlineStr"/>
       <c r="C1188" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1188" t="inlineStr">
@@ -21446,7 +21450,7 @@
       <c r="B1194" t="inlineStr"/>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1194" t="inlineStr">
@@ -21590,7 +21594,7 @@
       <c r="B1202" t="inlineStr"/>
       <c r="C1202" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1202" t="inlineStr">
@@ -21680,7 +21684,7 @@
       <c r="B1207" t="inlineStr"/>
       <c r="C1207" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1207" t="inlineStr">
@@ -21878,7 +21882,7 @@
       <c r="B1218" t="inlineStr"/>
       <c r="C1218" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1218" t="inlineStr">
@@ -22112,7 +22116,7 @@
       <c r="B1231" t="inlineStr"/>
       <c r="C1231" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1231" t="inlineStr">
@@ -22166,7 +22170,7 @@
       <c r="B1234" t="inlineStr"/>
       <c r="C1234" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1234" t="inlineStr">
@@ -22256,7 +22260,7 @@
       <c r="B1239" t="inlineStr"/>
       <c r="C1239" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1239" t="inlineStr">
@@ -22328,7 +22332,7 @@
       <c r="B1243" t="inlineStr"/>
       <c r="C1243" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1243" t="inlineStr">
@@ -22418,7 +22422,7 @@
       <c r="B1248" t="inlineStr"/>
       <c r="C1248" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1248" t="inlineStr">
@@ -22472,7 +22476,7 @@
       <c r="B1251" t="inlineStr"/>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1251" t="inlineStr">
@@ -22562,7 +22566,7 @@
       <c r="B1256" t="inlineStr"/>
       <c r="C1256" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1256" t="inlineStr">
@@ -22598,7 +22602,7 @@
       <c r="B1258" t="inlineStr"/>
       <c r="C1258" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1258" t="inlineStr">
@@ -22634,7 +22638,7 @@
       <c r="B1260" t="inlineStr"/>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1260" t="inlineStr">
@@ -22670,7 +22674,7 @@
       <c r="B1262" t="inlineStr"/>
       <c r="C1262" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1262" t="inlineStr">
@@ -22688,7 +22692,7 @@
       <c r="B1263" t="inlineStr"/>
       <c r="C1263" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1263" t="inlineStr">
@@ -22706,7 +22710,7 @@
       <c r="B1264" t="inlineStr"/>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1264" t="inlineStr">
@@ -22814,7 +22818,7 @@
       <c r="B1270" t="inlineStr"/>
       <c r="C1270" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1270" t="inlineStr">
@@ -22896,7 +22900,7 @@
       <c r="B1275" t="inlineStr"/>
       <c r="C1275" t="inlineStr">
         <is>
-          <t>SSR Grain</t>
+          <t>SSR Trip Train (Weston Milling)</t>
         </is>
       </c>
       <c r="D1275" t="inlineStr">
@@ -23594,7 +23598,7 @@
       <c r="B1314" t="inlineStr"/>
       <c r="C1314" t="inlineStr">
         <is>
-          <t>PN Intermodal Shuttle</t>
+          <t>PN Containerised Freight</t>
         </is>
       </c>
       <c r="D1314" t="inlineStr">
@@ -24786,7 +24790,7 @@
       <c r="B1382" t="inlineStr"/>
       <c r="C1382" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D1382" t="inlineStr">
@@ -27426,7 +27430,7 @@
       <c r="B1538" t="inlineStr"/>
       <c r="C1538" t="inlineStr">
         <is>
-          <t>SCT Intermodal</t>
+          <t>SCT Light Engine Movement</t>
         </is>
       </c>
       <c r="D1538" t="inlineStr">
@@ -27588,7 +27592,7 @@
       <c r="B1547" t="inlineStr"/>
       <c r="C1547" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1547" t="inlineStr">
@@ -28722,7 +28726,7 @@
       <c r="B1614" t="inlineStr"/>
       <c r="C1614" t="inlineStr">
         <is>
-          <t>QUBE Maryvale Paper Train</t>
+          <t>QUBE Light Engine Movement</t>
         </is>
       </c>
       <c r="D1614" t="inlineStr">
@@ -36800,7 +36804,7 @@
       <c r="B2063" t="inlineStr"/>
       <c r="C2063" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (ex NT34)</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D2063" t="inlineStr">
@@ -42749,7 +42753,7 @@
       <c r="B298" t="inlineStr"/>
       <c r="C298" t="inlineStr">
         <is>
-          <t>SCT Intermodal</t>
+          <t>SCT Light Engine Movement</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -42785,7 +42789,7 @@
       <c r="B300" t="inlineStr"/>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -42857,7 +42861,7 @@
       <c r="B304" t="inlineStr"/>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -43771,7 +43775,7 @@
       <c r="B355" t="inlineStr"/>
       <c r="C355" t="inlineStr">
         <is>
-          <t>QUBE Empty Containerised Ore</t>
+          <t>Qube Trip Train</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -44239,7 +44243,7 @@
       <c r="B381" t="inlineStr"/>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -45377,7 +45381,7 @@
       <c r="B446" t="inlineStr"/>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -45395,7 +45399,7 @@
       <c r="B447" t="inlineStr"/>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -45697,7 +45701,7 @@
       <c r="B464" t="inlineStr"/>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -45805,7 +45809,7 @@
       <c r="B470" t="inlineStr"/>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -46467,7 +46471,7 @@
       <c r="B507" t="inlineStr"/>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
@@ -47911,7 +47915,11 @@
         </is>
       </c>
       <c r="B590" t="inlineStr"/>
-      <c r="C590" t="inlineStr"/>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>SRS Light Engine</t>
+        </is>
+      </c>
       <c r="D590" t="inlineStr">
         <is>
           <t>2026-04-06 23:02:27</t>
@@ -48161,7 +48169,7 @@
       <c r="B604" t="inlineStr"/>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
@@ -48809,7 +48817,7 @@
       <c r="B640" t="inlineStr"/>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
@@ -49493,7 +49501,7 @@
       <c r="B678" t="inlineStr"/>
       <c r="C678" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
@@ -49565,7 +49573,7 @@
       <c r="B682" t="inlineStr"/>
       <c r="C682" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
@@ -49997,7 +50005,7 @@
       <c r="B706" t="inlineStr"/>
       <c r="C706" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
@@ -50781,7 +50789,7 @@
       <c r="B750" t="inlineStr"/>
       <c r="C750" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
@@ -51411,7 +51419,7 @@
       <c r="B785" t="inlineStr"/>
       <c r="C785" t="inlineStr">
         <is>
-          <t>SRS/SCT Sadleirs Trip Train</t>
+          <t>SRS Light Engine</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
@@ -52637,7 +52645,7 @@
       <c r="B854" t="inlineStr"/>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
@@ -53507,7 +53515,7 @@
       <c r="B903" t="inlineStr"/>
       <c r="C903" t="inlineStr">
         <is>
-          <t>QUBE Maryvale Paper Train</t>
+          <t>QUBE Light Engine Movement</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
@@ -54389,7 +54397,7 @@
       <c r="B952" t="inlineStr"/>
       <c r="C952" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D952" t="inlineStr">
@@ -54749,7 +54757,7 @@
       <c r="B972" t="inlineStr"/>
       <c r="C972" t="inlineStr">
         <is>
-          <t>PN Loaded BG Grain</t>
+          <t>PN Empty BG Grain</t>
         </is>
       </c>
       <c r="D972" t="inlineStr">
@@ -55195,7 +55203,7 @@
       <c r="B997" t="inlineStr"/>
       <c r="C997" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D997" t="inlineStr">
@@ -55393,7 +55401,7 @@
       <c r="B1008" t="inlineStr"/>
       <c r="C1008" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1008" t="inlineStr">
@@ -55411,7 +55419,7 @@
       <c r="B1009" t="inlineStr"/>
       <c r="C1009" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1009" t="inlineStr">
@@ -55645,7 +55653,7 @@
       <c r="B1022" t="inlineStr"/>
       <c r="C1022" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1022" t="inlineStr">
@@ -56461,7 +56469,7 @@
       <c r="B1068" t="inlineStr"/>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1068" t="inlineStr">
@@ -56871,7 +56879,7 @@
       <c r="B1091" t="inlineStr"/>
       <c r="C1091" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1091" t="inlineStr">
@@ -56943,7 +56951,7 @@
       <c r="B1095" t="inlineStr"/>
       <c r="C1095" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1095" t="inlineStr">
@@ -57385,7 +57393,7 @@
       <c r="B1120" t="inlineStr"/>
       <c r="C1120" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1120" t="inlineStr">
@@ -57475,7 +57483,7 @@
       <c r="B1125" t="inlineStr"/>
       <c r="C1125" t="inlineStr">
         <is>
-          <t>PN Intermodal Shuttle</t>
+          <t>PN Containerised Freight</t>
         </is>
       </c>
       <c r="D1125" t="inlineStr">
@@ -58195,7 +58203,7 @@
       <c r="B1165" t="inlineStr"/>
       <c r="C1165" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1165" t="inlineStr">
@@ -58249,7 +58257,7 @@
       <c r="B1168" t="inlineStr"/>
       <c r="C1168" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1168" t="inlineStr">
@@ -58407,7 +58415,7 @@
       <c r="B1177" t="inlineStr"/>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1177" t="inlineStr">
@@ -59145,7 +59153,7 @@
       <c r="B1218" t="inlineStr"/>
       <c r="C1218" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1218" t="inlineStr">
@@ -59181,7 +59189,7 @@
       <c r="B1220" t="inlineStr"/>
       <c r="C1220" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1220" t="inlineStr">
@@ -61273,7 +61281,7 @@
       <c r="B1338" t="inlineStr"/>
       <c r="C1338" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1338" t="inlineStr">
@@ -61485,7 +61493,7 @@
       <c r="B1350" t="inlineStr"/>
       <c r="C1350" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1350" t="inlineStr">
@@ -61729,7 +61737,7 @@
       <c r="B1364" t="inlineStr"/>
       <c r="C1364" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Gippsland Line Service</t>
         </is>
       </c>
       <c r="D1364" t="inlineStr">
@@ -61909,7 +61917,7 @@
       <c r="B1374" t="inlineStr"/>
       <c r="C1374" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1374" t="inlineStr">
@@ -62734,7 +62742,7 @@
       <c r="B1420" t="inlineStr"/>
       <c r="C1420" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1420" t="inlineStr">
@@ -62932,7 +62940,7 @@
       <c r="B1431" t="inlineStr"/>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1431" t="inlineStr">
@@ -62950,7 +62958,7 @@
       <c r="B1432" t="inlineStr"/>
       <c r="C1432" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>North Eastern Line BG Service</t>
         </is>
       </c>
       <c r="D1432" t="inlineStr">
@@ -63167,7 +63175,7 @@
       <c r="B1444" t="inlineStr"/>
       <c r="C1444" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1444" t="inlineStr">
@@ -63239,7 +63247,7 @@
       <c r="B1448" t="inlineStr"/>
       <c r="C1448" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1448" t="inlineStr">
@@ -63293,7 +63301,7 @@
       <c r="B1451" t="inlineStr"/>
       <c r="C1451" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1451" t="inlineStr">
@@ -63897,7 +63905,7 @@
       <c r="B1485" t="inlineStr"/>
       <c r="C1485" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1485" t="inlineStr">
@@ -64721,7 +64729,7 @@
       <c r="B1531" t="inlineStr"/>
       <c r="C1531" t="inlineStr">
         <is>
-          <t>SSR Grain</t>
+          <t>SSR Trip Train (Weston Milling)</t>
         </is>
       </c>
       <c r="D1531" t="inlineStr">
@@ -64757,7 +64765,7 @@
       <c r="B1533" t="inlineStr"/>
       <c r="C1533" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D1533" t="inlineStr">
@@ -64857,7 +64865,7 @@
       <c r="B1539" t="inlineStr"/>
       <c r="C1539" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (ex NT34)</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1539" t="inlineStr">
@@ -64893,7 +64901,7 @@
       <c r="B1541" t="inlineStr"/>
       <c r="C1541" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1541" t="inlineStr">
@@ -65595,7 +65603,7 @@
       <c r="B1580" t="inlineStr"/>
       <c r="C1580" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1580" t="inlineStr">
@@ -66555,7 +66563,7 @@
       <c r="B1634" t="inlineStr"/>
       <c r="C1634" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1634" t="inlineStr">
@@ -66961,7 +66969,7 @@
       <c r="B1657" t="inlineStr"/>
       <c r="C1657" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1657" t="inlineStr">
@@ -67699,7 +67707,7 @@
       <c r="B1698" t="inlineStr"/>
       <c r="C1698" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1698" t="inlineStr">
@@ -70031,7 +70039,7 @@
       <c r="B1834" t="inlineStr"/>
       <c r="C1834" t="inlineStr">
         <is>
-          <t>SSR Loaded Manildra Flour</t>
+          <t>SSR Empty Manildra Flour</t>
         </is>
       </c>
       <c r="D1834" t="inlineStr">
@@ -70211,7 +70219,7 @@
       <c r="B1844" t="inlineStr"/>
       <c r="C1844" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1844" t="inlineStr">
@@ -70337,7 +70345,7 @@
       <c r="B1851" t="inlineStr"/>
       <c r="C1851" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1851" t="inlineStr">
@@ -70589,7 +70597,7 @@
       <c r="B1865" t="inlineStr"/>
       <c r="C1865" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1865" t="inlineStr">
@@ -70625,7 +70633,7 @@
       <c r="B1867" t="inlineStr"/>
       <c r="C1867" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1867" t="inlineStr">
@@ -70697,7 +70705,7 @@
       <c r="B1871" t="inlineStr"/>
       <c r="C1871" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1871" t="inlineStr">
@@ -70787,7 +70795,7 @@
       <c r="B1876" t="inlineStr"/>
       <c r="C1876" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1876" t="inlineStr">
@@ -70859,7 +70867,7 @@
       <c r="B1880" t="inlineStr"/>
       <c r="C1880" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1880" t="inlineStr">
@@ -71039,7 +71047,7 @@
       <c r="B1890" t="inlineStr"/>
       <c r="C1890" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1890" t="inlineStr">
@@ -71075,7 +71083,7 @@
       <c r="B1892" t="inlineStr"/>
       <c r="C1892" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1892" t="inlineStr">
@@ -71435,7 +71443,7 @@
       <c r="B1912" t="inlineStr"/>
       <c r="C1912" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1912" t="inlineStr">
@@ -71543,7 +71551,7 @@
       <c r="B1918" t="inlineStr"/>
       <c r="C1918" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1918" t="inlineStr">
@@ -71687,7 +71695,7 @@
       <c r="B1926" t="inlineStr"/>
       <c r="C1926" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1926" t="inlineStr">
@@ -71777,7 +71785,7 @@
       <c r="B1931" t="inlineStr"/>
       <c r="C1931" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1931" t="inlineStr">
@@ -71867,7 +71875,7 @@
       <c r="B1936" t="inlineStr"/>
       <c r="C1936" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1936" t="inlineStr">
@@ -71885,7 +71893,7 @@
       <c r="B1937" t="inlineStr"/>
       <c r="C1937" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1937" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -868,7 +868,7 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1246,7 +1246,7 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>V/Line Track Scrubbing</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1706,7 +1706,7 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>V/Line Track Scrubbing</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2062,7 +2062,7 @@
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Northern Line</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2440,7 +2440,7 @@
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>North East Line BG Service</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4674,7 +4674,7 @@
       <c r="B241" t="inlineStr"/>
       <c r="C241" t="inlineStr">
         <is>
-          <t>PN Intermodal Trip Train - RSS Crewed</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -6506,7 +6506,11 @@
         </is>
       </c>
       <c r="B344" t="inlineStr"/>
-      <c r="C344" t="inlineStr"/>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>PN Coal</t>
+        </is>
+      </c>
       <c r="D344" t="inlineStr">
         <is>
           <t>2026-04-17 09:47:59</t>
@@ -9672,7 +9676,7 @@
       <c r="B534" t="inlineStr"/>
       <c r="C534" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
@@ -9888,7 +9892,7 @@
       <c r="B546" t="inlineStr"/>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Aurizon Empty Ore (Diverted 4801)</t>
+          <t>Aurizon Loaded Ore (diverted 8402)</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
@@ -11120,7 +11124,7 @@
       <c r="B615" t="inlineStr"/>
       <c r="C615" t="inlineStr">
         <is>
-          <t>QUBE Containerised Freight</t>
+          <t>QUBE Empty Aggregates</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -11298,7 +11302,11 @@
         </is>
       </c>
       <c r="B625" t="inlineStr"/>
-      <c r="C625" t="inlineStr"/>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>PN Containerised Freight</t>
+        </is>
+      </c>
       <c r="D625" t="inlineStr">
         <is>
           <t>2026-04-17 07:15:59</t>
@@ -12340,7 +12348,7 @@
       <c r="B685" t="inlineStr"/>
       <c r="C685" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
@@ -16236,7 +16244,7 @@
       <c r="B905" t="inlineStr"/>
       <c r="C905" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D905" t="inlineStr">
@@ -17874,7 +17882,7 @@
       <c r="B996" t="inlineStr"/>
       <c r="C996" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D996" t="inlineStr">
@@ -17928,7 +17936,7 @@
       <c r="B999" t="inlineStr"/>
       <c r="C999" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D999" t="inlineStr">
@@ -18216,7 +18224,7 @@
       <c r="B1015" t="inlineStr"/>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1015" t="inlineStr">
@@ -19350,7 +19358,7 @@
       <c r="B1078" t="inlineStr"/>
       <c r="C1078" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1078" t="inlineStr">
@@ -19782,7 +19790,7 @@
       <c r="B1102" t="inlineStr"/>
       <c r="C1102" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1102" t="inlineStr">
@@ -20070,7 +20078,7 @@
       <c r="B1118" t="inlineStr"/>
       <c r="C1118" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1118" t="inlineStr">
@@ -20286,7 +20294,7 @@
       <c r="B1130" t="inlineStr"/>
       <c r="C1130" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1130" t="inlineStr">
@@ -20340,7 +20348,7 @@
       <c r="B1133" t="inlineStr"/>
       <c r="C1133" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1133" t="inlineStr">
@@ -21060,7 +21068,7 @@
       <c r="B1173" t="inlineStr"/>
       <c r="C1173" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D1173" t="inlineStr">
@@ -21456,7 +21464,7 @@
       <c r="B1195" t="inlineStr"/>
       <c r="C1195" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1195" t="inlineStr">
@@ -21582,7 +21590,7 @@
       <c r="B1202" t="inlineStr"/>
       <c r="C1202" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1202" t="inlineStr">
@@ -21600,7 +21608,7 @@
       <c r="B1203" t="inlineStr"/>
       <c r="C1203" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1203" t="inlineStr">
@@ -21798,7 +21806,7 @@
       <c r="B1214" t="inlineStr"/>
       <c r="C1214" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1214" t="inlineStr">
@@ -21924,7 +21932,7 @@
       <c r="B1221" t="inlineStr"/>
       <c r="C1221" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1221" t="inlineStr">
@@ -22014,7 +22022,7 @@
       <c r="B1226" t="inlineStr"/>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1226" t="inlineStr">
@@ -22086,7 +22094,7 @@
       <c r="B1230" t="inlineStr"/>
       <c r="C1230" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1230" t="inlineStr">
@@ -22158,7 +22166,7 @@
       <c r="B1234" t="inlineStr"/>
       <c r="C1234" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1234" t="inlineStr">
@@ -22482,7 +22490,7 @@
       <c r="B1252" t="inlineStr"/>
       <c r="C1252" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1252" t="inlineStr">
@@ -22698,7 +22706,7 @@
       <c r="B1264" t="inlineStr"/>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1264" t="inlineStr">
@@ -22734,7 +22742,7 @@
       <c r="B1266" t="inlineStr"/>
       <c r="C1266" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1266" t="inlineStr">
@@ -22896,7 +22904,7 @@
       <c r="B1275" t="inlineStr"/>
       <c r="C1275" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1275" t="inlineStr">
@@ -36936,7 +36944,7 @@
       <c r="B2071" t="inlineStr"/>
       <c r="C2071" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (Forms ST23)</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D2071" t="inlineStr">
@@ -37062,7 +37070,7 @@
       <c r="B2078" t="inlineStr"/>
       <c r="C2078" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty XPT (Forms NT33)</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D2078" t="inlineStr">
@@ -37797,7 +37805,11 @@
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PN Coal</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>2026-04-17 09:47:59</t>
@@ -37933,7 +37945,11 @@
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PN Containerised Freight</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>2026-04-17 07:15:59</t>
@@ -44597,7 +44613,7 @@
       <c r="B392" t="inlineStr"/>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -46109,7 +46125,7 @@
       <c r="B478" t="inlineStr"/>
       <c r="C478" t="inlineStr">
         <is>
-          <t>QUBE Containerised Freight</t>
+          <t>QUBE Empty Aggregates</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -46199,7 +46215,7 @@
       <c r="B483" t="inlineStr"/>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -50305,7 +50321,7 @@
       <c r="B714" t="inlineStr"/>
       <c r="C714" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
@@ -50873,7 +50889,7 @@
       <c r="B746" t="inlineStr"/>
       <c r="C746" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
@@ -51233,7 +51249,7 @@
       <c r="B766" t="inlineStr"/>
       <c r="C766" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D766" t="inlineStr">
@@ -51431,7 +51447,7 @@
       <c r="B777" t="inlineStr"/>
       <c r="C777" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (Forms ST23)</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
@@ -51503,7 +51519,7 @@
       <c r="B781" t="inlineStr"/>
       <c r="C781" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D781" t="inlineStr">
@@ -52981,7 +52997,7 @@
       <c r="B864" t="inlineStr"/>
       <c r="C864" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D864" t="inlineStr">
@@ -53815,7 +53831,7 @@
       <c r="B911" t="inlineStr"/>
       <c r="C911" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D911" t="inlineStr">
@@ -53923,7 +53939,7 @@
       <c r="B917" t="inlineStr"/>
       <c r="C917" t="inlineStr">
         <is>
-          <t>PN Intermodal Trip Train - RSS Crewed</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D917" t="inlineStr">
@@ -54319,7 +54335,7 @@
       <c r="B939" t="inlineStr"/>
       <c r="C939" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D939" t="inlineStr">
@@ -57251,7 +57267,7 @@
       <c r="B1103" t="inlineStr"/>
       <c r="C1103" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1103" t="inlineStr">
@@ -58557,7 +58573,7 @@
       <c r="B1176" t="inlineStr"/>
       <c r="C1176" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>V/Line Track Scrubbing</t>
         </is>
       </c>
       <c r="D1176" t="inlineStr">
@@ -59327,7 +59343,7 @@
       <c r="B1219" t="inlineStr"/>
       <c r="C1219" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>North East Line BG Service</t>
         </is>
       </c>
       <c r="D1219" t="inlineStr">
@@ -62956,7 +62972,7 @@
       <c r="B1423" t="inlineStr"/>
       <c r="C1423" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>V/Line Track Scrubbing</t>
         </is>
       </c>
       <c r="D1423" t="inlineStr">
@@ -63096,7 +63112,7 @@
       <c r="B1431" t="inlineStr"/>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1431" t="inlineStr">
@@ -63475,7 +63491,7 @@
       <c r="B1452" t="inlineStr"/>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1452" t="inlineStr">
@@ -63835,7 +63851,7 @@
       <c r="B1472" t="inlineStr"/>
       <c r="C1472" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty XPT (Forms NT33)</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1472" t="inlineStr">
@@ -63957,7 +63973,7 @@
       <c r="B1479" t="inlineStr"/>
       <c r="C1479" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1479" t="inlineStr">
@@ -65417,7 +65433,7 @@
       <c r="B1561" t="inlineStr"/>
       <c r="C1561" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1561" t="inlineStr">
@@ -66413,7 +66429,7 @@
       <c r="B1617" t="inlineStr"/>
       <c r="C1617" t="inlineStr">
         <is>
-          <t>Aurizon Empty Ore (Diverted 4801)</t>
+          <t>Aurizon Loaded Ore (diverted 8402)</t>
         </is>
       </c>
       <c r="D1617" t="inlineStr">
@@ -66773,7 +66789,7 @@
       <c r="B1637" t="inlineStr"/>
       <c r="C1637" t="inlineStr">
         <is>
-          <t>Northern Line</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1637" t="inlineStr">
@@ -67093,7 +67109,7 @@
       <c r="B1655" t="inlineStr"/>
       <c r="C1655" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1655" t="inlineStr">
@@ -69573,7 +69589,7 @@
       <c r="B1799" t="inlineStr"/>
       <c r="C1799" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1799" t="inlineStr">
@@ -70681,7 +70697,7 @@
       <c r="B1861" t="inlineStr"/>
       <c r="C1861" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1861" t="inlineStr">
@@ -71095,7 +71111,7 @@
       <c r="B1884" t="inlineStr"/>
       <c r="C1884" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1884" t="inlineStr">
@@ -71221,7 +71237,7 @@
       <c r="B1891" t="inlineStr"/>
       <c r="C1891" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1891" t="inlineStr">
@@ -71257,7 +71273,7 @@
       <c r="B1893" t="inlineStr"/>
       <c r="C1893" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1893" t="inlineStr">
@@ -71653,7 +71669,7 @@
       <c r="B1915" t="inlineStr"/>
       <c r="C1915" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1915" t="inlineStr">
@@ -71797,7 +71813,7 @@
       <c r="B1923" t="inlineStr"/>
       <c r="C1923" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1923" t="inlineStr">
@@ -71851,7 +71867,7 @@
       <c r="B1926" t="inlineStr"/>
       <c r="C1926" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1926" t="inlineStr">
@@ -72085,7 +72101,7 @@
       <c r="B1939" t="inlineStr"/>
       <c r="C1939" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1939" t="inlineStr">
@@ -72211,7 +72227,7 @@
       <c r="B1946" t="inlineStr"/>
       <c r="C1946" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1946" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1048,7 +1048,7 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1246,7 +1246,7 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>V/Line Track Scrubbing</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5284,7 +5284,7 @@
       <c r="B276" t="inlineStr"/>
       <c r="C276" t="inlineStr">
         <is>
-          <t>PN Intermodal Trip Train - RSS Crewed</t>
+          <t>Maintenance Train</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -5536,7 +5536,7 @@
       <c r="B290" t="inlineStr"/>
       <c r="C290" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>Empty Coal</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -5590,7 +5590,7 @@
       <c r="B293" t="inlineStr"/>
       <c r="C293" t="inlineStr">
         <is>
-          <t>PN Ballast</t>
+          <t>Empty Coal</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -10590,7 +10590,7 @@
       <c r="B585" t="inlineStr"/>
       <c r="C585" t="inlineStr">
         <is>
-          <t>SCT Steel Shunt</t>
+          <t>SCT Steel Shunt / Wine Train</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
@@ -11142,7 +11142,7 @@
       <c r="B616" t="inlineStr"/>
       <c r="C616" t="inlineStr">
         <is>
-          <t>QUBE Empty Aggregates</t>
+          <t>QUBE Loaded Aggregates</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
@@ -14994,7 +14994,7 @@
       <c r="B834" t="inlineStr"/>
       <c r="C834" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D834" t="inlineStr">
@@ -15740,7 +15740,7 @@
       <c r="B877" t="inlineStr"/>
       <c r="C877" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D877" t="inlineStr">
@@ -15812,7 +15812,7 @@
       <c r="B881" t="inlineStr"/>
       <c r="C881" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D881" t="inlineStr">
@@ -16010,7 +16010,7 @@
       <c r="B892" t="inlineStr"/>
       <c r="C892" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D892" t="inlineStr">
@@ -16046,7 +16046,7 @@
       <c r="B894" t="inlineStr"/>
       <c r="C894" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D894" t="inlineStr">
@@ -16910,7 +16910,7 @@
       <c r="B942" t="inlineStr"/>
       <c r="C942" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D942" t="inlineStr">
@@ -17252,7 +17252,7 @@
       <c r="B961" t="inlineStr"/>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D961" t="inlineStr">
@@ -17720,7 +17720,7 @@
       <c r="B987" t="inlineStr"/>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D987" t="inlineStr">
@@ -17954,7 +17954,7 @@
       <c r="B1000" t="inlineStr"/>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1000" t="inlineStr">
@@ -18170,7 +18170,7 @@
       <c r="B1012" t="inlineStr"/>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1012" t="inlineStr">
@@ -18242,7 +18242,7 @@
       <c r="B1016" t="inlineStr"/>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1016" t="inlineStr">
@@ -18350,7 +18350,7 @@
       <c r="B1022" t="inlineStr"/>
       <c r="C1022" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1022" t="inlineStr">
@@ -18530,7 +18530,7 @@
       <c r="B1032" t="inlineStr"/>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1032" t="inlineStr">
@@ -18602,7 +18602,7 @@
       <c r="B1036" t="inlineStr"/>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1036" t="inlineStr">
@@ -18908,7 +18908,7 @@
       <c r="B1053" t="inlineStr"/>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1053" t="inlineStr">
@@ -19088,7 +19088,7 @@
       <c r="B1063" t="inlineStr"/>
       <c r="C1063" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1063" t="inlineStr">
@@ -19178,7 +19178,7 @@
       <c r="B1068" t="inlineStr"/>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1068" t="inlineStr">
@@ -19682,7 +19682,7 @@
       <c r="B1096" t="inlineStr"/>
       <c r="C1096" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1096" t="inlineStr">
@@ -19808,7 +19808,7 @@
       <c r="B1103" t="inlineStr"/>
       <c r="C1103" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1103" t="inlineStr">
@@ -19952,7 +19952,7 @@
       <c r="B1111" t="inlineStr"/>
       <c r="C1111" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1111" t="inlineStr">
@@ -20024,7 +20024,7 @@
       <c r="B1115" t="inlineStr"/>
       <c r="C1115" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1115" t="inlineStr">
@@ -20096,7 +20096,7 @@
       <c r="B1119" t="inlineStr"/>
       <c r="C1119" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1119" t="inlineStr">
@@ -20222,7 +20222,7 @@
       <c r="B1126" t="inlineStr"/>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1126" t="inlineStr">
@@ -20636,7 +20636,7 @@
       <c r="B1149" t="inlineStr"/>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1149" t="inlineStr">
@@ -20744,7 +20744,7 @@
       <c r="B1155" t="inlineStr"/>
       <c r="C1155" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1155" t="inlineStr">
@@ -21230,7 +21230,7 @@
       <c r="B1182" t="inlineStr"/>
       <c r="C1182" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1182" t="inlineStr">
@@ -21662,7 +21662,7 @@
       <c r="B1206" t="inlineStr"/>
       <c r="C1206" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1206" t="inlineStr">
@@ -21698,7 +21698,7 @@
       <c r="B1208" t="inlineStr"/>
       <c r="C1208" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1208" t="inlineStr">
@@ -21770,7 +21770,7 @@
       <c r="B1212" t="inlineStr"/>
       <c r="C1212" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1212" t="inlineStr">
@@ -21860,7 +21860,7 @@
       <c r="B1217" t="inlineStr"/>
       <c r="C1217" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1217" t="inlineStr">
@@ -21914,7 +21914,7 @@
       <c r="B1220" t="inlineStr"/>
       <c r="C1220" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1220" t="inlineStr">
@@ -21950,7 +21950,7 @@
       <c r="B1222" t="inlineStr"/>
       <c r="C1222" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1222" t="inlineStr">
@@ -22076,7 +22076,7 @@
       <c r="B1229" t="inlineStr"/>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1229" t="inlineStr">
@@ -22112,7 +22112,7 @@
       <c r="B1231" t="inlineStr"/>
       <c r="C1231" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1231" t="inlineStr">
@@ -22184,7 +22184,7 @@
       <c r="B1235" t="inlineStr"/>
       <c r="C1235" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1235" t="inlineStr">
@@ -22238,7 +22238,7 @@
       <c r="B1238" t="inlineStr"/>
       <c r="C1238" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1238" t="inlineStr">
@@ -22382,7 +22382,7 @@
       <c r="B1246" t="inlineStr"/>
       <c r="C1246" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1246" t="inlineStr">
@@ -22508,7 +22508,7 @@
       <c r="B1253" t="inlineStr"/>
       <c r="C1253" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1253" t="inlineStr">
@@ -22544,7 +22544,7 @@
       <c r="B1255" t="inlineStr"/>
       <c r="C1255" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1255" t="inlineStr">
@@ -22760,7 +22760,7 @@
       <c r="B1267" t="inlineStr"/>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1267" t="inlineStr">
@@ -22796,7 +22796,7 @@
       <c r="B1269" t="inlineStr"/>
       <c r="C1269" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1269" t="inlineStr">
@@ -27732,7 +27732,7 @@
       <c r="B1555" t="inlineStr"/>
       <c r="C1555" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1555" t="inlineStr">
@@ -27768,7 +27768,7 @@
       <c r="B1557" t="inlineStr"/>
       <c r="C1557" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1557" t="inlineStr">
@@ -28866,7 +28866,7 @@
       <c r="B1622" t="inlineStr"/>
       <c r="C1622" t="inlineStr">
         <is>
-          <t>QUBE Light Engine Movement</t>
+          <t>QUBE Containerised Freight</t>
         </is>
       </c>
       <c r="D1622" t="inlineStr">
@@ -38549,7 +38549,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -40807,7 +40807,7 @@
       <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -43335,7 +43335,7 @@
       <c r="B319" t="inlineStr"/>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -44249,7 +44249,7 @@
       <c r="B370" t="inlineStr"/>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -45801,7 +45801,7 @@
       <c r="B458" t="inlineStr"/>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -46017,7 +46017,7 @@
       <c r="B470" t="inlineStr"/>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -46121,7 +46121,7 @@
       <c r="B476" t="inlineStr"/>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -46193,7 +46193,7 @@
       <c r="B480" t="inlineStr"/>
       <c r="C480" t="inlineStr">
         <is>
-          <t>QUBE Empty Aggregates</t>
+          <t>QUBE Loaded Aggregates</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
@@ -46283,7 +46283,7 @@
       <c r="B485" t="inlineStr"/>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -49129,7 +49129,7 @@
       <c r="B646" t="inlineStr"/>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
@@ -49507,7 +49507,7 @@
       <c r="B667" t="inlineStr"/>
       <c r="C667" t="inlineStr">
         <is>
-          <t>SCT Steel Shunt</t>
+          <t>SCT Steel Shunt / Wine Train</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
@@ -51317,7 +51317,7 @@
       <c r="B768" t="inlineStr"/>
       <c r="C768" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D768" t="inlineStr">
@@ -53737,7 +53737,7 @@
       <c r="B904" t="inlineStr"/>
       <c r="C904" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D904" t="inlineStr">
@@ -53935,7 +53935,7 @@
       <c r="B915" t="inlineStr"/>
       <c r="C915" t="inlineStr">
         <is>
-          <t>QUBE Light Engine Movement</t>
+          <t>QUBE Containerised Freight</t>
         </is>
       </c>
       <c r="D915" t="inlineStr">
@@ -56037,7 +56037,7 @@
       <c r="B1032" t="inlineStr"/>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1032" t="inlineStr">
@@ -56055,7 +56055,7 @@
       <c r="B1033" t="inlineStr"/>
       <c r="C1033" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1033" t="inlineStr">
@@ -57155,7 +57155,7 @@
       <c r="B1095" t="inlineStr"/>
       <c r="C1095" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1095" t="inlineStr">
@@ -57227,7 +57227,7 @@
       <c r="B1099" t="inlineStr"/>
       <c r="C1099" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1099" t="inlineStr">
@@ -57335,7 +57335,7 @@
       <c r="B1105" t="inlineStr"/>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1105" t="inlineStr">
@@ -58641,7 +58641,7 @@
       <c r="B1178" t="inlineStr"/>
       <c r="C1178" t="inlineStr">
         <is>
-          <t>V/Line Track Scrubbing</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1178" t="inlineStr">
@@ -59983,7 +59983,7 @@
       <c r="B1253" t="inlineStr"/>
       <c r="C1253" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1253" t="inlineStr">
@@ -60001,7 +60001,7 @@
       <c r="B1254" t="inlineStr"/>
       <c r="C1254" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1254" t="inlineStr">
@@ -60511,7 +60511,7 @@
       <c r="B1283" t="inlineStr"/>
       <c r="C1283" t="inlineStr">
         <is>
-          <t>PN Intermodal Trip Train - RSS Crewed</t>
+          <t>Maintenance Train</t>
         </is>
       </c>
       <c r="D1283" t="inlineStr">
@@ -61917,7 +61917,7 @@
       <c r="B1362" t="inlineStr"/>
       <c r="C1362" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1362" t="inlineStr">
@@ -62179,7 +62179,7 @@
       <c r="B1377" t="inlineStr"/>
       <c r="C1377" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1377" t="inlineStr">
@@ -62341,7 +62341,7 @@
       <c r="B1386" t="inlineStr"/>
       <c r="C1386" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1386" t="inlineStr">
@@ -63062,7 +63062,7 @@
       <c r="B1426" t="inlineStr"/>
       <c r="C1426" t="inlineStr">
         <is>
-          <t>PN Ballast</t>
+          <t>Empty Coal</t>
         </is>
       </c>
       <c r="D1426" t="inlineStr">
@@ -63491,7 +63491,7 @@
       <c r="B1450" t="inlineStr"/>
       <c r="C1450" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1450" t="inlineStr">
@@ -63527,7 +63527,7 @@
       <c r="B1452" t="inlineStr"/>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1452" t="inlineStr">
@@ -63563,7 +63563,7 @@
       <c r="B1454" t="inlineStr"/>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1454" t="inlineStr">
@@ -63599,7 +63599,7 @@
       <c r="B1456" t="inlineStr"/>
       <c r="C1456" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1456" t="inlineStr">
@@ -64329,7 +64329,7 @@
       <c r="B1497" t="inlineStr"/>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1497" t="inlineStr">
@@ -64509,7 +64509,7 @@
       <c r="B1507" t="inlineStr"/>
       <c r="C1507" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>Empty Coal</t>
         </is>
       </c>
       <c r="D1507" t="inlineStr">
@@ -70733,7 +70733,7 @@
       <c r="B1861" t="inlineStr"/>
       <c r="C1861" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1861" t="inlineStr">
@@ -70769,7 +70769,7 @@
       <c r="B1863" t="inlineStr"/>
       <c r="C1863" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1863" t="inlineStr">
@@ -70895,7 +70895,7 @@
       <c r="B1870" t="inlineStr"/>
       <c r="C1870" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1870" t="inlineStr">
@@ -70931,7 +70931,7 @@
       <c r="B1872" t="inlineStr"/>
       <c r="C1872" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1872" t="inlineStr">
@@ -70967,7 +70967,7 @@
       <c r="B1874" t="inlineStr"/>
       <c r="C1874" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1874" t="inlineStr">
@@ -71039,7 +71039,7 @@
       <c r="B1878" t="inlineStr"/>
       <c r="C1878" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1878" t="inlineStr">
@@ -71075,7 +71075,7 @@
       <c r="B1880" t="inlineStr"/>
       <c r="C1880" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1880" t="inlineStr">
@@ -71183,7 +71183,7 @@
       <c r="B1886" t="inlineStr"/>
       <c r="C1886" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1886" t="inlineStr">
@@ -71273,7 +71273,7 @@
       <c r="B1891" t="inlineStr"/>
       <c r="C1891" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1891" t="inlineStr">
@@ -71543,7 +71543,7 @@
       <c r="B1906" t="inlineStr"/>
       <c r="C1906" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1906" t="inlineStr">
@@ -71813,7 +71813,7 @@
       <c r="B1921" t="inlineStr"/>
       <c r="C1921" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1921" t="inlineStr">
@@ -71849,7 +71849,7 @@
       <c r="B1923" t="inlineStr"/>
       <c r="C1923" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1923" t="inlineStr">
@@ -71903,7 +71903,7 @@
       <c r="B1926" t="inlineStr"/>
       <c r="C1926" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1926" t="inlineStr">
@@ -71939,7 +71939,7 @@
       <c r="B1928" t="inlineStr"/>
       <c r="C1928" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1928" t="inlineStr">
@@ -72119,7 +72119,7 @@
       <c r="B1938" t="inlineStr"/>
       <c r="C1938" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1938" t="inlineStr">
@@ -72173,7 +72173,7 @@
       <c r="B1941" t="inlineStr"/>
       <c r="C1941" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1941" t="inlineStr">
@@ -72299,7 +72299,7 @@
       <c r="B1948" t="inlineStr"/>
       <c r="C1948" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1948" t="inlineStr">
@@ -73427,7 +73427,7 @@
       <c r="B2016" t="inlineStr"/>
       <c r="C2016" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D2016" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1688,7 +1688,7 @@
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -7346,7 +7346,7 @@
       <c r="B393" t="inlineStr"/>
       <c r="C393" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>ARTC Maintenance Train</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -8374,7 +8374,7 @@
       <c r="B455" t="inlineStr"/>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Copper</t>
+          <t>Aurizon Empty Copper</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -9784,7 +9784,7 @@
       <c r="B540" t="inlineStr"/>
       <c r="C540" t="inlineStr">
         <is>
-          <t>QUBE Light Engine</t>
+          <t>QUBE Grain</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
@@ -11124,7 +11124,7 @@
       <c r="B615" t="inlineStr"/>
       <c r="C615" t="inlineStr">
         <is>
-          <t>SSR Cement</t>
+          <t>SSR Light Engine</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -12442,7 +12442,7 @@
       <c r="B690" t="inlineStr"/>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
@@ -15978,7 +15978,7 @@
       <c r="B890" t="inlineStr"/>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D890" t="inlineStr">
@@ -17976,7 +17976,7 @@
       <c r="B1001" t="inlineStr"/>
       <c r="C1001" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1001" t="inlineStr">
@@ -18264,7 +18264,7 @@
       <c r="B1017" t="inlineStr"/>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1017" t="inlineStr">
@@ -18372,7 +18372,7 @@
       <c r="B1023" t="inlineStr"/>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1023" t="inlineStr">
@@ -18930,7 +18930,7 @@
       <c r="B1054" t="inlineStr"/>
       <c r="C1054" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1054" t="inlineStr">
@@ -19974,7 +19974,7 @@
       <c r="B1112" t="inlineStr"/>
       <c r="C1112" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1112" t="inlineStr">
@@ -20766,7 +20766,7 @@
       <c r="B1156" t="inlineStr"/>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1156" t="inlineStr">
@@ -21648,7 +21648,7 @@
       <c r="B1205" t="inlineStr"/>
       <c r="C1205" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1205" t="inlineStr">
@@ -21684,7 +21684,7 @@
       <c r="B1207" t="inlineStr"/>
       <c r="C1207" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1207" t="inlineStr">
@@ -21720,7 +21720,7 @@
       <c r="B1209" t="inlineStr"/>
       <c r="C1209" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1209" t="inlineStr">
@@ -21972,7 +21972,7 @@
       <c r="B1223" t="inlineStr"/>
       <c r="C1223" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1223" t="inlineStr">
@@ -22134,7 +22134,7 @@
       <c r="B1232" t="inlineStr"/>
       <c r="C1232" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1232" t="inlineStr">
@@ -22530,7 +22530,7 @@
       <c r="B1254" t="inlineStr"/>
       <c r="C1254" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1254" t="inlineStr">
@@ -22782,7 +22782,7 @@
       <c r="B1268" t="inlineStr"/>
       <c r="C1268" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1268" t="inlineStr">
@@ -23080,7 +23080,7 @@
       <c r="B1285" t="inlineStr"/>
       <c r="C1285" t="inlineStr">
         <is>
-          <t>SSR Limestone</t>
+          <t>SSR Cement</t>
         </is>
       </c>
       <c r="D1285" t="inlineStr">
@@ -44289,7 +44289,7 @@
       <c r="B371" t="inlineStr"/>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -46715,7 +46715,7 @@
       <c r="B508" t="inlineStr"/>
       <c r="C508" t="inlineStr">
         <is>
-          <t>QUBE Light Engine</t>
+          <t>QUBE Grain</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
@@ -46751,7 +46751,7 @@
       <c r="B510" t="inlineStr"/>
       <c r="C510" t="inlineStr">
         <is>
-          <t>SSR Cement</t>
+          <t>SSR Light Engine</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
@@ -48611,7 +48611,7 @@
       <c r="B616" t="inlineStr"/>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
@@ -49169,7 +49169,7 @@
       <c r="B647" t="inlineStr"/>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
@@ -51627,7 +51627,7 @@
       <c r="B784" t="inlineStr"/>
       <c r="C784" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
@@ -56059,7 +56059,7 @@
       <c r="B1032" t="inlineStr"/>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1032" t="inlineStr">
@@ -57375,7 +57375,7 @@
       <c r="B1106" t="inlineStr"/>
       <c r="C1106" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1106" t="inlineStr">
@@ -60041,7 +60041,7 @@
       <c r="B1255" t="inlineStr"/>
       <c r="C1255" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1255" t="inlineStr">
@@ -63603,7 +63603,7 @@
       <c r="B1455" t="inlineStr"/>
       <c r="C1455" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1455" t="inlineStr">
@@ -64819,7 +64819,7 @@
       <c r="B1523" t="inlineStr"/>
       <c r="C1523" t="inlineStr">
         <is>
-          <t>SSR Limestone</t>
+          <t>SSR Cement</t>
         </is>
       </c>
       <c r="D1523" t="inlineStr">
@@ -67261,7 +67261,7 @@
       <c r="B1660" t="inlineStr"/>
       <c r="C1660" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1660" t="inlineStr">
@@ -68983,7 +68983,7 @@
       <c r="B1757" t="inlineStr"/>
       <c r="C1757" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>ARTC Maintenance Train</t>
         </is>
       </c>
       <c r="D1757" t="inlineStr">
@@ -69221,7 +69221,7 @@
       <c r="B1772" t="inlineStr"/>
       <c r="C1772" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Copper</t>
+          <t>Aurizon Empty Copper</t>
         </is>
       </c>
       <c r="D1772" t="inlineStr">
@@ -70813,7 +70813,7 @@
       <c r="B1864" t="inlineStr"/>
       <c r="C1864" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1864" t="inlineStr">
@@ -71011,7 +71011,7 @@
       <c r="B1875" t="inlineStr"/>
       <c r="C1875" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1875" t="inlineStr">
@@ -71587,7 +71587,7 @@
       <c r="B1907" t="inlineStr"/>
       <c r="C1907" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1907" t="inlineStr">
@@ -71857,7 +71857,7 @@
       <c r="B1922" t="inlineStr"/>
       <c r="C1922" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1922" t="inlineStr">
@@ -71983,7 +71983,7 @@
       <c r="B1929" t="inlineStr"/>
       <c r="C1929" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1929" t="inlineStr">
@@ -72217,7 +72217,7 @@
       <c r="B1942" t="inlineStr"/>
       <c r="C1942" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1942" t="inlineStr">
@@ -72343,7 +72343,7 @@
       <c r="B1949" t="inlineStr"/>
       <c r="C1949" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1949" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -3062,7 +3062,7 @@
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>QUBE Shunter</t>
+          <t>QUBE Trip Train</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -6594,7 +6594,7 @@
       <c r="B349" t="inlineStr"/>
       <c r="C349" t="inlineStr">
         <is>
-          <t>PN Grain via Greta TSF</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -12424,7 +12424,7 @@
       <c r="B689" t="inlineStr"/>
       <c r="C689" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
@@ -16284,7 +16284,7 @@
       <c r="B907" t="inlineStr"/>
       <c r="C907" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
@@ -18192,7 +18192,7 @@
       <c r="B1013" t="inlineStr"/>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1013" t="inlineStr">
@@ -18372,7 +18372,7 @@
       <c r="B1023" t="inlineStr"/>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1023" t="inlineStr">
@@ -18552,7 +18552,7 @@
       <c r="B1033" t="inlineStr"/>
       <c r="C1033" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1033" t="inlineStr">
@@ -20244,7 +20244,7 @@
       <c r="B1127" t="inlineStr"/>
       <c r="C1127" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1127" t="inlineStr">
@@ -21558,7 +21558,7 @@
       <c r="B1200" t="inlineStr"/>
       <c r="C1200" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1200" t="inlineStr">
@@ -21828,7 +21828,7 @@
       <c r="B1215" t="inlineStr"/>
       <c r="C1215" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1215" t="inlineStr">
@@ -22314,7 +22314,7 @@
       <c r="B1242" t="inlineStr"/>
       <c r="C1242" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1242" t="inlineStr">
@@ -26218,7 +26218,7 @@
       <c r="B1468" t="inlineStr"/>
       <c r="C1468" t="inlineStr">
         <is>
-          <t>QUBE BlueScope Steel</t>
+          <t>QUBE Light Engine</t>
         </is>
       </c>
       <c r="D1468" t="inlineStr">
@@ -37933,7 +37933,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>QUBE Shunter</t>
+          <t>QUBE Trip Train</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -49169,7 +49169,7 @@
       <c r="B647" t="inlineStr"/>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
@@ -50429,7 +50429,7 @@
       <c r="B717" t="inlineStr"/>
       <c r="C717" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
@@ -56167,7 +56167,7 @@
       <c r="B1038" t="inlineStr"/>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1038" t="inlineStr">
@@ -57267,7 +57267,7 @@
       <c r="B1100" t="inlineStr"/>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1100" t="inlineStr">
@@ -62291,7 +62291,7 @@
       <c r="B1382" t="inlineStr"/>
       <c r="C1382" t="inlineStr">
         <is>
-          <t>PN Grain via Greta TSF</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D1382" t="inlineStr">
@@ -63639,7 +63639,7 @@
       <c r="B1457" t="inlineStr"/>
       <c r="C1457" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1457" t="inlineStr">
@@ -63765,7 +63765,7 @@
       <c r="B1464" t="inlineStr"/>
       <c r="C1464" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1464" t="inlineStr">
@@ -70223,7 +70223,7 @@
       <c r="B1831" t="inlineStr"/>
       <c r="C1831" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1831" t="inlineStr">
@@ -71317,7 +71317,7 @@
       <c r="B1892" t="inlineStr"/>
       <c r="C1892" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1892" t="inlineStr">
@@ -71911,7 +71911,7 @@
       <c r="B1925" t="inlineStr"/>
       <c r="C1925" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1925" t="inlineStr">
@@ -73243,7 +73243,7 @@
       <c r="B2003" t="inlineStr"/>
       <c r="C2003" t="inlineStr">
         <is>
-          <t>QUBE BlueScope Steel</t>
+          <t>QUBE Light Engine</t>
         </is>
       </c>
       <c r="D2003" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -3116,7 +3116,7 @@
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>QUBE Light Engine</t>
+          <t>QUBE Containerised Freight</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -4376,7 +4376,7 @@
       <c r="B224" t="inlineStr"/>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Aurizon Empty Ore (Diverted 4801)</t>
+          <t>Aurizon Loaded Ore (diverted 8402)</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -9712,7 +9712,7 @@
       <c r="B536" t="inlineStr"/>
       <c r="C536" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
@@ -9802,7 +9802,7 @@
       <c r="B541" t="inlineStr"/>
       <c r="C541" t="inlineStr">
         <is>
-          <t>QUBE Light Engine</t>
+          <t>QUBE Grain</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -12226,7 +12226,7 @@
       <c r="B678" t="inlineStr"/>
       <c r="C678" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
@@ -15138,7 +15138,7 @@
       <c r="B842" t="inlineStr"/>
       <c r="C842" t="inlineStr">
         <is>
-          <t>South Coast Service</t>
+          <t>South Coast Empty Car Transfer</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
@@ -15762,7 +15762,7 @@
       <c r="B878" t="inlineStr"/>
       <c r="C878" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D878" t="inlineStr">
@@ -18192,7 +18192,7 @@
       <c r="B1013" t="inlineStr"/>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1013" t="inlineStr">
@@ -18552,7 +18552,7 @@
       <c r="B1033" t="inlineStr"/>
       <c r="C1033" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1033" t="inlineStr">
@@ -19110,7 +19110,7 @@
       <c r="B1064" t="inlineStr"/>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1064" t="inlineStr">
@@ -20046,7 +20046,7 @@
       <c r="B1116" t="inlineStr"/>
       <c r="C1116" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1116" t="inlineStr">
@@ -22530,7 +22530,7 @@
       <c r="B1254" t="inlineStr"/>
       <c r="C1254" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1254" t="inlineStr">
@@ -22818,7 +22818,7 @@
       <c r="B1270" t="inlineStr"/>
       <c r="C1270" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1270" t="inlineStr">
@@ -27754,7 +27754,7 @@
       <c r="B1556" t="inlineStr"/>
       <c r="C1556" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1556" t="inlineStr">
@@ -27844,7 +27844,7 @@
       <c r="B1561" t="inlineStr"/>
       <c r="C1561" t="inlineStr">
         <is>
-          <t>Watco Trip Train</t>
+          <t>Watco Light Engine</t>
         </is>
       </c>
       <c r="D1561" t="inlineStr">
@@ -28432,7 +28432,7 @@
       <c r="B1597" t="inlineStr"/>
       <c r="C1597" t="inlineStr">
         <is>
-          <t>PN Trip Train, ex 8124</t>
+          <t>PN Minerals</t>
         </is>
       </c>
       <c r="D1597" t="inlineStr">
@@ -38589,7 +38589,7 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -39089,7 +39089,7 @@
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>QUBE Light Engine</t>
+          <t>QUBE Containerised Freight</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -40965,7 +40965,7 @@
       <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
         <is>
-          <t>PN Trip Train, ex 8124</t>
+          <t>PN Minerals</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -43231,7 +43231,7 @@
       <c r="B312" t="inlineStr"/>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Watco Trip Train</t>
+          <t>Watco Light Engine</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -56559,7 +56559,7 @@
       <c r="B1060" t="inlineStr"/>
       <c r="C1060" t="inlineStr">
         <is>
-          <t>Aurizon Empty Ore (Diverted 4801)</t>
+          <t>Aurizon Loaded Ore (diverted 8402)</t>
         </is>
       </c>
       <c r="D1060" t="inlineStr">
@@ -57267,7 +57267,7 @@
       <c r="B1100" t="inlineStr"/>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1100" t="inlineStr">
@@ -59577,7 +59577,7 @@
       <c r="B1229" t="inlineStr"/>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>QUBE Light Engine</t>
+          <t>QUBE Grain</t>
         </is>
       </c>
       <c r="D1229" t="inlineStr">
@@ -61957,7 +61957,7 @@
       <c r="B1363" t="inlineStr"/>
       <c r="C1363" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1363" t="inlineStr">
@@ -63531,7 +63531,7 @@
       <c r="B1451" t="inlineStr"/>
       <c r="C1451" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1451" t="inlineStr">
@@ -63639,7 +63639,7 @@
       <c r="B1457" t="inlineStr"/>
       <c r="C1457" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1457" t="inlineStr">
@@ -64369,7 +64369,7 @@
       <c r="B1498" t="inlineStr"/>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1498" t="inlineStr">
@@ -64639,7 +64639,7 @@
       <c r="B1513" t="inlineStr"/>
       <c r="C1513" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1513" t="inlineStr">
@@ -64891,7 +64891,7 @@
       <c r="B1527" t="inlineStr"/>
       <c r="C1527" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1527" t="inlineStr">
@@ -70403,7 +70403,7 @@
       <c r="B1841" t="inlineStr"/>
       <c r="C1841" t="inlineStr">
         <is>
-          <t>South Coast Service</t>
+          <t>South Coast Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1841" t="inlineStr">
@@ -71083,7 +71083,7 @@
       <c r="B1879" t="inlineStr"/>
       <c r="C1879" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1879" t="inlineStr">
@@ -72217,7 +72217,7 @@
       <c r="B1942" t="inlineStr"/>
       <c r="C1942" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1942" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -994,7 +994,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -8352,7 +8352,7 @@
       <c r="B454" t="inlineStr"/>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Aurizon Intermodal</t>
+          <t>Aurizon North Quay Container Shuttle</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -9274,7 +9274,7 @@
       <c r="B511" t="inlineStr"/>
       <c r="C511" t="inlineStr">
         <is>
-          <t>PN Containerised Freight</t>
+          <t>PN Wagon Transfer</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
@@ -15134,7 +15134,7 @@
       <c r="B842" t="inlineStr"/>
       <c r="C842" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
@@ -15614,7 +15614,7 @@
       <c r="B870" t="inlineStr"/>
       <c r="C870" t="inlineStr">
         <is>
-          <t>SSR Empty Manildra Flour</t>
+          <t>SSR Freight Shuttle</t>
         </is>
       </c>
       <c r="D870" t="inlineStr">
@@ -17180,7 +17180,7 @@
       <c r="B957" t="inlineStr"/>
       <c r="C957" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D957" t="inlineStr">
@@ -18278,7 +18278,7 @@
       <c r="B1018" t="inlineStr"/>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1018" t="inlineStr">
@@ -18386,7 +18386,7 @@
       <c r="B1024" t="inlineStr"/>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1024" t="inlineStr">
@@ -18566,7 +18566,7 @@
       <c r="B1034" t="inlineStr"/>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1034" t="inlineStr">
@@ -18602,7 +18602,7 @@
       <c r="B1036" t="inlineStr"/>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1036" t="inlineStr">
@@ -20060,7 +20060,7 @@
       <c r="B1117" t="inlineStr"/>
       <c r="C1117" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1117" t="inlineStr">
@@ -20330,7 +20330,7 @@
       <c r="B1132" t="inlineStr"/>
       <c r="C1132" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1132" t="inlineStr">
@@ -21356,7 +21356,7 @@
       <c r="B1189" t="inlineStr"/>
       <c r="C1189" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1189" t="inlineStr">
@@ -21410,7 +21410,7 @@
       <c r="B1192" t="inlineStr"/>
       <c r="C1192" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1192" t="inlineStr">
@@ -21482,7 +21482,7 @@
       <c r="B1196" t="inlineStr"/>
       <c r="C1196" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1196" t="inlineStr">
@@ -21986,7 +21986,7 @@
       <c r="B1224" t="inlineStr"/>
       <c r="C1224" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1224" t="inlineStr">
@@ -22328,7 +22328,7 @@
       <c r="B1243" t="inlineStr"/>
       <c r="C1243" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1243" t="inlineStr">
@@ -22526,7 +22526,7 @@
       <c r="B1254" t="inlineStr"/>
       <c r="C1254" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1254" t="inlineStr">
@@ -22832,7 +22832,7 @@
       <c r="B1271" t="inlineStr"/>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1271" t="inlineStr">
@@ -22958,7 +22958,7 @@
       <c r="B1278" t="inlineStr"/>
       <c r="C1278" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1278" t="inlineStr">
@@ -28050,7 +28050,7 @@
       <c r="B1574" t="inlineStr"/>
       <c r="C1574" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1574" t="inlineStr">
@@ -38257,7 +38257,7 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -38645,7 +38645,7 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -39909,7 +39909,7 @@
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>PN Containerised Freight</t>
+          <t>PN Wagon Transfer</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -40419,7 +40419,7 @@
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -49225,7 +49225,7 @@
       <c r="B649" t="inlineStr"/>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
@@ -53467,7 +53467,7 @@
       <c r="B886" t="inlineStr"/>
       <c r="C886" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D886" t="inlineStr">
@@ -54913,7 +54913,7 @@
       <c r="B967" t="inlineStr"/>
       <c r="C967" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D967" t="inlineStr">
@@ -55935,7 +55935,7 @@
       <c r="B1024" t="inlineStr"/>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1024" t="inlineStr">
@@ -59773,7 +59773,7 @@
       <c r="B1239" t="inlineStr"/>
       <c r="C1239" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1239" t="inlineStr">
@@ -60025,7 +60025,7 @@
       <c r="B1253" t="inlineStr"/>
       <c r="C1253" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1253" t="inlineStr">
@@ -62013,7 +62013,7 @@
       <c r="B1365" t="inlineStr"/>
       <c r="C1365" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1365" t="inlineStr">
@@ -63280,7 +63280,7 @@
       <c r="B1436" t="inlineStr"/>
       <c r="C1436" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1436" t="inlineStr">
@@ -63659,7 +63659,7 @@
       <c r="B1457" t="inlineStr"/>
       <c r="C1457" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1457" t="inlineStr">
@@ -63695,7 +63695,7 @@
       <c r="B1459" t="inlineStr"/>
       <c r="C1459" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1459" t="inlineStr">
@@ -63749,7 +63749,7 @@
       <c r="B1462" t="inlineStr"/>
       <c r="C1462" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1462" t="inlineStr">
@@ -63821,7 +63821,7 @@
       <c r="B1466" t="inlineStr"/>
       <c r="C1466" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1466" t="inlineStr">
@@ -68123,7 +68123,7 @@
       <c r="B1707" t="inlineStr"/>
       <c r="C1707" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1707" t="inlineStr">
@@ -69259,7 +69259,7 @@
       <c r="B1773" t="inlineStr"/>
       <c r="C1773" t="inlineStr">
         <is>
-          <t>Aurizon Intermodal</t>
+          <t>Aurizon North Quay Container Shuttle</t>
         </is>
       </c>
       <c r="D1773" t="inlineStr">
@@ -70635,7 +70635,7 @@
       <c r="B1853" t="inlineStr"/>
       <c r="C1853" t="inlineStr">
         <is>
-          <t>SSR Empty Manildra Flour</t>
+          <t>SSR Freight Shuttle</t>
         </is>
       </c>
       <c r="D1853" t="inlineStr">
@@ -72039,7 +72039,7 @@
       <c r="B1931" t="inlineStr"/>
       <c r="C1931" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1931" t="inlineStr">
@@ -72255,7 +72255,7 @@
       <c r="B1943" t="inlineStr"/>
       <c r="C1943" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1943" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -742,7 +742,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>V/Line Light Engine</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2904,7 +2904,7 @@
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>North East SG Line Service</t>
+          <t>North East Line SG Service</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8352,7 +8352,7 @@
       <c r="B454" t="inlineStr"/>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Aurizon North Quay Container Shuttle</t>
+          <t>Aurizon Intermodal</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -9636,7 +9636,7 @@
       <c r="B532" t="inlineStr"/>
       <c r="C532" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
@@ -9744,7 +9744,7 @@
       <c r="B538" t="inlineStr"/>
       <c r="C538" t="inlineStr">
         <is>
-          <t>SRS Shunter</t>
+          <t>SRS Loaded Log Train</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
@@ -10854,7 +10854,7 @@
       <c r="B600" t="inlineStr"/>
       <c r="C600" t="inlineStr">
         <is>
-          <t>NSW TrainLink Xplorer</t>
+          <t>NSW Trainlink empty car transfer</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
@@ -11896,7 +11896,7 @@
       <c r="B659" t="inlineStr"/>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Grain</t>
+          <t>Aurizon Wagon Transfer</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
@@ -12222,7 +12222,7 @@
       <c r="B678" t="inlineStr"/>
       <c r="C678" t="inlineStr">
         <is>
-          <t>Hunter Railcar Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
@@ -12240,7 +12240,7 @@
       <c r="B679" t="inlineStr"/>
       <c r="C679" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
@@ -12366,7 +12366,7 @@
       <c r="B686" t="inlineStr"/>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
@@ -15152,7 +15152,7 @@
       <c r="B843" t="inlineStr"/>
       <c r="C843" t="inlineStr">
         <is>
-          <t>South Coast Empty Car Transfer</t>
+          <t>South Coast Service</t>
         </is>
       </c>
       <c r="D843" t="inlineStr">
@@ -15776,7 +15776,7 @@
       <c r="B879" t="inlineStr"/>
       <c r="C879" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D879" t="inlineStr">
@@ -16298,7 +16298,7 @@
       <c r="B908" t="inlineStr"/>
       <c r="C908" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D908" t="inlineStr">
@@ -16802,7 +16802,7 @@
       <c r="B936" t="inlineStr"/>
       <c r="C936" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D936" t="inlineStr">
@@ -16856,7 +16856,7 @@
       <c r="B939" t="inlineStr"/>
       <c r="C939" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D939" t="inlineStr">
@@ -17666,7 +17666,7 @@
       <c r="B984" t="inlineStr"/>
       <c r="C984" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D984" t="inlineStr">
@@ -18944,7 +18944,7 @@
       <c r="B1055" t="inlineStr"/>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1055" t="inlineStr">
@@ -19124,7 +19124,7 @@
       <c r="B1065" t="inlineStr"/>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1065" t="inlineStr">
@@ -19340,7 +19340,7 @@
       <c r="B1077" t="inlineStr"/>
       <c r="C1077" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1077" t="inlineStr">
@@ -19952,7 +19952,7 @@
       <c r="B1111" t="inlineStr"/>
       <c r="C1111" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1111" t="inlineStr">
@@ -20474,7 +20474,7 @@
       <c r="B1140" t="inlineStr"/>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1140" t="inlineStr">
@@ -20852,7 +20852,7 @@
       <c r="B1161" t="inlineStr"/>
       <c r="C1161" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1161" t="inlineStr">
@@ -20942,7 +20942,7 @@
       <c r="B1166" t="inlineStr"/>
       <c r="C1166" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1166" t="inlineStr">
@@ -22058,7 +22058,7 @@
       <c r="B1228" t="inlineStr"/>
       <c r="C1228" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1228" t="inlineStr">
@@ -22184,7 +22184,7 @@
       <c r="B1235" t="inlineStr"/>
       <c r="C1235" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1235" t="inlineStr">
@@ -22220,7 +22220,7 @@
       <c r="B1237" t="inlineStr"/>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1237" t="inlineStr">
@@ -22364,7 +22364,7 @@
       <c r="B1245" t="inlineStr"/>
       <c r="C1245" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1245" t="inlineStr">
@@ -22544,7 +22544,7 @@
       <c r="B1255" t="inlineStr"/>
       <c r="C1255" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1255" t="inlineStr">
@@ -43323,7 +43323,7 @@
       <c r="B316" t="inlineStr"/>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -45861,7 +45861,7 @@
       <c r="B459" t="inlineStr"/>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -46379,7 +46379,7 @@
       <c r="B488" t="inlineStr"/>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
@@ -46397,7 +46397,7 @@
       <c r="B489" t="inlineStr"/>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -50485,7 +50485,7 @@
       <c r="B719" t="inlineStr"/>
       <c r="C719" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
@@ -51161,7 +51161,7 @@
       <c r="B757" t="inlineStr"/>
       <c r="C757" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D757" t="inlineStr">
@@ -51881,7 +51881,7 @@
       <c r="B797" t="inlineStr"/>
       <c r="C797" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D797" t="inlineStr">
@@ -52823,7 +52823,7 @@
       <c r="B850" t="inlineStr"/>
       <c r="C850" t="inlineStr">
         <is>
-          <t>SRS Shunter</t>
+          <t>SRS Loaded Log Train</t>
         </is>
       </c>
       <c r="D850" t="inlineStr">
@@ -54139,7 +54139,7 @@
       <c r="B924" t="inlineStr"/>
       <c r="C924" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D924" t="inlineStr">
@@ -54445,7 +54445,7 @@
       <c r="B941" t="inlineStr"/>
       <c r="C941" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D941" t="inlineStr">
@@ -56097,7 +56097,7 @@
       <c r="B1033" t="inlineStr"/>
       <c r="C1033" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Grain</t>
+          <t>Aurizon Wagon Transfer</t>
         </is>
       </c>
       <c r="D1033" t="inlineStr">
@@ -57287,7 +57287,7 @@
       <c r="B1100" t="inlineStr"/>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1100" t="inlineStr">
@@ -57341,7 +57341,7 @@
       <c r="B1103" t="inlineStr"/>
       <c r="C1103" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1103" t="inlineStr">
@@ -62257,7 +62257,7 @@
       <c r="B1379" t="inlineStr"/>
       <c r="C1379" t="inlineStr">
         <is>
-          <t>V/Line Light Engine</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1379" t="inlineStr">
@@ -63587,7 +63587,7 @@
       <c r="B1453" t="inlineStr"/>
       <c r="C1453" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1453" t="inlineStr">
@@ -63767,7 +63767,7 @@
       <c r="B1463" t="inlineStr"/>
       <c r="C1463" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1463" t="inlineStr">
@@ -64695,7 +64695,7 @@
       <c r="B1515" t="inlineStr"/>
       <c r="C1515" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1515" t="inlineStr">
@@ -65943,7 +65943,7 @@
       <c r="B1585" t="inlineStr"/>
       <c r="C1585" t="inlineStr">
         <is>
-          <t>North East SG Line Service</t>
+          <t>North East Line SG Service</t>
         </is>
       </c>
       <c r="D1585" t="inlineStr">
@@ -67245,7 +67245,7 @@
       <c r="B1658" t="inlineStr"/>
       <c r="C1658" t="inlineStr">
         <is>
-          <t>Hunter Railcar Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1658" t="inlineStr">
@@ -69259,7 +69259,7 @@
       <c r="B1773" t="inlineStr"/>
       <c r="C1773" t="inlineStr">
         <is>
-          <t>Aurizon North Quay Container Shuttle</t>
+          <t>Aurizon Intermodal</t>
         </is>
       </c>
       <c r="D1773" t="inlineStr">
@@ -69707,7 +69707,7 @@
       <c r="B1801" t="inlineStr"/>
       <c r="C1801" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1801" t="inlineStr">
@@ -69995,7 +69995,7 @@
       <c r="B1817" t="inlineStr"/>
       <c r="C1817" t="inlineStr">
         <is>
-          <t>NSW TrainLink Xplorer</t>
+          <t>NSW Trainlink empty car transfer</t>
         </is>
       </c>
       <c r="D1817" t="inlineStr">
@@ -70459,7 +70459,7 @@
       <c r="B1843" t="inlineStr"/>
       <c r="C1843" t="inlineStr">
         <is>
-          <t>South Coast Empty Car Transfer</t>
+          <t>South Coast Service</t>
         </is>
       </c>
       <c r="D1843" t="inlineStr">
@@ -71067,7 +71067,7 @@
       <c r="B1877" t="inlineStr"/>
       <c r="C1877" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1877" t="inlineStr">
@@ -71139,7 +71139,7 @@
       <c r="B1881" t="inlineStr"/>
       <c r="C1881" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1881" t="inlineStr">
@@ -71499,7 +71499,7 @@
       <c r="B1901" t="inlineStr"/>
       <c r="C1901" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1901" t="inlineStr">
@@ -72093,7 +72093,7 @@
       <c r="B1934" t="inlineStr"/>
       <c r="C1934" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1934" t="inlineStr">
@@ -72273,7 +72273,7 @@
       <c r="B1944" t="inlineStr"/>
       <c r="C1944" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1944" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -472,7 +472,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -634,7 +634,7 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1688,7 +1688,7 @@
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Northeast Line BG Service</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2958,7 +2958,7 @@
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>North East SG Line Service</t>
+          <t>North East Line SG Service</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -9370,7 +9370,7 @@
       <c r="B517" t="inlineStr"/>
       <c r="C517" t="inlineStr">
         <is>
-          <t>SSR Freight Shuttle</t>
+          <t>SSR Containerised Freight</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
@@ -10266,7 +10266,7 @@
       <c r="B567" t="inlineStr"/>
       <c r="C567" t="inlineStr">
         <is>
-          <t>QUBE Light Engine</t>
+          <t>QUBE Shunter</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
@@ -11120,7 +11120,7 @@
       <c r="B615" t="inlineStr"/>
       <c r="C615" t="inlineStr">
         <is>
-          <t>SSR Cement</t>
+          <t>SSR Loaded Cement</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -15030,7 +15030,7 @@
       <c r="B836" t="inlineStr"/>
       <c r="C836" t="inlineStr">
         <is>
-          <t>Bathurst Bullet - Transfer</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D836" t="inlineStr">
@@ -17126,7 +17126,7 @@
       <c r="B954" t="inlineStr"/>
       <c r="C954" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D954" t="inlineStr">
@@ -17900,7 +17900,7 @@
       <c r="B997" t="inlineStr"/>
       <c r="C997" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D997" t="inlineStr">
@@ -18278,7 +18278,7 @@
       <c r="B1018" t="inlineStr"/>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1018" t="inlineStr">
@@ -18386,7 +18386,7 @@
       <c r="B1024" t="inlineStr"/>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1024" t="inlineStr">
@@ -18566,7 +18566,7 @@
       <c r="B1034" t="inlineStr"/>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1034" t="inlineStr">
@@ -18602,7 +18602,7 @@
       <c r="B1036" t="inlineStr"/>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1036" t="inlineStr">
@@ -19124,7 +19124,7 @@
       <c r="B1065" t="inlineStr"/>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1065" t="inlineStr">
@@ -19844,7 +19844,7 @@
       <c r="B1105" t="inlineStr"/>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1105" t="inlineStr">
@@ -20060,7 +20060,7 @@
       <c r="B1117" t="inlineStr"/>
       <c r="C1117" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1117" t="inlineStr">
@@ -20330,7 +20330,7 @@
       <c r="B1132" t="inlineStr"/>
       <c r="C1132" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1132" t="inlineStr">
@@ -20456,7 +20456,7 @@
       <c r="B1139" t="inlineStr"/>
       <c r="C1139" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1139" t="inlineStr">
@@ -21320,7 +21320,7 @@
       <c r="B1187" t="inlineStr"/>
       <c r="C1187" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1187" t="inlineStr">
@@ -21410,7 +21410,7 @@
       <c r="B1192" t="inlineStr"/>
       <c r="C1192" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1192" t="inlineStr">
@@ -21986,7 +21986,7 @@
       <c r="B1224" t="inlineStr"/>
       <c r="C1224" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1224" t="inlineStr">
@@ -22364,7 +22364,7 @@
       <c r="B1245" t="inlineStr"/>
       <c r="C1245" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1245" t="inlineStr">
@@ -22526,7 +22526,7 @@
       <c r="B1254" t="inlineStr"/>
       <c r="C1254" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1254" t="inlineStr">
@@ -22580,7 +22580,7 @@
       <c r="B1257" t="inlineStr"/>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1257" t="inlineStr">
@@ -22724,7 +22724,7 @@
       <c r="B1265" t="inlineStr"/>
       <c r="C1265" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1265" t="inlineStr">
@@ -22778,7 +22778,7 @@
       <c r="B1268" t="inlineStr"/>
       <c r="C1268" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1268" t="inlineStr">
@@ -28136,7 +28136,7 @@
       <c r="B1579" t="inlineStr"/>
       <c r="C1579" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>Empty Car Provisioning (Forms SN34)</t>
         </is>
       </c>
       <c r="D1579" t="inlineStr">
@@ -37264,7 +37264,7 @@
       <c r="B2089" t="inlineStr"/>
       <c r="C2089" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (Forms ST23)</t>
         </is>
       </c>
       <c r="D2089" t="inlineStr">
@@ -38383,7 +38383,7 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -38645,7 +38645,7 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -39077,7 +39077,7 @@
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>QUBE Light Engine</t>
+          <t>QUBE Shunter</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -40419,7 +40419,7 @@
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -40745,7 +40745,7 @@
       <c r="B169" t="inlineStr"/>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Alamein Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -45653,7 +45653,7 @@
       <c r="B447" t="inlineStr"/>
       <c r="C447" t="inlineStr">
         <is>
-          <t>SSR Freight Shuttle</t>
+          <t>SSR Containerised Freight</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -45897,7 +45897,7 @@
       <c r="B461" t="inlineStr"/>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -45915,7 +45915,7 @@
       <c r="B462" t="inlineStr"/>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -46397,7 +46397,7 @@
       <c r="B489" t="inlineStr"/>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -48667,7 +48667,7 @@
       <c r="B618" t="inlineStr"/>
       <c r="C618" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Northeast Line BG Service</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
@@ -49063,7 +49063,7 @@
       <c r="B640" t="inlineStr"/>
       <c r="C640" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
@@ -49225,7 +49225,7 @@
       <c r="B649" t="inlineStr"/>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
@@ -51305,7 +51305,7 @@
       <c r="B765" t="inlineStr"/>
       <c r="C765" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
@@ -53467,7 +53467,7 @@
       <c r="B886" t="inlineStr"/>
       <c r="C886" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D886" t="inlineStr">
@@ -55917,7 +55917,7 @@
       <c r="B1023" t="inlineStr"/>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1023" t="inlineStr">
@@ -57251,7 +57251,7 @@
       <c r="B1098" t="inlineStr"/>
       <c r="C1098" t="inlineStr">
         <is>
-          <t>Bathurst Bullet - Transfer</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D1098" t="inlineStr">
@@ -63244,7 +63244,7 @@
       <c r="B1434" t="inlineStr"/>
       <c r="C1434" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1434" t="inlineStr">
@@ -63659,7 +63659,7 @@
       <c r="B1457" t="inlineStr"/>
       <c r="C1457" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1457" t="inlineStr">
@@ -63695,7 +63695,7 @@
       <c r="B1459" t="inlineStr"/>
       <c r="C1459" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1459" t="inlineStr">
@@ -63749,7 +63749,7 @@
       <c r="B1462" t="inlineStr"/>
       <c r="C1462" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1462" t="inlineStr">
@@ -65565,7 +65565,7 @@
       <c r="B1564" t="inlineStr"/>
       <c r="C1564" t="inlineStr">
         <is>
-          <t>SSR Cement</t>
+          <t>SSR Loaded Cement</t>
         </is>
       </c>
       <c r="D1564" t="inlineStr">
@@ -67925,7 +67925,7 @@
       <c r="B1696" t="inlineStr"/>
       <c r="C1696" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (Forms ST23)</t>
         </is>
       </c>
       <c r="D1696" t="inlineStr">
@@ -68321,7 +68321,7 @@
       <c r="B1718" t="inlineStr"/>
       <c r="C1718" t="inlineStr">
         <is>
-          <t>North East SG Line Service</t>
+          <t>North East Line SG Service</t>
         </is>
       </c>
       <c r="D1718" t="inlineStr">
@@ -71139,7 +71139,7 @@
       <c r="B1881" t="inlineStr"/>
       <c r="C1881" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1881" t="inlineStr">
@@ -71283,7 +71283,7 @@
       <c r="B1889" t="inlineStr"/>
       <c r="C1889" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1889" t="inlineStr">
@@ -71481,7 +71481,7 @@
       <c r="B1900" t="inlineStr"/>
       <c r="C1900" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1900" t="inlineStr">
@@ -72039,7 +72039,7 @@
       <c r="B1931" t="inlineStr"/>
       <c r="C1931" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1931" t="inlineStr">
@@ -72255,7 +72255,7 @@
       <c r="B1943" t="inlineStr"/>
       <c r="C1943" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1943" t="inlineStr">
@@ -73599,7 +73599,7 @@
       <c r="B2023" t="inlineStr"/>
       <c r="C2023" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>Empty Car Provisioning (Forms SN34)</t>
         </is>
       </c>
       <c r="D2023" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1012,7 +1012,7 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SouthWest Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1264,7 +1264,7 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2206,7 +2206,7 @@
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3468,7 +3468,7 @@
       <c r="B170" t="inlineStr"/>
       <c r="C170" t="inlineStr">
         <is>
-          <t>JBRE "Aurora Australis" - Empty Car Transfer</t>
+          <t>LVR Shunter</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -5162,7 +5162,7 @@
       <c r="B269" t="inlineStr"/>
       <c r="C269" t="inlineStr">
         <is>
-          <t>PN Grain Shuttle</t>
+          <t>PN Cootamundra Shunter</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -5536,7 +5536,7 @@
       <c r="B290" t="inlineStr"/>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Empty Coal</t>
+          <t>Maintenance Train</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -12366,7 +12366,7 @@
       <c r="B686" t="inlineStr"/>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
@@ -18440,7 +18440,7 @@
       <c r="B1027" t="inlineStr"/>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1027" t="inlineStr">
@@ -18566,7 +18566,7 @@
       <c r="B1034" t="inlineStr"/>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1034" t="inlineStr">
@@ -18944,7 +18944,7 @@
       <c r="B1055" t="inlineStr"/>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1055" t="inlineStr">
@@ -19160,7 +19160,7 @@
       <c r="B1067" t="inlineStr"/>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1067" t="inlineStr">
@@ -19340,7 +19340,7 @@
       <c r="B1077" t="inlineStr"/>
       <c r="C1077" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1077" t="inlineStr">
@@ -19844,7 +19844,7 @@
       <c r="B1105" t="inlineStr"/>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1105" t="inlineStr">
@@ -20096,7 +20096,7 @@
       <c r="B1119" t="inlineStr"/>
       <c r="C1119" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1119" t="inlineStr">
@@ -20474,7 +20474,7 @@
       <c r="B1140" t="inlineStr"/>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1140" t="inlineStr">
@@ -20654,7 +20654,7 @@
       <c r="B1150" t="inlineStr"/>
       <c r="C1150" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1150" t="inlineStr">
@@ -20942,7 +20942,7 @@
       <c r="B1166" t="inlineStr"/>
       <c r="C1166" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1166" t="inlineStr">
@@ -21176,7 +21176,7 @@
       <c r="B1179" t="inlineStr"/>
       <c r="C1179" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1179" t="inlineStr">
@@ -21320,7 +21320,7 @@
       <c r="B1187" t="inlineStr"/>
       <c r="C1187" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1187" t="inlineStr">
@@ -21482,7 +21482,7 @@
       <c r="B1196" t="inlineStr"/>
       <c r="C1196" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1196" t="inlineStr">
@@ -21734,7 +21734,7 @@
       <c r="B1210" t="inlineStr"/>
       <c r="C1210" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1210" t="inlineStr">
@@ -21842,7 +21842,7 @@
       <c r="B1216" t="inlineStr"/>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1216" t="inlineStr">
@@ -21860,7 +21860,7 @@
       <c r="B1217" t="inlineStr"/>
       <c r="C1217" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1217" t="inlineStr">
@@ -22220,7 +22220,7 @@
       <c r="B1237" t="inlineStr"/>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1237" t="inlineStr">
@@ -22328,7 +22328,7 @@
       <c r="B1243" t="inlineStr"/>
       <c r="C1243" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1243" t="inlineStr">
@@ -22490,7 +22490,7 @@
       <c r="B1252" t="inlineStr"/>
       <c r="C1252" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1252" t="inlineStr">
@@ -22706,7 +22706,7 @@
       <c r="B1264" t="inlineStr"/>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1264" t="inlineStr">
@@ -22814,7 +22814,7 @@
       <c r="B1270" t="inlineStr"/>
       <c r="C1270" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1270" t="inlineStr">
@@ -22832,7 +22832,7 @@
       <c r="B1271" t="inlineStr"/>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1271" t="inlineStr">
@@ -22850,7 +22850,7 @@
       <c r="B1272" t="inlineStr"/>
       <c r="C1272" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1272" t="inlineStr">
@@ -28050,7 +28050,7 @@
       <c r="B1574" t="inlineStr"/>
       <c r="C1574" t="inlineStr">
         <is>
-          <t>Bathurst Bullet - Transfer</t>
+          <t>Additional Bathurst Service</t>
         </is>
       </c>
       <c r="D1574" t="inlineStr">
@@ -28154,7 +28154,7 @@
       <c r="B1580" t="inlineStr"/>
       <c r="C1580" t="inlineStr">
         <is>
-          <t>Bathurst Bullet - Transfer</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D1580" t="inlineStr">
@@ -37192,7 +37192,7 @@
       <c r="B2085" t="inlineStr"/>
       <c r="C2085" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW TrainLink XPT</t>
         </is>
       </c>
       <c r="D2085" t="inlineStr">
@@ -37210,7 +37210,7 @@
       <c r="B2086" t="inlineStr"/>
       <c r="C2086" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (ex NT34)</t>
         </is>
       </c>
       <c r="D2086" t="inlineStr">
@@ -43323,7 +43323,7 @@
       <c r="B316" t="inlineStr"/>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -44651,7 +44651,7 @@
       <c r="B390" t="inlineStr"/>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -44687,7 +44687,7 @@
       <c r="B392" t="inlineStr"/>
       <c r="C392" t="inlineStr">
         <is>
-          <t>PN Grain Shuttle</t>
+          <t>PN Cootamundra Shunter</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -45861,7 +45861,7 @@
       <c r="B459" t="inlineStr"/>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -46379,7 +46379,7 @@
       <c r="B488" t="inlineStr"/>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
@@ -46987,7 +46987,7 @@
       <c r="B522" t="inlineStr"/>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
@@ -54139,7 +54139,7 @@
       <c r="B924" t="inlineStr"/>
       <c r="C924" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D924" t="inlineStr">
@@ -54913,7 +54913,7 @@
       <c r="B967" t="inlineStr"/>
       <c r="C967" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D967" t="inlineStr">
@@ -55917,7 +55917,7 @@
       <c r="B1023" t="inlineStr"/>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1023" t="inlineStr">
@@ -56241,7 +56241,7 @@
       <c r="B1041" t="inlineStr"/>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1041" t="inlineStr">
@@ -57963,7 +57963,7 @@
       <c r="B1138" t="inlineStr"/>
       <c r="C1138" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1138" t="inlineStr">
@@ -59773,7 +59773,7 @@
       <c r="B1239" t="inlineStr"/>
       <c r="C1239" t="inlineStr">
         <is>
-          <t>Bathurst Bullet - Transfer</t>
+          <t>Additional Bathurst Service</t>
         </is>
       </c>
       <c r="D1239" t="inlineStr">
@@ -60061,7 +60061,7 @@
       <c r="B1255" t="inlineStr"/>
       <c r="C1255" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1255" t="inlineStr">
@@ -60571,7 +60571,7 @@
       <c r="B1284" t="inlineStr"/>
       <c r="C1284" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1284" t="inlineStr">
@@ -62013,7 +62013,7 @@
       <c r="B1365" t="inlineStr"/>
       <c r="C1365" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1365" t="inlineStr">
@@ -63695,7 +63695,7 @@
       <c r="B1459" t="inlineStr"/>
       <c r="C1459" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1459" t="inlineStr">
@@ -63821,7 +63821,7 @@
       <c r="B1466" t="inlineStr"/>
       <c r="C1466" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1466" t="inlineStr">
@@ -63929,7 +63929,7 @@
       <c r="B1472" t="inlineStr"/>
       <c r="C1472" t="inlineStr">
         <is>
-          <t>Bathurst Bullet - Transfer</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D1472" t="inlineStr">
@@ -64605,7 +64605,7 @@
       <c r="B1510" t="inlineStr"/>
       <c r="C1510" t="inlineStr">
         <is>
-          <t>Empty Coal</t>
+          <t>Maintenance Train</t>
         </is>
       </c>
       <c r="D1510" t="inlineStr">
@@ -67101,7 +67101,7 @@
       <c r="B1650" t="inlineStr"/>
       <c r="C1650" t="inlineStr">
         <is>
-          <t>SouthWest Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1650" t="inlineStr">
@@ -68371,7 +68371,7 @@
       <c r="B1721" t="inlineStr"/>
       <c r="C1721" t="inlineStr">
         <is>
-          <t>JBRE "Aurora Australis" - Empty Car Transfer</t>
+          <t>LVR Shunter</t>
         </is>
       </c>
       <c r="D1721" t="inlineStr">
@@ -70941,7 +70941,7 @@
       <c r="B1870" t="inlineStr"/>
       <c r="C1870" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1870" t="inlineStr">
@@ -71067,7 +71067,7 @@
       <c r="B1877" t="inlineStr"/>
       <c r="C1877" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1877" t="inlineStr">
@@ -71283,7 +71283,7 @@
       <c r="B1889" t="inlineStr"/>
       <c r="C1889" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1889" t="inlineStr">
@@ -71319,7 +71319,7 @@
       <c r="B1891" t="inlineStr"/>
       <c r="C1891" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1891" t="inlineStr">
@@ -71499,7 +71499,7 @@
       <c r="B1901" t="inlineStr"/>
       <c r="C1901" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1901" t="inlineStr">
@@ -71589,7 +71589,7 @@
       <c r="B1906" t="inlineStr"/>
       <c r="C1906" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1906" t="inlineStr">
@@ -71913,7 +71913,7 @@
       <c r="B1924" t="inlineStr"/>
       <c r="C1924" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1924" t="inlineStr">
@@ -71967,7 +71967,7 @@
       <c r="B1927" t="inlineStr"/>
       <c r="C1927" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1927" t="inlineStr">
@@ -71985,7 +71985,7 @@
       <c r="B1928" t="inlineStr"/>
       <c r="C1928" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1928" t="inlineStr">
@@ -72381,7 +72381,7 @@
       <c r="B1950" t="inlineStr"/>
       <c r="C1950" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1950" t="inlineStr">
@@ -72417,7 +72417,7 @@
       <c r="B1952" t="inlineStr"/>
       <c r="C1952" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1952" t="inlineStr">
@@ -74571,7 +74571,7 @@
       <c r="B2077" t="inlineStr"/>
       <c r="C2077" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW TrainLink XPT</t>
         </is>
       </c>
       <c r="D2077" t="inlineStr">
@@ -74589,7 +74589,7 @@
       <c r="B2078" t="inlineStr"/>
       <c r="C2078" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (ex NT34)</t>
         </is>
       </c>
       <c r="D2078" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -850,7 +850,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2368,7 +2368,7 @@
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5698,7 +5698,7 @@
       <c r="B299" t="inlineStr"/>
       <c r="C299" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Cement</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -5964,7 +5964,7 @@
       <c r="B314" t="inlineStr"/>
       <c r="C314" t="inlineStr">
         <is>
-          <t>PN Trip Train, pre 1533</t>
+          <t>PN Trip Train</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -9938,7 +9938,7 @@
       <c r="B549" t="inlineStr"/>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Cockburn Cement Empty Coal</t>
+          <t>Aurizon Loaded Grain</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
@@ -10388,7 +10388,7 @@
       <c r="B574" t="inlineStr"/>
       <c r="C574" t="inlineStr">
         <is>
-          <t>SRS Light Engine</t>
+          <t>SRS-Crawfords Container Train</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
@@ -10921,7 +10921,7 @@
       <c r="B604" t="inlineStr"/>
       <c r="C604" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer to Sydney (connects with NP24)</t>
+          <t>NSW Trainlink Xplorer</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
@@ -15681,7 +15681,7 @@
       <c r="B874" t="inlineStr"/>
       <c r="C874" t="inlineStr">
         <is>
-          <t>SSR Freight Shuttle</t>
+          <t>SSR Manildra Grain Shuttle</t>
         </is>
       </c>
       <c r="D874" t="inlineStr">
@@ -15915,7 +15915,7 @@
       <c r="B887" t="inlineStr"/>
       <c r="C887" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D887" t="inlineStr">
@@ -16005,7 +16005,7 @@
       <c r="B892" t="inlineStr"/>
       <c r="C892" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D892" t="inlineStr">
@@ -16113,7 +16113,7 @@
       <c r="B898" t="inlineStr"/>
       <c r="C898" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D898" t="inlineStr">
@@ -16149,7 +16149,7 @@
       <c r="B900" t="inlineStr"/>
       <c r="C900" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D900" t="inlineStr">
@@ -16239,7 +16239,7 @@
       <c r="B905" t="inlineStr"/>
       <c r="C905" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D905" t="inlineStr">
@@ -16329,7 +16329,7 @@
       <c r="B910" t="inlineStr"/>
       <c r="C910" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D910" t="inlineStr">
@@ -16455,7 +16455,7 @@
       <c r="B917" t="inlineStr"/>
       <c r="C917" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D917" t="inlineStr">
@@ -17661,7 +17661,7 @@
       <c r="B984" t="inlineStr"/>
       <c r="C984" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D984" t="inlineStr">
@@ -18219,7 +18219,7 @@
       <c r="B1015" t="inlineStr"/>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1015" t="inlineStr">
@@ -18417,7 +18417,7 @@
       <c r="B1026" t="inlineStr"/>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1026" t="inlineStr">
@@ -18507,7 +18507,7 @@
       <c r="B1031" t="inlineStr"/>
       <c r="C1031" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1031" t="inlineStr">
@@ -18669,7 +18669,7 @@
       <c r="B1040" t="inlineStr"/>
       <c r="C1040" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1040" t="inlineStr">
@@ -18957,7 +18957,7 @@
       <c r="B1056" t="inlineStr"/>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1056" t="inlineStr">
@@ -19191,7 +19191,7 @@
       <c r="B1069" t="inlineStr"/>
       <c r="C1069" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1069" t="inlineStr">
@@ -19911,7 +19911,7 @@
       <c r="B1109" t="inlineStr"/>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1109" t="inlineStr">
@@ -20019,7 +20019,7 @@
       <c r="B1115" t="inlineStr"/>
       <c r="C1115" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1115" t="inlineStr">
@@ -20163,7 +20163,7 @@
       <c r="B1123" t="inlineStr"/>
       <c r="C1123" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1123" t="inlineStr">
@@ -20397,7 +20397,7 @@
       <c r="B1136" t="inlineStr"/>
       <c r="C1136" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1136" t="inlineStr">
@@ -20487,7 +20487,7 @@
       <c r="B1141" t="inlineStr"/>
       <c r="C1141" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1141" t="inlineStr">
@@ -20541,7 +20541,7 @@
       <c r="B1144" t="inlineStr"/>
       <c r="C1144" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1144" t="inlineStr">
@@ -20721,7 +20721,7 @@
       <c r="B1154" t="inlineStr"/>
       <c r="C1154" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1154" t="inlineStr">
@@ -21171,7 +21171,7 @@
       <c r="B1179" t="inlineStr"/>
       <c r="C1179" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1179" t="inlineStr">
@@ -21225,7 +21225,7 @@
       <c r="B1182" t="inlineStr"/>
       <c r="C1182" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1182" t="inlineStr">
@@ -21243,7 +21243,7 @@
       <c r="B1183" t="inlineStr"/>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1183" t="inlineStr">
@@ -21333,7 +21333,7 @@
       <c r="B1188" t="inlineStr"/>
       <c r="C1188" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1188" t="inlineStr">
@@ -21549,7 +21549,7 @@
       <c r="B1200" t="inlineStr"/>
       <c r="C1200" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1200" t="inlineStr">
@@ -21711,7 +21711,7 @@
       <c r="B1209" t="inlineStr"/>
       <c r="C1209" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1209" t="inlineStr">
@@ -21801,7 +21801,7 @@
       <c r="B1214" t="inlineStr"/>
       <c r="C1214" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1214" t="inlineStr">
@@ -21909,7 +21909,7 @@
       <c r="B1220" t="inlineStr"/>
       <c r="C1220" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1220" t="inlineStr">
@@ -21927,7 +21927,7 @@
       <c r="B1221" t="inlineStr"/>
       <c r="C1221" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1221" t="inlineStr">
@@ -21945,7 +21945,7 @@
       <c r="B1222" t="inlineStr"/>
       <c r="C1222" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1222" t="inlineStr">
@@ -22125,7 +22125,7 @@
       <c r="B1232" t="inlineStr"/>
       <c r="C1232" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1232" t="inlineStr">
@@ -22251,7 +22251,7 @@
       <c r="B1239" t="inlineStr"/>
       <c r="C1239" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1239" t="inlineStr">
@@ -22287,7 +22287,7 @@
       <c r="B1241" t="inlineStr"/>
       <c r="C1241" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1241" t="inlineStr">
@@ -22377,7 +22377,7 @@
       <c r="B1246" t="inlineStr"/>
       <c r="C1246" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1246" t="inlineStr">
@@ -22395,7 +22395,7 @@
       <c r="B1247" t="inlineStr"/>
       <c r="C1247" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1247" t="inlineStr">
@@ -22431,7 +22431,7 @@
       <c r="B1249" t="inlineStr"/>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1249" t="inlineStr">
@@ -22467,7 +22467,7 @@
       <c r="B1251" t="inlineStr"/>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1251" t="inlineStr">
@@ -22557,7 +22557,7 @@
       <c r="B1256" t="inlineStr"/>
       <c r="C1256" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1256" t="inlineStr">
@@ -22575,7 +22575,7 @@
       <c r="B1257" t="inlineStr"/>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1257" t="inlineStr">
@@ -22593,7 +22593,7 @@
       <c r="B1258" t="inlineStr"/>
       <c r="C1258" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1258" t="inlineStr">
@@ -22611,7 +22611,7 @@
       <c r="B1259" t="inlineStr"/>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1259" t="inlineStr">
@@ -22647,7 +22647,7 @@
       <c r="B1261" t="inlineStr"/>
       <c r="C1261" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1261" t="inlineStr">
@@ -22665,7 +22665,7 @@
       <c r="B1262" t="inlineStr"/>
       <c r="C1262" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1262" t="inlineStr">
@@ -22701,7 +22701,7 @@
       <c r="B1264" t="inlineStr"/>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1264" t="inlineStr">
@@ -22773,7 +22773,7 @@
       <c r="B1268" t="inlineStr"/>
       <c r="C1268" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1268" t="inlineStr">
@@ -22791,7 +22791,7 @@
       <c r="B1269" t="inlineStr"/>
       <c r="C1269" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1269" t="inlineStr">
@@ -22845,7 +22845,7 @@
       <c r="B1272" t="inlineStr"/>
       <c r="C1272" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1272" t="inlineStr">
@@ -22917,7 +22917,7 @@
       <c r="B1276" t="inlineStr"/>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1276" t="inlineStr">
@@ -23025,7 +23025,7 @@
       <c r="B1282" t="inlineStr"/>
       <c r="C1282" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1282" t="inlineStr">
@@ -23575,7 +23575,7 @@
       <c r="B1313" t="inlineStr"/>
       <c r="C1313" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D1313" t="inlineStr">
@@ -24659,7 +24659,7 @@
       <c r="B1375" t="inlineStr"/>
       <c r="C1375" t="inlineStr">
         <is>
-          <t>JBR The Ghan</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D1375" t="inlineStr">
@@ -25437,7 +25437,11 @@
         </is>
       </c>
       <c r="B1419" t="inlineStr"/>
-      <c r="C1419" t="inlineStr"/>
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>RMS Tour / Transfer</t>
+        </is>
+      </c>
       <c r="D1419" t="inlineStr">
         <is>
           <t>2026-04-17 23:55:34</t>
@@ -27047,7 +27051,7 @@
       <c r="B1515" t="inlineStr"/>
       <c r="C1515" t="inlineStr">
         <is>
-          <t>SSR Bank Engine</t>
+          <t>SSR Light Engine</t>
         </is>
       </c>
       <c r="D1515" t="inlineStr">
@@ -27299,7 +27303,7 @@
       <c r="B1531" t="inlineStr"/>
       <c r="C1531" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>North East Line BG Service</t>
         </is>
       </c>
       <c r="D1531" t="inlineStr">
@@ -27457,7 +27461,7 @@
       <c r="B1540" t="inlineStr"/>
       <c r="C1540" t="inlineStr">
         <is>
-          <t>NorthEast BG Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D1540" t="inlineStr">
@@ -27673,7 +27677,7 @@
       <c r="B1552" t="inlineStr"/>
       <c r="C1552" t="inlineStr">
         <is>
-          <t>SCT Aurizon Loading Transfer</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D1552" t="inlineStr">
@@ -28153,7 +28157,7 @@
       <c r="B1580" t="inlineStr"/>
       <c r="C1580" t="inlineStr">
         <is>
-          <t>Additional Bathurst Service</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1580" t="inlineStr">
@@ -31373,7 +31377,7 @@
       <c r="B1762" t="inlineStr"/>
       <c r="C1762" t="inlineStr">
         <is>
-          <t>Ararat - Melbourne Via Ballarat</t>
+          <t>Ballarat - Melbourne Via Melton</t>
         </is>
       </c>
       <c r="D1762" t="inlineStr">
@@ -31391,7 +31395,7 @@
       <c r="B1763" t="inlineStr"/>
       <c r="C1763" t="inlineStr">
         <is>
-          <t>Ararat - Melbourne Via Ballarat</t>
+          <t>Ballarat - Melbourne Via Melton</t>
         </is>
       </c>
       <c r="D1763" t="inlineStr">
@@ -37291,7 +37295,7 @@
       <c r="B2091" t="inlineStr"/>
       <c r="C2091" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D2091" t="inlineStr">
@@ -37931,7 +37935,7 @@
       <c r="B2127" t="inlineStr"/>
       <c r="C2127" t="inlineStr">
         <is>
-          <t>SRV Tour/Shuttle</t>
+          <t>SRV Tour/Transfer</t>
         </is>
       </c>
       <c r="D2127" t="inlineStr">
@@ -38026,7 +38030,11 @@
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>RMS Tour / Transfer</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>2026-04-17 23:55:34</t>
@@ -38096,7 +38104,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SRV Tour/Shuttle</t>
+          <t>SRV Tour/Transfer</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -38578,7 +38586,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -38808,7 +38816,7 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -40270,7 +40278,7 @@
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -42640,7 +42648,7 @@
       <c r="B269" t="inlineStr"/>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -45418,7 +45426,7 @@
       <c r="B426" t="inlineStr"/>
       <c r="C426" t="inlineStr">
         <is>
-          <t>SSR Bank Engine</t>
+          <t>SSR Light Engine</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -46096,7 +46104,7 @@
       <c r="B465" t="inlineStr"/>
       <c r="C465" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Cement</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -46168,7 +46176,7 @@
       <c r="B469" t="inlineStr"/>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -46186,7 +46194,7 @@
       <c r="B470" t="inlineStr"/>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -46650,7 +46658,7 @@
       <c r="B496" t="inlineStr"/>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
@@ -46668,7 +46676,7 @@
       <c r="B497" t="inlineStr"/>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
@@ -47240,7 +47248,7 @@
       <c r="B529" t="inlineStr"/>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
@@ -47258,7 +47266,7 @@
       <c r="B530" t="inlineStr"/>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
@@ -48704,7 +48712,7 @@
       <c r="B613" t="inlineStr"/>
       <c r="C613" t="inlineStr">
         <is>
-          <t>SRS Light Engine</t>
+          <t>SRS-Crawfords Container Train</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
@@ -49082,7 +49090,7 @@
       <c r="B634" t="inlineStr"/>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
@@ -50324,7 +50332,7 @@
       <c r="B703" t="inlineStr"/>
       <c r="C703" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
@@ -51432,7 +51440,7 @@
       <c r="B765" t="inlineStr"/>
       <c r="C765" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
@@ -53738,7 +53746,7 @@
       <c r="B894" t="inlineStr"/>
       <c r="C894" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D894" t="inlineStr">
@@ -53846,7 +53854,7 @@
       <c r="B900" t="inlineStr"/>
       <c r="C900" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D900" t="inlineStr">
@@ -54770,7 +54778,7 @@
       <c r="B952" t="inlineStr"/>
       <c r="C952" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D952" t="inlineStr">
@@ -55184,7 +55192,7 @@
       <c r="B975" t="inlineStr"/>
       <c r="C975" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D975" t="inlineStr">
@@ -56242,7 +56250,7 @@
       <c r="B1034" t="inlineStr"/>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>JBR The Ghan</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D1034" t="inlineStr">
@@ -56458,7 +56466,7 @@
       <c r="B1046" t="inlineStr"/>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1046" t="inlineStr">
@@ -57576,7 +57584,7 @@
       <c r="B1109" t="inlineStr"/>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1109" t="inlineStr">
@@ -57612,7 +57620,7 @@
       <c r="B1111" t="inlineStr"/>
       <c r="C1111" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1111" t="inlineStr">
@@ -57666,7 +57674,7 @@
       <c r="B1114" t="inlineStr"/>
       <c r="C1114" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1114" t="inlineStr">
@@ -57684,7 +57692,7 @@
       <c r="B1115" t="inlineStr"/>
       <c r="C1115" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1115" t="inlineStr">
@@ -58234,7 +58242,7 @@
       <c r="B1146" t="inlineStr"/>
       <c r="C1146" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1146" t="inlineStr">
@@ -60044,7 +60052,7 @@
       <c r="B1247" t="inlineStr"/>
       <c r="C1247" t="inlineStr">
         <is>
-          <t>Additional Bathurst Service</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1247" t="inlineStr">
@@ -60062,7 +60070,7 @@
       <c r="B1248" t="inlineStr"/>
       <c r="C1248" t="inlineStr">
         <is>
-          <t>Ararat - Melbourne Via Ballarat</t>
+          <t>Ballarat - Melbourne Via Melton</t>
         </is>
       </c>
       <c r="D1248" t="inlineStr">
@@ -60080,7 +60088,7 @@
       <c r="B1249" t="inlineStr"/>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>Ararat - Melbourne Via Ballarat</t>
+          <t>Ballarat - Melbourne Via Melton</t>
         </is>
       </c>
       <c r="D1249" t="inlineStr">
@@ -60170,7 +60178,7 @@
       <c r="B1254" t="inlineStr"/>
       <c r="C1254" t="inlineStr">
         <is>
-          <t>PN Trip Train, pre 1533</t>
+          <t>PN Trip Train</t>
         </is>
       </c>
       <c r="D1254" t="inlineStr">
@@ -60350,7 +60358,7 @@
       <c r="B1264" t="inlineStr"/>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1264" t="inlineStr">
@@ -60554,7 +60562,7 @@
       <c r="B1276" t="inlineStr"/>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>NorthEast BG Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D1276" t="inlineStr">
@@ -61604,7 +61612,7 @@
       <c r="B1335" t="inlineStr"/>
       <c r="C1335" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>North East Line BG Service</t>
         </is>
       </c>
       <c r="D1335" t="inlineStr">
@@ -63086,7 +63094,7 @@
       <c r="B1418" t="inlineStr"/>
       <c r="C1418" t="inlineStr">
         <is>
-          <t>Cockburn Cement Empty Coal</t>
+          <t>Aurizon Loaded Grain</t>
         </is>
       </c>
       <c r="D1418" t="inlineStr">
@@ -63447,7 +63455,7 @@
       <c r="B1438" t="inlineStr"/>
       <c r="C1438" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer to Sydney (connects with NP24)</t>
+          <t>NSW Trainlink Xplorer</t>
         </is>
       </c>
       <c r="D1438" t="inlineStr">
@@ -63515,7 +63523,7 @@
       <c r="B1442" t="inlineStr"/>
       <c r="C1442" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1442" t="inlineStr">
@@ -63551,7 +63559,7 @@
       <c r="B1444" t="inlineStr"/>
       <c r="C1444" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1444" t="inlineStr">
@@ -63893,7 +63901,7 @@
       <c r="B1463" t="inlineStr"/>
       <c r="C1463" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1463" t="inlineStr">
@@ -64019,7 +64027,7 @@
       <c r="B1470" t="inlineStr"/>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1470" t="inlineStr">
@@ -64091,7 +64099,7 @@
       <c r="B1474" t="inlineStr"/>
       <c r="C1474" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1474" t="inlineStr">
@@ -64393,7 +64401,7 @@
       <c r="B1491" t="inlineStr"/>
       <c r="C1491" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1491" t="inlineStr">
@@ -64659,7 +64667,7 @@
       <c r="B1506" t="inlineStr"/>
       <c r="C1506" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1506" t="inlineStr">
@@ -67299,7 +67307,7 @@
       <c r="B1654" t="inlineStr"/>
       <c r="C1654" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1654" t="inlineStr">
@@ -67353,7 +67361,7 @@
       <c r="B1657" t="inlineStr"/>
       <c r="C1657" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1657" t="inlineStr">
@@ -67763,7 +67771,7 @@
       <c r="B1680" t="inlineStr"/>
       <c r="C1680" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1680" t="inlineStr">
@@ -70905,7 +70913,7 @@
       <c r="B1861" t="inlineStr"/>
       <c r="C1861" t="inlineStr">
         <is>
-          <t>SSR Freight Shuttle</t>
+          <t>SSR Manildra Grain Shuttle</t>
         </is>
       </c>
       <c r="D1861" t="inlineStr">
@@ -71175,7 +71183,7 @@
       <c r="B1876" t="inlineStr"/>
       <c r="C1876" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1876" t="inlineStr">
@@ -71211,7 +71219,7 @@
       <c r="B1878" t="inlineStr"/>
       <c r="C1878" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1878" t="inlineStr">
@@ -71265,7 +71273,7 @@
       <c r="B1881" t="inlineStr"/>
       <c r="C1881" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1881" t="inlineStr">
@@ -71301,7 +71309,7 @@
       <c r="B1883" t="inlineStr"/>
       <c r="C1883" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1883" t="inlineStr">
@@ -71409,7 +71417,7 @@
       <c r="B1889" t="inlineStr"/>
       <c r="C1889" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1889" t="inlineStr">
@@ -71553,7 +71561,7 @@
       <c r="B1897" t="inlineStr"/>
       <c r="C1897" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1897" t="inlineStr">
@@ -71589,7 +71597,7 @@
       <c r="B1899" t="inlineStr"/>
       <c r="C1899" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1899" t="inlineStr">
@@ -71769,7 +71777,7 @@
       <c r="B1909" t="inlineStr"/>
       <c r="C1909" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1909" t="inlineStr">
@@ -71859,7 +71867,7 @@
       <c r="B1914" t="inlineStr"/>
       <c r="C1914" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1914" t="inlineStr">
@@ -72183,7 +72191,7 @@
       <c r="B1932" t="inlineStr"/>
       <c r="C1932" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1932" t="inlineStr">
@@ -72237,7 +72245,7 @@
       <c r="B1935" t="inlineStr"/>
       <c r="C1935" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1935" t="inlineStr">
@@ -72255,7 +72263,7 @@
       <c r="B1936" t="inlineStr"/>
       <c r="C1936" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1936" t="inlineStr">
@@ -72363,7 +72371,7 @@
       <c r="B1942" t="inlineStr"/>
       <c r="C1942" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1942" t="inlineStr">
@@ -72471,7 +72479,7 @@
       <c r="B1948" t="inlineStr"/>
       <c r="C1948" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1948" t="inlineStr">
@@ -72525,7 +72533,7 @@
       <c r="B1951" t="inlineStr"/>
       <c r="C1951" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1951" t="inlineStr">
@@ -72543,7 +72551,7 @@
       <c r="B1952" t="inlineStr"/>
       <c r="C1952" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1952" t="inlineStr">
@@ -72579,7 +72587,7 @@
       <c r="B1954" t="inlineStr"/>
       <c r="C1954" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1954" t="inlineStr">
@@ -72651,7 +72659,7 @@
       <c r="B1958" t="inlineStr"/>
       <c r="C1958" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1958" t="inlineStr">
@@ -72687,7 +72695,7 @@
       <c r="B1960" t="inlineStr"/>
       <c r="C1960" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1960" t="inlineStr">
@@ -73779,7 +73787,7 @@
       <c r="B2026" t="inlineStr"/>
       <c r="C2026" t="inlineStr">
         <is>
-          <t>SCT Aurizon Loading Transfer</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D2026" t="inlineStr">
@@ -74823,7 +74831,7 @@
       <c r="B2084" t="inlineStr"/>
       <c r="C2084" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D2084" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -2170,7 +2170,7 @@
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2422,7 +2422,7 @@
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -9776,7 +9776,7 @@
       <c r="B540" t="inlineStr"/>
       <c r="C540" t="inlineStr">
         <is>
-          <t>SRS Loaded Log Train</t>
+          <t>SRS Empty Log Train</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
@@ -10903,7 +10903,7 @@
       <c r="B603" t="inlineStr"/>
       <c r="C603" t="inlineStr">
         <is>
-          <t>NSW Trainlink empty car transfer</t>
+          <t>NSW Trainlink Xplorer</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
@@ -15097,7 +15097,7 @@
       <c r="B840" t="inlineStr"/>
       <c r="C840" t="inlineStr">
         <is>
-          <t>Additional Bathurst Service</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
@@ -16239,7 +16239,7 @@
       <c r="B905" t="inlineStr"/>
       <c r="C905" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D905" t="inlineStr">
@@ -18345,7 +18345,7 @@
       <c r="B1022" t="inlineStr"/>
       <c r="C1022" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1022" t="inlineStr">
@@ -18669,7 +18669,7 @@
       <c r="B1040" t="inlineStr"/>
       <c r="C1040" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1040" t="inlineStr">
@@ -19011,7 +19011,7 @@
       <c r="B1059" t="inlineStr"/>
       <c r="C1059" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1059" t="inlineStr">
@@ -20721,7 +20721,7 @@
       <c r="B1154" t="inlineStr"/>
       <c r="C1154" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1154" t="inlineStr">
@@ -21171,7 +21171,7 @@
       <c r="B1179" t="inlineStr"/>
       <c r="C1179" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1179" t="inlineStr">
@@ -22035,7 +22035,7 @@
       <c r="B1227" t="inlineStr"/>
       <c r="C1227" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1227" t="inlineStr">
@@ -22053,7 +22053,7 @@
       <c r="B1228" t="inlineStr"/>
       <c r="C1228" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1228" t="inlineStr">
@@ -22287,7 +22287,7 @@
       <c r="B1241" t="inlineStr"/>
       <c r="C1241" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1241" t="inlineStr">
@@ -22665,7 +22665,7 @@
       <c r="B1262" t="inlineStr"/>
       <c r="C1262" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1262" t="inlineStr">
@@ -22881,7 +22881,7 @@
       <c r="B1274" t="inlineStr"/>
       <c r="C1274" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1274" t="inlineStr">
@@ -25349,7 +25349,7 @@
       <c r="B1414" t="inlineStr"/>
       <c r="C1414" t="inlineStr">
         <is>
-          <t>PN Freight</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D1414" t="inlineStr">
@@ -38816,7 +38816,7 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -46658,7 +46658,7 @@
       <c r="B496" t="inlineStr"/>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
@@ -53102,7 +53102,7 @@
       <c r="B858" t="inlineStr"/>
       <c r="C858" t="inlineStr">
         <is>
-          <t>SRS Loaded Log Train</t>
+          <t>SRS Empty Log Train</t>
         </is>
       </c>
       <c r="D858" t="inlineStr">
@@ -53494,7 +53494,7 @@
       <c r="B880" t="inlineStr"/>
       <c r="C880" t="inlineStr">
         <is>
-          <t>PN Freight</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D880" t="inlineStr">
@@ -53746,7 +53746,7 @@
       <c r="B894" t="inlineStr"/>
       <c r="C894" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D894" t="inlineStr">
@@ -53854,7 +53854,7 @@
       <c r="B900" t="inlineStr"/>
       <c r="C900" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D900" t="inlineStr">
@@ -56520,7 +56520,7 @@
       <c r="B1049" t="inlineStr"/>
       <c r="C1049" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1049" t="inlineStr">
@@ -57530,7 +57530,7 @@
       <c r="B1106" t="inlineStr"/>
       <c r="C1106" t="inlineStr">
         <is>
-          <t>Additional Bathurst Service</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D1106" t="inlineStr">
@@ -62040,7 +62040,7 @@
       <c r="B1359" t="inlineStr"/>
       <c r="C1359" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1359" t="inlineStr">
@@ -63937,7 +63937,7 @@
       <c r="B1465" t="inlineStr"/>
       <c r="C1465" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1465" t="inlineStr">
@@ -64401,7 +64401,7 @@
       <c r="B1491" t="inlineStr"/>
       <c r="C1491" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1491" t="inlineStr">
@@ -67271,7 +67271,7 @@
       <c r="B1652" t="inlineStr"/>
       <c r="C1652" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1652" t="inlineStr">
@@ -70273,7 +70273,7 @@
       <c r="B1825" t="inlineStr"/>
       <c r="C1825" t="inlineStr">
         <is>
-          <t>NSW Trainlink empty car transfer</t>
+          <t>NSW Trainlink Xplorer</t>
         </is>
       </c>
       <c r="D1825" t="inlineStr">
@@ -71345,7 +71345,7 @@
       <c r="B1885" t="inlineStr"/>
       <c r="C1885" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1885" t="inlineStr">
@@ -71867,7 +71867,7 @@
       <c r="B1914" t="inlineStr"/>
       <c r="C1914" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1914" t="inlineStr">
@@ -72299,7 +72299,7 @@
       <c r="B1938" t="inlineStr"/>
       <c r="C1938" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1938" t="inlineStr">
@@ -72317,7 +72317,7 @@
       <c r="B1939" t="inlineStr"/>
       <c r="C1939" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1939" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -472,7 +472,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4902,7 +4902,11 @@
         </is>
       </c>
       <c r="B254" t="inlineStr"/>
-      <c r="C254" t="inlineStr"/>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>PN Light Engine</t>
+        </is>
+      </c>
       <c r="D254" t="inlineStr">
         <is>
           <t>2026-04-18 05:28:15</t>
@@ -5212,7 +5216,7 @@
       <c r="B272" t="inlineStr"/>
       <c r="C272" t="inlineStr">
         <is>
-          <t>PN Cootamundra Shunter</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -5910,7 +5914,7 @@
       <c r="B311" t="inlineStr"/>
       <c r="C311" t="inlineStr">
         <is>
-          <t>PN Trip Train, pre 1821</t>
+          <t>PN Garbage Train</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -6608,7 +6612,7 @@
       <c r="B350" t="inlineStr"/>
       <c r="C350" t="inlineStr">
         <is>
-          <t>PN Grain</t>
+          <t>PN Morandoo Shunter</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -7728,7 +7732,7 @@
       <c r="B416" t="inlineStr"/>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Qube Light Engine</t>
+          <t>Qube Trip Train</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -10881,7 +10885,8 @@
       <c r="B602" t="inlineStr"/>
       <c r="C602" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer (Joins SP34)</t>
+          <t>NSW TrainLink Xplorer
+(from NP23)</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
@@ -16549,7 +16554,7 @@
       <c r="B922" t="inlineStr"/>
       <c r="C922" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D922" t="inlineStr">
@@ -18709,7 +18714,7 @@
       <c r="B1042" t="inlineStr"/>
       <c r="C1042" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1042" t="inlineStr">
@@ -18889,7 +18894,7 @@
       <c r="B1052" t="inlineStr"/>
       <c r="C1052" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1052" t="inlineStr">
@@ -19051,7 +19056,7 @@
       <c r="B1061" t="inlineStr"/>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1061" t="inlineStr">
@@ -20203,7 +20208,7 @@
       <c r="B1125" t="inlineStr"/>
       <c r="C1125" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1125" t="inlineStr">
@@ -20581,7 +20586,7 @@
       <c r="B1146" t="inlineStr"/>
       <c r="C1146" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1146" t="inlineStr">
@@ -21283,7 +21288,7 @@
       <c r="B1185" t="inlineStr"/>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1185" t="inlineStr">
@@ -21589,7 +21594,7 @@
       <c r="B1202" t="inlineStr"/>
       <c r="C1202" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1202" t="inlineStr">
@@ -21967,7 +21972,7 @@
       <c r="B1223" t="inlineStr"/>
       <c r="C1223" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1223" t="inlineStr">
@@ -22615,7 +22620,7 @@
       <c r="B1259" t="inlineStr"/>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1259" t="inlineStr">
@@ -22633,7 +22638,7 @@
       <c r="B1260" t="inlineStr"/>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1260" t="inlineStr">
@@ -22687,7 +22692,7 @@
       <c r="B1263" t="inlineStr"/>
       <c r="C1263" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1263" t="inlineStr">
@@ -22957,7 +22962,7 @@
       <c r="B1278" t="inlineStr"/>
       <c r="C1278" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1278" t="inlineStr">
@@ -23065,7 +23070,7 @@
       <c r="B1284" t="inlineStr"/>
       <c r="C1284" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1284" t="inlineStr">
@@ -24065,7 +24070,7 @@
       <c r="B1340" t="inlineStr"/>
       <c r="C1340" t="inlineStr">
         <is>
-          <t>PN Shunter</t>
+          <t>PN Infrabuild Steel</t>
         </is>
       </c>
       <c r="D1340" t="inlineStr">
@@ -26239,7 +26244,7 @@
       <c r="B1469" t="inlineStr"/>
       <c r="C1469" t="inlineStr">
         <is>
-          <t>QUBE Container Train</t>
+          <t>QUBE Shuttle</t>
         </is>
       </c>
       <c r="D1469" t="inlineStr">
@@ -27645,7 +27650,7 @@
       <c r="B1550" t="inlineStr"/>
       <c r="C1550" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>North Eastern Line BG Service</t>
         </is>
       </c>
       <c r="D1550" t="inlineStr">
@@ -33573,7 +33578,7 @@
       <c r="B1884" t="inlineStr"/>
       <c r="C1884" t="inlineStr">
         <is>
-          <t>Traralgon - Melbourne Via Pakenham, Moe &amp; Morwell</t>
+          <t>Gippsland Line Service</t>
         </is>
       </c>
       <c r="D1884" t="inlineStr">
@@ -38102,7 +38107,11 @@
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PN Light Engine</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>2026-04-18 05:28:15</t>
@@ -41282,7 +41291,7 @@
       <c r="B188" t="inlineStr"/>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -45120,7 +45129,7 @@
       <c r="B405" t="inlineStr"/>
       <c r="C405" t="inlineStr">
         <is>
-          <t>PN Cootamundra Shunter</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -45472,7 +45481,7 @@
       <c r="B425" t="inlineStr"/>
       <c r="C425" t="inlineStr">
         <is>
-          <t>PN Grain</t>
+          <t>PN Morandoo Shunter</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -46330,7 +46339,7 @@
       <c r="B474" t="inlineStr"/>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
@@ -47826,7 +47835,7 @@
       <c r="B558" t="inlineStr"/>
       <c r="C558" t="inlineStr">
         <is>
-          <t>QUBE Container Train</t>
+          <t>QUBE Shuttle</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
@@ -49068,7 +49077,7 @@
       <c r="B629" t="inlineStr"/>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
@@ -49500,7 +49509,7 @@
       <c r="B653" t="inlineStr"/>
       <c r="C653" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
@@ -52642,7 +52651,7 @@
       <c r="B828" t="inlineStr"/>
       <c r="C828" t="inlineStr">
         <is>
-          <t>PN Trip Train, pre 1821</t>
+          <t>PN Garbage Train</t>
         </is>
       </c>
       <c r="D828" t="inlineStr">
@@ -53904,7 +53913,7 @@
       <c r="B899" t="inlineStr"/>
       <c r="C899" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
@@ -55350,7 +55359,7 @@
       <c r="B980" t="inlineStr"/>
       <c r="C980" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D980" t="inlineStr">
@@ -58400,7 +58409,7 @@
       <c r="B1151" t="inlineStr"/>
       <c r="C1151" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1151" t="inlineStr">
@@ -58832,7 +58841,7 @@
       <c r="B1175" t="inlineStr"/>
       <c r="C1175" t="inlineStr">
         <is>
-          <t>Traralgon - Melbourne Via Pakenham, Moe &amp; Morwell</t>
+          <t>Gippsland Line Service</t>
         </is>
       </c>
       <c r="D1175" t="inlineStr">
@@ -59998,7 +60007,7 @@
       <c r="B1240" t="inlineStr"/>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>Qube Light Engine</t>
+          <t>Qube Trip Train</t>
         </is>
       </c>
       <c r="D1240" t="inlineStr">
@@ -63717,7 +63726,7 @@
       <c r="B1449" t="inlineStr"/>
       <c r="C1449" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1449" t="inlineStr">
@@ -64275,7 +64284,7 @@
       <c r="B1480" t="inlineStr"/>
       <c r="C1480" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1480" t="inlineStr">
@@ -64505,7 +64514,8 @@
       <c r="B1493" t="inlineStr"/>
       <c r="C1493" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer (Joins SP34)</t>
+          <t>NSW TrainLink Xplorer
+(from NP23)</t>
         </is>
       </c>
       <c r="D1493" t="inlineStr">
@@ -64825,7 +64835,7 @@
       <c r="B1511" t="inlineStr"/>
       <c r="C1511" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1511" t="inlineStr">
@@ -66073,7 +66083,7 @@
       <c r="B1581" t="inlineStr"/>
       <c r="C1581" t="inlineStr">
         <is>
-          <t>PN Shunter</t>
+          <t>PN Infrabuild Steel</t>
         </is>
       </c>
       <c r="D1581" t="inlineStr">
@@ -71503,7 +71513,7 @@
       <c r="B1890" t="inlineStr"/>
       <c r="C1890" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1890" t="inlineStr">
@@ -71755,7 +71765,7 @@
       <c r="B1904" t="inlineStr"/>
       <c r="C1904" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1904" t="inlineStr">
@@ -71935,7 +71945,7 @@
       <c r="B1914" t="inlineStr"/>
       <c r="C1914" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1914" t="inlineStr">
@@ -72421,7 +72431,7 @@
       <c r="B1941" t="inlineStr"/>
       <c r="C1941" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1941" t="inlineStr">
@@ -72691,7 +72701,7 @@
       <c r="B1956" t="inlineStr"/>
       <c r="C1956" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1956" t="inlineStr">
@@ -72853,7 +72863,7 @@
       <c r="B1965" t="inlineStr"/>
       <c r="C1965" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1965" t="inlineStr">
@@ -73909,7 +73919,7 @@
       <c r="B2029" t="inlineStr"/>
       <c r="C2029" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>North Eastern Line BG Service</t>
         </is>
       </c>
       <c r="D2029" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -490,7 +490,7 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1476,7 +1476,7 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Northeast Line BG Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2422,7 +2422,7 @@
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2868,7 +2868,7 @@
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>North East SG Line Service</t>
+          <t>North East Line SG Service</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -2940,7 +2940,7 @@
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>V/Line SG Special</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -3436,7 +3436,7 @@
       <c r="B168" t="inlineStr"/>
       <c r="C168" t="inlineStr">
         <is>
-          <t>THNSW Tour/Transfer</t>
+          <t>THNSW Tour / Transfer</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -3594,7 +3594,7 @@
       <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer</t>
+          <t>NSW Trainlink - Light Engine</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -5806,7 +5806,7 @@
       <c r="B305" t="inlineStr"/>
       <c r="C305" t="inlineStr">
         <is>
-          <t>PN Cootamundra Shunter</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -8650,7 +8650,7 @@
       <c r="B471" t="inlineStr"/>
       <c r="C471" t="inlineStr">
         <is>
-          <t>MRL Empty Iron Ore</t>
+          <t>MRL Loaded Iron Ore</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -11224,7 +11224,7 @@
       <c r="B621" t="inlineStr"/>
       <c r="C621" t="inlineStr">
         <is>
-          <t>SSR Light Engine</t>
+          <t>SSR Container Train Banker</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
@@ -12470,7 +12470,7 @@
       <c r="B692" t="inlineStr"/>
       <c r="C692" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
@@ -15138,7 +15138,7 @@
       <c r="B842" t="inlineStr"/>
       <c r="C842" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Additional Bathurst Service</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
@@ -16050,7 +16050,7 @@
       <c r="B894" t="inlineStr"/>
       <c r="C894" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D894" t="inlineStr">
@@ -16194,7 +16194,7 @@
       <c r="B902" t="inlineStr"/>
       <c r="C902" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D902" t="inlineStr">
@@ -16284,7 +16284,7 @@
       <c r="B907" t="inlineStr"/>
       <c r="C907" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
@@ -16374,7 +16374,7 @@
       <c r="B912" t="inlineStr"/>
       <c r="C912" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D912" t="inlineStr">
@@ -17976,7 +17976,7 @@
       <c r="B1001" t="inlineStr"/>
       <c r="C1001" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1001" t="inlineStr">
@@ -18390,7 +18390,7 @@
       <c r="B1024" t="inlineStr"/>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1024" t="inlineStr">
@@ -18480,7 +18480,7 @@
       <c r="B1029" t="inlineStr"/>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1029" t="inlineStr">
@@ -18552,7 +18552,7 @@
       <c r="B1033" t="inlineStr"/>
       <c r="C1033" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1033" t="inlineStr">
@@ -20064,7 +20064,7 @@
       <c r="B1117" t="inlineStr"/>
       <c r="C1117" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1117" t="inlineStr">
@@ -20172,7 +20172,7 @@
       <c r="B1123" t="inlineStr"/>
       <c r="C1123" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1123" t="inlineStr">
@@ -20532,7 +20532,7 @@
       <c r="B1143" t="inlineStr"/>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1143" t="inlineStr">
@@ -20568,7 +20568,7 @@
       <c r="B1145" t="inlineStr"/>
       <c r="C1145" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1145" t="inlineStr">
@@ -20766,7 +20766,7 @@
       <c r="B1156" t="inlineStr"/>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1156" t="inlineStr">
@@ -21216,7 +21216,7 @@
       <c r="B1181" t="inlineStr"/>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1181" t="inlineStr">
@@ -21270,7 +21270,7 @@
       <c r="B1184" t="inlineStr"/>
       <c r="C1184" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1184" t="inlineStr">
@@ -21846,7 +21846,7 @@
       <c r="B1216" t="inlineStr"/>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1216" t="inlineStr">
@@ -21954,7 +21954,7 @@
       <c r="B1222" t="inlineStr"/>
       <c r="C1222" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1222" t="inlineStr">
@@ -21990,7 +21990,7 @@
       <c r="B1224" t="inlineStr"/>
       <c r="C1224" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1224" t="inlineStr">
@@ -22080,7 +22080,7 @@
       <c r="B1229" t="inlineStr"/>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1229" t="inlineStr">
@@ -22242,7 +22242,7 @@
       <c r="B1238" t="inlineStr"/>
       <c r="C1238" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1238" t="inlineStr">
@@ -22296,7 +22296,7 @@
       <c r="B1241" t="inlineStr"/>
       <c r="C1241" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1241" t="inlineStr">
@@ -22332,7 +22332,7 @@
       <c r="B1243" t="inlineStr"/>
       <c r="C1243" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1243" t="inlineStr">
@@ -22440,7 +22440,7 @@
       <c r="B1249" t="inlineStr"/>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1249" t="inlineStr">
@@ -22602,7 +22602,7 @@
       <c r="B1258" t="inlineStr"/>
       <c r="C1258" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1258" t="inlineStr">
@@ -22656,7 +22656,7 @@
       <c r="B1261" t="inlineStr"/>
       <c r="C1261" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1261" t="inlineStr">
@@ -22710,7 +22710,7 @@
       <c r="B1264" t="inlineStr"/>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1264" t="inlineStr">
@@ -22746,7 +22746,7 @@
       <c r="B1266" t="inlineStr"/>
       <c r="C1266" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1266" t="inlineStr">
@@ -22836,7 +22836,7 @@
       <c r="B1271" t="inlineStr"/>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1271" t="inlineStr">
@@ -22926,7 +22926,7 @@
       <c r="B1276" t="inlineStr"/>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1276" t="inlineStr">
@@ -22944,7 +22944,7 @@
       <c r="B1277" t="inlineStr"/>
       <c r="C1277" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1277" t="inlineStr">
@@ -27348,7 +27348,7 @@
       <c r="B1533" t="inlineStr"/>
       <c r="C1533" t="inlineStr">
         <is>
-          <t>North East Line BG Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D1533" t="inlineStr">
@@ -31544,7 +31544,7 @@
       <c r="B1771" t="inlineStr"/>
       <c r="C1771" t="inlineStr">
         <is>
-          <t>Ararat - Melbourne Via Ballarat</t>
+          <t>Ballarat - Melbourne Via Melton</t>
         </is>
       </c>
       <c r="D1771" t="inlineStr">
@@ -38213,7 +38213,7 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>THNSW Tour/Transfer</t>
+          <t>THNSW Tour / Transfer</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -38749,7 +38749,7 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -38979,7 +38979,7 @@
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -39087,7 +39087,7 @@
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -42811,7 +42811,7 @@
       <c r="B274" t="inlineStr"/>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -46357,7 +46357,7 @@
       <c r="B475" t="inlineStr"/>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -46821,7 +46821,7 @@
       <c r="B501" t="inlineStr"/>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
@@ -47249,7 +47249,7 @@
       <c r="B525" t="inlineStr"/>
       <c r="C525" t="inlineStr">
         <is>
-          <t>SSR Light Engine</t>
+          <t>SSR Container Train Banker</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
@@ -47429,7 +47429,7 @@
       <c r="B535" t="inlineStr"/>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
@@ -48083,7 +48083,7 @@
       <c r="B572" t="inlineStr"/>
       <c r="C572" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer</t>
+          <t>NSW Trainlink - Light Engine</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
@@ -50013,7 +50013,7 @@
       <c r="B681" t="inlineStr"/>
       <c r="C681" t="inlineStr">
         <is>
-          <t>Northeast Line BG Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
@@ -51607,7 +51607,7 @@
       <c r="B770" t="inlineStr"/>
       <c r="C770" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D770" t="inlineStr">
@@ -52633,7 +52633,7 @@
       <c r="B827" t="inlineStr"/>
       <c r="C827" t="inlineStr">
         <is>
-          <t>PN Cootamundra Shunter</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
@@ -54021,7 +54021,7 @@
       <c r="B905" t="inlineStr"/>
       <c r="C905" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D905" t="inlineStr">
@@ -55485,7 +55485,7 @@
       <c r="B987" t="inlineStr"/>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Ararat - Melbourne Via Ballarat</t>
+          <t>Ballarat - Melbourne Via Melton</t>
         </is>
       </c>
       <c r="D987" t="inlineStr">
@@ -56687,7 +56687,7 @@
       <c r="B1054" t="inlineStr"/>
       <c r="C1054" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1054" t="inlineStr">
@@ -57697,7 +57697,7 @@
       <c r="B1111" t="inlineStr"/>
       <c r="C1111" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Additional Bathurst Service</t>
         </is>
       </c>
       <c r="D1111" t="inlineStr">
@@ -57787,7 +57787,7 @@
       <c r="B1116" t="inlineStr"/>
       <c r="C1116" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1116" t="inlineStr">
@@ -57841,7 +57841,7 @@
       <c r="B1119" t="inlineStr"/>
       <c r="C1119" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1119" t="inlineStr">
@@ -57859,7 +57859,7 @@
       <c r="B1120" t="inlineStr"/>
       <c r="C1120" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1120" t="inlineStr">
@@ -61779,7 +61779,7 @@
       <c r="B1340" t="inlineStr"/>
       <c r="C1340" t="inlineStr">
         <is>
-          <t>North East Line BG Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D1340" t="inlineStr">
@@ -62207,7 +62207,7 @@
       <c r="B1364" t="inlineStr"/>
       <c r="C1364" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1364" t="inlineStr">
@@ -62459,7 +62459,7 @@
       <c r="B1378" t="inlineStr"/>
       <c r="C1378" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1378" t="inlineStr">
@@ -62865,7 +62865,7 @@
       <c r="B1401" t="inlineStr"/>
       <c r="C1401" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1401" t="inlineStr">
@@ -64104,7 +64104,7 @@
       <c r="B1470" t="inlineStr"/>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1470" t="inlineStr">
@@ -64266,7 +64266,7 @@
       <c r="B1479" t="inlineStr"/>
       <c r="C1479" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1479" t="inlineStr">
@@ -64569,7 +64569,7 @@
       <c r="B1496" t="inlineStr"/>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1496" t="inlineStr">
@@ -65533,7 +65533,7 @@
       <c r="B1550" t="inlineStr"/>
       <c r="C1550" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1550" t="inlineStr">
@@ -66407,7 +66407,7 @@
       <c r="B1599" t="inlineStr"/>
       <c r="C1599" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>V/Line SG Special</t>
         </is>
       </c>
       <c r="D1599" t="inlineStr">
@@ -67097,7 +67097,7 @@
       <c r="B1638" t="inlineStr"/>
       <c r="C1638" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1638" t="inlineStr">
@@ -67939,7 +67939,7 @@
       <c r="B1685" t="inlineStr"/>
       <c r="C1685" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1685" t="inlineStr">
@@ -68749,7 +68749,7 @@
       <c r="B1730" t="inlineStr"/>
       <c r="C1730" t="inlineStr">
         <is>
-          <t>North East SG Line Service</t>
+          <t>North East Line SG Service</t>
         </is>
       </c>
       <c r="D1730" t="inlineStr">
@@ -69831,7 +69831,7 @@
       <c r="B1793" t="inlineStr"/>
       <c r="C1793" t="inlineStr">
         <is>
-          <t>MRL Empty Iron Ore</t>
+          <t>MRL Loaded Iron Ore</t>
         </is>
       </c>
       <c r="D1793" t="inlineStr">
@@ -71369,7 +71369,7 @@
       <c r="B1882" t="inlineStr"/>
       <c r="C1882" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1882" t="inlineStr">
@@ -71387,7 +71387,7 @@
       <c r="B1883" t="inlineStr"/>
       <c r="C1883" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1883" t="inlineStr">
@@ -71477,7 +71477,7 @@
       <c r="B1888" t="inlineStr"/>
       <c r="C1888" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1888" t="inlineStr">
@@ -71927,7 +71927,7 @@
       <c r="B1913" t="inlineStr"/>
       <c r="C1913" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1913" t="inlineStr">
@@ -72035,7 +72035,7 @@
       <c r="B1919" t="inlineStr"/>
       <c r="C1919" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1919" t="inlineStr">
@@ -72359,7 +72359,7 @@
       <c r="B1937" t="inlineStr"/>
       <c r="C1937" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1937" t="inlineStr">
@@ -72413,7 +72413,7 @@
       <c r="B1940" t="inlineStr"/>
       <c r="C1940" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1940" t="inlineStr">
@@ -72467,7 +72467,7 @@
       <c r="B1943" t="inlineStr"/>
       <c r="C1943" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1943" t="inlineStr">
@@ -72575,7 +72575,7 @@
       <c r="B1949" t="inlineStr"/>
       <c r="C1949" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1949" t="inlineStr">
@@ -72719,7 +72719,7 @@
       <c r="B1957" t="inlineStr"/>
       <c r="C1957" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1957" t="inlineStr">
@@ -72755,7 +72755,7 @@
       <c r="B1959" t="inlineStr"/>
       <c r="C1959" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1959" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -688,7 +688,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>V/Line Football Special via Werribee</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1264,7 +1264,7 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2080,7 +2080,7 @@
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2350,7 +2350,7 @@
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2958,7 +2958,7 @@
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>North East Line SG Service</t>
+          <t>North East SG Line Service</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -5806,7 +5806,7 @@
       <c r="B305" t="inlineStr"/>
       <c r="C305" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Cootamundra Shunter</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -7132,7 +7132,7 @@
       <c r="B380" t="inlineStr"/>
       <c r="C380" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Coal</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -9704,7 +9704,7 @@
       <c r="B536" t="inlineStr"/>
       <c r="C536" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
@@ -16284,7 +16284,7 @@
       <c r="B907" t="inlineStr"/>
       <c r="C907" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
@@ -16374,7 +16374,7 @@
       <c r="B912" t="inlineStr"/>
       <c r="C912" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D912" t="inlineStr">
@@ -17184,7 +17184,7 @@
       <c r="B957" t="inlineStr"/>
       <c r="C957" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D957" t="inlineStr">
@@ -17616,7 +17616,7 @@
       <c r="B981" t="inlineStr"/>
       <c r="C981" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D981" t="inlineStr">
@@ -18408,7 +18408,7 @@
       <c r="B1025" t="inlineStr"/>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1025" t="inlineStr">
@@ -19254,7 +19254,7 @@
       <c r="B1072" t="inlineStr"/>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1072" t="inlineStr">
@@ -19956,7 +19956,7 @@
       <c r="B1111" t="inlineStr"/>
       <c r="C1111" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1111" t="inlineStr">
@@ -20082,7 +20082,7 @@
       <c r="B1118" t="inlineStr"/>
       <c r="C1118" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1118" t="inlineStr">
@@ -20190,7 +20190,7 @@
       <c r="B1124" t="inlineStr"/>
       <c r="C1124" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1124" t="inlineStr">
@@ -20532,7 +20532,7 @@
       <c r="B1143" t="inlineStr"/>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1143" t="inlineStr">
@@ -20550,7 +20550,7 @@
       <c r="B1144" t="inlineStr"/>
       <c r="C1144" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1144" t="inlineStr">
@@ -20586,7 +20586,7 @@
       <c r="B1146" t="inlineStr"/>
       <c r="C1146" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1146" t="inlineStr">
@@ -20658,7 +20658,7 @@
       <c r="B1150" t="inlineStr"/>
       <c r="C1150" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1150" t="inlineStr">
@@ -21234,7 +21234,7 @@
       <c r="B1182" t="inlineStr"/>
       <c r="C1182" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1182" t="inlineStr">
@@ -21288,7 +21288,7 @@
       <c r="B1185" t="inlineStr"/>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1185" t="inlineStr">
@@ -21306,7 +21306,7 @@
       <c r="B1186" t="inlineStr"/>
       <c r="C1186" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1186" t="inlineStr">
@@ -21540,7 +21540,7 @@
       <c r="B1199" t="inlineStr"/>
       <c r="C1199" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1199" t="inlineStr">
@@ -21864,7 +21864,7 @@
       <c r="B1217" t="inlineStr"/>
       <c r="C1217" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1217" t="inlineStr">
@@ -21990,7 +21990,7 @@
       <c r="B1224" t="inlineStr"/>
       <c r="C1224" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1224" t="inlineStr">
@@ -22098,7 +22098,7 @@
       <c r="B1230" t="inlineStr"/>
       <c r="C1230" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1230" t="inlineStr">
@@ -22116,7 +22116,7 @@
       <c r="B1231" t="inlineStr"/>
       <c r="C1231" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1231" t="inlineStr">
@@ -22260,7 +22260,7 @@
       <c r="B1239" t="inlineStr"/>
       <c r="C1239" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1239" t="inlineStr">
@@ -22314,7 +22314,7 @@
       <c r="B1242" t="inlineStr"/>
       <c r="C1242" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1242" t="inlineStr">
@@ -22620,7 +22620,7 @@
       <c r="B1259" t="inlineStr"/>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1259" t="inlineStr">
@@ -22638,7 +22638,7 @@
       <c r="B1260" t="inlineStr"/>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1260" t="inlineStr">
@@ -22656,7 +22656,7 @@
       <c r="B1261" t="inlineStr"/>
       <c r="C1261" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1261" t="inlineStr">
@@ -22764,7 +22764,7 @@
       <c r="B1267" t="inlineStr"/>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1267" t="inlineStr">
@@ -22854,7 +22854,7 @@
       <c r="B1272" t="inlineStr"/>
       <c r="C1272" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1272" t="inlineStr">
@@ -22944,7 +22944,7 @@
       <c r="B1277" t="inlineStr"/>
       <c r="C1277" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1277" t="inlineStr">
@@ -22962,7 +22962,7 @@
       <c r="B1278" t="inlineStr"/>
       <c r="C1278" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1278" t="inlineStr">
@@ -22980,7 +22980,7 @@
       <c r="B1279" t="inlineStr"/>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1279" t="inlineStr">
@@ -28238,7 +28238,7 @@
       <c r="B1584" t="inlineStr"/>
       <c r="C1584" t="inlineStr">
         <is>
-          <t>Additional Bathurst Service</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D1584" t="inlineStr">
@@ -31544,7 +31544,7 @@
       <c r="B1771" t="inlineStr"/>
       <c r="C1771" t="inlineStr">
         <is>
-          <t>Ararat - Melbourne Via Ballarat</t>
+          <t>Ballarat - Melbourne Via Melton</t>
         </is>
       </c>
       <c r="D1771" t="inlineStr">
@@ -37760,7 +37760,7 @@
       <c r="B2117" t="inlineStr"/>
       <c r="C2117" t="inlineStr">
         <is>
-          <t>ORA Light Engine</t>
+          <t>ORA Coal</t>
         </is>
       </c>
       <c r="D2117" t="inlineStr">
@@ -38821,7 +38821,7 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -39051,7 +39051,7 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -39159,7 +39159,7 @@
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -39273,7 +39273,7 @@
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -40933,7 +40933,7 @@
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -43819,7 +43819,7 @@
       <c r="B330" t="inlineStr"/>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -46429,7 +46429,7 @@
       <c r="B477" t="inlineStr"/>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -47501,7 +47501,7 @@
       <c r="B537" t="inlineStr"/>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
@@ -51679,7 +51679,7 @@
       <c r="B772" t="inlineStr"/>
       <c r="C772" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D772" t="inlineStr">
@@ -52705,7 +52705,7 @@
       <c r="B829" t="inlineStr"/>
       <c r="C829" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Cootamundra Shunter</t>
         </is>
       </c>
       <c r="D829" t="inlineStr">
@@ -54243,7 +54243,7 @@
       <c r="B916" t="inlineStr"/>
       <c r="C916" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Coal</t>
         </is>
       </c>
       <c r="D916" t="inlineStr">
@@ -56237,7 +56237,7 @@
       <c r="B1027" t="inlineStr"/>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1027" t="inlineStr">
@@ -56759,7 +56759,7 @@
       <c r="B1056" t="inlineStr"/>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1056" t="inlineStr">
@@ -57431,7 +57431,7 @@
       <c r="B1094" t="inlineStr"/>
       <c r="C1094" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D1094" t="inlineStr">
@@ -57859,7 +57859,7 @@
       <c r="B1118" t="inlineStr"/>
       <c r="C1118" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1118" t="inlineStr">
@@ -57913,7 +57913,7 @@
       <c r="B1121" t="inlineStr"/>
       <c r="C1121" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1121" t="inlineStr">
@@ -58481,7 +58481,7 @@
       <c r="B1153" t="inlineStr"/>
       <c r="C1153" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1153" t="inlineStr">
@@ -60291,7 +60291,7 @@
       <c r="B1254" t="inlineStr"/>
       <c r="C1254" t="inlineStr">
         <is>
-          <t>Additional Bathurst Service</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D1254" t="inlineStr">
@@ -61089,7 +61089,7 @@
       <c r="B1299" t="inlineStr"/>
       <c r="C1299" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D1299" t="inlineStr">
@@ -62531,7 +62531,7 @@
       <c r="B1380" t="inlineStr"/>
       <c r="C1380" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1380" t="inlineStr">
@@ -64176,7 +64176,7 @@
       <c r="B1472" t="inlineStr"/>
       <c r="C1472" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1472" t="inlineStr">
@@ -64641,7 +64641,7 @@
       <c r="B1498" t="inlineStr"/>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1498" t="inlineStr">
@@ -64907,7 +64907,7 @@
       <c r="B1513" t="inlineStr"/>
       <c r="C1513" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1513" t="inlineStr">
@@ -66371,7 +66371,7 @@
       <c r="B1595" t="inlineStr"/>
       <c r="C1595" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>V/Line Football Special via Werribee</t>
         </is>
       </c>
       <c r="D1595" t="inlineStr">
@@ -68011,7 +68011,7 @@
       <c r="B1687" t="inlineStr"/>
       <c r="C1687" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1687" t="inlineStr">
@@ -68839,7 +68839,7 @@
       <c r="B1733" t="inlineStr"/>
       <c r="C1733" t="inlineStr">
         <is>
-          <t>North East Line SG Service</t>
+          <t>North East SG Line Service</t>
         </is>
       </c>
       <c r="D1733" t="inlineStr">
@@ -70225,7 +70225,7 @@
       <c r="B1816" t="inlineStr"/>
       <c r="C1816" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1816" t="inlineStr">
@@ -71261,7 +71261,7 @@
       <c r="B1874" t="inlineStr"/>
       <c r="C1874" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1874" t="inlineStr">
@@ -71657,7 +71657,7 @@
       <c r="B1896" t="inlineStr"/>
       <c r="C1896" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1896" t="inlineStr">
@@ -71963,7 +71963,7 @@
       <c r="B1913" t="inlineStr"/>
       <c r="C1913" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1913" t="inlineStr">
@@ -71999,7 +71999,7 @@
       <c r="B1915" t="inlineStr"/>
       <c r="C1915" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1915" t="inlineStr">
@@ -72053,7 +72053,7 @@
       <c r="B1918" t="inlineStr"/>
       <c r="C1918" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1918" t="inlineStr">
@@ -72431,7 +72431,7 @@
       <c r="B1939" t="inlineStr"/>
       <c r="C1939" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1939" t="inlineStr">
@@ -72503,7 +72503,7 @@
       <c r="B1943" t="inlineStr"/>
       <c r="C1943" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1943" t="inlineStr">
@@ -72539,7 +72539,7 @@
       <c r="B1945" t="inlineStr"/>
       <c r="C1945" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1945" t="inlineStr">
@@ -72557,7 +72557,7 @@
       <c r="B1946" t="inlineStr"/>
       <c r="C1946" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1946" t="inlineStr">
@@ -72647,7 +72647,7 @@
       <c r="B1951" t="inlineStr"/>
       <c r="C1951" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1951" t="inlineStr">
@@ -72773,7 +72773,7 @@
       <c r="B1958" t="inlineStr"/>
       <c r="C1958" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1958" t="inlineStr">
@@ -72827,7 +72827,7 @@
       <c r="B1961" t="inlineStr"/>
       <c r="C1961" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1961" t="inlineStr">
@@ -72935,7 +72935,7 @@
       <c r="B1967" t="inlineStr"/>
       <c r="C1967" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1967" t="inlineStr">
@@ -74531,7 +74531,7 @@
       <c r="B2061" t="inlineStr"/>
       <c r="C2061" t="inlineStr">
         <is>
-          <t>Ararat - Melbourne Via Ballarat</t>
+          <t>Ballarat - Melbourne Via Melton</t>
         </is>
       </c>
       <c r="D2061" t="inlineStr">
@@ -75251,7 +75251,7 @@
       <c r="B2101" t="inlineStr"/>
       <c r="C2101" t="inlineStr">
         <is>
-          <t>ORA Light Engine</t>
+          <t>ORA Coal</t>
         </is>
       </c>
       <c r="D2101" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1386,7 +1386,7 @@
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1580,7 +1580,7 @@
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>V/Line Football Special via Werribee</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1706,7 +1706,7 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>V/Line Track Scrubbing</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2544,7 +2544,7 @@
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Northern Line Service (combined with 8077 Echuca service)</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -2922,7 +2922,7 @@
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>NorthEast Special Movement</t>
+          <t>V/Line SG Special Movement</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4690,7 +4690,11 @@
         </is>
       </c>
       <c r="B242" t="inlineStr"/>
-      <c r="C242" t="inlineStr"/>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Maintenance Train</t>
+        </is>
+      </c>
       <c r="D242" t="inlineStr">
         <is>
           <t>2026-04-17 11:13:39</t>
@@ -6702,7 +6706,7 @@
       <c r="B355" t="inlineStr"/>
       <c r="C355" t="inlineStr">
         <is>
-          <t>PN Morandoo Shunter</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -9848,7 +9852,7 @@
       <c r="B544" t="inlineStr"/>
       <c r="C544" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
@@ -10352,7 +10356,7 @@
       <c r="B572" t="inlineStr"/>
       <c r="C572" t="inlineStr">
         <is>
-          <t>QUBE Loaded Balco &amp; Zinc</t>
+          <t>QUBE Loaded Zinc</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
@@ -12416,7 +12420,7 @@
       <c r="B689" t="inlineStr"/>
       <c r="C689" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
@@ -15138,7 +15142,7 @@
       <c r="B842" t="inlineStr"/>
       <c r="C842" t="inlineStr">
         <is>
-          <t>Additional Bathurst Service</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
@@ -15690,7 +15694,7 @@
       <c r="B874" t="inlineStr"/>
       <c r="C874" t="inlineStr">
         <is>
-          <t>SSR Loaded Manildra Flour</t>
+          <t>SSR Empty Manildra Flour</t>
         </is>
       </c>
       <c r="D874" t="inlineStr">
@@ -16032,7 +16036,7 @@
       <c r="B893" t="inlineStr"/>
       <c r="C893" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D893" t="inlineStr">
@@ -16050,7 +16054,7 @@
       <c r="B894" t="inlineStr"/>
       <c r="C894" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D894" t="inlineStr">
@@ -16194,7 +16198,7 @@
       <c r="B902" t="inlineStr"/>
       <c r="C902" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D902" t="inlineStr">
@@ -16338,7 +16342,7 @@
       <c r="B910" t="inlineStr"/>
       <c r="C910" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D910" t="inlineStr">
@@ -16464,7 +16468,7 @@
       <c r="B917" t="inlineStr"/>
       <c r="C917" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D917" t="inlineStr">
@@ -16554,7 +16558,7 @@
       <c r="B922" t="inlineStr"/>
       <c r="C922" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D922" t="inlineStr">
@@ -16950,7 +16954,7 @@
       <c r="B944" t="inlineStr"/>
       <c r="C944" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D944" t="inlineStr">
@@ -17292,7 +17296,7 @@
       <c r="B963" t="inlineStr"/>
       <c r="C963" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D963" t="inlineStr">
@@ -17580,7 +17584,7 @@
       <c r="B979" t="inlineStr"/>
       <c r="C979" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D979" t="inlineStr">
@@ -18570,7 +18574,7 @@
       <c r="B1034" t="inlineStr"/>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1034" t="inlineStr">
@@ -18732,7 +18736,7 @@
       <c r="B1043" t="inlineStr"/>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1043" t="inlineStr">
@@ -19074,7 +19078,7 @@
       <c r="B1062" t="inlineStr"/>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1062" t="inlineStr">
@@ -19956,7 +19960,7 @@
       <c r="B1111" t="inlineStr"/>
       <c r="C1111" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1111" t="inlineStr">
@@ -19974,7 +19978,7 @@
       <c r="B1112" t="inlineStr"/>
       <c r="C1112" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1112" t="inlineStr">
@@ -20226,7 +20230,7 @@
       <c r="B1126" t="inlineStr"/>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1126" t="inlineStr">
@@ -20442,7 +20446,7 @@
       <c r="B1138" t="inlineStr"/>
       <c r="C1138" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1138" t="inlineStr">
@@ -20496,7 +20500,7 @@
       <c r="B1141" t="inlineStr"/>
       <c r="C1141" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1141" t="inlineStr">
@@ -20604,7 +20608,7 @@
       <c r="B1147" t="inlineStr"/>
       <c r="C1147" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1147" t="inlineStr">
@@ -20640,7 +20644,7 @@
       <c r="B1149" t="inlineStr"/>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1149" t="inlineStr">
@@ -20658,7 +20662,7 @@
       <c r="B1150" t="inlineStr"/>
       <c r="C1150" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1150" t="inlineStr">
@@ -21072,7 +21076,7 @@
       <c r="B1173" t="inlineStr"/>
       <c r="C1173" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1173" t="inlineStr">
@@ -21306,7 +21310,7 @@
       <c r="B1186" t="inlineStr"/>
       <c r="C1186" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1186" t="inlineStr">
@@ -21486,7 +21490,7 @@
       <c r="B1196" t="inlineStr"/>
       <c r="C1196" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1196" t="inlineStr">
@@ -21720,7 +21724,7 @@
       <c r="B1209" t="inlineStr"/>
       <c r="C1209" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1209" t="inlineStr">
@@ -21972,7 +21976,7 @@
       <c r="B1223" t="inlineStr"/>
       <c r="C1223" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1223" t="inlineStr">
@@ -22188,7 +22192,7 @@
       <c r="B1235" t="inlineStr"/>
       <c r="C1235" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1235" t="inlineStr">
@@ -22260,7 +22264,7 @@
       <c r="B1239" t="inlineStr"/>
       <c r="C1239" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1239" t="inlineStr">
@@ -22350,7 +22354,7 @@
       <c r="B1244" t="inlineStr"/>
       <c r="C1244" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1244" t="inlineStr">
@@ -22440,7 +22444,7 @@
       <c r="B1249" t="inlineStr"/>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1249" t="inlineStr">
@@ -22458,7 +22462,7 @@
       <c r="B1250" t="inlineStr"/>
       <c r="C1250" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1250" t="inlineStr">
@@ -22674,7 +22678,7 @@
       <c r="B1262" t="inlineStr"/>
       <c r="C1262" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1262" t="inlineStr">
@@ -22728,7 +22732,7 @@
       <c r="B1265" t="inlineStr"/>
       <c r="C1265" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1265" t="inlineStr">
@@ -22836,7 +22840,7 @@
       <c r="B1271" t="inlineStr"/>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1271" t="inlineStr">
@@ -22926,7 +22930,7 @@
       <c r="B1276" t="inlineStr"/>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1276" t="inlineStr">
@@ -23034,7 +23038,7 @@
       <c r="B1282" t="inlineStr"/>
       <c r="C1282" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1282" t="inlineStr">
@@ -27042,7 +27046,7 @@
       <c r="B1514" t="inlineStr"/>
       <c r="C1514" t="inlineStr">
         <is>
-          <t>Qube Trip Train</t>
+          <t>QUBE Trip Train</t>
         </is>
       </c>
       <c r="D1514" t="inlineStr">
@@ -27668,7 +27672,7 @@
       <c r="B1551" t="inlineStr"/>
       <c r="C1551" t="inlineStr">
         <is>
-          <t>North Eastern Line BG Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D1551" t="inlineStr">
@@ -28960,7 +28964,7 @@
       <c r="B1627" t="inlineStr"/>
       <c r="C1627" t="inlineStr">
         <is>
-          <t>PN Coal (Train Rake Unit 2)</t>
+          <t>PN Coal</t>
         </is>
       </c>
       <c r="D1627" t="inlineStr">
@@ -37264,7 +37268,7 @@
       <c r="B2089" t="inlineStr"/>
       <c r="C2089" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (Forms ST21)</t>
         </is>
       </c>
       <c r="D2089" t="inlineStr">
@@ -37480,7 +37484,7 @@
       <c r="B2101" t="inlineStr"/>
       <c r="C2101" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D2101" t="inlineStr">
@@ -38127,7 +38131,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -38447,7 +38451,11 @@
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Maintenance Train</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>2026-04-17 11:13:39</t>
@@ -38767,7 +38775,7 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -38911,7 +38919,7 @@
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PN Morandoo Shunter</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -42883,7 +42891,7 @@
       <c r="B276" t="inlineStr"/>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -43819,7 +43827,7 @@
       <c r="B330" t="inlineStr"/>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -43837,7 +43845,7 @@
       <c r="B331" t="inlineStr"/>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -46519,7 +46527,7 @@
       <c r="B482" t="inlineStr"/>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -46893,7 +46901,7 @@
       <c r="B503" t="inlineStr"/>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
@@ -48807,7 +48815,7 @@
       <c r="B612" t="inlineStr"/>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Qube Trip Train</t>
+          <t>QUBE Trip Train</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
@@ -49041,7 +49049,7 @@
       <c r="B625" t="inlineStr"/>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
@@ -50265,7 +50273,7 @@
       <c r="B693" t="inlineStr"/>
       <c r="C693" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
@@ -52129,7 +52137,7 @@
       <c r="B797" t="inlineStr"/>
       <c r="C797" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (Forms ST21)</t>
         </is>
       </c>
       <c r="D797" t="inlineStr">
@@ -53985,7 +53993,7 @@
       <c r="B901" t="inlineStr"/>
       <c r="C901" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D901" t="inlineStr">
@@ -54093,7 +54101,7 @@
       <c r="B907" t="inlineStr"/>
       <c r="C907" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
@@ -56453,7 +56461,7 @@
       <c r="B1039" t="inlineStr"/>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1039" t="inlineStr">
@@ -56687,7 +56695,7 @@
       <c r="B1052" t="inlineStr"/>
       <c r="C1052" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1052" t="inlineStr">
@@ -57395,7 +57403,7 @@
       <c r="B1092" t="inlineStr"/>
       <c r="C1092" t="inlineStr">
         <is>
-          <t>PN Coal (Train Rake Unit 2)</t>
+          <t>PN Coal</t>
         </is>
       </c>
       <c r="D1092" t="inlineStr">
@@ -57769,7 +57777,7 @@
       <c r="B1113" t="inlineStr"/>
       <c r="C1113" t="inlineStr">
         <is>
-          <t>Additional Bathurst Service</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1113" t="inlineStr">
@@ -58481,7 +58489,7 @@
       <c r="B1153" t="inlineStr"/>
       <c r="C1153" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1153" t="inlineStr">
@@ -59359,7 +59367,7 @@
       <c r="B1202" t="inlineStr"/>
       <c r="C1202" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1202" t="inlineStr">
@@ -61107,7 +61115,7 @@
       <c r="B1300" t="inlineStr"/>
       <c r="C1300" t="inlineStr">
         <is>
-          <t>NorthEast Special Movement</t>
+          <t>V/Line SG Special Movement</t>
         </is>
       </c>
       <c r="D1300" t="inlineStr">
@@ -62351,7 +62359,7 @@
       <c r="B1370" t="inlineStr"/>
       <c r="C1370" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1370" t="inlineStr">
@@ -63658,7 +63666,7 @@
       <c r="B1443" t="inlineStr"/>
       <c r="C1443" t="inlineStr">
         <is>
-          <t>V/Line Track Scrubbing</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1443" t="inlineStr">
@@ -63996,7 +64004,7 @@
       <c r="B1462" t="inlineStr"/>
       <c r="C1462" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>V/Line Football Special via Werribee</t>
         </is>
       </c>
       <c r="D1462" t="inlineStr">
@@ -64338,7 +64346,7 @@
       <c r="B1481" t="inlineStr"/>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1481" t="inlineStr">
@@ -64356,7 +64364,7 @@
       <c r="B1482" t="inlineStr"/>
       <c r="C1482" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1482" t="inlineStr">
@@ -65141,7 +65149,7 @@
       <c r="B1526" t="inlineStr"/>
       <c r="C1526" t="inlineStr">
         <is>
-          <t>QUBE Loaded Balco &amp; Zinc</t>
+          <t>QUBE Loaded Zinc</t>
         </is>
       </c>
       <c r="D1526" t="inlineStr">
@@ -67241,7 +67249,7 @@
       <c r="B1644" t="inlineStr"/>
       <c r="C1644" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1644" t="inlineStr">
@@ -68551,7 +68559,7 @@
       <c r="B1717" t="inlineStr"/>
       <c r="C1717" t="inlineStr">
         <is>
-          <t>Northern Line Service (combined with 8077 Echuca service)</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1717" t="inlineStr">
@@ -70761,7 +70769,7 @@
       <c r="B1846" t="inlineStr"/>
       <c r="C1846" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1846" t="inlineStr">
@@ -71135,7 +71143,7 @@
       <c r="B1867" t="inlineStr"/>
       <c r="C1867" t="inlineStr">
         <is>
-          <t>SSR Loaded Manildra Flour</t>
+          <t>SSR Empty Manildra Flour</t>
         </is>
       </c>
       <c r="D1867" t="inlineStr">
@@ -71459,7 +71467,7 @@
       <c r="B1885" t="inlineStr"/>
       <c r="C1885" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1885" t="inlineStr">
@@ -71549,7 +71557,7 @@
       <c r="B1890" t="inlineStr"/>
       <c r="C1890" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1890" t="inlineStr">
@@ -71585,7 +71593,7 @@
       <c r="B1892" t="inlineStr"/>
       <c r="C1892" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1892" t="inlineStr">
@@ -71801,7 +71809,7 @@
       <c r="B1904" t="inlineStr"/>
       <c r="C1904" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1904" t="inlineStr">
@@ -71819,7 +71827,7 @@
       <c r="B1905" t="inlineStr"/>
       <c r="C1905" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1905" t="inlineStr">
@@ -71837,7 +71845,7 @@
       <c r="B1906" t="inlineStr"/>
       <c r="C1906" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1906" t="inlineStr">
@@ -71945,7 +71953,7 @@
       <c r="B1912" t="inlineStr"/>
       <c r="C1912" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1912" t="inlineStr">
@@ -72017,7 +72025,7 @@
       <c r="B1916" t="inlineStr"/>
       <c r="C1916" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1916" t="inlineStr">
@@ -72053,7 +72061,7 @@
       <c r="B1918" t="inlineStr"/>
       <c r="C1918" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1918" t="inlineStr">
@@ -72377,7 +72385,7 @@
       <c r="B1936" t="inlineStr"/>
       <c r="C1936" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1936" t="inlineStr">
@@ -72485,7 +72493,7 @@
       <c r="B1942" t="inlineStr"/>
       <c r="C1942" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1942" t="inlineStr">
@@ -72611,7 +72619,7 @@
       <c r="B1949" t="inlineStr"/>
       <c r="C1949" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1949" t="inlineStr">
@@ -72647,7 +72655,7 @@
       <c r="B1951" t="inlineStr"/>
       <c r="C1951" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1951" t="inlineStr">
@@ -72719,7 +72727,7 @@
       <c r="B1955" t="inlineStr"/>
       <c r="C1955" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1955" t="inlineStr">
@@ -72791,7 +72799,7 @@
       <c r="B1959" t="inlineStr"/>
       <c r="C1959" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1959" t="inlineStr">
@@ -72899,7 +72907,7 @@
       <c r="B1965" t="inlineStr"/>
       <c r="C1965" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1965" t="inlineStr">
@@ -72917,7 +72925,7 @@
       <c r="B1966" t="inlineStr"/>
       <c r="C1966" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1966" t="inlineStr">
@@ -72971,7 +72979,7 @@
       <c r="B1969" t="inlineStr"/>
       <c r="C1969" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1969" t="inlineStr">
@@ -73991,7 +73999,7 @@
       <c r="B2031" t="inlineStr"/>
       <c r="C2031" t="inlineStr">
         <is>
-          <t>North Eastern Line BG Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D2031" t="inlineStr">
@@ -75143,7 +75151,7 @@
       <c r="B2095" t="inlineStr"/>
       <c r="C2095" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D2095" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1174,7 +1174,7 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2526,7 +2526,7 @@
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -2922,7 +2922,7 @@
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>V/Line SG Special Movement</t>
+          <t>NorthEast Special Movement</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18736,7 +18736,7 @@
       <c r="B1043" t="inlineStr"/>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1043" t="inlineStr">
@@ -20788,7 +20788,7 @@
       <c r="B1157" t="inlineStr"/>
       <c r="C1157" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1157" t="inlineStr">
@@ -21616,7 +21616,7 @@
       <c r="B1203" t="inlineStr"/>
       <c r="C1203" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1203" t="inlineStr">
@@ -21994,7 +21994,7 @@
       <c r="B1224" t="inlineStr"/>
       <c r="C1224" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1224" t="inlineStr">
@@ -22012,7 +22012,7 @@
       <c r="B1225" t="inlineStr"/>
       <c r="C1225" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1225" t="inlineStr">
@@ -22462,7 +22462,7 @@
       <c r="B1250" t="inlineStr"/>
       <c r="C1250" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1250" t="inlineStr">
@@ -22498,7 +22498,7 @@
       <c r="B1252" t="inlineStr"/>
       <c r="C1252" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1252" t="inlineStr">
@@ -22912,7 +22912,7 @@
       <c r="B1275" t="inlineStr"/>
       <c r="C1275" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1275" t="inlineStr">
@@ -23092,7 +23092,7 @@
       <c r="B1285" t="inlineStr"/>
       <c r="C1285" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1285" t="inlineStr">
@@ -27370,7 +27370,7 @@
       <c r="B1534" t="inlineStr"/>
       <c r="C1534" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1534" t="inlineStr">
@@ -27546,7 +27546,7 @@
       <c r="B1544" t="inlineStr"/>
       <c r="C1544" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D1544" t="inlineStr">
@@ -27960,7 +27960,7 @@
       <c r="B1567" t="inlineStr"/>
       <c r="C1567" t="inlineStr">
         <is>
-          <t>SSR Light Engine Movement</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1567" t="inlineStr">
@@ -37592,7 +37592,7 @@
       <c r="B2107" t="inlineStr"/>
       <c r="C2107" t="inlineStr">
         <is>
-          <t>PN Containerised Freight</t>
+          <t>PN Light Engine Movement</t>
         </is>
       </c>
       <c r="D2107" t="inlineStr">
@@ -38693,7 +38693,7 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PN Containerised Freight</t>
+          <t>PN Light Engine Movement</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -46919,7 +46919,7 @@
       <c r="B504" t="inlineStr"/>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
@@ -53993,7 +53993,7 @@
       <c r="B901" t="inlineStr"/>
       <c r="C901" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D901" t="inlineStr">
@@ -54413,7 +54413,7 @@
       <c r="B925" t="inlineStr"/>
       <c r="C925" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D925" t="inlineStr">
@@ -55439,7 +55439,7 @@
       <c r="B982" t="inlineStr"/>
       <c r="C982" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D982" t="inlineStr">
@@ -56803,7 +56803,7 @@
       <c r="B1058" t="inlineStr"/>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1058" t="inlineStr">
@@ -57939,7 +57939,7 @@
       <c r="B1122" t="inlineStr"/>
       <c r="C1122" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1122" t="inlineStr">
@@ -59245,7 +59245,7 @@
       <c r="B1195" t="inlineStr"/>
       <c r="C1195" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1195" t="inlineStr">
@@ -61115,7 +61115,7 @@
       <c r="B1300" t="inlineStr"/>
       <c r="C1300" t="inlineStr">
         <is>
-          <t>V/Line SG Special Movement</t>
+          <t>NorthEast Special Movement</t>
         </is>
       </c>
       <c r="D1300" t="inlineStr">
@@ -61859,7 +61859,7 @@
       <c r="B1342" t="inlineStr"/>
       <c r="C1342" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1342" t="inlineStr">
@@ -63770,7 +63770,7 @@
       <c r="B1449" t="inlineStr"/>
       <c r="C1449" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1449" t="inlineStr">
@@ -63806,7 +63806,7 @@
       <c r="B1451" t="inlineStr"/>
       <c r="C1451" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1451" t="inlineStr">
@@ -64346,7 +64346,7 @@
       <c r="B1481" t="inlineStr"/>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1481" t="inlineStr">
@@ -68073,7 +68073,7 @@
       <c r="B1690" t="inlineStr"/>
       <c r="C1690" t="inlineStr">
         <is>
-          <t>SSR Light Engine Movement</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1690" t="inlineStr">
@@ -72115,7 +72115,7 @@
       <c r="B1921" t="inlineStr"/>
       <c r="C1921" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1921" t="inlineStr">
@@ -72511,7 +72511,7 @@
       <c r="B1943" t="inlineStr"/>
       <c r="C1943" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1943" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -688,7 +688,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>V/Line Football Special via Werribee</t>
+          <t>V/Line rail cleaning train</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1228,7 +1228,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -10816,8 +10816,7 @@
       <c r="B598" t="inlineStr"/>
       <c r="C598" t="inlineStr">
         <is>
-          <t>NSW TrainLink Xplorer
-(from NP23)</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
@@ -12234,7 +12233,7 @@
       <c r="B678" t="inlineStr"/>
       <c r="C678" t="inlineStr">
         <is>
-          <t>Aurizon Empty Grain/Wagon Transfer</t>
+          <t>Aurizon Wagon Transfer</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
@@ -12474,7 +12473,7 @@
       <c r="B692" t="inlineStr"/>
       <c r="C692" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
@@ -17998,7 +17997,7 @@
       <c r="B1002" t="inlineStr"/>
       <c r="C1002" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1002" t="inlineStr">
@@ -18574,7 +18573,7 @@
       <c r="B1034" t="inlineStr"/>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1034" t="inlineStr">
@@ -19420,7 +19419,7 @@
       <c r="B1081" t="inlineStr"/>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1081" t="inlineStr">
@@ -20230,7 +20229,7 @@
       <c r="B1126" t="inlineStr"/>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1126" t="inlineStr">
@@ -21292,7 +21291,7 @@
       <c r="B1185" t="inlineStr"/>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1185" t="inlineStr">
@@ -21454,7 +21453,7 @@
       <c r="B1194" t="inlineStr"/>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1194" t="inlineStr">
@@ -21544,7 +21543,7 @@
       <c r="B1199" t="inlineStr"/>
       <c r="C1199" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1199" t="inlineStr">
@@ -21868,7 +21867,7 @@
       <c r="B1217" t="inlineStr"/>
       <c r="C1217" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1217" t="inlineStr">
@@ -22318,7 +22317,7 @@
       <c r="B1242" t="inlineStr"/>
       <c r="C1242" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1242" t="inlineStr">
@@ -22372,7 +22371,7 @@
       <c r="B1245" t="inlineStr"/>
       <c r="C1245" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1245" t="inlineStr">
@@ -22624,7 +22623,7 @@
       <c r="B1259" t="inlineStr"/>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1259" t="inlineStr">
@@ -22714,7 +22713,7 @@
       <c r="B1264" t="inlineStr"/>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1264" t="inlineStr">
@@ -22732,7 +22731,7 @@
       <c r="B1265" t="inlineStr"/>
       <c r="C1265" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1265" t="inlineStr">
@@ -22768,7 +22767,7 @@
       <c r="B1267" t="inlineStr"/>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1267" t="inlineStr">
@@ -22840,7 +22839,7 @@
       <c r="B1271" t="inlineStr"/>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1271" t="inlineStr">
@@ -22948,7 +22947,7 @@
       <c r="B1277" t="inlineStr"/>
       <c r="C1277" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1277" t="inlineStr">
@@ -22984,7 +22983,7 @@
       <c r="B1279" t="inlineStr"/>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1279" t="inlineStr">
@@ -23092,7 +23091,7 @@
       <c r="B1285" t="inlineStr"/>
       <c r="C1285" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1285" t="inlineStr">
@@ -24020,7 +24019,7 @@
       <c r="B1337" t="inlineStr"/>
       <c r="C1337" t="inlineStr">
         <is>
-          <t>JBR Indian Pacifc</t>
+          <t>JBR Indian Pacific</t>
         </is>
       </c>
       <c r="D1337" t="inlineStr">
@@ -31584,7 +31583,7 @@
       <c r="B1773" t="inlineStr"/>
       <c r="C1773" t="inlineStr">
         <is>
-          <t>Ararat - Melbourne Via Ballarat</t>
+          <t>Ballarat - Melbourne Via Melton</t>
         </is>
       </c>
       <c r="D1773" t="inlineStr">
@@ -40941,7 +40940,7 @@
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -46419,7 +46418,7 @@
       <c r="B476" t="inlineStr"/>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -47509,7 +47508,7 @@
       <c r="B537" t="inlineStr"/>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
@@ -51687,7 +51686,7 @@
       <c r="B772" t="inlineStr"/>
       <c r="C772" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D772" t="inlineStr">
@@ -51957,7 +51956,7 @@
       <c r="B787" t="inlineStr"/>
       <c r="C787" t="inlineStr">
         <is>
-          <t>JBR Indian Pacifc</t>
+          <t>JBR Indian Pacific</t>
         </is>
       </c>
       <c r="D787" t="inlineStr">
@@ -54101,7 +54100,7 @@
       <c r="B907" t="inlineStr"/>
       <c r="C907" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
@@ -56443,7 +56442,7 @@
       <c r="B1038" t="inlineStr"/>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1038" t="inlineStr">
@@ -56767,7 +56766,7 @@
       <c r="B1056" t="inlineStr"/>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1056" t="inlineStr">
@@ -57921,7 +57920,7 @@
       <c r="B1121" t="inlineStr"/>
       <c r="C1121" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1121" t="inlineStr">
@@ -60069,7 +60068,7 @@
       <c r="B1241" t="inlineStr"/>
       <c r="C1241" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1241" t="inlineStr">
@@ -62945,7 +62944,7 @@
       <c r="B1403" t="inlineStr"/>
       <c r="C1403" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1403" t="inlineStr">
@@ -63377,8 +63376,7 @@
       <c r="B1427" t="inlineStr"/>
       <c r="C1427" t="inlineStr">
         <is>
-          <t>NSW TrainLink Xplorer
-(from NP23)</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="D1427" t="inlineStr">
@@ -63806,7 +63804,7 @@
       <c r="B1451" t="inlineStr"/>
       <c r="C1451" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1451" t="inlineStr">
@@ -64256,7 +64254,7 @@
       <c r="B1476" t="inlineStr"/>
       <c r="C1476" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1476" t="inlineStr">
@@ -66379,7 +66377,7 @@
       <c r="B1595" t="inlineStr"/>
       <c r="C1595" t="inlineStr">
         <is>
-          <t>V/Line Football Special via Werribee</t>
+          <t>V/Line rail cleaning train</t>
         </is>
       </c>
       <c r="D1595" t="inlineStr">
@@ -67177,7 +67175,7 @@
       <c r="B1640" t="inlineStr"/>
       <c r="C1640" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1640" t="inlineStr">
@@ -67375,7 +67373,7 @@
       <c r="B1651" t="inlineStr"/>
       <c r="C1651" t="inlineStr">
         <is>
-          <t>Ararat - Melbourne Via Ballarat</t>
+          <t>Ballarat - Melbourne Via Melton</t>
         </is>
       </c>
       <c r="D1651" t="inlineStr">
@@ -70715,7 +70713,7 @@
       <c r="B1843" t="inlineStr"/>
       <c r="C1843" t="inlineStr">
         <is>
-          <t>Aurizon Empty Grain/Wagon Transfer</t>
+          <t>Aurizon Wagon Transfer</t>
         </is>
       </c>
       <c r="D1843" t="inlineStr">
@@ -71467,7 +71465,7 @@
       <c r="B1885" t="inlineStr"/>
       <c r="C1885" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1885" t="inlineStr">
@@ -71845,7 +71843,7 @@
       <c r="B1906" t="inlineStr"/>
       <c r="C1906" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1906" t="inlineStr">
@@ -72439,7 +72437,7 @@
       <c r="B1939" t="inlineStr"/>
       <c r="C1939" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1939" t="inlineStr">
@@ -72691,7 +72689,7 @@
       <c r="B1953" t="inlineStr"/>
       <c r="C1953" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1953" t="inlineStr">
@@ -72835,7 +72833,7 @@
       <c r="B1961" t="inlineStr"/>
       <c r="C1961" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1961" t="inlineStr">
@@ -72907,7 +72905,7 @@
       <c r="B1965" t="inlineStr"/>
       <c r="C1965" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1965" t="inlineStr">
@@ -72943,7 +72941,7 @@
       <c r="B1967" t="inlineStr"/>
       <c r="C1967" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1967" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1174,7 +1174,7 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1580,7 +1580,7 @@
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>V/Line Football Special via Werribee</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -6220,7 +6220,7 @@
       <c r="B328" t="inlineStr"/>
       <c r="C328" t="inlineStr">
         <is>
-          <t>PN Containerised Cotton</t>
+          <t>PN Garbage Train</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -10762,7 +10762,7 @@
       <c r="B595" t="inlineStr"/>
       <c r="C595" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer</t>
+          <t>NSW Trainlink Empty Car Transfer (ex SP36)</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
@@ -12233,7 +12233,7 @@
       <c r="B678" t="inlineStr"/>
       <c r="C678" t="inlineStr">
         <is>
-          <t>Aurizon Wagon Transfer</t>
+          <t>Aurizon Intermodal</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
@@ -16377,7 +16377,7 @@
       <c r="B912" t="inlineStr"/>
       <c r="C912" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D912" t="inlineStr">
@@ -17115,7 +17115,7 @@
       <c r="B953" t="inlineStr"/>
       <c r="C953" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D953" t="inlineStr">
@@ -18699,7 +18699,7 @@
       <c r="B1041" t="inlineStr"/>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1041" t="inlineStr">
@@ -18735,7 +18735,7 @@
       <c r="B1043" t="inlineStr"/>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1043" t="inlineStr">
@@ -19977,7 +19977,7 @@
       <c r="B1112" t="inlineStr"/>
       <c r="C1112" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1112" t="inlineStr">
@@ -20229,7 +20229,7 @@
       <c r="B1126" t="inlineStr"/>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1126" t="inlineStr">
@@ -20607,7 +20607,7 @@
       <c r="B1147" t="inlineStr"/>
       <c r="C1147" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1147" t="inlineStr">
@@ -20643,7 +20643,7 @@
       <c r="B1149" t="inlineStr"/>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1149" t="inlineStr">
@@ -21237,7 +21237,7 @@
       <c r="B1182" t="inlineStr"/>
       <c r="C1182" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1182" t="inlineStr">
@@ -21453,7 +21453,7 @@
       <c r="B1194" t="inlineStr"/>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1194" t="inlineStr">
@@ -21489,7 +21489,7 @@
       <c r="B1196" t="inlineStr"/>
       <c r="C1196" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1196" t="inlineStr">
@@ -21615,7 +21615,7 @@
       <c r="B1203" t="inlineStr"/>
       <c r="C1203" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1203" t="inlineStr">
@@ -21777,7 +21777,7 @@
       <c r="B1212" t="inlineStr"/>
       <c r="C1212" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1212" t="inlineStr">
@@ -22101,7 +22101,7 @@
       <c r="B1230" t="inlineStr"/>
       <c r="C1230" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1230" t="inlineStr">
@@ -22119,7 +22119,7 @@
       <c r="B1231" t="inlineStr"/>
       <c r="C1231" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1231" t="inlineStr">
@@ -22191,7 +22191,7 @@
       <c r="B1235" t="inlineStr"/>
       <c r="C1235" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1235" t="inlineStr">
@@ -22263,7 +22263,7 @@
       <c r="B1239" t="inlineStr"/>
       <c r="C1239" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1239" t="inlineStr">
@@ -22371,7 +22371,7 @@
       <c r="B1245" t="inlineStr"/>
       <c r="C1245" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1245" t="inlineStr">
@@ -22443,7 +22443,7 @@
       <c r="B1249" t="inlineStr"/>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1249" t="inlineStr">
@@ -22713,7 +22713,7 @@
       <c r="B1264" t="inlineStr"/>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1264" t="inlineStr">
@@ -22767,7 +22767,7 @@
       <c r="B1267" t="inlineStr"/>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1267" t="inlineStr">
@@ -22911,7 +22911,7 @@
       <c r="B1275" t="inlineStr"/>
       <c r="C1275" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1275" t="inlineStr">
@@ -22965,7 +22965,7 @@
       <c r="B1278" t="inlineStr"/>
       <c r="C1278" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1278" t="inlineStr">
@@ -25591,7 +25591,7 @@
       <c r="B1427" t="inlineStr"/>
       <c r="C1427" t="inlineStr">
         <is>
-          <t>SSR / Metro Maintenance Train</t>
+          <t>SSR/Metro Maintenance Train</t>
         </is>
       </c>
       <c r="D1427" t="inlineStr">
@@ -26531,7 +26531,7 @@
       <c r="B1485" t="inlineStr"/>
       <c r="C1485" t="inlineStr">
         <is>
-          <t>QUBE Loaded Containerised Ore</t>
+          <t>QUBE BlueScope Steel</t>
         </is>
       </c>
       <c r="D1485" t="inlineStr">
@@ -37519,7 +37519,7 @@
       <c r="B2103" t="inlineStr"/>
       <c r="C2103" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (Forms ST23)</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D2103" t="inlineStr">
@@ -38864,7 +38864,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -41966,7 +41966,7 @@
       <c r="B223" t="inlineStr"/>
       <c r="C223" t="inlineStr">
         <is>
-          <t>PN Containerised Cotton</t>
+          <t>PN Garbage Train</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -43016,7 +43016,7 @@
       <c r="B282" t="inlineStr"/>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -46454,7 +46454,7 @@
       <c r="B477" t="inlineStr"/>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -46972,7 +46972,7 @@
       <c r="B506" t="inlineStr"/>
       <c r="C506" t="inlineStr">
         <is>
-          <t>QUBE Loaded Containerised Ore</t>
+          <t>QUBE BlueScope Steel</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
@@ -50308,7 +50308,7 @@
       <c r="B694" t="inlineStr"/>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
@@ -54028,7 +54028,7 @@
       <c r="B902" t="inlineStr"/>
       <c r="C902" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D902" t="inlineStr">
@@ -55060,7 +55060,7 @@
       <c r="B960" t="inlineStr"/>
       <c r="C960" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D960" t="inlineStr">
@@ -55474,7 +55474,7 @@
       <c r="B983" t="inlineStr"/>
       <c r="C983" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D983" t="inlineStr">
@@ -56478,7 +56478,7 @@
       <c r="B1039" t="inlineStr"/>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1039" t="inlineStr">
@@ -56496,7 +56496,7 @@
       <c r="B1040" t="inlineStr"/>
       <c r="C1040" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1040" t="inlineStr">
@@ -59280,7 +59280,7 @@
       <c r="B1196" t="inlineStr"/>
       <c r="C1196" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1196" t="inlineStr">
@@ -62574,7 +62574,7 @@
       <c r="B1381" t="inlineStr"/>
       <c r="C1381" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1381" t="inlineStr">
@@ -63804,7 +63804,7 @@
       <c r="B1450" t="inlineStr"/>
       <c r="C1450" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1450" t="inlineStr">
@@ -64038,7 +64038,7 @@
       <c r="B1463" t="inlineStr"/>
       <c r="C1463" t="inlineStr">
         <is>
-          <t>V/Line Football Special via Werribee</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1463" t="inlineStr">
@@ -64254,7 +64254,7 @@
       <c r="B1475" t="inlineStr"/>
       <c r="C1475" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1475" t="inlineStr">
@@ -64683,7 +64683,7 @@
       <c r="B1499" t="inlineStr"/>
       <c r="C1499" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1499" t="inlineStr">
@@ -65593,7 +65593,7 @@
       <c r="B1550" t="inlineStr"/>
       <c r="C1550" t="inlineStr">
         <is>
-          <t>SSR / Metro Maintenance Train</t>
+          <t>SSR/Metro Maintenance Train</t>
         </is>
       </c>
       <c r="D1550" t="inlineStr">
@@ -68485,7 +68485,7 @@
       <c r="B1712" t="inlineStr"/>
       <c r="C1712" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (Forms ST23)</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1712" t="inlineStr">
@@ -70537,7 +70537,7 @@
       <c r="B1832" t="inlineStr"/>
       <c r="C1832" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer</t>
+          <t>NSW Trainlink Empty Car Transfer (ex SP36)</t>
         </is>
       </c>
       <c r="D1832" t="inlineStr">
@@ -70749,7 +70749,7 @@
       <c r="B1844" t="inlineStr"/>
       <c r="C1844" t="inlineStr">
         <is>
-          <t>Aurizon Wagon Transfer</t>
+          <t>Aurizon Intermodal</t>
         </is>
       </c>
       <c r="D1844" t="inlineStr">
@@ -71843,7 +71843,7 @@
       <c r="B1905" t="inlineStr"/>
       <c r="C1905" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1905" t="inlineStr">
@@ -71879,7 +71879,7 @@
       <c r="B1907" t="inlineStr"/>
       <c r="C1907" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1907" t="inlineStr">
@@ -72059,7 +72059,7 @@
       <c r="B1917" t="inlineStr"/>
       <c r="C1917" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1917" t="inlineStr">
@@ -72581,7 +72581,7 @@
       <c r="B1946" t="inlineStr"/>
       <c r="C1946" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1946" t="inlineStr">
@@ -72599,7 +72599,7 @@
       <c r="B1947" t="inlineStr"/>
       <c r="C1947" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1947" t="inlineStr">
@@ -72653,7 +72653,7 @@
       <c r="B1950" t="inlineStr"/>
       <c r="C1950" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1950" t="inlineStr">
@@ -72689,7 +72689,7 @@
       <c r="B1952" t="inlineStr"/>
       <c r="C1952" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1952" t="inlineStr">
@@ -72725,7 +72725,7 @@
       <c r="B1954" t="inlineStr"/>
       <c r="C1954" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1954" t="inlineStr">
@@ -72761,7 +72761,7 @@
       <c r="B1956" t="inlineStr"/>
       <c r="C1956" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1956" t="inlineStr">
@@ -72869,7 +72869,7 @@
       <c r="B1962" t="inlineStr"/>
       <c r="C1962" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1962" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1368,7 +1368,7 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4782,7 +4782,7 @@
       <c r="B247" t="inlineStr"/>
       <c r="C247" t="inlineStr">
         <is>
-          <t>PN Morandoo Shunter</t>
+          <t>PN Light Engine Movement</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -10410,7 +10410,7 @@
       <c r="B575" t="inlineStr"/>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Aurizon Mineral Sands Shuttle</t>
+          <t>Aurizon Shunter</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
@@ -16053,7 +16053,7 @@
       <c r="B894" t="inlineStr"/>
       <c r="C894" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D894" t="inlineStr">
@@ -17331,7 +17331,7 @@
       <c r="B965" t="inlineStr"/>
       <c r="C965" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D965" t="inlineStr">
@@ -18411,7 +18411,7 @@
       <c r="B1025" t="inlineStr"/>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1025" t="inlineStr">
@@ -18483,7 +18483,7 @@
       <c r="B1029" t="inlineStr"/>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1029" t="inlineStr">
@@ -18573,7 +18573,7 @@
       <c r="B1034" t="inlineStr"/>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1034" t="inlineStr">
@@ -18699,7 +18699,7 @@
       <c r="B1041" t="inlineStr"/>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1041" t="inlineStr">
@@ -18735,7 +18735,7 @@
       <c r="B1043" t="inlineStr"/>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1043" t="inlineStr">
@@ -19203,7 +19203,7 @@
       <c r="B1069" t="inlineStr"/>
       <c r="C1069" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1069" t="inlineStr">
@@ -19419,7 +19419,7 @@
       <c r="B1081" t="inlineStr"/>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1081" t="inlineStr">
@@ -19473,7 +19473,7 @@
       <c r="B1084" t="inlineStr"/>
       <c r="C1084" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1084" t="inlineStr">
@@ -19815,7 +19815,7 @@
       <c r="B1103" t="inlineStr"/>
       <c r="C1103" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1103" t="inlineStr">
@@ -19977,7 +19977,7 @@
       <c r="B1112" t="inlineStr"/>
       <c r="C1112" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1112" t="inlineStr">
@@ -20085,7 +20085,7 @@
       <c r="B1118" t="inlineStr"/>
       <c r="C1118" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1118" t="inlineStr">
@@ -20481,7 +20481,7 @@
       <c r="B1140" t="inlineStr"/>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1140" t="inlineStr">
@@ -20607,7 +20607,7 @@
       <c r="B1147" t="inlineStr"/>
       <c r="C1147" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1147" t="inlineStr">
@@ -20643,7 +20643,7 @@
       <c r="B1149" t="inlineStr"/>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1149" t="inlineStr">
@@ -20787,7 +20787,7 @@
       <c r="B1157" t="inlineStr"/>
       <c r="C1157" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1157" t="inlineStr">
@@ -21075,7 +21075,7 @@
       <c r="B1173" t="inlineStr"/>
       <c r="C1173" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1173" t="inlineStr">
@@ -21291,7 +21291,7 @@
       <c r="B1185" t="inlineStr"/>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1185" t="inlineStr">
@@ -21327,7 +21327,7 @@
       <c r="B1187" t="inlineStr"/>
       <c r="C1187" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1187" t="inlineStr">
@@ -21543,7 +21543,7 @@
       <c r="B1199" t="inlineStr"/>
       <c r="C1199" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1199" t="inlineStr">
@@ -21867,7 +21867,7 @@
       <c r="B1217" t="inlineStr"/>
       <c r="C1217" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1217" t="inlineStr">
@@ -21993,7 +21993,7 @@
       <c r="B1224" t="inlineStr"/>
       <c r="C1224" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1224" t="inlineStr">
@@ -22101,7 +22101,7 @@
       <c r="B1230" t="inlineStr"/>
       <c r="C1230" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1230" t="inlineStr">
@@ -22263,7 +22263,7 @@
       <c r="B1239" t="inlineStr"/>
       <c r="C1239" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1239" t="inlineStr">
@@ -22497,7 +22497,7 @@
       <c r="B1252" t="inlineStr"/>
       <c r="C1252" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1252" t="inlineStr">
@@ -22623,7 +22623,7 @@
       <c r="B1259" t="inlineStr"/>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1259" t="inlineStr">
@@ -22839,7 +22839,7 @@
       <c r="B1271" t="inlineStr"/>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1271" t="inlineStr">
@@ -22857,7 +22857,7 @@
       <c r="B1272" t="inlineStr"/>
       <c r="C1272" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1272" t="inlineStr">
@@ -22947,7 +22947,7 @@
       <c r="B1277" t="inlineStr"/>
       <c r="C1277" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1277" t="inlineStr">
@@ -22983,7 +22983,7 @@
       <c r="B1279" t="inlineStr"/>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1279" t="inlineStr">
@@ -23091,7 +23091,7 @@
       <c r="B1285" t="inlineStr"/>
       <c r="C1285" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1285" t="inlineStr">
@@ -37943,7 +37943,7 @@
       <c r="B2127" t="inlineStr"/>
       <c r="C2127" t="inlineStr">
         <is>
-          <t>ORA Coal</t>
+          <t>ORA Shunter</t>
         </is>
       </c>
       <c r="D2127" t="inlineStr">
@@ -40976,7 +40976,7 @@
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -41718,7 +41718,7 @@
       <c r="B209" t="inlineStr"/>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -42926,7 +42926,7 @@
       <c r="B277" t="inlineStr"/>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -43880,7 +43880,7 @@
       <c r="B332" t="inlineStr"/>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -46174,7 +46174,7 @@
       <c r="B461" t="inlineStr"/>
       <c r="C461" t="inlineStr">
         <is>
-          <t>PN Morandoo Shunter</t>
+          <t>PN Light Engine Movement</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -46418,7 +46418,7 @@
       <c r="B475" t="inlineStr"/>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -46472,7 +46472,7 @@
       <c r="B478" t="inlineStr"/>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -46954,7 +46954,7 @@
       <c r="B505" t="inlineStr"/>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
@@ -47544,7 +47544,7 @@
       <c r="B538" t="inlineStr"/>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
@@ -49642,7 +49642,7 @@
       <c r="B657" t="inlineStr"/>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
@@ -50308,7 +50308,7 @@
       <c r="B694" t="inlineStr"/>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
@@ -52924,7 +52924,7 @@
       <c r="B840" t="inlineStr"/>
       <c r="C840" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
@@ -54028,7 +54028,7 @@
       <c r="B902" t="inlineStr"/>
       <c r="C902" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D902" t="inlineStr">
@@ -54934,7 +54934,7 @@
       <c r="B953" t="inlineStr"/>
       <c r="C953" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D953" t="inlineStr">
@@ -56802,7 +56802,7 @@
       <c r="B1057" t="inlineStr"/>
       <c r="C1057" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1057" t="inlineStr">
@@ -57902,7 +57902,7 @@
       <c r="B1119" t="inlineStr"/>
       <c r="C1119" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1119" t="inlineStr">
@@ -57956,7 +57956,7 @@
       <c r="B1122" t="inlineStr"/>
       <c r="C1122" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1122" t="inlineStr">
@@ -60514,7 +60514,7 @@
       <c r="B1265" t="inlineStr"/>
       <c r="C1265" t="inlineStr">
         <is>
-          <t>Aurizon Mineral Sands Shuttle</t>
+          <t>Aurizon Shunter</t>
         </is>
       </c>
       <c r="D1265" t="inlineStr">
@@ -63840,7 +63840,7 @@
       <c r="B1452" t="inlineStr"/>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1452" t="inlineStr">
@@ -64218,7 +64218,7 @@
       <c r="B1473" t="inlineStr"/>
       <c r="C1473" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1473" t="inlineStr">
@@ -64254,7 +64254,7 @@
       <c r="B1475" t="inlineStr"/>
       <c r="C1475" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1475" t="inlineStr">
@@ -64290,7 +64290,7 @@
       <c r="B1477" t="inlineStr"/>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1477" t="inlineStr">
@@ -71465,7 +71465,7 @@
       <c r="B1884" t="inlineStr"/>
       <c r="C1884" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1884" t="inlineStr">
@@ -71501,7 +71501,7 @@
       <c r="B1886" t="inlineStr"/>
       <c r="C1886" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1886" t="inlineStr">
@@ -71843,7 +71843,7 @@
       <c r="B1905" t="inlineStr"/>
       <c r="C1905" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1905" t="inlineStr">
@@ -71969,7 +71969,7 @@
       <c r="B1912" t="inlineStr"/>
       <c r="C1912" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1912" t="inlineStr">
@@ -72059,7 +72059,7 @@
       <c r="B1917" t="inlineStr"/>
       <c r="C1917" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1917" t="inlineStr">
@@ -72149,7 +72149,7 @@
       <c r="B1922" t="inlineStr"/>
       <c r="C1922" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1922" t="inlineStr">
@@ -72311,7 +72311,7 @@
       <c r="B1931" t="inlineStr"/>
       <c r="C1931" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1931" t="inlineStr">
@@ -72473,7 +72473,7 @@
       <c r="B1940" t="inlineStr"/>
       <c r="C1940" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1940" t="inlineStr">
@@ -72545,7 +72545,7 @@
       <c r="B1944" t="inlineStr"/>
       <c r="C1944" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1944" t="inlineStr">
@@ -72581,7 +72581,7 @@
       <c r="B1946" t="inlineStr"/>
       <c r="C1946" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1946" t="inlineStr">
@@ -72689,7 +72689,7 @@
       <c r="B1952" t="inlineStr"/>
       <c r="C1952" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1952" t="inlineStr">
@@ -72941,7 +72941,7 @@
       <c r="B1966" t="inlineStr"/>
       <c r="C1966" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1966" t="inlineStr">
@@ -72977,7 +72977,7 @@
       <c r="B1968" t="inlineStr"/>
       <c r="C1968" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1968" t="inlineStr">
@@ -75365,7 +75365,7 @@
       <c r="B2106" t="inlineStr"/>
       <c r="C2106" t="inlineStr">
         <is>
-          <t>ORA Coal</t>
+          <t>ORA Shunter</t>
         </is>
       </c>
       <c r="D2106" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -5986,7 +5986,7 @@
       <c r="B315" t="inlineStr"/>
       <c r="C315" t="inlineStr">
         <is>
-          <t>PN Grain</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -8288,7 +8288,7 @@
       <c r="B450" t="inlineStr"/>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Aurizon Shunter</t>
+          <t>Aurizon Empty Mineral Sands Shuttle</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -18713,7 +18713,7 @@
       <c r="B1042" t="inlineStr"/>
       <c r="C1042" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1042" t="inlineStr">
@@ -19829,7 +19829,7 @@
       <c r="B1104" t="inlineStr"/>
       <c r="C1104" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1104" t="inlineStr">
@@ -19991,7 +19991,7 @@
       <c r="B1113" t="inlineStr"/>
       <c r="C1113" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1113" t="inlineStr">
@@ -20495,7 +20495,7 @@
       <c r="B1141" t="inlineStr"/>
       <c r="C1141" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1141" t="inlineStr">
@@ -20621,7 +20621,7 @@
       <c r="B1148" t="inlineStr"/>
       <c r="C1148" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1148" t="inlineStr">
@@ -20657,7 +20657,7 @@
       <c r="B1150" t="inlineStr"/>
       <c r="C1150" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1150" t="inlineStr">
@@ -21089,7 +21089,7 @@
       <c r="B1174" t="inlineStr"/>
       <c r="C1174" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1174" t="inlineStr">
@@ -21467,7 +21467,7 @@
       <c r="B1195" t="inlineStr"/>
       <c r="C1195" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1195" t="inlineStr">
@@ -21791,7 +21791,7 @@
       <c r="B1213" t="inlineStr"/>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1213" t="inlineStr">
@@ -22007,7 +22007,7 @@
       <c r="B1225" t="inlineStr"/>
       <c r="C1225" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1225" t="inlineStr">
@@ -22511,7 +22511,7 @@
       <c r="B1253" t="inlineStr"/>
       <c r="C1253" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1253" t="inlineStr">
@@ -22727,7 +22727,7 @@
       <c r="B1265" t="inlineStr"/>
       <c r="C1265" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1265" t="inlineStr">
@@ -43908,7 +43908,7 @@
       <c r="B333" t="inlineStr"/>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -46482,7 +46482,7 @@
       <c r="B478" t="inlineStr"/>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -46982,7 +46982,7 @@
       <c r="B506" t="inlineStr"/>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
@@ -50336,7 +50336,7 @@
       <c r="B695" t="inlineStr"/>
       <c r="C695" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
@@ -52812,7 +52812,7 @@
       <c r="B833" t="inlineStr"/>
       <c r="C833" t="inlineStr">
         <is>
-          <t>PN Grain</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D833" t="inlineStr">
@@ -53502,7 +53502,7 @@
       <c r="B872" t="inlineStr"/>
       <c r="C872" t="inlineStr">
         <is>
-          <t>Aurizon Shunter</t>
+          <t>Aurizon Empty Mineral Sands Shuttle</t>
         </is>
       </c>
       <c r="D872" t="inlineStr">
@@ -54962,7 +54962,7 @@
       <c r="B954" t="inlineStr"/>
       <c r="C954" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D954" t="inlineStr">
@@ -55088,7 +55088,7 @@
       <c r="B961" t="inlineStr"/>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D961" t="inlineStr">
@@ -56506,7 +56506,7 @@
       <c r="B1040" t="inlineStr"/>
       <c r="C1040" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1040" t="inlineStr">
@@ -64282,7 +64282,7 @@
       <c r="B1476" t="inlineStr"/>
       <c r="C1476" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1476" t="inlineStr">
@@ -71871,7 +71871,7 @@
       <c r="B1906" t="inlineStr"/>
       <c r="C1906" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1906" t="inlineStr">
@@ -71997,7 +71997,7 @@
       <c r="B1913" t="inlineStr"/>
       <c r="C1913" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1913" t="inlineStr">
@@ -72087,7 +72087,7 @@
       <c r="B1918" t="inlineStr"/>
       <c r="C1918" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1918" t="inlineStr">
@@ -72573,7 +72573,7 @@
       <c r="B1945" t="inlineStr"/>
       <c r="C1945" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1945" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -2544,7 +2544,7 @@
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>V/Line Transfer</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -9762,7 +9762,7 @@
       <c r="B539" t="inlineStr"/>
       <c r="C539" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
@@ -9814,7 +9814,11 @@
         </is>
       </c>
       <c r="B542" t="inlineStr"/>
-      <c r="C542" t="inlineStr"/>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>SRS Empty Log Train</t>
+        </is>
+      </c>
       <c r="D542" t="inlineStr">
         <is>
           <t>2026-04-18 14:25:08</t>
@@ -12379,7 +12383,7 @@
       <c r="B687" t="inlineStr"/>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
@@ -18587,7 +18591,7 @@
       <c r="B1035" t="inlineStr"/>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1035" t="inlineStr">
@@ -19217,7 +19221,7 @@
       <c r="B1070" t="inlineStr"/>
       <c r="C1070" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1070" t="inlineStr">
@@ -20243,7 +20247,7 @@
       <c r="B1127" t="inlineStr"/>
       <c r="C1127" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1127" t="inlineStr">
@@ -21305,7 +21309,7 @@
       <c r="B1186" t="inlineStr"/>
       <c r="C1186" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1186" t="inlineStr">
@@ -21557,7 +21561,7 @@
       <c r="B1200" t="inlineStr"/>
       <c r="C1200" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1200" t="inlineStr">
@@ -22637,7 +22641,7 @@
       <c r="B1260" t="inlineStr"/>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1260" t="inlineStr">
@@ -22961,7 +22965,7 @@
       <c r="B1278" t="inlineStr"/>
       <c r="C1278" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1278" t="inlineStr">
@@ -24847,7 +24851,7 @@
       <c r="B1385" t="inlineStr"/>
       <c r="C1385" t="inlineStr">
         <is>
-          <t>PN Infrabuild Steel</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D1385" t="inlineStr">
@@ -38160,7 +38164,11 @@
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SRS Empty Log Train</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>2026-04-18 14:25:08</t>
@@ -41004,7 +41012,7 @@
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -41746,7 +41754,7 @@
       <c r="B210" t="inlineStr"/>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -47572,7 +47580,7 @@
       <c r="B539" t="inlineStr"/>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
@@ -56830,7 +56838,7 @@
       <c r="B1058" t="inlineStr"/>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1058" t="inlineStr">
@@ -57984,7 +57992,7 @@
       <c r="B1123" t="inlineStr"/>
       <c r="C1123" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1123" t="inlineStr">
@@ -64995,7 +65003,7 @@
       <c r="B1516" t="inlineStr"/>
       <c r="C1516" t="inlineStr">
         <is>
-          <t>PN Infrabuild Steel</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D1516" t="inlineStr">
@@ -68621,7 +68629,7 @@
       <c r="B1719" t="inlineStr"/>
       <c r="C1719" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>V/Line Transfer</t>
         </is>
       </c>
       <c r="D1719" t="inlineStr">
@@ -70331,7 +70339,7 @@
       <c r="B1820" t="inlineStr"/>
       <c r="C1820" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1820" t="inlineStr">
@@ -70813,7 +70821,7 @@
       <c r="B1847" t="inlineStr"/>
       <c r="C1847" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1847" t="inlineStr">
@@ -71529,7 +71537,7 @@
       <c r="B1887" t="inlineStr"/>
       <c r="C1887" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1887" t="inlineStr">
@@ -71907,7 +71915,7 @@
       <c r="B1908" t="inlineStr"/>
       <c r="C1908" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1908" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -12039,7 +12039,7 @@
       <c r="B667" t="inlineStr"/>
       <c r="C667" t="inlineStr">
         <is>
-          <t>Aurizon Empty Ore</t>
+          <t>Aurizon Loaded Ore</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
@@ -12437,7 +12437,7 @@
       <c r="B690" t="inlineStr"/>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
@@ -16395,7 +16395,7 @@
       <c r="B913" t="inlineStr"/>
       <c r="C913" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D913" t="inlineStr">
@@ -19491,7 +19491,7 @@
       <c r="B1085" t="inlineStr"/>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1085" t="inlineStr">
@@ -19833,7 +19833,7 @@
       <c r="B1104" t="inlineStr"/>
       <c r="C1104" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1104" t="inlineStr">
@@ -20103,7 +20103,7 @@
       <c r="B1119" t="inlineStr"/>
       <c r="C1119" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1119" t="inlineStr">
@@ -38900,7 +38900,7 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -41930,7 +41930,7 @@
       <c r="B220" t="inlineStr"/>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Aurizon Empty Ore</t>
+          <t>Aurizon Loaded Ore</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -46454,7 +46454,7 @@
       <c r="B476" t="inlineStr"/>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -54970,7 +54970,7 @@
       <c r="B954" t="inlineStr"/>
       <c r="C954" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D954" t="inlineStr">
@@ -57938,7 +57938,7 @@
       <c r="B1120" t="inlineStr"/>
       <c r="C1120" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1120" t="inlineStr">
@@ -70839,7 +70839,7 @@
       <c r="B1848" t="inlineStr"/>
       <c r="C1848" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1848" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -12437,7 +12437,7 @@
       <c r="B690" t="inlineStr"/>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
@@ -18717,7 +18717,7 @@
       <c r="B1042" t="inlineStr"/>
       <c r="C1042" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1042" t="inlineStr">
@@ -19833,7 +19833,7 @@
       <c r="B1104" t="inlineStr"/>
       <c r="C1104" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1104" t="inlineStr">
@@ -20247,7 +20247,7 @@
       <c r="B1127" t="inlineStr"/>
       <c r="C1127" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1127" t="inlineStr">
@@ -22515,7 +22515,7 @@
       <c r="B1253" t="inlineStr"/>
       <c r="C1253" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1253" t="inlineStr">
@@ -22965,7 +22965,7 @@
       <c r="B1278" t="inlineStr"/>
       <c r="C1278" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1278" t="inlineStr">
@@ -25609,7 +25609,7 @@
       <c r="B1428" t="inlineStr"/>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>SSR/Metro Maintenance Train</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D1428" t="inlineStr">
@@ -28345,7 +28345,7 @@
       <c r="B1590" t="inlineStr"/>
       <c r="C1590" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>South Coast Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1590" t="inlineStr">
@@ -47018,7 +47018,7 @@
       <c r="B507" t="inlineStr"/>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
@@ -54998,7 +54998,7 @@
       <c r="B955" t="inlineStr"/>
       <c r="C955" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D955" t="inlineStr">
@@ -56866,7 +56866,7 @@
       <c r="B1059" t="inlineStr"/>
       <c r="C1059" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1059" t="inlineStr">
@@ -64318,7 +64318,7 @@
       <c r="B1477" t="inlineStr"/>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1477" t="inlineStr">
@@ -65657,7 +65657,7 @@
       <c r="B1552" t="inlineStr"/>
       <c r="C1552" t="inlineStr">
         <is>
-          <t>SSR/Metro Maintenance Train</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D1552" t="inlineStr">
@@ -70867,7 +70867,7 @@
       <c r="B1849" t="inlineStr"/>
       <c r="C1849" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1849" t="inlineStr">
@@ -71943,7 +71943,7 @@
       <c r="B1909" t="inlineStr"/>
       <c r="C1909" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1909" t="inlineStr">
@@ -74223,7 +74223,7 @@
       <c r="B2041" t="inlineStr"/>
       <c r="C2041" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>South Coast Empty Car Transfer</t>
         </is>
       </c>
       <c r="D2041" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -5810,7 +5810,7 @@
       <c r="B305" t="inlineStr"/>
       <c r="C305" t="inlineStr">
         <is>
-          <t>PN Cootamundra Shunter</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -12545,7 +12545,7 @@
       <c r="B696" t="inlineStr"/>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
@@ -16035,7 +16035,7 @@
       <c r="B893" t="inlineStr"/>
       <c r="C893" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D893" t="inlineStr">
@@ -16629,7 +16629,7 @@
       <c r="B926" t="inlineStr"/>
       <c r="C926" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D926" t="inlineStr">
@@ -17349,7 +17349,7 @@
       <c r="B966" t="inlineStr"/>
       <c r="C966" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D966" t="inlineStr">
@@ -19491,7 +19491,7 @@
       <c r="B1085" t="inlineStr"/>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1085" t="inlineStr">
@@ -20103,7 +20103,7 @@
       <c r="B1119" t="inlineStr"/>
       <c r="C1119" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1119" t="inlineStr">
@@ -28345,7 +28345,7 @@
       <c r="B1590" t="inlineStr"/>
       <c r="C1590" t="inlineStr">
         <is>
-          <t>South Coast Empty Car Transfer</t>
+          <t>NSW Trainlink South Coast Service</t>
         </is>
       </c>
       <c r="D1590" t="inlineStr">
@@ -46482,7 +46482,7 @@
       <c r="B477" t="inlineStr"/>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -51840,7 +51840,7 @@
       <c r="B778" t="inlineStr"/>
       <c r="C778" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D778" t="inlineStr">
@@ -52812,7 +52812,7 @@
       <c r="B832" t="inlineStr"/>
       <c r="C832" t="inlineStr">
         <is>
-          <t>PN Cootamundra Shunter</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D832" t="inlineStr">
@@ -52988,7 +52988,7 @@
       <c r="B842" t="inlineStr"/>
       <c r="C842" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
@@ -57966,7 +57966,7 @@
       <c r="B1121" t="inlineStr"/>
       <c r="C1121" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1121" t="inlineStr">
@@ -70903,7 +70903,7 @@
       <c r="B1851" t="inlineStr"/>
       <c r="C1851" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1851" t="inlineStr">
@@ -71475,7 +71475,7 @@
       <c r="B1883" t="inlineStr"/>
       <c r="C1883" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1883" t="inlineStr">
@@ -74223,7 +74223,7 @@
       <c r="B2041" t="inlineStr"/>
       <c r="C2041" t="inlineStr">
         <is>
-          <t>South Coast Empty Car Transfer</t>
+          <t>NSW Trainlink South Coast Service</t>
         </is>
       </c>
       <c r="D2041" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -9906,7 +9906,7 @@
       <c r="B547" t="inlineStr"/>
       <c r="C547" t="inlineStr">
         <is>
-          <t>QUBE Grain</t>
+          <t>QUBE Empty Grain</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
@@ -18015,7 +18015,7 @@
       <c r="B1003" t="inlineStr"/>
       <c r="C1003" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1003" t="inlineStr">
@@ -18591,7 +18591,7 @@
       <c r="B1035" t="inlineStr"/>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1035" t="inlineStr">
@@ -18717,7 +18717,7 @@
       <c r="B1042" t="inlineStr"/>
       <c r="C1042" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1042" t="inlineStr">
@@ -19221,7 +19221,7 @@
       <c r="B1070" t="inlineStr"/>
       <c r="C1070" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1070" t="inlineStr">
@@ -19995,7 +19995,7 @@
       <c r="B1113" t="inlineStr"/>
       <c r="C1113" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1113" t="inlineStr">
@@ -20247,7 +20247,7 @@
       <c r="B1127" t="inlineStr"/>
       <c r="C1127" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1127" t="inlineStr">
@@ -20751,7 +20751,7 @@
       <c r="B1155" t="inlineStr"/>
       <c r="C1155" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1155" t="inlineStr">
@@ -21813,7 +21813,7 @@
       <c r="B1214" t="inlineStr"/>
       <c r="C1214" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1214" t="inlineStr">
@@ -21849,7 +21849,7 @@
       <c r="B1216" t="inlineStr"/>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1216" t="inlineStr">
@@ -22641,7 +22641,7 @@
       <c r="B1260" t="inlineStr"/>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1260" t="inlineStr">
@@ -22983,7 +22983,7 @@
       <c r="B1279" t="inlineStr"/>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1279" t="inlineStr">
@@ -25609,7 +25609,7 @@
       <c r="B1428" t="inlineStr"/>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SSR/Metro Maintenance Train</t>
         </is>
       </c>
       <c r="D1428" t="inlineStr">
@@ -26219,7 +26219,7 @@
       <c r="B1467" t="inlineStr"/>
       <c r="C1467" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Annhydrous Ammonia Tanks</t>
+          <t>Aurizon Loaded Annhydrous Ammonia</t>
         </is>
       </c>
       <c r="D1467" t="inlineStr">
@@ -28259,7 +28259,7 @@
       <c r="B1585" t="inlineStr"/>
       <c r="C1585" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1585" t="inlineStr">
@@ -28277,7 +28277,7 @@
       <c r="B1586" t="inlineStr"/>
       <c r="C1586" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1586" t="inlineStr">
@@ -41782,7 +41782,7 @@
       <c r="B211" t="inlineStr"/>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -47608,7 +47608,7 @@
       <c r="B540" t="inlineStr"/>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
@@ -52308,7 +52308,7 @@
       <c r="B804" t="inlineStr"/>
       <c r="C804" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D804" t="inlineStr">
@@ -60258,7 +60258,7 @@
       <c r="B1249" t="inlineStr"/>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>QUBE Grain</t>
+          <t>QUBE Empty Grain</t>
         </is>
       </c>
       <c r="D1249" t="inlineStr">
@@ -60398,7 +60398,7 @@
       <c r="B1257" t="inlineStr"/>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1257" t="inlineStr">
@@ -60722,7 +60722,7 @@
       <c r="B1275" t="inlineStr"/>
       <c r="C1275" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1275" t="inlineStr">
@@ -62638,7 +62638,7 @@
       <c r="B1383" t="inlineStr"/>
       <c r="C1383" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1383" t="inlineStr">
@@ -63044,7 +63044,7 @@
       <c r="B1406" t="inlineStr"/>
       <c r="C1406" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1406" t="inlineStr">
@@ -64318,7 +64318,7 @@
       <c r="B1477" t="inlineStr"/>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1477" t="inlineStr">
@@ -65657,7 +65657,7 @@
       <c r="B1552" t="inlineStr"/>
       <c r="C1552" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SSR/Metro Maintenance Train</t>
         </is>
       </c>
       <c r="D1552" t="inlineStr">
@@ -67401,7 +67401,7 @@
       <c r="B1650" t="inlineStr"/>
       <c r="C1650" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1650" t="inlineStr">
@@ -71565,7 +71565,7 @@
       <c r="B1888" t="inlineStr"/>
       <c r="C1888" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1888" t="inlineStr">
@@ -71907,7 +71907,7 @@
       <c r="B1907" t="inlineStr"/>
       <c r="C1907" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1907" t="inlineStr">
@@ -71943,7 +71943,7 @@
       <c r="B1909" t="inlineStr"/>
       <c r="C1909" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1909" t="inlineStr">
@@ -72195,7 +72195,7 @@
       <c r="B1923" t="inlineStr"/>
       <c r="C1923" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1923" t="inlineStr">
@@ -73841,7 +73841,7 @@
       <c r="B2018" t="inlineStr"/>
       <c r="C2018" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Annhydrous Ammonia Tanks</t>
+          <t>Aurizon Loaded Annhydrous Ammonia</t>
         </is>
       </c>
       <c r="D2018" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -3950,7 +3950,7 @@
       <c r="B199" t="inlineStr"/>
       <c r="C199" t="inlineStr">
         <is>
-          <t>AZ Light Engine</t>
+          <t>AZ Coal</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -4728,7 +4728,7 @@
       <c r="B244" t="inlineStr"/>
       <c r="C244" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>Maintenance Train</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -8744,7 +8744,7 @@
       <c r="B476" t="inlineStr"/>
       <c r="C476" t="inlineStr">
         <is>
-          <t>MRL Empty Iron Ore</t>
+          <t>Yilgarn Iron Iron Ore</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -9780,7 +9780,7 @@
       <c r="B540" t="inlineStr"/>
       <c r="C540" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR - NSW TrainLink Transfer</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
@@ -10122,7 +10122,7 @@
       <c r="B559" t="inlineStr"/>
       <c r="C559" t="inlineStr">
         <is>
-          <t>SCT Intermodal</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
@@ -11227,7 +11227,7 @@
       <c r="B621" t="inlineStr"/>
       <c r="C621" t="inlineStr">
         <is>
-          <t>SSR Loaded Cement</t>
+          <t>SSR Empty Cement</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
@@ -12329,7 +12329,7 @@
       <c r="B684" t="inlineStr"/>
       <c r="C684" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
@@ -12455,7 +12455,7 @@
       <c r="B691" t="inlineStr"/>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
@@ -15195,7 +15195,7 @@
       <c r="B845" t="inlineStr"/>
       <c r="C845" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
@@ -15245,7 +15245,7 @@
       <c r="B848" t="inlineStr"/>
       <c r="C848" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>South Coast Service</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
@@ -19221,7 +19221,7 @@
       <c r="B1070" t="inlineStr"/>
       <c r="C1070" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1070" t="inlineStr">
@@ -19833,7 +19833,7 @@
       <c r="B1104" t="inlineStr"/>
       <c r="C1104" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1104" t="inlineStr">
@@ -20103,7 +20103,7 @@
       <c r="B1119" t="inlineStr"/>
       <c r="C1119" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1119" t="inlineStr">
@@ -22515,7 +22515,7 @@
       <c r="B1253" t="inlineStr"/>
       <c r="C1253" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1253" t="inlineStr">
@@ -22929,7 +22929,7 @@
       <c r="B1276" t="inlineStr"/>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1276" t="inlineStr">
@@ -25887,7 +25887,7 @@
       <c r="B1447" t="inlineStr"/>
       <c r="C1447" t="inlineStr">
         <is>
-          <t>Watco Trip Train</t>
+          <t>Watco Light Engine</t>
         </is>
       </c>
       <c r="D1447" t="inlineStr">
@@ -27725,7 +27725,7 @@
       <c r="B1554" t="inlineStr"/>
       <c r="C1554" t="inlineStr">
         <is>
-          <t>SCT Intermodal</t>
+          <t>SCT Shuttle</t>
         </is>
       </c>
       <c r="D1554" t="inlineStr">
@@ -28067,7 +28067,7 @@
       <c r="B1573" t="inlineStr"/>
       <c r="C1573" t="inlineStr">
         <is>
-          <t>SSR Cement Transfer</t>
+          <t>SSR Cement</t>
         </is>
       </c>
       <c r="D1573" t="inlineStr">
@@ -28345,7 +28345,7 @@
       <c r="B1590" t="inlineStr"/>
       <c r="C1590" t="inlineStr">
         <is>
-          <t>NSW Trainlink South Coast Service</t>
+          <t>South Coast Service</t>
         </is>
       </c>
       <c r="D1590" t="inlineStr">
@@ -41782,7 +41782,7 @@
       <c r="B211" t="inlineStr"/>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41940,7 +41940,7 @@
       <c r="B220" t="inlineStr"/>
       <c r="C220" t="inlineStr">
         <is>
-          <t>AZ Light Engine</t>
+          <t>AZ Coal</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -47018,7 +47018,7 @@
       <c r="B507" t="inlineStr"/>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
@@ -53376,7 +53376,7 @@
       <c r="B864" t="inlineStr"/>
       <c r="C864" t="inlineStr">
         <is>
-          <t>SSR Cement Transfer</t>
+          <t>SSR Cement</t>
         </is>
       </c>
       <c r="D864" t="inlineStr">
@@ -54728,7 +54728,7 @@
       <c r="B940" t="inlineStr"/>
       <c r="C940" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>Maintenance Train</t>
         </is>
       </c>
       <c r="D940" t="inlineStr">
@@ -54998,7 +54998,7 @@
       <c r="B955" t="inlineStr"/>
       <c r="C955" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D955" t="inlineStr">
@@ -57966,7 +57966,7 @@
       <c r="B1121" t="inlineStr"/>
       <c r="C1121" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1121" t="inlineStr">
@@ -58164,7 +58164,7 @@
       <c r="B1132" t="inlineStr"/>
       <c r="C1132" t="inlineStr">
         <is>
-          <t>Watco Trip Train</t>
+          <t>Watco Light Engine</t>
         </is>
       </c>
       <c r="D1132" t="inlineStr">
@@ -61278,7 +61278,7 @@
       <c r="B1307" t="inlineStr"/>
       <c r="C1307" t="inlineStr">
         <is>
-          <t>MRL Empty Iron Ore</t>
+          <t>Yilgarn Iron Iron Ore</t>
         </is>
       </c>
       <c r="D1307" t="inlineStr">
@@ -63868,7 +63868,7 @@
       <c r="B1452" t="inlineStr"/>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1452" t="inlineStr">
@@ -64815,7 +64815,7 @@
       <c r="B1505" t="inlineStr"/>
       <c r="C1505" t="inlineStr">
         <is>
-          <t>SCT Intermodal</t>
+          <t>SCT Shuttle</t>
         </is>
       </c>
       <c r="D1505" t="inlineStr">
@@ -66189,7 +66189,7 @@
       <c r="B1582" t="inlineStr"/>
       <c r="C1582" t="inlineStr">
         <is>
-          <t>SSR Loaded Cement</t>
+          <t>SSR Empty Cement</t>
         </is>
       </c>
       <c r="D1582" t="inlineStr">
@@ -66207,7 +66207,7 @@
       <c r="B1583" t="inlineStr"/>
       <c r="C1583" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>South Coast Service</t>
         </is>
       </c>
       <c r="D1583" t="inlineStr">
@@ -67869,7 +67869,7 @@
       <c r="B1676" t="inlineStr"/>
       <c r="C1676" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1676" t="inlineStr">
@@ -68031,7 +68031,7 @@
       <c r="B1685" t="inlineStr"/>
       <c r="C1685" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1685" t="inlineStr">
@@ -70385,7 +70385,7 @@
       <c r="B1822" t="inlineStr"/>
       <c r="C1822" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR - NSW TrainLink Transfer</t>
         </is>
       </c>
       <c r="D1822" t="inlineStr">
@@ -70457,7 +70457,7 @@
       <c r="B1826" t="inlineStr"/>
       <c r="C1826" t="inlineStr">
         <is>
-          <t>SCT Intermodal</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D1826" t="inlineStr">
@@ -70885,7 +70885,7 @@
       <c r="B1850" t="inlineStr"/>
       <c r="C1850" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1850" t="inlineStr">
@@ -74223,7 +74223,7 @@
       <c r="B2041" t="inlineStr"/>
       <c r="C2041" t="inlineStr">
         <is>
-          <t>NSW Trainlink South Coast Service</t>
+          <t>South Coast Service</t>
         </is>
       </c>
       <c r="D2041" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -2886,7 +2886,7 @@
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>North East SG Line Service</t>
+          <t>North East Line SG Service</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -2904,7 +2904,7 @@
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>North East SG Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -2940,7 +2940,7 @@
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>V/Line SG Special</t>
+          <t>North East Line SG Service</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -3242,7 +3242,7 @@
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr">
         <is>
-          <t>QUBE Trip Train</t>
+          <t>QUBE Light Engine</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -15177,7 +15177,7 @@
       <c r="B844" t="inlineStr"/>
       <c r="C844" t="inlineStr">
         <is>
-          <t>Empty Car Transfer (forms WN17 - Bathurst Bullet)</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D844" t="inlineStr">
@@ -18015,7 +18015,7 @@
       <c r="B1003" t="inlineStr"/>
       <c r="C1003" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1003" t="inlineStr">
@@ -19491,7 +19491,7 @@
       <c r="B1085" t="inlineStr"/>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1085" t="inlineStr">
@@ -19635,7 +19635,7 @@
       <c r="B1093" t="inlineStr"/>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1093" t="inlineStr">
@@ -22173,7 +22173,7 @@
       <c r="B1234" t="inlineStr"/>
       <c r="C1234" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1234" t="inlineStr">
@@ -22641,7 +22641,7 @@
       <c r="B1260" t="inlineStr"/>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1260" t="inlineStr">
@@ -27477,7 +27477,7 @@
       <c r="B1540" t="inlineStr"/>
       <c r="C1540" t="inlineStr">
         <is>
-          <t>North-East BG Service</t>
+          <t>V/Line Light Engine Movement</t>
         </is>
       </c>
       <c r="D1540" t="inlineStr">
@@ -28295,7 +28295,7 @@
       <c r="B1587" t="inlineStr"/>
       <c r="C1587" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1587" t="inlineStr">
@@ -43800,7 +43800,7 @@
       <c r="B326" t="inlineStr"/>
       <c r="C326" t="inlineStr">
         <is>
-          <t>QUBE Trip Train</t>
+          <t>QUBE Light Engine</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -46482,7 +46482,7 @@
       <c r="B477" t="inlineStr"/>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -46752,7 +46752,7 @@
       <c r="B492" t="inlineStr"/>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
@@ -47608,7 +47608,7 @@
       <c r="B540" t="inlineStr"/>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
@@ -53966,7 +53966,7 @@
       <c r="B897" t="inlineStr"/>
       <c r="C897" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D897" t="inlineStr">
@@ -54854,7 +54854,7 @@
       <c r="B947" t="inlineStr"/>
       <c r="C947" t="inlineStr">
         <is>
-          <t>Empty Car Transfer (forms WN17 - Bathurst Bullet)</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D947" t="inlineStr">
@@ -62494,7 +62494,7 @@
       <c r="B1375" t="inlineStr"/>
       <c r="C1375" t="inlineStr">
         <is>
-          <t>North East SG Line Service</t>
+          <t>North East Line SG Service</t>
         </is>
       </c>
       <c r="D1375" t="inlineStr">
@@ -63044,7 +63044,7 @@
       <c r="B1406" t="inlineStr"/>
       <c r="C1406" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1406" t="inlineStr">
@@ -65955,7 +65955,7 @@
       <c r="B1569" t="inlineStr"/>
       <c r="C1569" t="inlineStr">
         <is>
-          <t>North-East BG Service</t>
+          <t>V/Line Light Engine Movement</t>
         </is>
       </c>
       <c r="D1569" t="inlineStr">
@@ -66567,7 +66567,7 @@
       <c r="B1603" t="inlineStr"/>
       <c r="C1603" t="inlineStr">
         <is>
-          <t>North East SG Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1603" t="inlineStr">
@@ -66585,7 +66585,7 @@
       <c r="B1604" t="inlineStr"/>
       <c r="C1604" t="inlineStr">
         <is>
-          <t>V/Line SG Special</t>
+          <t>North East Line SG Service</t>
         </is>
       </c>
       <c r="D1604" t="inlineStr">
@@ -68207,7 +68207,7 @@
       <c r="B1695" t="inlineStr"/>
       <c r="C1695" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1695" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1368,7 +1368,7 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>V/Line Test Train</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7154,7 +7154,7 @@
       <c r="B381" t="inlineStr"/>
       <c r="C381" t="inlineStr">
         <is>
-          <t>PN Coal</t>
+          <t>PN Port Waratah Shunter</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -10032,7 +10032,7 @@
       <c r="B554" t="inlineStr"/>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Grain</t>
+          <t>Aurizon Empty Grain</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
@@ -18591,7 +18591,7 @@
       <c r="B1035" t="inlineStr"/>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1035" t="inlineStr">
@@ -19239,7 +19239,7 @@
       <c r="B1071" t="inlineStr"/>
       <c r="C1071" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1071" t="inlineStr">
@@ -19995,7 +19995,7 @@
       <c r="B1113" t="inlineStr"/>
       <c r="C1113" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1113" t="inlineStr">
@@ -20247,7 +20247,7 @@
       <c r="B1127" t="inlineStr"/>
       <c r="C1127" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1127" t="inlineStr">
@@ -20751,7 +20751,7 @@
       <c r="B1155" t="inlineStr"/>
       <c r="C1155" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1155" t="inlineStr">
@@ -22965,7 +22965,7 @@
       <c r="B1278" t="inlineStr"/>
       <c r="C1278" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1278" t="inlineStr">
@@ -29103,7 +29103,7 @@
       <c r="B1635" t="inlineStr"/>
       <c r="C1635" t="inlineStr">
         <is>
-          <t>QUBE Light Engine Movement</t>
+          <t>QUBE Containerised Freight</t>
         </is>
       </c>
       <c r="D1635" t="inlineStr">
@@ -45462,7 +45462,7 @@
       <c r="B419" t="inlineStr"/>
       <c r="C419" t="inlineStr">
         <is>
-          <t>QUBE Light Engine Movement</t>
+          <t>QUBE Containerised Freight</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -49706,7 +49706,7 @@
       <c r="B659" t="inlineStr"/>
       <c r="C659" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>V/Line Test Train</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
@@ -54020,7 +54020,7 @@
       <c r="B900" t="inlineStr"/>
       <c r="C900" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D900" t="inlineStr">
@@ -56866,7 +56866,7 @@
       <c r="B1059" t="inlineStr"/>
       <c r="C1059" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1059" t="inlineStr">
@@ -69559,7 +69559,7 @@
       <c r="B1771" t="inlineStr"/>
       <c r="C1771" t="inlineStr">
         <is>
-          <t>PN Coal</t>
+          <t>PN Port Waratah Shunter</t>
         </is>
       </c>
       <c r="D1771" t="inlineStr">
@@ -70403,7 +70403,7 @@
       <c r="B1823" t="inlineStr"/>
       <c r="C1823" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Grain</t>
+          <t>Aurizon Empty Grain</t>
         </is>
       </c>
       <c r="D1823" t="inlineStr">
@@ -71565,7 +71565,7 @@
       <c r="B1888" t="inlineStr"/>
       <c r="C1888" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1888" t="inlineStr">
@@ -71907,7 +71907,7 @@
       <c r="B1907" t="inlineStr"/>
       <c r="C1907" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1907" t="inlineStr">
@@ -71943,7 +71943,7 @@
       <c r="B1909" t="inlineStr"/>
       <c r="C1909" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1909" t="inlineStr">
@@ -72195,7 +72195,7 @@
       <c r="B1923" t="inlineStr"/>
       <c r="C1923" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1923" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1030,7 +1030,7 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>V1132</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2778,7 +2778,7 @@
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Gippsland Line Service</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -11051,7 +11051,7 @@
       <c r="B611" t="inlineStr"/>
       <c r="C611" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer</t>
+          <t>NSW Trainlink Xplorer to Sydney (connects with NP24)</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
@@ -15195,7 +15195,7 @@
       <c r="B845" t="inlineStr"/>
       <c r="C845" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
@@ -18717,7 +18717,7 @@
       <c r="B1042" t="inlineStr"/>
       <c r="C1042" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1042" t="inlineStr">
@@ -19833,7 +19833,7 @@
       <c r="B1104" t="inlineStr"/>
       <c r="C1104" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1104" t="inlineStr">
@@ -20751,7 +20751,7 @@
       <c r="B1155" t="inlineStr"/>
       <c r="C1155" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1155" t="inlineStr">
@@ -21345,7 +21345,7 @@
       <c r="B1188" t="inlineStr"/>
       <c r="C1188" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1188" t="inlineStr">
@@ -22407,7 +22407,7 @@
       <c r="B1247" t="inlineStr"/>
       <c r="C1247" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1247" t="inlineStr">
@@ -22929,7 +22929,7 @@
       <c r="B1276" t="inlineStr"/>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1276" t="inlineStr">
@@ -22983,7 +22983,7 @@
       <c r="B1279" t="inlineStr"/>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1279" t="inlineStr">
@@ -25451,7 +25451,7 @@
       <c r="B1419" t="inlineStr"/>
       <c r="C1419" t="inlineStr">
         <is>
-          <t>PN Keswick Shunter</t>
+          <t>PN Shunter</t>
         </is>
       </c>
       <c r="D1419" t="inlineStr">
@@ -25887,7 +25887,7 @@
       <c r="B1447" t="inlineStr"/>
       <c r="C1447" t="inlineStr">
         <is>
-          <t>Watco Light Engine</t>
+          <t>Watco Trip Train</t>
         </is>
       </c>
       <c r="D1447" t="inlineStr">
@@ -29139,7 +29139,7 @@
       <c r="B1637" t="inlineStr"/>
       <c r="C1637" t="inlineStr">
         <is>
-          <t>QUBE Containerised Freight</t>
+          <t>QUBE Light Engine Movement</t>
         </is>
       </c>
       <c r="D1637" t="inlineStr">
@@ -37339,7 +37339,7 @@
       <c r="B2093" t="inlineStr"/>
       <c r="C2093" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW TrainLink XPT</t>
         </is>
       </c>
       <c r="D2093" t="inlineStr">
@@ -38083,7 +38083,7 @@
       <c r="B2135" t="inlineStr"/>
       <c r="C2135" t="inlineStr">
         <is>
-          <t>ORA Coal</t>
+          <t>ORA Shunter</t>
         </is>
       </c>
       <c r="D2135" t="inlineStr">
@@ -42468,7 +42468,7 @@
       <c r="B250" t="inlineStr"/>
       <c r="C250" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Gippsland Line Service</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -53250,7 +53250,7 @@
       <c r="B857" t="inlineStr"/>
       <c r="C857" t="inlineStr">
         <is>
-          <t>ORA Coal</t>
+          <t>ORA Shunter</t>
         </is>
       </c>
       <c r="D857" t="inlineStr">
@@ -54656,7 +54656,7 @@
       <c r="B936" t="inlineStr"/>
       <c r="C936" t="inlineStr">
         <is>
-          <t>QUBE Containerised Freight</t>
+          <t>QUBE Light Engine Movement</t>
         </is>
       </c>
       <c r="D936" t="inlineStr">
@@ -54998,7 +54998,7 @@
       <c r="B955" t="inlineStr"/>
       <c r="C955" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D955" t="inlineStr">
@@ -58164,7 +58164,7 @@
       <c r="B1132" t="inlineStr"/>
       <c r="C1132" t="inlineStr">
         <is>
-          <t>Watco Light Engine</t>
+          <t>Watco Trip Train</t>
         </is>
       </c>
       <c r="D1132" t="inlineStr">
@@ -60754,7 +60754,7 @@
       <c r="B1277" t="inlineStr"/>
       <c r="C1277" t="inlineStr">
         <is>
-          <t>PN Keswick Shunter</t>
+          <t>PN Shunter</t>
         </is>
       </c>
       <c r="D1277" t="inlineStr">
@@ -62548,7 +62548,7 @@
       <c r="B1378" t="inlineStr"/>
       <c r="C1378" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer</t>
+          <t>NSW Trainlink Xplorer to Sydney (connects with NP24)</t>
         </is>
       </c>
       <c r="D1378" t="inlineStr">
@@ -62638,7 +62638,7 @@
       <c r="B1383" t="inlineStr"/>
       <c r="C1383" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1383" t="inlineStr">
@@ -63868,7 +63868,7 @@
       <c r="B1452" t="inlineStr"/>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1452" t="inlineStr">
@@ -64318,7 +64318,7 @@
       <c r="B1477" t="inlineStr"/>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1477" t="inlineStr">
@@ -65729,7 +65729,7 @@
       <c r="B1556" t="inlineStr"/>
       <c r="C1556" t="inlineStr">
         <is>
-          <t>V1132</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1556" t="inlineStr">
@@ -66009,7 +66009,7 @@
       <c r="B1572" t="inlineStr"/>
       <c r="C1572" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW TrainLink XPT</t>
         </is>
       </c>
       <c r="D1572" t="inlineStr">
@@ -68031,7 +68031,7 @@
       <c r="B1685" t="inlineStr"/>
       <c r="C1685" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1685" t="inlineStr">
@@ -72195,7 +72195,7 @@
       <c r="B1923" t="inlineStr"/>
       <c r="C1923" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1923" t="inlineStr">
@@ -72375,7 +72375,7 @@
       <c r="B1933" t="inlineStr"/>
       <c r="C1933" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1933" t="inlineStr">
@@ -72807,7 +72807,7 @@
       <c r="B1957" t="inlineStr"/>
       <c r="C1957" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1957" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1368,7 +1368,7 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>V/Line Test Train</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1688,7 +1688,7 @@
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Northeast Line BG Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4940,7 +4940,7 @@
       <c r="B256" t="inlineStr"/>
       <c r="C256" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Morandoo Shunter</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -10943,7 +10943,7 @@
       <c r="B605" t="inlineStr"/>
       <c r="C605" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer</t>
+          <t>NSW Trainlink Xplorer</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
@@ -10979,7 +10979,7 @@
       <c r="B607" t="inlineStr"/>
       <c r="C607" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer</t>
+          <t>NSW Trainlink Empty Car Transfer</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
@@ -16035,7 +16035,7 @@
       <c r="B893" t="inlineStr"/>
       <c r="C893" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D893" t="inlineStr">
@@ -16071,7 +16071,7 @@
       <c r="B895" t="inlineStr"/>
       <c r="C895" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D895" t="inlineStr">
@@ -16089,7 +16089,7 @@
       <c r="B896" t="inlineStr"/>
       <c r="C896" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
@@ -18591,7 +18591,7 @@
       <c r="B1035" t="inlineStr"/>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1035" t="inlineStr">
@@ -19221,7 +19221,7 @@
       <c r="B1070" t="inlineStr"/>
       <c r="C1070" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1070" t="inlineStr">
@@ -19275,7 +19275,7 @@
       <c r="B1073" t="inlineStr"/>
       <c r="C1073" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1073" t="inlineStr">
@@ -19383,7 +19383,7 @@
       <c r="B1079" t="inlineStr"/>
       <c r="C1079" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1079" t="inlineStr">
@@ -19509,7 +19509,7 @@
       <c r="B1086" t="inlineStr"/>
       <c r="C1086" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1086" t="inlineStr">
@@ -19563,7 +19563,7 @@
       <c r="B1089" t="inlineStr"/>
       <c r="C1089" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1089" t="inlineStr">
@@ -19941,7 +19941,7 @@
       <c r="B1110" t="inlineStr"/>
       <c r="C1110" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1110" t="inlineStr">
@@ -20139,7 +20139,7 @@
       <c r="B1121" t="inlineStr"/>
       <c r="C1121" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1121" t="inlineStr">
@@ -20499,7 +20499,7 @@
       <c r="B1141" t="inlineStr"/>
       <c r="C1141" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1141" t="inlineStr">
@@ -20805,7 +20805,7 @@
       <c r="B1158" t="inlineStr"/>
       <c r="C1158" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1158" t="inlineStr">
@@ -21507,7 +21507,7 @@
       <c r="B1197" t="inlineStr"/>
       <c r="C1197" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1197" t="inlineStr">
@@ -22389,7 +22389,7 @@
       <c r="B1246" t="inlineStr"/>
       <c r="C1246" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1246" t="inlineStr">
@@ -22443,7 +22443,7 @@
       <c r="B1249" t="inlineStr"/>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1249" t="inlineStr">
@@ -22479,7 +22479,7 @@
       <c r="B1251" t="inlineStr"/>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1251" t="inlineStr">
@@ -22515,7 +22515,7 @@
       <c r="B1253" t="inlineStr"/>
       <c r="C1253" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1253" t="inlineStr">
@@ -22713,7 +22713,7 @@
       <c r="B1264" t="inlineStr"/>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1264" t="inlineStr">
@@ -22965,7 +22965,7 @@
       <c r="B1278" t="inlineStr"/>
       <c r="C1278" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1278" t="inlineStr">
@@ -39576,7 +39576,7 @@
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -41810,7 +41810,7 @@
       <c r="B212" t="inlineStr"/>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -43018,7 +43018,7 @@
       <c r="B280" t="inlineStr"/>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -44994,7 +44994,7 @@
       <c r="B392" t="inlineStr"/>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -46528,7 +46528,7 @@
       <c r="B479" t="inlineStr"/>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -46884,7 +46884,7 @@
       <c r="B499" t="inlineStr"/>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
@@ -47046,7 +47046,7 @@
       <c r="B508" t="inlineStr"/>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
@@ -49320,7 +49320,7 @@
       <c r="B637" t="inlineStr"/>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Northeast Line BG Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
@@ -49734,7 +49734,7 @@
       <c r="B660" t="inlineStr"/>
       <c r="C660" t="inlineStr">
         <is>
-          <t>V/Line Test Train</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
@@ -54648,7 +54648,7 @@
       <c r="B935" t="inlineStr"/>
       <c r="C935" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D935" t="inlineStr">
@@ -56588,7 +56588,7 @@
       <c r="B1043" t="inlineStr"/>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1043" t="inlineStr">
@@ -56894,7 +56894,7 @@
       <c r="B1060" t="inlineStr"/>
       <c r="C1060" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1060" t="inlineStr">
@@ -59512,7 +59512,7 @@
       <c r="B1207" t="inlineStr"/>
       <c r="C1207" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer</t>
+          <t>NSW Trainlink Xplorer</t>
         </is>
       </c>
       <c r="D1207" t="inlineStr">
@@ -61428,7 +61428,7 @@
       <c r="B1315" t="inlineStr"/>
       <c r="C1315" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1315" t="inlineStr">
@@ -63828,7 +63828,7 @@
       <c r="B1449" t="inlineStr"/>
       <c r="C1449" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer</t>
+          <t>NSW Trainlink Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1449" t="inlineStr">
@@ -63878,7 +63878,7 @@
       <c r="B1452" t="inlineStr"/>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1452" t="inlineStr">
@@ -64472,7 +64472,7 @@
       <c r="B1485" t="inlineStr"/>
       <c r="C1485" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1485" t="inlineStr">
@@ -69389,7 +69389,7 @@
       <c r="B1761" t="inlineStr"/>
       <c r="C1761" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Morandoo Shunter</t>
         </is>
       </c>
       <c r="D1761" t="inlineStr">
@@ -71503,7 +71503,7 @@
       <c r="B1884" t="inlineStr"/>
       <c r="C1884" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1884" t="inlineStr">
@@ -71593,7 +71593,7 @@
       <c r="B1889" t="inlineStr"/>
       <c r="C1889" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1889" t="inlineStr">
@@ -71791,7 +71791,7 @@
       <c r="B1900" t="inlineStr"/>
       <c r="C1900" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1900" t="inlineStr">
@@ -71845,7 +71845,7 @@
       <c r="B1903" t="inlineStr"/>
       <c r="C1903" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1903" t="inlineStr">
@@ -72061,7 +72061,7 @@
       <c r="B1915" t="inlineStr"/>
       <c r="C1915" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1915" t="inlineStr">
@@ -72241,7 +72241,7 @@
       <c r="B1925" t="inlineStr"/>
       <c r="C1925" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1925" t="inlineStr">
@@ -72817,7 +72817,7 @@
       <c r="B1957" t="inlineStr"/>
       <c r="C1957" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1957" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -688,7 +688,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>V/Line rail cleaning train</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1458,7 +1458,7 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>South Western Line service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1598,7 +1598,7 @@
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1990,7 +1990,7 @@
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -8270,7 +8270,7 @@
       <c r="B449" t="inlineStr"/>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Aurizon Kalgoorlie Mixed Freight</t>
+          <t>Aurizon Cockburn Cement - Lime and Cement Train</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -10852,7 +10852,7 @@
       <c r="B600" t="inlineStr"/>
       <c r="C600" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (ex NP24)</t>
+          <t>NSW Trainlink Xplorer</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
@@ -16683,7 +16683,7 @@
       <c r="B929" t="inlineStr"/>
       <c r="C929" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D929" t="inlineStr">
@@ -18033,7 +18033,7 @@
       <c r="B1004" t="inlineStr"/>
       <c r="C1004" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1004" t="inlineStr">
@@ -19509,7 +19509,7 @@
       <c r="B1086" t="inlineStr"/>
       <c r="C1086" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1086" t="inlineStr">
@@ -20103,7 +20103,7 @@
       <c r="B1119" t="inlineStr"/>
       <c r="C1119" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1119" t="inlineStr">
@@ -20751,7 +20751,7 @@
       <c r="B1155" t="inlineStr"/>
       <c r="C1155" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1155" t="inlineStr">
@@ -21111,7 +21111,7 @@
       <c r="B1175" t="inlineStr"/>
       <c r="C1175" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1175" t="inlineStr">
@@ -21633,7 +21633,7 @@
       <c r="B1204" t="inlineStr"/>
       <c r="C1204" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1204" t="inlineStr">
@@ -21795,7 +21795,7 @@
       <c r="B1213" t="inlineStr"/>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1213" t="inlineStr">
@@ -21849,7 +21849,7 @@
       <c r="B1216" t="inlineStr"/>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1216" t="inlineStr">
@@ -22011,7 +22011,7 @@
       <c r="B1225" t="inlineStr"/>
       <c r="C1225" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1225" t="inlineStr">
@@ -22209,7 +22209,7 @@
       <c r="B1236" t="inlineStr"/>
       <c r="C1236" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1236" t="inlineStr">
@@ -22407,7 +22407,7 @@
       <c r="B1247" t="inlineStr"/>
       <c r="C1247" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1247" t="inlineStr">
@@ -22641,7 +22641,7 @@
       <c r="B1260" t="inlineStr"/>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1260" t="inlineStr">
@@ -22785,7 +22785,7 @@
       <c r="B1268" t="inlineStr"/>
       <c r="C1268" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1268" t="inlineStr">
@@ -22857,7 +22857,7 @@
       <c r="B1272" t="inlineStr"/>
       <c r="C1272" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1272" t="inlineStr">
@@ -22911,7 +22911,7 @@
       <c r="B1275" t="inlineStr"/>
       <c r="C1275" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1275" t="inlineStr">
@@ -22983,7 +22983,7 @@
       <c r="B1279" t="inlineStr"/>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1279" t="inlineStr">
@@ -23749,7 +23749,7 @@
       <c r="B1322" t="inlineStr"/>
       <c r="C1322" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>NR8</t>
         </is>
       </c>
       <c r="D1322" t="inlineStr">
@@ -24213,7 +24213,7 @@
       <c r="B1348" t="inlineStr"/>
       <c r="C1348" t="inlineStr">
         <is>
-          <t>PN Broken Hill Shunter</t>
+          <t>NR39</t>
         </is>
       </c>
       <c r="D1348" t="inlineStr">
@@ -24413,7 +24413,7 @@
       <c r="B1360" t="inlineStr"/>
       <c r="C1360" t="inlineStr">
         <is>
-          <t>PN Steel Transfer</t>
+          <t>PN Infrabuild Steel via Lithgow</t>
         </is>
       </c>
       <c r="D1360" t="inlineStr">
@@ -37849,7 +37849,7 @@
       <c r="B2122" t="inlineStr"/>
       <c r="C2122" t="inlineStr">
         <is>
-          <t>ORA Shunter</t>
+          <t>ORA Light Engine</t>
         </is>
       </c>
       <c r="D2122" t="inlineStr">
@@ -42716,7 +42716,7 @@
       <c r="B263" t="inlineStr"/>
       <c r="C263" t="inlineStr">
         <is>
-          <t>ORA Shunter</t>
+          <t>ORA Light Engine</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -43660,7 +43660,7 @@
       <c r="B317" t="inlineStr"/>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Alamein Line</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -47658,7 +47658,7 @@
       <c r="B542" t="inlineStr"/>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
@@ -49324,7 +49324,7 @@
       <c r="B637" t="inlineStr"/>
       <c r="C637" t="inlineStr">
         <is>
-          <t>South Western Line service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
@@ -53836,7 +53836,7 @@
       <c r="B889" t="inlineStr"/>
       <c r="C889" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D889" t="inlineStr">
@@ -54124,7 +54124,7 @@
       <c r="B905" t="inlineStr"/>
       <c r="C905" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D905" t="inlineStr">
@@ -55174,7 +55174,7 @@
       <c r="B964" t="inlineStr"/>
       <c r="C964" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D964" t="inlineStr">
@@ -55588,7 +55588,7 @@
       <c r="B987" t="inlineStr"/>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D987" t="inlineStr">
@@ -57498,7 +57498,7 @@
       <c r="B1094" t="inlineStr"/>
       <c r="C1094" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (ex NP24)</t>
+          <t>NSW Trainlink Xplorer</t>
         </is>
       </c>
       <c r="D1094" t="inlineStr">
@@ -58016,7 +58016,7 @@
       <c r="B1123" t="inlineStr"/>
       <c r="C1123" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1123" t="inlineStr">
@@ -60398,7 +60398,7 @@
       <c r="B1256" t="inlineStr"/>
       <c r="C1256" t="inlineStr">
         <is>
-          <t>PN Steel Transfer</t>
+          <t>PN Infrabuild Steel via Lithgow</t>
         </is>
       </c>
       <c r="D1256" t="inlineStr">
@@ -60772,7 +60772,7 @@
       <c r="B1277" t="inlineStr"/>
       <c r="C1277" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1277" t="inlineStr">
@@ -60836,7 +60836,7 @@
       <c r="B1281" t="inlineStr"/>
       <c r="C1281" t="inlineStr">
         <is>
-          <t>PN Broken Hill Shunter</t>
+          <t>NR39</t>
         </is>
       </c>
       <c r="D1281" t="inlineStr">
@@ -62526,7 +62526,7 @@
       <c r="B1376" t="inlineStr"/>
       <c r="C1376" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1376" t="inlineStr">
@@ -62688,7 +62688,7 @@
       <c r="B1385" t="inlineStr"/>
       <c r="C1385" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1385" t="inlineStr">
@@ -65567,7 +65567,7 @@
       <c r="B1546" t="inlineStr"/>
       <c r="C1546" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>NR8</t>
         </is>
       </c>
       <c r="D1546" t="inlineStr">
@@ -66527,7 +66527,7 @@
       <c r="B1600" t="inlineStr"/>
       <c r="C1600" t="inlineStr">
         <is>
-          <t>V/Line rail cleaning train</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1600" t="inlineStr">
@@ -68959,7 +68959,7 @@
       <c r="B1736" t="inlineStr"/>
       <c r="C1736" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D1736" t="inlineStr">
@@ -69897,7 +69897,7 @@
       <c r="B1791" t="inlineStr"/>
       <c r="C1791" t="inlineStr">
         <is>
-          <t>Aurizon Kalgoorlie Mixed Freight</t>
+          <t>Aurizon Cockburn Cement - Lime and Cement Train</t>
         </is>
       </c>
       <c r="D1791" t="inlineStr">
@@ -71867,7 +71867,7 @@
       <c r="B1904" t="inlineStr"/>
       <c r="C1904" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1904" t="inlineStr">
@@ -72245,7 +72245,7 @@
       <c r="B1925" t="inlineStr"/>
       <c r="C1925" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1925" t="inlineStr">
@@ -72335,7 +72335,7 @@
       <c r="B1930" t="inlineStr"/>
       <c r="C1930" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1930" t="inlineStr">
@@ -72659,7 +72659,7 @@
       <c r="B1948" t="inlineStr"/>
       <c r="C1948" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1948" t="inlineStr">
@@ -72767,7 +72767,7 @@
       <c r="B1954" t="inlineStr"/>
       <c r="C1954" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1954" t="inlineStr">
@@ -72857,7 +72857,7 @@
       <c r="B1959" t="inlineStr"/>
       <c r="C1959" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1959" t="inlineStr">
@@ -72983,7 +72983,7 @@
       <c r="B1966" t="inlineStr"/>
       <c r="C1966" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1966" t="inlineStr">
@@ -73055,7 +73055,7 @@
       <c r="B1970" t="inlineStr"/>
       <c r="C1970" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1970" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1138,7 +1138,7 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1494,7 +1494,7 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>North East Line Service</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2760,7 +2760,7 @@
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -2868,7 +2868,7 @@
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>North East Line SG Service</t>
+          <t>North East SG Line Service</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -5968,7 +5968,7 @@
       <c r="B314" t="inlineStr"/>
       <c r="C314" t="inlineStr">
         <is>
-          <t>PN Empty Ore</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -7736,7 +7736,7 @@
       <c r="B416" t="inlineStr"/>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Qube Trip Train</t>
+          <t>QUBE Trip Train</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -9152,7 +9152,7 @@
       <c r="B504" t="inlineStr"/>
       <c r="C504" t="inlineStr">
         <is>
-          <t>SSR Trip Train</t>
+          <t>AK Cars</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
@@ -9978,7 +9978,7 @@
       <c r="B551" t="inlineStr"/>
       <c r="C551" t="inlineStr">
         <is>
-          <t>QUBE Grain</t>
+          <t>Qube Grain</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
@@ -11051,7 +11051,7 @@
       <c r="B611" t="inlineStr"/>
       <c r="C611" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer to Sydney (connects with NP24)</t>
+          <t>NSW Trainlink Xplorer</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
@@ -11159,7 +11159,7 @@
       <c r="B617" t="inlineStr"/>
       <c r="C617" t="inlineStr">
         <is>
-          <t>SSR Containerised Freight</t>
+          <t>Fletchers Containerised Freight (Bank Engine)</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
@@ -12383,7 +12383,7 @@
       <c r="B687" t="inlineStr"/>
       <c r="C687" t="inlineStr">
         <is>
-          <t>NSW Trainlink Passenger Service</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
@@ -12455,7 +12455,7 @@
       <c r="B691" t="inlineStr"/>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
@@ -15177,7 +15177,7 @@
       <c r="B844" t="inlineStr"/>
       <c r="C844" t="inlineStr">
         <is>
-          <t>Additional Bathurst Service</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D844" t="inlineStr">
@@ -15567,7 +15567,7 @@
       <c r="B867" t="inlineStr"/>
       <c r="C867" t="inlineStr">
         <is>
-          <t>SSR Manildra Grain Shuttle</t>
+          <t>SSR Loaded Manildra Flour</t>
         </is>
       </c>
       <c r="D867" t="inlineStr">
@@ -15657,7 +15657,7 @@
       <c r="B872" t="inlineStr"/>
       <c r="C872" t="inlineStr">
         <is>
-          <t>SSR Empty Manildra Flour</t>
+          <t>SSR - NSW TrainLink Transfer</t>
         </is>
       </c>
       <c r="D872" t="inlineStr">
@@ -16305,7 +16305,7 @@
       <c r="B908" t="inlineStr"/>
       <c r="C908" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D908" t="inlineStr">
@@ -16485,7 +16485,7 @@
       <c r="B918" t="inlineStr"/>
       <c r="C918" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D918" t="inlineStr">
@@ -16575,7 +16575,7 @@
       <c r="B923" t="inlineStr"/>
       <c r="C923" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D923" t="inlineStr">
@@ -17079,7 +17079,7 @@
       <c r="B951" t="inlineStr"/>
       <c r="C951" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D951" t="inlineStr">
@@ -17349,7 +17349,7 @@
       <c r="B966" t="inlineStr"/>
       <c r="C966" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D966" t="inlineStr">
@@ -17547,7 +17547,7 @@
       <c r="B977" t="inlineStr"/>
       <c r="C977" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D977" t="inlineStr">
@@ -17691,7 +17691,7 @@
       <c r="B985" t="inlineStr"/>
       <c r="C985" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D985" t="inlineStr">
@@ -17889,7 +17889,7 @@
       <c r="B996" t="inlineStr"/>
       <c r="C996" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D996" t="inlineStr">
@@ -18051,7 +18051,7 @@
       <c r="B1005" t="inlineStr"/>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1005" t="inlineStr">
@@ -18483,7 +18483,7 @@
       <c r="B1029" t="inlineStr"/>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1029" t="inlineStr">
@@ -18663,7 +18663,7 @@
       <c r="B1039" t="inlineStr"/>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1039" t="inlineStr">
@@ -18681,7 +18681,7 @@
       <c r="B1040" t="inlineStr"/>
       <c r="C1040" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1040" t="inlineStr">
@@ -18735,7 +18735,7 @@
       <c r="B1043" t="inlineStr"/>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1043" t="inlineStr">
@@ -19041,7 +19041,7 @@
       <c r="B1060" t="inlineStr"/>
       <c r="C1060" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1060" t="inlineStr">
@@ -19527,7 +19527,7 @@
       <c r="B1087" t="inlineStr"/>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1087" t="inlineStr">
@@ -20517,7 +20517,7 @@
       <c r="B1142" t="inlineStr"/>
       <c r="C1142" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1142" t="inlineStr">
@@ -20553,7 +20553,7 @@
       <c r="B1144" t="inlineStr"/>
       <c r="C1144" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1144" t="inlineStr">
@@ -20571,7 +20571,7 @@
       <c r="B1145" t="inlineStr"/>
       <c r="C1145" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1145" t="inlineStr">
@@ -20679,7 +20679,7 @@
       <c r="B1151" t="inlineStr"/>
       <c r="C1151" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1151" t="inlineStr">
@@ -20823,7 +20823,7 @@
       <c r="B1159" t="inlineStr"/>
       <c r="C1159" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1159" t="inlineStr">
@@ -21075,7 +21075,7 @@
       <c r="B1173" t="inlineStr"/>
       <c r="C1173" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1173" t="inlineStr">
@@ -21129,7 +21129,7 @@
       <c r="B1176" t="inlineStr"/>
       <c r="C1176" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1176" t="inlineStr">
@@ -21237,7 +21237,7 @@
       <c r="B1182" t="inlineStr"/>
       <c r="C1182" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1182" t="inlineStr">
@@ -21327,7 +21327,7 @@
       <c r="B1187" t="inlineStr"/>
       <c r="C1187" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1187" t="inlineStr">
@@ -21759,7 +21759,7 @@
       <c r="B1211" t="inlineStr"/>
       <c r="C1211" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1211" t="inlineStr">
@@ -21813,7 +21813,7 @@
       <c r="B1214" t="inlineStr"/>
       <c r="C1214" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1214" t="inlineStr">
@@ -21867,7 +21867,7 @@
       <c r="B1217" t="inlineStr"/>
       <c r="C1217" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1217" t="inlineStr">
@@ -21939,7 +21939,7 @@
       <c r="B1221" t="inlineStr"/>
       <c r="C1221" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1221" t="inlineStr">
@@ -22029,7 +22029,7 @@
       <c r="B1226" t="inlineStr"/>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1226" t="inlineStr">
@@ -22119,7 +22119,7 @@
       <c r="B1231" t="inlineStr"/>
       <c r="C1231" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1231" t="inlineStr">
@@ -22227,7 +22227,7 @@
       <c r="B1237" t="inlineStr"/>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1237" t="inlineStr">
@@ -22389,7 +22389,7 @@
       <c r="B1246" t="inlineStr"/>
       <c r="C1246" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1246" t="inlineStr">
@@ -22425,7 +22425,7 @@
       <c r="B1248" t="inlineStr"/>
       <c r="C1248" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1248" t="inlineStr">
@@ -22461,7 +22461,7 @@
       <c r="B1250" t="inlineStr"/>
       <c r="C1250" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1250" t="inlineStr">
@@ -22551,7 +22551,7 @@
       <c r="B1255" t="inlineStr"/>
       <c r="C1255" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1255" t="inlineStr">
@@ -22659,7 +22659,7 @@
       <c r="B1261" t="inlineStr"/>
       <c r="C1261" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1261" t="inlineStr">
@@ -22677,7 +22677,7 @@
       <c r="B1262" t="inlineStr"/>
       <c r="C1262" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1262" t="inlineStr">
@@ -22749,7 +22749,7 @@
       <c r="B1266" t="inlineStr"/>
       <c r="C1266" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1266" t="inlineStr">
@@ -22767,7 +22767,7 @@
       <c r="B1267" t="inlineStr"/>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1267" t="inlineStr">
@@ -22803,7 +22803,7 @@
       <c r="B1269" t="inlineStr"/>
       <c r="C1269" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1269" t="inlineStr">
@@ -22875,7 +22875,7 @@
       <c r="B1273" t="inlineStr"/>
       <c r="C1273" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1273" t="inlineStr">
@@ -22929,7 +22929,7 @@
       <c r="B1276" t="inlineStr"/>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1276" t="inlineStr">
@@ -22947,7 +22947,7 @@
       <c r="B1277" t="inlineStr"/>
       <c r="C1277" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1277" t="inlineStr">
@@ -22983,7 +22983,7 @@
       <c r="B1279" t="inlineStr"/>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1279" t="inlineStr">
@@ -23001,7 +23001,7 @@
       <c r="B1280" t="inlineStr"/>
       <c r="C1280" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1280" t="inlineStr">
@@ -23019,7 +23019,7 @@
       <c r="B1281" t="inlineStr"/>
       <c r="C1281" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1281" t="inlineStr">
@@ -23073,7 +23073,7 @@
       <c r="B1284" t="inlineStr"/>
       <c r="C1284" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1284" t="inlineStr">
@@ -23371,7 +23371,7 @@
       <c r="B1301" t="inlineStr"/>
       <c r="C1301" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>N453</t>
         </is>
       </c>
       <c r="D1301" t="inlineStr">
@@ -23749,7 +23749,7 @@
       <c r="B1322" t="inlineStr"/>
       <c r="C1322" t="inlineStr">
         <is>
-          <t>NR7</t>
+          <t>PN Wagon Transfer</t>
         </is>
       </c>
       <c r="D1322" t="inlineStr">
@@ -24743,7 +24743,7 @@
       <c r="B1379" t="inlineStr"/>
       <c r="C1379" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>JBR The Ghan</t>
         </is>
       </c>
       <c r="D1379" t="inlineStr">
@@ -26657,7 +26657,7 @@
       <c r="B1492" t="inlineStr"/>
       <c r="C1492" t="inlineStr">
         <is>
-          <t>QUBE Empty Grain</t>
+          <t>QUBE Trip Train</t>
         </is>
       </c>
       <c r="D1492" t="inlineStr">
@@ -28017,7 +28017,7 @@
       <c r="B1570" t="inlineStr"/>
       <c r="C1570" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Light Engine</t>
         </is>
       </c>
       <c r="D1570" t="inlineStr">
@@ -28913,7 +28913,7 @@
       <c r="B1624" t="inlineStr"/>
       <c r="C1624" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D1624" t="inlineStr">
@@ -38119,7 +38119,7 @@
       <c r="B2137" t="inlineStr"/>
       <c r="C2137" t="inlineStr">
         <is>
-          <t>ORA Shunter</t>
+          <t>ORA Coal</t>
         </is>
       </c>
       <c r="D2137" t="inlineStr">
@@ -38234,7 +38234,7 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>QUBE Empty Grain</t>
+          <t>QUBE Trip Train</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -39086,7 +39086,7 @@
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -39244,7 +39244,7 @@
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -42680,7 +42680,7 @@
       <c r="B260" t="inlineStr"/>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -42734,7 +42734,7 @@
       <c r="B263" t="inlineStr"/>
       <c r="C263" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -43814,7 +43814,7 @@
       <c r="B325" t="inlineStr"/>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -44462,7 +44462,7 @@
       <c r="B361" t="inlineStr"/>
       <c r="C361" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -44674,7 +44674,7 @@
       <c r="B373" t="inlineStr"/>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -45466,7 +45466,7 @@
       <c r="B417" t="inlineStr"/>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -45962,7 +45962,7 @@
       <c r="B445" t="inlineStr"/>
       <c r="C445" t="inlineStr">
         <is>
-          <t>PN Empty Ore</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -46586,7 +46586,7 @@
       <c r="B481" t="inlineStr"/>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -46604,7 +46604,7 @@
       <c r="B482" t="inlineStr"/>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -46820,7 +46820,7 @@
       <c r="B494" t="inlineStr"/>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
@@ -47086,7 +47086,7 @@
       <c r="B509" t="inlineStr"/>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
@@ -47316,7 +47316,7 @@
       <c r="B522" t="inlineStr"/>
       <c r="C522" t="inlineStr">
         <is>
-          <t>QUBE Grain</t>
+          <t>Qube Grain</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
@@ -47640,7 +47640,7 @@
       <c r="B540" t="inlineStr"/>
       <c r="C540" t="inlineStr">
         <is>
-          <t>SSR Manildra Grain Shuttle</t>
+          <t>SSR Loaded Manildra Flour</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
@@ -47694,7 +47694,7 @@
       <c r="B543" t="inlineStr"/>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
@@ -47712,7 +47712,7 @@
       <c r="B544" t="inlineStr"/>
       <c r="C544" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>JBR The Ghan</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
@@ -48946,7 +48946,7 @@
       <c r="B615" t="inlineStr"/>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -50062,7 +50062,7 @@
       <c r="B677" t="inlineStr"/>
       <c r="C677" t="inlineStr">
         <is>
-          <t>NR7</t>
+          <t>PN Wagon Transfer</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
@@ -50458,7 +50458,7 @@
       <c r="B699" t="inlineStr"/>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
@@ -53074,7 +53074,7 @@
       <c r="B845" t="inlineStr"/>
       <c r="C845" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
@@ -53336,7 +53336,7 @@
       <c r="B860" t="inlineStr"/>
       <c r="C860" t="inlineStr">
         <is>
-          <t>ORA Shunter</t>
+          <t>ORA Coal</t>
         </is>
       </c>
       <c r="D860" t="inlineStr">
@@ -53872,7 +53872,7 @@
       <c r="B890" t="inlineStr"/>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D890" t="inlineStr">
@@ -54286,7 +54286,7 @@
       <c r="B913" t="inlineStr"/>
       <c r="C913" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D913" t="inlineStr">
@@ -54544,7 +54544,7 @@
       <c r="B928" t="inlineStr"/>
       <c r="C928" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D928" t="inlineStr">
@@ -54634,7 +54634,7 @@
       <c r="B933" t="inlineStr"/>
       <c r="C933" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>North East Line Service</t>
         </is>
       </c>
       <c r="D933" t="inlineStr">
@@ -54778,7 +54778,7 @@
       <c r="B941" t="inlineStr"/>
       <c r="C941" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D941" t="inlineStr">
@@ -54940,7 +54940,7 @@
       <c r="B950" t="inlineStr"/>
       <c r="C950" t="inlineStr">
         <is>
-          <t>Additional Bathurst Service</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D950" t="inlineStr">
@@ -55210,7 +55210,7 @@
       <c r="B965" t="inlineStr"/>
       <c r="C965" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D965" t="inlineStr">
@@ -55228,7 +55228,7 @@
       <c r="B966" t="inlineStr"/>
       <c r="C966" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D966" t="inlineStr">
@@ -56038,7 +56038,7 @@
       <c r="B1011" t="inlineStr"/>
       <c r="C1011" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>N453</t>
         </is>
       </c>
       <c r="D1011" t="inlineStr">
@@ -56466,7 +56466,7 @@
       <c r="B1035" t="inlineStr"/>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>SSR Trip Train</t>
+          <t>AK Cars</t>
         </is>
       </c>
       <c r="D1035" t="inlineStr">
@@ -56880,7 +56880,7 @@
       <c r="B1058" t="inlineStr"/>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1058" t="inlineStr">
@@ -56952,7 +56952,7 @@
       <c r="B1062" t="inlineStr"/>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1062" t="inlineStr">
@@ -58106,7 +58106,7 @@
       <c r="B1127" t="inlineStr"/>
       <c r="C1127" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1127" t="inlineStr">
@@ -58160,7 +58160,7 @@
       <c r="B1130" t="inlineStr"/>
       <c r="C1130" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1130" t="inlineStr">
@@ -60272,7 +60272,7 @@
       <c r="B1248" t="inlineStr"/>
       <c r="C1248" t="inlineStr">
         <is>
-          <t>Qube Trip Train</t>
+          <t>QUBE Trip Train</t>
         </is>
       </c>
       <c r="D1248" t="inlineStr">
@@ -60380,7 +60380,7 @@
       <c r="B1254" t="inlineStr"/>
       <c r="C1254" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1254" t="inlineStr">
@@ -60416,7 +60416,7 @@
       <c r="B1256" t="inlineStr"/>
       <c r="C1256" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1256" t="inlineStr">
@@ -60808,7 +60808,7 @@
       <c r="B1278" t="inlineStr"/>
       <c r="C1278" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1278" t="inlineStr">
@@ -62634,7 +62634,7 @@
       <c r="B1381" t="inlineStr"/>
       <c r="C1381" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer to Sydney (connects with NP24)</t>
+          <t>NSW Trainlink Xplorer</t>
         </is>
       </c>
       <c r="D1381" t="inlineStr">
@@ -62724,7 +62724,7 @@
       <c r="B1386" t="inlineStr"/>
       <c r="C1386" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1386" t="inlineStr">
@@ -63954,7 +63954,7 @@
       <c r="B1455" t="inlineStr"/>
       <c r="C1455" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1455" t="inlineStr">
@@ -64314,7 +64314,7 @@
       <c r="B1475" t="inlineStr"/>
       <c r="C1475" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1475" t="inlineStr">
@@ -64404,7 +64404,7 @@
       <c r="B1480" t="inlineStr"/>
       <c r="C1480" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1480" t="inlineStr">
@@ -64548,7 +64548,7 @@
       <c r="B1488" t="inlineStr"/>
       <c r="C1488" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1488" t="inlineStr">
@@ -65099,7 +65099,7 @@
       <c r="B1519" t="inlineStr"/>
       <c r="C1519" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1519" t="inlineStr">
@@ -67077,7 +67077,7 @@
       <c r="B1630" t="inlineStr"/>
       <c r="C1630" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1630" t="inlineStr">
@@ -69013,7 +69013,7 @@
       <c r="B1738" t="inlineStr"/>
       <c r="C1738" t="inlineStr">
         <is>
-          <t>North East Line SG Service</t>
+          <t>North East SG Line Service</t>
         </is>
       </c>
       <c r="D1738" t="inlineStr">
@@ -70723,7 +70723,7 @@
       <c r="B1839" t="inlineStr"/>
       <c r="C1839" t="inlineStr">
         <is>
-          <t>SSR Containerised Freight</t>
+          <t>Fletchers Containerised Freight (Bank Engine)</t>
         </is>
       </c>
       <c r="D1839" t="inlineStr">
@@ -70935,7 +70935,7 @@
       <c r="B1851" t="inlineStr"/>
       <c r="C1851" t="inlineStr">
         <is>
-          <t>NSW Trainlink Passenger Service</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1851" t="inlineStr">
@@ -70971,7 +70971,7 @@
       <c r="B1853" t="inlineStr"/>
       <c r="C1853" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1853" t="inlineStr">
@@ -71291,7 +71291,7 @@
       <c r="B1871" t="inlineStr"/>
       <c r="C1871" t="inlineStr">
         <is>
-          <t>SSR Empty Manildra Flour</t>
+          <t>SSR - NSW TrainLink Transfer</t>
         </is>
       </c>
       <c r="D1871" t="inlineStr">
@@ -71669,7 +71669,7 @@
       <c r="B1892" t="inlineStr"/>
       <c r="C1892" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1892" t="inlineStr">
@@ -71903,7 +71903,7 @@
       <c r="B1905" t="inlineStr"/>
       <c r="C1905" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1905" t="inlineStr">
@@ -72119,7 +72119,7 @@
       <c r="B1917" t="inlineStr"/>
       <c r="C1917" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1917" t="inlineStr">
@@ -72155,7 +72155,7 @@
       <c r="B1919" t="inlineStr"/>
       <c r="C1919" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1919" t="inlineStr">
@@ -72299,7 +72299,7 @@
       <c r="B1927" t="inlineStr"/>
       <c r="C1927" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1927" t="inlineStr">
@@ -72371,7 +72371,7 @@
       <c r="B1931" t="inlineStr"/>
       <c r="C1931" t="inlineStr">
         <is>
-          <t>Lilydale Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1931" t="inlineStr">
@@ -72569,7 +72569,7 @@
       <c r="B1942" t="inlineStr"/>
       <c r="C1942" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1942" t="inlineStr">
@@ -72695,7 +72695,7 @@
       <c r="B1949" t="inlineStr"/>
       <c r="C1949" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1949" t="inlineStr">
@@ -72803,7 +72803,7 @@
       <c r="B1955" t="inlineStr"/>
       <c r="C1955" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1955" t="inlineStr">
@@ -72893,7 +72893,7 @@
       <c r="B1960" t="inlineStr"/>
       <c r="C1960" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1960" t="inlineStr">
@@ -73019,7 +73019,7 @@
       <c r="B1967" t="inlineStr"/>
       <c r="C1967" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1967" t="inlineStr">
@@ -73091,7 +73091,7 @@
       <c r="B1971" t="inlineStr"/>
       <c r="C1971" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1971" t="inlineStr">
@@ -73127,7 +73127,7 @@
       <c r="B1973" t="inlineStr"/>
       <c r="C1973" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1973" t="inlineStr">
@@ -73163,7 +73163,7 @@
       <c r="B1975" t="inlineStr"/>
       <c r="C1975" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1975" t="inlineStr">
@@ -74237,7 +74237,7 @@
       <c r="B2040" t="inlineStr"/>
       <c r="C2040" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Light Engine</t>
         </is>
       </c>
       <c r="D2040" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -850,7 +850,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2796,7 +2796,7 @@
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>North-East BG Service</t>
+          <t>NorthEast BG Line Service</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -2904,7 +2904,7 @@
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>North East SG Line Service</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -2958,7 +2958,7 @@
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>North East SG Line Service</t>
+          <t>North East Line SG Service</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -3454,7 +3454,7 @@
       <c r="B169" t="inlineStr"/>
       <c r="C169" t="inlineStr">
         <is>
-          <t>THNSW Tour / Transfer</t>
+          <t>THNSW Tour/Transfer</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -8518,7 +8518,7 @@
       <c r="B463" t="inlineStr"/>
       <c r="C463" t="inlineStr">
         <is>
-          <t>SCT Aurizon Loading Transfer</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -16071,7 +16071,7 @@
       <c r="B895" t="inlineStr"/>
       <c r="C895" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D895" t="inlineStr">
@@ -16089,7 +16089,7 @@
       <c r="B896" t="inlineStr"/>
       <c r="C896" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
@@ -17421,7 +17421,7 @@
       <c r="B970" t="inlineStr"/>
       <c r="C970" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D970" t="inlineStr">
@@ -18609,7 +18609,7 @@
       <c r="B1036" t="inlineStr"/>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1036" t="inlineStr">
@@ -19221,7 +19221,7 @@
       <c r="B1070" t="inlineStr"/>
       <c r="C1070" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1070" t="inlineStr">
@@ -19401,7 +19401,7 @@
       <c r="B1080" t="inlineStr"/>
       <c r="C1080" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1080" t="inlineStr">
@@ -19509,7 +19509,7 @@
       <c r="B1086" t="inlineStr"/>
       <c r="C1086" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1086" t="inlineStr">
@@ -20121,7 +20121,7 @@
       <c r="B1120" t="inlineStr"/>
       <c r="C1120" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1120" t="inlineStr">
@@ -20157,7 +20157,7 @@
       <c r="B1122" t="inlineStr"/>
       <c r="C1122" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1122" t="inlineStr">
@@ -20229,7 +20229,7 @@
       <c r="B1126" t="inlineStr"/>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1126" t="inlineStr">
@@ -20517,7 +20517,7 @@
       <c r="B1142" t="inlineStr"/>
       <c r="C1142" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1142" t="inlineStr">
@@ -21381,7 +21381,7 @@
       <c r="B1190" t="inlineStr"/>
       <c r="C1190" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1190" t="inlineStr">
@@ -22407,7 +22407,7 @@
       <c r="B1247" t="inlineStr"/>
       <c r="C1247" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1247" t="inlineStr">
@@ -22497,7 +22497,7 @@
       <c r="B1252" t="inlineStr"/>
       <c r="C1252" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1252" t="inlineStr">
@@ -22551,7 +22551,7 @@
       <c r="B1255" t="inlineStr"/>
       <c r="C1255" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1255" t="inlineStr">
@@ -22731,7 +22731,7 @@
       <c r="B1265" t="inlineStr"/>
       <c r="C1265" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1265" t="inlineStr">
@@ -23055,7 +23055,7 @@
       <c r="B1283" t="inlineStr"/>
       <c r="C1283" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1283" t="inlineStr">
@@ -23073,7 +23073,7 @@
       <c r="B1284" t="inlineStr"/>
       <c r="C1284" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1284" t="inlineStr">
@@ -23091,7 +23091,7 @@
       <c r="B1285" t="inlineStr"/>
       <c r="C1285" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1285" t="inlineStr">
@@ -23127,7 +23127,7 @@
       <c r="B1287" t="inlineStr"/>
       <c r="C1287" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1287" t="inlineStr">
@@ -23785,7 +23785,7 @@
       <c r="B1324" t="inlineStr"/>
       <c r="C1324" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>PN Wagon Transfer</t>
         </is>
       </c>
       <c r="D1324" t="inlineStr">
@@ -33639,7 +33639,7 @@
       <c r="B1887" t="inlineStr"/>
       <c r="C1887" t="inlineStr">
         <is>
-          <t>Gippsland Line Service</t>
+          <t>Traralgon - Melbourne Via Pakenham, Moe &amp; Morwell</t>
         </is>
       </c>
       <c r="D1887" t="inlineStr">
@@ -39352,7 +39352,7 @@
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -41610,7 +41610,7 @@
       <c r="B199" t="inlineStr"/>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -43076,7 +43076,7 @@
       <c r="B282" t="inlineStr"/>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -45052,7 +45052,7 @@
       <c r="B394" t="inlineStr"/>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -46568,7 +46568,7 @@
       <c r="B480" t="inlineStr"/>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
@@ -46942,7 +46942,7 @@
       <c r="B501" t="inlineStr"/>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
@@ -49396,7 +49396,7 @@
       <c r="B640" t="inlineStr"/>
       <c r="C640" t="inlineStr">
         <is>
-          <t>North-East BG Service</t>
+          <t>NorthEast BG Line Service</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
@@ -50476,7 +50476,7 @@
       <c r="B700" t="inlineStr"/>
       <c r="C700" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
@@ -58052,7 +58052,7 @@
       <c r="B1124" t="inlineStr"/>
       <c r="C1124" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1124" t="inlineStr">
@@ -58160,7 +58160,7 @@
       <c r="B1130" t="inlineStr"/>
       <c r="C1130" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1130" t="inlineStr">
@@ -59106,7 +59106,7 @@
       <c r="B1183" t="inlineStr"/>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>Gippsland Line Service</t>
+          <t>Traralgon - Melbourne Via Pakenham, Moe &amp; Morwell</t>
         </is>
       </c>
       <c r="D1183" t="inlineStr">
@@ -61486,7 +61486,7 @@
       <c r="B1317" t="inlineStr"/>
       <c r="C1317" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1317" t="inlineStr">
@@ -63616,7 +63616,7 @@
       <c r="B1436" t="inlineStr"/>
       <c r="C1436" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1436" t="inlineStr">
@@ -63936,7 +63936,7 @@
       <c r="B1454" t="inlineStr"/>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1454" t="inlineStr">
@@ -63990,7 +63990,7 @@
       <c r="B1457" t="inlineStr"/>
       <c r="C1457" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1457" t="inlineStr">
@@ -64224,7 +64224,7 @@
       <c r="B1470" t="inlineStr"/>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>THNSW Tour / Transfer</t>
+          <t>THNSW Tour/Transfer</t>
         </is>
       </c>
       <c r="D1470" t="inlineStr">
@@ -64530,7 +64530,7 @@
       <c r="B1487" t="inlineStr"/>
       <c r="C1487" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1487" t="inlineStr">
@@ -66653,7 +66653,7 @@
       <c r="B1606" t="inlineStr"/>
       <c r="C1606" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>North East SG Line Service</t>
         </is>
       </c>
       <c r="D1606" t="inlineStr">
@@ -67253,7 +67253,7 @@
       <c r="B1640" t="inlineStr"/>
       <c r="C1640" t="inlineStr">
         <is>
-          <t>SCT Aurizon Loading Transfer</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D1640" t="inlineStr">
@@ -67793,7 +67793,7 @@
       <c r="B1670" t="inlineStr"/>
       <c r="C1670" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1670" t="inlineStr">
@@ -69031,7 +69031,7 @@
       <c r="B1739" t="inlineStr"/>
       <c r="C1739" t="inlineStr">
         <is>
-          <t>North East SG Line Service</t>
+          <t>North East Line SG Service</t>
         </is>
       </c>
       <c r="D1739" t="inlineStr">
@@ -71651,7 +71651,7 @@
       <c r="B1891" t="inlineStr"/>
       <c r="C1891" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1891" t="inlineStr">
@@ -71813,7 +71813,7 @@
       <c r="B1900" t="inlineStr"/>
       <c r="C1900" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1900" t="inlineStr">
@@ -72119,7 +72119,7 @@
       <c r="B1917" t="inlineStr"/>
       <c r="C1917" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1917" t="inlineStr">
@@ -72875,7 +72875,7 @@
       <c r="B1959" t="inlineStr"/>
       <c r="C1959" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1959" t="inlineStr">
@@ -73145,7 +73145,7 @@
       <c r="B1974" t="inlineStr"/>
       <c r="C1974" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1974" t="inlineStr">
@@ -73163,7 +73163,7 @@
       <c r="B1975" t="inlineStr"/>
       <c r="C1975" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1975" t="inlineStr">
@@ -73501,7 +73501,7 @@
       <c r="B1994" t="inlineStr"/>
       <c r="C1994" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>PN Wagon Transfer</t>
         </is>
       </c>
       <c r="D1994" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -616,7 +616,7 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>V/Line Empty Car Transfer</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1706,7 +1706,7 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2796,7 +2796,7 @@
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>NorthEast BG Line Service</t>
+          <t>Northeast Line BG Service</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -8446,7 +8446,7 @@
       <c r="B459" t="inlineStr"/>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Copper</t>
+          <t>Aurizon Empty Copper</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -9960,7 +9960,7 @@
       <c r="B550" t="inlineStr"/>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Qube Trip Train</t>
+          <t>QUBE Loaded Containerised Ore</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
@@ -18177,7 +18177,7 @@
       <c r="B1012" t="inlineStr"/>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1012" t="inlineStr">
@@ -18681,7 +18681,7 @@
       <c r="B1040" t="inlineStr"/>
       <c r="C1040" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1040" t="inlineStr">
@@ -18699,7 +18699,7 @@
       <c r="B1041" t="inlineStr"/>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1041" t="inlineStr">
@@ -19239,7 +19239,7 @@
       <c r="B1071" t="inlineStr"/>
       <c r="C1071" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1071" t="inlineStr">
@@ -22029,7 +22029,7 @@
       <c r="B1226" t="inlineStr"/>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1226" t="inlineStr">
@@ -22479,7 +22479,7 @@
       <c r="B1251" t="inlineStr"/>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1251" t="inlineStr">
@@ -22875,7 +22875,7 @@
       <c r="B1273" t="inlineStr"/>
       <c r="C1273" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1273" t="inlineStr">
@@ -23019,7 +23019,7 @@
       <c r="B1281" t="inlineStr"/>
       <c r="C1281" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1281" t="inlineStr">
@@ -28299,7 +28299,7 @@
       <c r="B1587" t="inlineStr"/>
       <c r="C1587" t="inlineStr">
         <is>
-          <t>Bathurst Bullet - Transfer</t>
+          <t>Additional Bathurst Service</t>
         </is>
       </c>
       <c r="D1587" t="inlineStr">
@@ -39052,7 +39052,7 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -41924,7 +41924,7 @@
       <c r="B216" t="inlineStr"/>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -45054,7 +45054,7 @@
       <c r="B393" t="inlineStr"/>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Qube Trip Train</t>
+          <t>QUBE Loaded Containerised Ore</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -49452,7 +49452,7 @@
       <c r="B642" t="inlineStr"/>
       <c r="C642" t="inlineStr">
         <is>
-          <t>NorthEast BG Line Service</t>
+          <t>Northeast Line BG Service</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
@@ -59662,7 +59662,7 @@
       <c r="B1213" t="inlineStr"/>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1213" t="inlineStr">
@@ -60436,7 +60436,7 @@
       <c r="B1256" t="inlineStr"/>
       <c r="C1256" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1256" t="inlineStr">
@@ -63906,7 +63906,7 @@
       <c r="B1451" t="inlineStr"/>
       <c r="C1451" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1451" t="inlineStr">
@@ -67543,7 +67543,7 @@
       <c r="B1655" t="inlineStr"/>
       <c r="C1655" t="inlineStr">
         <is>
-          <t>Bathurst Bullet - Transfer</t>
+          <t>Additional Bathurst Service</t>
         </is>
       </c>
       <c r="D1655" t="inlineStr">
@@ -68727,7 +68727,7 @@
       <c r="B1721" t="inlineStr"/>
       <c r="C1721" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>V/Line Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1721" t="inlineStr">
@@ -70043,7 +70043,7 @@
       <c r="B1797" t="inlineStr"/>
       <c r="C1797" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Copper</t>
+          <t>Aurizon Empty Copper</t>
         </is>
       </c>
       <c r="D1797" t="inlineStr">
@@ -72751,7 +72751,7 @@
       <c r="B1951" t="inlineStr"/>
       <c r="C1951" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1951" t="inlineStr">
@@ -72967,7 +72967,7 @@
       <c r="B1963" t="inlineStr"/>
       <c r="C1963" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1963" t="inlineStr">
@@ -73147,7 +73147,7 @@
       <c r="B1973" t="inlineStr"/>
       <c r="C1973" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1973" t="inlineStr">
@@ -73183,7 +73183,7 @@
       <c r="B1975" t="inlineStr"/>
       <c r="C1975" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1975" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -2242,7 +2242,7 @@
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3684,7 +3684,7 @@
       <c r="B182" t="inlineStr"/>
       <c r="C182" t="inlineStr">
         <is>
-          <t>SRS Tour / Transfer</t>
+          <t>SRS/SCT Sadleirs Trip Train</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -4782,7 +4782,7 @@
       <c r="B247" t="inlineStr"/>
       <c r="C247" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN - Infrabuild Shunter</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -6058,7 +6058,7 @@
       <c r="B319" t="inlineStr"/>
       <c r="C319" t="inlineStr">
         <is>
-          <t>PN Grain Shuttle</t>
+          <t>PN Loaded Ore / Grain</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -9726,7 +9726,7 @@
       <c r="B537" t="inlineStr"/>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Cockburn Cement Empty Coal</t>
+          <t>Aurizon Grain via Hexham TSF</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
@@ -17889,7 +17889,7 @@
       <c r="B996" t="inlineStr"/>
       <c r="C996" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D996" t="inlineStr">
@@ -19527,7 +19527,7 @@
       <c r="B1087" t="inlineStr"/>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1087" t="inlineStr">
@@ -19545,7 +19545,7 @@
       <c r="B1088" t="inlineStr"/>
       <c r="C1088" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1088" t="inlineStr">
@@ -21813,7 +21813,7 @@
       <c r="B1214" t="inlineStr"/>
       <c r="C1214" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1214" t="inlineStr">
@@ -22659,7 +22659,7 @@
       <c r="B1261" t="inlineStr"/>
       <c r="C1261" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1261" t="inlineStr">
@@ -22929,7 +22929,7 @@
       <c r="B1276" t="inlineStr"/>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1276" t="inlineStr">
@@ -43870,7 +43870,7 @@
       <c r="B327" t="inlineStr"/>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -46380,7 +46380,7 @@
       <c r="B468" t="inlineStr"/>
       <c r="C468" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN - Infrabuild Shunter</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -46470,7 +46470,7 @@
       <c r="B473" t="inlineStr"/>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -47750,7 +47750,7 @@
       <c r="B545" t="inlineStr"/>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
@@ -52774,7 +52774,7 @@
       <c r="B827" t="inlineStr"/>
       <c r="C827" t="inlineStr">
         <is>
-          <t>PN Grain Shuttle</t>
+          <t>PN Loaded Ore / Grain</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
@@ -53928,7 +53928,7 @@
       <c r="B892" t="inlineStr"/>
       <c r="C892" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D892" t="inlineStr">
@@ -55266,7 +55266,7 @@
       <c r="B967" t="inlineStr"/>
       <c r="C967" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D967" t="inlineStr">
@@ -55572,7 +55572,7 @@
       <c r="B984" t="inlineStr"/>
       <c r="C984" t="inlineStr">
         <is>
-          <t>Cockburn Cement Empty Coal</t>
+          <t>Aurizon Grain via Hexham TSF</t>
         </is>
       </c>
       <c r="D984" t="inlineStr">
@@ -67079,7 +67079,7 @@
       <c r="B1629" t="inlineStr"/>
       <c r="C1629" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1629" t="inlineStr">
@@ -69155,7 +69155,7 @@
       <c r="B1745" t="inlineStr"/>
       <c r="C1745" t="inlineStr">
         <is>
-          <t>SRS Tour / Transfer</t>
+          <t>SRS/SCT Sadleirs Trip Train</t>
         </is>
       </c>
       <c r="D1745" t="inlineStr">
@@ -71959,7 +71959,7 @@
       <c r="B1907" t="inlineStr"/>
       <c r="C1907" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1907" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1228,7 +1228,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2908,7 +2908,7 @@
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>North East SG Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -3404,7 +3404,7 @@
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
-          <t>THNSW Tour / Transfer</t>
+          <t>THNSW Light Engine</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -9730,7 +9730,7 @@
       <c r="B537" t="inlineStr"/>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Aurizon Grain via Hexham TSF</t>
+          <t>Aurizon Empty Grain</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
@@ -10784,7 +10784,7 @@
       <c r="B596" t="inlineStr"/>
       <c r="C596" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (ex SP36)</t>
+          <t>NSW Trainlink Xplorer</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
@@ -10802,7 +10802,7 @@
       <c r="B597" t="inlineStr"/>
       <c r="C597" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer</t>
+          <t>NSW Trainlink Empty Car Transfer (ex NP24)</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
@@ -17084,7 +17084,7 @@
       <c r="B951" t="inlineStr"/>
       <c r="C951" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D951" t="inlineStr">
@@ -19064,7 +19064,7 @@
       <c r="B1061" t="inlineStr"/>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1061" t="inlineStr">
@@ -20432,7 +20432,7 @@
       <c r="B1137" t="inlineStr"/>
       <c r="C1137" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1137" t="inlineStr">
@@ -20594,7 +20594,7 @@
       <c r="B1146" t="inlineStr"/>
       <c r="C1146" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1146" t="inlineStr">
@@ -21242,7 +21242,7 @@
       <c r="B1182" t="inlineStr"/>
       <c r="C1182" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1182" t="inlineStr">
@@ -22412,7 +22412,7 @@
       <c r="B1247" t="inlineStr"/>
       <c r="C1247" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1247" t="inlineStr">
@@ -22556,7 +22556,7 @@
       <c r="B1255" t="inlineStr"/>
       <c r="C1255" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1255" t="inlineStr">
@@ -23078,7 +23078,7 @@
       <c r="B1284" t="inlineStr"/>
       <c r="C1284" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1284" t="inlineStr">
@@ -23132,7 +23132,7 @@
       <c r="B1287" t="inlineStr"/>
       <c r="C1287" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1287" t="inlineStr">
@@ -27450,7 +27450,7 @@
       <c r="B1538" t="inlineStr"/>
       <c r="C1538" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>V/Line Transfer</t>
         </is>
       </c>
       <c r="D1538" t="inlineStr">
@@ -28356,7 +28356,11 @@
         </is>
       </c>
       <c r="B1590" t="inlineStr"/>
-      <c r="C1590" t="inlineStr"/>
+      <c r="C1590" t="inlineStr">
+        <is>
+          <t>Southern Highlands Service</t>
+        </is>
+      </c>
       <c r="D1590" t="inlineStr">
         <is>
           <t>2026-04-03 21:22:22</t>
@@ -39985,7 +39989,7 @@
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>THNSW Tour / Transfer</t>
+          <t>THNSW Light Engine</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -49687,7 +49691,7 @@
       <c r="B652" t="inlineStr"/>
       <c r="C652" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
@@ -54709,7 +54713,7 @@
       <c r="B933" t="inlineStr"/>
       <c r="C933" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D933" t="inlineStr">
@@ -54745,7 +54749,7 @@
       <c r="B935" t="inlineStr"/>
       <c r="C935" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>V/Line Transfer</t>
         </is>
       </c>
       <c r="D935" t="inlineStr">
@@ -55681,7 +55685,7 @@
       <c r="B987" t="inlineStr"/>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Aurizon Grain via Hexham TSF</t>
+          <t>Aurizon Empty Grain</t>
         </is>
       </c>
       <c r="D987" t="inlineStr">
@@ -58325,7 +58329,7 @@
       <c r="B1135" t="inlineStr"/>
       <c r="C1135" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1135" t="inlineStr">
@@ -60419,7 +60423,7 @@
       <c r="B1252" t="inlineStr"/>
       <c r="C1252" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D1252" t="inlineStr">
@@ -60581,7 +60585,7 @@
       <c r="B1261" t="inlineStr"/>
       <c r="C1261" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1261" t="inlineStr">
@@ -62955,7 +62959,11 @@
         </is>
       </c>
       <c r="B1395" t="inlineStr"/>
-      <c r="C1395" t="inlineStr"/>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>Southern Highlands Service</t>
+        </is>
+      </c>
       <c r="D1395" t="inlineStr">
         <is>
           <t>2026-04-03 21:22:22</t>
@@ -64156,7 +64164,7 @@
       <c r="B1462" t="inlineStr"/>
       <c r="C1462" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1462" t="inlineStr">
@@ -64426,7 +64434,7 @@
       <c r="B1477" t="inlineStr"/>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer</t>
+          <t>NSW Trainlink Empty Car Transfer (ex NP24)</t>
         </is>
       </c>
       <c r="D1477" t="inlineStr">
@@ -66819,7 +66827,7 @@
       <c r="B1611" t="inlineStr"/>
       <c r="C1611" t="inlineStr">
         <is>
-          <t>North East SG Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1611" t="inlineStr">
@@ -68369,7 +68377,7 @@
       <c r="B1698" t="inlineStr"/>
       <c r="C1698" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1698" t="inlineStr">
@@ -70853,7 +70861,7 @@
       <c r="B1842" t="inlineStr"/>
       <c r="C1842" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (ex SP36)</t>
+          <t>NSW Trainlink Xplorer</t>
         </is>
       </c>
       <c r="D1842" t="inlineStr">
@@ -72249,7 +72257,7 @@
       <c r="B1920" t="inlineStr"/>
       <c r="C1920" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1920" t="inlineStr">
@@ -73041,7 +73049,7 @@
       <c r="B1964" t="inlineStr"/>
       <c r="C1964" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1964" t="inlineStr">
@@ -73329,7 +73337,7 @@
       <c r="B1980" t="inlineStr"/>
       <c r="C1980" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1980" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1494,7 +1494,7 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>North East Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2800,7 +2800,7 @@
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -2926,7 +2926,7 @@
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>NorthEast Special Movement</t>
+          <t>North East SG Line Service</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -8310,7 +8310,7 @@
       <c r="B451" t="inlineStr"/>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Aurizon Mineral Sands Shuttle</t>
+          <t>Aurizon Loaded Mineral Sands Shuttle</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -8432,7 +8432,7 @@
       <c r="B458" t="inlineStr"/>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Aurizon Intermodal</t>
+          <t>Aurizon Wagon Transfer</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -10662,7 +10662,7 @@
       <c r="B589" t="inlineStr"/>
       <c r="C589" t="inlineStr">
         <is>
-          <t>SCT Intermodal</t>
+          <t>SCT Light Engine</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
@@ -12388,7 +12388,7 @@
       <c r="B687" t="inlineStr"/>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
@@ -16094,7 +16094,7 @@
       <c r="B896" t="inlineStr"/>
       <c r="C896" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
@@ -16220,7 +16220,7 @@
       <c r="B903" t="inlineStr"/>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
@@ -16580,7 +16580,7 @@
       <c r="B923" t="inlineStr"/>
       <c r="C923" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D923" t="inlineStr">
@@ -18452,7 +18452,7 @@
       <c r="B1027" t="inlineStr"/>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1027" t="inlineStr">
@@ -19226,7 +19226,7 @@
       <c r="B1070" t="inlineStr"/>
       <c r="C1070" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1070" t="inlineStr">
@@ -20126,7 +20126,7 @@
       <c r="B1120" t="inlineStr"/>
       <c r="C1120" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1120" t="inlineStr">
@@ -21512,7 +21512,7 @@
       <c r="B1197" t="inlineStr"/>
       <c r="C1197" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1197" t="inlineStr">
@@ -22304,7 +22304,7 @@
       <c r="B1241" t="inlineStr"/>
       <c r="C1241" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1241" t="inlineStr">
@@ -22430,7 +22430,7 @@
       <c r="B1248" t="inlineStr"/>
       <c r="C1248" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1248" t="inlineStr">
@@ -22484,7 +22484,7 @@
       <c r="B1251" t="inlineStr"/>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1251" t="inlineStr">
@@ -22592,7 +22592,7 @@
       <c r="B1257" t="inlineStr"/>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1257" t="inlineStr">
@@ -22754,7 +22754,7 @@
       <c r="B1266" t="inlineStr"/>
       <c r="C1266" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1266" t="inlineStr">
@@ -23060,7 +23060,7 @@
       <c r="B1283" t="inlineStr"/>
       <c r="C1283" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1283" t="inlineStr">
@@ -23096,7 +23096,7 @@
       <c r="B1285" t="inlineStr"/>
       <c r="C1285" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1285" t="inlineStr">
@@ -25928,7 +25928,7 @@
       <c r="B1449" t="inlineStr"/>
       <c r="C1449" t="inlineStr">
         <is>
-          <t>Watco Light Engine</t>
+          <t>Watco Trip Train</t>
         </is>
       </c>
       <c r="D1449" t="inlineStr">
@@ -28304,7 +28304,7 @@
       <c r="B1587" t="inlineStr"/>
       <c r="C1587" t="inlineStr">
         <is>
-          <t>Additional Bathurst Service</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D1587" t="inlineStr">
@@ -40233,7 +40233,7 @@
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Watco Light Engine</t>
+          <t>Watco Trip Train</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -46773,7 +46773,7 @@
       <c r="B487" t="inlineStr"/>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
@@ -46971,7 +46971,7 @@
       <c r="B498" t="inlineStr"/>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
@@ -49565,7 +49565,7 @@
       <c r="B645" t="inlineStr"/>
       <c r="C645" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
@@ -54803,7 +54803,7 @@
       <c r="B938" t="inlineStr"/>
       <c r="C938" t="inlineStr">
         <is>
-          <t>North East Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D938" t="inlineStr">
@@ -55163,7 +55163,7 @@
       <c r="B958" t="inlineStr"/>
       <c r="C958" t="inlineStr">
         <is>
-          <t>Aurizon Mineral Sands Shuttle</t>
+          <t>Aurizon Loaded Mineral Sands Shuttle</t>
         </is>
       </c>
       <c r="D958" t="inlineStr">
@@ -57969,7 +57969,7 @@
       <c r="B1115" t="inlineStr"/>
       <c r="C1115" t="inlineStr">
         <is>
-          <t>Aurizon Intermodal</t>
+          <t>Aurizon Wagon Transfer</t>
         </is>
       </c>
       <c r="D1115" t="inlineStr">
@@ -58221,7 +58221,7 @@
       <c r="B1129" t="inlineStr"/>
       <c r="C1129" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1129" t="inlineStr">
@@ -61469,7 +61469,7 @@
       <c r="B1311" t="inlineStr"/>
       <c r="C1311" t="inlineStr">
         <is>
-          <t>NorthEast Special Movement</t>
+          <t>North East SG Line Service</t>
         </is>
       </c>
       <c r="D1311" t="inlineStr">
@@ -61655,7 +61655,7 @@
       <c r="B1322" t="inlineStr"/>
       <c r="C1322" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D1322" t="inlineStr">
@@ -63790,7 +63790,7 @@
       <c r="B1441" t="inlineStr"/>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1441" t="inlineStr">
@@ -64542,7 +64542,7 @@
       <c r="B1483" t="inlineStr"/>
       <c r="C1483" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Werribee Line</t>
         </is>
       </c>
       <c r="D1483" t="inlineStr">
@@ -64722,7 +64722,7 @@
       <c r="B1493" t="inlineStr"/>
       <c r="C1493" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Belgrave Line</t>
         </is>
       </c>
       <c r="D1493" t="inlineStr">
@@ -67661,7 +67661,7 @@
       <c r="B1658" t="inlineStr"/>
       <c r="C1658" t="inlineStr">
         <is>
-          <t>Additional Bathurst Service</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D1658" t="inlineStr">
@@ -70825,7 +70825,7 @@
       <c r="B1840" t="inlineStr"/>
       <c r="C1840" t="inlineStr">
         <is>
-          <t>SCT Intermodal</t>
+          <t>SCT Light Engine</t>
         </is>
       </c>
       <c r="D1840" t="inlineStr">
@@ -71109,7 +71109,7 @@
       <c r="B1856" t="inlineStr"/>
       <c r="C1856" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1856" t="inlineStr">
@@ -71915,7 +71915,7 @@
       <c r="B1901" t="inlineStr"/>
       <c r="C1901" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1901" t="inlineStr">
@@ -71987,7 +71987,7 @@
       <c r="B1905" t="inlineStr"/>
       <c r="C1905" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1905" t="inlineStr">
@@ -73013,7 +73013,7 @@
       <c r="B1962" t="inlineStr"/>
       <c r="C1962" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1962" t="inlineStr">
@@ -73067,7 +73067,7 @@
       <c r="B1965" t="inlineStr"/>
       <c r="C1965" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1965" t="inlineStr">
@@ -73085,7 +73085,7 @@
       <c r="B1966" t="inlineStr"/>
       <c r="C1966" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1966" t="inlineStr">
@@ -73103,7 +73103,7 @@
       <c r="B1967" t="inlineStr"/>
       <c r="C1967" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1967" t="inlineStr">
@@ -73319,7 +73319,7 @@
       <c r="B1979" t="inlineStr"/>
       <c r="C1979" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1979" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1706,7 +1706,7 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8360,7 +8360,7 @@
       <c r="B454" t="inlineStr"/>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Aurizon Intermodal</t>
+          <t>Aurizon Wagon Transfer</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -16310,7 +16310,7 @@
       <c r="B908" t="inlineStr"/>
       <c r="C908" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D908" t="inlineStr">
@@ -16436,7 +16436,7 @@
       <c r="B915" t="inlineStr"/>
       <c r="C915" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D915" t="inlineStr">
@@ -17894,7 +17894,7 @@
       <c r="B996" t="inlineStr"/>
       <c r="C996" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D996" t="inlineStr">
@@ -18560,7 +18560,7 @@
       <c r="B1033" t="inlineStr"/>
       <c r="C1033" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1033" t="inlineStr">
@@ -18614,7 +18614,7 @@
       <c r="B1036" t="inlineStr"/>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1036" t="inlineStr">
@@ -19244,7 +19244,7 @@
       <c r="B1071" t="inlineStr"/>
       <c r="C1071" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1071" t="inlineStr">
@@ -19514,7 +19514,7 @@
       <c r="B1086" t="inlineStr"/>
       <c r="C1086" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1086" t="inlineStr">
@@ -19766,7 +19766,7 @@
       <c r="B1100" t="inlineStr"/>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1100" t="inlineStr">
@@ -22034,7 +22034,7 @@
       <c r="B1226" t="inlineStr"/>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1226" t="inlineStr">
@@ -22142,7 +22142,7 @@
       <c r="B1232" t="inlineStr"/>
       <c r="C1232" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1232" t="inlineStr">
@@ -22682,7 +22682,7 @@
       <c r="B1262" t="inlineStr"/>
       <c r="C1262" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1262" t="inlineStr">
@@ -22808,7 +22808,7 @@
       <c r="B1269" t="inlineStr"/>
       <c r="C1269" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1269" t="inlineStr">
@@ -22880,7 +22880,7 @@
       <c r="B1273" t="inlineStr"/>
       <c r="C1273" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1273" t="inlineStr">
@@ -23006,7 +23006,7 @@
       <c r="B1280" t="inlineStr"/>
       <c r="C1280" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1280" t="inlineStr">
@@ -23042,7 +23042,7 @@
       <c r="B1282" t="inlineStr"/>
       <c r="C1282" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1282" t="inlineStr">
@@ -39413,7 +39413,7 @@
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -42037,7 +42037,7 @@
       <c r="B219" t="inlineStr"/>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -43983,7 +43983,7 @@
       <c r="B330" t="inlineStr"/>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -46737,7 +46737,7 @@
       <c r="B485" t="inlineStr"/>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -50105,7 +50105,7 @@
       <c r="B675" t="inlineStr"/>
       <c r="C675" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
@@ -51365,7 +51365,7 @@
       <c r="B745" t="inlineStr"/>
       <c r="C745" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
@@ -62893,7 +62893,7 @@
       <c r="B1391" t="inlineStr"/>
       <c r="C1391" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1391" t="inlineStr">
@@ -64024,7 +64024,7 @@
       <c r="B1454" t="inlineStr"/>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D1454" t="inlineStr">
@@ -64146,7 +64146,7 @@
       <c r="B1461" t="inlineStr"/>
       <c r="C1461" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1461" t="inlineStr">
@@ -65273,7 +65273,7 @@
       <c r="B1524" t="inlineStr"/>
       <c r="C1524" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1524" t="inlineStr">
@@ -66115,7 +66115,7 @@
       <c r="B1571" t="inlineStr"/>
       <c r="C1571" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Sandringham Line</t>
         </is>
       </c>
       <c r="D1571" t="inlineStr">
@@ -70125,7 +70125,7 @@
       <c r="B1798" t="inlineStr"/>
       <c r="C1798" t="inlineStr">
         <is>
-          <t>Aurizon Intermodal</t>
+          <t>Aurizon Wagon Transfer</t>
         </is>
       </c>
       <c r="D1798" t="inlineStr">
@@ -71825,7 +71825,7 @@
       <c r="B1896" t="inlineStr"/>
       <c r="C1896" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1896" t="inlineStr">
@@ -72869,7 +72869,7 @@
       <c r="B1954" t="inlineStr"/>
       <c r="C1954" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1954" t="inlineStr">
@@ -72905,7 +72905,7 @@
       <c r="B1956" t="inlineStr"/>
       <c r="C1956" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1956" t="inlineStr">
@@ -73193,7 +73193,7 @@
       <c r="B1972" t="inlineStr"/>
       <c r="C1972" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1972" t="inlineStr">
@@ -73265,7 +73265,7 @@
       <c r="B1976" t="inlineStr"/>
       <c r="C1976" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1976" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1954,7 +1954,7 @@
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>V/Line Football Special via Werribee</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2062,7 +2062,7 @@
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2350,7 +2350,7 @@
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2836,7 +2836,7 @@
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>North Eastern Line BG Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -5652,7 +5652,7 @@
       <c r="B296" t="inlineStr"/>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Empty Coal</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -8432,7 +8432,7 @@
       <c r="B458" t="inlineStr"/>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Aurizon Wagon Transfer</t>
+          <t>Aurizon Intermodal</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -15716,7 +15716,7 @@
       <c r="B875" t="inlineStr"/>
       <c r="C875" t="inlineStr">
         <is>
-          <t>SSR Empty Manildra Flour</t>
+          <t>Swift Trip Train</t>
         </is>
       </c>
       <c r="D875" t="inlineStr">
@@ -16076,7 +16076,7 @@
       <c r="B895" t="inlineStr"/>
       <c r="C895" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D895" t="inlineStr">
@@ -17426,7 +17426,7 @@
       <c r="B970" t="inlineStr"/>
       <c r="C970" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D970" t="inlineStr">
@@ -17552,7 +17552,7 @@
       <c r="B977" t="inlineStr"/>
       <c r="C977" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D977" t="inlineStr">
@@ -18506,7 +18506,7 @@
       <c r="B1030" t="inlineStr"/>
       <c r="C1030" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1030" t="inlineStr">
@@ -18668,7 +18668,7 @@
       <c r="B1039" t="inlineStr"/>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1039" t="inlineStr">
@@ -18722,7 +18722,7 @@
       <c r="B1042" t="inlineStr"/>
       <c r="C1042" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1042" t="inlineStr">
@@ -19532,7 +19532,7 @@
       <c r="B1087" t="inlineStr"/>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1087" t="inlineStr">
@@ -19568,7 +19568,7 @@
       <c r="B1089" t="inlineStr"/>
       <c r="C1089" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D1089" t="inlineStr">
@@ -20018,7 +20018,7 @@
       <c r="B1114" t="inlineStr"/>
       <c r="C1114" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1114" t="inlineStr">
@@ -20594,7 +20594,7 @@
       <c r="B1146" t="inlineStr"/>
       <c r="C1146" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1146" t="inlineStr">
@@ -20630,7 +20630,7 @@
       <c r="B1148" t="inlineStr"/>
       <c r="C1148" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1148" t="inlineStr">
@@ -21386,7 +21386,7 @@
       <c r="B1190" t="inlineStr"/>
       <c r="C1190" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1190" t="inlineStr">
@@ -21746,7 +21746,7 @@
       <c r="B1210" t="inlineStr"/>
       <c r="C1210" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1210" t="inlineStr">
@@ -21764,7 +21764,7 @@
       <c r="B1211" t="inlineStr"/>
       <c r="C1211" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1211" t="inlineStr">
@@ -21818,7 +21818,7 @@
       <c r="B1214" t="inlineStr"/>
       <c r="C1214" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1214" t="inlineStr">
@@ -21980,7 +21980,7 @@
       <c r="B1223" t="inlineStr"/>
       <c r="C1223" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1223" t="inlineStr">
@@ -21998,7 +21998,7 @@
       <c r="B1224" t="inlineStr"/>
       <c r="C1224" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1224" t="inlineStr">
@@ -22232,7 +22232,7 @@
       <c r="B1237" t="inlineStr"/>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1237" t="inlineStr">
@@ -22394,7 +22394,7 @@
       <c r="B1246" t="inlineStr"/>
       <c r="C1246" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1246" t="inlineStr">
@@ -22502,7 +22502,7 @@
       <c r="B1252" t="inlineStr"/>
       <c r="C1252" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1252" t="inlineStr">
@@ -22664,7 +22664,7 @@
       <c r="B1261" t="inlineStr"/>
       <c r="C1261" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1261" t="inlineStr">
@@ -22736,7 +22736,7 @@
       <c r="B1265" t="inlineStr"/>
       <c r="C1265" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1265" t="inlineStr">
@@ -22826,7 +22826,7 @@
       <c r="B1270" t="inlineStr"/>
       <c r="C1270" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1270" t="inlineStr">
@@ -22934,7 +22934,7 @@
       <c r="B1276" t="inlineStr"/>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1276" t="inlineStr">
@@ -22952,7 +22952,7 @@
       <c r="B1277" t="inlineStr"/>
       <c r="C1277" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1277" t="inlineStr">
@@ -23024,7 +23024,7 @@
       <c r="B1281" t="inlineStr"/>
       <c r="C1281" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1281" t="inlineStr">
@@ -23060,7 +23060,7 @@
       <c r="B1283" t="inlineStr"/>
       <c r="C1283" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1283" t="inlineStr">
@@ -23790,7 +23790,7 @@
       <c r="B1324" t="inlineStr"/>
       <c r="C1324" t="inlineStr">
         <is>
-          <t>PN Wagon Transfer</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D1324" t="inlineStr">
@@ -28286,7 +28286,7 @@
       <c r="B1586" t="inlineStr"/>
       <c r="C1586" t="inlineStr">
         <is>
-          <t>Bathurst Bullet - Transfer</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D1586" t="inlineStr">
@@ -37470,7 +37470,7 @@
       <c r="B2100" t="inlineStr"/>
       <c r="C2100" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (Forms ST21)</t>
         </is>
       </c>
       <c r="D2100" t="inlineStr">
@@ -40197,7 +40197,7 @@
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (Forms ST21)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -41779,7 +41779,7 @@
       <c r="B204" t="inlineStr"/>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -43245,7 +43245,7 @@
       <c r="B287" t="inlineStr"/>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -43263,7 +43263,7 @@
       <c r="B288" t="inlineStr"/>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Sandringham Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -43371,7 +43371,7 @@
       <c r="B294" t="inlineStr"/>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Williamstown Line</t>
+          <t>Frankston Line</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -47111,7 +47111,7 @@
       <c r="B506" t="inlineStr"/>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
@@ -47255,7 +47255,7 @@
       <c r="B514" t="inlineStr"/>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
@@ -47827,7 +47827,7 @@
       <c r="B546" t="inlineStr"/>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
@@ -47863,7 +47863,7 @@
       <c r="B548" t="inlineStr"/>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
@@ -49115,7 +49115,7 @@
       <c r="B620" t="inlineStr"/>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Hurstbridge Line</t>
+          <t>Mernda Line</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
@@ -50645,7 +50645,7 @@
       <c r="B705" t="inlineStr"/>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
@@ -54041,7 +54041,7 @@
       <c r="B895" t="inlineStr"/>
       <c r="C895" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D895" t="inlineStr">
@@ -55379,7 +55379,7 @@
       <c r="B970" t="inlineStr"/>
       <c r="C970" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D970" t="inlineStr">
@@ -57103,7 +57103,7 @@
       <c r="B1066" t="inlineStr"/>
       <c r="C1066" t="inlineStr">
         <is>
-          <t>Belgrave Line</t>
+          <t>Lilydale Line</t>
         </is>
       </c>
       <c r="D1066" t="inlineStr">
@@ -57793,7 +57793,7 @@
       <c r="B1105" t="inlineStr"/>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1105" t="inlineStr">
@@ -57969,7 +57969,7 @@
       <c r="B1115" t="inlineStr"/>
       <c r="C1115" t="inlineStr">
         <is>
-          <t>Aurizon Wagon Transfer</t>
+          <t>Aurizon Intermodal</t>
         </is>
       </c>
       <c r="D1115" t="inlineStr">
@@ -60653,7 +60653,7 @@
       <c r="B1265" t="inlineStr"/>
       <c r="C1265" t="inlineStr">
         <is>
-          <t>Bathurst Bullet - Transfer</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D1265" t="inlineStr">
@@ -64042,7 +64042,7 @@
       <c r="B1455" t="inlineStr"/>
       <c r="C1455" t="inlineStr">
         <is>
-          <t>Empty Coal</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D1455" t="inlineStr">
@@ -64128,7 +64128,7 @@
       <c r="B1460" t="inlineStr"/>
       <c r="C1460" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1460" t="inlineStr">
@@ -64704,7 +64704,7 @@
       <c r="B1492" t="inlineStr"/>
       <c r="C1492" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1492" t="inlineStr">
@@ -66791,7 +66791,7 @@
       <c r="B1609" t="inlineStr"/>
       <c r="C1609" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>V/Line Football Special via Werribee</t>
         </is>
       </c>
       <c r="D1609" t="inlineStr">
@@ -66809,7 +66809,7 @@
       <c r="B1610" t="inlineStr"/>
       <c r="C1610" t="inlineStr">
         <is>
-          <t>North Eastern Line BG Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D1610" t="inlineStr">
@@ -67841,7 +67841,7 @@
       <c r="B1668" t="inlineStr"/>
       <c r="C1668" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1668" t="inlineStr">
@@ -68377,7 +68377,7 @@
       <c r="B1698" t="inlineStr"/>
       <c r="C1698" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1698" t="inlineStr">
@@ -71501,7 +71501,7 @@
       <c r="B1878" t="inlineStr"/>
       <c r="C1878" t="inlineStr">
         <is>
-          <t>SSR Empty Manildra Flour</t>
+          <t>Swift Trip Train</t>
         </is>
       </c>
       <c r="D1878" t="inlineStr">
@@ -71843,7 +71843,7 @@
       <c r="B1897" t="inlineStr"/>
       <c r="C1897" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1897" t="inlineStr">
@@ -71861,7 +71861,7 @@
       <c r="B1898" t="inlineStr"/>
       <c r="C1898" t="inlineStr">
         <is>
-          <t>Frankston Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1898" t="inlineStr">
@@ -72077,7 +72077,7 @@
       <c r="B1910" t="inlineStr"/>
       <c r="C1910" t="inlineStr">
         <is>
-          <t>Upfield Line</t>
+          <t>Craigieburn Line</t>
         </is>
       </c>
       <c r="D1910" t="inlineStr">
@@ -72167,7 +72167,7 @@
       <c r="B1915" t="inlineStr"/>
       <c r="C1915" t="inlineStr">
         <is>
-          <t>Werribee Line</t>
+          <t>Williamstown Line</t>
         </is>
       </c>
       <c r="D1915" t="inlineStr">
@@ -72365,7 +72365,7 @@
       <c r="B1926" t="inlineStr"/>
       <c r="C1926" t="inlineStr">
         <is>
-          <t>Craigieburn Line</t>
+          <t>Upfield Line</t>
         </is>
       </c>
       <c r="D1926" t="inlineStr">
@@ -72743,7 +72743,7 @@
       <c r="B1947" t="inlineStr"/>
       <c r="C1947" t="inlineStr">
         <is>
-          <t>Mernda Line</t>
+          <t>Hurstbridge Line</t>
         </is>
       </c>
       <c r="D1947" t="inlineStr">
@@ -72833,7 +72833,7 @@
       <c r="B1952" t="inlineStr"/>
       <c r="C1952" t="inlineStr">
         <is>
-          <t>Cranbourne Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1952" t="inlineStr">
@@ -72977,7 +72977,7 @@
       <c r="B1960" t="inlineStr"/>
       <c r="C1960" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1960" t="inlineStr">
@@ -73211,7 +73211,7 @@
       <c r="B1973" t="inlineStr"/>
       <c r="C1973" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Pakenham Line</t>
         </is>
       </c>
       <c r="D1973" t="inlineStr">
@@ -73301,7 +73301,7 @@
       <c r="B1978" t="inlineStr"/>
       <c r="C1978" t="inlineStr">
         <is>
-          <t>Pakenham Line</t>
+          <t>Sunbury Line</t>
         </is>
       </c>
       <c r="D1978" t="inlineStr">
@@ -73319,7 +73319,7 @@
       <c r="B1979" t="inlineStr"/>
       <c r="C1979" t="inlineStr">
         <is>
-          <t>Sunbury Line</t>
+          <t>Cranbourne Line</t>
         </is>
       </c>
       <c r="D1979" t="inlineStr">
@@ -73675,7 +73675,7 @@
       <c r="B1999" t="inlineStr"/>
       <c r="C1999" t="inlineStr">
         <is>
-          <t>PN Wagon Transfer</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D1999" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -2494,7 +2494,7 @@
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -2836,7 +2836,7 @@
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3734,7 +3734,7 @@
       <c r="B185" t="inlineStr"/>
       <c r="C185" t="inlineStr">
         <is>
-          <t>SSR Cement</t>
+          <t>SSR Cement Trip Train</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -12388,7 +12388,7 @@
       <c r="B687" t="inlineStr"/>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
@@ -12496,7 +12496,7 @@
       <c r="B693" t="inlineStr"/>
       <c r="C693" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
@@ -13430,7 +13430,7 @@
       <c r="B748" t="inlineStr"/>
       <c r="C748" t="inlineStr">
         <is>
-          <t>SSR Loaded Manildra Flour</t>
+          <t>Swift Trip Train</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
@@ -16816,7 +16816,7 @@
       <c r="B945" t="inlineStr"/>
       <c r="C945" t="inlineStr">
         <is>
-          <t>QUBE Grain</t>
+          <t>QUBE Light Engine</t>
         </is>
       </c>
       <c r="D945" t="inlineStr">
@@ -27998,7 +27998,7 @@
       <c r="B1574" t="inlineStr"/>
       <c r="C1574" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (ex NT32)</t>
         </is>
       </c>
       <c r="D1574" t="inlineStr">
@@ -33733,7 +33733,7 @@
       <c r="B294" t="inlineStr"/>
       <c r="C294" t="inlineStr">
         <is>
-          <t>QUBE Grain</t>
+          <t>QUBE Light Engine</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -46139,7 +46139,7 @@
       <c r="B993" t="inlineStr"/>
       <c r="C993" t="inlineStr">
         <is>
-          <t>SSR Cement</t>
+          <t>SSR Cement Trip Train</t>
         </is>
       </c>
       <c r="D993" t="inlineStr">
@@ -49745,7 +49745,7 @@
       <c r="B1195" t="inlineStr"/>
       <c r="C1195" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D1195" t="inlineStr">
@@ -49799,7 +49799,7 @@
       <c r="B1198" t="inlineStr"/>
       <c r="C1198" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1198" t="inlineStr">
@@ -50507,7 +50507,7 @@
       <c r="B1238" t="inlineStr"/>
       <c r="C1238" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1238" t="inlineStr">
@@ -53937,7 +53937,7 @@
       <c r="B1435" t="inlineStr"/>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1435" t="inlineStr">
@@ -54131,7 +54131,7 @@
       <c r="B1446" t="inlineStr"/>
       <c r="C1446" t="inlineStr">
         <is>
-          <t>SSR Loaded Manildra Flour</t>
+          <t>Swift Trip Train</t>
         </is>
       </c>
       <c r="D1446" t="inlineStr">
@@ -56321,7 +56321,7 @@
       <c r="B1573" t="inlineStr"/>
       <c r="C1573" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (ex NT32)</t>
         </is>
       </c>
       <c r="D1573" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1228,7 +1228,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>North East Line BG Service</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1332,7 +1332,7 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>V1149</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1458,7 +1458,7 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>SouthWest Line Service</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2008,7 +2008,7 @@
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12334,7 +12334,7 @@
       <c r="B684" t="inlineStr"/>
       <c r="C684" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
@@ -36317,7 +36317,7 @@
       <c r="B442" t="inlineStr"/>
       <c r="C442" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>SouthWest Line Service</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -42841,7 +42841,7 @@
       <c r="B808" t="inlineStr"/>
       <c r="C808" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D808" t="inlineStr">
@@ -44403,7 +44403,7 @@
       <c r="B895" t="inlineStr"/>
       <c r="C895" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>North East Line BG Service</t>
         </is>
       </c>
       <c r="D895" t="inlineStr">
@@ -49349,7 +49349,7 @@
       <c r="B1173" t="inlineStr"/>
       <c r="C1173" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>V1149</t>
         </is>
       </c>
       <c r="D1173" t="inlineStr">
@@ -51065,7 +51065,7 @@
       <c r="B1269" t="inlineStr"/>
       <c r="C1269" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1269" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -12514,7 +12514,7 @@
       <c r="B694" t="inlineStr"/>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
@@ -51101,7 +51101,7 @@
       <c r="B1271" t="inlineStr"/>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1271" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -742,7 +742,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>North Eastern Line BG Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1084,7 +1084,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2890,7 +2890,7 @@
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>North East Line SG Service</t>
+          <t>North East SG Line Service</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -46513,7 +46513,7 @@
       <c r="B1014" t="inlineStr"/>
       <c r="C1014" t="inlineStr">
         <is>
-          <t>North East Line SG Service</t>
+          <t>North East SG Line Service</t>
         </is>
       </c>
       <c r="D1014" t="inlineStr">
@@ -46833,7 +46833,7 @@
       <c r="B1032" t="inlineStr"/>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>North Eastern Line BG Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1032" t="inlineStr">
@@ -51853,7 +51853,7 @@
       <c r="B1313" t="inlineStr"/>
       <c r="C1313" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D1313" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -2872,7 +2872,7 @@
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>North East SG Line Service</t>
+          <t>V/Line SG Special</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7158,7 +7158,7 @@
       <c r="B381" t="inlineStr"/>
       <c r="C381" t="inlineStr">
         <is>
-          <t>PN Port Waratah Shunter</t>
+          <t>PN Coal</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -8012,7 +8012,7 @@
       <c r="B432" t="inlineStr"/>
       <c r="C432" t="inlineStr">
         <is>
-          <t>SSR Light Engine</t>
+          <t>SSR BG Grain</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -12370,7 +12370,7 @@
       <c r="B686" t="inlineStr"/>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Hunter Railcar Transfer</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
@@ -12568,7 +12568,7 @@
       <c r="B697" t="inlineStr"/>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
@@ -13036,7 +13036,7 @@
       <c r="B725" t="inlineStr"/>
       <c r="C725" t="inlineStr">
         <is>
-          <t>South Coast Service</t>
+          <t>South Coast Empty Car Transfer</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
@@ -28016,7 +28016,7 @@
       <c r="B1575" t="inlineStr"/>
       <c r="C1575" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (ex WT28)</t>
         </is>
       </c>
       <c r="D1575" t="inlineStr">
@@ -35961,7 +35961,7 @@
       <c r="B422" t="inlineStr"/>
       <c r="C422" t="inlineStr">
         <is>
-          <t>SSR Light Engine</t>
+          <t>SSR BG Grain</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -49493,7 +49493,7 @@
       <c r="B1181" t="inlineStr"/>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>South Coast Service</t>
+          <t>South Coast Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1181" t="inlineStr">
@@ -51137,7 +51137,7 @@
       <c r="B1273" t="inlineStr"/>
       <c r="C1273" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1273" t="inlineStr">
@@ -52015,7 +52015,7 @@
       <c r="B1322" t="inlineStr"/>
       <c r="C1322" t="inlineStr">
         <is>
-          <t>North East SG Line Service</t>
+          <t>V/Line SG Special</t>
         </is>
       </c>
       <c r="D1322" t="inlineStr">
@@ -52647,7 +52647,7 @@
       <c r="B1358" t="inlineStr"/>
       <c r="C1358" t="inlineStr">
         <is>
-          <t>PN Port Waratah Shunter</t>
+          <t>PN Coal</t>
         </is>
       </c>
       <c r="D1358" t="inlineStr">
@@ -53919,7 +53919,7 @@
       <c r="B1434" t="inlineStr"/>
       <c r="C1434" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Hunter Railcar Transfer</t>
         </is>
       </c>
       <c r="D1434" t="inlineStr">
@@ -56339,7 +56339,7 @@
       <c r="B1574" t="inlineStr"/>
       <c r="C1574" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (ex WT28)</t>
         </is>
       </c>
       <c r="D1574" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -3120,7 +3120,7 @@
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>QUBE Containerised Freight</t>
+          <t>QUBE Trip Train</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -10072,7 +10072,7 @@
       <c r="B556" t="inlineStr"/>
       <c r="C556" t="inlineStr">
         <is>
-          <t>SCT Shuttle</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
@@ -16816,7 +16816,7 @@
       <c r="B945" t="inlineStr"/>
       <c r="C945" t="inlineStr">
         <is>
-          <t>QUBE Light Engine</t>
+          <t>QUBE BlueScope Steel</t>
         </is>
       </c>
       <c r="D945" t="inlineStr">
@@ -18728,7 +18728,7 @@
       <c r="B1055" t="inlineStr"/>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1055" t="inlineStr">
@@ -29995,7 +29995,7 @@
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>QUBE Containerised Freight</t>
+          <t>QUBE Trip Train</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -33733,7 +33733,7 @@
       <c r="B294" t="inlineStr"/>
       <c r="C294" t="inlineStr">
         <is>
-          <t>QUBE Light Engine</t>
+          <t>QUBE BlueScope Steel</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -51295,7 +51295,7 @@
       <c r="B1282" t="inlineStr"/>
       <c r="C1282" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1282" t="inlineStr">
@@ -53527,7 +53527,7 @@
       <c r="B1412" t="inlineStr"/>
       <c r="C1412" t="inlineStr">
         <is>
-          <t>SCT Shuttle</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D1412" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -2854,7 +2854,7 @@
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -5886,7 +5886,7 @@
       <c r="B309" t="inlineStr"/>
       <c r="C309" t="inlineStr">
         <is>
-          <t>PN Coal</t>
+          <t>PN Coal (invalid Train No.) - Dendrobium Mine</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -8712,7 +8712,7 @@
       <c r="B474" t="inlineStr"/>
       <c r="C474" t="inlineStr">
         <is>
-          <t>MRL Loaded Iron Ore</t>
+          <t>MRL Empty Iron Ore</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
@@ -10270,7 +10270,7 @@
       <c r="B567" t="inlineStr"/>
       <c r="C567" t="inlineStr">
         <is>
-          <t>SSR Light Engine Movement</t>
+          <t>SSR Light Engine</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
@@ -11376,7 +11376,7 @@
       <c r="B629" t="inlineStr"/>
       <c r="C629" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>G523</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
@@ -18392,7 +18392,7 @@
       <c r="B1035" t="inlineStr"/>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>SSR Aggregates Wagon Transfer</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1035" t="inlineStr">
@@ -31923,7 +31923,7 @@
       <c r="B191" t="inlineStr"/>
       <c r="C191" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>G523</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -36713,7 +36713,7 @@
       <c r="B464" t="inlineStr"/>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -39695,7 +39695,7 @@
       <c r="B631" t="inlineStr"/>
       <c r="C631" t="inlineStr">
         <is>
-          <t>SSR Light Engine Movement</t>
+          <t>SSR Light Engine</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
@@ -39935,7 +39935,7 @@
       <c r="B645" t="inlineStr"/>
       <c r="C645" t="inlineStr">
         <is>
-          <t>MRL Loaded Iron Ore</t>
+          <t>MRL Empty Iron Ore</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
@@ -47283,7 +47283,7 @@
       <c r="B1057" t="inlineStr"/>
       <c r="C1057" t="inlineStr">
         <is>
-          <t>PN Coal</t>
+          <t>PN Coal (invalid Train No.) - Dendrobium Mine</t>
         </is>
       </c>
       <c r="D1057" t="inlineStr">
@@ -48407,7 +48407,7 @@
       <c r="B1120" t="inlineStr"/>
       <c r="C1120" t="inlineStr">
         <is>
-          <t>SSR Aggregates Wagon Transfer</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1120" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -5688,7 +5688,7 @@
       <c r="B298" t="inlineStr"/>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Maintenance Train</t>
+          <t>PN Trip Train</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -9572,7 +9572,7 @@
       <c r="B528" t="inlineStr"/>
       <c r="C528" t="inlineStr">
         <is>
-          <t>SSR Limestone</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
@@ -9784,7 +9784,7 @@
       <c r="B540" t="inlineStr"/>
       <c r="C540" t="inlineStr">
         <is>
-          <t>SSR - NSW TrainLink Transfer</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
@@ -14942,7 +14942,7 @@
       <c r="B834" t="inlineStr"/>
       <c r="C834" t="inlineStr">
         <is>
-          <t>NR61</t>
+          <t>Maintenance Train</t>
         </is>
       </c>
       <c r="D834" t="inlineStr">
@@ -17496,7 +17496,7 @@
       <c r="B983" t="inlineStr"/>
       <c r="C983" t="inlineStr">
         <is>
-          <t>QUBE Containerised Freight</t>
+          <t>QUBE Trip Train</t>
         </is>
       </c>
       <c r="D983" t="inlineStr">
@@ -36065,7 +36065,7 @@
       <c r="B428" t="inlineStr"/>
       <c r="C428" t="inlineStr">
         <is>
-          <t>QUBE Containerised Freight</t>
+          <t>QUBE Trip Train</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -49403,7 +49403,7 @@
       <c r="B1176" t="inlineStr"/>
       <c r="C1176" t="inlineStr">
         <is>
-          <t>Maintenance Train</t>
+          <t>PN Trip Train</t>
         </is>
       </c>
       <c r="D1176" t="inlineStr">
@@ -53365,7 +53365,7 @@
       <c r="B1403" t="inlineStr"/>
       <c r="C1403" t="inlineStr">
         <is>
-          <t>SSR Limestone</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1403" t="inlineStr">
@@ -53473,7 +53473,7 @@
       <c r="B1409" t="inlineStr"/>
       <c r="C1409" t="inlineStr">
         <is>
-          <t>SSR - NSW TrainLink Transfer</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1409" t="inlineStr">
@@ -54451,7 +54451,7 @@
       <c r="B1464" t="inlineStr"/>
       <c r="C1464" t="inlineStr">
         <is>
-          <t>NR61</t>
+          <t>Maintenance Train</t>
         </is>
       </c>
       <c r="D1464" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -9712,7 +9712,7 @@
       <c r="B536" t="inlineStr"/>
       <c r="C536" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
@@ -53419,7 +53419,7 @@
       <c r="B1406" t="inlineStr"/>
       <c r="C1406" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1406" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -5688,7 +5688,7 @@
       <c r="B298" t="inlineStr"/>
       <c r="C298" t="inlineStr">
         <is>
-          <t>PN Trip Train</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -12770,7 +12770,7 @@
       <c r="B710" t="inlineStr"/>
       <c r="C710" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Coal</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
@@ -16942,7 +16942,7 @@
       <c r="B952" t="inlineStr"/>
       <c r="C952" t="inlineStr">
         <is>
-          <t>QUBE BlueScope Steel</t>
+          <t>QUBE BlueScope Steel Shunt</t>
         </is>
       </c>
       <c r="D952" t="inlineStr">
@@ -16996,7 +16996,7 @@
       <c r="B955" t="inlineStr"/>
       <c r="C955" t="inlineStr">
         <is>
-          <t>QUBE Trip Train</t>
+          <t>QUBE Light Engine</t>
         </is>
       </c>
       <c r="D955" t="inlineStr">
@@ -17122,7 +17122,7 @@
       <c r="B962" t="inlineStr"/>
       <c r="C962" t="inlineStr">
         <is>
-          <t>QUBE BlueScope Steel</t>
+          <t>QUBE BlueScope Steel Shunt</t>
         </is>
       </c>
       <c r="D962" t="inlineStr">
@@ -30929,7 +30929,7 @@
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>QUBE BlueScope Steel</t>
+          <t>QUBE BlueScope Steel Shunt</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -35011,7 +35011,7 @@
       <c r="B367" t="inlineStr"/>
       <c r="C367" t="inlineStr">
         <is>
-          <t>QUBE Trip Train</t>
+          <t>QUBE Light Engine</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -35667,7 +35667,7 @@
       <c r="B405" t="inlineStr"/>
       <c r="C405" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Coal</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -38109,7 +38109,7 @@
       <c r="B542" t="inlineStr"/>
       <c r="C542" t="inlineStr">
         <is>
-          <t>QUBE BlueScope Steel</t>
+          <t>QUBE BlueScope Steel Shunt</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
@@ -49403,7 +49403,7 @@
       <c r="B1176" t="inlineStr"/>
       <c r="C1176" t="inlineStr">
         <is>
-          <t>PN Trip Train</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D1176" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -12352,7 +12352,7 @@
       <c r="B685" t="inlineStr"/>
       <c r="C685" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
@@ -12424,7 +12424,7 @@
       <c r="B689" t="inlineStr"/>
       <c r="C689" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
@@ -12514,7 +12514,7 @@
       <c r="B694" t="inlineStr"/>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
@@ -18782,7 +18782,7 @@
       <c r="B1058" t="inlineStr"/>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>South Coast Service</t>
+          <t>South Coast Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1058" t="inlineStr">
@@ -48641,7 +48641,7 @@
       <c r="B1133" t="inlineStr"/>
       <c r="C1133" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1133" t="inlineStr">
@@ -50489,7 +50489,7 @@
       <c r="B1237" t="inlineStr"/>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1237" t="inlineStr">
@@ -51101,7 +51101,7 @@
       <c r="B1271" t="inlineStr"/>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1271" t="inlineStr">
@@ -55331,7 +55331,7 @@
       <c r="B1518" t="inlineStr"/>
       <c r="C1518" t="inlineStr">
         <is>
-          <t>South Coast Service</t>
+          <t>South Coast Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1518" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -5224,7 +5224,7 @@
       <c r="B272" t="inlineStr"/>
       <c r="C272" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Grain Shuttle</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -5472,7 +5472,7 @@
       <c r="B286" t="inlineStr"/>
       <c r="C286" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Limestone</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -5688,7 +5688,7 @@
       <c r="B298" t="inlineStr"/>
       <c r="C298" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Trip Train</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -9446,7 +9446,7 @@
       <c r="B521" t="inlineStr"/>
       <c r="C521" t="inlineStr">
         <is>
-          <t>SSR Containerised Freight</t>
+          <t>SSR Freight Shuttle</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
@@ -12550,7 +12550,7 @@
       <c r="B696" t="inlineStr"/>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
@@ -15496,7 +15496,7 @@
       <c r="B865" t="inlineStr"/>
       <c r="C865" t="inlineStr">
         <is>
-          <t>PN Loaded Fuel Service</t>
+          <t>PN Fuel Train</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
@@ -16852,7 +16852,7 @@
       <c r="B947" t="inlineStr"/>
       <c r="C947" t="inlineStr">
         <is>
-          <t>QUBE Light Engine</t>
+          <t>QUBE Light Engine Movement</t>
         </is>
       </c>
       <c r="D947" t="inlineStr">
@@ -18782,7 +18782,7 @@
       <c r="B1058" t="inlineStr"/>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>South Coast Empty Car Transfer</t>
+          <t>NSW Trainlink South Coast Service</t>
         </is>
       </c>
       <c r="D1058" t="inlineStr">
@@ -33683,7 +33683,7 @@
       <c r="B291" t="inlineStr"/>
       <c r="C291" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Grain Shuttle</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -34343,7 +34343,7 @@
       <c r="B329" t="inlineStr"/>
       <c r="C329" t="inlineStr">
         <is>
-          <t>SSR Containerised Freight</t>
+          <t>SSR Freight Shuttle</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -39141,7 +39141,7 @@
       <c r="B600" t="inlineStr"/>
       <c r="C600" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Limestone</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
@@ -49403,7 +49403,7 @@
       <c r="B1176" t="inlineStr"/>
       <c r="C1176" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Trip Train</t>
         </is>
       </c>
       <c r="D1176" t="inlineStr">
@@ -53991,7 +53991,7 @@
       <c r="B1438" t="inlineStr"/>
       <c r="C1438" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1438" t="inlineStr">
@@ -55031,7 +55031,7 @@
       <c r="B1500" t="inlineStr"/>
       <c r="C1500" t="inlineStr">
         <is>
-          <t>QUBE Light Engine</t>
+          <t>QUBE Light Engine Movement</t>
         </is>
       </c>
       <c r="D1500" t="inlineStr">
@@ -55331,7 +55331,7 @@
       <c r="B1518" t="inlineStr"/>
       <c r="C1518" t="inlineStr">
         <is>
-          <t>South Coast Empty Car Transfer</t>
+          <t>NSW Trainlink South Coast Service</t>
         </is>
       </c>
       <c r="D1518" t="inlineStr">
@@ -56623,7 +56623,7 @@
       <c r="B1590" t="inlineStr"/>
       <c r="C1590" t="inlineStr">
         <is>
-          <t>PN Loaded Fuel Service</t>
+          <t>PN Fuel Train</t>
         </is>
       </c>
       <c r="D1590" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -2602,7 +2602,7 @@
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Wyndham Vale</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6548,7 +6548,7 @@
       <c r="B346" t="inlineStr"/>
       <c r="C346" t="inlineStr">
         <is>
-          <t>PN Grain</t>
+          <t>PN Grain Shuttle</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -12220,7 +12220,7 @@
       <c r="B677" t="inlineStr"/>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Aurizon Empty Ore</t>
+          <t>Aurizon Loaded Ore</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
@@ -12514,7 +12514,7 @@
       <c r="B694" t="inlineStr"/>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
@@ -12914,7 +12914,7 @@
       <c r="B718" t="inlineStr"/>
       <c r="C718" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>Empty Car Provisioning (Forms SN34)</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
@@ -13036,7 +13036,7 @@
       <c r="B725" t="inlineStr"/>
       <c r="C725" t="inlineStr">
         <is>
-          <t>South Coast Empty Car Transfer</t>
+          <t>South Coast Service</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
@@ -18710,7 +18710,7 @@
       <c r="B1054" t="inlineStr"/>
       <c r="C1054" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1054" t="inlineStr">
@@ -38577,7 +38577,7 @@
       <c r="B568" t="inlineStr"/>
       <c r="C568" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Wyndham Vale</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
@@ -42507,7 +42507,7 @@
       <c r="B789" t="inlineStr"/>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Aurizon Empty Ore</t>
+          <t>Aurizon Loaded Ore</t>
         </is>
       </c>
       <c r="D789" t="inlineStr">
@@ -43723,7 +43723,7 @@
       <c r="B857" t="inlineStr"/>
       <c r="C857" t="inlineStr">
         <is>
-          <t>PN Grain</t>
+          <t>PN Grain Shuttle</t>
         </is>
       </c>
       <c r="D857" t="inlineStr">
@@ -49493,7 +49493,7 @@
       <c r="B1181" t="inlineStr"/>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>South Coast Empty Car Transfer</t>
+          <t>South Coast Service</t>
         </is>
       </c>
       <c r="D1181" t="inlineStr">
@@ -50525,7 +50525,7 @@
       <c r="B1239" t="inlineStr"/>
       <c r="C1239" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>Empty Car Provisioning (Forms SN34)</t>
         </is>
       </c>
       <c r="D1239" t="inlineStr">
@@ -50597,7 +50597,7 @@
       <c r="B1243" t="inlineStr"/>
       <c r="C1243" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1243" t="inlineStr">
@@ -51101,7 +51101,7 @@
       <c r="B1271" t="inlineStr"/>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1271" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -526,7 +526,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1616,7 +1616,7 @@
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4058,7 +4058,7 @@
       <c r="B205" t="inlineStr"/>
       <c r="C205" t="inlineStr">
         <is>
-          <t>AZ Coal</t>
+          <t>AZ COal</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -10288,7 +10288,7 @@
       <c r="B568" t="inlineStr"/>
       <c r="C568" t="inlineStr">
         <is>
-          <t>CLP12</t>
+          <t>SSR Grain</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
@@ -12334,7 +12334,7 @@
       <c r="B684" t="inlineStr"/>
       <c r="C684" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
@@ -12352,7 +12352,7 @@
       <c r="B685" t="inlineStr"/>
       <c r="C685" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
@@ -12442,7 +12442,7 @@
       <c r="B690" t="inlineStr"/>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
@@ -16334,7 +16334,7 @@
       <c r="B916" t="inlineStr"/>
       <c r="C916" t="inlineStr">
         <is>
-          <t>Watco Trip Train</t>
+          <t>Watco Light Engine</t>
         </is>
       </c>
       <c r="D916" t="inlineStr">
@@ -16852,7 +16852,7 @@
       <c r="B947" t="inlineStr"/>
       <c r="C947" t="inlineStr">
         <is>
-          <t>QUBE Light Engine Movement</t>
+          <t>QUBE BlueScope Steel</t>
         </is>
       </c>
       <c r="D947" t="inlineStr">
@@ -18392,7 +18392,7 @@
       <c r="B1035" t="inlineStr"/>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1035" t="inlineStr">
@@ -18782,7 +18782,7 @@
       <c r="B1058" t="inlineStr"/>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>NSW Trainlink South Coast Service</t>
+          <t>South Coast Service</t>
         </is>
       </c>
       <c r="D1058" t="inlineStr">
@@ -27944,7 +27944,7 @@
       <c r="B1571" t="inlineStr"/>
       <c r="C1571" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink Empty XPT (Forms NT33)</t>
         </is>
       </c>
       <c r="D1571" t="inlineStr">
@@ -30117,7 +30117,7 @@
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Watco Trip Train</t>
+          <t>Watco Light Engine</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -34379,7 +34379,7 @@
       <c r="B331" t="inlineStr"/>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -39677,7 +39677,7 @@
       <c r="B630" t="inlineStr"/>
       <c r="C630" t="inlineStr">
         <is>
-          <t>CLP12</t>
+          <t>SSR Grain</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
@@ -48126,7 +48126,7 @@
       <c r="B1104" t="inlineStr"/>
       <c r="C1104" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink Empty XPT (Forms NT33)</t>
         </is>
       </c>
       <c r="D1104" t="inlineStr">
@@ -48407,7 +48407,7 @@
       <c r="B1120" t="inlineStr"/>
       <c r="C1120" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1120" t="inlineStr">
@@ -48641,7 +48641,7 @@
       <c r="B1133" t="inlineStr"/>
       <c r="C1133" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1133" t="inlineStr">
@@ -51065,7 +51065,7 @@
       <c r="B1269" t="inlineStr"/>
       <c r="C1269" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1269" t="inlineStr">
@@ -51907,7 +51907,7 @@
       <c r="B1316" t="inlineStr"/>
       <c r="C1316" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1316" t="inlineStr">
@@ -52251,7 +52251,7 @@
       <c r="B1336" t="inlineStr"/>
       <c r="C1336" t="inlineStr">
         <is>
-          <t>AZ Coal</t>
+          <t>AZ COal</t>
         </is>
       </c>
       <c r="D1336" t="inlineStr">
@@ -53955,7 +53955,7 @@
       <c r="B1436" t="inlineStr"/>
       <c r="C1436" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1436" t="inlineStr">
@@ -55031,7 +55031,7 @@
       <c r="B1500" t="inlineStr"/>
       <c r="C1500" t="inlineStr">
         <is>
-          <t>QUBE Light Engine Movement</t>
+          <t>QUBE BlueScope Steel</t>
         </is>
       </c>
       <c r="D1500" t="inlineStr">
@@ -55331,7 +55331,7 @@
       <c r="B1518" t="inlineStr"/>
       <c r="C1518" t="inlineStr">
         <is>
-          <t>NSW Trainlink South Coast Service</t>
+          <t>South Coast Service</t>
         </is>
       </c>
       <c r="D1518" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -634,7 +634,7 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1084,7 +1084,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1246,7 +1246,7 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1314,7 +1314,7 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1332,7 +1332,7 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>V1149</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1368,7 +1368,7 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>South Western Line diverted via Werribee</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1954,7 +1954,7 @@
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>V/Line Football Special via Werribee</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2278,7 +2278,7 @@
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning (forms 8103)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2764,7 +2764,7 @@
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -2872,7 +2872,7 @@
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>V/Line SG Special</t>
+          <t>NorthEast Special Movement</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -9784,7 +9784,7 @@
       <c r="B540" t="inlineStr"/>
       <c r="C540" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
@@ -12968,7 +12968,7 @@
       <c r="B721" t="inlineStr"/>
       <c r="C721" t="inlineStr">
         <is>
-          <t>Bathurst Bullet - Transfer</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
@@ -13376,7 +13376,7 @@
       <c r="B745" t="inlineStr"/>
       <c r="C745" t="inlineStr">
         <is>
-          <t>SSR Manildra Grain Banker</t>
+          <t>SSR Loaded Manildra Grain</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
@@ -14642,7 +14642,7 @@
       <c r="B816" t="inlineStr"/>
       <c r="C816" t="inlineStr">
         <is>
-          <t>NR39</t>
+          <t>PN Shunter</t>
         </is>
       </c>
       <c r="D816" t="inlineStr">
@@ -17122,7 +17122,7 @@
       <c r="B962" t="inlineStr"/>
       <c r="C962" t="inlineStr">
         <is>
-          <t>QUBE BlueScope Steel Shunt</t>
+          <t>QUBE BlueScope Steel</t>
         </is>
       </c>
       <c r="D962" t="inlineStr">
@@ -17514,7 +17514,7 @@
       <c r="B984" t="inlineStr"/>
       <c r="C984" t="inlineStr">
         <is>
-          <t>SSR Grain</t>
+          <t>SSR D Set Transfer / Grain Shuttle</t>
         </is>
       </c>
       <c r="D984" t="inlineStr">
@@ -18620,7 +18620,7 @@
       <c r="B1049" t="inlineStr"/>
       <c r="C1049" t="inlineStr">
         <is>
-          <t>Sydney Trains Empty Car Transfer</t>
+          <t>Southern Highlands Service</t>
         </is>
       </c>
       <c r="D1049" t="inlineStr">
@@ -18692,7 +18692,7 @@
       <c r="B1053" t="inlineStr"/>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1053" t="inlineStr">
@@ -18818,7 +18818,7 @@
       <c r="B1060" t="inlineStr"/>
       <c r="C1060" t="inlineStr">
         <is>
-          <t>South Coast Empty Car Transfer</t>
+          <t>Southern Highlands Service</t>
         </is>
       </c>
       <c r="D1060" t="inlineStr">
@@ -30929,7 +30929,7 @@
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>QUBE BlueScope Steel Shunt</t>
+          <t>QUBE BlueScope Steel</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -36677,7 +36677,7 @@
       <c r="B462" t="inlineStr"/>
       <c r="C462" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>South Western Line diverted via Werribee</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -38253,7 +38253,7 @@
       <c r="B550" t="inlineStr"/>
       <c r="C550" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
@@ -40223,7 +40223,7 @@
       <c r="B661" t="inlineStr"/>
       <c r="C661" t="inlineStr">
         <is>
-          <t>Bathurst Bullet - Transfer</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
@@ -43669,7 +43669,7 @@
       <c r="B854" t="inlineStr"/>
       <c r="C854" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
@@ -44579,7 +44579,7 @@
       <c r="B905" t="inlineStr"/>
       <c r="C905" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D905" t="inlineStr">
@@ -44859,7 +44859,7 @@
       <c r="B921" t="inlineStr"/>
       <c r="C921" t="inlineStr">
         <is>
-          <t>NR39</t>
+          <t>PN Shunter</t>
         </is>
       </c>
       <c r="D921" t="inlineStr">
@@ -45761,7 +45761,7 @@
       <c r="B972" t="inlineStr"/>
       <c r="C972" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D972" t="inlineStr">
@@ -49349,7 +49349,7 @@
       <c r="B1173" t="inlineStr"/>
       <c r="C1173" t="inlineStr">
         <is>
-          <t>V1149</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1173" t="inlineStr">
@@ -49781,7 +49781,7 @@
       <c r="B1197" t="inlineStr"/>
       <c r="C1197" t="inlineStr">
         <is>
-          <t>V/Line Football Special via Werribee</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D1197" t="inlineStr">
@@ -50223,7 +50223,7 @@
       <c r="B1222" t="inlineStr"/>
       <c r="C1222" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1222" t="inlineStr">
@@ -50615,7 +50615,7 @@
       <c r="B1244" t="inlineStr"/>
       <c r="C1244" t="inlineStr">
         <is>
-          <t>South Coast Empty Car Transfer</t>
+          <t>Southern Highlands Service</t>
         </is>
       </c>
       <c r="D1244" t="inlineStr">
@@ -51223,7 +51223,7 @@
       <c r="B1278" t="inlineStr"/>
       <c r="C1278" t="inlineStr">
         <is>
-          <t>SSR Grain</t>
+          <t>SSR D Set Transfer / Grain Shuttle</t>
         </is>
       </c>
       <c r="D1278" t="inlineStr">
@@ -51277,7 +51277,7 @@
       <c r="B1281" t="inlineStr"/>
       <c r="C1281" t="inlineStr">
         <is>
-          <t>Sydney Trains Empty Car Transfer</t>
+          <t>Southern Highlands Service</t>
         </is>
       </c>
       <c r="D1281" t="inlineStr">
@@ -51709,7 +51709,7 @@
       <c r="B1305" t="inlineStr"/>
       <c r="C1305" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning (forms 8103)</t>
         </is>
       </c>
       <c r="D1305" t="inlineStr">
@@ -51853,7 +51853,7 @@
       <c r="B1313" t="inlineStr"/>
       <c r="C1313" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D1313" t="inlineStr">
@@ -52015,7 +52015,7 @@
       <c r="B1322" t="inlineStr"/>
       <c r="C1322" t="inlineStr">
         <is>
-          <t>V/Line SG Special</t>
+          <t>NorthEast Special Movement</t>
         </is>
       </c>
       <c r="D1322" t="inlineStr">
@@ -53473,7 +53473,7 @@
       <c r="B1409" t="inlineStr"/>
       <c r="C1409" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1409" t="inlineStr">
@@ -54113,7 +54113,7 @@
       <c r="B1445" t="inlineStr"/>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>SSR Manildra Grain Banker</t>
+          <t>SSR Loaded Manildra Grain</t>
         </is>
       </c>
       <c r="D1445" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -616,7 +616,7 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>V/Line Empty Car Transfer</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1084,7 +1084,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Northeast Line BG Service</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1314,7 +1314,7 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1634,7 +1634,7 @@
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1864,7 +1864,7 @@
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -1882,7 +1882,7 @@
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>V/Line empty cars</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -1918,7 +1918,7 @@
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2062,7 +2062,7 @@
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2206,7 +2206,7 @@
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2602,7 +2602,7 @@
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3418,7 +3418,7 @@
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="inlineStr">
         <is>
-          <t>THNSW Light Engine</t>
+          <t>THNSW Tour / Transfer</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -9514,7 +9514,7 @@
       <c r="B525" t="inlineStr"/>
       <c r="C525" t="inlineStr">
         <is>
-          <t>SSR Containerised Freight</t>
+          <t>SSR Manildra Grain Shuttle</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
@@ -9960,7 +9960,7 @@
       <c r="B550" t="inlineStr"/>
       <c r="C550" t="inlineStr">
         <is>
-          <t>QUBE Trip Train</t>
+          <t>QUBE Light Engine</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
@@ -10998,7 +10998,7 @@
       <c r="B608" t="inlineStr"/>
       <c r="C608" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer</t>
+          <t>NSW Trainlink Xplorer to Sydney (connects with NP24)</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
@@ -12456,7 +12456,7 @@
       <c r="B691" t="inlineStr"/>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
@@ -13616,7 +13616,7 @@
       <c r="B759" t="inlineStr"/>
       <c r="C759" t="inlineStr">
         <is>
-          <t>SSR Light Engine</t>
+          <t>SSR Grain</t>
         </is>
       </c>
       <c r="D759" t="inlineStr">
@@ -13886,7 +13886,7 @@
       <c r="B774" t="inlineStr"/>
       <c r="C774" t="inlineStr">
         <is>
-          <t>N460</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D774" t="inlineStr">
@@ -18724,7 +18724,7 @@
       <c r="B1055" t="inlineStr"/>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>Bathurst Bullet - Transfer</t>
+          <t>Additional Bathurst Service</t>
         </is>
       </c>
       <c r="D1055" t="inlineStr">
@@ -27854,7 +27854,7 @@
       <c r="B1566" t="inlineStr"/>
       <c r="C1566" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (ex NT34)</t>
         </is>
       </c>
       <c r="D1566" t="inlineStr">
@@ -28012,7 +28012,7 @@
       <c r="B1575" t="inlineStr"/>
       <c r="C1575" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (ex NT32)</t>
+          <t>NSW TrainLink XPT</t>
         </is>
       </c>
       <c r="D1575" t="inlineStr">
@@ -28030,7 +28030,7 @@
       <c r="B1576" t="inlineStr"/>
       <c r="C1576" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (ex WT28)</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1576" t="inlineStr">
@@ -30019,7 +30019,7 @@
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>THNSW Light Engine</t>
+          <t>THNSW Tour / Transfer</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -32555,7 +32555,7 @@
       <c r="B227" t="inlineStr"/>
       <c r="C227" t="inlineStr">
         <is>
-          <t>SSR Light Engine</t>
+          <t>SSR Grain</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -33361,7 +33361,7 @@
       <c r="B272" t="inlineStr"/>
       <c r="C272" t="inlineStr">
         <is>
-          <t>QUBE Trip Train</t>
+          <t>QUBE Light Engine</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -33703,7 +33703,7 @@
       <c r="B291" t="inlineStr"/>
       <c r="C291" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -36211,7 +36211,7 @@
       <c r="B435" t="inlineStr"/>
       <c r="C435" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -38633,7 +38633,7 @@
       <c r="B570" t="inlineStr"/>
       <c r="C570" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
@@ -38813,7 +38813,7 @@
       <c r="B580" t="inlineStr"/>
       <c r="C580" t="inlineStr">
         <is>
-          <t>N460</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
@@ -39539,7 +39539,7 @@
       <c r="B621" t="inlineStr"/>
       <c r="C621" t="inlineStr">
         <is>
-          <t>V/Line empty cars</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
@@ -42879,7 +42879,7 @@
       <c r="B809" t="inlineStr"/>
       <c r="C809" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D809" t="inlineStr">
@@ -45443,7 +45443,7 @@
       <c r="B953" t="inlineStr"/>
       <c r="C953" t="inlineStr">
         <is>
-          <t>SSR Containerised Freight</t>
+          <t>SSR Manildra Grain Shuttle</t>
         </is>
       </c>
       <c r="D953" t="inlineStr">
@@ -45817,7 +45817,7 @@
       <c r="B974" t="inlineStr"/>
       <c r="C974" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D974" t="inlineStr">
@@ -47700,7 +47700,7 @@
       <c r="B1079" t="inlineStr"/>
       <c r="C1079" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer</t>
+          <t>NSW Trainlink Xplorer to Sydney (connects with NP24)</t>
         </is>
       </c>
       <c r="D1079" t="inlineStr">
@@ -49351,7 +49351,7 @@
       <c r="B1172" t="inlineStr"/>
       <c r="C1172" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (ex NT34)</t>
         </is>
       </c>
       <c r="D1172" t="inlineStr">
@@ -50653,7 +50653,7 @@
       <c r="B1245" t="inlineStr"/>
       <c r="C1245" t="inlineStr">
         <is>
-          <t>Bathurst Bullet - Transfer</t>
+          <t>Additional Bathurst Service</t>
         </is>
       </c>
       <c r="D1245" t="inlineStr">
@@ -50833,7 +50833,7 @@
       <c r="B1255" t="inlineStr"/>
       <c r="C1255" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1255" t="inlineStr">
@@ -51729,7 +51729,7 @@
       <c r="B1305" t="inlineStr"/>
       <c r="C1305" t="inlineStr">
         <is>
-          <t>V/Line Empty Car Transfer</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1305" t="inlineStr">
@@ -51909,7 +51909,7 @@
       <c r="B1315" t="inlineStr"/>
       <c r="C1315" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Northeast Line BG Service</t>
         </is>
       </c>
       <c r="D1315" t="inlineStr">
@@ -52017,7 +52017,7 @@
       <c r="B1321" t="inlineStr"/>
       <c r="C1321" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1321" t="inlineStr">
@@ -54011,7 +54011,7 @@
       <c r="B1438" t="inlineStr"/>
       <c r="C1438" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1438" t="inlineStr">
@@ -56377,7 +56377,7 @@
       <c r="B1575" t="inlineStr"/>
       <c r="C1575" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (ex NT32)</t>
+          <t>NSW TrainLink XPT</t>
         </is>
       </c>
       <c r="D1575" t="inlineStr">
@@ -56395,7 +56395,7 @@
       <c r="B1576" t="inlineStr"/>
       <c r="C1576" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (ex WT28)</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1576" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -958,7 +958,7 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>V1227</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1012,7 +1012,7 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1138,7 +1138,7 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1332,7 +1332,7 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1368,7 +1368,7 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>South Western Line diverted via Werribee</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1476,7 +1476,7 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1494,7 +1494,7 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2008,7 +2008,7 @@
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2062,7 +2062,7 @@
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2206,7 +2206,7 @@
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2620,7 +2620,7 @@
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>North Eastern BG Line Service</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -12348,7 +12348,7 @@
       <c r="B685" t="inlineStr"/>
       <c r="C685" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
@@ -12582,7 +12582,7 @@
       <c r="B698" t="inlineStr"/>
       <c r="C698" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
@@ -12928,7 +12928,7 @@
       <c r="B719" t="inlineStr"/>
       <c r="C719" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning (Forms SN34)</t>
+          <t>Southern Highlands Service</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
@@ -15114,7 +15114,7 @@
       <c r="B844" t="inlineStr"/>
       <c r="C844" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>PN Parkes Logistics Terminal Local Shunter</t>
         </is>
       </c>
       <c r="D844" t="inlineStr">
@@ -17686,7 +17686,7 @@
       <c r="B994" t="inlineStr"/>
       <c r="C994" t="inlineStr">
         <is>
-          <t>SSR Container Train Banker</t>
+          <t>SSR Trip Train</t>
         </is>
       </c>
       <c r="D994" t="inlineStr">
@@ -18742,7 +18742,7 @@
       <c r="B1056" t="inlineStr"/>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1056" t="inlineStr">
@@ -27872,7 +27872,7 @@
       <c r="B1567" t="inlineStr"/>
       <c r="C1567" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (ex ST22)</t>
         </is>
       </c>
       <c r="D1567" t="inlineStr">
@@ -32879,7 +32879,7 @@
       <c r="B245" t="inlineStr"/>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -33703,7 +33703,7 @@
       <c r="B291" t="inlineStr"/>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -35787,7 +35787,7 @@
       <c r="B411" t="inlineStr"/>
       <c r="C411" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>PN Parkes Logistics Terminal Local Shunter</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -36733,7 +36733,7 @@
       <c r="B464" t="inlineStr"/>
       <c r="C464" t="inlineStr">
         <is>
-          <t>South Western Line diverted via Werribee</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -37003,7 +37003,7 @@
       <c r="B479" t="inlineStr"/>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -39377,7 +39377,7 @@
       <c r="B612" t="inlineStr"/>
       <c r="C612" t="inlineStr">
         <is>
-          <t>V1227</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
@@ -40117,7 +40117,7 @@
       <c r="B654" t="inlineStr"/>
       <c r="C654" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
@@ -42897,7 +42897,7 @@
       <c r="B810" t="inlineStr"/>
       <c r="C810" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D810" t="inlineStr">
@@ -48679,7 +48679,7 @@
       <c r="B1134" t="inlineStr"/>
       <c r="C1134" t="inlineStr">
         <is>
-          <t>SSR Container Train Banker</t>
+          <t>SSR Trip Train</t>
         </is>
       </c>
       <c r="D1134" t="inlineStr">
@@ -49405,7 +49405,7 @@
       <c r="B1175" t="inlineStr"/>
       <c r="C1175" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1175" t="inlineStr">
@@ -50243,7 +50243,7 @@
       <c r="B1222" t="inlineStr"/>
       <c r="C1222" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>North Eastern BG Line Service</t>
         </is>
       </c>
       <c r="D1222" t="inlineStr">
@@ -50581,7 +50581,7 @@
       <c r="B1241" t="inlineStr"/>
       <c r="C1241" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning (Forms SN34)</t>
+          <t>Southern Highlands Service</t>
         </is>
       </c>
       <c r="D1241" t="inlineStr">
@@ -50833,7 +50833,7 @@
       <c r="B1255" t="inlineStr"/>
       <c r="C1255" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1255" t="inlineStr">
@@ -50977,7 +50977,7 @@
       <c r="B1263" t="inlineStr"/>
       <c r="C1263" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1263" t="inlineStr">
@@ -51121,7 +51121,7 @@
       <c r="B1271" t="inlineStr"/>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1271" t="inlineStr">
@@ -51193,7 +51193,7 @@
       <c r="B1275" t="inlineStr"/>
       <c r="C1275" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1275" t="inlineStr">
@@ -51351,7 +51351,7 @@
       <c r="B1284" t="inlineStr"/>
       <c r="C1284" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1284" t="inlineStr">
@@ -51657,7 +51657,7 @@
       <c r="B1301" t="inlineStr"/>
       <c r="C1301" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (ex ST22)</t>
         </is>
       </c>
       <c r="D1301" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -508,7 +508,7 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -922,7 +922,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1368,7 +1368,7 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northern Line</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1918,7 +1918,7 @@
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2422,7 +2422,7 @@
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2494,7 +2494,7 @@
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>NorthEast BG Service</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7294,7 +7294,7 @@
       <c r="B389" t="inlineStr"/>
       <c r="C389" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Coal</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -8464,7 +8464,7 @@
       <c r="B460" t="inlineStr"/>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Aurizon Empty Copper</t>
+          <t>Aurizon Loaded Copper</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -12348,7 +12348,7 @@
       <c r="B685" t="inlineStr"/>
       <c r="C685" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
@@ -14444,7 +14444,7 @@
       <c r="B805" t="inlineStr"/>
       <c r="C805" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>NR24</t>
         </is>
       </c>
       <c r="D805" t="inlineStr">
@@ -15046,7 +15046,7 @@
       <c r="B840" t="inlineStr"/>
       <c r="C840" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>NR65</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
@@ -15150,7 +15150,7 @@
       <c r="B846" t="inlineStr"/>
       <c r="C846" t="inlineStr">
         <is>
-          <t>JBR The Overland</t>
+          <t>NR71</t>
         </is>
       </c>
       <c r="D846" t="inlineStr">
@@ -18424,7 +18424,7 @@
       <c r="B1037" t="inlineStr"/>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1037" t="inlineStr">
@@ -34779,7 +34779,7 @@
       <c r="B352" t="inlineStr"/>
       <c r="C352" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Coal</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -36535,7 +36535,7 @@
       <c r="B452" t="inlineStr"/>
       <c r="C452" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>NR24</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -36769,7 +36769,7 @@
       <c r="B465" t="inlineStr"/>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northern Line</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -42915,7 +42915,7 @@
       <c r="B810" t="inlineStr"/>
       <c r="C810" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D810" t="inlineStr">
@@ -46497,7 +46497,7 @@
       <c r="B1011" t="inlineStr"/>
       <c r="C1011" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1011" t="inlineStr">
@@ -48499,7 +48499,7 @@
       <c r="B1123" t="inlineStr"/>
       <c r="C1123" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1123" t="inlineStr">
@@ -49801,7 +49801,7 @@
       <c r="B1196" t="inlineStr"/>
       <c r="C1196" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1196" t="inlineStr">
@@ -49837,7 +49837,7 @@
       <c r="B1198" t="inlineStr"/>
       <c r="C1198" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>NorthEast BG Service</t>
         </is>
       </c>
       <c r="D1198" t="inlineStr">
@@ -51157,7 +51157,7 @@
       <c r="B1272" t="inlineStr"/>
       <c r="C1272" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1272" t="inlineStr">
@@ -51909,7 +51909,7 @@
       <c r="B1314" t="inlineStr"/>
       <c r="C1314" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D1314" t="inlineStr">
@@ -53081,7 +53081,7 @@
       <c r="B1382" t="inlineStr"/>
       <c r="C1382" t="inlineStr">
         <is>
-          <t>Aurizon Empty Copper</t>
+          <t>Aurizon Loaded Copper</t>
         </is>
       </c>
       <c r="D1382" t="inlineStr">
@@ -54561,7 +54561,7 @@
       <c r="B1468" t="inlineStr"/>
       <c r="C1468" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>NR65</t>
         </is>
       </c>
       <c r="D1468" t="inlineStr">
@@ -54597,7 +54597,7 @@
       <c r="B1470" t="inlineStr"/>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>JBR The Overland</t>
+          <t>NR71</t>
         </is>
       </c>
       <c r="D1470" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -526,7 +526,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -796,7 +796,7 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>North East Line Service</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -958,7 +958,7 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1246,7 +1246,7 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1368,7 +1368,7 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Northern Line</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1494,7 +1494,7 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2548,7 +2548,7 @@
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -4072,7 +4072,7 @@
       <c r="B206" t="inlineStr"/>
       <c r="C206" t="inlineStr">
         <is>
-          <t>AZ COal</t>
+          <t>AZ Coal</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -4656,7 +4656,7 @@
       <c r="B240" t="inlineStr"/>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Qube Light Engine</t>
+          <t>QUBE Light Engine</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -5024,7 +5024,11 @@
         </is>
       </c>
       <c r="B261" t="inlineStr"/>
-      <c r="C261" t="inlineStr"/>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>PN Melbourne Freight Terminal Shunter</t>
+        </is>
+      </c>
       <c r="D261" t="inlineStr">
         <is>
           <t>2026-04-12 05:38:41</t>
@@ -5378,7 +5382,7 @@
       <c r="B281" t="inlineStr"/>
       <c r="C281" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Light Engine Movement</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -5558,7 +5562,7 @@
       <c r="B291" t="inlineStr"/>
       <c r="C291" t="inlineStr">
         <is>
-          <t>PN Cement - RailTrain Crewed</t>
+          <t>PN Cement</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -5666,7 +5670,7 @@
       <c r="B297" t="inlineStr"/>
       <c r="C297" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Trip Train</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -5846,7 +5850,7 @@
       <c r="B307" t="inlineStr"/>
       <c r="C307" t="inlineStr">
         <is>
-          <t>PN Coal</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -6706,7 +6710,7 @@
       <c r="B355" t="inlineStr"/>
       <c r="C355" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Light Engine Movement</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -8324,7 +8328,7 @@
       <c r="B452" t="inlineStr"/>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Aurizon Empty Mineral Sands Shuttle</t>
+          <t>Aurizon Mineral Sands Shuttle</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -9834,7 +9838,7 @@
       <c r="B543" t="inlineStr"/>
       <c r="C543" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
@@ -10998,7 +11002,7 @@
       <c r="B608" t="inlineStr"/>
       <c r="C608" t="inlineStr">
         <is>
-          <t>NSW Trainlink empty car transfer</t>
+          <t>NSW Trainlink Xplorer</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
@@ -11016,7 +11020,7 @@
       <c r="B609" t="inlineStr"/>
       <c r="C609" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer to Sydney (connects with NP24)</t>
+          <t>NSW Trainlink Xplorer</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
@@ -11760,7 +11764,7 @@
       <c r="B651" t="inlineStr"/>
       <c r="C651" t="inlineStr">
         <is>
-          <t>Maintenance Train</t>
+          <t>SSR Light Engine</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
@@ -12474,7 +12478,7 @@
       <c r="B692" t="inlineStr"/>
       <c r="C692" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
@@ -13054,7 +13058,7 @@
       <c r="B726" t="inlineStr"/>
       <c r="C726" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
@@ -13480,7 +13484,7 @@
       <c r="B751" t="inlineStr"/>
       <c r="C751" t="inlineStr">
         <is>
-          <t>Swift Trip Train</t>
+          <t>SSR Loaded Manildra Flour</t>
         </is>
       </c>
       <c r="D751" t="inlineStr">
@@ -14746,7 +14750,7 @@
       <c r="B822" t="inlineStr"/>
       <c r="C822" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>PN Infrabuild Steel via Lithgow</t>
         </is>
       </c>
       <c r="D822" t="inlineStr">
@@ -16402,7 +16406,7 @@
       <c r="B920" t="inlineStr"/>
       <c r="C920" t="inlineStr">
         <is>
-          <t>Watco Light Engine</t>
+          <t>Watco Trip Train</t>
         </is>
       </c>
       <c r="D920" t="inlineStr">
@@ -18064,7 +18068,7 @@
       <c r="B1017" t="inlineStr"/>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1017" t="inlineStr">
@@ -18118,7 +18122,7 @@
       <c r="B1020" t="inlineStr"/>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>NorthEast BG Line Service</t>
         </is>
       </c>
       <c r="D1020" t="inlineStr">
@@ -27944,7 +27948,7 @@
       <c r="B1571" t="inlineStr"/>
       <c r="C1571" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (Forms ST21)</t>
+          <t>NSW TrainLink XPT</t>
         </is>
       </c>
       <c r="D1571" t="inlineStr">
@@ -30245,7 +30249,7 @@
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Light Engine Movement</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -30263,7 +30267,7 @@
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (Forms ST21)</t>
+          <t>NSW TrainLink XPT</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -30281,7 +30285,7 @@
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Watco Light Engine</t>
+          <t>Watco Trip Train</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -30941,7 +30945,11 @@
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
-      <c r="C130" t="inlineStr"/>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>PN Melbourne Freight Terminal Shunter</t>
+        </is>
+      </c>
       <c r="D130" t="inlineStr">
         <is>
           <t>2026-04-12 05:38:41</t>
@@ -32825,7 +32833,7 @@
       <c r="B239" t="inlineStr"/>
       <c r="C239" t="inlineStr">
         <is>
-          <t>PN Coal</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -34543,7 +34551,7 @@
       <c r="B336" t="inlineStr"/>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -34833,7 +34841,7 @@
       <c r="B353" t="inlineStr"/>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -36841,7 +36849,7 @@
       <c r="B467" t="inlineStr"/>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Northern Line</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -37219,7 +37227,7 @@
       <c r="B488" t="inlineStr"/>
       <c r="C488" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>PN Infrabuild Steel via Lithgow</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
@@ -38849,7 +38857,7 @@
       <c r="B579" t="inlineStr"/>
       <c r="C579" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Light Engine Movement</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
@@ -39485,7 +39493,7 @@
       <c r="B615" t="inlineStr"/>
       <c r="C615" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -39503,7 +39511,7 @@
       <c r="B616" t="inlineStr"/>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Aurizon Empty Mineral Sands Shuttle</t>
+          <t>Aurizon Mineral Sands Shuttle</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
@@ -40189,7 +40197,7 @@
       <c r="B655" t="inlineStr"/>
       <c r="C655" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
@@ -40225,7 +40233,7 @@
       <c r="B657" t="inlineStr"/>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
@@ -40783,7 +40791,7 @@
       <c r="B688" t="inlineStr"/>
       <c r="C688" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>NorthEast BG Line Service</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
@@ -43833,7 +43841,7 @@
       <c r="B859" t="inlineStr"/>
       <c r="C859" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D859" t="inlineStr">
@@ -44621,7 +44629,7 @@
       <c r="B903" t="inlineStr"/>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Qube Light Engine</t>
+          <t>QUBE Light Engine</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
@@ -47015,7 +47023,7 @@
       <c r="B1038" t="inlineStr"/>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1038" t="inlineStr">
@@ -47790,7 +47798,7 @@
       <c r="B1081" t="inlineStr"/>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Trip Train</t>
         </is>
       </c>
       <c r="D1081" t="inlineStr">
@@ -47808,7 +47816,7 @@
       <c r="B1082" t="inlineStr"/>
       <c r="C1082" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer to Sydney (connects with NP24)</t>
+          <t>NSW Trainlink Xplorer</t>
         </is>
       </c>
       <c r="D1082" t="inlineStr">
@@ -48002,7 +48010,7 @@
       <c r="B1093" t="inlineStr"/>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>North East Line Service</t>
         </is>
       </c>
       <c r="D1093" t="inlineStr">
@@ -49057,7 +49065,7 @@
       <c r="B1152" t="inlineStr"/>
       <c r="C1152" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1152" t="inlineStr">
@@ -50653,7 +50661,7 @@
       <c r="B1242" t="inlineStr"/>
       <c r="C1242" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1242" t="inlineStr">
@@ -51139,7 +51147,7 @@
       <c r="B1269" t="inlineStr"/>
       <c r="C1269" t="inlineStr">
         <is>
-          <t>PN Cement - RailTrain Crewed</t>
+          <t>PN Cement</t>
         </is>
       </c>
       <c r="D1269" t="inlineStr">
@@ -51211,7 +51219,7 @@
       <c r="B1273" t="inlineStr"/>
       <c r="C1273" t="inlineStr">
         <is>
-          <t>Maintenance Train</t>
+          <t>SSR Light Engine</t>
         </is>
       </c>
       <c r="D1273" t="inlineStr">
@@ -51909,7 +51917,7 @@
       <c r="B1312" t="inlineStr"/>
       <c r="C1312" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1312" t="inlineStr">
@@ -52415,7 +52423,7 @@
       <c r="B1341" t="inlineStr"/>
       <c r="C1341" t="inlineStr">
         <is>
-          <t>AZ COal</t>
+          <t>AZ Coal</t>
         </is>
       </c>
       <c r="D1341" t="inlineStr">
@@ -53871,7 +53879,7 @@
       <c r="B1427" t="inlineStr"/>
       <c r="C1427" t="inlineStr">
         <is>
-          <t>NSW Trainlink empty car transfer</t>
+          <t>NSW Trainlink Xplorer</t>
         </is>
       </c>
       <c r="D1427" t="inlineStr">
@@ -54295,7 +54303,7 @@
       <c r="B1451" t="inlineStr"/>
       <c r="C1451" t="inlineStr">
         <is>
-          <t>Swift Trip Train</t>
+          <t>SSR Loaded Manildra Flour</t>
         </is>
       </c>
       <c r="D1451" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -472,7 +472,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -562,7 +562,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>V/Line Empty Car Transfer</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -616,7 +616,7 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -742,7 +742,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -778,7 +778,7 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -832,7 +832,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1084,7 +1084,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>North Eastern Line BG Service</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1298,7 +1298,11 @@
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Northern Line Service</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
           <t>2026-04-03 10:12:34</t>
@@ -1580,7 +1584,7 @@
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1598,7 +1602,7 @@
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1652,7 +1656,7 @@
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -1814,7 +1818,7 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2332,7 +2336,7 @@
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2386,7 +2390,7 @@
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2638,7 +2642,7 @@
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -2818,7 +2822,7 @@
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>V/Line Empty Car Transfer</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -2836,7 +2840,7 @@
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>North East SG Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3400,7 +3404,7 @@
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Aurizon Light Engine Movement</t>
+          <t>Aurizon Intermodal Shuttle</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -3702,7 +3706,7 @@
       <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
         <is>
-          <t>SRS/SCT Sadleirs Trip Train</t>
+          <t>SRS Light Engine</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -5544,7 +5548,7 @@
       <c r="B290" t="inlineStr"/>
       <c r="C290" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Local Shunter</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -5562,7 +5566,7 @@
       <c r="B291" t="inlineStr"/>
       <c r="C291" t="inlineStr">
         <is>
-          <t>PN Cement</t>
+          <t>PN Cement - RailTrain Crewed</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -6620,7 +6624,7 @@
       <c r="B350" t="inlineStr"/>
       <c r="C350" t="inlineStr">
         <is>
-          <t>PN Grain</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -8712,7 +8716,7 @@
       <c r="B474" t="inlineStr"/>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Aurizon Empty Grain/Wagon Transfer</t>
+          <t>Aurizon Fuel Shunt/Wagon Transfer</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
@@ -10054,7 +10058,7 @@
       <c r="B555" t="inlineStr"/>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Ore (diverted 8402)</t>
+          <t>Aurizon Empty Ore (Diverted 4801)</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
@@ -10540,7 +10544,7 @@
       <c r="B582" t="inlineStr"/>
       <c r="C582" t="inlineStr">
         <is>
-          <t>SCT Light Engine Movement</t>
+          <t>SCT Steel Shunt / Wine Train</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
@@ -10716,7 +10720,7 @@
       <c r="B592" t="inlineStr"/>
       <c r="C592" t="inlineStr">
         <is>
-          <t>SCT Intermodal</t>
+          <t>SCT Steel Transfer</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
@@ -14232,7 +14236,7 @@
       <c r="B793" t="inlineStr"/>
       <c r="C793" t="inlineStr">
         <is>
-          <t>NR8</t>
+          <t>PN Containerised Freight</t>
         </is>
       </c>
       <c r="D793" t="inlineStr">
@@ -18764,7 +18768,7 @@
       <c r="B1057" t="inlineStr"/>
       <c r="C1057" t="inlineStr">
         <is>
-          <t>Bathurst Bullet - Transfer</t>
+          <t>Southern Highlands Service</t>
         </is>
       </c>
       <c r="D1057" t="inlineStr">
@@ -27912,7 +27916,7 @@
       <c r="B1569" t="inlineStr"/>
       <c r="C1569" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (ex NT34)</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1569" t="inlineStr">
@@ -27998,7 +28002,7 @@
       <c r="B1574" t="inlineStr"/>
       <c r="C1574" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (Forms WT27)</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1574" t="inlineStr">
@@ -30077,7 +30081,7 @@
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -31083,7 +31087,7 @@
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Local Shunter</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -34895,7 +34899,7 @@
       <c r="B356" t="inlineStr"/>
       <c r="C356" t="inlineStr">
         <is>
-          <t>PN Grain</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -36543,7 +36547,7 @@
       <c r="B450" t="inlineStr"/>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>V/Line Empty Car Transfer</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -36831,7 +36835,7 @@
       <c r="B466" t="inlineStr"/>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -37101,7 +37105,7 @@
       <c r="B481" t="inlineStr"/>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -38731,7 +38735,7 @@
       <c r="B572" t="inlineStr"/>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Aurizon Light Engine Movement</t>
+          <t>Aurizon Intermodal Shuttle</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
@@ -41899,7 +41903,7 @@
       <c r="B750" t="inlineStr"/>
       <c r="C750" t="inlineStr">
         <is>
-          <t>V/Line Empty Car Transfer</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
@@ -41971,7 +41975,7 @@
       <c r="B754" t="inlineStr"/>
       <c r="C754" t="inlineStr">
         <is>
-          <t>SCT Intermodal</t>
+          <t>SCT Steel Transfer</t>
         </is>
       </c>
       <c r="D754" t="inlineStr">
@@ -42395,7 +42399,7 @@
       <c r="B778" t="inlineStr"/>
       <c r="C778" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D778" t="inlineStr">
@@ -43877,7 +43881,7 @@
       <c r="B861" t="inlineStr"/>
       <c r="C861" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D861" t="inlineStr">
@@ -44751,7 +44755,7 @@
       <c r="B910" t="inlineStr"/>
       <c r="C910" t="inlineStr">
         <is>
-          <t>Bathurst Bullet - Transfer</t>
+          <t>Southern Highlands Service</t>
         </is>
       </c>
       <c r="D910" t="inlineStr">
@@ -46667,7 +46671,7 @@
       <c r="B1018" t="inlineStr"/>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1018" t="inlineStr">
@@ -47005,7 +47009,7 @@
       <c r="B1037" t="inlineStr"/>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1037" t="inlineStr">
@@ -47992,7 +47996,7 @@
       <c r="B1092" t="inlineStr"/>
       <c r="C1092" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1092" t="inlineStr">
@@ -48028,7 +48032,7 @@
       <c r="B1094" t="inlineStr"/>
       <c r="C1094" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1094" t="inlineStr">
@@ -48957,7 +48961,7 @@
       <c r="B1146" t="inlineStr"/>
       <c r="C1146" t="inlineStr">
         <is>
-          <t>SCT Light Engine Movement</t>
+          <t>SCT Steel Shunt / Wine Train</t>
         </is>
       </c>
       <c r="D1146" t="inlineStr">
@@ -49011,7 +49015,7 @@
       <c r="B1149" t="inlineStr"/>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>NR8</t>
+          <t>PN Containerised Freight</t>
         </is>
       </c>
       <c r="D1149" t="inlineStr">
@@ -49467,7 +49471,7 @@
       <c r="B1175" t="inlineStr"/>
       <c r="C1175" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (ex NT34)</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1175" t="inlineStr">
@@ -49503,7 +49507,7 @@
       <c r="B1177" t="inlineStr"/>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1177" t="inlineStr">
@@ -49971,7 +49975,7 @@
       <c r="B1203" t="inlineStr"/>
       <c r="C1203" t="inlineStr">
         <is>
-          <t>North East SG Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1203" t="inlineStr">
@@ -50429,7 +50433,11 @@
         </is>
       </c>
       <c r="B1229" t="inlineStr"/>
-      <c r="C1229" t="inlineStr"/>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>Northern Line Service</t>
+        </is>
+      </c>
       <c r="D1229" t="inlineStr">
         <is>
           <t>2026-04-03 10:12:34</t>
@@ -50589,7 +50597,7 @@
       <c r="B1238" t="inlineStr"/>
       <c r="C1238" t="inlineStr">
         <is>
-          <t>Aurizon Empty Grain/Wagon Transfer</t>
+          <t>Aurizon Fuel Shunt/Wagon Transfer</t>
         </is>
       </c>
       <c r="D1238" t="inlineStr">
@@ -50625,7 +50633,7 @@
       <c r="B1240" t="inlineStr"/>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Ore (diverted 8402)</t>
+          <t>Aurizon Empty Ore (Diverted 4801)</t>
         </is>
       </c>
       <c r="D1240" t="inlineStr">
@@ -51147,7 +51155,7 @@
       <c r="B1269" t="inlineStr"/>
       <c r="C1269" t="inlineStr">
         <is>
-          <t>PN Cement</t>
+          <t>PN Cement - RailTrain Crewed</t>
         </is>
       </c>
       <c r="D1269" t="inlineStr">
@@ -51791,7 +51799,7 @@
       <c r="B1305" t="inlineStr"/>
       <c r="C1305" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (Forms WT27)</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1305" t="inlineStr">
@@ -51845,7 +51853,7 @@
       <c r="B1308" t="inlineStr"/>
       <c r="C1308" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1308" t="inlineStr">
@@ -51971,7 +51979,7 @@
       <c r="B1315" t="inlineStr"/>
       <c r="C1315" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1315" t="inlineStr">
@@ -52025,7 +52033,7 @@
       <c r="B1318" t="inlineStr"/>
       <c r="C1318" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>North Eastern Line BG Service</t>
         </is>
       </c>
       <c r="D1318" t="inlineStr">
@@ -52273,7 +52281,7 @@
       <c r="B1332" t="inlineStr"/>
       <c r="C1332" t="inlineStr">
         <is>
-          <t>SRS/SCT Sadleirs Trip Train</t>
+          <t>SRS Light Engine</t>
         </is>
       </c>
       <c r="D1332" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -490,7 +490,7 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -508,7 +508,7 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning, pre 8945</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -670,7 +670,7 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -742,7 +742,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>V/Line Light Engine</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -796,7 +796,7 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>North East Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -958,7 +958,7 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1120,7 +1120,7 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1138,7 +1138,7 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1156,7 +1156,7 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1246,7 +1246,7 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1318,7 +1318,7 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1408,7 +1408,7 @@
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1584,7 +1584,7 @@
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1728,7 +1728,7 @@
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -1800,7 +1800,7 @@
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -1886,7 +1886,7 @@
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2624,7 +2624,7 @@
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>North Eastern BG Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3142,7 +3142,7 @@
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
-          <t>QUBE Container Train</t>
+          <t>QUBE Shuttle</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -6084,7 +6084,7 @@
       <c r="B320" t="inlineStr"/>
       <c r="C320" t="inlineStr">
         <is>
-          <t>PN Loaded Ore / Grain</t>
+          <t>PN Empty Ore</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -7586,7 +7586,11 @@
         </is>
       </c>
       <c r="B406" t="inlineStr"/>
-      <c r="C406" t="inlineStr"/>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>PN Intermodal</t>
+        </is>
+      </c>
       <c r="D406" t="inlineStr">
         <is>
           <t>2026-04-12 13:46:42</t>
@@ -7902,7 +7906,7 @@
       <c r="B425" t="inlineStr"/>
       <c r="C425" t="inlineStr">
         <is>
-          <t>SSR Light Engine</t>
+          <t>SSR Manildra Grain Shuttle</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -10576,7 +10580,7 @@
       <c r="B584" t="inlineStr"/>
       <c r="C584" t="inlineStr">
         <is>
-          <t>SCT Sadleirs Transfer</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
@@ -10970,7 +10974,7 @@
       <c r="B606" t="inlineStr"/>
       <c r="C606" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer</t>
+          <t>NSW TrainLink Xplorer</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
@@ -13696,7 +13700,7 @@
       <c r="B763" t="inlineStr"/>
       <c r="C763" t="inlineStr">
         <is>
-          <t>SSR Grain</t>
+          <t>SSR Trip Train (Weston Milling)</t>
         </is>
       </c>
       <c r="D763" t="inlineStr">
@@ -13912,7 +13916,7 @@
       <c r="B775" t="inlineStr"/>
       <c r="C775" t="inlineStr">
         <is>
-          <t>V/Line Light Engine Movement</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
@@ -16910,7 +16914,7 @@
       <c r="B950" t="inlineStr"/>
       <c r="C950" t="inlineStr">
         <is>
-          <t>QUBE Containerised Cotton</t>
+          <t>QUBE Containerised Freight</t>
         </is>
       </c>
       <c r="D950" t="inlineStr">
@@ -17572,7 +17576,7 @@
       <c r="B987" t="inlineStr"/>
       <c r="C987" t="inlineStr">
         <is>
-          <t>QUBE Trip Train</t>
+          <t>QUBE Containerised Freight</t>
         </is>
       </c>
       <c r="D987" t="inlineStr">
@@ -17608,7 +17612,7 @@
       <c r="B989" t="inlineStr"/>
       <c r="C989" t="inlineStr">
         <is>
-          <t>SSR Grain</t>
+          <t>SSR Local Transfer Train</t>
         </is>
       </c>
       <c r="D989" t="inlineStr">
@@ -18162,7 +18166,7 @@
       <c r="B1022" t="inlineStr"/>
       <c r="C1022" t="inlineStr">
         <is>
-          <t>North Eastern Line BG Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D1022" t="inlineStr">
@@ -18468,7 +18472,7 @@
       <c r="B1039" t="inlineStr"/>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1039" t="inlineStr">
@@ -18696,7 +18700,7 @@
       <c r="B1053" t="inlineStr"/>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D1053" t="inlineStr">
@@ -18786,7 +18790,7 @@
       <c r="B1058" t="inlineStr"/>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>Additional Bathurst Service</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D1058" t="inlineStr">
@@ -19128,7 +19132,7 @@
       <c r="B1079" t="inlineStr"/>
       <c r="C1079" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D1079" t="inlineStr">
@@ -30849,7 +30853,11 @@
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
-      <c r="C124" t="inlineStr"/>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>PN Intermodal</t>
+        </is>
+      </c>
       <c r="D124" t="inlineStr">
         <is>
           <t>2026-04-12 13:46:42</t>
@@ -32999,7 +33007,7 @@
       <c r="B248" t="inlineStr"/>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -35331,7 +35339,7 @@
       <c r="B380" t="inlineStr"/>
       <c r="C380" t="inlineStr">
         <is>
-          <t>QUBE Container Train</t>
+          <t>QUBE Shuttle</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -36241,7 +36249,7 @@
       <c r="B433" t="inlineStr"/>
       <c r="C433" t="inlineStr">
         <is>
-          <t>QUBE Trip Train</t>
+          <t>QUBE Containerised Freight</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -38091,7 +38099,7 @@
       <c r="B536" t="inlineStr"/>
       <c r="C536" t="inlineStr">
         <is>
-          <t>SSR Light Engine</t>
+          <t>SSR Manildra Grain Shuttle</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
@@ -38897,7 +38905,7 @@
       <c r="B581" t="inlineStr"/>
       <c r="C581" t="inlineStr">
         <is>
-          <t>PN Loaded Ore / Grain</t>
+          <t>PN Empty Ore</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
@@ -39497,7 +39505,7 @@
       <c r="B615" t="inlineStr"/>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -39659,7 +39667,7 @@
       <c r="B624" t="inlineStr"/>
       <c r="C624" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
@@ -40543,7 +40551,7 @@
       <c r="B674" t="inlineStr"/>
       <c r="C674" t="inlineStr">
         <is>
-          <t>SSR Grain</t>
+          <t>SSR Local Transfer Train</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
@@ -42345,7 +42353,7 @@
       <c r="B775" t="inlineStr"/>
       <c r="C775" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
@@ -42981,7 +42989,7 @@
       <c r="B811" t="inlineStr"/>
       <c r="C811" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D811" t="inlineStr">
@@ -43845,7 +43853,7 @@
       <c r="B859" t="inlineStr"/>
       <c r="C859" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D859" t="inlineStr">
@@ -43863,7 +43871,7 @@
       <c r="B860" t="inlineStr"/>
       <c r="C860" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D860" t="inlineStr">
@@ -45937,7 +45945,7 @@
       <c r="B977" t="inlineStr"/>
       <c r="C977" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D977" t="inlineStr">
@@ -46617,7 +46625,7 @@
       <c r="B1015" t="inlineStr"/>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1015" t="inlineStr">
@@ -47009,7 +47017,7 @@
       <c r="B1037" t="inlineStr"/>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>V/Line Light Engine</t>
         </is>
       </c>
       <c r="D1037" t="inlineStr">
@@ -47135,7 +47143,7 @@
       <c r="B1044" t="inlineStr"/>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>V/Line Light Engine Movement</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1044" t="inlineStr">
@@ -48014,7 +48022,7 @@
       <c r="B1093" t="inlineStr"/>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>North East Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D1093" t="inlineStr">
@@ -48032,7 +48040,7 @@
       <c r="B1094" t="inlineStr"/>
       <c r="C1094" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1094" t="inlineStr">
@@ -48457,7 +48465,7 @@
       <c r="B1118" t="inlineStr"/>
       <c r="C1118" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D1118" t="inlineStr">
@@ -48583,7 +48591,7 @@
       <c r="B1125" t="inlineStr"/>
       <c r="C1125" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1125" t="inlineStr">
@@ -49209,7 +49217,7 @@
       <c r="B1160" t="inlineStr"/>
       <c r="C1160" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1160" t="inlineStr">
@@ -49335,7 +49343,7 @@
       <c r="B1167" t="inlineStr"/>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>SSR Grain</t>
+          <t>SSR Trip Train (Weston Milling)</t>
         </is>
       </c>
       <c r="D1167" t="inlineStr">
@@ -49633,7 +49641,7 @@
       <c r="B1184" t="inlineStr"/>
       <c r="C1184" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer</t>
+          <t>NSW TrainLink Xplorer</t>
         </is>
       </c>
       <c r="D1184" t="inlineStr">
@@ -49885,7 +49893,7 @@
       <c r="B1198" t="inlineStr"/>
       <c r="C1198" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning, pre 8945</t>
         </is>
       </c>
       <c r="D1198" t="inlineStr">
@@ -50363,7 +50371,7 @@
       <c r="B1225" t="inlineStr"/>
       <c r="C1225" t="inlineStr">
         <is>
-          <t>North Eastern BG Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D1225" t="inlineStr">
@@ -50453,7 +50461,7 @@
       <c r="B1230" t="inlineStr"/>
       <c r="C1230" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1230" t="inlineStr">
@@ -50777,7 +50785,7 @@
       <c r="B1248" t="inlineStr"/>
       <c r="C1248" t="inlineStr">
         <is>
-          <t>Additional Bathurst Service</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D1248" t="inlineStr">
@@ -51119,7 +51127,7 @@
       <c r="B1267" t="inlineStr"/>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1267" t="inlineStr">
@@ -51421,7 +51429,7 @@
       <c r="B1284" t="inlineStr"/>
       <c r="C1284" t="inlineStr">
         <is>
-          <t>North Eastern Line BG Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D1284" t="inlineStr">
@@ -51457,7 +51465,7 @@
       <c r="B1286" t="inlineStr"/>
       <c r="C1286" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D1286" t="inlineStr">
@@ -53797,7 +53805,7 @@
       <c r="B1422" t="inlineStr"/>
       <c r="C1422" t="inlineStr">
         <is>
-          <t>SCT Sadleirs Transfer</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D1422" t="inlineStr">
@@ -55193,7 +55201,7 @@
       <c r="B1504" t="inlineStr"/>
       <c r="C1504" t="inlineStr">
         <is>
-          <t>QUBE Containerised Cotton</t>
+          <t>QUBE Containerised Freight</t>
         </is>
       </c>
       <c r="D1504" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -598,7 +598,7 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -724,7 +724,7 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>V/Line Transfer</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1102,7 +1102,7 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1192,7 +1192,7 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2246,7 +2246,7 @@
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2372,7 +2372,7 @@
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3404,7 +3404,7 @@
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Aurizon Intermodal Shuttle</t>
+          <t>Aurizon Light Engine Movement</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -5638,7 +5638,7 @@
       <c r="B295" t="inlineStr"/>
       <c r="C295" t="inlineStr">
         <is>
-          <t>PN Grain Shuttle</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -7462,7 +7462,7 @@
       <c r="B399" t="inlineStr"/>
       <c r="C399" t="inlineStr">
         <is>
-          <t>ARTC Maintenance Train</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -9810,7 +9810,7 @@
       <c r="B541" t="inlineStr"/>
       <c r="C541" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -10008,7 +10008,7 @@
       <c r="B552" t="inlineStr"/>
       <c r="C552" t="inlineStr">
         <is>
-          <t>QUBE Loaded Containerised Ore</t>
+          <t>QUBE Empty Containerised Ore</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
@@ -10314,7 +10314,7 @@
       <c r="B569" t="inlineStr"/>
       <c r="C569" t="inlineStr">
         <is>
-          <t>SSR Light Engine</t>
+          <t>SSR Grain</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
@@ -10724,7 +10724,7 @@
       <c r="B592" t="inlineStr"/>
       <c r="C592" t="inlineStr">
         <is>
-          <t>SCT Steel Transfer</t>
+          <t>SCT Sadleirs Transfer</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
@@ -11276,7 +11276,7 @@
       <c r="B623" t="inlineStr"/>
       <c r="C623" t="inlineStr">
         <is>
-          <t>SSR Empty Cement</t>
+          <t>SSR Cement</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
@@ -11312,7 +11312,7 @@
       <c r="B625" t="inlineStr"/>
       <c r="C625" t="inlineStr">
         <is>
-          <t>QUBE Loaded Aggregates</t>
+          <t>QUBE Empty Aggregates</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
@@ -12432,7 +12432,7 @@
       <c r="B689" t="inlineStr"/>
       <c r="C689" t="inlineStr">
         <is>
-          <t>Hunter Railcar Transfer</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
@@ -13012,7 +13012,7 @@
       <c r="B723" t="inlineStr"/>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Southern Highlands Service</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
@@ -13030,7 +13030,7 @@
       <c r="B724" t="inlineStr"/>
       <c r="C724" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
@@ -15094,7 +15094,7 @@
       <c r="B842" t="inlineStr"/>
       <c r="C842" t="inlineStr">
         <is>
-          <t>NR65</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
@@ -16414,7 +16414,7 @@
       <c r="B920" t="inlineStr"/>
       <c r="C920" t="inlineStr">
         <is>
-          <t>Watco Trip Train</t>
+          <t>Watco Light Engine</t>
         </is>
       </c>
       <c r="D920" t="inlineStr">
@@ -17918,7 +17918,7 @@
       <c r="B1008" t="inlineStr"/>
       <c r="C1008" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1008" t="inlineStr">
@@ -28024,7 +28024,7 @@
       <c r="B1575" t="inlineStr"/>
       <c r="C1575" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty XPT (Forms NT33)</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1575" t="inlineStr">
@@ -28580,7 +28580,7 @@
       <c r="B1607" t="inlineStr"/>
       <c r="C1607" t="inlineStr">
         <is>
-          <t>ORA Light Engine</t>
+          <t>ORA Shunter</t>
         </is>
       </c>
       <c r="D1607" t="inlineStr">
@@ -30293,7 +30293,7 @@
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Watco Trip Train</t>
+          <t>Watco Light Engine</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -33507,7 +33507,7 @@
       <c r="B276" t="inlineStr"/>
       <c r="C276" t="inlineStr">
         <is>
-          <t>QUBE Loaded Containerised Ore</t>
+          <t>QUBE Empty Containerised Ore</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -34749,7 +34749,7 @@
       <c r="B347" t="inlineStr"/>
       <c r="C347" t="inlineStr">
         <is>
-          <t>QUBE Loaded Aggregates</t>
+          <t>QUBE Empty Aggregates</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -38257,7 +38257,7 @@
       <c r="B545" t="inlineStr"/>
       <c r="C545" t="inlineStr">
         <is>
-          <t>PN Grain Shuttle</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
@@ -38743,7 +38743,7 @@
       <c r="B572" t="inlineStr"/>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Aurizon Intermodal Shuttle</t>
+          <t>Aurizon Light Engine Movement</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
@@ -39879,7 +39879,7 @@
       <c r="B636" t="inlineStr"/>
       <c r="C636" t="inlineStr">
         <is>
-          <t>SSR Light Engine</t>
+          <t>SSR Grain</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
@@ -40407,7 +40407,7 @@
       <c r="B666" t="inlineStr"/>
       <c r="C666" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
@@ -41983,7 +41983,7 @@
       <c r="B754" t="inlineStr"/>
       <c r="C754" t="inlineStr">
         <is>
-          <t>SCT Steel Transfer</t>
+          <t>SCT Sadleirs Transfer</t>
         </is>
       </c>
       <c r="D754" t="inlineStr">
@@ -42209,7 +42209,7 @@
       <c r="B767" t="inlineStr"/>
       <c r="C767" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D767" t="inlineStr">
@@ -42425,7 +42425,7 @@
       <c r="B779" t="inlineStr"/>
       <c r="C779" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D779" t="inlineStr">
@@ -42709,7 +42709,7 @@
       <c r="B795" t="inlineStr"/>
       <c r="C795" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Southern Highlands Service</t>
         </is>
       </c>
       <c r="D795" t="inlineStr">
@@ -43993,7 +43993,7 @@
       <c r="B867" t="inlineStr"/>
       <c r="C867" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D867" t="inlineStr">
@@ -44569,7 +44569,7 @@
       <c r="B899" t="inlineStr"/>
       <c r="C899" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>V/Line Transfer</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
@@ -48310,7 +48310,7 @@
       <c r="B1109" t="inlineStr"/>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty XPT (Forms NT33)</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1109" t="inlineStr">
@@ -49659,7 +49659,7 @@
       <c r="B1185" t="inlineStr"/>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>SSR Empty Cement</t>
+          <t>SSR Cement</t>
         </is>
       </c>
       <c r="D1185" t="inlineStr">
@@ -50353,7 +50353,7 @@
       <c r="B1224" t="inlineStr"/>
       <c r="C1224" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1224" t="inlineStr">
@@ -51037,7 +51037,7 @@
       <c r="B1262" t="inlineStr"/>
       <c r="C1262" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1262" t="inlineStr">
@@ -52059,7 +52059,7 @@
       <c r="B1319" t="inlineStr"/>
       <c r="C1319" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D1319" t="inlineStr">
@@ -52939,7 +52939,7 @@
       <c r="B1369" t="inlineStr"/>
       <c r="C1369" t="inlineStr">
         <is>
-          <t>ARTC Maintenance Train</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D1369" t="inlineStr">
@@ -53643,7 +53643,7 @@
       <c r="B1413" t="inlineStr"/>
       <c r="C1413" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1413" t="inlineStr">
@@ -54107,7 +54107,7 @@
       <c r="B1439" t="inlineStr"/>
       <c r="C1439" t="inlineStr">
         <is>
-          <t>Hunter Railcar Transfer</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1439" t="inlineStr">
@@ -54657,7 +54657,7 @@
       <c r="B1470" t="inlineStr"/>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>NR65</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D1470" t="inlineStr">
@@ -56707,7 +56707,7 @@
       <c r="B1589" t="inlineStr"/>
       <c r="C1589" t="inlineStr">
         <is>
-          <t>ORA Light Engine</t>
+          <t>ORA Shunter</t>
         </is>
       </c>
       <c r="D1589" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1656,7 +1656,7 @@
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4714,7 +4714,7 @@
       <c r="B243" t="inlineStr"/>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Maintenance Train</t>
+          <t>PN Empty Containerised Logs</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -5368,7 +5368,7 @@
       <c r="B280" t="inlineStr"/>
       <c r="C280" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>Loaded Coal</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -7094,7 +7094,7 @@
       <c r="B377" t="inlineStr"/>
       <c r="C377" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -9526,7 +9526,7 @@
       <c r="B525" t="inlineStr"/>
       <c r="C525" t="inlineStr">
         <is>
-          <t>SSR Manildra Grain Shuttle</t>
+          <t>SSR Light Engine Movement</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
@@ -9544,7 +9544,7 @@
       <c r="B526" t="inlineStr"/>
       <c r="C526" t="inlineStr">
         <is>
-          <t>SSR Manildra Grain Shuttle</t>
+          <t>SSR Containerised Freight</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
@@ -10278,7 +10278,7 @@
       <c r="B567" t="inlineStr"/>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Aurizon Empty Grain</t>
+          <t>Aurizon Wagon Transfer</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
@@ -11510,7 +11510,7 @@
       <c r="B636" t="inlineStr"/>
       <c r="C636" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Containerised Freight</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
@@ -12432,7 +12432,7 @@
       <c r="B689" t="inlineStr"/>
       <c r="C689" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
@@ -12450,7 +12450,7 @@
       <c r="B690" t="inlineStr"/>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Hunter Railcar Transfer</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
@@ -12486,7 +12486,7 @@
       <c r="B692" t="inlineStr"/>
       <c r="C692" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
@@ -13348,7 +13348,7 @@
       <c r="B743" t="inlineStr"/>
       <c r="C743" t="inlineStr">
         <is>
-          <t>SSR Light Engine Movement</t>
+          <t>SSR Light Engine</t>
         </is>
       </c>
       <c r="D743" t="inlineStr">
@@ -13564,7 +13564,7 @@
       <c r="B755" t="inlineStr"/>
       <c r="C755" t="inlineStr">
         <is>
-          <t>Swift Trip Train</t>
+          <t>SSR Empty Manildra Flour</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
@@ -14366,7 +14366,7 @@
       <c r="B800" t="inlineStr"/>
       <c r="C800" t="inlineStr">
         <is>
-          <t>PN Empty Fuel</t>
+          <t>PN Fuel Train</t>
         </is>
       </c>
       <c r="D800" t="inlineStr">
@@ -15414,7 +15414,7 @@
       <c r="B860" t="inlineStr"/>
       <c r="C860" t="inlineStr">
         <is>
-          <t>JBR Indian Pacific</t>
+          <t>JBR Indian Pacifc</t>
         </is>
       </c>
       <c r="D860" t="inlineStr">
@@ -18490,7 +18490,7 @@
       <c r="B1040" t="inlineStr"/>
       <c r="C1040" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1040" t="inlineStr">
@@ -18790,7 +18790,7 @@
       <c r="B1058" t="inlineStr"/>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1058" t="inlineStr">
@@ -27938,7 +27938,7 @@
       <c r="B1570" t="inlineStr"/>
       <c r="C1570" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (ex ST22)</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1570" t="inlineStr">
@@ -27974,7 +27974,7 @@
       <c r="B1572" t="inlineStr"/>
       <c r="C1572" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (ex-ST24)</t>
         </is>
       </c>
       <c r="D1572" t="inlineStr">
@@ -28060,7 +28060,7 @@
       <c r="B1577" t="inlineStr"/>
       <c r="C1577" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (ex NT32)</t>
         </is>
       </c>
       <c r="D1577" t="inlineStr">
@@ -28096,7 +28096,7 @@
       <c r="B1579" t="inlineStr"/>
       <c r="C1579" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (ex WT28)</t>
         </is>
       </c>
       <c r="D1579" t="inlineStr">
@@ -28290,7 +28290,7 @@
       <c r="B1590" t="inlineStr"/>
       <c r="C1590" t="inlineStr">
         <is>
-          <t>ORA Coal</t>
+          <t>ORA Shunter</t>
         </is>
       </c>
       <c r="D1590" t="inlineStr">
@@ -29349,7 +29349,7 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Maintenance Train</t>
+          <t>PN Empty Containerised Logs</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -30085,7 +30085,7 @@
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -34695,7 +34695,7 @@
       <c r="B344" t="inlineStr"/>
       <c r="C344" t="inlineStr">
         <is>
-          <t>ORA Coal</t>
+          <t>ORA Shunter</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -39685,7 +39685,7 @@
       <c r="B625" t="inlineStr"/>
       <c r="C625" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Containerised Freight</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
@@ -39717,7 +39717,7 @@
       <c r="B627" t="inlineStr"/>
       <c r="C627" t="inlineStr">
         <is>
-          <t>SSR Manildra Grain Shuttle</t>
+          <t>SSR Light Engine Movement</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
@@ -45489,7 +45489,7 @@
       <c r="B951" t="inlineStr"/>
       <c r="C951" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>Loaded Coal</t>
         </is>
       </c>
       <c r="D951" t="inlineStr">
@@ -45571,7 +45571,7 @@
       <c r="B956" t="inlineStr"/>
       <c r="C956" t="inlineStr">
         <is>
-          <t>SSR Manildra Grain Shuttle</t>
+          <t>SSR Containerised Freight</t>
         </is>
       </c>
       <c r="D956" t="inlineStr">
@@ -45607,7 +45607,7 @@
       <c r="B958" t="inlineStr"/>
       <c r="C958" t="inlineStr">
         <is>
-          <t>Aurizon Empty Grain</t>
+          <t>Aurizon Wagon Transfer</t>
         </is>
       </c>
       <c r="D958" t="inlineStr">
@@ -49767,7 +49767,7 @@
       <c r="B1191" t="inlineStr"/>
       <c r="C1191" t="inlineStr">
         <is>
-          <t>JBR Indian Pacific</t>
+          <t>JBR Indian Pacifc</t>
         </is>
       </c>
       <c r="D1191" t="inlineStr">
@@ -50677,7 +50677,7 @@
       <c r="B1242" t="inlineStr"/>
       <c r="C1242" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1242" t="inlineStr">
@@ -50785,7 +50785,7 @@
       <c r="B1248" t="inlineStr"/>
       <c r="C1248" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1248" t="inlineStr">
@@ -51447,7 +51447,7 @@
       <c r="B1285" t="inlineStr"/>
       <c r="C1285" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1285" t="inlineStr">
@@ -51789,7 +51789,7 @@
       <c r="B1304" t="inlineStr"/>
       <c r="C1304" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (ex ST22)</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1304" t="inlineStr">
@@ -52799,7 +52799,7 @@
       <c r="B1361" t="inlineStr"/>
       <c r="C1361" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D1361" t="inlineStr">
@@ -54107,7 +54107,7 @@
       <c r="B1439" t="inlineStr"/>
       <c r="C1439" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1439" t="inlineStr">
@@ -54125,7 +54125,7 @@
       <c r="B1440" t="inlineStr"/>
       <c r="C1440" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Hunter Railcar Transfer</t>
         </is>
       </c>
       <c r="D1440" t="inlineStr">
@@ -54265,7 +54265,7 @@
       <c r="B1448" t="inlineStr"/>
       <c r="C1448" t="inlineStr">
         <is>
-          <t>SSR Light Engine Movement</t>
+          <t>SSR Light Engine</t>
         </is>
       </c>
       <c r="D1448" t="inlineStr">
@@ -54373,7 +54373,7 @@
       <c r="B1454" t="inlineStr"/>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>Swift Trip Train</t>
+          <t>SSR Empty Manildra Flour</t>
         </is>
       </c>
       <c r="D1454" t="inlineStr">
@@ -54499,7 +54499,7 @@
       <c r="B1461" t="inlineStr"/>
       <c r="C1461" t="inlineStr">
         <is>
-          <t>PN Empty Fuel</t>
+          <t>PN Fuel Train</t>
         </is>
       </c>
       <c r="D1461" t="inlineStr">
@@ -56455,7 +56455,7 @@
       <c r="B1575" t="inlineStr"/>
       <c r="C1575" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (ex-ST24)</t>
         </is>
       </c>
       <c r="D1575" t="inlineStr">
@@ -56491,7 +56491,7 @@
       <c r="B1577" t="inlineStr"/>
       <c r="C1577" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (ex NT32)</t>
         </is>
       </c>
       <c r="D1577" t="inlineStr">
@@ -56527,7 +56527,7 @@
       <c r="B1579" t="inlineStr"/>
       <c r="C1579" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (ex WT28)</t>
         </is>
       </c>
       <c r="D1579" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -742,7 +742,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>V/Line Light Engine</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -796,7 +796,7 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1102,7 +1102,7 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>North East Line BG Service</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1174,7 +1174,7 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>V/Line Empty Cars Provisioning</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1246,7 +1246,7 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>V/Line Empty Cars Provisioning</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1958,7 +1958,7 @@
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2534,7 +2534,7 @@
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5246,7 +5246,7 @@
       <c r="B273" t="inlineStr"/>
       <c r="C273" t="inlineStr">
         <is>
-          <t>PN Grain Shuttle</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -5782,7 +5782,7 @@
       <c r="B303" t="inlineStr"/>
       <c r="C303" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Light Engine Movement</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -9526,7 +9526,7 @@
       <c r="B525" t="inlineStr"/>
       <c r="C525" t="inlineStr">
         <is>
-          <t>SSR Light Engine Movement</t>
+          <t>SSR Manildra Grain Shuttle</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
@@ -12070,7 +12070,7 @@
       <c r="B668" t="inlineStr"/>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Aurizon Empty Ore</t>
+          <t>Aurizon Loaded Ore</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
@@ -12124,7 +12124,7 @@
       <c r="B671" t="inlineStr"/>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Copper</t>
+          <t>Aurizon Empty Copper</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
@@ -12414,7 +12414,7 @@
       <c r="B688" t="inlineStr"/>
       <c r="C688" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Hunter Railcar Transfer</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
@@ -12940,7 +12940,7 @@
       <c r="B719" t="inlineStr"/>
       <c r="C719" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
@@ -13098,7 +13098,7 @@
       <c r="B728" t="inlineStr"/>
       <c r="C728" t="inlineStr">
         <is>
-          <t>South Coast Service</t>
+          <t>Sydney Trains Empty Car Transfer</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
@@ -13952,7 +13952,7 @@
       <c r="B777" t="inlineStr"/>
       <c r="C777" t="inlineStr">
         <is>
-          <t>SSR Grain Shuttle</t>
+          <t>SSR BG Grain</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
@@ -19010,7 +19010,11 @@
         </is>
       </c>
       <c r="B1071" t="inlineStr"/>
-      <c r="C1071" t="inlineStr"/>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>Maintenance Train</t>
+        </is>
+      </c>
       <c r="D1071" t="inlineStr">
         <is>
           <t>2026-04-17 22:24:00</t>
@@ -19186,7 +19190,7 @@
       <c r="B1082" t="inlineStr"/>
       <c r="C1082" t="inlineStr">
         <is>
-          <t>PN Empty Aggregate</t>
+          <t>PN Minerals</t>
         </is>
       </c>
       <c r="D1082" t="inlineStr">
@@ -29269,7 +29273,11 @@
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Maintenance Train</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>2026-04-17 22:24:00</t>
@@ -31389,7 +31397,7 @@
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr">
         <is>
-          <t>PN Empty Aggregate</t>
+          <t>PN Minerals</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -33867,7 +33875,7 @@
       <c r="B296" t="inlineStr"/>
       <c r="C296" t="inlineStr">
         <is>
-          <t>PN Grain Shuttle</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -39717,7 +39725,7 @@
       <c r="B627" t="inlineStr"/>
       <c r="C627" t="inlineStr">
         <is>
-          <t>SSR Light Engine Movement</t>
+          <t>SSR Manildra Grain Shuttle</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
@@ -39933,7 +39941,7 @@
       <c r="B639" t="inlineStr"/>
       <c r="C639" t="inlineStr">
         <is>
-          <t>SSR Grain Shuttle</t>
+          <t>SSR BG Grain</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
@@ -40767,7 +40775,7 @@
       <c r="B686" t="inlineStr"/>
       <c r="C686" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Light Engine Movement</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
@@ -41843,7 +41851,7 @@
       <c r="B746" t="inlineStr"/>
       <c r="C746" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
@@ -43835,7 +43843,7 @@
       <c r="B858" t="inlineStr"/>
       <c r="C858" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>V/Line Empty Cars Provisioning</t>
         </is>
       </c>
       <c r="D858" t="inlineStr">
@@ -43853,7 +43861,7 @@
       <c r="B859" t="inlineStr"/>
       <c r="C859" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>V/Line Empty Cars Provisioning</t>
         </is>
       </c>
       <c r="D859" t="inlineStr">
@@ -47017,7 +47025,7 @@
       <c r="B1037" t="inlineStr"/>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>V/Line Light Engine</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1037" t="inlineStr">
@@ -48022,7 +48030,7 @@
       <c r="B1093" t="inlineStr"/>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1093" t="inlineStr">
@@ -48537,7 +48545,7 @@
       <c r="B1122" t="inlineStr"/>
       <c r="C1122" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Copper</t>
+          <t>Aurizon Empty Copper</t>
         </is>
       </c>
       <c r="D1122" t="inlineStr">
@@ -48825,7 +48833,7 @@
       <c r="B1138" t="inlineStr"/>
       <c r="C1138" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Hunter Railcar Transfer</t>
         </is>
       </c>
       <c r="D1138" t="inlineStr">
@@ -49677,7 +49685,7 @@
       <c r="B1186" t="inlineStr"/>
       <c r="C1186" t="inlineStr">
         <is>
-          <t>South Coast Service</t>
+          <t>Sydney Trains Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1186" t="inlineStr">
@@ -49965,7 +49973,7 @@
       <c r="B1202" t="inlineStr"/>
       <c r="C1202" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D1202" t="inlineStr">
@@ -51343,7 +51351,7 @@
       <c r="B1279" t="inlineStr"/>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1279" t="inlineStr">
@@ -52059,7 +52067,7 @@
       <c r="B1319" t="inlineStr"/>
       <c r="C1319" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>North East Line BG Service</t>
         </is>
       </c>
       <c r="D1319" t="inlineStr">
@@ -54035,7 +54043,7 @@
       <c r="B1435" t="inlineStr"/>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>Aurizon Empty Ore</t>
+          <t>Aurizon Loaded Ore</t>
         </is>
       </c>
       <c r="D1435" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -562,7 +562,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -10760,7 +10760,7 @@
       <c r="B594" t="inlineStr"/>
       <c r="C594" t="inlineStr">
         <is>
-          <t>SCT Steel Shunt / Wine Train</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
@@ -17576,7 +17576,7 @@
       <c r="B987" t="inlineStr"/>
       <c r="C987" t="inlineStr">
         <is>
-          <t>QUBE Containerised Freight</t>
+          <t>Qube Trip Train</t>
         </is>
       </c>
       <c r="D987" t="inlineStr">
@@ -36285,7 +36285,7 @@
       <c r="B434" t="inlineStr"/>
       <c r="C434" t="inlineStr">
         <is>
-          <t>QUBE Containerised Freight</t>
+          <t>Qube Trip Train</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -37203,7 +37203,7 @@
       <c r="B485" t="inlineStr"/>
       <c r="C485" t="inlineStr">
         <is>
-          <t>SCT Steel Shunt / Wine Train</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -41947,7 +41947,7 @@
       <c r="B751" t="inlineStr"/>
       <c r="C751" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D751" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -3878,7 +3878,11 @@
         </is>
       </c>
       <c r="B194" t="inlineStr"/>
-      <c r="C194" t="inlineStr"/>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Aurizon Light Engine Movement</t>
+        </is>
+      </c>
       <c r="D194" t="inlineStr">
         <is>
           <t>2026-04-03 08:48:43</t>
@@ -4674,7 +4678,7 @@
       <c r="B241" t="inlineStr"/>
       <c r="C241" t="inlineStr">
         <is>
-          <t>QUBE Light Engine</t>
+          <t>Qube Light Engine</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -7108,7 +7112,7 @@
       <c r="B378" t="inlineStr"/>
       <c r="C378" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Coal</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -9612,7 +9616,7 @@
       <c r="B530" t="inlineStr"/>
       <c r="C530" t="inlineStr">
         <is>
-          <t>SSR Limestone</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
@@ -12608,7 +12612,7 @@
       <c r="B699" t="inlineStr"/>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
@@ -12644,7 +12648,7 @@
       <c r="B701" t="inlineStr"/>
       <c r="C701" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
@@ -16910,7 +16914,7 @@
       <c r="B950" t="inlineStr"/>
       <c r="C950" t="inlineStr">
         <is>
-          <t>QUBE BlueScope Steel</t>
+          <t>QUBE Light Engine</t>
         </is>
       </c>
       <c r="D950" t="inlineStr">
@@ -18876,7 +18880,7 @@
       <c r="B1063" t="inlineStr"/>
       <c r="C1063" t="inlineStr">
         <is>
-          <t>South Coast Service</t>
+          <t>Sydney Trains Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1063" t="inlineStr">
@@ -19666,7 +19670,7 @@
       <c r="B1110" t="inlineStr"/>
       <c r="C1110" t="inlineStr">
         <is>
-          <t>QUBE Containerised Freight</t>
+          <t>QUBE Maryvale Paper Train</t>
         </is>
       </c>
       <c r="D1110" t="inlineStr">
@@ -33981,7 +33985,7 @@
       <c r="B301" t="inlineStr"/>
       <c r="C301" t="inlineStr">
         <is>
-          <t>QUBE BlueScope Steel</t>
+          <t>QUBE Light Engine</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -34013,7 +34017,7 @@
       <c r="B303" t="inlineStr"/>
       <c r="C303" t="inlineStr">
         <is>
-          <t>QUBE Containerised Freight</t>
+          <t>QUBE Maryvale Paper Train</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -44705,7 +44709,7 @@
       <c r="B905" t="inlineStr"/>
       <c r="C905" t="inlineStr">
         <is>
-          <t>QUBE Light Engine</t>
+          <t>Qube Light Engine</t>
         </is>
       </c>
       <c r="D905" t="inlineStr">
@@ -51371,7 +51375,7 @@
       <c r="B1279" t="inlineStr"/>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1279" t="inlineStr">
@@ -51389,7 +51393,7 @@
       <c r="B1280" t="inlineStr"/>
       <c r="C1280" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1280" t="inlineStr">
@@ -52405,7 +52409,11 @@
         </is>
       </c>
       <c r="B1337" t="inlineStr"/>
-      <c r="C1337" t="inlineStr"/>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>Aurizon Light Engine Movement</t>
+        </is>
+      </c>
       <c r="D1337" t="inlineStr">
         <is>
           <t>2026-04-03 08:48:43</t>
@@ -52863,7 +52871,7 @@
       <c r="B1363" t="inlineStr"/>
       <c r="C1363" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Coal</t>
         </is>
       </c>
       <c r="D1363" t="inlineStr">
@@ -53599,7 +53607,7 @@
       <c r="B1409" t="inlineStr"/>
       <c r="C1409" t="inlineStr">
         <is>
-          <t>SSR Limestone</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1409" t="inlineStr">
@@ -55583,7 +55591,7 @@
       <c r="B1525" t="inlineStr"/>
       <c r="C1525" t="inlineStr">
         <is>
-          <t>South Coast Service</t>
+          <t>Sydney Trains Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1525" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -8056,7 +8056,7 @@
       <c r="B434" t="inlineStr"/>
       <c r="C434" t="inlineStr">
         <is>
-          <t>V/Line Light Engine</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -11686,7 +11686,7 @@
       <c r="B646" t="inlineStr"/>
       <c r="C646" t="inlineStr">
         <is>
-          <t>PN Empty BG Grain</t>
+          <t>PN Loaded BG Grain</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
@@ -12414,7 +12414,7 @@
       <c r="B688" t="inlineStr"/>
       <c r="C688" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
@@ -18718,7 +18718,7 @@
       <c r="B1054" t="inlineStr"/>
       <c r="C1054" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1054" t="inlineStr">
@@ -18880,7 +18880,7 @@
       <c r="B1063" t="inlineStr"/>
       <c r="C1063" t="inlineStr">
         <is>
-          <t>Sydney Trains Empty Car Transfer</t>
+          <t>NSW Trainlink South Coast Service</t>
         </is>
       </c>
       <c r="D1063" t="inlineStr">
@@ -41713,7 +41713,7 @@
       <c r="B737" t="inlineStr"/>
       <c r="C737" t="inlineStr">
         <is>
-          <t>PN Empty BG Grain</t>
+          <t>PN Loaded BG Grain</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
@@ -42597,7 +42597,7 @@
       <c r="B787" t="inlineStr"/>
       <c r="C787" t="inlineStr">
         <is>
-          <t>V/Line Light Engine</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D787" t="inlineStr">
@@ -51321,7 +51321,7 @@
       <c r="B1276" t="inlineStr"/>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1276" t="inlineStr">
@@ -51533,7 +51533,7 @@
       <c r="B1288" t="inlineStr"/>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1288" t="inlineStr">
@@ -55591,7 +55591,7 @@
       <c r="B1525" t="inlineStr"/>
       <c r="C1525" t="inlineStr">
         <is>
-          <t>Sydney Trains Empty Car Transfer</t>
+          <t>NSW Trainlink South Coast Service</t>
         </is>
       </c>
       <c r="D1525" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -12468,7 +12468,7 @@
       <c r="B691" t="inlineStr"/>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Hunter Railcar Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
@@ -12540,7 +12540,7 @@
       <c r="B695" t="inlineStr"/>
       <c r="C695" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
@@ -12940,7 +12940,7 @@
       <c r="B719" t="inlineStr"/>
       <c r="C719" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>Empty Car Provisioning (Forms SN34)</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
@@ -47626,7 +47626,7 @@
       <c r="B1069" t="inlineStr"/>
       <c r="C1069" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>Empty Car Provisioning (Forms SN34)</t>
         </is>
       </c>
       <c r="D1069" t="inlineStr">
@@ -54197,7 +54197,7 @@
       <c r="B1442" t="inlineStr"/>
       <c r="C1442" t="inlineStr">
         <is>
-          <t>Hunter Railcar Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1442" t="inlineStr">
@@ -54233,7 +54233,7 @@
       <c r="B1444" t="inlineStr"/>
       <c r="C1444" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1444" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -22024,7 +22024,7 @@
       <c r="B1241" t="inlineStr"/>
       <c r="C1241" t="inlineStr">
         <is>
-          <t>Ballarat - Melbourne Via Melton</t>
+          <t>Ararat - Melbourne Via Ballarat</t>
         </is>
       </c>
       <c r="D1241" t="inlineStr">
@@ -47698,7 +47698,7 @@
       <c r="B1073" t="inlineStr"/>
       <c r="C1073" t="inlineStr">
         <is>
-          <t>Ballarat - Melbourne Via Melton</t>
+          <t>Ararat - Melbourne Via Ballarat</t>
         </is>
       </c>
       <c r="D1073" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -22060,7 +22060,7 @@
       <c r="B1243" t="inlineStr"/>
       <c r="C1243" t="inlineStr">
         <is>
-          <t>Ballarat - Melbourne Via Melton</t>
+          <t>Ararat - Melbourne Via Ballarat</t>
         </is>
       </c>
       <c r="D1243" t="inlineStr">
@@ -46941,7 +46941,7 @@
       <c r="B1031" t="inlineStr"/>
       <c r="C1031" t="inlineStr">
         <is>
-          <t>Ballarat - Melbourne Via Melton</t>
+          <t>Ararat - Melbourne Via Ballarat</t>
         </is>
       </c>
       <c r="D1031" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -22042,7 +22042,7 @@
       <c r="B1242" t="inlineStr"/>
       <c r="C1242" t="inlineStr">
         <is>
-          <t>Ballarat - Melbourne Via Melton</t>
+          <t>Ararat - Melbourne Via Ballarat</t>
         </is>
       </c>
       <c r="D1242" t="inlineStr">
@@ -47391,7 +47391,7 @@
       <c r="B1056" t="inlineStr"/>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>Ballarat - Melbourne Via Melton</t>
+          <t>Ararat - Melbourne Via Ballarat</t>
         </is>
       </c>
       <c r="D1056" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1012,7 +1012,7 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Gippsland Line Service</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1246,7 +1246,7 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>V/Line Empty Cars Provisioning</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1886,7 +1886,7 @@
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -1958,7 +1958,7 @@
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>North Eastern Line BG Service</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2084,7 +2084,7 @@
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2246,7 +2246,7 @@
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2480,7 +2480,7 @@
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -2804,7 +2804,7 @@
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -5944,7 +5944,7 @@
       <c r="B312" t="inlineStr"/>
       <c r="C312" t="inlineStr">
         <is>
-          <t>PN Grain Shuttle</t>
+          <t>PN Cootamundra Shunter</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -9304,7 +9304,7 @@
       <c r="B512" t="inlineStr"/>
       <c r="C512" t="inlineStr">
         <is>
-          <t>BL28</t>
+          <t>PN Empty BG Grain</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
@@ -9322,7 +9322,7 @@
       <c r="B513" t="inlineStr"/>
       <c r="C513" t="inlineStr">
         <is>
-          <t>PN Empty BG Grain</t>
+          <t>BL29</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
@@ -12464,7 +12464,7 @@
       <c r="B691" t="inlineStr"/>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
@@ -12554,7 +12554,7 @@
       <c r="B696" t="inlineStr"/>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
@@ -18558,7 +18558,7 @@
       <c r="B1044" t="inlineStr"/>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1044" t="inlineStr">
@@ -32487,7 +32487,7 @@
       <c r="B212" t="inlineStr"/>
       <c r="C212" t="inlineStr">
         <is>
-          <t>PN Grain Shuttle</t>
+          <t>PN Cootamundra Shunter</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -35093,7 +35093,7 @@
       <c r="B361" t="inlineStr"/>
       <c r="C361" t="inlineStr">
         <is>
-          <t>BL28</t>
+          <t>PN Empty BG Grain</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -36741,7 +36741,7 @@
       <c r="B455" t="inlineStr"/>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -39871,7 +39871,7 @@
       <c r="B630" t="inlineStr"/>
       <c r="C630" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
@@ -41349,7 +41349,7 @@
       <c r="B713" t="inlineStr"/>
       <c r="C713" t="inlineStr">
         <is>
-          <t>PN Empty BG Grain</t>
+          <t>BL29</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
@@ -41759,7 +41759,7 @@
       <c r="B736" t="inlineStr"/>
       <c r="C736" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
@@ -44057,7 +44057,7 @@
       <c r="B865" t="inlineStr"/>
       <c r="C865" t="inlineStr">
         <is>
-          <t>V/Line Empty Cars Provisioning</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
@@ -50169,7 +50169,7 @@
       <c r="B1208" t="inlineStr"/>
       <c r="C1208" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>North Eastern Line BG Service</t>
         </is>
       </c>
       <c r="D1208" t="inlineStr">
@@ -50557,7 +50557,7 @@
       <c r="B1230" t="inlineStr"/>
       <c r="C1230" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1230" t="inlineStr">
@@ -51259,7 +51259,7 @@
       <c r="B1269" t="inlineStr"/>
       <c r="C1269" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1269" t="inlineStr">
@@ -51313,7 +51313,7 @@
       <c r="B1272" t="inlineStr"/>
       <c r="C1272" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Gippsland Line Service</t>
         </is>
       </c>
       <c r="D1272" t="inlineStr">
@@ -51651,7 +51651,7 @@
       <c r="B1291" t="inlineStr"/>
       <c r="C1291" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1291" t="inlineStr">
@@ -54315,7 +54315,7 @@
       <c r="B1445" t="inlineStr"/>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1445" t="inlineStr">
@@ -54369,7 +54369,7 @@
       <c r="B1448" t="inlineStr"/>
       <c r="C1448" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1448" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -490,7 +490,7 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1264,7 +1264,7 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1372,7 +1372,7 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1656,7 +1656,7 @@
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2012,7 +2012,7 @@
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2282,7 +2282,7 @@
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning, ex 8464</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5192,7 +5192,7 @@
       <c r="B270" t="inlineStr"/>
       <c r="C270" t="inlineStr">
         <is>
-          <t>PN Port Waratah Shunter</t>
+          <t>PN Light Engine Movement</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -6066,7 +6066,7 @@
       <c r="B319" t="inlineStr"/>
       <c r="C319" t="inlineStr">
         <is>
-          <t>PN Cement</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -11060,7 +11060,7 @@
       <c r="B611" t="inlineStr"/>
       <c r="C611" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer</t>
+          <t>NSW TrainLink Xplorer</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
@@ -12174,7 +12174,7 @@
       <c r="B674" t="inlineStr"/>
       <c r="C674" t="inlineStr">
         <is>
-          <t>Aurizon Empty Copper</t>
+          <t>Aurizon Loaded Copper</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
@@ -18162,7 +18162,7 @@
       <c r="B1022" t="inlineStr"/>
       <c r="C1022" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D1022" t="inlineStr">
@@ -19294,7 +19294,7 @@
       <c r="B1088" t="inlineStr"/>
       <c r="C1088" t="inlineStr">
         <is>
-          <t>PN Minerals</t>
+          <t>PN Empty Aggregate</t>
         </is>
       </c>
       <c r="D1088" t="inlineStr">
@@ -22254,7 +22254,7 @@
       <c r="B1254" t="inlineStr"/>
       <c r="C1254" t="inlineStr">
         <is>
-          <t>Ballarat - Melbourne Via Melton</t>
+          <t>Ararat - Melbourne Via Ballarat</t>
         </is>
       </c>
       <c r="D1254" t="inlineStr">
@@ -30375,7 +30375,7 @@
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -31683,7 +31683,7 @@
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr">
         <is>
-          <t>PN Minerals</t>
+          <t>PN Empty Aggregate</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -37159,7 +37159,7 @@
       <c r="B476" t="inlineStr"/>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -40507,7 +40507,7 @@
       <c r="B664" t="inlineStr"/>
       <c r="C664" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
@@ -41209,7 +41209,7 @@
       <c r="B703" t="inlineStr"/>
       <c r="C703" t="inlineStr">
         <is>
-          <t>Ballarat - Melbourne Via Melton</t>
+          <t>Ararat - Melbourne Via Ballarat</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
@@ -43323,7 +43323,7 @@
       <c r="B822" t="inlineStr"/>
       <c r="C822" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D822" t="inlineStr">
@@ -45187,7 +45187,7 @@
       <c r="B926" t="inlineStr"/>
       <c r="C926" t="inlineStr">
         <is>
-          <t>PN Cement</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D926" t="inlineStr">
@@ -45751,7 +45751,7 @@
       <c r="B958" t="inlineStr"/>
       <c r="C958" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D958" t="inlineStr">
@@ -48835,7 +48835,7 @@
       <c r="B1131" t="inlineStr"/>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>Aurizon Empty Copper</t>
+          <t>Aurizon Loaded Copper</t>
         </is>
       </c>
       <c r="D1131" t="inlineStr">
@@ -49515,7 +49515,7 @@
       <c r="B1169" t="inlineStr"/>
       <c r="C1169" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1169" t="inlineStr">
@@ -49867,7 +49867,7 @@
       <c r="B1189" t="inlineStr"/>
       <c r="C1189" t="inlineStr">
         <is>
-          <t>PN Port Waratah Shunter</t>
+          <t>PN Light Engine Movement</t>
         </is>
       </c>
       <c r="D1189" t="inlineStr">
@@ -52195,7 +52195,7 @@
       <c r="B1319" t="inlineStr"/>
       <c r="C1319" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning, ex 8464</t>
         </is>
       </c>
       <c r="D1319" t="inlineStr">
@@ -54197,7 +54197,7 @@
       <c r="B1436" t="inlineStr"/>
       <c r="C1436" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer</t>
+          <t>NSW TrainLink Xplorer</t>
         </is>
       </c>
       <c r="D1436" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -508,7 +508,7 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Northeast Line BG Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -814,7 +814,7 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -850,7 +850,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1084,7 +1084,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>North East Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1174,7 +1174,7 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>V/Line Empty Cars Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1246,7 +1246,7 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1728,7 +1728,7 @@
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -1836,7 +1836,7 @@
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -1922,7 +1922,7 @@
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2336,7 +2336,7 @@
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2372,7 +2372,7 @@
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -2534,7 +2534,7 @@
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning, pre 8145</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -2606,7 +2606,7 @@
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -2660,7 +2660,7 @@
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -2678,7 +2678,7 @@
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3124,7 +3124,7 @@
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>QUBE Trip Train</t>
+          <t>QUBE Containerised Freight</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -6102,7 +6102,7 @@
       <c r="B321" t="inlineStr"/>
       <c r="C321" t="inlineStr">
         <is>
-          <t>PN Garbage Train</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -10292,7 +10292,7 @@
       <c r="B568" t="inlineStr"/>
       <c r="C568" t="inlineStr">
         <is>
-          <t>SRS Light Engine</t>
+          <t>SRS Wagon Transfer</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
@@ -15392,7 +15392,7 @@
       <c r="B859" t="inlineStr"/>
       <c r="C859" t="inlineStr">
         <is>
-          <t>PN Trip Train</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D859" t="inlineStr">
@@ -17126,7 +17126,7 @@
       <c r="B962" t="inlineStr"/>
       <c r="C962" t="inlineStr">
         <is>
-          <t>QUBE Container Shuttle / Grain Shuttle</t>
+          <t>QUBE Containerised Grain</t>
         </is>
       </c>
       <c r="D962" t="inlineStr">
@@ -17324,7 +17324,7 @@
       <c r="B973" t="inlineStr"/>
       <c r="C973" t="inlineStr">
         <is>
-          <t>QUBE Empty Containerised Ore</t>
+          <t>QUBE Loaded Containerised Ore</t>
         </is>
       </c>
       <c r="D973" t="inlineStr">
@@ -18270,7 +18270,7 @@
       <c r="B1028" t="inlineStr"/>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>North Eastern Line BG Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D1028" t="inlineStr">
@@ -18786,7 +18786,7 @@
       <c r="B1058" t="inlineStr"/>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>Additional Bathurst Service</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D1058" t="inlineStr">
@@ -18858,7 +18858,7 @@
       <c r="B1062" t="inlineStr"/>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D1062" t="inlineStr">
@@ -30461,7 +30461,7 @@
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>QUBE Trip Train</t>
+          <t>QUBE Containerised Freight</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -31185,7 +31185,7 @@
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>QUBE Empty Containerised Ore</t>
+          <t>QUBE Loaded Containerised Ore</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -38325,7 +38325,7 @@
       <c r="B541" t="inlineStr"/>
       <c r="C541" t="inlineStr">
         <is>
-          <t>North Eastern Line BG Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -39059,7 +39059,7 @@
       <c r="B582" t="inlineStr"/>
       <c r="C582" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
@@ -42141,7 +42141,7 @@
       <c r="B755" t="inlineStr"/>
       <c r="C755" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning, pre 8145</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
@@ -43305,7 +43305,7 @@
       <c r="B821" t="inlineStr"/>
       <c r="C821" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D821" t="inlineStr">
@@ -44133,7 +44133,7 @@
       <c r="B867" t="inlineStr"/>
       <c r="C867" t="inlineStr">
         <is>
-          <t>V/Line Empty Cars Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D867" t="inlineStr">
@@ -44151,7 +44151,7 @@
       <c r="B868" t="inlineStr"/>
       <c r="C868" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D868" t="inlineStr">
@@ -44169,7 +44169,7 @@
       <c r="B869" t="inlineStr"/>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D869" t="inlineStr">
@@ -45061,7 +45061,7 @@
       <c r="B919" t="inlineStr"/>
       <c r="C919" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D919" t="inlineStr">
@@ -45733,7 +45733,7 @@
       <c r="B957" t="inlineStr"/>
       <c r="C957" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D957" t="inlineStr">
@@ -45955,7 +45955,7 @@
       <c r="B970" t="inlineStr"/>
       <c r="C970" t="inlineStr">
         <is>
-          <t>PN Trip Train</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D970" t="inlineStr">
@@ -47333,7 +47333,7 @@
       <c r="B1047" t="inlineStr"/>
       <c r="C1047" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1047" t="inlineStr">
@@ -49813,7 +49813,7 @@
       <c r="B1186" t="inlineStr"/>
       <c r="C1186" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1186" t="inlineStr">
@@ -49903,7 +49903,7 @@
       <c r="B1191" t="inlineStr"/>
       <c r="C1191" t="inlineStr">
         <is>
-          <t>PN Garbage Train</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D1191" t="inlineStr">
@@ -50191,7 +50191,7 @@
       <c r="B1207" t="inlineStr"/>
       <c r="C1207" t="inlineStr">
         <is>
-          <t>Northeast Line BG Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D1207" t="inlineStr">
@@ -50687,7 +50687,7 @@
       <c r="B1235" t="inlineStr"/>
       <c r="C1235" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1235" t="inlineStr">
@@ -51335,7 +51335,7 @@
       <c r="B1271" t="inlineStr"/>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1271" t="inlineStr">
@@ -51389,7 +51389,7 @@
       <c r="B1274" t="inlineStr"/>
       <c r="C1274" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1274" t="inlineStr">
@@ -51763,7 +51763,7 @@
       <c r="B1295" t="inlineStr"/>
       <c r="C1295" t="inlineStr">
         <is>
-          <t>Additional Bathurst Service</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D1295" t="inlineStr">
@@ -52267,7 +52267,7 @@
       <c r="B1323" t="inlineStr"/>
       <c r="C1323" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1323" t="inlineStr">
@@ -52339,7 +52339,7 @@
       <c r="B1327" t="inlineStr"/>
       <c r="C1327" t="inlineStr">
         <is>
-          <t>North East Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D1327" t="inlineStr">
@@ -52429,7 +52429,7 @@
       <c r="B1332" t="inlineStr"/>
       <c r="C1332" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1332" t="inlineStr">
@@ -54053,7 +54053,7 @@
       <c r="B1428" t="inlineStr"/>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>SRS Light Engine</t>
+          <t>SRS Wagon Transfer</t>
         </is>
       </c>
       <c r="D1428" t="inlineStr">
@@ -55557,7 +55557,7 @@
       <c r="B1516" t="inlineStr"/>
       <c r="C1516" t="inlineStr">
         <is>
-          <t>QUBE Container Shuttle / Grain Shuttle</t>
+          <t>QUBE Containerised Grain</t>
         </is>
       </c>
       <c r="D1516" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -544,7 +544,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -958,7 +958,7 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1138,7 +1138,7 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1246,7 +1246,7 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1602,7 +1602,7 @@
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Empty V/Line Cars</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1958,7 +1958,7 @@
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>North Eastern Line BG Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2966,7 +2966,7 @@
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>North East Line SG Service</t>
+          <t>North East SG Line Service</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -3178,7 +3178,7 @@
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
-          <t>QUBE Shunter</t>
+          <t>QUBE BlueScope Steel Transfer</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -6102,7 +6102,7 @@
       <c r="B321" t="inlineStr"/>
       <c r="C321" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Cement - RailTrain Crewed</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -7198,7 +7198,7 @@
       <c r="B383" t="inlineStr"/>
       <c r="C383" t="inlineStr">
         <is>
-          <t>PN Coal</t>
+          <t>PN Port Waratah Shunter</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -8404,7 +8404,7 @@
       <c r="B456" t="inlineStr"/>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Aurizon Mineral Sands shuttle</t>
+          <t>Aurizon Mineral Sands Shuttle</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -9322,7 +9322,7 @@
       <c r="B513" t="inlineStr"/>
       <c r="C513" t="inlineStr">
         <is>
-          <t>PN Loaded BG Grain</t>
+          <t>PN Empty BG Grain</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
@@ -10472,7 +10472,7 @@
       <c r="B578" t="inlineStr"/>
       <c r="C578" t="inlineStr">
         <is>
-          <t>QUBE Loaded Balco &amp; Zinc</t>
+          <t>QUBE Loaded Zinc</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
@@ -10720,7 +10720,7 @@
       <c r="B592" t="inlineStr"/>
       <c r="C592" t="inlineStr">
         <is>
-          <t>SCT Intermodal</t>
+          <t>SCT Sadleirs Transfer</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
@@ -10987,7 +10987,7 @@
       <c r="B607" t="inlineStr"/>
       <c r="C607" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer</t>
+          <t>NSW Trainlink Empty Car Transfer (ex NP24)</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
@@ -11362,7 +11362,7 @@
       <c r="B628" t="inlineStr"/>
       <c r="C628" t="inlineStr">
         <is>
-          <t>QUBE Empty Aggregates</t>
+          <t>QUBE Loaded Aggregates</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
@@ -12608,7 +12608,7 @@
       <c r="B699" t="inlineStr"/>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
@@ -14768,7 +14768,7 @@
       <c r="B823" t="inlineStr"/>
       <c r="C823" t="inlineStr">
         <is>
-          <t>PN Steel Transfer</t>
+          <t>PN Infrabuild Steel</t>
         </is>
       </c>
       <c r="D823" t="inlineStr">
@@ -15852,7 +15852,7 @@
       <c r="B885" t="inlineStr"/>
       <c r="C885" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>Maintenance Train</t>
         </is>
       </c>
       <c r="D885" t="inlineStr">
@@ -16700,7 +16700,7 @@
       <c r="B937" t="inlineStr"/>
       <c r="C937" t="inlineStr">
         <is>
-          <t>Aurizon Cockburn Cement - Lime and Cement Train</t>
+          <t>Aurizon Cockburn Cement - Empty Lime and Cement Train</t>
         </is>
       </c>
       <c r="D937" t="inlineStr">
@@ -18822,7 +18822,7 @@
       <c r="B1060" t="inlineStr"/>
       <c r="C1060" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Southern Highlands Service</t>
         </is>
       </c>
       <c r="D1060" t="inlineStr">
@@ -22272,7 +22272,7 @@
       <c r="B1255" t="inlineStr"/>
       <c r="C1255" t="inlineStr">
         <is>
-          <t>Ballarat - Melbourne Via Melton</t>
+          <t>Ararat - Melbourne Via Ballarat</t>
         </is>
       </c>
       <c r="D1255" t="inlineStr">
@@ -33305,7 +33305,7 @@
       <c r="B257" t="inlineStr"/>
       <c r="C257" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -33769,7 +33769,7 @@
       <c r="B283" t="inlineStr"/>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -35047,7 +35047,7 @@
       <c r="B356" t="inlineStr"/>
       <c r="C356" t="inlineStr">
         <is>
-          <t>QUBE Empty Aggregates</t>
+          <t>QUBE Loaded Aggregates</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -35133,7 +35133,7 @@
       <c r="B361" t="inlineStr"/>
       <c r="C361" t="inlineStr">
         <is>
-          <t>QUBE Shunter</t>
+          <t>QUBE BlueScope Steel Transfer</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -35187,7 +35187,7 @@
       <c r="B364" t="inlineStr"/>
       <c r="C364" t="inlineStr">
         <is>
-          <t>PN Loaded BG Grain</t>
+          <t>PN Empty BG Grain</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -39803,7 +39803,7 @@
       <c r="B624" t="inlineStr"/>
       <c r="C624" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
@@ -40381,7 +40381,7 @@
       <c r="B657" t="inlineStr"/>
       <c r="C657" t="inlineStr">
         <is>
-          <t>PN Coal</t>
+          <t>PN Port Waratah Shunter</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
@@ -40741,7 +40741,7 @@
       <c r="B677" t="inlineStr"/>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Aurizon Mineral Sands shuttle</t>
+          <t>Aurizon Mineral Sands Shuttle</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
@@ -42899,7 +42899,7 @@
       <c r="B798" t="inlineStr"/>
       <c r="C798" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer</t>
+          <t>NSW Trainlink Empty Car Transfer (ex NP24)</t>
         </is>
       </c>
       <c r="D798" t="inlineStr">
@@ -44151,7 +44151,7 @@
       <c r="B868" t="inlineStr"/>
       <c r="C868" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D868" t="inlineStr">
@@ -45341,7 +45341,7 @@
       <c r="B935" t="inlineStr"/>
       <c r="C935" t="inlineStr">
         <is>
-          <t>PN Steel Transfer</t>
+          <t>PN Infrabuild Steel</t>
         </is>
       </c>
       <c r="D935" t="inlineStr">
@@ -46977,7 +46977,7 @@
       <c r="B1027" t="inlineStr"/>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Empty V/Line Cars</t>
         </is>
       </c>
       <c r="D1027" t="inlineStr">
@@ -49051,7 +49051,7 @@
       <c r="B1143" t="inlineStr"/>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>QUBE Loaded Balco &amp; Zinc</t>
+          <t>QUBE Loaded Zinc</t>
         </is>
       </c>
       <c r="D1143" t="inlineStr">
@@ -49903,7 +49903,7 @@
       <c r="B1191" t="inlineStr"/>
       <c r="C1191" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Cement - RailTrain Crewed</t>
         </is>
       </c>
       <c r="D1191" t="inlineStr">
@@ -50263,7 +50263,7 @@
       <c r="B1211" t="inlineStr"/>
       <c r="C1211" t="inlineStr">
         <is>
-          <t>North Eastern Line BG Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D1211" t="inlineStr">
@@ -50993,7 +50993,7 @@
       <c r="B1252" t="inlineStr"/>
       <c r="C1252" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1252" t="inlineStr">
@@ -51155,7 +51155,7 @@
       <c r="B1261" t="inlineStr"/>
       <c r="C1261" t="inlineStr">
         <is>
-          <t>Ballarat - Melbourne Via Melton</t>
+          <t>Ararat - Melbourne Via Ballarat</t>
         </is>
       </c>
       <c r="D1261" t="inlineStr">
@@ -52519,7 +52519,7 @@
       <c r="B1337" t="inlineStr"/>
       <c r="C1337" t="inlineStr">
         <is>
-          <t>North East Line SG Service</t>
+          <t>North East SG Line Service</t>
         </is>
       </c>
       <c r="D1337" t="inlineStr">
@@ -54125,7 +54125,7 @@
       <c r="B1432" t="inlineStr"/>
       <c r="C1432" t="inlineStr">
         <is>
-          <t>SCT Intermodal</t>
+          <t>SCT Sadleirs Transfer</t>
         </is>
       </c>
       <c r="D1432" t="inlineStr">
@@ -54765,7 +54765,7 @@
       <c r="B1468" t="inlineStr"/>
       <c r="C1468" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>Maintenance Train</t>
         </is>
       </c>
       <c r="D1468" t="inlineStr">
@@ -55357,7 +55357,7 @@
       <c r="B1504" t="inlineStr"/>
       <c r="C1504" t="inlineStr">
         <is>
-          <t>Aurizon Cockburn Cement - Lime and Cement Train</t>
+          <t>Aurizon Cockburn Cement - Empty Lime and Cement Train</t>
         </is>
       </c>
       <c r="D1504" t="inlineStr">
@@ -55785,7 +55785,7 @@
       <c r="B1530" t="inlineStr"/>
       <c r="C1530" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Southern Highlands Service</t>
         </is>
       </c>
       <c r="D1530" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -724,7 +724,7 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1174,7 +1174,7 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1462,7 +1462,7 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SouthWest Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2642,7 +2642,7 @@
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6732,7 +6732,7 @@
       <c r="B356" t="inlineStr"/>
       <c r="C356" t="inlineStr">
         <is>
-          <t>PN Grain</t>
+          <t>8253</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -7588,7 +7588,7 @@
       <c r="B406" t="inlineStr"/>
       <c r="C406" t="inlineStr">
         <is>
-          <t>PN Infrabuild Steel</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -9806,7 +9806,7 @@
       <c r="B541" t="inlineStr"/>
       <c r="C541" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -11150,7 +11150,7 @@
       <c r="B616" t="inlineStr"/>
       <c r="C616" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer</t>
+          <t>NSW Trainlink Empty Car Transfer</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
@@ -12278,7 +12278,7 @@
       <c r="B680" t="inlineStr"/>
       <c r="C680" t="inlineStr">
         <is>
-          <t>ORA Shunter</t>
+          <t>ORA Coal</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
@@ -12482,7 +12482,7 @@
       <c r="B692" t="inlineStr"/>
       <c r="C692" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
@@ -12990,7 +12990,7 @@
       <c r="B722" t="inlineStr"/>
       <c r="C722" t="inlineStr">
         <is>
-          <t>Additional Bathurst Service</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
@@ -13080,7 +13080,7 @@
       <c r="B727" t="inlineStr"/>
       <c r="C727" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Southern Highlands Service</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
@@ -15518,7 +15518,7 @@
       <c r="B866" t="inlineStr"/>
       <c r="C866" t="inlineStr">
         <is>
-          <t>PN Container Shuttle</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
@@ -20562,7 +20562,7 @@
       <c r="B1160" t="inlineStr"/>
       <c r="C1160" t="inlineStr">
         <is>
-          <t>Bendigo - Melbourne Via Sunbury</t>
+          <t>Echuca/Moama - Melbourne Via Bendigo or Heathcote</t>
         </is>
       </c>
       <c r="D1160" t="inlineStr">
@@ -28240,7 +28240,7 @@
       <c r="B1587" t="inlineStr"/>
       <c r="C1587" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1587" t="inlineStr">
@@ -28434,7 +28434,7 @@
       <c r="B1598" t="inlineStr"/>
       <c r="C1598" t="inlineStr">
         <is>
-          <t>ORA trip train</t>
+          <t>ORA Light Engine</t>
         </is>
       </c>
       <c r="D1598" t="inlineStr">
@@ -29263,7 +29263,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ORA trip train</t>
+          <t>ORA Light Engine</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -31203,7 +31203,7 @@
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>PN Infrabuild Steel</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -31529,7 +31529,7 @@
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr">
         <is>
-          <t>PN Grain</t>
+          <t>8253</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -36799,7 +36799,7 @@
       <c r="B456" t="inlineStr"/>
       <c r="C456" t="inlineStr">
         <is>
-          <t>SouthWest Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -37411,7 +37411,7 @@
       <c r="B490" t="inlineStr"/>
       <c r="C490" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
@@ -37501,7 +37501,7 @@
       <c r="B495" t="inlineStr"/>
       <c r="C495" t="inlineStr">
         <is>
-          <t>ORA Shunter</t>
+          <t>ORA Coal</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
@@ -40705,7 +40705,7 @@
       <c r="B675" t="inlineStr"/>
       <c r="C675" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Southern Highlands Service</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
@@ -44133,7 +44133,7 @@
       <c r="B867" t="inlineStr"/>
       <c r="C867" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D867" t="inlineStr">
@@ -44867,7 +44867,7 @@
       <c r="B908" t="inlineStr"/>
       <c r="C908" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D908" t="inlineStr">
@@ -47049,7 +47049,7 @@
       <c r="B1031" t="inlineStr"/>
       <c r="C1031" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer</t>
+          <t>NSW Trainlink Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1031" t="inlineStr">
@@ -51641,7 +51641,7 @@
       <c r="B1288" t="inlineStr"/>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>Additional Bathurst Service</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1288" t="inlineStr">
@@ -53909,7 +53909,7 @@
       <c r="B1420" t="inlineStr"/>
       <c r="C1420" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1420" t="inlineStr">
@@ -54409,7 +54409,7 @@
       <c r="B1448" t="inlineStr"/>
       <c r="C1448" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1448" t="inlineStr">
@@ -56037,7 +56037,7 @@
       <c r="B1544" t="inlineStr"/>
       <c r="C1544" t="inlineStr">
         <is>
-          <t>Bendigo - Melbourne Via Sunbury</t>
+          <t>Echuca/Moama - Melbourne Via Bendigo or Heathcote</t>
         </is>
       </c>
       <c r="D1544" t="inlineStr">
@@ -56847,7 +56847,7 @@
       <c r="B1589" t="inlineStr"/>
       <c r="C1589" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1589" t="inlineStr">
@@ -57095,7 +57095,7 @@
       <c r="B1603" t="inlineStr"/>
       <c r="C1603" t="inlineStr">
         <is>
-          <t>PN Container Shuttle</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D1603" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1638,7 +1638,7 @@
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1922,7 +1922,7 @@
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>North East Line BG Service</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3752,7 +3752,7 @@
       <c r="B186" t="inlineStr"/>
       <c r="C186" t="inlineStr">
         <is>
-          <t>SSR Light Engine</t>
+          <t>SSR Cement Trip Train</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -8752,7 +8752,7 @@
       <c r="B476" t="inlineStr"/>
       <c r="C476" t="inlineStr">
         <is>
-          <t>MRL Loaded Iron Ore</t>
+          <t>MRL Empty Iron Ore</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -8770,7 +8770,7 @@
       <c r="B477" t="inlineStr"/>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Aurizon Fuel Shunt/Wagon Transfer</t>
+          <t>Aurizon Loaded Grain</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -12482,7 +12482,7 @@
       <c r="B692" t="inlineStr"/>
       <c r="C692" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
@@ -12572,7 +12572,7 @@
       <c r="B697" t="inlineStr"/>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
@@ -12608,7 +12608,7 @@
       <c r="B699" t="inlineStr"/>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
@@ -13614,7 +13614,7 @@
       <c r="B758" t="inlineStr"/>
       <c r="C758" t="inlineStr">
         <is>
-          <t>SSR Empty Manildra Flour</t>
+          <t>SSR Loaded Manildra Flour</t>
         </is>
       </c>
       <c r="D758" t="inlineStr">
@@ -16500,7 +16500,7 @@
       <c r="B925" t="inlineStr"/>
       <c r="C925" t="inlineStr">
         <is>
-          <t>Watco Light Engine</t>
+          <t>Watco Trip Train</t>
         </is>
       </c>
       <c r="D925" t="inlineStr">
@@ -30583,7 +30583,7 @@
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Watco Light Engine</t>
+          <t>Watco Trip Train</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -36637,7 +36637,7 @@
       <c r="B447" t="inlineStr"/>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -43305,7 +43305,7 @@
       <c r="B821" t="inlineStr"/>
       <c r="C821" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>North East Line BG Service</t>
         </is>
       </c>
       <c r="D821" t="inlineStr">
@@ -46621,7 +46621,7 @@
       <c r="B1007" t="inlineStr"/>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>SSR Light Engine</t>
+          <t>SSR Cement Trip Train</t>
         </is>
       </c>
       <c r="D1007" t="inlineStr">
@@ -50903,7 +50903,7 @@
       <c r="B1247" t="inlineStr"/>
       <c r="C1247" t="inlineStr">
         <is>
-          <t>Aurizon Fuel Shunt/Wagon Transfer</t>
+          <t>Aurizon Loaded Grain</t>
         </is>
       </c>
       <c r="D1247" t="inlineStr">
@@ -50993,7 +50993,7 @@
       <c r="B1252" t="inlineStr"/>
       <c r="C1252" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1252" t="inlineStr">
@@ -53587,7 +53587,7 @@
       <c r="B1399" t="inlineStr"/>
       <c r="C1399" t="inlineStr">
         <is>
-          <t>MRL Loaded Iron Ore</t>
+          <t>MRL Empty Iron Ore</t>
         </is>
       </c>
       <c r="D1399" t="inlineStr">
@@ -54409,7 +54409,7 @@
       <c r="B1448" t="inlineStr"/>
       <c r="C1448" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1448" t="inlineStr">
@@ -54463,7 +54463,7 @@
       <c r="B1451" t="inlineStr"/>
       <c r="C1451" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1451" t="inlineStr">
@@ -54675,7 +54675,7 @@
       <c r="B1463" t="inlineStr"/>
       <c r="C1463" t="inlineStr">
         <is>
-          <t>SSR Empty Manildra Flour</t>
+          <t>SSR Loaded Manildra Flour</t>
         </is>
       </c>
       <c r="D1463" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1318,7 +1318,7 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1728,7 +1728,7 @@
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2534,7 +2534,7 @@
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning, pre 8145</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6750,7 +6750,7 @@
       <c r="B357" t="inlineStr"/>
       <c r="C357" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -9968,7 +9968,7 @@
       <c r="B550" t="inlineStr"/>
       <c r="C550" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
@@ -11736,7 +11736,7 @@
       <c r="B649" t="inlineStr"/>
       <c r="C649" t="inlineStr">
         <is>
-          <t>SCT Steel Shunt / Wine Train</t>
+          <t>SCT Wine Train / Steel Shunt</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
@@ -12120,7 +12120,7 @@
       <c r="B671" t="inlineStr"/>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Ore</t>
+          <t>Aurizon Empty Ore</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
@@ -12572,7 +12572,7 @@
       <c r="B697" t="inlineStr"/>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
@@ -12608,7 +12608,7 @@
       <c r="B699" t="inlineStr"/>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Hunter Railcar Transfer</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
@@ -17036,7 +17036,7 @@
       <c r="B957" t="inlineStr"/>
       <c r="C957" t="inlineStr">
         <is>
-          <t>QUBE BlueScope Steel</t>
+          <t>QUBE Grain</t>
         </is>
       </c>
       <c r="D957" t="inlineStr">
@@ -28046,7 +28046,7 @@
       <c r="B1576" t="inlineStr"/>
       <c r="C1576" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (ex NT32)</t>
         </is>
       </c>
       <c r="D1576" t="inlineStr">
@@ -28082,7 +28082,7 @@
       <c r="B1578" t="inlineStr"/>
       <c r="C1578" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1578" t="inlineStr">
@@ -28222,7 +28222,7 @@
       <c r="B1586" t="inlineStr"/>
       <c r="C1586" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (ex WT28)</t>
         </is>
       </c>
       <c r="D1586" t="inlineStr">
@@ -28416,7 +28416,7 @@
       <c r="B1597" t="inlineStr"/>
       <c r="C1597" t="inlineStr">
         <is>
-          <t>ORA Shunter</t>
+          <t>ORA Coal</t>
         </is>
       </c>
       <c r="D1597" t="inlineStr">
@@ -30547,7 +30547,7 @@
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -30565,7 +30565,7 @@
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -31095,7 +31095,7 @@
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>QUBE BlueScope Steel</t>
+          <t>QUBE Grain</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -33197,7 +33197,7 @@
       <c r="B251" t="inlineStr"/>
       <c r="C251" t="inlineStr">
         <is>
-          <t>SCT Steel Shunt / Wine Train</t>
+          <t>SCT Wine Train / Steel Shunt</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -34993,7 +34993,7 @@
       <c r="B353" t="inlineStr"/>
       <c r="C353" t="inlineStr">
         <is>
-          <t>ORA Shunter</t>
+          <t>ORA Coal</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -42141,7 +42141,7 @@
       <c r="B755" t="inlineStr"/>
       <c r="C755" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning, pre 8145</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
@@ -44169,7 +44169,7 @@
       <c r="B869" t="inlineStr"/>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D869" t="inlineStr">
@@ -44255,7 +44255,7 @@
       <c r="B874" t="inlineStr"/>
       <c r="C874" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D874" t="inlineStr">
@@ -46243,7 +46243,7 @@
       <c r="B986" t="inlineStr"/>
       <c r="C986" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D986" t="inlineStr">
@@ -49777,7 +49777,7 @@
       <c r="B1184" t="inlineStr"/>
       <c r="C1184" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (ex NT32)</t>
         </is>
       </c>
       <c r="D1184" t="inlineStr">
@@ -50993,7 +50993,7 @@
       <c r="B1252" t="inlineStr"/>
       <c r="C1252" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Hunter Railcar Transfer</t>
         </is>
       </c>
       <c r="D1252" t="inlineStr">
@@ -54337,7 +54337,7 @@
       <c r="B1444" t="inlineStr"/>
       <c r="C1444" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Ore</t>
+          <t>Aurizon Empty Ore</t>
         </is>
       </c>
       <c r="D1444" t="inlineStr">
@@ -54463,7 +54463,7 @@
       <c r="B1451" t="inlineStr"/>
       <c r="C1451" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1451" t="inlineStr">
@@ -56829,7 +56829,7 @@
       <c r="B1588" t="inlineStr"/>
       <c r="C1588" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (ex WT28)</t>
         </is>
       </c>
       <c r="D1588" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -2282,7 +2282,7 @@
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning, ex 8464</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -11736,7 +11736,7 @@
       <c r="B649" t="inlineStr"/>
       <c r="C649" t="inlineStr">
         <is>
-          <t>SCT Wine Train / Steel Shunt</t>
+          <t>SCT Steel Shunt / Wine Train</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
@@ -12102,7 +12102,7 @@
       <c r="B670" t="inlineStr"/>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Grain</t>
+          <t>Aurizon Wagon Transfer</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
@@ -13062,7 +13062,7 @@
       <c r="B726" t="inlineStr"/>
       <c r="C726" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
@@ -15816,7 +15816,7 @@
       <c r="B883" t="inlineStr"/>
       <c r="C883" t="inlineStr">
         <is>
-          <t>NR106</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D883" t="inlineStr">
@@ -17108,7 +17108,7 @@
       <c r="B961" t="inlineStr"/>
       <c r="C961" t="inlineStr">
         <is>
-          <t>QUBE BlueScope Steel Shunt</t>
+          <t>QUBE BlueScope Steel</t>
         </is>
       </c>
       <c r="D961" t="inlineStr">
@@ -18894,7 +18894,7 @@
       <c r="B1064" t="inlineStr"/>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Hunter Railcar Transfer</t>
         </is>
       </c>
       <c r="D1064" t="inlineStr">
@@ -28364,7 +28364,11 @@
         </is>
       </c>
       <c r="B1594" t="inlineStr"/>
-      <c r="C1594" t="inlineStr"/>
+      <c r="C1594" t="inlineStr">
+        <is>
+          <t>PN Loaded BG Grain</t>
+        </is>
+      </c>
       <c r="D1594" t="inlineStr">
         <is>
           <t>2026-04-11 18:03:14</t>
@@ -31495,7 +31499,11 @@
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
-      <c r="C153" t="inlineStr"/>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>PN Loaded BG Grain</t>
+        </is>
+      </c>
       <c r="D153" t="inlineStr">
         <is>
           <t>2026-04-11 18:03:14</t>
@@ -33197,7 +33205,7 @@
       <c r="B251" t="inlineStr"/>
       <c r="C251" t="inlineStr">
         <is>
-          <t>SCT Wine Train / Steel Shunt</t>
+          <t>SCT Steel Shunt / Wine Train</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -38591,7 +38599,7 @@
       <c r="B556" t="inlineStr"/>
       <c r="C556" t="inlineStr">
         <is>
-          <t>QUBE BlueScope Steel Shunt</t>
+          <t>QUBE BlueScope Steel</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
@@ -40033,7 +40041,7 @@
       <c r="B637" t="inlineStr"/>
       <c r="C637" t="inlineStr">
         <is>
-          <t>NR106</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
@@ -42105,7 +42113,7 @@
       <c r="B753" t="inlineStr"/>
       <c r="C753" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Grain</t>
+          <t>Aurizon Wagon Transfer</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
@@ -43007,7 +43015,7 @@
       <c r="B804" t="inlineStr"/>
       <c r="C804" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D804" t="inlineStr">
@@ -51781,7 +51789,7 @@
       <c r="B1296" t="inlineStr"/>
       <c r="C1296" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Hunter Railcar Transfer</t>
         </is>
       </c>
       <c r="D1296" t="inlineStr">
@@ -52195,7 +52203,7 @@
       <c r="B1319" t="inlineStr"/>
       <c r="C1319" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning, ex 8464</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1319" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1958,7 +1958,7 @@
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -6102,7 +6102,7 @@
       <c r="B321" t="inlineStr"/>
       <c r="C321" t="inlineStr">
         <is>
-          <t>PN Cement - RailTrain Crewed</t>
+          <t>PN Garbage Train</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -14934,7 +14934,11 @@
         </is>
       </c>
       <c r="B833" t="inlineStr"/>
-      <c r="C833" t="inlineStr"/>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>PN Intermodal</t>
+        </is>
+      </c>
       <c r="D833" t="inlineStr">
         <is>
           <t>2026-04-03 08:48:43</t>
@@ -19330,7 +19334,7 @@
       <c r="B1090" t="inlineStr"/>
       <c r="C1090" t="inlineStr">
         <is>
-          <t>PN Loaded Aggregate</t>
+          <t>PN Minerals</t>
         </is>
       </c>
       <c r="D1090" t="inlineStr">
@@ -19792,7 +19796,7 @@
       <c r="B1117" t="inlineStr"/>
       <c r="C1117" t="inlineStr">
         <is>
-          <t>QUBE Maryvale Paper Train</t>
+          <t>QUBE Containerised Freight</t>
         </is>
       </c>
       <c r="D1117" t="inlineStr">
@@ -38815,7 +38819,7 @@
       <c r="B568" t="inlineStr"/>
       <c r="C568" t="inlineStr">
         <is>
-          <t>PN Loaded Aggregate</t>
+          <t>PN Minerals</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
@@ -40605,7 +40609,7 @@
       <c r="B669" t="inlineStr"/>
       <c r="C669" t="inlineStr">
         <is>
-          <t>QUBE Maryvale Paper Train</t>
+          <t>QUBE Containerised Freight</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
@@ -49911,7 +49915,7 @@
       <c r="B1191" t="inlineStr"/>
       <c r="C1191" t="inlineStr">
         <is>
-          <t>PN Cement - RailTrain Crewed</t>
+          <t>PN Garbage Train</t>
         </is>
       </c>
       <c r="D1191" t="inlineStr">
@@ -50271,7 +50275,7 @@
       <c r="B1211" t="inlineStr"/>
       <c r="C1211" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1211" t="inlineStr">
@@ -54915,7 +54919,11 @@
         </is>
       </c>
       <c r="B1476" t="inlineStr"/>
-      <c r="C1476" t="inlineStr"/>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>PN Intermodal</t>
+        </is>
+      </c>
       <c r="D1476" t="inlineStr">
         <is>
           <t>2026-04-03 08:48:43</t>

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1246,7 +1246,7 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2534,7 +2534,7 @@
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -2642,7 +2642,7 @@
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -10328,7 +10328,7 @@
       <c r="B570" t="inlineStr"/>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Aurizon Empty Grain</t>
+          <t>SHUNT</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
@@ -15324,7 +15324,7 @@
       <c r="B855" t="inlineStr"/>
       <c r="C855" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D855" t="inlineStr">
@@ -18364,7 +18364,7 @@
       <c r="B1033" t="inlineStr"/>
       <c r="C1033" t="inlineStr">
         <is>
-          <t>SCT Steel Transfer</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D1033" t="inlineStr">
@@ -37423,7 +37423,7 @@
       <c r="B490" t="inlineStr"/>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
@@ -41991,7 +41991,7 @@
       <c r="B746" t="inlineStr"/>
       <c r="C746" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
@@ -42153,7 +42153,7 @@
       <c r="B755" t="inlineStr"/>
       <c r="C755" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
@@ -44163,7 +44163,7 @@
       <c r="B868" t="inlineStr"/>
       <c r="C868" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D868" t="inlineStr">
@@ -45917,7 +45917,7 @@
       <c r="B967" t="inlineStr"/>
       <c r="C967" t="inlineStr">
         <is>
-          <t>Aurizon Empty Grain</t>
+          <t>SHUNT</t>
         </is>
       </c>
       <c r="D967" t="inlineStr">
@@ -55747,7 +55747,7 @@
       <c r="B1527" t="inlineStr"/>
       <c r="C1527" t="inlineStr">
         <is>
-          <t>SCT Steel Transfer</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D1527" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -4982,7 +4982,11 @@
         </is>
       </c>
       <c r="B258" t="inlineStr"/>
-      <c r="C258" t="inlineStr"/>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>PN Light Engine</t>
+        </is>
+      </c>
       <c r="D258" t="inlineStr">
         <is>
           <t>2026-04-14 23:58:35</t>
@@ -12102,7 +12106,7 @@
       <c r="B670" t="inlineStr"/>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Aurizon Wagon Transfer</t>
+          <t>Aurizon Empty Grain</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
@@ -13202,7 +13206,7 @@
       <c r="B734" t="inlineStr"/>
       <c r="C734" t="inlineStr">
         <is>
-          <t>CBH SG Empty Grain</t>
+          <t>CBH SG Loaded Grain</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
@@ -15378,7 +15382,7 @@
       <c r="B858" t="inlineStr"/>
       <c r="C858" t="inlineStr">
         <is>
-          <t>PN Infrabuild Steel</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D858" t="inlineStr">
@@ -17202,7 +17206,7 @@
       <c r="B966" t="inlineStr"/>
       <c r="C966" t="inlineStr">
         <is>
-          <t>QUBE BlueScope Steel Shunt</t>
+          <t>QUBE BlueScope Steel</t>
         </is>
       </c>
       <c r="D966" t="inlineStr">
@@ -17684,7 +17688,7 @@
       <c r="B993" t="inlineStr"/>
       <c r="C993" t="inlineStr">
         <is>
-          <t>SSR Local Transfer Train</t>
+          <t>SSR Grain</t>
         </is>
       </c>
       <c r="D993" t="inlineStr">
@@ -18436,7 +18440,7 @@
       <c r="B1037" t="inlineStr"/>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>SCT Sadleirs Transfer</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D1037" t="inlineStr">
@@ -30453,7 +30457,11 @@
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
-      <c r="C92" t="inlineStr"/>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>PN Light Engine</t>
+        </is>
+      </c>
       <c r="D92" t="inlineStr">
         <is>
           <t>2026-04-14 23:58:35</t>
@@ -38693,7 +38701,7 @@
       <c r="B561" t="inlineStr"/>
       <c r="C561" t="inlineStr">
         <is>
-          <t>QUBE BlueScope Steel Shunt</t>
+          <t>QUBE BlueScope Steel</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
@@ -38855,7 +38863,7 @@
       <c r="B570" t="inlineStr"/>
       <c r="C570" t="inlineStr">
         <is>
-          <t>CBH SG Empty Grain</t>
+          <t>CBH SG Loaded Grain</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
@@ -42117,7 +42125,7 @@
       <c r="B753" t="inlineStr"/>
       <c r="C753" t="inlineStr">
         <is>
-          <t>Aurizon Wagon Transfer</t>
+          <t>Aurizon Empty Grain</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
@@ -43091,7 +43099,7 @@
       <c r="B808" t="inlineStr"/>
       <c r="C808" t="inlineStr">
         <is>
-          <t>PN Infrabuild Steel</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D808" t="inlineStr">
@@ -51077,7 +51085,7 @@
       <c r="B1256" t="inlineStr"/>
       <c r="C1256" t="inlineStr">
         <is>
-          <t>SCT Sadleirs Transfer</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D1256" t="inlineStr">
@@ -51721,7 +51729,7 @@
       <c r="B1292" t="inlineStr"/>
       <c r="C1292" t="inlineStr">
         <is>
-          <t>SSR Local Transfer Train</t>
+          <t>SSR Grain</t>
         </is>
       </c>
       <c r="D1292" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1800,7 +1800,7 @@
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty V/Line Cars</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9510,7 +9510,11 @@
         </is>
       </c>
       <c r="B524" t="inlineStr"/>
-      <c r="C524" t="inlineStr"/>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Maintenance Train</t>
+        </is>
+      </c>
       <c r="D524" t="inlineStr">
         <is>
           <t>2026-04-17 22:24:00</t>
@@ -11618,7 +11622,7 @@
       <c r="B642" t="inlineStr"/>
       <c r="C642" t="inlineStr">
         <is>
-          <t>QUBE Loaded Aggregates</t>
+          <t>QUBE Maryvale Paper Train</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
@@ -18956,7 +18960,7 @@
       <c r="B1067" t="inlineStr"/>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>South Coast Service</t>
+          <t>South Coast Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1067" t="inlineStr">
@@ -29553,7 +29557,11 @@
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Maintenance Train</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
           <t>2026-04-17 22:24:00</t>
@@ -36495,7 +36503,7 @@
       <c r="B438" t="inlineStr"/>
       <c r="C438" t="inlineStr">
         <is>
-          <t>QUBE Loaded Aggregates</t>
+          <t>QUBE Maryvale Paper Train</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -51445,7 +51453,7 @@
       <c r="B1276" t="inlineStr"/>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty V/Line Cars</t>
         </is>
       </c>
       <c r="D1276" t="inlineStr">
@@ -55845,7 +55853,7 @@
       <c r="B1532" t="inlineStr"/>
       <c r="C1532" t="inlineStr">
         <is>
-          <t>South Coast Service</t>
+          <t>South Coast Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1532" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -4984,7 +4984,7 @@
       <c r="B258" t="inlineStr"/>
       <c r="C258" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Grain Shuttle</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -5588,7 +5588,7 @@
       <c r="B292" t="inlineStr"/>
       <c r="C292" t="inlineStr">
         <is>
-          <t>PN Local Shunter</t>
+          <t>PN Grain Shuttle</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -8774,7 +8774,7 @@
       <c r="B477" t="inlineStr"/>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Grain</t>
+          <t>Aurizon Wagon Transfer</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -9814,7 +9814,7 @@
       <c r="B541" t="inlineStr"/>
       <c r="C541" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -12544,7 +12544,7 @@
       <c r="B695" t="inlineStr"/>
       <c r="C695" t="inlineStr">
         <is>
-          <t>Hunter Railcar Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
@@ -12562,7 +12562,7 @@
       <c r="B696" t="inlineStr"/>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
@@ -13124,7 +13124,7 @@
       <c r="B729" t="inlineStr"/>
       <c r="C729" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
@@ -16512,7 +16512,7 @@
       <c r="B925" t="inlineStr"/>
       <c r="C925" t="inlineStr">
         <is>
-          <t>Watco Trip Train</t>
+          <t>Watco Light Engine</t>
         </is>
       </c>
       <c r="D925" t="inlineStr">
@@ -18588,7 +18588,7 @@
       <c r="B1045" t="inlineStr"/>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1045" t="inlineStr">
@@ -18870,7 +18870,7 @@
       <c r="B1062" t="inlineStr"/>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1062" t="inlineStr">
@@ -18960,7 +18960,7 @@
       <c r="B1067" t="inlineStr"/>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>South Coast Empty Car Transfer</t>
+          <t>NSW Trainlink South Coast Service</t>
         </is>
       </c>
       <c r="D1067" t="inlineStr">
@@ -30467,7 +30467,7 @@
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Grain Shuttle</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -30607,7 +30607,7 @@
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Watco Trip Train</t>
+          <t>Watco Light Engine</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -31413,7 +31413,7 @@
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>PN Local Shunter</t>
+          <t>PN Grain Shuttle</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -35179,7 +35179,7 @@
       <c r="B362" t="inlineStr"/>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -45089,7 +45089,7 @@
       <c r="B919" t="inlineStr"/>
       <c r="C919" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D919" t="inlineStr">
@@ -50931,7 +50931,7 @@
       <c r="B1247" t="inlineStr"/>
       <c r="C1247" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Grain</t>
+          <t>Aurizon Wagon Transfer</t>
         </is>
       </c>
       <c r="D1247" t="inlineStr">
@@ -51003,7 +51003,7 @@
       <c r="B1251" t="inlineStr"/>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>Hunter Railcar Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1251" t="inlineStr">
@@ -51773,7 +51773,7 @@
       <c r="B1294" t="inlineStr"/>
       <c r="C1294" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1294" t="inlineStr">
@@ -53937,7 +53937,7 @@
       <c r="B1420" t="inlineStr"/>
       <c r="C1420" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1420" t="inlineStr">
@@ -54473,7 +54473,7 @@
       <c r="B1450" t="inlineStr"/>
       <c r="C1450" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1450" t="inlineStr">
@@ -55853,7 +55853,7 @@
       <c r="B1532" t="inlineStr"/>
       <c r="C1532" t="inlineStr">
         <is>
-          <t>South Coast Empty Car Transfer</t>
+          <t>NSW Trainlink South Coast Service</t>
         </is>
       </c>
       <c r="D1532" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -796,7 +796,7 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Wyndham Vale</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4840,7 +4840,7 @@
       <c r="B250" t="inlineStr"/>
       <c r="C250" t="inlineStr">
         <is>
-          <t>PN - Infrabuild Shunter</t>
+          <t>PN Morandoo Shunter</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -5552,7 +5552,7 @@
       <c r="B290" t="inlineStr"/>
       <c r="C290" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Limestone</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -9548,7 +9548,7 @@
       <c r="B526" t="inlineStr"/>
       <c r="C526" t="inlineStr">
         <is>
-          <t>SSR Containerised Freight</t>
+          <t>SSR Freight Shuttle</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
@@ -9692,7 +9692,7 @@
       <c r="B534" t="inlineStr"/>
       <c r="C534" t="inlineStr">
         <is>
-          <t>SSR Grain</t>
+          <t>SSR Limestone</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
@@ -12562,7 +12562,7 @@
       <c r="B696" t="inlineStr"/>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
@@ -12616,7 +12616,7 @@
       <c r="B699" t="inlineStr"/>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Hunter Railcar Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
@@ -13034,7 +13034,7 @@
       <c r="B724" t="inlineStr"/>
       <c r="C724" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>Empty Car Provisioning (Forms SN34)</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
@@ -13106,7 +13106,7 @@
       <c r="B728" t="inlineStr"/>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
@@ -16666,7 +16666,7 @@
       <c r="B934" t="inlineStr"/>
       <c r="C934" t="inlineStr">
         <is>
-          <t>Aurizon Empty Sulphur Containers</t>
+          <t>Aurizon Kalgoorlie Mixed Freight</t>
         </is>
       </c>
       <c r="D934" t="inlineStr">
@@ -17390,7 +17390,7 @@
       <c r="B976" t="inlineStr"/>
       <c r="C976" t="inlineStr">
         <is>
-          <t>QUBE Container Shuttle</t>
+          <t>QUBE Grain</t>
         </is>
       </c>
       <c r="D976" t="inlineStr">
@@ -18960,7 +18960,7 @@
       <c r="B1067" t="inlineStr"/>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>NSW Trainlink South Coast Service</t>
+          <t>South Coast Service</t>
         </is>
       </c>
       <c r="D1067" t="inlineStr">
@@ -31743,7 +31743,7 @@
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Limestone</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -34817,7 +34817,7 @@
       <c r="B341" t="inlineStr"/>
       <c r="C341" t="inlineStr">
         <is>
-          <t>PN - Infrabuild Shunter</t>
+          <t>PN Morandoo Shunter</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -34853,7 +34853,7 @@
       <c r="B343" t="inlineStr"/>
       <c r="C343" t="inlineStr">
         <is>
-          <t>SSR Containerised Freight</t>
+          <t>SSR Freight Shuttle</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -38529,7 +38529,7 @@
       <c r="B551" t="inlineStr"/>
       <c r="C551" t="inlineStr">
         <is>
-          <t>QUBE Container Shuttle</t>
+          <t>QUBE Grain</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
@@ -48348,7 +48348,7 @@
       <c r="B1102" t="inlineStr"/>
       <c r="C1102" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Wyndham Vale</t>
         </is>
       </c>
       <c r="D1102" t="inlineStr">
@@ -51021,7 +51021,7 @@
       <c r="B1252" t="inlineStr"/>
       <c r="C1252" t="inlineStr">
         <is>
-          <t>Hunter Railcar Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1252" t="inlineStr">
@@ -51039,7 +51039,7 @@
       <c r="B1253" t="inlineStr"/>
       <c r="C1253" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>Empty Car Provisioning (Forms SN34)</t>
         </is>
       </c>
       <c r="D1253" t="inlineStr">
@@ -51687,7 +51687,7 @@
       <c r="B1289" t="inlineStr"/>
       <c r="C1289" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1289" t="inlineStr">
@@ -53901,7 +53901,7 @@
       <c r="B1418" t="inlineStr"/>
       <c r="C1418" t="inlineStr">
         <is>
-          <t>SSR Grain</t>
+          <t>SSR Limestone</t>
         </is>
       </c>
       <c r="D1418" t="inlineStr">
@@ -54473,7 +54473,7 @@
       <c r="B1450" t="inlineStr"/>
       <c r="C1450" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1450" t="inlineStr">
@@ -55357,7 +55357,7 @@
       <c r="B1502" t="inlineStr"/>
       <c r="C1502" t="inlineStr">
         <is>
-          <t>Aurizon Empty Sulphur Containers</t>
+          <t>Aurizon Kalgoorlie Mixed Freight</t>
         </is>
       </c>
       <c r="D1502" t="inlineStr">
@@ -55853,7 +55853,7 @@
       <c r="B1532" t="inlineStr"/>
       <c r="C1532" t="inlineStr">
         <is>
-          <t>NSW Trainlink South Coast Service</t>
+          <t>South Coast Service</t>
         </is>
       </c>
       <c r="D1532" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -922,7 +922,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4786,7 +4786,7 @@
       <c r="B247" t="inlineStr"/>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Maintenance Train</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -10408,7 +10408,7 @@
       <c r="B574" t="inlineStr"/>
       <c r="C574" t="inlineStr">
         <is>
-          <t>SSR Cement</t>
+          <t>SSR Cement Clinker</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
@@ -17674,7 +17674,7 @@
       <c r="B992" t="inlineStr"/>
       <c r="C992" t="inlineStr">
         <is>
-          <t>QUBE Trip Train</t>
+          <t>QUBE Containerised Freight</t>
         </is>
       </c>
       <c r="D992" t="inlineStr">
@@ -18798,7 +18798,7 @@
       <c r="B1058" t="inlineStr"/>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1058" t="inlineStr">
@@ -36575,7 +36575,7 @@
       <c r="B442" t="inlineStr"/>
       <c r="C442" t="inlineStr">
         <is>
-          <t>QUBE Trip Train</t>
+          <t>QUBE Containerised Freight</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -40661,7 +40661,7 @@
       <c r="B671" t="inlineStr"/>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Maintenance Train</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
@@ -51791,7 +51791,7 @@
       <c r="B1295" t="inlineStr"/>
       <c r="C1295" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1295" t="inlineStr">
@@ -52331,7 +52331,7 @@
       <c r="B1325" t="inlineStr"/>
       <c r="C1325" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1325" t="inlineStr">
@@ -54117,7 +54117,7 @@
       <c r="B1430" t="inlineStr"/>
       <c r="C1430" t="inlineStr">
         <is>
-          <t>SSR Cement</t>
+          <t>SSR Cement Clinker</t>
         </is>
       </c>
       <c r="D1430" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -796,7 +796,7 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Wyndham Vale</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1264,7 +1264,7 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2660,7 +2660,7 @@
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -2894,7 +2894,7 @@
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>North East Line SG Service</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -2948,7 +2948,7 @@
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>North East SG Line Service</t>
+          <t>North East Line SG Service</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -11086,7 +11086,7 @@
       <c r="B612" t="inlineStr"/>
       <c r="C612" t="inlineStr">
         <is>
-          <t>NSW TrainLink Xplorer</t>
+          <t>NSW Trainlink empty car transfer</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
@@ -14928,7 +14928,11 @@
         </is>
       </c>
       <c r="B832" t="inlineStr"/>
-      <c r="C832" t="inlineStr"/>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>PN Intermodal</t>
+        </is>
+      </c>
       <c r="D832" t="inlineStr">
         <is>
           <t>2026-04-07 01:06:21</t>
@@ -18088,7 +18092,7 @@
       <c r="B1017" t="inlineStr"/>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>North Eastern Line BG Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D1017" t="inlineStr">
@@ -18696,7 +18700,7 @@
       <c r="B1051" t="inlineStr"/>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>SSR Cement</t>
+          <t>SSR Shunter</t>
         </is>
       </c>
       <c r="D1051" t="inlineStr">
@@ -28180,7 +28184,7 @@
       <c r="B1583" t="inlineStr"/>
       <c r="C1583" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW TrainLink XPT</t>
         </is>
       </c>
       <c r="D1583" t="inlineStr">
@@ -28288,7 +28292,7 @@
       <c r="B1589" t="inlineStr"/>
       <c r="C1589" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (Forms ST23)</t>
         </is>
       </c>
       <c r="D1589" t="inlineStr">
@@ -36243,7 +36247,11 @@
         </is>
       </c>
       <c r="B422" t="inlineStr"/>
-      <c r="C422" t="inlineStr"/>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>PN Intermodal</t>
+        </is>
+      </c>
       <c r="D422" t="inlineStr">
         <is>
           <t>2026-04-07 01:06:21</t>
@@ -39759,7 +39767,7 @@
       <c r="B619" t="inlineStr"/>
       <c r="C619" t="inlineStr">
         <is>
-          <t>SSR Cement</t>
+          <t>SSR Shunter</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
@@ -45815,7 +45823,7 @@
       <c r="B959" t="inlineStr"/>
       <c r="C959" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D959" t="inlineStr">
@@ -47059,7 +47067,7 @@
       <c r="B1029" t="inlineStr"/>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>North East Line SG Service</t>
         </is>
       </c>
       <c r="D1029" t="inlineStr">
@@ -47559,7 +47567,7 @@
       <c r="B1057" t="inlineStr"/>
       <c r="C1057" t="inlineStr">
         <is>
-          <t>North Eastern Line BG Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D1057" t="inlineStr">
@@ -48384,7 +48392,7 @@
       <c r="B1103" t="inlineStr"/>
       <c r="C1103" t="inlineStr">
         <is>
-          <t>Wyndham Vale</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1103" t="inlineStr">
@@ -48672,7 +48680,7 @@
       <c r="B1119" t="inlineStr"/>
       <c r="C1119" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW TrainLink XPT</t>
         </is>
       </c>
       <c r="D1119" t="inlineStr">
@@ -50381,7 +50389,7 @@
       <c r="B1215" t="inlineStr"/>
       <c r="C1215" t="inlineStr">
         <is>
-          <t>North East SG Line Service</t>
+          <t>North East Line SG Service</t>
         </is>
       </c>
       <c r="D1215" t="inlineStr">
@@ -50751,7 +50759,7 @@
       <c r="B1236" t="inlineStr"/>
       <c r="C1236" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1236" t="inlineStr">
@@ -52187,7 +52195,7 @@
       <c r="B1316" t="inlineStr"/>
       <c r="C1316" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (Forms ST23)</t>
         </is>
       </c>
       <c r="D1316" t="inlineStr">
@@ -54261,7 +54269,7 @@
       <c r="B1437" t="inlineStr"/>
       <c r="C1437" t="inlineStr">
         <is>
-          <t>NSW TrainLink Xplorer</t>
+          <t>NSW Trainlink empty car transfer</t>
         </is>
       </c>
       <c r="D1437" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -580,7 +580,7 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -778,7 +778,7 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>V1217</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1656,7 +1656,7 @@
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2624,7 +2624,7 @@
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -8792,7 +8792,7 @@
       <c r="B478" t="inlineStr"/>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Aurizon Wagon Transfer</t>
+          <t>Aurizon Empty Grain/Wagon Transfer</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -13142,7 +13142,7 @@
       <c r="B730" t="inlineStr"/>
       <c r="C730" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
@@ -14582,7 +14582,7 @@
       <c r="B812" t="inlineStr"/>
       <c r="C812" t="inlineStr">
         <is>
-          <t>NR24</t>
+          <t>PN Steel Transfer</t>
         </is>
       </c>
       <c r="D812" t="inlineStr">
@@ -30435,7 +30435,7 @@
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -35219,7 +35219,7 @@
       <c r="B363" t="inlineStr"/>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -36997,7 +36997,7 @@
       <c r="B464" t="inlineStr"/>
       <c r="C464" t="inlineStr">
         <is>
-          <t>NR24</t>
+          <t>PN Steel Transfer</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -42777,7 +42777,7 @@
       <c r="B788" t="inlineStr"/>
       <c r="C788" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>V1217</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
@@ -48126,7 +48126,7 @@
       <c r="B1088" t="inlineStr"/>
       <c r="C1088" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1088" t="inlineStr">
@@ -50741,7 +50741,7 @@
       <c r="B1235" t="inlineStr"/>
       <c r="C1235" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1235" t="inlineStr">
@@ -50975,7 +50975,7 @@
       <c r="B1248" t="inlineStr"/>
       <c r="C1248" t="inlineStr">
         <is>
-          <t>Aurizon Wagon Transfer</t>
+          <t>Aurizon Empty Grain/Wagon Transfer</t>
         </is>
       </c>
       <c r="D1248" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -850,7 +850,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -994,7 +994,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>V/Line Empty Car Transfer</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1156,7 +1156,7 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1602,7 +1602,7 @@
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Empty V/Line Cars</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1638,7 +1638,7 @@
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Northeast Line BG Service</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2210,7 +2210,7 @@
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2714,7 +2714,7 @@
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -2786,7 +2786,7 @@
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -7960,7 +7960,7 @@
       <c r="B428" t="inlineStr"/>
       <c r="C428" t="inlineStr">
         <is>
-          <t>SSR Manildra Grain Shuttle</t>
+          <t>SSR Light Engine</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -10624,7 +10624,7 @@
       <c r="B586" t="inlineStr"/>
       <c r="C586" t="inlineStr">
         <is>
-          <t>SCT Sadliers Transfer</t>
+          <t>SCT Light Engine Movement</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
@@ -13776,7 +13776,7 @@
       <c r="B767" t="inlineStr"/>
       <c r="C767" t="inlineStr">
         <is>
-          <t>SSR Trip Train (Weston Milling)</t>
+          <t>SSR Grain</t>
         </is>
       </c>
       <c r="D767" t="inlineStr">
@@ -32289,7 +32289,7 @@
       <c r="B196" t="inlineStr"/>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -34197,7 +34197,7 @@
       <c r="B304" t="inlineStr"/>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -36709,7 +36709,7 @@
       <c r="B448" t="inlineStr"/>
       <c r="C448" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Northeast Line BG Service</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -38469,7 +38469,7 @@
       <c r="B546" t="inlineStr"/>
       <c r="C546" t="inlineStr">
         <is>
-          <t>SSR Manildra Grain Shuttle</t>
+          <t>SSR Light Engine</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
@@ -46977,7 +46977,7 @@
       <c r="B1024" t="inlineStr"/>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1024" t="inlineStr">
@@ -46995,7 +46995,7 @@
       <c r="B1025" t="inlineStr"/>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1025" t="inlineStr">
@@ -47049,7 +47049,7 @@
       <c r="B1028" t="inlineStr"/>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>Empty V/Line Cars</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1028" t="inlineStr">
@@ -49339,7 +49339,7 @@
       <c r="B1156" t="inlineStr"/>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>SCT Sadliers Transfer</t>
+          <t>SCT Light Engine Movement</t>
         </is>
       </c>
       <c r="D1156" t="inlineStr">
@@ -49713,7 +49713,7 @@
       <c r="B1177" t="inlineStr"/>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>SSR Trip Train (Weston Milling)</t>
+          <t>SSR Grain</t>
         </is>
       </c>
       <c r="D1177" t="inlineStr">
@@ -51461,7 +51461,7 @@
       <c r="B1275" t="inlineStr"/>
       <c r="C1275" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1275" t="inlineStr">
@@ -52393,7 +52393,7 @@
       <c r="B1327" t="inlineStr"/>
       <c r="C1327" t="inlineStr">
         <is>
-          <t>V/Line Empty Car Transfer</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1327" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -778,7 +778,7 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>V1217</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -796,7 +796,7 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -814,7 +814,7 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -922,7 +922,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1264,7 +1264,7 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1836,7 +1836,7 @@
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2300,7 +2300,7 @@
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2354,7 +2354,7 @@
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2606,7 +2606,7 @@
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -2768,7 +2768,7 @@
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -2840,7 +2840,7 @@
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -8458,7 +8458,7 @@
       <c r="B459" t="inlineStr"/>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Aurizon Wagon Transfer</t>
+          <t>Aurizon Intermodal</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -13016,7 +13016,7 @@
       <c r="B723" t="inlineStr"/>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Bathurst Bullet - Transfer</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
@@ -13124,7 +13124,7 @@
       <c r="B729" t="inlineStr"/>
       <c r="C729" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
@@ -13142,7 +13142,7 @@
       <c r="B730" t="inlineStr"/>
       <c r="C730" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
@@ -13496,7 +13496,7 @@
       <c r="B751" t="inlineStr"/>
       <c r="C751" t="inlineStr">
         <is>
-          <t>SSR Loaded Manildra Flour</t>
+          <t>SSR Manildra Grain Shuttle</t>
         </is>
       </c>
       <c r="D751" t="inlineStr">
@@ -14024,7 +14024,7 @@
       <c r="B781" t="inlineStr"/>
       <c r="C781" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>V/Line Light Engine</t>
         </is>
       </c>
       <c r="D781" t="inlineStr">
@@ -15796,7 +15796,7 @@
       <c r="B881" t="inlineStr"/>
       <c r="C881" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>NR103</t>
         </is>
       </c>
       <c r="D881" t="inlineStr">
@@ -18892,7 +18892,7 @@
       <c r="B1063" t="inlineStr"/>
       <c r="C1063" t="inlineStr">
         <is>
-          <t>Bathurst Bullet - Transfer</t>
+          <t>Additional Bathurst Service</t>
         </is>
       </c>
       <c r="D1063" t="inlineStr">
@@ -18928,7 +18928,7 @@
       <c r="B1065" t="inlineStr"/>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>Hunter Railcar Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1065" t="inlineStr">
@@ -19328,7 +19328,7 @@
       <c r="B1089" t="inlineStr"/>
       <c r="C1089" t="inlineStr">
         <is>
-          <t>PN Minerals</t>
+          <t>PN Empty Aggregate</t>
         </is>
       </c>
       <c r="D1089" t="inlineStr">
@@ -28044,7 +28044,7 @@
       <c r="B1575" t="inlineStr"/>
       <c r="C1575" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW TrainLink XPT</t>
         </is>
       </c>
       <c r="D1575" t="inlineStr">
@@ -28080,7 +28080,7 @@
       <c r="B1577" t="inlineStr"/>
       <c r="C1577" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (ex NT32)</t>
+          <t>NSW TrainLink XPT</t>
         </is>
       </c>
       <c r="D1577" t="inlineStr">
@@ -28220,7 +28220,7 @@
       <c r="B1585" t="inlineStr"/>
       <c r="C1585" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (ex NT34)</t>
         </is>
       </c>
       <c r="D1585" t="inlineStr">
@@ -31751,7 +31751,7 @@
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr">
         <is>
-          <t>PN Minerals</t>
+          <t>PN Empty Aggregate</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -35219,7 +35219,7 @@
       <c r="B363" t="inlineStr"/>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -35525,7 +35525,7 @@
       <c r="B380" t="inlineStr"/>
       <c r="C380" t="inlineStr">
         <is>
-          <t>SSR Loaded Manildra Flour</t>
+          <t>SSR Manildra Grain Shuttle</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -39005,7 +39005,7 @@
       <c r="B576" t="inlineStr"/>
       <c r="C576" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW TrainLink XPT</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
@@ -39131,7 +39131,7 @@
       <c r="B583" t="inlineStr"/>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
@@ -39311,7 +39311,7 @@
       <c r="B593" t="inlineStr"/>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>V/Line Light Engine</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
@@ -42741,7 +42741,7 @@
       <c r="B786" t="inlineStr"/>
       <c r="C786" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
@@ -42777,7 +42777,7 @@
       <c r="B788" t="inlineStr"/>
       <c r="C788" t="inlineStr">
         <is>
-          <t>V1217</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
@@ -43467,7 +43467,7 @@
       <c r="B827" t="inlineStr"/>
       <c r="C827" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>NR103</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
@@ -45133,7 +45133,7 @@
       <c r="B920" t="inlineStr"/>
       <c r="C920" t="inlineStr">
         <is>
-          <t>Bathurst Bullet - Transfer</t>
+          <t>Additional Bathurst Service</t>
         </is>
       </c>
       <c r="D920" t="inlineStr">
@@ -45823,7 +45823,7 @@
       <c r="B959" t="inlineStr"/>
       <c r="C959" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D959" t="inlineStr">
@@ -48392,7 +48392,7 @@
       <c r="B1103" t="inlineStr"/>
       <c r="C1103" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1103" t="inlineStr">
@@ -49849,7 +49849,7 @@
       <c r="B1185" t="inlineStr"/>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (ex NT32)</t>
+          <t>NSW TrainLink XPT</t>
         </is>
       </c>
       <c r="D1185" t="inlineStr">
@@ -50353,7 +50353,7 @@
       <c r="B1213" t="inlineStr"/>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1213" t="inlineStr">
@@ -50777,7 +50777,7 @@
       <c r="B1237" t="inlineStr"/>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1237" t="inlineStr">
@@ -51713,7 +51713,7 @@
       <c r="B1289" t="inlineStr"/>
       <c r="C1289" t="inlineStr">
         <is>
-          <t>Bathurst Bullet - Transfer</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D1289" t="inlineStr">
@@ -51731,7 +51731,7 @@
       <c r="B1290" t="inlineStr"/>
       <c r="C1290" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1290" t="inlineStr">
@@ -51853,7 +51853,7 @@
       <c r="B1297" t="inlineStr"/>
       <c r="C1297" t="inlineStr">
         <is>
-          <t>Hunter Railcar Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1297" t="inlineStr">
@@ -52285,7 +52285,7 @@
       <c r="B1321" t="inlineStr"/>
       <c r="C1321" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1321" t="inlineStr">
@@ -52339,7 +52339,7 @@
       <c r="B1324" t="inlineStr"/>
       <c r="C1324" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1324" t="inlineStr">
@@ -52375,7 +52375,7 @@
       <c r="B1326" t="inlineStr"/>
       <c r="C1326" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1326" t="inlineStr">
@@ -52501,7 +52501,7 @@
       <c r="B1333" t="inlineStr"/>
       <c r="C1333" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1333" t="inlineStr">
@@ -53515,7 +53515,7 @@
       <c r="B1392" t="inlineStr"/>
       <c r="C1392" t="inlineStr">
         <is>
-          <t>Aurizon Wagon Transfer</t>
+          <t>Aurizon Intermodal</t>
         </is>
       </c>
       <c r="D1392" t="inlineStr">
@@ -56869,7 +56869,7 @@
       <c r="B1587" t="inlineStr"/>
       <c r="C1587" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (ex NT34)</t>
         </is>
       </c>
       <c r="D1587" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -688,7 +688,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -742,7 +742,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1012,7 +1012,7 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Gippsland Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1156,7 +1156,7 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1372,7 +1372,7 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1602,7 +1602,7 @@
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1800,7 +1800,7 @@
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Empty V/Line Cars</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -1818,7 +1818,7 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>North Eastern BG Line Service</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -1958,7 +1958,7 @@
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2246,7 +2246,7 @@
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2282,7 +2282,7 @@
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2480,7 +2480,7 @@
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -9602,7 +9602,7 @@
       <c r="B529" t="inlineStr"/>
       <c r="C529" t="inlineStr">
         <is>
-          <t>SSR Manildra Grain Shuttle</t>
+          <t>C504</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
@@ -10710,7 +10710,7 @@
       <c r="B591" t="inlineStr"/>
       <c r="C591" t="inlineStr">
         <is>
-          <t>SCT Containerised Freight</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
@@ -11050,7 +11050,7 @@
       <c r="B610" t="inlineStr"/>
       <c r="C610" t="inlineStr">
         <is>
-          <t>NSW TrainLink Xplorer</t>
+          <t>NSW Trainlink Xplorer</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
@@ -11104,7 +11104,7 @@
       <c r="B613" t="inlineStr"/>
       <c r="C613" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer</t>
+          <t>NSW Trainlink Xplorer to Sydney (connects with NP24)</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
@@ -12706,7 +12706,7 @@
       <c r="B704" t="inlineStr"/>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
@@ -13052,7 +13052,7 @@
       <c r="B725" t="inlineStr"/>
       <c r="C725" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning (Forms SN34)</t>
+          <t>Southern Highlands Service</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
@@ -14758,7 +14758,7 @@
       <c r="B822" t="inlineStr"/>
       <c r="C822" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>NR37</t>
         </is>
       </c>
       <c r="D822" t="inlineStr">
@@ -18610,7 +18610,7 @@
       <c r="B1046" t="inlineStr"/>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1046" t="inlineStr">
@@ -18786,7 +18786,11 @@
         </is>
       </c>
       <c r="B1057" t="inlineStr"/>
-      <c r="C1057" t="inlineStr"/>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>Maintenance Train</t>
+        </is>
+      </c>
       <c r="D1057" t="inlineStr">
         <is>
           <t>2026-04-07 21:03:47</t>
@@ -18946,7 +18950,7 @@
       <c r="B1066" t="inlineStr"/>
       <c r="C1066" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Hunter Railcar Transfer</t>
         </is>
       </c>
       <c r="D1066" t="inlineStr">
@@ -35045,7 +35049,11 @@
         </is>
       </c>
       <c r="B353" t="inlineStr"/>
-      <c r="C353" t="inlineStr"/>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Maintenance Train</t>
+        </is>
+      </c>
       <c r="D353" t="inlineStr">
         <is>
           <t>2026-04-07 21:03:47</t>
@@ -37231,7 +37239,7 @@
       <c r="B477" t="inlineStr"/>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -40087,7 +40095,7 @@
       <c r="B637" t="inlineStr"/>
       <c r="C637" t="inlineStr">
         <is>
-          <t>SSR Manildra Grain Shuttle</t>
+          <t>C504</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
@@ -40353,7 +40361,7 @@
       <c r="B652" t="inlineStr"/>
       <c r="C652" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>NR37</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
@@ -42953,7 +42961,7 @@
       <c r="B798" t="inlineStr"/>
       <c r="C798" t="inlineStr">
         <is>
-          <t>SCT Containerised Freight</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D798" t="inlineStr">
@@ -44259,7 +44267,7 @@
       <c r="B871" t="inlineStr"/>
       <c r="C871" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>North Eastern BG Line Service</t>
         </is>
       </c>
       <c r="D871" t="inlineStr">
@@ -46995,7 +47003,7 @@
       <c r="B1025" t="inlineStr"/>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1025" t="inlineStr">
@@ -47049,7 +47057,7 @@
       <c r="B1028" t="inlineStr"/>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1028" t="inlineStr">
@@ -47387,7 +47395,7 @@
       <c r="B1047" t="inlineStr"/>
       <c r="C1047" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1047" t="inlineStr">
@@ -48198,7 +48206,7 @@
       <c r="B1092" t="inlineStr"/>
       <c r="C1092" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer</t>
+          <t>NSW Trainlink Xplorer to Sydney (connects with NP24)</t>
         </is>
       </c>
       <c r="D1092" t="inlineStr">
@@ -48979,7 +48987,7 @@
       <c r="B1136" t="inlineStr"/>
       <c r="C1136" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Hunter Railcar Transfer</t>
         </is>
       </c>
       <c r="D1136" t="inlineStr">
@@ -50011,7 +50019,7 @@
       <c r="B1194" t="inlineStr"/>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>NSW TrainLink Xplorer</t>
+          <t>NSW Trainlink Xplorer</t>
         </is>
       </c>
       <c r="D1194" t="inlineStr">
@@ -50281,7 +50289,7 @@
       <c r="B1209" t="inlineStr"/>
       <c r="C1209" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1209" t="inlineStr">
@@ -50335,7 +50343,7 @@
       <c r="B1212" t="inlineStr"/>
       <c r="C1212" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1212" t="inlineStr">
@@ -50723,7 +50731,7 @@
       <c r="B1234" t="inlineStr"/>
       <c r="C1234" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1234" t="inlineStr">
@@ -51083,7 +51091,7 @@
       <c r="B1254" t="inlineStr"/>
       <c r="C1254" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning (Forms SN34)</t>
+          <t>Southern Highlands Service</t>
         </is>
       </c>
       <c r="D1254" t="inlineStr">
@@ -51425,7 +51433,7 @@
       <c r="B1273" t="inlineStr"/>
       <c r="C1273" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1273" t="inlineStr">
@@ -51479,7 +51487,7 @@
       <c r="B1276" t="inlineStr"/>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>Gippsland Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1276" t="inlineStr">
@@ -51497,7 +51505,7 @@
       <c r="B1277" t="inlineStr"/>
       <c r="C1277" t="inlineStr">
         <is>
-          <t>Empty V/Line Cars</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1277" t="inlineStr">
@@ -51695,7 +51703,7 @@
       <c r="B1288" t="inlineStr"/>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1288" t="inlineStr">
@@ -51817,7 +51825,7 @@
       <c r="B1295" t="inlineStr"/>
       <c r="C1295" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1295" t="inlineStr">
@@ -52267,7 +52275,7 @@
       <c r="B1320" t="inlineStr"/>
       <c r="C1320" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1320" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -598,7 +598,7 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -742,7 +742,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1120,7 +1120,7 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1192,7 +1192,7 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1548,7 +1548,7 @@
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>V/Line rail cleaning train</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1638,7 +1638,7 @@
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1728,7 +1728,7 @@
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2210,7 +2210,7 @@
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2282,7 +2282,7 @@
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2300,7 +2300,7 @@
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2390,7 +2390,7 @@
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2570,7 +2570,7 @@
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -2714,7 +2714,7 @@
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -10642,7 +10642,7 @@
       <c r="B587" t="inlineStr"/>
       <c r="C587" t="inlineStr">
         <is>
-          <t>SCT Light Engine Movement</t>
+          <t>SCT Sadleirs Transfer</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
@@ -11442,7 +11442,7 @@
       <c r="B632" t="inlineStr"/>
       <c r="C632" t="inlineStr">
         <is>
-          <t>PN Containerised Freight</t>
+          <t>G519</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
@@ -15620,7 +15620,7 @@
       <c r="B871" t="inlineStr"/>
       <c r="C871" t="inlineStr">
         <is>
-          <t>NR89</t>
+          <t>PN Infrabuild Steel</t>
         </is>
       </c>
       <c r="D871" t="inlineStr">
@@ -16656,7 +16656,7 @@
       <c r="B933" t="inlineStr"/>
       <c r="C933" t="inlineStr">
         <is>
-          <t>SRS-Crawfords Container Train</t>
+          <t>SRS Light Engine Movement</t>
         </is>
       </c>
       <c r="D933" t="inlineStr">
@@ -17048,7 +17048,7 @@
       <c r="B957" t="inlineStr"/>
       <c r="C957" t="inlineStr">
         <is>
-          <t>QUBE Grain</t>
+          <t>QUBE Container / Grain Shuttle</t>
         </is>
       </c>
       <c r="D957" t="inlineStr">
@@ -18300,7 +18300,7 @@
       <c r="B1029" t="inlineStr"/>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>NorthEast BG Line Service</t>
+          <t>North Eastern Line BG Service</t>
         </is>
       </c>
       <c r="D1029" t="inlineStr">
@@ -19000,7 +19000,7 @@
       <c r="B1069" t="inlineStr"/>
       <c r="C1069" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1069" t="inlineStr">
@@ -28454,7 +28454,7 @@
       <c r="B1598" t="inlineStr"/>
       <c r="C1598" t="inlineStr">
         <is>
-          <t>PN Loaded BG Grain</t>
+          <t>PN Empty BG Grain</t>
         </is>
       </c>
       <c r="D1598" t="inlineStr">
@@ -34373,7 +34373,7 @@
       <c r="B309" t="inlineStr"/>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -36889,7 +36889,7 @@
       <c r="B453" t="inlineStr"/>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -37429,7 +37429,7 @@
       <c r="B483" t="inlineStr"/>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>V/Line rail cleaning train</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -41353,7 +41353,7 @@
       <c r="B703" t="inlineStr"/>
       <c r="C703" t="inlineStr">
         <is>
-          <t>NorthEast BG Line Service</t>
+          <t>North Eastern Line BG Service</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
@@ -42623,7 +42623,7 @@
       <c r="B774" t="inlineStr"/>
       <c r="C774" t="inlineStr">
         <is>
-          <t>NR89</t>
+          <t>PN Infrabuild Steel</t>
         </is>
       </c>
       <c r="D774" t="inlineStr">
@@ -42759,7 +42759,7 @@
       <c r="B782" t="inlineStr"/>
       <c r="C782" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
@@ -42975,7 +42975,7 @@
       <c r="B794" t="inlineStr"/>
       <c r="C794" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D794" t="inlineStr">
@@ -43539,7 +43539,7 @@
       <c r="B826" t="inlineStr"/>
       <c r="C826" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D826" t="inlineStr">
@@ -44421,7 +44421,7 @@
       <c r="B875" t="inlineStr"/>
       <c r="C875" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D875" t="inlineStr">
@@ -45643,7 +45643,7 @@
       <c r="B944" t="inlineStr"/>
       <c r="C944" t="inlineStr">
         <is>
-          <t>SRS-Crawfords Container Train</t>
+          <t>SRS Light Engine Movement</t>
         </is>
       </c>
       <c r="D944" t="inlineStr">
@@ -47157,7 +47157,7 @@
       <c r="B1029" t="inlineStr"/>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1029" t="inlineStr">
@@ -47567,7 +47567,7 @@
       <c r="B1052" t="inlineStr"/>
       <c r="C1052" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1052" t="inlineStr">
@@ -48554,7 +48554,7 @@
       <c r="B1107" t="inlineStr"/>
       <c r="C1107" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1107" t="inlineStr">
@@ -49159,7 +49159,7 @@
       <c r="B1141" t="inlineStr"/>
       <c r="C1141" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1141" t="inlineStr">
@@ -49519,7 +49519,7 @@
       <c r="B1161" t="inlineStr"/>
       <c r="C1161" t="inlineStr">
         <is>
-          <t>SCT Light Engine Movement</t>
+          <t>SCT Sadleirs Transfer</t>
         </is>
       </c>
       <c r="D1161" t="inlineStr">
@@ -50047,7 +50047,7 @@
       <c r="B1191" t="inlineStr"/>
       <c r="C1191" t="inlineStr">
         <is>
-          <t>PN Loaded BG Grain</t>
+          <t>PN Empty BG Grain</t>
         </is>
       </c>
       <c r="D1191" t="inlineStr">
@@ -50695,7 +50695,7 @@
       <c r="B1227" t="inlineStr"/>
       <c r="C1227" t="inlineStr">
         <is>
-          <t>PN Containerised Freight</t>
+          <t>G519</t>
         </is>
       </c>
       <c r="D1227" t="inlineStr">
@@ -51623,7 +51623,7 @@
       <c r="B1279" t="inlineStr"/>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1279" t="inlineStr">
@@ -52447,7 +52447,7 @@
       <c r="B1325" t="inlineStr"/>
       <c r="C1325" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1325" t="inlineStr">
@@ -52465,7 +52465,7 @@
       <c r="B1326" t="inlineStr"/>
       <c r="C1326" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1326" t="inlineStr">
@@ -55741,7 +55741,7 @@
       <c r="B1518" t="inlineStr"/>
       <c r="C1518" t="inlineStr">
         <is>
-          <t>QUBE Grain</t>
+          <t>QUBE Container / Grain Shuttle</t>
         </is>
       </c>
       <c r="D1518" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -490,7 +490,7 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -508,7 +508,7 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -688,7 +688,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -796,7 +796,7 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -868,7 +868,7 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -994,7 +994,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning, pre 8145</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1548,7 +1548,7 @@
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>V/Line rail cleaning train</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1602,7 +1602,7 @@
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1692,7 +1692,7 @@
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1958,7 +1958,7 @@
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2084,7 +2084,7 @@
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2102,7 +2102,7 @@
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2354,7 +2354,7 @@
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -4732,7 +4732,7 @@
       <c r="B244" t="inlineStr"/>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Maintenance Train</t>
+          <t>SSR EMU Transfer Service</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -6754,7 +6754,7 @@
       <c r="B357" t="inlineStr"/>
       <c r="C357" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>PN Light Engine Movement</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -9398,7 +9398,7 @@
       <c r="B517" t="inlineStr"/>
       <c r="C517" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Grain/Wagon Transfer</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
@@ -9904,7 +9904,7 @@
       <c r="B546" t="inlineStr"/>
       <c r="C546" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
@@ -9940,7 +9940,7 @@
       <c r="B548" t="inlineStr"/>
       <c r="C548" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
@@ -11140,7 +11140,7 @@
       <c r="B615" t="inlineStr"/>
       <c r="C615" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer</t>
+          <t>NSW TrainLink Xplorer</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -11866,7 +11866,7 @@
       <c r="B656" t="inlineStr"/>
       <c r="C656" t="inlineStr">
         <is>
-          <t>SSR Light Engine</t>
+          <t>Maintenance Train</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
@@ -12738,7 +12738,7 @@
       <c r="B706" t="inlineStr"/>
       <c r="C706" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
@@ -13084,7 +13084,7 @@
       <c r="B727" t="inlineStr"/>
       <c r="C727" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
@@ -13772,7 +13772,7 @@
       <c r="B767" t="inlineStr"/>
       <c r="C767" t="inlineStr">
         <is>
-          <t>SSR Trip Train (Weston Milling)</t>
+          <t>SSR Grain</t>
         </is>
       </c>
       <c r="D767" t="inlineStr">
@@ -14506,7 +14506,7 @@
       <c r="B808" t="inlineStr"/>
       <c r="C808" t="inlineStr">
         <is>
-          <t>PN Fuel Train</t>
+          <t>PN Empty Fuel</t>
         </is>
       </c>
       <c r="D808" t="inlineStr">
@@ -14808,7 +14808,7 @@
       <c r="B825" t="inlineStr"/>
       <c r="C825" t="inlineStr">
         <is>
-          <t>NR37</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D825" t="inlineStr">
@@ -17728,7 +17728,7 @@
       <c r="B995" t="inlineStr"/>
       <c r="C995" t="inlineStr">
         <is>
-          <t>SSR Light Engine</t>
+          <t>SSR Grain</t>
         </is>
       </c>
       <c r="D995" t="inlineStr">
@@ -18106,7 +18106,7 @@
       <c r="B1018" t="inlineStr"/>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>North Eastern Line BG Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D1018" t="inlineStr">
@@ -18660,7 +18660,7 @@
       <c r="B1049" t="inlineStr"/>
       <c r="C1049" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1049" t="inlineStr">
@@ -18946,7 +18946,7 @@
       <c r="B1066" t="inlineStr"/>
       <c r="C1066" t="inlineStr">
         <is>
-          <t>Additional Bathurst Service</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D1066" t="inlineStr">
@@ -31773,7 +31773,7 @@
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>PN Light Engine Movement</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32627,7 +32627,7 @@
       <c r="B210" t="inlineStr"/>
       <c r="C210" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Grain/Wagon Transfer</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -35169,7 +35169,7 @@
       <c r="B355" t="inlineStr"/>
       <c r="C355" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -37069,7 +37069,7 @@
       <c r="B463" t="inlineStr"/>
       <c r="C463" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -37429,7 +37429,7 @@
       <c r="B483" t="inlineStr"/>
       <c r="C483" t="inlineStr">
         <is>
-          <t>V/Line rail cleaning train</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -38771,7 +38771,7 @@
       <c r="B558" t="inlineStr"/>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
@@ -40357,7 +40357,7 @@
       <c r="B647" t="inlineStr"/>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Maintenance Train</t>
+          <t>SSR EMU Transfer Service</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
@@ -40533,7 +40533,7 @@
       <c r="B657" t="inlineStr"/>
       <c r="C657" t="inlineStr">
         <is>
-          <t>NR37</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
@@ -40741,7 +40741,7 @@
       <c r="B669" t="inlineStr"/>
       <c r="C669" t="inlineStr">
         <is>
-          <t>North Eastern Line BG Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
@@ -42105,7 +42105,7 @@
       <c r="B745" t="inlineStr"/>
       <c r="C745" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
@@ -42921,7 +42921,7 @@
       <c r="B791" t="inlineStr"/>
       <c r="C791" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D791" t="inlineStr">
@@ -45313,7 +45313,7 @@
       <c r="B925" t="inlineStr"/>
       <c r="C925" t="inlineStr">
         <is>
-          <t>Additional Bathurst Service</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D925" t="inlineStr">
@@ -47229,7 +47229,7 @@
       <c r="B1033" t="inlineStr"/>
       <c r="C1033" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1033" t="inlineStr">
@@ -47585,7 +47585,7 @@
       <c r="B1053" t="inlineStr"/>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1053" t="inlineStr">
@@ -47675,7 +47675,7 @@
       <c r="B1058" t="inlineStr"/>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer</t>
+          <t>NSW TrainLink Xplorer</t>
         </is>
       </c>
       <c r="D1058" t="inlineStr">
@@ -48572,7 +48572,7 @@
       <c r="B1108" t="inlineStr"/>
       <c r="C1108" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D1108" t="inlineStr">
@@ -49105,7 +49105,7 @@
       <c r="B1138" t="inlineStr"/>
       <c r="C1138" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D1138" t="inlineStr">
@@ -49627,7 +49627,7 @@
       <c r="B1167" t="inlineStr"/>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1167" t="inlineStr">
@@ -49767,7 +49767,7 @@
       <c r="B1175" t="inlineStr"/>
       <c r="C1175" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1175" t="inlineStr">
@@ -50335,7 +50335,7 @@
       <c r="B1207" t="inlineStr"/>
       <c r="C1207" t="inlineStr">
         <is>
-          <t>SSR Light Engine</t>
+          <t>SSR Grain</t>
         </is>
       </c>
       <c r="D1207" t="inlineStr">
@@ -50443,7 +50443,7 @@
       <c r="B1213" t="inlineStr"/>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1213" t="inlineStr">
@@ -50461,7 +50461,7 @@
       <c r="B1214" t="inlineStr"/>
       <c r="C1214" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1214" t="inlineStr">
@@ -50515,7 +50515,7 @@
       <c r="B1217" t="inlineStr"/>
       <c r="C1217" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1217" t="inlineStr">
@@ -51785,7 +51785,7 @@
       <c r="B1288" t="inlineStr"/>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>SSR Light Engine</t>
+          <t>Maintenance Train</t>
         </is>
       </c>
       <c r="D1288" t="inlineStr">
@@ -51997,7 +51997,7 @@
       <c r="B1300" t="inlineStr"/>
       <c r="C1300" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1300" t="inlineStr">
@@ -52573,7 +52573,7 @@
       <c r="B1332" t="inlineStr"/>
       <c r="C1332" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Empty Car Provisioning, pre 8145</t>
         </is>
       </c>
       <c r="D1332" t="inlineStr">
@@ -54197,7 +54197,7 @@
       <c r="B1428" t="inlineStr"/>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1428" t="inlineStr">
@@ -54733,7 +54733,7 @@
       <c r="B1458" t="inlineStr"/>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1458" t="inlineStr">
@@ -54963,7 +54963,7 @@
       <c r="B1471" t="inlineStr"/>
       <c r="C1471" t="inlineStr">
         <is>
-          <t>SSR Trip Train (Weston Milling)</t>
+          <t>SSR Grain</t>
         </is>
       </c>
       <c r="D1471" t="inlineStr">
@@ -55053,7 +55053,7 @@
       <c r="B1476" t="inlineStr"/>
       <c r="C1476" t="inlineStr">
         <is>
-          <t>PN Fuel Train</t>
+          <t>PN Empty Fuel</t>
         </is>
       </c>
       <c r="D1476" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -670,7 +670,7 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -796,7 +796,7 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -814,7 +814,7 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -832,7 +832,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1084,7 +1084,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1602,7 +1602,7 @@
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1710,7 +1710,7 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Empty V/Line Cars</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1818,7 +1818,7 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2156,7 +2156,7 @@
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>North Eastern Line BG Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2588,7 +2588,7 @@
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -2732,7 +2732,7 @@
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -2912,7 +2912,7 @@
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>North East SG Line Service</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -2930,7 +2930,7 @@
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>NorthEast Special Movement</t>
+          <t>V/Line SG Special Movement</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6052,7 +6052,7 @@
       <c r="B318" t="inlineStr"/>
       <c r="C318" t="inlineStr">
         <is>
-          <t>PN Loaded Ore / Grain</t>
+          <t>PN Empty Ore</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -6790,7 +6790,7 @@
       <c r="B359" t="inlineStr"/>
       <c r="C359" t="inlineStr">
         <is>
-          <t>PN Grain</t>
+          <t>PN Grain Shuttle</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -7220,7 +7220,7 @@
       <c r="B384" t="inlineStr"/>
       <c r="C384" t="inlineStr">
         <is>
-          <t>PN Port Waratah Shunter</t>
+          <t>PN Coal</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -8390,7 +8390,7 @@
       <c r="B455" t="inlineStr"/>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Aurizon Cockburn Cement - Lime and Cement Train</t>
+          <t>Aurizon Kalgoorlie Mixed Freight</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -8882,7 +8882,7 @@
       <c r="B483" t="inlineStr"/>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Yilgarn Iron Iron Ore</t>
+          <t>Yilgarn Iron Ore</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -10390,7 +10390,7 @@
       <c r="B573" t="inlineStr"/>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Aurizon Wagon Transfer</t>
+          <t>Aurizon Light Engine</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
@@ -10800,7 +10800,7 @@
       <c r="B596" t="inlineStr"/>
       <c r="C596" t="inlineStr">
         <is>
-          <t>SCT Light Engine</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
@@ -11194,7 +11194,7 @@
       <c r="B618" t="inlineStr"/>
       <c r="C618" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer</t>
+          <t>NSW Trainlink Xplorer (Divides from SP33)</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
@@ -12408,7 +12408,7 @@
       <c r="B687" t="inlineStr"/>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Ore</t>
+          <t>Aurizon Empty Ore</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
@@ -12522,7 +12522,7 @@
       <c r="B694" t="inlineStr"/>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
@@ -13066,7 +13066,7 @@
       <c r="B726" t="inlineStr"/>
       <c r="C726" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Southern Highlands Service</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
@@ -14326,7 +14326,7 @@
       <c r="B798" t="inlineStr"/>
       <c r="C798" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>PN Infrabuild Steel</t>
         </is>
       </c>
       <c r="D798" t="inlineStr">
@@ -14740,7 +14740,7 @@
       <c r="B821" t="inlineStr"/>
       <c r="C821" t="inlineStr">
         <is>
-          <t>PN Infrabuild Steel</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D821" t="inlineStr">
@@ -16656,7 +16656,7 @@
       <c r="B933" t="inlineStr"/>
       <c r="C933" t="inlineStr">
         <is>
-          <t>SRS Light Engine Movement</t>
+          <t>SRS/SCT Sadleirs Trip Train</t>
         </is>
       </c>
       <c r="D933" t="inlineStr">
@@ -17444,7 +17444,7 @@
       <c r="B979" t="inlineStr"/>
       <c r="C979" t="inlineStr">
         <is>
-          <t>QUBE BlueScope Steel</t>
+          <t>QUBE BlueScope Steel Transfer</t>
         </is>
       </c>
       <c r="D979" t="inlineStr">
@@ -17800,7 +17800,7 @@
       <c r="B999" t="inlineStr"/>
       <c r="C999" t="inlineStr">
         <is>
-          <t>SSR Manildra Grain Shuttle</t>
+          <t>SSR Grain</t>
         </is>
       </c>
       <c r="D999" t="inlineStr">
@@ -28292,7 +28292,7 @@
       <c r="B1589" t="inlineStr"/>
       <c r="C1589" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1589" t="inlineStr">
@@ -30219,7 +30219,7 @@
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>PN Grain</t>
+          <t>PN Grain Shuttle</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -34851,7 +34851,7 @@
       <c r="B336" t="inlineStr"/>
       <c r="C336" t="inlineStr">
         <is>
-          <t>PN Loaded Ore / Grain</t>
+          <t>PN Empty Ore</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -37033,7 +37033,7 @@
       <c r="B461" t="inlineStr"/>
       <c r="C461" t="inlineStr">
         <is>
-          <t>North Eastern Line BG Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -37645,7 +37645,7 @@
       <c r="B495" t="inlineStr"/>
       <c r="C495" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
@@ -39221,7 +39221,7 @@
       <c r="B583" t="inlineStr"/>
       <c r="C583" t="inlineStr">
         <is>
-          <t>SSR Manildra Grain Shuttle</t>
+          <t>SSR Grain</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
@@ -40163,7 +40163,7 @@
       <c r="B636" t="inlineStr"/>
       <c r="C636" t="inlineStr">
         <is>
-          <t>QUBE BlueScope Steel</t>
+          <t>QUBE BlueScope Steel Transfer</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
@@ -40633,7 +40633,7 @@
       <c r="B663" t="inlineStr"/>
       <c r="C663" t="inlineStr">
         <is>
-          <t>PN Port Waratah Shunter</t>
+          <t>PN Coal</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
@@ -42903,7 +42903,7 @@
       <c r="B790" t="inlineStr"/>
       <c r="C790" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
@@ -43241,7 +43241,7 @@
       <c r="B809" t="inlineStr"/>
       <c r="C809" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Ore</t>
+          <t>Aurizon Empty Ore</t>
         </is>
       </c>
       <c r="D809" t="inlineStr">
@@ -44439,7 +44439,7 @@
       <c r="B876" t="inlineStr"/>
       <c r="C876" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D876" t="inlineStr">
@@ -45643,7 +45643,7 @@
       <c r="B944" t="inlineStr"/>
       <c r="C944" t="inlineStr">
         <is>
-          <t>SRS Light Engine Movement</t>
+          <t>SRS/SCT Sadleirs Trip Train</t>
         </is>
       </c>
       <c r="D944" t="inlineStr">
@@ -46021,7 +46021,7 @@
       <c r="B965" t="inlineStr"/>
       <c r="C965" t="inlineStr">
         <is>
-          <t>NorthEast Special Movement</t>
+          <t>V/Line SG Special Movement</t>
         </is>
       </c>
       <c r="D965" t="inlineStr">
@@ -46085,7 +46085,7 @@
       <c r="B969" t="inlineStr"/>
       <c r="C969" t="inlineStr">
         <is>
-          <t>Yilgarn Iron Iron Ore</t>
+          <t>Yilgarn Iron Ore</t>
         </is>
       </c>
       <c r="D969" t="inlineStr">
@@ -47229,7 +47229,7 @@
       <c r="B1033" t="inlineStr"/>
       <c r="C1033" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1033" t="inlineStr">
@@ -47301,7 +47301,7 @@
       <c r="B1037" t="inlineStr"/>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer</t>
+          <t>NSW Trainlink Xplorer (Divides from SP33)</t>
         </is>
       </c>
       <c r="D1037" t="inlineStr">
@@ -47549,7 +47549,7 @@
       <c r="B1051" t="inlineStr"/>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1051" t="inlineStr">
@@ -48342,7 +48342,7 @@
       <c r="B1095" t="inlineStr"/>
       <c r="C1095" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Empty V/Line Cars</t>
         </is>
       </c>
       <c r="D1095" t="inlineStr">
@@ -48572,7 +48572,7 @@
       <c r="B1108" t="inlineStr"/>
       <c r="C1108" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D1108" t="inlineStr">
@@ -50245,7 +50245,7 @@
       <c r="B1202" t="inlineStr"/>
       <c r="C1202" t="inlineStr">
         <is>
-          <t>PN Infrabuild Steel</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D1202" t="inlineStr">
@@ -50263,7 +50263,7 @@
       <c r="B1203" t="inlineStr"/>
       <c r="C1203" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>PN Infrabuild Steel</t>
         </is>
       </c>
       <c r="D1203" t="inlineStr">
@@ -50551,7 +50551,7 @@
       <c r="B1219" t="inlineStr"/>
       <c r="C1219" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>North East SG Line Service</t>
         </is>
       </c>
       <c r="D1219" t="inlineStr">
@@ -50623,7 +50623,7 @@
       <c r="B1223" t="inlineStr"/>
       <c r="C1223" t="inlineStr">
         <is>
-          <t>Aurizon Wagon Transfer</t>
+          <t>Aurizon Light Engine</t>
         </is>
       </c>
       <c r="D1223" t="inlineStr">
@@ -51803,7 +51803,7 @@
       <c r="B1289" t="inlineStr"/>
       <c r="C1289" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1289" t="inlineStr">
@@ -51893,7 +51893,7 @@
       <c r="B1294" t="inlineStr"/>
       <c r="C1294" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Southern Highlands Service</t>
         </is>
       </c>
       <c r="D1294" t="inlineStr">
@@ -52519,7 +52519,7 @@
       <c r="B1329" t="inlineStr"/>
       <c r="C1329" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1329" t="inlineStr">
@@ -52537,7 +52537,7 @@
       <c r="B1330" t="inlineStr"/>
       <c r="C1330" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D1330" t="inlineStr">
@@ -52591,7 +52591,7 @@
       <c r="B1333" t="inlineStr"/>
       <c r="C1333" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D1333" t="inlineStr">
@@ -53677,7 +53677,7 @@
       <c r="B1396" t="inlineStr"/>
       <c r="C1396" t="inlineStr">
         <is>
-          <t>Aurizon Cockburn Cement - Lime and Cement Train</t>
+          <t>Aurizon Kalgoorlie Mixed Freight</t>
         </is>
       </c>
       <c r="D1396" t="inlineStr">
@@ -54395,7 +54395,7 @@
       <c r="B1439" t="inlineStr"/>
       <c r="C1439" t="inlineStr">
         <is>
-          <t>SCT Light Engine</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D1439" t="inlineStr">
@@ -57031,7 +57031,7 @@
       <c r="B1591" t="inlineStr"/>
       <c r="C1591" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1591" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -562,7 +562,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>North East Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -976,7 +976,7 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>V/Line Light Engine</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1228,7 +1228,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2606,7 +2606,7 @@
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4660,7 +4660,7 @@
       <c r="B240" t="inlineStr"/>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Grain</t>
+          <t>Aurizon Empty Grain</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -8792,7 +8792,7 @@
       <c r="B478" t="inlineStr"/>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Aurizon Empty Ore</t>
+          <t>Aurizon Loaded Ore</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -9584,7 +9584,7 @@
       <c r="B528" t="inlineStr"/>
       <c r="C528" t="inlineStr">
         <is>
-          <t>SSR Freight Shuttle</t>
+          <t>SSR Containerised Freight</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
@@ -10642,7 +10642,7 @@
       <c r="B587" t="inlineStr"/>
       <c r="C587" t="inlineStr">
         <is>
-          <t>SCT Sadleirs Transfer</t>
+          <t>SCT Sadliers Transfer</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
@@ -11812,7 +11812,7 @@
       <c r="B653" t="inlineStr"/>
       <c r="C653" t="inlineStr">
         <is>
-          <t>SCT Light Engine Movement</t>
+          <t>SCT Steel Shunt / Wine Train</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
@@ -11884,7 +11884,7 @@
       <c r="B657" t="inlineStr"/>
       <c r="C657" t="inlineStr">
         <is>
-          <t>QUBE Empty Zinc</t>
+          <t>QUBE Empty Balco</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
@@ -12092,7 +12092,7 @@
       <c r="B669" t="inlineStr"/>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Aurizon Empty Grain</t>
+          <t>Aurizon Loaded Grain</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
@@ -12522,7 +12522,7 @@
       <c r="B694" t="inlineStr"/>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
@@ -13138,7 +13138,7 @@
       <c r="B730" t="inlineStr"/>
       <c r="C730" t="inlineStr">
         <is>
-          <t>Additional Bathurst Service</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
@@ -14542,7 +14542,7 @@
       <c r="B810" t="inlineStr"/>
       <c r="C810" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>PN Infrabuild Steel</t>
         </is>
       </c>
       <c r="D810" t="inlineStr">
@@ -16848,7 +16848,7 @@
       <c r="B945" t="inlineStr"/>
       <c r="C945" t="inlineStr">
         <is>
-          <t>Aurizon BP Loaded Fuel</t>
+          <t>Gold Valley Iron Ore</t>
         </is>
       </c>
       <c r="D945" t="inlineStr">
@@ -19000,7 +19000,7 @@
       <c r="B1069" t="inlineStr"/>
       <c r="C1069" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1069" t="inlineStr">
@@ -28382,7 +28382,7 @@
       <c r="B1594" t="inlineStr"/>
       <c r="C1594" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (Forms ST23)</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1594" t="inlineStr">
@@ -28508,7 +28508,7 @@
       <c r="B1601" t="inlineStr"/>
       <c r="C1601" t="inlineStr">
         <is>
-          <t>PN Grain</t>
+          <t>XR559</t>
         </is>
       </c>
       <c r="D1601" t="inlineStr">
@@ -28806,7 +28806,7 @@
       <c r="B1618" t="inlineStr"/>
       <c r="C1618" t="inlineStr">
         <is>
-          <t>ORA Shunter</t>
+          <t>ORA Coal</t>
         </is>
       </c>
       <c r="D1618" t="inlineStr">
@@ -29161,7 +29161,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aurizon Empty Ore</t>
+          <t>Aurizon Loaded Ore</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -32121,7 +32121,7 @@
       <c r="B181" t="inlineStr"/>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Aurizon Empty Grain</t>
+          <t>Aurizon Loaded Grain</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -35069,7 +35069,7 @@
       <c r="B349" t="inlineStr"/>
       <c r="C349" t="inlineStr">
         <is>
-          <t>SSR Freight Shuttle</t>
+          <t>SSR Containerised Freight</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -35489,7 +35489,7 @@
       <c r="B373" t="inlineStr"/>
       <c r="C373" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>PN Infrabuild Steel</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -39203,7 +39203,7 @@
       <c r="B582" t="inlineStr"/>
       <c r="C582" t="inlineStr">
         <is>
-          <t>QUBE Empty Zinc</t>
+          <t>QUBE Empty Balco</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
@@ -39311,7 +39311,7 @@
       <c r="B588" t="inlineStr"/>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
@@ -39793,7 +39793,7 @@
       <c r="B615" t="inlineStr"/>
       <c r="C615" t="inlineStr">
         <is>
-          <t>PN Grain</t>
+          <t>XR559</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -40447,7 +40447,7 @@
       <c r="B652" t="inlineStr"/>
       <c r="C652" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Grain</t>
+          <t>Aurizon Empty Grain</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
@@ -42461,7 +42461,7 @@
       <c r="B765" t="inlineStr"/>
       <c r="C765" t="inlineStr">
         <is>
-          <t>North East Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
@@ -43259,7 +43259,7 @@
       <c r="B810" t="inlineStr"/>
       <c r="C810" t="inlineStr">
         <is>
-          <t>Additional Bathurst Service</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D810" t="inlineStr">
@@ -43521,7 +43521,7 @@
       <c r="B825" t="inlineStr"/>
       <c r="C825" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>V/Line Light Engine</t>
         </is>
       </c>
       <c r="D825" t="inlineStr">
@@ -45137,7 +45137,7 @@
       <c r="B915" t="inlineStr"/>
       <c r="C915" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D915" t="inlineStr">
@@ -46225,7 +46225,7 @@
       <c r="B977" t="inlineStr"/>
       <c r="C977" t="inlineStr">
         <is>
-          <t>Aurizon BP Loaded Fuel</t>
+          <t>Gold Valley Iron Ore</t>
         </is>
       </c>
       <c r="D977" t="inlineStr">
@@ -49159,7 +49159,7 @@
       <c r="B1141" t="inlineStr"/>
       <c r="C1141" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1141" t="inlineStr">
@@ -49519,7 +49519,7 @@
       <c r="B1161" t="inlineStr"/>
       <c r="C1161" t="inlineStr">
         <is>
-          <t>SCT Sadleirs Transfer</t>
+          <t>SCT Sadliers Transfer</t>
         </is>
       </c>
       <c r="D1161" t="inlineStr">
@@ -51803,7 +51803,7 @@
       <c r="B1289" t="inlineStr"/>
       <c r="C1289" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1289" t="inlineStr">
@@ -52375,7 +52375,7 @@
       <c r="B1321" t="inlineStr"/>
       <c r="C1321" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (Forms ST23)</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1321" t="inlineStr">
@@ -54521,7 +54521,7 @@
       <c r="B1446" t="inlineStr"/>
       <c r="C1446" t="inlineStr">
         <is>
-          <t>SCT Light Engine Movement</t>
+          <t>SCT Steel Shunt / Wine Train</t>
         </is>
       </c>
       <c r="D1446" t="inlineStr">
@@ -57247,7 +57247,7 @@
       <c r="B1603" t="inlineStr"/>
       <c r="C1603" t="inlineStr">
         <is>
-          <t>ORA Shunter</t>
+          <t>ORA Coal</t>
         </is>
       </c>
       <c r="D1603" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -994,7 +994,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning, pre 8145</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1462,7 +1462,7 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>V/Line Light Engine Movement</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2534,7 +2534,7 @@
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4330,7 +4330,7 @@
       <c r="B221" t="inlineStr"/>
       <c r="C221" t="inlineStr">
         <is>
-          <t>AZ Coal</t>
+          <t>AZ Light Engine</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -5948,7 +5948,7 @@
       <c r="B312" t="inlineStr"/>
       <c r="C312" t="inlineStr">
         <is>
-          <t>PN Coal</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -6610,7 +6610,7 @@
       <c r="B349" t="inlineStr"/>
       <c r="C349" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -9642,7 +9642,7 @@
       <c r="B531" t="inlineStr"/>
       <c r="C531" t="inlineStr">
         <is>
-          <t>SSR Manildra Grain Shuttle</t>
+          <t>SSR Containerised Freight</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
@@ -9926,7 +9926,7 @@
       <c r="B547" t="inlineStr"/>
       <c r="C547" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
@@ -10088,7 +10088,7 @@
       <c r="B556" t="inlineStr"/>
       <c r="C556" t="inlineStr">
         <is>
-          <t>QUBE Light Engine</t>
+          <t>QUBE BlueScope Steel</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
@@ -10340,7 +10340,7 @@
       <c r="B570" t="inlineStr"/>
       <c r="C570" t="inlineStr">
         <is>
-          <t>SRS Wagon Transfer</t>
+          <t>SRS Containerised Freight</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
@@ -10646,7 +10646,7 @@
       <c r="B587" t="inlineStr"/>
       <c r="C587" t="inlineStr">
         <is>
-          <t>SCT Sadliers Transfer</t>
+          <t>SCT Light Engine Movement</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
@@ -11464,7 +11464,7 @@
       <c r="B633" t="inlineStr"/>
       <c r="C633" t="inlineStr">
         <is>
-          <t>PN Wagon Transfer</t>
+          <t>PN Containerised Freight</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
@@ -11816,7 +11816,7 @@
       <c r="B653" t="inlineStr"/>
       <c r="C653" t="inlineStr">
         <is>
-          <t>SCT Steel Shunt / Wine Train</t>
+          <t>SCT Wine Train / Steel Shunt</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
@@ -12526,7 +12526,7 @@
       <c r="B694" t="inlineStr"/>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Hunter Railcar Transfer</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
@@ -13622,7 +13622,7 @@
       <c r="B758" t="inlineStr"/>
       <c r="C758" t="inlineStr">
         <is>
-          <t>SSR Loaded Manildra Flour</t>
+          <t>SSR Empty Manildra Flour</t>
         </is>
       </c>
       <c r="D758" t="inlineStr">
@@ -14582,7 +14582,7 @@
       <c r="B812" t="inlineStr"/>
       <c r="C812" t="inlineStr">
         <is>
-          <t>JBR The Ghan Expedition</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D812" t="inlineStr">
@@ -17412,7 +17412,7 @@
       <c r="B977" t="inlineStr"/>
       <c r="C977" t="inlineStr">
         <is>
-          <t>QUBE Loaded Containerised Ore</t>
+          <t>QUBE BlueScope Steel</t>
         </is>
       </c>
       <c r="D977" t="inlineStr">
@@ -19004,7 +19004,7 @@
       <c r="B1069" t="inlineStr"/>
       <c r="C1069" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1069" t="inlineStr">
@@ -19404,7 +19404,7 @@
       <c r="B1093" t="inlineStr"/>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>PN Empty Aggregate</t>
+          <t>PN Minerals</t>
         </is>
       </c>
       <c r="D1093" t="inlineStr">
@@ -30611,7 +30611,7 @@
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -31443,7 +31443,7 @@
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>QUBE Loaded Containerised Ore</t>
+          <t>QUBE BlueScope Steel</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -31945,7 +31945,7 @@
       <c r="B171" t="inlineStr"/>
       <c r="C171" t="inlineStr">
         <is>
-          <t>PN Empty Aggregate</t>
+          <t>PN Minerals</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34049,7 +34049,7 @@
       <c r="B291" t="inlineStr"/>
       <c r="C291" t="inlineStr">
         <is>
-          <t>QUBE Light Engine</t>
+          <t>QUBE BlueScope Steel</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -35579,7 +35579,7 @@
       <c r="B378" t="inlineStr"/>
       <c r="C378" t="inlineStr">
         <is>
-          <t>AZ Coal</t>
+          <t>AZ Light Engine</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -37069,7 +37069,7 @@
       <c r="B463" t="inlineStr"/>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>V/Line Light Engine Movement</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -41029,7 +41029,7 @@
       <c r="B685" t="inlineStr"/>
       <c r="C685" t="inlineStr">
         <is>
-          <t>PN Wagon Transfer</t>
+          <t>PN Containerised Freight</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
@@ -42411,7 +42411,7 @@
       <c r="B762" t="inlineStr"/>
       <c r="C762" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D762" t="inlineStr">
@@ -46139,7 +46139,7 @@
       <c r="B972" t="inlineStr"/>
       <c r="C972" t="inlineStr">
         <is>
-          <t>SSR Manildra Grain Shuttle</t>
+          <t>SSR Containerised Freight</t>
         </is>
       </c>
       <c r="D972" t="inlineStr">
@@ -48662,7 +48662,7 @@
       <c r="B1113" t="inlineStr"/>
       <c r="C1113" t="inlineStr">
         <is>
-          <t>PN Coal</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D1113" t="inlineStr">
@@ -49177,7 +49177,7 @@
       <c r="B1142" t="inlineStr"/>
       <c r="C1142" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1142" t="inlineStr">
@@ -49537,7 +49537,7 @@
       <c r="B1162" t="inlineStr"/>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>SCT Sadliers Transfer</t>
+          <t>SCT Light Engine Movement</t>
         </is>
       </c>
       <c r="D1162" t="inlineStr">
@@ -51821,7 +51821,7 @@
       <c r="B1290" t="inlineStr"/>
       <c r="C1290" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Hunter Railcar Transfer</t>
         </is>
       </c>
       <c r="D1290" t="inlineStr">
@@ -52591,7 +52591,7 @@
       <c r="B1333" t="inlineStr"/>
       <c r="C1333" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning, pre 8145</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1333" t="inlineStr">
@@ -54233,7 +54233,7 @@
       <c r="B1430" t="inlineStr"/>
       <c r="C1430" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1430" t="inlineStr">
@@ -54323,7 +54323,7 @@
       <c r="B1435" t="inlineStr"/>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>SRS Wagon Transfer</t>
+          <t>SRS Containerised Freight</t>
         </is>
       </c>
       <c r="D1435" t="inlineStr">
@@ -54539,7 +54539,7 @@
       <c r="B1447" t="inlineStr"/>
       <c r="C1447" t="inlineStr">
         <is>
-          <t>SCT Steel Shunt / Wine Train</t>
+          <t>SCT Wine Train / Steel Shunt</t>
         </is>
       </c>
       <c r="D1447" t="inlineStr">
@@ -54891,7 +54891,7 @@
       <c r="B1467" t="inlineStr"/>
       <c r="C1467" t="inlineStr">
         <is>
-          <t>SSR Loaded Manildra Flour</t>
+          <t>SSR Empty Manildra Flour</t>
         </is>
       </c>
       <c r="D1467" t="inlineStr">
@@ -55107,7 +55107,7 @@
       <c r="B1479" t="inlineStr"/>
       <c r="C1479" t="inlineStr">
         <is>
-          <t>JBR The Ghan Expedition</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D1479" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1102,7 +1102,7 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>North East Line BG Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5930,7 +5930,7 @@
       <c r="B311" t="inlineStr"/>
       <c r="C311" t="inlineStr">
         <is>
-          <t>PN Coal</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -8868,7 +8868,7 @@
       <c r="B482" t="inlineStr"/>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Aurizon Intermodal</t>
+          <t>Aurizon Wagon Transfer</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -10124,7 +10124,7 @@
       <c r="B558" t="inlineStr"/>
       <c r="C558" t="inlineStr">
         <is>
-          <t>QUBE Container / Grain Shuttle</t>
+          <t>QUBE Grain</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
@@ -35489,7 +35489,7 @@
       <c r="B373" t="inlineStr"/>
       <c r="C373" t="inlineStr">
         <is>
-          <t>QUBE Container / Grain Shuttle</t>
+          <t>QUBE Grain</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -40109,7 +40109,7 @@
       <c r="B633" t="inlineStr"/>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Aurizon Intermodal</t>
+          <t>Aurizon Wagon Transfer</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
@@ -46585,7 +46585,7 @@
       <c r="B997" t="inlineStr"/>
       <c r="C997" t="inlineStr">
         <is>
-          <t>PN Coal</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D997" t="inlineStr">
@@ -52627,7 +52627,7 @@
       <c r="B1335" t="inlineStr"/>
       <c r="C1335" t="inlineStr">
         <is>
-          <t>North East Line BG Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1335" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1602,7 +1602,7 @@
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty V/Line Cars</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -6466,7 +6466,7 @@
       <c r="B341" t="inlineStr"/>
       <c r="C341" t="inlineStr">
         <is>
-          <t>PN Port Waratah Shunter</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -10336,7 +10336,7 @@
       <c r="B570" t="inlineStr"/>
       <c r="C570" t="inlineStr">
         <is>
-          <t>SRS Light Engine</t>
+          <t>AF&amp;F Container Train, SRS Crewed</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
@@ -12648,7 +12648,7 @@
       <c r="B701" t="inlineStr"/>
       <c r="C701" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
@@ -13192,7 +13192,7 @@
       <c r="B733" t="inlineStr"/>
       <c r="C733" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
@@ -17192,7 +17192,7 @@
       <c r="B965" t="inlineStr"/>
       <c r="C965" t="inlineStr">
         <is>
-          <t>QUBE BlueScope Steel</t>
+          <t>QUBE BlueScope Steel Shunt</t>
         </is>
       </c>
       <c r="D965" t="inlineStr">
@@ -17300,7 +17300,7 @@
       <c r="B971" t="inlineStr"/>
       <c r="C971" t="inlineStr">
         <is>
-          <t>QUBE BlueScope Steel</t>
+          <t>QUBE BlueScope Steel Shunt</t>
         </is>
       </c>
       <c r="D971" t="inlineStr">
@@ -19054,7 +19054,7 @@
       <c r="B1072" t="inlineStr"/>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>South Coast Service</t>
+          <t>South Coast Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1072" t="inlineStr">
@@ -27810,7 +27810,7 @@
       <c r="B1562" t="inlineStr"/>
       <c r="C1562" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Coal</t>
         </is>
       </c>
       <c r="D1562" t="inlineStr">
@@ -38979,7 +38979,7 @@
       <c r="B569" t="inlineStr"/>
       <c r="C569" t="inlineStr">
         <is>
-          <t>QUBE BlueScope Steel</t>
+          <t>QUBE BlueScope Steel Shunt</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
@@ -39069,7 +39069,7 @@
       <c r="B574" t="inlineStr"/>
       <c r="C574" t="inlineStr">
         <is>
-          <t>PN Port Waratah Shunter</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
@@ -39731,7 +39731,7 @@
       <c r="B611" t="inlineStr"/>
       <c r="C611" t="inlineStr">
         <is>
-          <t>SRS Light Engine</t>
+          <t>AF&amp;F Container Train, SRS Crewed</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
@@ -47275,7 +47275,7 @@
       <c r="B1035" t="inlineStr"/>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty V/Line Cars</t>
         </is>
       </c>
       <c r="D1035" t="inlineStr">
@@ -50931,7 +50931,7 @@
       <c r="B1240" t="inlineStr"/>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Coal</t>
         </is>
       </c>
       <c r="D1240" t="inlineStr">
@@ -51957,7 +51957,7 @@
       <c r="B1297" t="inlineStr"/>
       <c r="C1297" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1297" t="inlineStr">
@@ -54743,7 +54743,7 @@
       <c r="B1458" t="inlineStr"/>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1458" t="inlineStr">
@@ -55841,7 +55841,7 @@
       <c r="B1523" t="inlineStr"/>
       <c r="C1523" t="inlineStr">
         <is>
-          <t>QUBE BlueScope Steel</t>
+          <t>QUBE BlueScope Steel Shunt</t>
         </is>
       </c>
       <c r="D1523" t="inlineStr">
@@ -56123,7 +56123,7 @@
       <c r="B1540" t="inlineStr"/>
       <c r="C1540" t="inlineStr">
         <is>
-          <t>South Coast Service</t>
+          <t>South Coast Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1540" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -8312,7 +8312,7 @@
       <c r="B450" t="inlineStr"/>
       <c r="C450" t="inlineStr">
         <is>
-          <t>CBH SG Empty Grain</t>
+          <t>CBH SG Loaded Grain</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -8584,7 +8584,7 @@
       <c r="B466" t="inlineStr"/>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Aurizon Empty Copper</t>
+          <t>Aurizon Loaded Copper</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -8900,7 +8900,7 @@
       <c r="B484" t="inlineStr"/>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Yilgarn Iron Ore</t>
+          <t>Yilgarn Iron Iron Ore</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
@@ -9922,7 +9922,7 @@
       <c r="B547" t="inlineStr"/>
       <c r="C547" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
@@ -13102,7 +13102,7 @@
       <c r="B728" t="inlineStr"/>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
@@ -18892,7 +18892,7 @@
       <c r="B1063" t="inlineStr"/>
       <c r="C1063" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>Empty Car Provisioning (Forms SN34)</t>
         </is>
       </c>
       <c r="D1063" t="inlineStr">
@@ -19054,7 +19054,7 @@
       <c r="B1072" t="inlineStr"/>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>South Coast Empty Car Transfer</t>
+          <t>NSW Trainlink South Coast Service</t>
         </is>
       </c>
       <c r="D1072" t="inlineStr">
@@ -46131,7 +46131,7 @@
       <c r="B971" t="inlineStr"/>
       <c r="C971" t="inlineStr">
         <is>
-          <t>Yilgarn Iron Ore</t>
+          <t>Yilgarn Iron Iron Ore</t>
         </is>
       </c>
       <c r="D971" t="inlineStr">
@@ -49151,7 +49151,7 @@
       <c r="B1140" t="inlineStr"/>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1140" t="inlineStr">
@@ -52061,7 +52061,7 @@
       <c r="B1303" t="inlineStr"/>
       <c r="C1303" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>Empty Car Provisioning (Forms SN34)</t>
         </is>
       </c>
       <c r="D1303" t="inlineStr">
@@ -53641,7 +53641,7 @@
       <c r="B1393" t="inlineStr"/>
       <c r="C1393" t="inlineStr">
         <is>
-          <t>CBH SG Empty Grain</t>
+          <t>CBH SG Loaded Grain</t>
         </is>
       </c>
       <c r="D1393" t="inlineStr">
@@ -53777,7 +53777,7 @@
       <c r="B1401" t="inlineStr"/>
       <c r="C1401" t="inlineStr">
         <is>
-          <t>Aurizon Empty Copper</t>
+          <t>Aurizon Loaded Copper</t>
         </is>
       </c>
       <c r="D1401" t="inlineStr">
@@ -54243,7 +54243,7 @@
       <c r="B1430" t="inlineStr"/>
       <c r="C1430" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1430" t="inlineStr">
@@ -56123,7 +56123,7 @@
       <c r="B1540" t="inlineStr"/>
       <c r="C1540" t="inlineStr">
         <is>
-          <t>South Coast Empty Car Transfer</t>
+          <t>NSW Trainlink South Coast Service</t>
         </is>
       </c>
       <c r="D1540" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -580,7 +580,7 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -742,7 +742,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>V/Line Empty Cars</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1084,7 +1084,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1228,7 +1228,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>V1143</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2552,7 +2552,7 @@
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -2642,7 +2642,7 @@
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4330,7 +4330,7 @@
       <c r="B221" t="inlineStr"/>
       <c r="C221" t="inlineStr">
         <is>
-          <t>AZ Light Engine</t>
+          <t>AZ Coal</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -5984,7 +5984,7 @@
       <c r="B314" t="inlineStr"/>
       <c r="C314" t="inlineStr">
         <is>
-          <t>PN Grain Shuttle</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -6754,7 +6754,7 @@
       <c r="B357" t="inlineStr"/>
       <c r="C357" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -11640,7 +11640,7 @@
       <c r="B643" t="inlineStr"/>
       <c r="C643" t="inlineStr">
         <is>
-          <t>PN Containerised Freight</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
@@ -12540,7 +12540,7 @@
       <c r="B695" t="inlineStr"/>
       <c r="C695" t="inlineStr">
         <is>
-          <t>Hunter Railcar Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
@@ -12684,7 +12684,7 @@
       <c r="B703" t="inlineStr"/>
       <c r="C703" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
@@ -13192,7 +13192,7 @@
       <c r="B733" t="inlineStr"/>
       <c r="C733" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
@@ -16602,7 +16602,7 @@
       <c r="B930" t="inlineStr"/>
       <c r="C930" t="inlineStr">
         <is>
-          <t>Watco Trip Train</t>
+          <t>Watco Light Engine</t>
         </is>
       </c>
       <c r="D930" t="inlineStr">
@@ -17192,7 +17192,7 @@
       <c r="B965" t="inlineStr"/>
       <c r="C965" t="inlineStr">
         <is>
-          <t>QUBE BlueScope Steel Shunt</t>
+          <t>QUBE BlueScope Steel</t>
         </is>
       </c>
       <c r="D965" t="inlineStr">
@@ -17728,7 +17728,7 @@
       <c r="B995" t="inlineStr"/>
       <c r="C995" t="inlineStr">
         <is>
-          <t>SSR Grain</t>
+          <t>SSR D Set Transfer / Grain Shuttle</t>
         </is>
       </c>
       <c r="D995" t="inlineStr">
@@ -18732,7 +18732,7 @@
       <c r="B1053" t="inlineStr"/>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>SSR Manildra Grain Shuttle</t>
+          <t>SSR Freight Shuttle</t>
         </is>
       </c>
       <c r="D1053" t="inlineStr">
@@ -18964,7 +18964,7 @@
       <c r="B1067" t="inlineStr"/>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1067" t="inlineStr">
@@ -19880,7 +19880,7 @@
       <c r="B1121" t="inlineStr"/>
       <c r="C1121" t="inlineStr">
         <is>
-          <t>QUBE Light Engine</t>
+          <t>QUBE Containerised Freight</t>
         </is>
       </c>
       <c r="D1121" t="inlineStr">
@@ -30869,7 +30869,7 @@
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Watco Trip Train</t>
+          <t>Watco Light Engine</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -31819,7 +31819,7 @@
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32871,7 +32871,7 @@
       <c r="B223" t="inlineStr"/>
       <c r="C223" t="inlineStr">
         <is>
-          <t>PN Grain Shuttle</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -34537,7 +34537,7 @@
       <c r="B318" t="inlineStr"/>
       <c r="C318" t="inlineStr">
         <is>
-          <t>QUBE Light Engine</t>
+          <t>QUBE Containerised Freight</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -35607,7 +35607,7 @@
       <c r="B379" t="inlineStr"/>
       <c r="C379" t="inlineStr">
         <is>
-          <t>AZ Light Engine</t>
+          <t>AZ Coal</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -37709,7 +37709,7 @@
       <c r="B498" t="inlineStr"/>
       <c r="C498" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
@@ -38781,7 +38781,7 @@
       <c r="B558" t="inlineStr"/>
       <c r="C558" t="inlineStr">
         <is>
-          <t>PN Containerised Freight</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
@@ -40967,7 +40967,7 @@
       <c r="B681" t="inlineStr"/>
       <c r="C681" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
@@ -43801,7 +43801,7 @@
       <c r="B840" t="inlineStr"/>
       <c r="C840" t="inlineStr">
         <is>
-          <t>SSR Grain</t>
+          <t>SSR D Set Transfer / Grain Shuttle</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
@@ -45183,7 +45183,7 @@
       <c r="B917" t="inlineStr"/>
       <c r="C917" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>V1143</t>
         </is>
       </c>
       <c r="D917" t="inlineStr">
@@ -45359,7 +45359,7 @@
       <c r="B927" t="inlineStr"/>
       <c r="C927" t="inlineStr">
         <is>
-          <t>Bathurst Bullet</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D927" t="inlineStr">
@@ -47613,7 +47613,7 @@
       <c r="B1054" t="inlineStr"/>
       <c r="C1054" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>V/Line Empty Cars</t>
         </is>
       </c>
       <c r="D1054" t="inlineStr">
@@ -48172,7 +48172,7 @@
       <c r="B1085" t="inlineStr"/>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>SSR Manildra Grain Shuttle</t>
+          <t>SSR Freight Shuttle</t>
         </is>
       </c>
       <c r="D1085" t="inlineStr">
@@ -48352,7 +48352,7 @@
       <c r="B1095" t="inlineStr"/>
       <c r="C1095" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1095" t="inlineStr">
@@ -51849,7 +51849,7 @@
       <c r="B1291" t="inlineStr"/>
       <c r="C1291" t="inlineStr">
         <is>
-          <t>Hunter Railcar Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1291" t="inlineStr">
@@ -51957,7 +51957,7 @@
       <c r="B1297" t="inlineStr"/>
       <c r="C1297" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1297" t="inlineStr">
@@ -52529,7 +52529,7 @@
       <c r="B1329" t="inlineStr"/>
       <c r="C1329" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1329" t="inlineStr">
@@ -52637,7 +52637,7 @@
       <c r="B1335" t="inlineStr"/>
       <c r="C1335" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1335" t="inlineStr">
@@ -55841,7 +55841,7 @@
       <c r="B1523" t="inlineStr"/>
       <c r="C1523" t="inlineStr">
         <is>
-          <t>QUBE BlueScope Steel Shunt</t>
+          <t>QUBE BlueScope Steel</t>
         </is>
       </c>
       <c r="D1523" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1800,7 +1800,7 @@
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -1818,7 +1818,7 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>North East Line BG Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2552,7 +2552,7 @@
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -2588,7 +2588,7 @@
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -2624,7 +2624,7 @@
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -2786,7 +2786,7 @@
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -2894,7 +2894,7 @@
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>North East SG Line Service</t>
+          <t>North East Line SG Service</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -5930,7 +5930,7 @@
       <c r="B311" t="inlineStr"/>
       <c r="C311" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Coal</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -9710,7 +9710,7 @@
       <c r="B535" t="inlineStr"/>
       <c r="C535" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Limestone</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
@@ -9940,7 +9940,7 @@
       <c r="B548" t="inlineStr"/>
       <c r="C548" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
@@ -11158,7 +11158,7 @@
       <c r="B616" t="inlineStr"/>
       <c r="C616" t="inlineStr">
         <is>
-          <t>NSW TrainLink Xplorer</t>
+          <t>NSW Trainlink empty car transfer</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
@@ -12648,7 +12648,7 @@
       <c r="B701" t="inlineStr"/>
       <c r="C701" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
@@ -14542,7 +14542,7 @@
       <c r="B810" t="inlineStr"/>
       <c r="C810" t="inlineStr">
         <is>
-          <t>PN Broken Hill Shunter</t>
+          <t>PN Loaded Lead/Zinc</t>
         </is>
       </c>
       <c r="D810" t="inlineStr">
@@ -14916,7 +14916,7 @@
       <c r="B831" t="inlineStr"/>
       <c r="C831" t="inlineStr">
         <is>
-          <t>PN Infrabuild Steel via Lithgow</t>
+          <t>PN Infrabuild Steel</t>
         </is>
       </c>
       <c r="D831" t="inlineStr">
@@ -16188,7 +16188,7 @@
       <c r="B903" t="inlineStr"/>
       <c r="C903" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>PN Light Engine Movement</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
@@ -17444,7 +17444,7 @@
       <c r="B979" t="inlineStr"/>
       <c r="C979" t="inlineStr">
         <is>
-          <t>QUBE Containerised Cotton</t>
+          <t>QUBE Containerised Freight</t>
         </is>
       </c>
       <c r="D979" t="inlineStr">
@@ -18318,7 +18318,7 @@
       <c r="B1030" t="inlineStr"/>
       <c r="C1030" t="inlineStr">
         <is>
-          <t>North Eastern Line BG Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D1030" t="inlineStr">
@@ -18910,7 +18910,7 @@
       <c r="B1064" t="inlineStr"/>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D1064" t="inlineStr">
@@ -19054,7 +19054,7 @@
       <c r="B1072" t="inlineStr"/>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>NSW Trainlink South Coast Service</t>
+          <t>South Coast Service</t>
         </is>
       </c>
       <c r="D1072" t="inlineStr">
@@ -32511,7 +32511,7 @@
       <c r="B203" t="inlineStr"/>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -36529,7 +36529,7 @@
       <c r="B432" t="inlineStr"/>
       <c r="C432" t="inlineStr">
         <is>
-          <t>QUBE Containerised Cotton</t>
+          <t>QUBE Containerised Freight</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -37691,7 +37691,7 @@
       <c r="B497" t="inlineStr"/>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
@@ -37835,7 +37835,7 @@
       <c r="B505" t="inlineStr"/>
       <c r="C505" t="inlineStr">
         <is>
-          <t>PN Infrabuild Steel via Lithgow</t>
+          <t>PN Infrabuild Steel</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
@@ -41399,7 +41399,7 @@
       <c r="B705" t="inlineStr"/>
       <c r="C705" t="inlineStr">
         <is>
-          <t>North Eastern Line BG Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
@@ -42913,7 +42913,7 @@
       <c r="B790" t="inlineStr"/>
       <c r="C790" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>PN Light Engine Movement</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
@@ -44485,7 +44485,7 @@
       <c r="B878" t="inlineStr"/>
       <c r="C878" t="inlineStr">
         <is>
-          <t>North East Line BG Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D878" t="inlineStr">
@@ -46613,7 +46613,7 @@
       <c r="B998" t="inlineStr"/>
       <c r="C998" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Coal</t>
         </is>
       </c>
       <c r="D998" t="inlineStr">
@@ -47293,7 +47293,7 @@
       <c r="B1036" t="inlineStr"/>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>North East SG Line Service</t>
+          <t>North East Line SG Service</t>
         </is>
       </c>
       <c r="D1036" t="inlineStr">
@@ -47721,7 +47721,7 @@
       <c r="B1060" t="inlineStr"/>
       <c r="C1060" t="inlineStr">
         <is>
-          <t>NSW TrainLink Xplorer</t>
+          <t>NSW Trainlink empty car transfer</t>
         </is>
       </c>
       <c r="D1060" t="inlineStr">
@@ -50967,7 +50967,7 @@
       <c r="B1242" t="inlineStr"/>
       <c r="C1242" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1242" t="inlineStr">
@@ -51723,7 +51723,7 @@
       <c r="B1284" t="inlineStr"/>
       <c r="C1284" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1284" t="inlineStr">
@@ -52529,7 +52529,7 @@
       <c r="B1329" t="inlineStr"/>
       <c r="C1329" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D1329" t="inlineStr">
@@ -54135,7 +54135,7 @@
       <c r="B1424" t="inlineStr"/>
       <c r="C1424" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Limestone</t>
         </is>
       </c>
       <c r="D1424" t="inlineStr">
@@ -54261,7 +54261,7 @@
       <c r="B1431" t="inlineStr"/>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1431" t="inlineStr">
@@ -54743,7 +54743,7 @@
       <c r="B1458" t="inlineStr"/>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1458" t="inlineStr">
@@ -55117,7 +55117,7 @@
       <c r="B1479" t="inlineStr"/>
       <c r="C1479" t="inlineStr">
         <is>
-          <t>PN Broken Hill Shunter</t>
+          <t>PN Loaded Lead/Zinc</t>
         </is>
       </c>
       <c r="D1479" t="inlineStr">
@@ -56069,7 +56069,7 @@
       <c r="B1537" t="inlineStr"/>
       <c r="C1537" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D1537" t="inlineStr">
@@ -56123,7 +56123,7 @@
       <c r="B1540" t="inlineStr"/>
       <c r="C1540" t="inlineStr">
         <is>
-          <t>NSW Trainlink South Coast Service</t>
+          <t>South Coast Service</t>
         </is>
       </c>
       <c r="D1540" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -472,7 +472,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -562,7 +562,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Northeast Line BG Service</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -742,7 +742,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>V/Line Empty Cars</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1084,7 +1084,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1228,7 +1228,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>V1143</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1480,7 +1480,7 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1602,7 +1602,7 @@
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Empty V/Line Cars</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1656,7 +1656,7 @@
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -1692,7 +1692,7 @@
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1728,7 +1728,7 @@
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -1746,7 +1746,7 @@
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -1940,7 +1940,7 @@
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -1958,7 +1958,7 @@
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2174,7 +2174,7 @@
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2966,7 +2966,7 @@
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>North East SG Line Service</t>
+          <t>North East Line SG Service</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -5948,7 +5948,7 @@
       <c r="B312" t="inlineStr"/>
       <c r="C312" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Coal</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -6322,7 +6322,7 @@
       <c r="B333" t="inlineStr"/>
       <c r="C333" t="inlineStr">
         <is>
-          <t>PN Local Shunter</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -10462,7 +10462,7 @@
       <c r="B577" t="inlineStr"/>
       <c r="C577" t="inlineStr">
         <is>
-          <t>SSR Cement Clinker</t>
+          <t>SSR Shunter</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
@@ -11194,7 +11194,7 @@
       <c r="B618" t="inlineStr"/>
       <c r="C618" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer</t>
+          <t>NSW Trainlink Xplorer to Sydney (connects with NP24)</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
@@ -12020,7 +12020,7 @@
       <c r="B665" t="inlineStr"/>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Aurizon Intermodal</t>
+          <t>Aurizon Light Engine</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
@@ -12480,7 +12480,7 @@
       <c r="B691" t="inlineStr"/>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Aurizon Wagon Transfer</t>
+          <t>Aurizon Empty Ore</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
@@ -13102,7 +13102,7 @@
       <c r="B728" t="inlineStr"/>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Bathurst Bullet - Transfer</t>
+          <t>Additional Bathurst Service</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
@@ -13564,7 +13564,7 @@
       <c r="B755" t="inlineStr"/>
       <c r="C755" t="inlineStr">
         <is>
-          <t>SSR Manildra Grain Shuttle</t>
+          <t>SSR Freight Shuttle</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
@@ -16188,7 +16188,7 @@
       <c r="B903" t="inlineStr"/>
       <c r="C903" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>JBR The Overland</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
@@ -18160,7 +18160,7 @@
       <c r="B1021" t="inlineStr"/>
       <c r="C1021" t="inlineStr">
         <is>
-          <t>NorthEast BG Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D1021" t="inlineStr">
@@ -18678,7 +18678,7 @@
       <c r="B1050" t="inlineStr"/>
       <c r="C1050" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1050" t="inlineStr">
@@ -18750,7 +18750,7 @@
       <c r="B1054" t="inlineStr"/>
       <c r="C1054" t="inlineStr">
         <is>
-          <t>Watco Trip Train</t>
+          <t>Watco Light Engine</t>
         </is>
       </c>
       <c r="D1054" t="inlineStr">
@@ -19454,7 +19454,7 @@
       <c r="B1096" t="inlineStr"/>
       <c r="C1096" t="inlineStr">
         <is>
-          <t>PN Minerals</t>
+          <t>PN Loaded Aggregate</t>
         </is>
       </c>
       <c r="D1096" t="inlineStr">
@@ -28224,7 +28224,7 @@
       <c r="B1585" t="inlineStr"/>
       <c r="C1585" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW TrainLink XPT</t>
         </is>
       </c>
       <c r="D1585" t="inlineStr">
@@ -28346,7 +28346,7 @@
       <c r="B1592" t="inlineStr"/>
       <c r="C1592" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW TrainLink XPT</t>
         </is>
       </c>
       <c r="D1592" t="inlineStr">
@@ -28382,7 +28382,7 @@
       <c r="B1594" t="inlineStr"/>
       <c r="C1594" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW TrainLink XPT</t>
         </is>
       </c>
       <c r="D1594" t="inlineStr">
@@ -30657,7 +30657,7 @@
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -30851,7 +30851,7 @@
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW TrainLink XPT</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -33061,7 +33061,7 @@
       <c r="B234" t="inlineStr"/>
       <c r="C234" t="inlineStr">
         <is>
-          <t>PN Local Shunter</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -33307,7 +33307,7 @@
       <c r="B249" t="inlineStr"/>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Watco Trip Train</t>
+          <t>Watco Light Engine</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -35751,7 +35751,7 @@
       <c r="B387" t="inlineStr"/>
       <c r="C387" t="inlineStr">
         <is>
-          <t>SSR Manildra Grain Shuttle</t>
+          <t>SSR Freight Shuttle</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -37115,7 +37115,7 @@
       <c r="B465" t="inlineStr"/>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -37439,7 +37439,7 @@
       <c r="B483" t="inlineStr"/>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -37727,7 +37727,7 @@
       <c r="B499" t="inlineStr"/>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
@@ -39105,7 +39105,7 @@
       <c r="B576" t="inlineStr"/>
       <c r="C576" t="inlineStr">
         <is>
-          <t>PN Minerals</t>
+          <t>PN Loaded Aggregate</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
@@ -40985,7 +40985,7 @@
       <c r="B682" t="inlineStr"/>
       <c r="C682" t="inlineStr">
         <is>
-          <t>Aurizon Wagon Transfer</t>
+          <t>Aurizon Empty Ore</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
@@ -42507,7 +42507,7 @@
       <c r="B767" t="inlineStr"/>
       <c r="C767" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Northeast Line BG Service</t>
         </is>
       </c>
       <c r="D767" t="inlineStr">
@@ -42913,7 +42913,7 @@
       <c r="B790" t="inlineStr"/>
       <c r="C790" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>JBR The Overland</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
@@ -43215,7 +43215,7 @@
       <c r="B807" t="inlineStr"/>
       <c r="C807" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer</t>
+          <t>NSW Trainlink Xplorer to Sydney (connects with NP24)</t>
         </is>
       </c>
       <c r="D807" t="inlineStr">
@@ -44467,7 +44467,7 @@
       <c r="B877" t="inlineStr"/>
       <c r="C877" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D877" t="inlineStr">
@@ -45183,7 +45183,7 @@
       <c r="B917" t="inlineStr"/>
       <c r="C917" t="inlineStr">
         <is>
-          <t>V1143</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D917" t="inlineStr">
@@ -47275,7 +47275,7 @@
       <c r="B1035" t="inlineStr"/>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>Empty V/Line Cars</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1035" t="inlineStr">
@@ -47613,7 +47613,7 @@
       <c r="B1054" t="inlineStr"/>
       <c r="C1054" t="inlineStr">
         <is>
-          <t>V/Line Empty Cars</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1054" t="inlineStr">
@@ -47793,7 +47793,7 @@
       <c r="B1064" t="inlineStr"/>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>NorthEast BG Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D1064" t="inlineStr">
@@ -48690,7 +48690,7 @@
       <c r="B1114" t="inlineStr"/>
       <c r="C1114" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Coal</t>
         </is>
       </c>
       <c r="D1114" t="inlineStr">
@@ -49151,7 +49151,7 @@
       <c r="B1140" t="inlineStr"/>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>Bathurst Bullet - Transfer</t>
+          <t>Additional Bathurst Service</t>
         </is>
       </c>
       <c r="D1140" t="inlineStr">
@@ -50561,7 +50561,7 @@
       <c r="B1219" t="inlineStr"/>
       <c r="C1219" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1219" t="inlineStr">
@@ -51597,7 +51597,7 @@
       <c r="B1277" t="inlineStr"/>
       <c r="C1277" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1277" t="inlineStr">
@@ -52043,7 +52043,7 @@
       <c r="B1302" t="inlineStr"/>
       <c r="C1302" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1302" t="inlineStr">
@@ -52637,7 +52637,7 @@
       <c r="B1335" t="inlineStr"/>
       <c r="C1335" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1335" t="inlineStr">
@@ -52709,7 +52709,7 @@
       <c r="B1339" t="inlineStr"/>
       <c r="C1339" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D1339" t="inlineStr">
@@ -52763,7 +52763,7 @@
       <c r="B1342" t="inlineStr"/>
       <c r="C1342" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1342" t="inlineStr">
@@ -52817,7 +52817,7 @@
       <c r="B1345" t="inlineStr"/>
       <c r="C1345" t="inlineStr">
         <is>
-          <t>North East SG Line Service</t>
+          <t>North East Line SG Service</t>
         </is>
       </c>
       <c r="D1345" t="inlineStr">
@@ -54387,7 +54387,7 @@
       <c r="B1438" t="inlineStr"/>
       <c r="C1438" t="inlineStr">
         <is>
-          <t>SSR Cement Clinker</t>
+          <t>SSR Shunter</t>
         </is>
       </c>
       <c r="D1438" t="inlineStr">
@@ -54599,7 +54599,7 @@
       <c r="B1450" t="inlineStr"/>
       <c r="C1450" t="inlineStr">
         <is>
-          <t>Aurizon Intermodal</t>
+          <t>Aurizon Light Engine</t>
         </is>
       </c>
       <c r="D1450" t="inlineStr">
@@ -57113,7 +57113,7 @@
       <c r="B1595" t="inlineStr"/>
       <c r="C1595" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW TrainLink XPT</t>
         </is>
       </c>
       <c r="D1595" t="inlineStr">
@@ -57149,7 +57149,7 @@
       <c r="B1597" t="inlineStr"/>
       <c r="C1597" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW TrainLink XPT</t>
         </is>
       </c>
       <c r="D1597" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -832,7 +832,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1922,7 +1922,7 @@
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2588,7 +2588,7 @@
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Northern Line</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -2768,7 +2768,7 @@
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -5268,7 +5268,7 @@
       <c r="B274" t="inlineStr"/>
       <c r="C274" t="inlineStr">
         <is>
-          <t>PN Grain</t>
+          <t>PN Grain Shuttle</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -5354,7 +5354,7 @@
       <c r="B279" t="inlineStr"/>
       <c r="C279" t="inlineStr">
         <is>
-          <t>PN Manildra Container Service</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -6322,7 +6322,7 @@
       <c r="B333" t="inlineStr"/>
       <c r="C333" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -8178,7 +8178,7 @@
       <c r="B441" t="inlineStr"/>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>SRHC Tour/ Private Charter</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -8736,7 +8736,11 @@
         </is>
       </c>
       <c r="B475" t="inlineStr"/>
-      <c r="C475" t="inlineStr"/>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Aurizon North Quay Container Shuttle</t>
+        </is>
+      </c>
       <c r="D475" t="inlineStr">
         <is>
           <t>2026-04-15 10:26:07</t>
@@ -12264,7 +12268,7 @@
       <c r="B679" t="inlineStr"/>
       <c r="C679" t="inlineStr">
         <is>
-          <t>Aurizon Empty Ore</t>
+          <t>Aurizon Loaded Ore</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
@@ -14930,7 +14934,7 @@
       <c r="B832" t="inlineStr"/>
       <c r="C832" t="inlineStr">
         <is>
-          <t>PN Infrabuild Steel</t>
+          <t>NR39</t>
         </is>
       </c>
       <c r="D832" t="inlineStr">
@@ -15332,7 +15336,7 @@
       <c r="B855" t="inlineStr"/>
       <c r="C855" t="inlineStr">
         <is>
-          <t>NR64</t>
+          <t>PN Containerised Freight</t>
         </is>
       </c>
       <c r="D855" t="inlineStr">
@@ -18210,7 +18214,7 @@
       <c r="B1024" t="inlineStr"/>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>North-East BG Service</t>
         </is>
       </c>
       <c r="D1024" t="inlineStr">
@@ -18330,7 +18334,11 @@
         </is>
       </c>
       <c r="B1031" t="inlineStr"/>
-      <c r="C1031" t="inlineStr"/>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>V/Line Test Train</t>
+        </is>
+      </c>
       <c r="D1031" t="inlineStr">
         <is>
           <t>2026-04-23 02:49:46</t>
@@ -18418,7 +18426,7 @@
       <c r="B1036" t="inlineStr"/>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>NorthEast BG Line Service</t>
         </is>
       </c>
       <c r="D1036" t="inlineStr">
@@ -19118,7 +19126,7 @@
       <c r="B1076" t="inlineStr"/>
       <c r="C1076" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1076" t="inlineStr">
@@ -19482,7 +19490,7 @@
       <c r="B1098" t="inlineStr"/>
       <c r="C1098" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D1098" t="inlineStr">
@@ -28662,7 +28670,7 @@
       <c r="B1610" t="inlineStr"/>
       <c r="C1610" t="inlineStr">
         <is>
-          <t>ORA Coal</t>
+          <t>ORA Shunter</t>
         </is>
       </c>
       <c r="D1610" t="inlineStr">
@@ -28680,7 +28688,7 @@
       <c r="B1611" t="inlineStr"/>
       <c r="C1611" t="inlineStr">
         <is>
-          <t>ORA trip train</t>
+          <t>ORA Shunter</t>
         </is>
       </c>
       <c r="D1611" t="inlineStr">
@@ -29205,7 +29213,11 @@
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>V/Line Test Train</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>2026-04-23 02:49:46</t>
@@ -29457,7 +29469,7 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -29741,7 +29753,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ORA trip train</t>
+          <t>ORA Shunter</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -30677,7 +30689,11 @@
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
-      <c r="C91" t="inlineStr"/>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Aurizon North Quay Container Shuttle</t>
+        </is>
+      </c>
       <c r="D91" t="inlineStr">
         <is>
           <t>2026-04-15 10:26:07</t>
@@ -31599,7 +31615,7 @@
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>PN Manildra Container Service</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -31965,7 +31981,7 @@
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
-          <t>PN Grain</t>
+          <t>PN Grain Shuttle</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33261,7 +33277,7 @@
       <c r="B240" t="inlineStr"/>
       <c r="C240" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -35487,7 +35503,7 @@
       <c r="B367" t="inlineStr"/>
       <c r="C367" t="inlineStr">
         <is>
-          <t>ORA Coal</t>
+          <t>ORA Shunter</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -37891,7 +37907,7 @@
       <c r="B503" t="inlineStr"/>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Northern Line</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
@@ -40987,7 +41003,7 @@
       <c r="B677" t="inlineStr"/>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>North-East BG Service</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
@@ -41599,7 +41615,7 @@
       <c r="B711" t="inlineStr"/>
       <c r="C711" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>NorthEast BG Line Service</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
@@ -43325,7 +43341,7 @@
       <c r="B808" t="inlineStr"/>
       <c r="C808" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>SRHC Tour/ Private Charter</t>
         </is>
       </c>
       <c r="D808" t="inlineStr">
@@ -43803,7 +43819,7 @@
       <c r="B835" t="inlineStr"/>
       <c r="C835" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D835" t="inlineStr">
@@ -45839,7 +45855,7 @@
       <c r="B949" t="inlineStr"/>
       <c r="C949" t="inlineStr">
         <is>
-          <t>PN Infrabuild Steel</t>
+          <t>NR39</t>
         </is>
       </c>
       <c r="D949" t="inlineStr">
@@ -47601,7 +47617,7 @@
       <c r="B1048" t="inlineStr"/>
       <c r="C1048" t="inlineStr">
         <is>
-          <t>NR64</t>
+          <t>PN Containerised Freight</t>
         </is>
       </c>
       <c r="D1048" t="inlineStr">
@@ -49405,7 +49421,7 @@
       <c r="B1149" t="inlineStr"/>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1149" t="inlineStr">
@@ -51203,7 +51219,7 @@
       <c r="B1250" t="inlineStr"/>
       <c r="C1250" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1250" t="inlineStr">
@@ -52783,7 +52799,7 @@
       <c r="B1338" t="inlineStr"/>
       <c r="C1338" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1338" t="inlineStr">
@@ -54835,7 +54851,7 @@
       <c r="B1458" t="inlineStr"/>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>Aurizon Empty Ore</t>
+          <t>Aurizon Loaded Ore</t>
         </is>
       </c>
       <c r="D1458" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -472,7 +472,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -562,7 +562,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -742,7 +742,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5642,7 +5642,7 @@
       <c r="B295" t="inlineStr"/>
       <c r="C295" t="inlineStr">
         <is>
-          <t>PN Trip Train, ex 8124</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -8688,7 +8688,7 @@
       <c r="B472" t="inlineStr"/>
       <c r="C472" t="inlineStr">
         <is>
-          <t>SCT Steel Transfer</t>
+          <t>SCT Aurizon Loading Transfer</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -9380,7 +9380,7 @@
       <c r="B516" t="inlineStr"/>
       <c r="C516" t="inlineStr">
         <is>
-          <t>SSR Wagon Transfer</t>
+          <t>SSR Light Engine</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
@@ -11266,7 +11266,7 @@
       <c r="B622" t="inlineStr"/>
       <c r="C622" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer (Joins SP34)</t>
+          <t>NSW Trainlink Xplorer</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
@@ -12648,7 +12648,7 @@
       <c r="B701" t="inlineStr"/>
       <c r="C701" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
@@ -15476,7 +15476,7 @@
       <c r="B863" t="inlineStr"/>
       <c r="C863" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>PN Light Engine Movement</t>
         </is>
       </c>
       <c r="D863" t="inlineStr">
@@ -19526,7 +19526,7 @@
       <c r="B1100" t="inlineStr"/>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>PN Minerals</t>
+          <t>PN Loaded Aggregate</t>
         </is>
       </c>
       <c r="D1100" t="inlineStr">
@@ -28418,7 +28418,7 @@
       <c r="B1596" t="inlineStr"/>
       <c r="C1596" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (Forms NT31)</t>
         </is>
       </c>
       <c r="D1596" t="inlineStr">
@@ -31389,7 +31389,7 @@
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SSR Wagon Transfer</t>
+          <t>SSR Light Engine</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -32189,7 +32189,7 @@
       <c r="B178" t="inlineStr"/>
       <c r="C178" t="inlineStr">
         <is>
-          <t>PN Minerals</t>
+          <t>PN Loaded Aggregate</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -37655,7 +37655,7 @@
       <c r="B489" t="inlineStr"/>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -42723,7 +42723,7 @@
       <c r="B773" t="inlineStr"/>
       <c r="C773" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D773" t="inlineStr">
@@ -47563,7 +47563,7 @@
       <c r="B1045" t="inlineStr"/>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer (Joins SP34)</t>
+          <t>NSW Trainlink Xplorer</t>
         </is>
       </c>
       <c r="D1045" t="inlineStr">
@@ -47829,7 +47829,7 @@
       <c r="B1060" t="inlineStr"/>
       <c r="C1060" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1060" t="inlineStr">
@@ -47901,7 +47901,7 @@
       <c r="B1064" t="inlineStr"/>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>PN Trip Train, ex 8124</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D1064" t="inlineStr">
@@ -49939,7 +49939,7 @@
       <c r="B1178" t="inlineStr"/>
       <c r="C1178" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>PN Light Engine Movement</t>
         </is>
       </c>
       <c r="D1178" t="inlineStr">
@@ -51381,7 +51381,7 @@
       <c r="B1259" t="inlineStr"/>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>SCT Steel Transfer</t>
+          <t>SCT Aurizon Loading Transfer</t>
         </is>
       </c>
       <c r="D1259" t="inlineStr">
@@ -54923,7 +54923,7 @@
       <c r="B1462" t="inlineStr"/>
       <c r="C1462" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1462" t="inlineStr">
@@ -57293,7 +57293,7 @@
       <c r="B1599" t="inlineStr"/>
       <c r="C1599" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (Forms NT31)</t>
         </is>
       </c>
       <c r="D1599" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1372,7 +1372,7 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2318,7 +2318,7 @@
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2840,7 +2840,7 @@
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Northeast Line BG Service</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3052,7 +3052,7 @@
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>QUBE Containerised Freight</t>
+          <t>QUBE Light Engine</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -5088,7 +5088,7 @@
       <c r="B264" t="inlineStr"/>
       <c r="C264" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Grain Shuttle</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -8086,7 +8086,7 @@
       <c r="B435" t="inlineStr"/>
       <c r="C435" t="inlineStr">
         <is>
-          <t>PN Sugar shuttle / shunter</t>
+          <t>PN Sugar Shuttle / Shunter</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -8738,7 +8738,7 @@
       <c r="B475" t="inlineStr"/>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Aurizon North Quay Container Shuttle</t>
+          <t>Aurizon Intermodal</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -12214,7 +12214,7 @@
       <c r="B676" t="inlineStr"/>
       <c r="C676" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Grain</t>
+          <t>Aurizon Wagon Transfer</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
@@ -12774,7 +12774,7 @@
       <c r="B708" t="inlineStr"/>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
@@ -12792,7 +12792,7 @@
       <c r="B709" t="inlineStr"/>
       <c r="C709" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
@@ -14848,7 +14848,7 @@
       <c r="B827" t="inlineStr"/>
       <c r="C827" t="inlineStr">
         <is>
-          <t>PN Infrabuild Steel</t>
+          <t>PN Steel Transfer</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
@@ -18858,7 +18858,7 @@
       <c r="B1060" t="inlineStr"/>
       <c r="C1060" t="inlineStr">
         <is>
-          <t>Watco Light Engine</t>
+          <t>Watco Trip Train</t>
         </is>
       </c>
       <c r="D1060" t="inlineStr">
@@ -19526,7 +19526,7 @@
       <c r="B1100" t="inlineStr"/>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>PN Loaded Aggregate</t>
+          <t>PN Empty Aggregate</t>
         </is>
       </c>
       <c r="D1100" t="inlineStr">
@@ -28296,7 +28296,7 @@
       <c r="B1589" t="inlineStr"/>
       <c r="C1589" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (ex NT34)</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1589" t="inlineStr">
@@ -28756,7 +28756,7 @@
       <c r="B1615" t="inlineStr"/>
       <c r="C1615" t="inlineStr">
         <is>
-          <t>ORA Coal</t>
+          <t>ORA Shunter</t>
         </is>
       </c>
       <c r="D1615" t="inlineStr">
@@ -30691,7 +30691,7 @@
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Aurizon North Quay Container Shuttle</t>
+          <t>Aurizon Intermodal</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -32189,7 +32189,7 @@
       <c r="B178" t="inlineStr"/>
       <c r="C178" t="inlineStr">
         <is>
-          <t>PN Loaded Aggregate</t>
+          <t>PN Empty Aggregate</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -32943,7 +32943,7 @@
       <c r="B221" t="inlineStr"/>
       <c r="C221" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Grain Shuttle</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -33523,7 +33523,7 @@
       <c r="B255" t="inlineStr"/>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Watco Light Engine</t>
+          <t>Watco Trip Train</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -33667,7 +33667,7 @@
       <c r="B263" t="inlineStr"/>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Grain</t>
+          <t>Aurizon Wagon Transfer</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -35769,7 +35769,7 @@
       <c r="B382" t="inlineStr"/>
       <c r="C382" t="inlineStr">
         <is>
-          <t>QUBE Containerised Freight</t>
+          <t>QUBE Light Engine</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -37673,7 +37673,7 @@
       <c r="B490" t="inlineStr"/>
       <c r="C490" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
@@ -39807,7 +39807,7 @@
       <c r="B609" t="inlineStr"/>
       <c r="C609" t="inlineStr">
         <is>
-          <t>PN Sugar shuttle / shunter</t>
+          <t>PN Sugar Shuttle / Shunter</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
@@ -50173,7 +50173,7 @@
       <c r="B1191" t="inlineStr"/>
       <c r="C1191" t="inlineStr">
         <is>
-          <t>PN Infrabuild Steel</t>
+          <t>PN Steel Transfer</t>
         </is>
       </c>
       <c r="D1191" t="inlineStr">
@@ -50291,7 +50291,7 @@
       <c r="B1198" t="inlineStr"/>
       <c r="C1198" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (ex NT34)</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1198" t="inlineStr">
@@ -50795,7 +50795,7 @@
       <c r="B1226" t="inlineStr"/>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Northeast Line BG Service</t>
         </is>
       </c>
       <c r="D1226" t="inlineStr">
@@ -51507,7 +51507,7 @@
       <c r="B1266" t="inlineStr"/>
       <c r="C1266" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1266" t="inlineStr">
@@ -51831,7 +51831,7 @@
       <c r="B1284" t="inlineStr"/>
       <c r="C1284" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1284" t="inlineStr">
@@ -52101,7 +52101,7 @@
       <c r="B1299" t="inlineStr"/>
       <c r="C1299" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1299" t="inlineStr">
@@ -57455,7 +57455,7 @@
       <c r="B1608" t="inlineStr"/>
       <c r="C1608" t="inlineStr">
         <is>
-          <t>ORA Coal</t>
+          <t>ORA Shunter</t>
         </is>
       </c>
       <c r="D1608" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -922,7 +922,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1958,7 +1958,7 @@
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>North East Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2084,7 +2084,7 @@
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2624,7 +2624,7 @@
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -2858,7 +2858,7 @@
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>V/Line Light Engine</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4786,7 +4786,7 @@
       <c r="B247" t="inlineStr"/>
       <c r="C247" t="inlineStr">
         <is>
-          <t>PN Empty Containerised Logs</t>
+          <t>PN Loaded Containerised Logs</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -7682,7 +7682,7 @@
       <c r="B411" t="inlineStr"/>
       <c r="C411" t="inlineStr">
         <is>
-          <t>ARTC Maintenance Train</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -10836,7 +10836,7 @@
       <c r="B598" t="inlineStr"/>
       <c r="C598" t="inlineStr">
         <is>
-          <t>SCT Intermodal</t>
+          <t>SCT Containerised Freight</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
@@ -11140,7 +11140,7 @@
       <c r="B615" t="inlineStr"/>
       <c r="C615" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer</t>
+          <t>NSW Trainlink Empty Car Transfer (ex NP24)</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -18732,7 +18732,7 @@
       <c r="B1053" t="inlineStr"/>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>SCT Aurizon Loading Transfer</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D1053" t="inlineStr">
@@ -30241,7 +30241,7 @@
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>PN Empty Containerised Logs</t>
+          <t>PN Loaded Containerised Logs</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -37817,7 +37817,7 @@
       <c r="B495" t="inlineStr"/>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>V/Line Light Engine</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
@@ -42475,7 +42475,7 @@
       <c r="B756" t="inlineStr"/>
       <c r="C756" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
@@ -42849,7 +42849,7 @@
       <c r="B777" t="inlineStr"/>
       <c r="C777" t="inlineStr">
         <is>
-          <t>ARTC Maintenance Train</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
@@ -43503,7 +43503,7 @@
       <c r="B814" t="inlineStr"/>
       <c r="C814" t="inlineStr">
         <is>
-          <t>SCT Intermodal</t>
+          <t>SCT Containerised Freight</t>
         </is>
       </c>
       <c r="D814" t="inlineStr">
@@ -43521,7 +43521,7 @@
       <c r="B815" t="inlineStr"/>
       <c r="C815" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer</t>
+          <t>NSW Trainlink Empty Car Transfer (ex NP24)</t>
         </is>
       </c>
       <c r="D815" t="inlineStr">
@@ -43769,7 +43769,7 @@
       <c r="B829" t="inlineStr"/>
       <c r="C829" t="inlineStr">
         <is>
-          <t>SCT Aurizon Loading Transfer</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D829" t="inlineStr">
@@ -50885,7 +50885,7 @@
       <c r="B1228" t="inlineStr"/>
       <c r="C1228" t="inlineStr">
         <is>
-          <t>North East Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D1228" t="inlineStr">
@@ -51291,7 +51291,7 @@
       <c r="B1251" t="inlineStr"/>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northeast BG Line Service</t>
         </is>
       </c>
       <c r="D1251" t="inlineStr">
@@ -52925,7 +52925,7 @@
       <c r="B1342" t="inlineStr"/>
       <c r="C1342" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1342" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1318,7 +1318,7 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>North Eastern Line BG Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1818,7 +1818,7 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -1922,7 +1922,7 @@
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2930,7 +2930,7 @@
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>V/Line SG Special Movement</t>
+          <t>NorthEast Special Movement</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -5588,7 +5588,7 @@
       <c r="B292" t="inlineStr"/>
       <c r="C292" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Cement - RailTrain Crewed</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -6304,7 +6304,7 @@
       <c r="B332" t="inlineStr"/>
       <c r="C332" t="inlineStr">
         <is>
-          <t>PN Garbage Train</t>
+          <t>PN Loaded Containerised Logs</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -6574,7 +6574,7 @@
       <c r="B347" t="inlineStr"/>
       <c r="C347" t="inlineStr">
         <is>
-          <t>PN Grain</t>
+          <t>PN Grain Shuttle</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -8670,7 +8670,7 @@
       <c r="B471" t="inlineStr"/>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Copper</t>
+          <t>Aurizon Empty Copper</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -8954,7 +8954,7 @@
       <c r="B487" t="inlineStr"/>
       <c r="C487" t="inlineStr">
         <is>
-          <t>MRL Loaded Iron Ore</t>
+          <t>MRL Empty Iron Ore</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
@@ -9800,7 +9800,7 @@
       <c r="B540" t="inlineStr"/>
       <c r="C540" t="inlineStr">
         <is>
-          <t>SSR Limestone</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
@@ -10120,7 +10120,7 @@
       <c r="B558" t="inlineStr"/>
       <c r="C558" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
@@ -10732,7 +10732,7 @@
       <c r="B592" t="inlineStr"/>
       <c r="C592" t="inlineStr">
         <is>
-          <t>SCT Sadliers Transfer</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
@@ -11586,7 +11586,7 @@
       <c r="B640" t="inlineStr"/>
       <c r="C640" t="inlineStr">
         <is>
-          <t>QUBE Light Engine Movement</t>
+          <t>QUBE Empty Balco</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
@@ -11784,7 +11784,7 @@
       <c r="B651" t="inlineStr"/>
       <c r="C651" t="inlineStr">
         <is>
-          <t>Aurizon Loading Shuttle (Ex 7PS1)</t>
+          <t>Aurizon Intermodal</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
@@ -12552,7 +12552,7 @@
       <c r="B695" t="inlineStr"/>
       <c r="C695" t="inlineStr">
         <is>
-          <t>Aurizon Empty Ore</t>
+          <t>Aurizon Loaded Ore</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
@@ -12648,7 +12648,7 @@
       <c r="B701" t="inlineStr"/>
       <c r="C701" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
@@ -15836,7 +15836,7 @@
       <c r="B883" t="inlineStr"/>
       <c r="C883" t="inlineStr">
         <is>
-          <t>PN Infrabuild Steel</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D883" t="inlineStr">
@@ -16782,7 +16782,7 @@
       <c r="B940" t="inlineStr"/>
       <c r="C940" t="inlineStr">
         <is>
-          <t>SRS Light Engine Movement</t>
+          <t>SRS/SCT Sadleirs Trip Train</t>
         </is>
       </c>
       <c r="D940" t="inlineStr">
@@ -18876,7 +18876,7 @@
       <c r="B1061" t="inlineStr"/>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>SSR Freight Shuttle</t>
+          <t>SSR Manildra Grain Shuttle</t>
         </is>
       </c>
       <c r="D1061" t="inlineStr">
@@ -18894,7 +18894,7 @@
       <c r="B1062" t="inlineStr"/>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>Watco Light Engine</t>
+          <t>Watco Trip Train</t>
         </is>
       </c>
       <c r="D1062" t="inlineStr">
@@ -19054,7 +19054,7 @@
       <c r="B1072" t="inlineStr"/>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>Additional Bathurst Service</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1072" t="inlineStr">
@@ -19162,7 +19162,7 @@
       <c r="B1078" t="inlineStr"/>
       <c r="C1078" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1078" t="inlineStr">
@@ -20830,7 +20830,7 @@
       <c r="B1174" t="inlineStr"/>
       <c r="C1174" t="inlineStr">
         <is>
-          <t>Echuca/Moama - Melbourne Via Bendigo or Heathcote</t>
+          <t>Bendigo - Melbourne Via Sunbury</t>
         </is>
       </c>
       <c r="D1174" t="inlineStr">
@@ -28454,7 +28454,7 @@
       <c r="B1598" t="inlineStr"/>
       <c r="C1598" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1598" t="inlineStr">
@@ -28562,7 +28562,7 @@
       <c r="B1604" t="inlineStr"/>
       <c r="C1604" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (Forms ST21)</t>
         </is>
       </c>
       <c r="D1604" t="inlineStr">
@@ -32329,7 +32329,7 @@
       <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Cement - RailTrain Crewed</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -33631,7 +33631,7 @@
       <c r="B258" t="inlineStr"/>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Watco Light Engine</t>
+          <t>Watco Trip Train</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -34437,7 +34437,7 @@
       <c r="B303" t="inlineStr"/>
       <c r="C303" t="inlineStr">
         <is>
-          <t>QUBE Light Engine Movement</t>
+          <t>QUBE Empty Balco</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -36291,7 +36291,7 @@
       <c r="B408" t="inlineStr"/>
       <c r="C408" t="inlineStr">
         <is>
-          <t>PN Grain</t>
+          <t>PN Grain Shuttle</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -41039,7 +41039,7 @@
       <c r="B676" t="inlineStr"/>
       <c r="C676" t="inlineStr">
         <is>
-          <t>MRL Loaded Iron Ore</t>
+          <t>MRL Empty Iron Ore</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
@@ -42867,7 +42867,7 @@
       <c r="B778" t="inlineStr"/>
       <c r="C778" t="inlineStr">
         <is>
-          <t>SCT Sadliers Transfer</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D778" t="inlineStr">
@@ -43927,7 +43927,7 @@
       <c r="B838" t="inlineStr"/>
       <c r="C838" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D838" t="inlineStr">
@@ -44809,7 +44809,7 @@
       <c r="B887" t="inlineStr"/>
       <c r="C887" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D887" t="inlineStr">
@@ -44877,7 +44877,7 @@
       <c r="B891" t="inlineStr"/>
       <c r="C891" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D891" t="inlineStr">
@@ -45579,7 +45579,7 @@
       <c r="B930" t="inlineStr"/>
       <c r="C930" t="inlineStr">
         <is>
-          <t>PN Garbage Train</t>
+          <t>PN Loaded Containerised Logs</t>
         </is>
       </c>
       <c r="D930" t="inlineStr">
@@ -45881,7 +45881,7 @@
       <c r="B947" t="inlineStr"/>
       <c r="C947" t="inlineStr">
         <is>
-          <t>Aurizon Loading Shuttle (Ex 7PS1)</t>
+          <t>Aurizon Intermodal</t>
         </is>
       </c>
       <c r="D947" t="inlineStr">
@@ -46391,7 +46391,7 @@
       <c r="B976" t="inlineStr"/>
       <c r="C976" t="inlineStr">
         <is>
-          <t>V/Line SG Special Movement</t>
+          <t>NorthEast Special Movement</t>
         </is>
       </c>
       <c r="D976" t="inlineStr">
@@ -46545,7 +46545,7 @@
       <c r="B985" t="inlineStr"/>
       <c r="C985" t="inlineStr">
         <is>
-          <t>Aurizon Empty Ore</t>
+          <t>Aurizon Loaded Ore</t>
         </is>
       </c>
       <c r="D985" t="inlineStr">
@@ -46865,7 +46865,7 @@
       <c r="B1003" t="inlineStr"/>
       <c r="C1003" t="inlineStr">
         <is>
-          <t>North Eastern Line BG Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D1003" t="inlineStr">
@@ -48496,7 +48496,7 @@
       <c r="B1094" t="inlineStr"/>
       <c r="C1094" t="inlineStr">
         <is>
-          <t>SSR Freight Shuttle</t>
+          <t>SSR Manildra Grain Shuttle</t>
         </is>
       </c>
       <c r="D1094" t="inlineStr">
@@ -49231,7 +49231,7 @@
       <c r="B1135" t="inlineStr"/>
       <c r="C1135" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1135" t="inlineStr">
@@ -49529,7 +49529,7 @@
       <c r="B1152" t="inlineStr"/>
       <c r="C1152" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1152" t="inlineStr">
@@ -52173,7 +52173,7 @@
       <c r="B1300" t="inlineStr"/>
       <c r="C1300" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1300" t="inlineStr">
@@ -52745,7 +52745,7 @@
       <c r="B1332" t="inlineStr"/>
       <c r="C1332" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (Forms ST21)</t>
         </is>
       </c>
       <c r="D1332" t="inlineStr">
@@ -54101,7 +54101,7 @@
       <c r="B1410" t="inlineStr"/>
       <c r="C1410" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Copper</t>
+          <t>Aurizon Empty Copper</t>
         </is>
       </c>
       <c r="D1410" t="inlineStr">
@@ -54459,7 +54459,7 @@
       <c r="B1433" t="inlineStr"/>
       <c r="C1433" t="inlineStr">
         <is>
-          <t>SSR Limestone</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1433" t="inlineStr">
@@ -55675,7 +55675,7 @@
       <c r="B1501" t="inlineStr"/>
       <c r="C1501" t="inlineStr">
         <is>
-          <t>PN Infrabuild Steel</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D1501" t="inlineStr">
@@ -55869,7 +55869,7 @@
       <c r="B1514" t="inlineStr"/>
       <c r="C1514" t="inlineStr">
         <is>
-          <t>SRS Light Engine Movement</t>
+          <t>SRS/SCT Sadleirs Trip Train</t>
         </is>
       </c>
       <c r="D1514" t="inlineStr">
@@ -56393,7 +56393,7 @@
       <c r="B1546" t="inlineStr"/>
       <c r="C1546" t="inlineStr">
         <is>
-          <t>Additional Bathurst Service</t>
+          <t>Bathurst Bullet - Transfer</t>
         </is>
       </c>
       <c r="D1546" t="inlineStr">
@@ -56663,7 +56663,7 @@
       <c r="B1561" t="inlineStr"/>
       <c r="C1561" t="inlineStr">
         <is>
-          <t>Echuca/Moama - Melbourne Via Bendigo or Heathcote</t>
+          <t>Bendigo - Melbourne Via Sunbury</t>
         </is>
       </c>
       <c r="D1561" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1818,7 +1818,7 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2336,7 +2336,7 @@
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2498,7 +2498,7 @@
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -9976,7 +9976,7 @@
       <c r="B550" t="inlineStr"/>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Aurizon Empty Grain</t>
+          <t>Aurizon Loaded Grain</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
@@ -12588,7 +12588,7 @@
       <c r="B697" t="inlineStr"/>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Aurizon Empty Ore</t>
+          <t>Aurizon Loaded Copper</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
@@ -12774,7 +12774,7 @@
       <c r="B708" t="inlineStr"/>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
@@ -15006,7 +15006,7 @@
       <c r="B836" t="inlineStr"/>
       <c r="C836" t="inlineStr">
         <is>
-          <t>PN Containerised Freight</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D836" t="inlineStr">
@@ -15872,7 +15872,7 @@
       <c r="B885" t="inlineStr"/>
       <c r="C885" t="inlineStr">
         <is>
-          <t>PN Fuel Train</t>
+          <t>PN Loaded Fuel Service</t>
         </is>
       </c>
       <c r="D885" t="inlineStr">
@@ -19126,7 +19126,7 @@
       <c r="B1076" t="inlineStr"/>
       <c r="C1076" t="inlineStr">
         <is>
-          <t>Sydney Trains Empty Car Transfer</t>
+          <t>Southern Highlands Service</t>
         </is>
       </c>
       <c r="D1076" t="inlineStr">
@@ -28314,7 +28314,7 @@
       <c r="B1590" t="inlineStr"/>
       <c r="C1590" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1590" t="inlineStr">
@@ -39555,7 +39555,7 @@
       <c r="B592" t="inlineStr"/>
       <c r="C592" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
@@ -41309,7 +41309,7 @@
       <c r="B691" t="inlineStr"/>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Aurizon Empty Ore</t>
+          <t>Aurizon Loaded Copper</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
@@ -41705,7 +41705,7 @@
       <c r="B713" t="inlineStr"/>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Aurizon Empty Grain</t>
+          <t>Aurizon Loaded Grain</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
@@ -43683,7 +43683,7 @@
       <c r="B824" t="inlineStr"/>
       <c r="C824" t="inlineStr">
         <is>
-          <t>PN Containerised Freight</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D824" t="inlineStr">
@@ -44809,7 +44809,7 @@
       <c r="B887" t="inlineStr"/>
       <c r="C887" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>North East BG Line Service</t>
         </is>
       </c>
       <c r="D887" t="inlineStr">
@@ -50435,7 +50435,7 @@
       <c r="B1203" t="inlineStr"/>
       <c r="C1203" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1203" t="inlineStr">
@@ -50849,7 +50849,7 @@
       <c r="B1226" t="inlineStr"/>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1226" t="inlineStr">
@@ -51705,7 +51705,7 @@
       <c r="B1274" t="inlineStr"/>
       <c r="C1274" t="inlineStr">
         <is>
-          <t>Sydney Trains Empty Car Transfer</t>
+          <t>Southern Highlands Service</t>
         </is>
       </c>
       <c r="D1274" t="inlineStr">
@@ -55085,7 +55085,7 @@
       <c r="B1468" t="inlineStr"/>
       <c r="C1468" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1468" t="inlineStr">
@@ -57739,7 +57739,7 @@
       <c r="B1621" t="inlineStr"/>
       <c r="C1621" t="inlineStr">
         <is>
-          <t>PN Fuel Train</t>
+          <t>PN Loaded Fuel Service</t>
         </is>
       </c>
       <c r="D1621" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -508,7 +508,7 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>SouthWest Line Service</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1480,7 +1480,7 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2300,7 +2300,7 @@
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2624,7 +2624,7 @@
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>North East Line BG Service</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -2660,7 +2660,7 @@
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6520,7 +6520,7 @@
       <c r="B344" t="inlineStr"/>
       <c r="C344" t="inlineStr">
         <is>
-          <t>PN Grain</t>
+          <t>PN Shunter</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -10908,7 +10908,7 @@
       <c r="B602" t="inlineStr"/>
       <c r="C602" t="inlineStr">
         <is>
-          <t>SCT Shuttle</t>
+          <t>SCT Light Engine Movement</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
@@ -11514,7 +11514,7 @@
       <c r="B636" t="inlineStr"/>
       <c r="C636" t="inlineStr">
         <is>
-          <t>QUBE Loaded Aggregates</t>
+          <t>QUBE Empty Aggregates</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
@@ -11938,7 +11938,7 @@
       <c r="B660" t="inlineStr"/>
       <c r="C660" t="inlineStr">
         <is>
-          <t>SCT Wine Train / Steel Shunt</t>
+          <t>SCT Wagon Transfer</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
@@ -12648,7 +12648,7 @@
       <c r="B701" t="inlineStr"/>
       <c r="C701" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
@@ -12864,7 +12864,7 @@
       <c r="B713" t="inlineStr"/>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
@@ -13438,7 +13438,11 @@
         </is>
       </c>
       <c r="B747" t="inlineStr"/>
-      <c r="C747" t="inlineStr"/>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>Aurizon Light Engine / Wagon Transfer</t>
+        </is>
+      </c>
       <c r="D747" t="inlineStr">
         <is>
           <t>2026-04-08 01:13:29</t>
@@ -18840,7 +18844,7 @@
       <c r="B1059" t="inlineStr"/>
       <c r="C1059" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1059" t="inlineStr">
@@ -19162,7 +19166,7 @@
       <c r="B1078" t="inlineStr"/>
       <c r="C1078" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1078" t="inlineStr">
@@ -28404,7 +28408,7 @@
       <c r="B1595" t="inlineStr"/>
       <c r="C1595" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (ex-ST24)</t>
         </is>
       </c>
       <c r="D1595" t="inlineStr">
@@ -35269,7 +35273,11 @@
         </is>
       </c>
       <c r="B350" t="inlineStr"/>
-      <c r="C350" t="inlineStr"/>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Aurizon Light Engine / Wagon Transfer</t>
+        </is>
+      </c>
       <c r="D350" t="inlineStr">
         <is>
           <t>2026-04-08 01:13:29</t>
@@ -35629,7 +35637,7 @@
       <c r="B371" t="inlineStr"/>
       <c r="C371" t="inlineStr">
         <is>
-          <t>PN Grain</t>
+          <t>PN Shunter</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -35665,7 +35673,7 @@
       <c r="B373" t="inlineStr"/>
       <c r="C373" t="inlineStr">
         <is>
-          <t>QUBE Loaded Aggregates</t>
+          <t>QUBE Empty Aggregates</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -38051,7 +38059,7 @@
       <c r="B508" t="inlineStr"/>
       <c r="C508" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
@@ -49529,7 +49537,7 @@
       <c r="B1152" t="inlineStr"/>
       <c r="C1152" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1152" t="inlineStr">
@@ -50813,7 +50821,7 @@
       <c r="B1224" t="inlineStr"/>
       <c r="C1224" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>SouthWest Line Service</t>
         </is>
       </c>
       <c r="D1224" t="inlineStr">
@@ -51291,7 +51299,7 @@
       <c r="B1251" t="inlineStr"/>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>North East Line BG Service</t>
         </is>
       </c>
       <c r="D1251" t="inlineStr">
@@ -51309,7 +51317,7 @@
       <c r="B1252" t="inlineStr"/>
       <c r="C1252" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1252" t="inlineStr">
@@ -52173,7 +52181,7 @@
       <c r="B1300" t="inlineStr"/>
       <c r="C1300" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1300" t="inlineStr">
@@ -52835,7 +52843,7 @@
       <c r="B1337" t="inlineStr"/>
       <c r="C1337" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1337" t="inlineStr">
@@ -54765,7 +54773,7 @@
       <c r="B1450" t="inlineStr"/>
       <c r="C1450" t="inlineStr">
         <is>
-          <t>SCT Shuttle</t>
+          <t>SCT Light Engine Movement</t>
         </is>
       </c>
       <c r="D1450" t="inlineStr">
@@ -54891,7 +54899,7 @@
       <c r="B1457" t="inlineStr"/>
       <c r="C1457" t="inlineStr">
         <is>
-          <t>SCT Wine Train / Steel Shunt</t>
+          <t>SCT Wagon Transfer</t>
         </is>
       </c>
       <c r="D1457" t="inlineStr">
@@ -55103,7 +55111,7 @@
       <c r="B1469" t="inlineStr"/>
       <c r="C1469" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1469" t="inlineStr">
@@ -56375,7 +56383,7 @@
       <c r="B1545" t="inlineStr"/>
       <c r="C1545" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1545" t="inlineStr">
@@ -57383,7 +57391,7 @@
       <c r="B1601" t="inlineStr"/>
       <c r="C1601" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (ex-ST24)</t>
         </is>
       </c>
       <c r="D1601" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1498,7 +1498,7 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Gippsland Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -12774,7 +12774,7 @@
       <c r="B708" t="inlineStr"/>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
@@ -13318,7 +13318,7 @@
       <c r="B740" t="inlineStr"/>
       <c r="C740" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Hunter Railcar Transfer</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
@@ -35777,7 +35777,7 @@
       <c r="B379" t="inlineStr"/>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Hunter Railcar Transfer</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -41173,7 +41173,7 @@
       <c r="B683" t="inlineStr"/>
       <c r="C683" t="inlineStr">
         <is>
-          <t>Gippsland Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
@@ -55093,7 +55093,7 @@
       <c r="B1468" t="inlineStr"/>
       <c r="C1468" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1468" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -472,7 +472,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1602,7 +1602,7 @@
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1710,7 +1710,7 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1746,7 +1746,7 @@
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2714,7 +2714,7 @@
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6646,7 +6646,7 @@
       <c r="B351" t="inlineStr"/>
       <c r="C351" t="inlineStr">
         <is>
-          <t>PN Grain</t>
+          <t>PN Grain Shuttle</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -8616,7 +8616,7 @@
       <c r="B468" t="inlineStr"/>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Aurizon Intermodal Shuttle</t>
+          <t>Aurizon Intermodal</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -10210,7 +10210,7 @@
       <c r="B563" t="inlineStr"/>
       <c r="C563" t="inlineStr">
         <is>
-          <t>QUBE Empty Containerised Ore</t>
+          <t>QUBE WM Shunter</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
@@ -11938,7 +11938,7 @@
       <c r="B660" t="inlineStr"/>
       <c r="C660" t="inlineStr">
         <is>
-          <t>SCT Wagon Transfer</t>
+          <t>SCT Steel Shunt / Wine Train</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
@@ -12702,7 +12702,7 @@
       <c r="B704" t="inlineStr"/>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
@@ -13748,7 +13748,7 @@
       <c r="B765" t="inlineStr"/>
       <c r="C765" t="inlineStr">
         <is>
-          <t>SSR Empty Manildra Flour</t>
+          <t>SSR Loaded Manildra Flour</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
@@ -16786,7 +16786,7 @@
       <c r="B940" t="inlineStr"/>
       <c r="C940" t="inlineStr">
         <is>
-          <t>SRS/SCT Sadleirs Trip Train</t>
+          <t>SRS Light Engine</t>
         </is>
       </c>
       <c r="D940" t="inlineStr">
@@ -18958,7 +18958,7 @@
       <c r="B1066" t="inlineStr"/>
       <c r="C1066" t="inlineStr">
         <is>
-          <t>SSR Light Engine</t>
+          <t>SSR Cement Trip Train</t>
         </is>
       </c>
       <c r="D1066" t="inlineStr">
@@ -30005,7 +30005,7 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SSR Light Engine</t>
+          <t>SSR Cement Trip Train</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -30967,7 +30967,7 @@
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>PN Grain</t>
+          <t>PN Grain Shuttle</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -34423,7 +34423,7 @@
       <c r="B302" t="inlineStr"/>
       <c r="C302" t="inlineStr">
         <is>
-          <t>QUBE Empty Containerised Ore</t>
+          <t>QUBE WM Shunter</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -37771,7 +37771,7 @@
       <c r="B492" t="inlineStr"/>
       <c r="C492" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Empty Car Provisioning</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
@@ -43191,7 +43191,7 @@
       <c r="B796" t="inlineStr"/>
       <c r="C796" t="inlineStr">
         <is>
-          <t>Aurizon Intermodal Shuttle</t>
+          <t>Aurizon Intermodal</t>
         </is>
       </c>
       <c r="D796" t="inlineStr">
@@ -46873,7 +46873,7 @@
       <c r="B1003" t="inlineStr"/>
       <c r="C1003" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1003" t="inlineStr">
@@ -47535,7 +47535,7 @@
       <c r="B1040" t="inlineStr"/>
       <c r="C1040" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1040" t="inlineStr">
@@ -47607,7 +47607,7 @@
       <c r="B1044" t="inlineStr"/>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Northern Line Service</t>
         </is>
       </c>
       <c r="D1044" t="inlineStr">
@@ -48720,7 +48720,7 @@
       <c r="B1106" t="inlineStr"/>
       <c r="C1106" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1106" t="inlineStr">
@@ -53041,7 +53041,7 @@
       <c r="B1348" t="inlineStr"/>
       <c r="C1348" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1348" t="inlineStr">
@@ -54899,7 +54899,7 @@
       <c r="B1457" t="inlineStr"/>
       <c r="C1457" t="inlineStr">
         <is>
-          <t>SCT Wagon Transfer</t>
+          <t>SCT Steel Shunt / Wine Train</t>
         </is>
       </c>
       <c r="D1457" t="inlineStr">
@@ -55057,7 +55057,7 @@
       <c r="B1466" t="inlineStr"/>
       <c r="C1466" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1466" t="inlineStr">
@@ -55251,7 +55251,7 @@
       <c r="B1477" t="inlineStr"/>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>SSR Empty Manildra Flour</t>
+          <t>SSR Loaded Manildra Flour</t>
         </is>
       </c>
       <c r="D1477" t="inlineStr">
@@ -55877,7 +55877,7 @@
       <c r="B1514" t="inlineStr"/>
       <c r="C1514" t="inlineStr">
         <is>
-          <t>SRS/SCT Sadleirs Trip Train</t>
+          <t>SRS Light Engine</t>
         </is>
       </c>
       <c r="D1514" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -994,7 +994,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2822,7 +2822,7 @@
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>V/Line Empty Car Transfer</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6862,7 +6862,7 @@
       <c r="B363" t="inlineStr"/>
       <c r="C363" t="inlineStr">
         <is>
-          <t>PN Grain</t>
+          <t>PN Grain via Greta TSF</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -8954,7 +8954,7 @@
       <c r="B487" t="inlineStr"/>
       <c r="C487" t="inlineStr">
         <is>
-          <t>MRL Empty Iron Ore</t>
+          <t>MRL Loaded Iron Ore</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
@@ -10606,7 +10606,7 @@
       <c r="B585" t="inlineStr"/>
       <c r="C585" t="inlineStr">
         <is>
-          <t>QUBE Shunter</t>
+          <t>SSR Grain</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
@@ -12128,7 +12128,7 @@
       <c r="B671" t="inlineStr"/>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Aurizon Light Engine</t>
+          <t>Aurizon Wagon Transfer</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
@@ -15660,7 +15660,7 @@
       <c r="B873" t="inlineStr"/>
       <c r="C873" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>PN Light Engine for NY3</t>
         </is>
       </c>
       <c r="D873" t="inlineStr">
@@ -28512,7 +28512,7 @@
       <c r="B1601" t="inlineStr"/>
       <c r="C1601" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (ex NT32)</t>
         </is>
       </c>
       <c r="D1601" t="inlineStr">
@@ -31057,7 +31057,7 @@
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>QUBE Shunter</t>
+          <t>SSR Grain</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -31953,7 +31953,7 @@
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr">
         <is>
-          <t>PN Grain</t>
+          <t>PN Grain via Greta TSF</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -37519,7 +37519,7 @@
       <c r="B477" t="inlineStr"/>
       <c r="C477" t="inlineStr">
         <is>
-          <t>V/Line Empty Car Transfer</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -41083,7 +41083,7 @@
       <c r="B677" t="inlineStr"/>
       <c r="C677" t="inlineStr">
         <is>
-          <t>MRL Empty Iron Ore</t>
+          <t>MRL Loaded Iron Ore</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
@@ -49537,7 +49537,7 @@
       <c r="B1151" t="inlineStr"/>
       <c r="C1151" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>PN Light Engine for NY3</t>
         </is>
       </c>
       <c r="D1151" t="inlineStr">
@@ -52987,7 +52987,7 @@
       <c r="B1344" t="inlineStr"/>
       <c r="C1344" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1344" t="inlineStr">
@@ -54967,7 +54967,7 @@
       <c r="B1460" t="inlineStr"/>
       <c r="C1460" t="inlineStr">
         <is>
-          <t>Aurizon Light Engine</t>
+          <t>Aurizon Wagon Transfer</t>
         </is>
       </c>
       <c r="D1460" t="inlineStr">
@@ -57463,7 +57463,7 @@
       <c r="B1604" t="inlineStr"/>
       <c r="C1604" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (ex NT32)</t>
         </is>
       </c>
       <c r="D1604" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1602,7 +1602,7 @@
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Empty Transfer for Maintenance</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5642,7 +5642,7 @@
       <c r="B295" t="inlineStr"/>
       <c r="C295" t="inlineStr">
         <is>
-          <t>PN Cement - RailTrain Crewed</t>
+          <t>PN Cement</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -6250,7 +6250,7 @@
       <c r="B329" t="inlineStr"/>
       <c r="C329" t="inlineStr">
         <is>
-          <t>PN Trip Train, pre 1533</t>
+          <t>PN Garbage Train</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -6574,7 +6574,7 @@
       <c r="B347" t="inlineStr"/>
       <c r="C347" t="inlineStr">
         <is>
-          <t>PN Grain Shuttle</t>
+          <t>PN Local Shunter</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -6826,7 +6826,7 @@
       <c r="B361" t="inlineStr"/>
       <c r="C361" t="inlineStr">
         <is>
-          <t>PN Grain Shuttle</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -12304,7 +12304,7 @@
       <c r="B681" t="inlineStr"/>
       <c r="C681" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Ore</t>
+          <t>Aurizon Empty Ore</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
@@ -19602,7 +19602,7 @@
       <c r="B1104" t="inlineStr"/>
       <c r="C1104" t="inlineStr">
         <is>
-          <t>PN Loaded Aggregate</t>
+          <t>PN Minerals</t>
         </is>
       </c>
       <c r="D1104" t="inlineStr">
@@ -30625,7 +30625,7 @@
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>PN Grain Shuttle</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -36335,7 +36335,7 @@
       <c r="B409" t="inlineStr"/>
       <c r="C409" t="inlineStr">
         <is>
-          <t>PN Grain Shuttle</t>
+          <t>PN Local Shunter</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -39473,7 +39473,7 @@
       <c r="B586" t="inlineStr"/>
       <c r="C586" t="inlineStr">
         <is>
-          <t>PN Loaded Aggregate</t>
+          <t>PN Minerals</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
@@ -47643,7 +47643,7 @@
       <c r="B1045" t="inlineStr"/>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Empty Transfer for Maintenance</t>
         </is>
       </c>
       <c r="D1045" t="inlineStr">
@@ -50235,7 +50235,7 @@
       <c r="B1190" t="inlineStr"/>
       <c r="C1190" t="inlineStr">
         <is>
-          <t>PN Trip Train, pre 1533</t>
+          <t>PN Garbage Train</t>
         </is>
       </c>
       <c r="D1190" t="inlineStr">
@@ -52127,7 +52127,7 @@
       <c r="B1296" t="inlineStr"/>
       <c r="C1296" t="inlineStr">
         <is>
-          <t>PN Cement - RailTrain Crewed</t>
+          <t>PN Cement</t>
         </is>
       </c>
       <c r="D1296" t="inlineStr">
@@ -55003,7 +55003,7 @@
       <c r="B1462" t="inlineStr"/>
       <c r="C1462" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Ore</t>
+          <t>Aurizon Empty Ore</t>
         </is>
       </c>
       <c r="D1462" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -562,7 +562,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -724,7 +724,7 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -958,7 +958,7 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>V1227</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1480,7 +1480,7 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1602,7 +1602,7 @@
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Empty Transfer for Maintenance</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1710,7 +1710,7 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>North Eastern Line BG Service</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1818,7 +1818,7 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>North East Line BG Service</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -1958,7 +1958,7 @@
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2786,7 +2786,7 @@
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Empty Transfer for Maintenance</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3106,7 +3106,7 @@
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
-          <t>QUBE Junee Shunter</t>
+          <t>QUBE Container Train</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4528,7 +4528,7 @@
       <c r="B232" t="inlineStr"/>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Aurizon Light Engine Movement</t>
+          <t>Aurizon Intermodal</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -4786,7 +4786,7 @@
       <c r="B247" t="inlineStr"/>
       <c r="C247" t="inlineStr">
         <is>
-          <t>PN Loaded Containerised Logs</t>
+          <t>PN Trip Train, pre 1821</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -5268,7 +5268,7 @@
       <c r="B274" t="inlineStr"/>
       <c r="C274" t="inlineStr">
         <is>
-          <t>PN Grain</t>
+          <t>PN Containerised Freight</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -5304,7 +5304,7 @@
       <c r="B276" t="inlineStr"/>
       <c r="C276" t="inlineStr">
         <is>
-          <t>PN Grain Shuttle</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -5516,7 +5516,7 @@
       <c r="B288" t="inlineStr"/>
       <c r="C288" t="inlineStr">
         <is>
-          <t>PN Grain Shuttle</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -6376,7 +6376,7 @@
       <c r="B336" t="inlineStr"/>
       <c r="C336" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Containerised Cotton</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -7946,7 +7946,7 @@
       <c r="B427" t="inlineStr"/>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Qube Trip Train</t>
+          <t>QUBE Light Engine</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -8670,7 +8670,7 @@
       <c r="B471" t="inlineStr"/>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Aurizon Empty Copper</t>
+          <t>Aurizon Loaded Copper</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -8918,7 +8918,7 @@
       <c r="B485" t="inlineStr"/>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Aurizon Wagon Transfer</t>
+          <t>Aurizon Empty Grain</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -9416,7 +9416,7 @@
       <c r="B518" t="inlineStr"/>
       <c r="C518" t="inlineStr">
         <is>
-          <t>SSR Light Engine</t>
+          <t>SSR/Metro Maintenance Train</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
@@ -10048,7 +10048,7 @@
       <c r="B554" t="inlineStr"/>
       <c r="C554" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
@@ -10210,7 +10210,7 @@
       <c r="B563" t="inlineStr"/>
       <c r="C563" t="inlineStr">
         <is>
-          <t>QUBE WM Shunter</t>
+          <t>QUBE BlueScope Steel</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
@@ -10750,7 +10750,7 @@
       <c r="B593" t="inlineStr"/>
       <c r="C593" t="inlineStr">
         <is>
-          <t>SCT Steel Transfer</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
@@ -10818,7 +10818,7 @@
       <c r="B597" t="inlineStr"/>
       <c r="C597" t="inlineStr">
         <is>
-          <t>SCT Intermodal</t>
+          <t>SCT Aurizon Loading Transfer</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
@@ -11140,7 +11140,7 @@
       <c r="B615" t="inlineStr"/>
       <c r="C615" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (ex NP24)</t>
+          <t>NSW Trainlink Xplorer</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -11212,7 +11212,7 @@
       <c r="B619" t="inlineStr"/>
       <c r="C619" t="inlineStr">
         <is>
-          <t>NSW TrainLink Xplorer</t>
+          <t>NSW Trainlink Xplorer</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
@@ -11230,7 +11230,7 @@
       <c r="B620" t="inlineStr"/>
       <c r="C620" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer</t>
+          <t>NSW Trainlink Xplorer</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
@@ -12128,7 +12128,7 @@
       <c r="B671" t="inlineStr"/>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Aurizon Wagon Transfer</t>
+          <t>Aurizon Intermodal</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
@@ -12756,7 +12756,7 @@
       <c r="B707" t="inlineStr"/>
       <c r="C707" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
@@ -12810,7 +12810,7 @@
       <c r="B710" t="inlineStr"/>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Hunter Railcar Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
@@ -13246,7 +13246,7 @@
       <c r="B736" t="inlineStr"/>
       <c r="C736" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>South Coast Service</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
@@ -13622,7 +13622,7 @@
       <c r="B758" t="inlineStr"/>
       <c r="C758" t="inlineStr">
         <is>
-          <t>SSR Manildra Grain Banker</t>
+          <t>SSR Loaded Manildra Grain</t>
         </is>
       </c>
       <c r="D758" t="inlineStr">
@@ -13712,7 +13712,7 @@
       <c r="B763" t="inlineStr"/>
       <c r="C763" t="inlineStr">
         <is>
-          <t>SSR Loaded Manildra Flour</t>
+          <t>SSR Empty Manildra Grain</t>
         </is>
       </c>
       <c r="D763" t="inlineStr">
@@ -13820,7 +13820,7 @@
       <c r="B769" t="inlineStr"/>
       <c r="C769" t="inlineStr">
         <is>
-          <t>SSR Loaded Manildra Flour</t>
+          <t>Swift Trip Train</t>
         </is>
       </c>
       <c r="D769" t="inlineStr">
@@ -14402,7 +14402,7 @@
       <c r="B802" t="inlineStr"/>
       <c r="C802" t="inlineStr">
         <is>
-          <t>PN Shunter</t>
+          <t>JBR The Overland</t>
         </is>
       </c>
       <c r="D802" t="inlineStr">
@@ -14654,7 +14654,7 @@
       <c r="B816" t="inlineStr"/>
       <c r="C816" t="inlineStr">
         <is>
-          <t>PN Loaded Lead/Zinc</t>
+          <t>PN Empty Lead/Zinc</t>
         </is>
       </c>
       <c r="D816" t="inlineStr">
@@ -14726,7 +14726,7 @@
       <c r="B820" t="inlineStr"/>
       <c r="C820" t="inlineStr">
         <is>
-          <t>PN Intermodal Shuttle</t>
+          <t>PN Containerised Freight</t>
         </is>
       </c>
       <c r="D820" t="inlineStr">
@@ -14798,7 +14798,7 @@
       <c r="B824" t="inlineStr"/>
       <c r="C824" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D824" t="inlineStr">
@@ -15322,7 +15322,7 @@
       <c r="B854" t="inlineStr"/>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Maintenance Train</t>
+          <t>PN Steel Transfer</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
@@ -15660,7 +15660,7 @@
       <c r="B873" t="inlineStr"/>
       <c r="C873" t="inlineStr">
         <is>
-          <t>PN Light Engine for NY3</t>
+          <t>PN Infrabuild Steel</t>
         </is>
       </c>
       <c r="D873" t="inlineStr">
@@ -16886,7 +16886,7 @@
       <c r="B946" t="inlineStr"/>
       <c r="C946" t="inlineStr">
         <is>
-          <t>Aurizon Kalgoorlie Mixed Freight</t>
+          <t>Aurizon Cockburn Cement - Lime and Cement Train</t>
         </is>
       </c>
       <c r="D946" t="inlineStr">
@@ -17146,7 +17146,7 @@
       <c r="B962" t="inlineStr"/>
       <c r="C962" t="inlineStr">
         <is>
-          <t>QUBE Containerised Grain</t>
+          <t>Qube Grain Shuttle</t>
         </is>
       </c>
       <c r="D962" t="inlineStr">
@@ -17196,7 +17196,7 @@
       <c r="B965" t="inlineStr"/>
       <c r="C965" t="inlineStr">
         <is>
-          <t>QUBE Grain</t>
+          <t>QUBE Empty Grain</t>
         </is>
       </c>
       <c r="D965" t="inlineStr">
@@ -18358,7 +18358,7 @@
       <c r="B1032" t="inlineStr"/>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>North-East BG Service</t>
         </is>
       </c>
       <c r="D1032" t="inlineStr">
@@ -18844,7 +18844,7 @@
       <c r="B1059" t="inlineStr"/>
       <c r="C1059" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1059" t="inlineStr">
@@ -19094,7 +19094,7 @@
       <c r="B1074" t="inlineStr"/>
       <c r="C1074" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>South Coast Service</t>
         </is>
       </c>
       <c r="D1074" t="inlineStr">
@@ -19788,7 +19788,7 @@
       <c r="B1115" t="inlineStr"/>
       <c r="C1115" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Light Engine Movement</t>
         </is>
       </c>
       <c r="D1115" t="inlineStr">
@@ -28426,7 +28426,7 @@
       <c r="B1596" t="inlineStr"/>
       <c r="C1596" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (ex-ST24)</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1596" t="inlineStr">
@@ -28476,7 +28476,7 @@
       <c r="B1599" t="inlineStr"/>
       <c r="C1599" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (Forms NT31)</t>
         </is>
       </c>
       <c r="D1599" t="inlineStr">
@@ -28494,7 +28494,7 @@
       <c r="B1600" t="inlineStr"/>
       <c r="C1600" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (Forms NT31)</t>
+          <t>NSW TrainLink XPT</t>
         </is>
       </c>
       <c r="D1600" t="inlineStr">
@@ -28512,7 +28512,7 @@
       <c r="B1601" t="inlineStr"/>
       <c r="C1601" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (ex NT32)</t>
+          <t>NSW TrainLink XPT</t>
         </is>
       </c>
       <c r="D1601" t="inlineStr">
@@ -28584,7 +28584,7 @@
       <c r="B1605" t="inlineStr"/>
       <c r="C1605" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (Forms ST21)</t>
+          <t>NSW TrainLink XPT</t>
         </is>
       </c>
       <c r="D1605" t="inlineStr">
@@ -28728,7 +28728,7 @@
       <c r="B1613" t="inlineStr"/>
       <c r="C1613" t="inlineStr">
         <is>
-          <t>ORA Shunter</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D1613" t="inlineStr">
@@ -30281,7 +30281,7 @@
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PN Loaded Containerised Logs</t>
+          <t>PN Trip Train, pre 1821</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -31537,7 +31537,7 @@
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>SSR Light Engine</t>
+          <t>SSR/Metro Maintenance Train</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -32129,7 +32129,7 @@
       <c r="B170" t="inlineStr"/>
       <c r="C170" t="inlineStr">
         <is>
-          <t>PN Grain Shuttle</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -32875,7 +32875,7 @@
       <c r="B213" t="inlineStr"/>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Empty Transfer for Maintenance</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -32983,7 +32983,7 @@
       <c r="B219" t="inlineStr"/>
       <c r="C219" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Light Engine Movement</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -33761,7 +33761,7 @@
       <c r="B264" t="inlineStr"/>
       <c r="C264" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Containerised Cotton</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -34459,7 +34459,7 @@
       <c r="B303" t="inlineStr"/>
       <c r="C303" t="inlineStr">
         <is>
-          <t>QUBE WM Shunter</t>
+          <t>QUBE BlueScope Steel</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -38095,7 +38095,7 @@
       <c r="B509" t="inlineStr"/>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
@@ -38725,7 +38725,7 @@
       <c r="B544" t="inlineStr"/>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>North-East BG Service</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
@@ -39455,7 +39455,7 @@
       <c r="B585" t="inlineStr"/>
       <c r="C585" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
@@ -39851,7 +39851,7 @@
       <c r="B607" t="inlineStr"/>
       <c r="C607" t="inlineStr">
         <is>
-          <t>PN Grain Shuttle</t>
+          <t>PN Light Engine</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
@@ -40153,7 +40153,7 @@
       <c r="B624" t="inlineStr"/>
       <c r="C624" t="inlineStr">
         <is>
-          <t>PN Intermodal Shuttle</t>
+          <t>PN Containerised Freight</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
@@ -40469,7 +40469,7 @@
       <c r="B642" t="inlineStr"/>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>V1227</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
@@ -41065,7 +41065,7 @@
       <c r="B676" t="inlineStr"/>
       <c r="C676" t="inlineStr">
         <is>
-          <t>SSR Manildra Grain Banker</t>
+          <t>SSR Loaded Manildra Grain</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
@@ -42875,7 +42875,7 @@
       <c r="B777" t="inlineStr"/>
       <c r="C777" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
@@ -43565,7 +43565,7 @@
       <c r="B816" t="inlineStr"/>
       <c r="C816" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (ex NP24)</t>
+          <t>NSW Trainlink Xplorer</t>
         </is>
       </c>
       <c r="D816" t="inlineStr">
@@ -44853,7 +44853,7 @@
       <c r="B888" t="inlineStr"/>
       <c r="C888" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>North East Line BG Service</t>
         </is>
       </c>
       <c r="D888" t="inlineStr">
@@ -45533,7 +45533,7 @@
       <c r="B926" t="inlineStr"/>
       <c r="C926" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D926" t="inlineStr">
@@ -45569,7 +45569,7 @@
       <c r="B928" t="inlineStr"/>
       <c r="C928" t="inlineStr">
         <is>
-          <t>Qube Trip Train</t>
+          <t>QUBE Light Engine</t>
         </is>
       </c>
       <c r="D928" t="inlineStr">
@@ -46891,7 +46891,7 @@
       <c r="B1003" t="inlineStr"/>
       <c r="C1003" t="inlineStr">
         <is>
-          <t>QUBE Junee Shunter</t>
+          <t>QUBE Container Train</t>
         </is>
       </c>
       <c r="D1003" t="inlineStr">
@@ -47359,7 +47359,7 @@
       <c r="B1029" t="inlineStr"/>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>QUBE Containerised Grain</t>
+          <t>Qube Grain Shuttle</t>
         </is>
       </c>
       <c r="D1029" t="inlineStr">
@@ -47643,7 +47643,7 @@
       <c r="B1045" t="inlineStr"/>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>Empty Transfer for Maintenance</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1045" t="inlineStr">
@@ -48035,7 +48035,7 @@
       <c r="B1067" t="inlineStr"/>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>PN Grain</t>
+          <t>PN Containerised Freight</t>
         </is>
       </c>
       <c r="D1067" t="inlineStr">
@@ -48756,7 +48756,7 @@
       <c r="B1107" t="inlineStr"/>
       <c r="C1107" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>North Eastern Line BG Service</t>
         </is>
       </c>
       <c r="D1107" t="inlineStr">
@@ -48792,7 +48792,7 @@
       <c r="B1109" t="inlineStr"/>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer</t>
+          <t>NSW Trainlink Xplorer</t>
         </is>
       </c>
       <c r="D1109" t="inlineStr">
@@ -49131,7 +49131,7 @@
       <c r="B1128" t="inlineStr"/>
       <c r="C1128" t="inlineStr">
         <is>
-          <t>PN Shunter</t>
+          <t>JBR The Overland</t>
         </is>
       </c>
       <c r="D1128" t="inlineStr">
@@ -49275,7 +49275,7 @@
       <c r="B1136" t="inlineStr"/>
       <c r="C1136" t="inlineStr">
         <is>
-          <t>NSW Trainlink XPT</t>
+          <t>NSW Trainlink Empty Car Transfer (Forms NT31)</t>
         </is>
       </c>
       <c r="D1136" t="inlineStr">
@@ -49483,7 +49483,7 @@
       <c r="B1148" t="inlineStr"/>
       <c r="C1148" t="inlineStr">
         <is>
-          <t>SCT Intermodal</t>
+          <t>SCT Aurizon Loading Transfer</t>
         </is>
       </c>
       <c r="D1148" t="inlineStr">
@@ -49537,7 +49537,7 @@
       <c r="B1151" t="inlineStr"/>
       <c r="C1151" t="inlineStr">
         <is>
-          <t>PN Light Engine for NY3</t>
+          <t>PN Infrabuild Steel</t>
         </is>
       </c>
       <c r="D1151" t="inlineStr">
@@ -49735,7 +49735,7 @@
       <c r="B1162" t="inlineStr"/>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>SSR Loaded Manildra Flour</t>
+          <t>SSR Empty Manildra Grain</t>
         </is>
       </c>
       <c r="D1162" t="inlineStr">
@@ -49933,7 +49933,7 @@
       <c r="B1173" t="inlineStr"/>
       <c r="C1173" t="inlineStr">
         <is>
-          <t>SCT Steel Transfer</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D1173" t="inlineStr">
@@ -50041,7 +50041,7 @@
       <c r="B1179" t="inlineStr"/>
       <c r="C1179" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1179" t="inlineStr">
@@ -50929,7 +50929,7 @@
       <c r="B1229" t="inlineStr"/>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>North East BG Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1229" t="inlineStr">
@@ -51569,7 +51569,7 @@
       <c r="B1265" t="inlineStr"/>
       <c r="C1265" t="inlineStr">
         <is>
-          <t>Aurizon Wagon Transfer</t>
+          <t>Aurizon Empty Grain</t>
         </is>
       </c>
       <c r="D1265" t="inlineStr">
@@ -51659,7 +51659,7 @@
       <c r="B1270" t="inlineStr"/>
       <c r="C1270" t="inlineStr">
         <is>
-          <t>Hunter Railcar Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1270" t="inlineStr">
@@ -51695,7 +51695,7 @@
       <c r="B1272" t="inlineStr"/>
       <c r="C1272" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>South Coast Service</t>
         </is>
       </c>
       <c r="D1272" t="inlineStr">
@@ -52789,7 +52789,7 @@
       <c r="B1333" t="inlineStr"/>
       <c r="C1333" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (Forms ST21)</t>
+          <t>NSW TrainLink XPT</t>
         </is>
       </c>
       <c r="D1333" t="inlineStr">
@@ -53515,7 +53515,7 @@
       <c r="B1374" t="inlineStr"/>
       <c r="C1374" t="inlineStr">
         <is>
-          <t>Aurizon Light Engine Movement</t>
+          <t>Aurizon Intermodal</t>
         </is>
       </c>
       <c r="D1374" t="inlineStr">
@@ -54145,7 +54145,7 @@
       <c r="B1411" t="inlineStr"/>
       <c r="C1411" t="inlineStr">
         <is>
-          <t>Aurizon Empty Copper</t>
+          <t>Aurizon Loaded Copper</t>
         </is>
       </c>
       <c r="D1411" t="inlineStr">
@@ -54863,7 +54863,7 @@
       <c r="B1454" t="inlineStr"/>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>NSW TrainLink Xplorer</t>
+          <t>NSW Trainlink Xplorer</t>
         </is>
       </c>
       <c r="D1454" t="inlineStr">
@@ -54967,7 +54967,7 @@
       <c r="B1460" t="inlineStr"/>
       <c r="C1460" t="inlineStr">
         <is>
-          <t>Aurizon Wagon Transfer</t>
+          <t>Aurizon Intermodal</t>
         </is>
       </c>
       <c r="D1460" t="inlineStr">
@@ -55111,7 +55111,7 @@
       <c r="B1468" t="inlineStr"/>
       <c r="C1468" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1468" t="inlineStr">
@@ -55341,7 +55341,7 @@
       <c r="B1481" t="inlineStr"/>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>SSR Loaded Manildra Flour</t>
+          <t>Swift Trip Train</t>
         </is>
       </c>
       <c r="D1481" t="inlineStr">
@@ -55485,7 +55485,7 @@
       <c r="B1489" t="inlineStr"/>
       <c r="C1489" t="inlineStr">
         <is>
-          <t>PN Loaded Lead/Zinc</t>
+          <t>PN Empty Lead/Zinc</t>
         </is>
       </c>
       <c r="D1489" t="inlineStr">
@@ -55611,7 +55611,7 @@
       <c r="B1496" t="inlineStr"/>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>Maintenance Train</t>
+          <t>PN Steel Transfer</t>
         </is>
       </c>
       <c r="D1496" t="inlineStr">
@@ -55995,7 +55995,7 @@
       <c r="B1520" t="inlineStr"/>
       <c r="C1520" t="inlineStr">
         <is>
-          <t>Aurizon Kalgoorlie Mixed Freight</t>
+          <t>Aurizon Cockburn Cement - Lime and Cement Train</t>
         </is>
       </c>
       <c r="D1520" t="inlineStr">
@@ -56155,7 +56155,7 @@
       <c r="B1530" t="inlineStr"/>
       <c r="C1530" t="inlineStr">
         <is>
-          <t>QUBE Grain</t>
+          <t>QUBE Empty Grain</t>
         </is>
       </c>
       <c r="D1530" t="inlineStr">
@@ -56419,7 +56419,7 @@
       <c r="B1546" t="inlineStr"/>
       <c r="C1546" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1546" t="inlineStr">
@@ -56473,7 +56473,7 @@
       <c r="B1549" t="inlineStr"/>
       <c r="C1549" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>South Coast Service</t>
         </is>
       </c>
       <c r="D1549" t="inlineStr">
@@ -57427,7 +57427,7 @@
       <c r="B1602" t="inlineStr"/>
       <c r="C1602" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (ex-ST24)</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1602" t="inlineStr">
@@ -57445,7 +57445,7 @@
       <c r="B1603" t="inlineStr"/>
       <c r="C1603" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (Forms NT31)</t>
+          <t>NSW TrainLink XPT</t>
         </is>
       </c>
       <c r="D1603" t="inlineStr">
@@ -57463,7 +57463,7 @@
       <c r="B1604" t="inlineStr"/>
       <c r="C1604" t="inlineStr">
         <is>
-          <t>NSW Trainlink Empty Car Transfer (ex NT32)</t>
+          <t>NSW TrainLink XPT</t>
         </is>
       </c>
       <c r="D1604" t="inlineStr">
@@ -57553,7 +57553,7 @@
       <c r="B1609" t="inlineStr"/>
       <c r="C1609" t="inlineStr">
         <is>
-          <t>ORA Shunter</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D1609" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -562,7 +562,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -742,7 +742,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1602,7 +1602,7 @@
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northeast Line BG Service</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1638,7 +1638,7 @@
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2372,7 +2372,7 @@
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -2822,7 +2822,7 @@
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -2840,7 +2840,7 @@
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4822,7 +4822,7 @@
       <c r="B249" t="inlineStr"/>
       <c r="C249" t="inlineStr">
         <is>
-          <t>PN Trip Train</t>
+          <t>PN Trip Train, ex 8124</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -9528,7 +9528,7 @@
       <c r="B524" t="inlineStr"/>
       <c r="C524" t="inlineStr">
         <is>
-          <t>PN Grain/Wagon Transfer</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
@@ -10196,7 +10196,7 @@
       <c r="B562" t="inlineStr"/>
       <c r="C562" t="inlineStr">
         <is>
-          <t>QUBE Container Train</t>
+          <t>QUBE Light Engine</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
@@ -12764,7 +12764,7 @@
       <c r="B707" t="inlineStr"/>
       <c r="C707" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
@@ -16480,7 +16480,7 @@
       <c r="B919" t="inlineStr"/>
       <c r="C919" t="inlineStr">
         <is>
-          <t>SSR Light Engine</t>
+          <t>Maintenance Train</t>
         </is>
       </c>
       <c r="D919" t="inlineStr">
@@ -17258,7 +17258,7 @@
       <c r="B968" t="inlineStr"/>
       <c r="C968" t="inlineStr">
         <is>
-          <t>QUBE Containerised Freight</t>
+          <t>QUBE Containerised Cotton</t>
         </is>
       </c>
       <c r="D968" t="inlineStr">
@@ -18924,7 +18924,7 @@
       <c r="B1063" t="inlineStr"/>
       <c r="C1063" t="inlineStr">
         <is>
-          <t>Watco Light Engine Movement</t>
+          <t>Watco Trip Train</t>
         </is>
       </c>
       <c r="D1063" t="inlineStr">
@@ -20054,7 +20054,7 @@
       <c r="B1130" t="inlineStr"/>
       <c r="C1130" t="inlineStr">
         <is>
-          <t>QUBE Containerised Freight</t>
+          <t>QUBE Maryvale Paper Train</t>
         </is>
       </c>
       <c r="D1130" t="inlineStr">
@@ -28556,7 +28556,7 @@
       <c r="B1603" t="inlineStr"/>
       <c r="C1603" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1603" t="inlineStr">
@@ -32855,7 +32855,7 @@
       <c r="B210" t="inlineStr"/>
       <c r="C210" t="inlineStr">
         <is>
-          <t>SSR Light Engine</t>
+          <t>Maintenance Train</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -33085,7 +33085,7 @@
       <c r="B223" t="inlineStr"/>
       <c r="C223" t="inlineStr">
         <is>
-          <t>PN Grain/Wagon Transfer</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -33719,7 +33719,7 @@
       <c r="B260" t="inlineStr"/>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Watco Light Engine Movement</t>
+          <t>Watco Trip Train</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -34949,7 +34949,7 @@
       <c r="B329" t="inlineStr"/>
       <c r="C329" t="inlineStr">
         <is>
-          <t>QUBE Containerised Freight</t>
+          <t>QUBE Maryvale Paper Train</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -36113,7 +36113,7 @@
       <c r="B395" t="inlineStr"/>
       <c r="C395" t="inlineStr">
         <is>
-          <t>QUBE Container Train</t>
+          <t>QUBE Light Engine</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -37351,7 +37351,7 @@
       <c r="B466" t="inlineStr"/>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -37567,7 +37567,7 @@
       <c r="B478" t="inlineStr"/>
       <c r="C478" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -41347,7 +41347,7 @@
       <c r="B690" t="inlineStr"/>
       <c r="C690" t="inlineStr">
         <is>
-          <t>PN Trip Train</t>
+          <t>PN Trip Train, ex 8124</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
@@ -42923,7 +42923,7 @@
       <c r="B778" t="inlineStr"/>
       <c r="C778" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D778" t="inlineStr">
@@ -47695,7 +47695,7 @@
       <c r="B1046" t="inlineStr"/>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>Northeast Line BG Service</t>
         </is>
       </c>
       <c r="D1046" t="inlineStr">
@@ -48033,7 +48033,7 @@
       <c r="B1065" t="inlineStr"/>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>Northern Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1065" t="inlineStr">
@@ -50999,7 +50999,7 @@
       <c r="B1231" t="inlineStr"/>
       <c r="C1231" t="inlineStr">
         <is>
-          <t>Northeast BG Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1231" t="inlineStr">
@@ -51693,7 +51693,7 @@
       <c r="B1270" t="inlineStr"/>
       <c r="C1270" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1270" t="inlineStr">
@@ -52053,7 +52053,7 @@
       <c r="B1290" t="inlineStr"/>
       <c r="C1290" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1290" t="inlineStr">
@@ -56225,7 +56225,7 @@
       <c r="B1532" t="inlineStr"/>
       <c r="C1532" t="inlineStr">
         <is>
-          <t>QUBE Containerised Freight</t>
+          <t>QUBE Containerised Cotton</t>
         </is>
       </c>
       <c r="D1532" t="inlineStr">
@@ -57533,7 +57533,7 @@
       <c r="B1606" t="inlineStr"/>
       <c r="C1606" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1606" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -814,7 +814,7 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1138,7 +1138,7 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NorthEast BG Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1710,7 +1710,7 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>North Eastern Line BG Service</t>
+          <t>North East Line BG Service</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2552,7 +2552,7 @@
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>North East Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -2912,7 +2912,7 @@
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>North East SG Line Service</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -3052,7 +3052,7 @@
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>QUBE Light Engine</t>
+          <t>QUBE Containerised Freight</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -5660,7 +5660,7 @@
       <c r="B296" t="inlineStr"/>
       <c r="C296" t="inlineStr">
         <is>
-          <t>PN Cement</t>
+          <t>PN Cement - RailTrain Crewed</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -6268,7 +6268,7 @@
       <c r="B330" t="inlineStr"/>
       <c r="C330" t="inlineStr">
         <is>
-          <t>PN Garbage Train</t>
+          <t>PN Trip Train</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -6610,7 +6610,7 @@
       <c r="B349" t="inlineStr"/>
       <c r="C349" t="inlineStr">
         <is>
-          <t>PN Trip Train</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -6664,7 +6664,7 @@
       <c r="B352" t="inlineStr"/>
       <c r="C352" t="inlineStr">
         <is>
-          <t>PN Grain Shuttle</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -7576,7 +7576,11 @@
         </is>
       </c>
       <c r="B405" t="inlineStr"/>
-      <c r="C405" t="inlineStr"/>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>PN Intermodal</t>
+        </is>
+      </c>
       <c r="D405" t="inlineStr">
         <is>
           <t>2026-04-22 10:44:54</t>
@@ -10034,7 +10038,7 @@
       <c r="B553" t="inlineStr"/>
       <c r="C553" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
@@ -10070,7 +10074,7 @@
       <c r="B555" t="inlineStr"/>
       <c r="C555" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
@@ -10574,7 +10578,7 @@
       <c r="B583" t="inlineStr"/>
       <c r="C583" t="inlineStr">
         <is>
-          <t>SSR Shunter</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
@@ -10840,7 +10844,7 @@
       <c r="B598" t="inlineStr"/>
       <c r="C598" t="inlineStr">
         <is>
-          <t>SCT Aurizon Loading Transfer</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
@@ -10858,7 +10862,7 @@
       <c r="B599" t="inlineStr"/>
       <c r="C599" t="inlineStr">
         <is>
-          <t>SCT Containerised Freight</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
@@ -11270,7 +11274,7 @@
       <c r="B622" t="inlineStr"/>
       <c r="C622" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer</t>
+          <t>NSW TrainLink Xplorer</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
@@ -11342,7 +11346,7 @@
       <c r="B626" t="inlineStr"/>
       <c r="C626" t="inlineStr">
         <is>
-          <t>SCT Containerised Freight</t>
+          <t>SCT Wine Train</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
@@ -11500,7 +11504,7 @@
       <c r="B635" t="inlineStr"/>
       <c r="C635" t="inlineStr">
         <is>
-          <t>SSR Cement</t>
+          <t>SSR Cement Clinker</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
@@ -11518,7 +11522,7 @@
       <c r="B636" t="inlineStr"/>
       <c r="C636" t="inlineStr">
         <is>
-          <t>SSR Containerised Freight</t>
+          <t>SSR Wagon Transfer</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
@@ -11860,7 +11864,7 @@
       <c r="B655" t="inlineStr"/>
       <c r="C655" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Containerised Freight</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
@@ -11960,7 +11964,7 @@
       <c r="B661" t="inlineStr"/>
       <c r="C661" t="inlineStr">
         <is>
-          <t>SCT Steel Shunt / Wine Train</t>
+          <t>SCT Light Engine Movement</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
@@ -12692,7 +12696,7 @@
       <c r="B703" t="inlineStr"/>
       <c r="C703" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Hunter Railcar Transfer</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
@@ -12764,7 +12768,7 @@
       <c r="B707" t="inlineStr"/>
       <c r="C707" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
@@ -12782,7 +12786,7 @@
       <c r="B708" t="inlineStr"/>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
@@ -13200,7 +13204,7 @@
       <c r="B733" t="inlineStr"/>
       <c r="C733" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
@@ -13648,7 +13652,7 @@
       <c r="B759" t="inlineStr"/>
       <c r="C759" t="inlineStr">
         <is>
-          <t>SSR Loaded Manildra Grain</t>
+          <t>SSR Manildra Grain Banker</t>
         </is>
       </c>
       <c r="D759" t="inlineStr">
@@ -14482,7 +14486,7 @@
       <c r="B806" t="inlineStr"/>
       <c r="C806" t="inlineStr">
         <is>
-          <t>PN Infrabuild Steel</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D806" t="inlineStr">
@@ -15000,7 +15004,7 @@
       <c r="B835" t="inlineStr"/>
       <c r="C835" t="inlineStr">
         <is>
-          <t>NR39</t>
+          <t>PN Containerised Freight</t>
         </is>
       </c>
       <c r="D835" t="inlineStr">
@@ -16272,7 +16276,7 @@
       <c r="B907" t="inlineStr"/>
       <c r="C907" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>PN Freight</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
@@ -16812,7 +16816,7 @@
       <c r="B941" t="inlineStr"/>
       <c r="C941" t="inlineStr">
         <is>
-          <t>SRS-Crawfords Container Train</t>
+          <t>SRS Light Engine</t>
         </is>
       </c>
       <c r="D941" t="inlineStr">
@@ -16912,7 +16916,7 @@
       <c r="B947" t="inlineStr"/>
       <c r="C947" t="inlineStr">
         <is>
-          <t>Aurizon Cockburn Cement - Lime and Cement Train</t>
+          <t>Aurizon Cockburn Cement - Empty Lime and Cement Train</t>
         </is>
       </c>
       <c r="D947" t="inlineStr">
@@ -17258,7 +17262,7 @@
       <c r="B968" t="inlineStr"/>
       <c r="C968" t="inlineStr">
         <is>
-          <t>QUBE Containerised Cotton</t>
+          <t>QUBE Containerised Freight</t>
         </is>
       </c>
       <c r="D968" t="inlineStr">
@@ -18852,7 +18856,7 @@
       <c r="B1059" t="inlineStr"/>
       <c r="C1059" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1059" t="inlineStr">
@@ -19228,7 +19232,7 @@
       <c r="B1081" t="inlineStr"/>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>South Coast Service</t>
+          <t>Southern Highlands Service</t>
         </is>
       </c>
       <c r="D1081" t="inlineStr">
@@ -19592,7 +19596,7 @@
       <c r="B1103" t="inlineStr"/>
       <c r="C1103" t="inlineStr">
         <is>
-          <t>PN Empty Aggregate</t>
+          <t>PN Minerals</t>
         </is>
       </c>
       <c r="D1103" t="inlineStr">
@@ -28434,7 +28438,7 @@
       <c r="B1596" t="inlineStr"/>
       <c r="C1596" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1596" t="inlineStr">
@@ -28592,7 +28596,7 @@
       <c r="B1605" t="inlineStr"/>
       <c r="C1605" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1605" t="inlineStr">
@@ -28772,7 +28776,7 @@
       <c r="B1615" t="inlineStr"/>
       <c r="C1615" t="inlineStr">
         <is>
-          <t>ORA Shunter</t>
+          <t>ORA Coal</t>
         </is>
       </c>
       <c r="D1615" t="inlineStr">
@@ -29479,7 +29483,7 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PN Light Engine</t>
+          <t>PN Containerised Freight</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -29509,7 +29513,11 @@
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PN Intermodal</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>2026-04-22 10:44:54</t>
@@ -31051,7 +31059,7 @@
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PN Grain Shuttle</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -31263,7 +31271,7 @@
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -32385,7 +32393,7 @@
       <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
         <is>
-          <t>PN Empty Aggregate</t>
+          <t>PN Minerals</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -32453,7 +32461,7 @@
       <c r="B187" t="inlineStr"/>
       <c r="C187" t="inlineStr">
         <is>
-          <t>SCT Containerised Freight</t>
+          <t>SCT Wine Train</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -34007,7 +34015,7 @@
       <c r="B276" t="inlineStr"/>
       <c r="C276" t="inlineStr">
         <is>
-          <t>NorthEast BG Service</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -35703,7 +35711,7 @@
       <c r="B372" t="inlineStr"/>
       <c r="C372" t="inlineStr">
         <is>
-          <t>ORA Shunter</t>
+          <t>ORA Coal</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -35969,7 +35977,7 @@
       <c r="B387" t="inlineStr"/>
       <c r="C387" t="inlineStr">
         <is>
-          <t>QUBE Light Engine</t>
+          <t>QUBE Containerised Freight</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -36131,7 +36139,7 @@
       <c r="B396" t="inlineStr"/>
       <c r="C396" t="inlineStr">
         <is>
-          <t>SSR Containerised Freight</t>
+          <t>SSR Wagon Transfer</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -40783,7 +40791,7 @@
       <c r="B658" t="inlineStr"/>
       <c r="C658" t="inlineStr">
         <is>
-          <t>PN Intermodal</t>
+          <t>PN Freight</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
@@ -41113,7 +41121,7 @@
       <c r="B677" t="inlineStr"/>
       <c r="C677" t="inlineStr">
         <is>
-          <t>SSR Loaded Manildra Grain</t>
+          <t>SSR Manildra Grain Banker</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
@@ -43595,7 +43603,7 @@
       <c r="B816" t="inlineStr"/>
       <c r="C816" t="inlineStr">
         <is>
-          <t>SCT Containerised Freight</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D816" t="inlineStr">
@@ -46055,7 +46063,7 @@
       <c r="B954" t="inlineStr"/>
       <c r="C954" t="inlineStr">
         <is>
-          <t>NR39</t>
+          <t>PN Containerised Freight</t>
         </is>
       </c>
       <c r="D954" t="inlineStr">
@@ -48141,7 +48149,7 @@
       <c r="B1071" t="inlineStr"/>
       <c r="C1071" t="inlineStr">
         <is>
-          <t>NSW Trainlink Xplorer</t>
+          <t>NSW TrainLink Xplorer</t>
         </is>
       </c>
       <c r="D1071" t="inlineStr">
@@ -48574,7 +48582,7 @@
       <c r="B1095" t="inlineStr"/>
       <c r="C1095" t="inlineStr">
         <is>
-          <t>Southern Highlands Service</t>
+          <t>Bathurst Bullet</t>
         </is>
       </c>
       <c r="D1095" t="inlineStr">
@@ -48808,7 +48816,7 @@
       <c r="B1108" t="inlineStr"/>
       <c r="C1108" t="inlineStr">
         <is>
-          <t>North Eastern Line BG Service</t>
+          <t>North East Line BG Service</t>
         </is>
       </c>
       <c r="D1108" t="inlineStr">
@@ -49535,7 +49543,7 @@
       <c r="B1149" t="inlineStr"/>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>SCT Aurizon Loading Transfer</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D1149" t="inlineStr">
@@ -49841,7 +49849,7 @@
       <c r="B1166" t="inlineStr"/>
       <c r="C1166" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Hunter Railcar Transfer</t>
         </is>
       </c>
       <c r="D1166" t="inlineStr">
@@ -50093,7 +50101,7 @@
       <c r="B1180" t="inlineStr"/>
       <c r="C1180" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1180" t="inlineStr">
@@ -50287,7 +50295,7 @@
       <c r="B1191" t="inlineStr"/>
       <c r="C1191" t="inlineStr">
         <is>
-          <t>PN Garbage Train</t>
+          <t>PN Trip Train</t>
         </is>
       </c>
       <c r="D1191" t="inlineStr">
@@ -50675,7 +50683,7 @@
       <c r="B1213" t="inlineStr"/>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>SSR Cement</t>
+          <t>SSR Cement Clinker</t>
         </is>
       </c>
       <c r="D1213" t="inlineStr">
@@ -50729,7 +50737,7 @@
       <c r="B1216" t="inlineStr"/>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>PN Infrabuild Steel</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D1216" t="inlineStr">
@@ -51017,7 +51025,7 @@
       <c r="B1232" t="inlineStr"/>
       <c r="C1232" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>North East SG Line Service</t>
         </is>
       </c>
       <c r="D1232" t="inlineStr">
@@ -51693,7 +51701,7 @@
       <c r="B1270" t="inlineStr"/>
       <c r="C1270" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1270" t="inlineStr">
@@ -52179,7 +52187,7 @@
       <c r="B1297" t="inlineStr"/>
       <c r="C1297" t="inlineStr">
         <is>
-          <t>PN Cement</t>
+          <t>PN Cement - RailTrain Crewed</t>
         </is>
       </c>
       <c r="D1297" t="inlineStr">
@@ -52463,7 +52471,7 @@
       <c r="B1313" t="inlineStr"/>
       <c r="C1313" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1313" t="inlineStr">
@@ -52949,7 +52957,7 @@
       <c r="B1340" t="inlineStr"/>
       <c r="C1340" t="inlineStr">
         <is>
-          <t>North East Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D1340" t="inlineStr">
@@ -52985,7 +52993,7 @@
       <c r="B1342" t="inlineStr"/>
       <c r="C1342" t="inlineStr">
         <is>
-          <t>Empty Car Provisioning</t>
+          <t>Western Line Service</t>
         </is>
       </c>
       <c r="D1342" t="inlineStr">
@@ -53729,7 +53737,7 @@
       <c r="B1384" t="inlineStr"/>
       <c r="C1384" t="inlineStr">
         <is>
-          <t>PN Trip Train</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D1384" t="inlineStr">
@@ -54663,7 +54671,7 @@
       <c r="B1441" t="inlineStr"/>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>SSR Loaded Aggregates</t>
+          <t>SSR Empty Aggregates</t>
         </is>
       </c>
       <c r="D1441" t="inlineStr">
@@ -54807,7 +54815,7 @@
       <c r="B1449" t="inlineStr"/>
       <c r="C1449" t="inlineStr">
         <is>
-          <t>SSR Shunter</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1449" t="inlineStr">
@@ -54987,7 +54995,7 @@
       <c r="B1459" t="inlineStr"/>
       <c r="C1459" t="inlineStr">
         <is>
-          <t>SCT Steel Shunt / Wine Train</t>
+          <t>SCT Light Engine Movement</t>
         </is>
       </c>
       <c r="D1459" t="inlineStr">
@@ -55163,7 +55171,7 @@
       <c r="B1469" t="inlineStr"/>
       <c r="C1469" t="inlineStr">
         <is>
-          <t>Empty Car Transfer</t>
+          <t>Hunter Line Service</t>
         </is>
       </c>
       <c r="D1469" t="inlineStr">
@@ -55965,7 +55973,7 @@
       <c r="B1516" t="inlineStr"/>
       <c r="C1516" t="inlineStr">
         <is>
-          <t>SRS-Crawfords Container Train</t>
+          <t>SRS Light Engine</t>
         </is>
       </c>
       <c r="D1516" t="inlineStr">
@@ -56047,7 +56055,7 @@
       <c r="B1521" t="inlineStr"/>
       <c r="C1521" t="inlineStr">
         <is>
-          <t>Aurizon Cockburn Cement - Lime and Cement Train</t>
+          <t>Aurizon Cockburn Cement - Empty Lime and Cement Train</t>
         </is>
       </c>
       <c r="D1521" t="inlineStr">
@@ -56225,7 +56233,7 @@
       <c r="B1532" t="inlineStr"/>
       <c r="C1532" t="inlineStr">
         <is>
-          <t>QUBE Containerised Cotton</t>
+          <t>QUBE Containerised Freight</t>
         </is>
       </c>
       <c r="D1532" t="inlineStr">
@@ -56543,7 +56551,7 @@
       <c r="B1551" t="inlineStr"/>
       <c r="C1551" t="inlineStr">
         <is>
-          <t>South Coast Service</t>
+          <t>Southern Highlands Service</t>
         </is>
       </c>
       <c r="D1551" t="inlineStr">
@@ -57569,7 +57577,7 @@
       <c r="B1608" t="inlineStr"/>
       <c r="C1608" t="inlineStr">
         <is>
-          <t>NSW TrainLink XPT</t>
+          <t>NSW Trainlink XPT</t>
         </is>
       </c>
       <c r="D1608" t="inlineStr">

--- a/downloads/loco_database.xlsx
+++ b/downloads/loco_database.xlsx
@@ -1656,7 +1656,7 @@
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2138,7 +2138,7 @@
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>V/Line Football Special via Werribee</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5894,7 +5894,7 @@
       <c r="B309" t="inlineStr"/>
       <c r="C309" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -6880,7 +6880,7 @@
       <c r="B364" t="inlineStr"/>
       <c r="C364" t="inlineStr">
         <is>
-          <t>PN Grain via Greta TSF</t>
+          <t>PN Grain Shuttle</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -8692,7 +8692,7 @@
       <c r="B472" t="inlineStr"/>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Copper</t>
+          <t>Aurizon Empty Copper</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -8746,7 +8746,7 @@
       <c r="B475" t="inlineStr"/>
       <c r="C475" t="inlineStr">
         <is>
-          <t>SCT Sadleirs Transfer</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -8926,7 +8926,7 @@
       <c r="B485" t="inlineStr"/>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Ore</t>
+          <t>Aurizon Empty Ore</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -10038,7 +10038,7 @@
       <c r="B553" t="inlineStr"/>
       <c r="C553" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
@@ -11738,7 +11738,7 @@
       <c r="B648" t="inlineStr"/>
       <c r="C648" t="inlineStr">
         <is>
-          <t>PN Containerised Freight</t>
+          <t>PN Wagon Transfer</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
@@ -11896,7 +11896,7 @@
       <c r="B657" t="inlineStr"/>
       <c r="C657" t="inlineStr">
         <is>
-          <t>G539</t>
+          <t>PN Containerised Freight</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
@@ -12858,7 +12858,7 @@
       <c r="B712" t="inlineStr"/>
       <c r="C712" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
@@ -13932,7 +13932,7 @@
       <c r="B775" t="inlineStr"/>
       <c r="C775" t="inlineStr">
         <is>
-          <t>SSR Grain</t>
+          <t>SSR Weston Milling Shunter</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
@@ -15230,7 +15230,7 @@
       <c r="B848" t="inlineStr"/>
       <c r="C848" t="inlineStr">
         <is>
-          <t>PN Infrabuild Steel via Lithgow</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
@@ -15334,7 +15334,7 @@
       <c r="B854" t="inlineStr"/>
       <c r="C854" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Minerals</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
@@ -15478,7 +15478,7 @@
       <c r="B862" t="inlineStr"/>
       <c r="C862" t="inlineStr">
         <is>
-          <t>PN Containerised Freight</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D862" t="inlineStr">
@@ -16096,7 +16096,7 @@
       <c r="B897" t="inlineStr"/>
       <c r="C897" t="inlineStr">
         <is>
-          <t>PN Containerised Freight</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D897" t="inlineStr">
@@ -16276,7 +16276,7 @@
       <c r="B907" t="inlineStr"/>
       <c r="C907" t="inlineStr">
         <is>
-          <t>PN Freight</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
@@ -16762,7 +16762,7 @@
       <c r="B938" t="inlineStr"/>
       <c r="C938" t="inlineStr">
         <is>
-          <t>Watco Light Engine</t>
+          <t>Watco Light Engine Movement</t>
         </is>
       </c>
       <c r="D938" t="inlineStr">
@@ -16816,7 +16816,7 @@
       <c r="B941" t="inlineStr"/>
       <c r="C941" t="inlineStr">
         <is>
-          <t>SRS Light Engine</t>
+          <t>SRS-Crawfords Container Train</t>
         </is>
       </c>
       <c r="D941" t="inlineStr">
@@ -17008,7 +17008,7 @@
       <c r="B953" t="inlineStr"/>
       <c r="C953" t="inlineStr">
         <is>
-          <t>Aurizon Empty Sulphur Containers</t>
+          <t>Aurizon Loaded Sulphur Containers</t>
         </is>
       </c>
       <c r="D953" t="inlineStr">
@@ -17026,7 +17026,7 @@
       <c r="B954" t="inlineStr"/>
       <c r="C954" t="inlineStr">
         <is>
-          <t>Gold Valley Iron Ore</t>
+          <t>Aurizon Lynas Containers</t>
         </is>
       </c>
       <c r="D954" t="inlineStr">
@@ -17622,7 +17622,7 @@
       <c r="B988" t="inlineStr"/>
       <c r="C988" t="inlineStr">
         <is>
-          <t>QUBE BlueScope Steel Transfer</t>
+          <t>QUBE BlueScope Steel</t>
         </is>
       </c>
       <c r="D988" t="inlineStr">
@@ -18838,7 +18838,7 @@
       <c r="B1058" t="inlineStr"/>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Cement</t>
         </is>
       </c>
       <c r="D1058" t="inlineStr">
@@ -18856,7 +18856,7 @@
       <c r="B1059" t="inlineStr"/>
       <c r="C1059" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1059" t="inlineStr">
@@ -19124,7 +19124,7 @@
       <c r="B1075" t="inlineStr"/>
       <c r="C1075" t="inlineStr">
         <is>
-          <t>South Coast Service</t>
+          <t>South Coast Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1075" t="inlineStr">
@@ -29623,7 +29623,7 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Ore</t>
+          <t>Aurizon Empty Ore</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -29815,7 +29815,7 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Minerals</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -31077,7 +31077,7 @@
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Western Line Service</t>
+          <t>South Western Line Service</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -31289,7 +31289,7 @@
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Watco Light Engine</t>
+          <t>Watco Light Engine Movement</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -32009,7 +32009,7 @@
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr">
         <is>
-          <t>PN Grain via Greta TSF</t>
+          <t>PN Grain Shuttle</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -40633,7 +40633,7 @@
       <c r="B649" t="inlineStr"/>
       <c r="C649" t="inlineStr">
         <is>
-          <t>QUBE BlueScope Steel Transfer</t>
+          <t>QUBE BlueScope Steel</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
@@ -40705,7 +40705,7 @@
       <c r="B653" t="inlineStr"/>
       <c r="C653" t="inlineStr">
         <is>
-          <t>PN Containerised Freight</t>
+          <t>PN Wagon Transfer</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
@@ -40773,7 +40773,7 @@
       <c r="B657" t="inlineStr"/>
       <c r="C657" t="inlineStr">
         <is>
-          <t>PN Containerised Freight</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
@@ -40791,7 +40791,7 @@
       <c r="B658" t="inlineStr"/>
       <c r="C658" t="inlineStr">
         <is>
-          <t>PN Freight</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
@@ -41499,7 +41499,7 @@
       <c r="B698" t="inlineStr"/>
       <c r="C698" t="inlineStr">
         <is>
-          <t>G539</t>
+          <t>PN Containerised Freight</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
@@ -41787,7 +41787,7 @@
       <c r="B714" t="inlineStr"/>
       <c r="C714" t="inlineStr">
         <is>
-          <t>PN Light Engine Movement</t>
+          <t>PN Grain</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
@@ -45733,7 +45733,7 @@
       <c r="B935" t="inlineStr"/>
       <c r="C935" t="inlineStr">
         <is>
-          <t>PN Infrabuild Steel via Lithgow</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D935" t="inlineStr">
@@ -46699,7 +46699,7 @@
       <c r="B990" t="inlineStr"/>
       <c r="C990" t="inlineStr">
         <is>
-          <t>Gold Valley Iron Ore</t>
+          <t>Aurizon Lynas Containers</t>
         </is>
       </c>
       <c r="D990" t="inlineStr">
@@ -47595,7 +47595,7 @@
       <c r="B1040" t="inlineStr"/>
       <c r="C1040" t="inlineStr">
         <is>
-          <t>South Western Line Service</t>
+          <t>V/Line Football Special via Werribee</t>
         </is>
       </c>
       <c r="D1040" t="inlineStr">
@@ -49615,7 +49615,7 @@
       <c r="B1153" t="inlineStr"/>
       <c r="C1153" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Cement</t>
         </is>
       </c>
       <c r="D1153" t="inlineStr">
@@ -49867,7 +49867,7 @@
       <c r="B1167" t="inlineStr"/>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>PN Containerised Freight</t>
+          <t>PN Intermodal</t>
         </is>
       </c>
       <c r="D1167" t="inlineStr">
@@ -51593,7 +51593,7 @@
       <c r="B1264" t="inlineStr"/>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>SCT Sadleirs Transfer</t>
+          <t>SCT Intermodal</t>
         </is>
       </c>
       <c r="D1264" t="inlineStr">
@@ -52313,7 +52313,7 @@
       <c r="B1304" t="inlineStr"/>
       <c r="C1304" t="inlineStr">
         <is>
-          <t>Hunter Line Service</t>
+          <t>Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1304" t="inlineStr">
@@ -52471,7 +52471,7 @@
       <c r="B1313" t="inlineStr"/>
       <c r="C1313" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1313" t="inlineStr">
@@ -54205,7 +54205,7 @@
       <c r="B1412" t="inlineStr"/>
       <c r="C1412" t="inlineStr">
         <is>
-          <t>Aurizon Loaded Copper</t>
+          <t>Aurizon Empty Copper</t>
         </is>
       </c>
       <c r="D1412" t="inlineStr">
@@ -54671,7 +54671,7 @@
       <c r="B1441" t="inlineStr"/>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>SSR Empty Aggregates</t>
+          <t>SSR Loaded Aggregates</t>
         </is>
       </c>
       <c r="D1441" t="inlineStr">
@@ -55437,7 +55437,7 @@
       <c r="B1484" t="inlineStr"/>
       <c r="C1484" t="inlineStr">
         <is>
-          <t>SSR Grain</t>
+          <t>SSR Weston Milling Shunter</t>
         </is>
       </c>
       <c r="D1484" t="inlineStr">
@@ -55973,7 +55973,7 @@
       <c r="B1516" t="inlineStr"/>
       <c r="C1516" t="inlineStr">
         <is>
-          <t>SRS Light Engine</t>
+          <t>SRS-Crawfords Container Train</t>
         </is>
       </c>
       <c r="D1516" t="inlineStr">
@@ -56119,7 +56119,7 @@
       <c r="B1525" t="inlineStr"/>
       <c r="C1525" t="inlineStr">
         <is>
-          <t>Aurizon Empty Sulphur Containers</t>
+          <t>Aurizon Loaded Sulphur Containers</t>
         </is>
       </c>
       <c r="D1525" t="inlineStr">
@@ -56533,7 +56533,7 @@
       <c r="B1550" t="inlineStr"/>
       <c r="C1550" t="inlineStr">
         <is>
-          <t>South Coast Service</t>
+          <t>South Coast Empty Car Transfer</t>
         </is>
       </c>
       <c r="D1550" t="inlineStr">
